--- a/Data/output/IND Stroke Position.xlsx
+++ b/Data/output/IND Stroke Position.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4089" uniqueCount="691">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4011" uniqueCount="678">
   <si>
     <t>Direct_or_Indirect</t>
   </si>
@@ -49,2044 +49,2005 @@
     <t>nan</t>
   </si>
   <si>
-    <t>[np.float64(686.1599953224687), np.float64(4.443931640764291)]</t>
-  </si>
-  <si>
-    <t>[np.float64(447.80637850139726), np.float64(75.5160520896683)]</t>
-  </si>
-  <si>
-    <t>[np.float64(784.4506332596187), np.float64(12.770159521060947)]</t>
-  </si>
-  <si>
-    <t>[np.float64(461.08529027737666), np.float64(54.596605402562204)]</t>
-  </si>
-  <si>
-    <t>[np.float64(88.90065652445345), np.float64(-95.87569542573813)]</t>
-  </si>
-  <si>
-    <t>[np.float64(152.88018077880528), np.float64(65.6438780363907)]</t>
-  </si>
-  <si>
-    <t>[np.float64(838.7304213843133), np.float64(-70.01336852185591)]</t>
-  </si>
-  <si>
-    <t>[np.float64(460.9550277117378), np.float64(84.20128623985036)]</t>
-  </si>
-  <si>
-    <t>[np.float64(710.5902285275778), np.float64(43.20913729773042)]</t>
-  </si>
-  <si>
-    <t>[np.float64(991.7081369509273), np.float64(39.620305175382526)]</t>
-  </si>
-  <si>
-    <t>[np.float64(180.48749426628308), np.float64(80.82513244910149)]</t>
-  </si>
-  <si>
-    <t>[np.float64(400.7055889284327), np.float64(75.1978877744053)]</t>
-  </si>
-  <si>
-    <t>[np.float64(465.98140259342637), np.float64(-88.09202704272856)]</t>
-  </si>
-  <si>
-    <t>[np.float64(33.22274781673518), np.float64(76.00642587548828)]</t>
-  </si>
-  <si>
-    <t>[np.float64(125.85709276635504), np.float64(51.24100995095381)]</t>
-  </si>
-  <si>
-    <t>[np.float64(873.1365973154686), np.float64(64.59588454562933)]</t>
-  </si>
-  <si>
-    <t>[np.float64(938.3879099739565), np.float64(-83.54085540294633)]</t>
-  </si>
-  <si>
-    <t>[np.float64(585.1040658711323), np.float64(3.4954557862872093)]</t>
-  </si>
-  <si>
-    <t>[np.float64(516.2252777039635), np.float64(37.8244035540574)]</t>
-  </si>
-  <si>
-    <t>[np.float64(631.1001985643205), np.float64(86.15848729289314)]</t>
-  </si>
-  <si>
-    <t>[np.float64(327.53957313781734), np.float64(16.937589837804225)]</t>
-  </si>
-  <si>
-    <t>[np.float64(161.05973097195036), np.float64(58.39943549295725)]</t>
-  </si>
-  <si>
-    <t>[np.float64(525.9500816696642), np.float64(9.182784203640182)]</t>
-  </si>
-  <si>
-    <t>[np.float64(611.8458577053882), np.float64(64.78892359455907)]</t>
-  </si>
-  <si>
-    <t>[np.float64(789.2624719965117), np.float64(-89.91290218282265)]</t>
-  </si>
-  <si>
-    <t>[np.float64(774.5723343048704), np.float64(87.29034230466831)]</t>
-  </si>
-  <si>
-    <t>[np.float64(460.5233497251474), np.float64(44.918967215149536)]</t>
-  </si>
-  <si>
-    <t>[np.float64(912.4457194309728), np.float64(-74.91583111866345)]</t>
-  </si>
-  <si>
-    <t>[np.float64(951.629732210634), np.float64(37.194286605865045)]</t>
-  </si>
-  <si>
-    <t>[np.float64(863.2960107884046), np.float64(25.532939811727573)]</t>
-  </si>
-  <si>
-    <t>[np.float64(868.3425272310466), np.float64(31.215919010293533)]</t>
-  </si>
-  <si>
-    <t>[np.float64(461.0395861635143), np.float64(0.867100609053324)]</t>
-  </si>
-  <si>
-    <t>[np.float64(306.33062003810574), np.float64(29.773418489823342)]</t>
-  </si>
-  <si>
-    <t>[np.float64(116.19416785634806), np.float64(-93.91620123568572)]</t>
-  </si>
-  <si>
-    <t>[np.float64(36.576825610690534), np.float64(18.462745797693643)]</t>
-  </si>
-  <si>
-    <t>[np.float64(875.8697248883456), np.float64(98.41251257575576)]</t>
-  </si>
-  <si>
-    <t>[np.float64(507.1990970251855), np.float64(67.817490847333)]</t>
-  </si>
-  <si>
-    <t>[np.float64(775.2201250200096), np.float64(29.296752841927173)]</t>
-  </si>
-  <si>
-    <t>[np.float64(259.40684942623204), np.float64(66.51234560779463)]</t>
-  </si>
-  <si>
-    <t>[np.float64(479.28835598667695), np.float64(51.438641526095694)]</t>
-  </si>
-  <si>
-    <t>[np.float64(939.7511484458548), np.float64(-86.25353447562757)]</t>
-  </si>
-  <si>
-    <t>[np.float64(58.2634067612563), np.float64(64.27694306167822)]</t>
-  </si>
-  <si>
-    <t>[np.float64(986.0522547500162), np.float64(92.32667277111167)]</t>
-  </si>
-  <si>
-    <t>[np.float64(374.8823081497136), np.float64(-90.31516938193718)]</t>
-  </si>
-  <si>
-    <t>[np.float64(943.8632303467242), np.float64(32.362763591220045)]</t>
-  </si>
-  <si>
-    <t>[np.float64(172.84473002271994), np.float64(18.96743026981271)]</t>
-  </si>
-  <si>
-    <t>[np.float64(430.7369518268165), np.float64(74.21377422092769)]</t>
-  </si>
-  <si>
-    <t>[np.float64(735.6227206555978), np.float64(42.97044564461564)]</t>
-  </si>
-  <si>
-    <t>[np.float64(26.59862942127411), np.float64(-82.61685755521732)]</t>
-  </si>
-  <si>
-    <t>[np.float64(567.6364547197517), np.float64(-92.80121151330087)]</t>
-  </si>
-  <si>
-    <t>[np.float64(662.7512633108506), np.float64(18.325073300519463)]</t>
-  </si>
-  <si>
-    <t>[np.float64(909.3661129213989), np.float64(-90.26175245931134)]</t>
-  </si>
-  <si>
-    <t>[np.float64(115.28935136912477), np.float64(79.32112532805579)]</t>
-  </si>
-  <si>
-    <t>[np.float64(974.8317389301967), np.float64(-58.070599203292694)]</t>
-  </si>
-  <si>
-    <t>[np.float64(71.55128377714392), np.float64(85.9650738770844)]</t>
-  </si>
-  <si>
-    <t>[np.float64(788.2872590900113), np.float64(10.580245184931215)]</t>
-  </si>
-  <si>
-    <t>[np.float64(822.1251609128354), np.float64(79.23729443437273)]</t>
-  </si>
-  <si>
-    <t>[np.float64(581.580972434639), np.float64(33.99876064974501)]</t>
-  </si>
-  <si>
-    <t>[np.float64(319.99481304461807), np.float64(62.96056766136829)]</t>
-  </si>
-  <si>
-    <t>[np.float64(294.33839048125463), np.float64(-84.39601404777395)]</t>
-  </si>
-  <si>
-    <t>[np.float64(49.355312842917385), np.float64(40.870408950557646)]</t>
-  </si>
-  <si>
-    <t>[np.float64(275.50980515947634), np.float64(-81.39983169867597)]</t>
-  </si>
-  <si>
-    <t>[np.float64(525.0480677060085), np.float64(-75.93775269714682)]</t>
-  </si>
-  <si>
-    <t>[np.float64(231.7905044579478), np.float64(48.240142438351086)]</t>
-  </si>
-  <si>
-    <t>[np.float64(143.83828035332758), np.float64(86.42233600389702)]</t>
-  </si>
-  <si>
-    <t>[np.float64(823.1146905860356), np.float64(38.53426639712677)]</t>
-  </si>
-  <si>
-    <t>[np.float64(513.8873180398958), np.float64(-96.68869008410425)]</t>
-  </si>
-  <si>
-    <t>[np.float64(885.015851150906), np.float64(38.610427278633296)]</t>
-  </si>
-  <si>
-    <t>[np.float64(44.927428626354235), np.float64(-59.93730335933422)]</t>
-  </si>
-  <si>
-    <t>[np.float64(600.3813668479855), np.float64(42.41658023989825)]</t>
-  </si>
-  <si>
-    <t>[np.float64(698.2236607020927), np.float64(83.38606916940299)]</t>
-  </si>
-  <si>
-    <t>[np.float64(483.7593544696258), np.float64(48.26431067449806)]</t>
-  </si>
-  <si>
-    <t>[np.float64(424.6374230785219), np.float64(71.85398438853423)]</t>
-  </si>
-  <si>
-    <t>[np.float64(866.7642355402187), np.float64(-68.93483664808242)]</t>
-  </si>
-  <si>
-    <t>[np.float64(300.30480428797404), np.float64(-83.05215184884128)]</t>
-  </si>
-  <si>
-    <t>[np.float64(939.1644261378855), np.float64(-95.50809127448072)]</t>
-  </si>
-  <si>
-    <t>[np.float64(411.57503653780816), np.float64(67.33360277487805)]</t>
-  </si>
-  <si>
-    <t>[np.float64(378.5607442410749), np.float64(35.620428251780595)]</t>
-  </si>
-  <si>
-    <t>[np.float64(988.6168635169707), np.float64(99.98901323902237)]</t>
-  </si>
-  <si>
-    <t>[np.float64(474.83744776580016), np.float64(72.24955404178402)]</t>
-  </si>
-  <si>
-    <t>[np.float64(113.44045197277109), np.float64(-61.02744883696578)]</t>
-  </si>
-  <si>
-    <t>[np.float64(19.70895986225529), np.float64(-74.05735491122974)]</t>
-  </si>
-  <si>
-    <t>[np.float64(663.4133619514137), np.float64(25.589952500642624)]</t>
-  </si>
-  <si>
-    <t>[np.float64(440.6422628397363), np.float64(10.561132558659509)]</t>
-  </si>
-  <si>
-    <t>[np.float64(119.344189804233), np.float64(65.44480235822147)]</t>
-  </si>
-  <si>
-    <t>[np.float64(927.6865474182948), np.float64(11.611864309367206)]</t>
-  </si>
-  <si>
-    <t>[np.float64(915.0521585074417), np.float64(25.326371511633724)]</t>
-  </si>
-  <si>
-    <t>[np.float64(69.5987729354991), np.float64(93.75713955346782)]</t>
-  </si>
-  <si>
-    <t>[np.float64(742.4996321104784), np.float64(17.604029131352235)]</t>
-  </si>
-  <si>
-    <t>[np.float64(580.4014866822669), np.float64(-96.06638070723395)]</t>
-  </si>
-  <si>
-    <t>[np.float64(940.2543750609925), np.float64(-88.0795753170301)]</t>
-  </si>
-  <si>
-    <t>[np.float64(924.1535240999772), np.float64(-84.40647639021068)]</t>
-  </si>
-  <si>
-    <t>[np.float64(397.5149997771519), np.float64(97.25822401248908)]</t>
-  </si>
-  <si>
-    <t>[np.float64(975.815057322641), np.float64(58.142980765887415)]</t>
-  </si>
-  <si>
-    <t>[np.float64(332.85223913047855), np.float64(98.00488207752491)]</t>
-  </si>
-  <si>
-    <t>[np.float64(431.600446932198), np.float64(-69.09481566643166)]</t>
-  </si>
-  <si>
-    <t>[np.float64(96.94851408154403), np.float64(26.748927465453747)]</t>
-  </si>
-  <si>
-    <t>[np.float64(964.9465270791139), np.float64(20.061740090141726)]</t>
-  </si>
-  <si>
-    <t>[np.float64(484.9525728303352), np.float64(74.2811232320696)]</t>
-  </si>
-  <si>
-    <t>[np.float64(424.0741715392372), np.float64(-96.12297667403224)]</t>
-  </si>
-  <si>
-    <t>[np.float64(702.5324412946662), np.float64(39.1153147788296)]</t>
-  </si>
-  <si>
-    <t>[np.float64(85.07702975166166), np.float64(54.104834626727694)]</t>
-  </si>
-  <si>
-    <t>[np.float64(342.7800259322407), np.float64(86.20107669153455)]</t>
-  </si>
-  <si>
-    <t>[np.float64(999.3416736830545), np.float64(24.453788360834025)]</t>
-  </si>
-  <si>
-    <t>[np.float64(399.210186178409), np.float64(-39.141983500715625)]</t>
-  </si>
-  <si>
-    <t>[np.float64(277.69931949425984), np.float64(-58.808183656920754)]</t>
-  </si>
-  <si>
-    <t>[np.float64(517.0653251628074), np.float64(66.88944400777663)]</t>
-  </si>
-  <si>
-    <t>[np.float64(15.750052561249618), np.float64(-57.221032438117625)]</t>
-  </si>
-  <si>
-    <t>[np.float64(374.038334469357), np.float64(-73.96975680217412)]</t>
-  </si>
-  <si>
-    <t>[np.float64(466.03011702750155), np.float64(-66.2838794381075)]</t>
-  </si>
-  <si>
-    <t>[np.float64(454.8794896751824), np.float64(68.77958598169835)]</t>
-  </si>
-  <si>
-    <t>[np.float64(577.6637446419884), np.float64(59.47053968445573)]</t>
-  </si>
-  <si>
-    <t>[np.float64(821.3555065154526), np.float64(50.26032758734965)]</t>
-  </si>
-  <si>
-    <t>[np.float64(702.7826563028029), np.float64(-81.89281194320426)]</t>
-  </si>
-  <si>
-    <t>[np.float64(347.60848100404496), np.float64(55.28025788664738)]</t>
-  </si>
-  <si>
-    <t>[np.float64(718.1958284702536), np.float64(42.82717551541765)]</t>
-  </si>
-  <si>
-    <t>[np.float64(381.964386836018), np.float64(98.52010474036967)]</t>
-  </si>
-  <si>
-    <t>[np.float64(695.1750909340254), np.float64(9.131987044636091)]</t>
-  </si>
-  <si>
-    <t>[np.float64(166.50272362818208), np.float64(-85.01284120040296)]</t>
-  </si>
-  <si>
-    <t>[np.float64(244.4271692590856), np.float64(91.30806421943302)]</t>
-  </si>
-  <si>
-    <t>[np.float64(536.1047391265269), np.float64(39.490342832048015)]</t>
-  </si>
-  <si>
-    <t>[np.float64(266.89381397456657), np.float64(20.808425005710944)]</t>
-  </si>
-  <si>
-    <t>[np.float64(241.24301547159067), np.float64(54.74063019065255)]</t>
-  </si>
-  <si>
-    <t>[np.float64(189.24829101153873), np.float64(-94.75215833808004)]</t>
-  </si>
-  <si>
-    <t>[np.float64(92.7200271316917), np.float64(-92.17628870437747)]</t>
-  </si>
-  <si>
-    <t>[np.float64(247.8609706930931), np.float64(13.660906448059933)]</t>
-  </si>
-  <si>
-    <t>[np.float64(36.32478027223407), np.float64(-95.9973995535265)]</t>
-  </si>
-  <si>
-    <t>[np.float64(482.1605784725418), np.float64(2.7503345818951033)]</t>
-  </si>
-  <si>
-    <t>[np.float64(694.6254167776694), np.float64(-36.84949013756569)]</t>
-  </si>
-  <si>
-    <t>[np.float64(484.07587741406576), np.float64(99.95851304971765)]</t>
-  </si>
-  <si>
-    <t>[np.float64(364.35092540996004), np.float64(94.26077386405382)]</t>
-  </si>
-  <si>
-    <t>[np.float64(228.37825135643942), np.float64(44.1290532989899)]</t>
-  </si>
-  <si>
-    <t>[np.float64(225.8878546066152), np.float64(97.96298069056382)]</t>
-  </si>
-  <si>
-    <t>[np.float64(155.03425699742934), np.float64(-14.771694200796361)]</t>
-  </si>
-  <si>
-    <t>[np.float64(877.969774404249), np.float64(-6.112062623824073)]</t>
-  </si>
-  <si>
-    <t>[np.float64(200.491804794794), np.float64(52.31028919156367)]</t>
-  </si>
-  <si>
-    <t>[np.float64(424.8039530042593), np.float64(74.37251941393916)]</t>
-  </si>
-  <si>
-    <t>[np.float64(172.66379968842327), np.float64(45.045215192728136)]</t>
-  </si>
-  <si>
-    <t>[np.float64(121.51681623683753), np.float64(78.1868115832834)]</t>
-  </si>
-  <si>
-    <t>[np.float64(248.1316565856676), np.float64(-98.45575681661573)]</t>
-  </si>
-  <si>
-    <t>[np.float64(919.8386463001199), np.float64(-95.78052723365002)]</t>
-  </si>
-  <si>
-    <t>[np.float64(280.9656862880323), np.float64(-72.84959691155768)]</t>
-  </si>
-  <si>
-    <t>[np.float64(140.92656913459456), np.float64(-76.86793746771194)]</t>
-  </si>
-  <si>
-    <t>[np.float64(232.6508336468016), np.float64(31.936718056113847)]</t>
-  </si>
-  <si>
-    <t>[np.float64(182.84502087537834), np.float64(55.4160417721117)]</t>
-  </si>
-  <si>
-    <t>[np.float64(299.13390070746516), np.float64(-83.35996596464096)]</t>
-  </si>
-  <si>
-    <t>[np.float64(549.9397283821282), np.float64(39.69508142280097)]</t>
-  </si>
-  <si>
-    <t>[np.float64(356.9998563330337), np.float64(11.977633710653151)]</t>
-  </si>
-  <si>
-    <t>[np.float64(380.74149273652614), np.float64(80.14841022843876)]</t>
-  </si>
-  <si>
-    <t>[np.float64(146.2433992706258), np.float64(99.58875962198655)]</t>
-  </si>
-  <si>
-    <t>[np.float64(816.1218552620378), np.float64(-20.637353802702734)]</t>
-  </si>
-  <si>
-    <t>[np.float64(233.49923521928372), np.float64(60.1871899156875)]</t>
-  </si>
-  <si>
-    <t>[np.float64(746.3265106832814), np.float64(49.50890995842232)]</t>
-  </si>
-  <si>
-    <t>[np.float64(515.2163622622171), np.float64(66.708158147814)]</t>
-  </si>
-  <si>
-    <t>[np.float64(900.2050413079508), np.float64(82.04653891653905)]</t>
-  </si>
-  <si>
-    <t>[np.float64(669.5024609154552), np.float64(94.92777280459805)]</t>
-  </si>
-  <si>
-    <t>[np.float64(457.81051602179036), np.float64(-6.595395095870529)]</t>
-  </si>
-  <si>
-    <t>[np.float64(613.5757146034869), np.float64(77.7152398592961)]</t>
-  </si>
-  <si>
-    <t>[np.float64(17.4485028725655), np.float64(85.30161792351754)]</t>
-  </si>
-  <si>
-    <t>[np.float64(748.7546470366849), np.float64(19.38033783086442)]</t>
-  </si>
-  <si>
-    <t>[np.float64(279.7852826589946), np.float64(78.36316528456683)]</t>
-  </si>
-  <si>
-    <t>[np.float64(157.9047315816756), np.float64(-91.56661180878942)]</t>
-  </si>
-  <si>
-    <t>[np.float64(278.9667374231227), np.float64(29.131859948422743)]</t>
-  </si>
-  <si>
-    <t>[np.float64(13.627260664123453), np.float64(29.123028357561424)]</t>
-  </si>
-  <si>
-    <t>[np.float64(202.18955331722245), np.float64(33.19571601217697)]</t>
-  </si>
-  <si>
-    <t>[np.float64(421.19330575413613), np.float64(-91.92043062284132)]</t>
-  </si>
-  <si>
-    <t>[np.float64(766.3514905142528), np.float64(76.38810840702058)]</t>
-  </si>
-  <si>
-    <t>[np.float64(83.59205859887497), np.float64(21.55441856844125)]</t>
-  </si>
-  <si>
-    <t>[np.float64(994.6150410400005), np.float64(14.063411423058753)]</t>
-  </si>
-  <si>
-    <t>[np.float64(788.4267923526216), np.float64(60.1171169406384)]</t>
-  </si>
-  <si>
-    <t>[np.float64(14.710728355829762), np.float64(-96.04283217177556)]</t>
-  </si>
-  <si>
-    <t>[np.float64(939.4650605997261), np.float64(-15.82953295999188)]</t>
-  </si>
-  <si>
-    <t>[np.float64(824.9087855583974), np.float64(-84.58401508373912)]</t>
-  </si>
-  <si>
-    <t>[np.float64(207.62121029122326), np.float64(99.1010196693978)]</t>
-  </si>
-  <si>
-    <t>[np.float64(415.3601008837914), np.float64(22.917994407044787)]</t>
-  </si>
-  <si>
-    <t>[np.float64(456.99003687972316), np.float64(-85.3191492491365)]</t>
-  </si>
-  <si>
-    <t>[np.float64(816.93054802288), np.float64(-39.67080338526969)]</t>
-  </si>
-  <si>
-    <t>[np.float64(701.8959746212231), np.float64(34.55915071059229)]</t>
-  </si>
-  <si>
-    <t>[np.float64(27.120229223251858), np.float64(45.93640050258787)]</t>
-  </si>
-  <si>
-    <t>[np.float64(231.9768481314256), np.float64(7.771319528495567)]</t>
-  </si>
-  <si>
-    <t>[np.float64(174.3249977992374), np.float64(4.878113277420667)]</t>
-  </si>
-  <si>
-    <t>[np.float64(847.4207773132338), np.float64(21.21205216372806)]</t>
-  </si>
-  <si>
-    <t>[np.float64(509.85412674156294), np.float64(66.4883982573144)]</t>
-  </si>
-  <si>
-    <t>[np.float64(899.6703390415896), np.float64(-94.08214614134106)]</t>
-  </si>
-  <si>
-    <t>[np.float64(562.925899655491), np.float64(28.321000667199428)]</t>
-  </si>
-  <si>
-    <t>[np.float64(381.2220339953957), np.float64(-75.28566267773974)]</t>
-  </si>
-  <si>
-    <t>[np.float64(574.0610076561816), np.float64(-95.30783753251404)]</t>
-  </si>
-  <si>
-    <t>[np.float64(260.8480132403822), np.float64(98.36602335721855)]</t>
-  </si>
-  <si>
-    <t>[np.float64(881.05053239793), np.float64(-81.70500903621803)]</t>
-  </si>
-  <si>
-    <t>[np.float64(76.72707845336014), np.float64(67.70376760846736)]</t>
-  </si>
-  <si>
-    <t>[np.float64(262.22491238348033), np.float64(93.6664049207111)]</t>
-  </si>
-  <si>
-    <t>[np.float64(755.5814703466818), np.float64(-3.5927601412095242)]</t>
-  </si>
-  <si>
-    <t>[np.float64(203.89810454330993), np.float64(38.383847957667314)]</t>
-  </si>
-  <si>
-    <t>[np.float64(848.789758852324), np.float64(65.77534583118992)]</t>
-  </si>
-  <si>
-    <t>[np.float64(705.6397719675504), np.float64(25.225554728465212)]</t>
-  </si>
-  <si>
-    <t>[np.float64(66.83119923838076), np.float64(88.26914750230338)]</t>
-  </si>
-  <si>
-    <t>[np.float64(357.42482533686314), np.float64(-95.72424824274917)]</t>
-  </si>
-  <si>
-    <t>[np.float64(469.0449844057252), np.float64(-71.39353320424743)]</t>
-  </si>
-  <si>
-    <t>[np.float64(939.0434296888637), np.float64(-5.056994730128366)]</t>
-  </si>
-  <si>
-    <t>[np.float64(134.79098348065898), np.float64(73.01459084690472)]</t>
-  </si>
-  <si>
-    <t>[np.float64(185.74356815430193), np.float64(69.04433467875154)]</t>
-  </si>
-  <si>
-    <t>[np.float64(616.1775938166551), np.float64(86.95044534394265)]</t>
-  </si>
-  <si>
-    <t>[np.float64(937.5819229589939), np.float64(-12.58134869268504)]</t>
-  </si>
-  <si>
-    <t>[np.float64(229.21777868004546), np.float64(-66.82083934883357)]</t>
-  </si>
-  <si>
-    <t>[np.float64(46.15036229187952), np.float64(96.79017009370051)]</t>
-  </si>
-  <si>
-    <t>[np.float64(516.6784159460489), np.float64(-83.10577093125582)]</t>
-  </si>
-  <si>
-    <t>[np.float64(792.2160901297063), np.float64(42.01661626448836)]</t>
-  </si>
-  <si>
-    <t>[np.float64(963.1332368951688), np.float64(5.043239941501284)]</t>
-  </si>
-  <si>
-    <t>[np.float64(450.1173648967518), np.float64(66.21544272750367)]</t>
-  </si>
-  <si>
-    <t>[np.float64(859.1597292950552), np.float64(57.16938813481741)]</t>
-  </si>
-  <si>
-    <t>[np.float64(233.1275489379815), np.float64(47.787175139484475)]</t>
-  </si>
-  <si>
-    <t>[np.float64(662.3823227575524), np.float64(96.91181837825835)]</t>
-  </si>
-  <si>
-    <t>[np.float64(384.94782509966916), np.float64(60.51465955277172)]</t>
-  </si>
-  <si>
-    <t>[np.float64(964.119460025233), np.float64(78.34242107245822)]</t>
-  </si>
-  <si>
-    <t>[np.float64(305.78132796505884), np.float64(55.00626905762985)]</t>
-  </si>
-  <si>
-    <t>[np.float64(948.093732445254), np.float64(89.4373083188191)]</t>
-  </si>
-  <si>
-    <t>[np.float64(493.9097624476681), np.float64(61.30575580703706)]</t>
-  </si>
-  <si>
-    <t>[np.float64(895.8707714492765), np.float64(28.977702630223604)]</t>
-  </si>
-  <si>
-    <t>[np.float64(949.0092104750692), np.float64(11.478956117239747)]</t>
-  </si>
-  <si>
-    <t>[np.float64(658.8933425265584), np.float64(-88.41964972279473)]</t>
-  </si>
-  <si>
-    <t>[np.float64(578.5894787593197), np.float64(51.962331315506816)]</t>
-  </si>
-  <si>
-    <t>[np.float64(995.7328112018429), np.float64(81.36425726175054)]</t>
-  </si>
-  <si>
-    <t>[np.float64(508.37952884496394), np.float64(56.79998828984782)]</t>
-  </si>
-  <si>
-    <t>[np.float64(858.5787557921298), np.float64(85.14639442398362)]</t>
-  </si>
-  <si>
-    <t>[np.float64(575.7925702885152), np.float64(46.3878499762497)]</t>
-  </si>
-  <si>
-    <t>[np.float64(727.5311095675407), np.float64(-90.99691031590507)]</t>
-  </si>
-  <si>
-    <t>[np.float64(99.67416541758334), np.float64(0.3924334792630333)]</t>
-  </si>
-  <si>
-    <t>[np.float64(321.2463165997804), np.float64(-75.21110804516738)]</t>
-  </si>
-  <si>
-    <t>[np.float64(865.7840871767966), np.float64(43.468903551008964)]</t>
-  </si>
-  <si>
-    <t>[np.float64(965.1225559315601), np.float64(58.18197283699806)]</t>
-  </si>
-  <si>
-    <t>[np.float64(842.0575452477491), np.float64(74.94572266604195)]</t>
-  </si>
-  <si>
-    <t>[np.float64(860.1447723724639), np.float64(70.9300567481157)]</t>
-  </si>
-  <si>
-    <t>[np.float64(452.97879992822254), np.float64(-57.779630763757964)]</t>
-  </si>
-  <si>
-    <t>[np.float64(975.8988295911802), np.float64(92.96777293624922)]</t>
-  </si>
-  <si>
-    <t>[np.float64(72.70147351103151), np.float64(-99.619616560113)]</t>
-  </si>
-  <si>
-    <t>[np.float64(175.3625095524345), np.float64(5.126541977626346)]</t>
-  </si>
-  <si>
-    <t>[np.float64(655.3576221517692), np.float64(85.46671079670787)]</t>
-  </si>
-  <si>
-    <t>[np.float64(987.6625173498389), np.float64(-84.91471562526702)]</t>
-  </si>
-  <si>
-    <t>[np.float64(276.98633570211405), np.float64(72.00688725026708)]</t>
-  </si>
-  <si>
-    <t>[np.float64(525.326636456491), np.float64(81.7568844058284)]</t>
-  </si>
-  <si>
-    <t>[np.float64(587.1835574207888), np.float64(57.07289364549999)]</t>
-  </si>
-  <si>
-    <t>[np.float64(542.9080523743298), np.float64(18.128343928215543)]</t>
-  </si>
-  <si>
-    <t>[np.float64(402.08556692777586), np.float64(99.23927214619556)]</t>
-  </si>
-  <si>
-    <t>[np.float64(692.4818662099293), np.float64(1.6363352900218757)]</t>
-  </si>
-  <si>
-    <t>[np.float64(938.8096541303594), np.float64(62.09833576139553)]</t>
-  </si>
-  <si>
-    <t>[np.float64(345.10664640067404), np.float64(-99.07341081648136)]</t>
-  </si>
-  <si>
-    <t>[np.float64(642.1324092027786), np.float64(78.00437449678304)]</t>
-  </si>
-  <si>
-    <t>[np.float64(329.3487141924727), np.float64(21.80505744423833)]</t>
-  </si>
-  <si>
-    <t>[np.float64(158.61647972147352), np.float64(-82.09328279379311)]</t>
-  </si>
-  <si>
-    <t>[np.float64(696.0158594902551), np.float64(42.035986258313784)]</t>
-  </si>
-  <si>
-    <t>[np.float64(929.3781445966167), np.float64(58.54038642491844)]</t>
-  </si>
-  <si>
-    <t>[np.float64(103.47580614366703), np.float64(69.24249241397715)]</t>
-  </si>
-  <si>
-    <t>[np.float64(277.5187222889398), np.float64(-54.99082873397803)]</t>
-  </si>
-  <si>
-    <t>[np.float64(827.6043169636868), np.float64(41.93683162347105)]</t>
-  </si>
-  <si>
-    <t>[np.float64(186.7925416983026), np.float64(94.57722824925742)]</t>
-  </si>
-  <si>
-    <t>[np.float64(454.87281506690226), np.float64(-80.06633601865873)]</t>
-  </si>
-  <si>
-    <t>[np.float64(833.9587922197314), np.float64(97.3464658685354)]</t>
-  </si>
-  <si>
-    <t>[np.float64(579.5890950429463), np.float64(-64.0071115921223)]</t>
-  </si>
-  <si>
-    <t>[np.float64(915.4270215560596), np.float64(94.12339391441711)]</t>
-  </si>
-  <si>
-    <t>[np.float64(10.319909076165645), np.float64(87.93052058975746)]</t>
-  </si>
-  <si>
-    <t>[np.float64(343.52811046220575), np.float64(-67.04982400784314)]</t>
-  </si>
-  <si>
-    <t>[np.float64(241.74097532123108), np.float64(88.54144296768678)]</t>
-  </si>
-  <si>
-    <t>[np.float64(981.9587551894311), np.float64(86.09893750602797)]</t>
-  </si>
-  <si>
-    <t>[np.float64(300.14321216716945), np.float64(0.35505269935754313)]</t>
-  </si>
-  <si>
-    <t>[np.float64(919.3003856407988), np.float64(-88.86933741701218)]</t>
-  </si>
-  <si>
-    <t>[np.float64(941.2611748209671), np.float64(9.96687164363486)]</t>
-  </si>
-  <si>
-    <t>[np.float64(154.75049189535406), np.float64(-29.155490880987387)]</t>
-  </si>
-  <si>
-    <t>[np.float64(812.7515614951487), np.float64(30.938753669829026)]</t>
-  </si>
-  <si>
-    <t>[np.float64(560.4452648787664), np.float64(-87.73529141111086)]</t>
-  </si>
-  <si>
-    <t>[np.float64(745.2287729953013), np.float64(-85.61279225351825)]</t>
-  </si>
-  <si>
-    <t>[np.float64(911.5556471344075), np.float64(-99.40702554761107)]</t>
-  </si>
-  <si>
-    <t>[np.float64(760.1695047367459), np.float64(77.68024097704728)]</t>
-  </si>
-  <si>
-    <t>[np.float64(202.96018102839707), np.float64(23.7061156786708)]</t>
-  </si>
-  <si>
-    <t>[np.float64(850.4031700585364), np.float64(13.569031672920445)]</t>
-  </si>
-  <si>
-    <t>[np.float64(762.8888506968699), np.float64(35.87246159245214)]</t>
-  </si>
-  <si>
-    <t>[np.float64(757.358628160226), np.float64(-92.30006932993614)]</t>
-  </si>
-  <si>
-    <t>[np.float64(268.50798972670174), np.float64(2.2291833948089277)]</t>
-  </si>
-  <si>
-    <t>[np.float64(155.39093788257486), np.float64(-35.27695872944551)]</t>
-  </si>
-  <si>
-    <t>[np.float64(586.3675023038081), np.float64(56.40534344249292)]</t>
-  </si>
-  <si>
-    <t>[np.float64(795.9519574746353), np.float64(89.00336232052695)]</t>
-  </si>
-  <si>
-    <t>[np.float64(836.0436332772169), np.float64(62.441246228534084)]</t>
-  </si>
-  <si>
-    <t>[np.float64(613.84068044827), np.float64(95.48201408645096)]</t>
-  </si>
-  <si>
-    <t>[np.float64(329.70760548566034), np.float64(-61.0178064812374)]</t>
-  </si>
-  <si>
-    <t>[np.float64(826.7378495834021), np.float64(46.3820292295087)]</t>
-  </si>
-  <si>
-    <t>[np.float64(994.7720953439941), np.float64(15.78453029860782)]</t>
-  </si>
-  <si>
-    <t>[np.float64(573.1721254807545), np.float64(53.48638394034356)]</t>
-  </si>
-  <si>
-    <t>[np.float64(808.5589103285973), np.float64(62.284960255963256)]</t>
-  </si>
-  <si>
-    <t>[np.float64(947.6374441094572), np.float64(81.29918052834134)]</t>
-  </si>
-  <si>
-    <t>[np.float64(16.29612461791552), np.float64(-79.05655752623878)]</t>
-  </si>
-  <si>
-    <t>[np.float64(900.0484896966407), np.float64(33.79100415382601)]</t>
-  </si>
-  <si>
-    <t>[np.float64(361.95540360177966), np.float64(4.982953167133218)]</t>
-  </si>
-  <si>
-    <t>[np.float64(314.0887325083274), np.float64(13.343877704190746)]</t>
-  </si>
-  <si>
-    <t>[np.float64(373.56970275746113), np.float64(72.15495928031893)]</t>
-  </si>
-  <si>
-    <t>[np.float64(230.11544566347564), np.float64(31.76841396622254)]</t>
-  </si>
-  <si>
-    <t>[np.float64(8.985868411041874), np.float64(-76.27501746099514)]</t>
-  </si>
-  <si>
-    <t>[np.float64(808.5048718776632), np.float64(67.39552551473838)]</t>
-  </si>
-  <si>
-    <t>[np.float64(326.72492480047345), np.float64(63.40836806905094)]</t>
-  </si>
-  <si>
-    <t>[np.float64(840.3543347912107), np.float64(51.66514270709058)]</t>
-  </si>
-  <si>
-    <t>[np.float64(845.1034019128377), np.float64(72.50812950184599)]</t>
-  </si>
-  <si>
-    <t>[np.float64(202.32305794697848), np.float64(34.52647664932715)]</t>
-  </si>
-  <si>
-    <t>[np.float64(61.80866966501108), np.float64(25.897372728305854)]</t>
-  </si>
-  <si>
-    <t>[np.float64(966.0003002829193), np.float64(96.8674116190152)]</t>
-  </si>
-  <si>
-    <t>[np.float64(223.69558980420467), np.float64(96.65800028435135)]</t>
-  </si>
-  <si>
-    <t>[np.float64(403.65025914322837), np.float64(11.312364463864526)]</t>
-  </si>
-  <si>
-    <t>[np.float64(39.54186085135669), np.float64(-41.8777942643215)]</t>
-  </si>
-  <si>
-    <t>[np.float64(477.14707619910956), np.float64(1.7720425584742117)]</t>
-  </si>
-  <si>
-    <t>[np.float64(966.9889905899423), np.float64(17.295373344654536)]</t>
-  </si>
-  <si>
-    <t>[np.float64(830.2137048213964), np.float64(10.345153888077462)]</t>
-  </si>
-  <si>
-    <t>[np.float64(568.3233033124396), np.float64(71.08994508729705)]</t>
-  </si>
-  <si>
-    <t>[np.float64(37.744647774535345), np.float64(12.097248479193041)]</t>
-  </si>
-  <si>
-    <t>[np.float64(928.6526182614219), np.float64(55.427477453119536)]</t>
-  </si>
-  <si>
-    <t>[np.float64(117.32452810139394), np.float64(56.6584437985388)]</t>
-  </si>
-  <si>
-    <t>[np.float64(415.131041275417), np.float64(5.566770802082615)]</t>
-  </si>
-  <si>
-    <t>[np.float64(430.11831417145083), np.float64(-98.676335219277)]</t>
-  </si>
-  <si>
-    <t>[np.float64(944.381021677196), np.float64(9.439946212983202)]</t>
-  </si>
-  <si>
-    <t>[np.float64(948.9229115024656), np.float64(59.593292272182225)]</t>
-  </si>
-  <si>
-    <t>[np.float64(735.746483272537), np.float64(-67.59874072431634)]</t>
-  </si>
-  <si>
-    <t>[np.float64(457.8156314553168), np.float64(49.827356309604056)]</t>
-  </si>
-  <si>
-    <t>[np.float64(948.9840507257711), np.float64(43.174248570653845)]</t>
-  </si>
-  <si>
-    <t>[np.float64(214.54498837282722), np.float64(77.09638348339243)]</t>
-  </si>
-  <si>
-    <t>[np.float64(107.43223649339373), np.float64(0.29649607824420343)]</t>
-  </si>
-  <si>
-    <t>[np.float64(198.48594536425213), np.float64(88.23670072414464)]</t>
-  </si>
-  <si>
-    <t>[np.float64(818.2631472377201), np.float64(76.82468002094757)]</t>
-  </si>
-  <si>
-    <t>[np.float64(424.03599507214227), np.float64(67.5696632771627)]</t>
-  </si>
-  <si>
-    <t>[np.float64(801.1423687410642), np.float64(35.81308941612187)]</t>
-  </si>
-  <si>
-    <t>[np.float64(335.8704633361075), np.float64(-98.69675831079705)]</t>
-  </si>
-  <si>
-    <t>[np.float64(654.3849372225711), np.float64(10.69642277775067)]</t>
-  </si>
-  <si>
-    <t>[np.float64(241.07272519212796), np.float64(49.16970792083407)]</t>
-  </si>
-  <si>
-    <t>[np.float64(760.72278369343), np.float64(3.4870520633444926)]</t>
-  </si>
-  <si>
-    <t>[np.float64(318.71549312616855), np.float64(69.94554124410544)]</t>
-  </si>
-  <si>
-    <t>[np.float64(725.5952360522903), np.float64(69.69885126090881)]</t>
-  </si>
-  <si>
-    <t>[np.float64(975.1681501974829), np.float64(56.693367916353395)]</t>
-  </si>
-  <si>
-    <t>[np.float64(296.86096816521655), np.float64(83.28138086597724)]</t>
-  </si>
-  <si>
-    <t>[np.float64(17.771533099783078), np.float64(48.839959095220706)]</t>
-  </si>
-  <si>
-    <t>[np.float64(565.174252011205), np.float64(70.31538816233669)]</t>
-  </si>
-  <si>
-    <t>[np.float64(292.40643847513525), np.float64(58.323220620919045)]</t>
-  </si>
-  <si>
-    <t>[np.float64(960.3634718388827), np.float64(70.59959576362175)]</t>
-  </si>
-  <si>
-    <t>[np.float64(584.5389378717676), np.float64(31.029143177668317)]</t>
-  </si>
-  <si>
-    <t>[np.float64(882.9341537172239), np.float64(57.583011290793536)]</t>
-  </si>
-  <si>
-    <t>[np.float64(405.74321265356707), np.float64(-64.8457701402118)]</t>
-  </si>
-  <si>
-    <t>[np.float64(192.21060084764753), np.float64(-97.55337851284764)]</t>
-  </si>
-  <si>
-    <t>[np.float64(11.743289362893151), np.float64(8.562550538377096)]</t>
-  </si>
-  <si>
-    <t>[np.float64(739.1535066307796), np.float64(42.27951167626878)]</t>
-  </si>
-  <si>
-    <t>[np.float64(316.61516796750846), np.float64(-87.56454777361083)]</t>
-  </si>
-  <si>
-    <t>[np.float64(917.198369465899), np.float64(-86.65226330717273)]</t>
-  </si>
-  <si>
-    <t>[np.float64(734.1814195121118), np.float64(98.17040049738372)]</t>
-  </si>
-  <si>
-    <t>[np.float64(998.6266371127459), np.float64(-43.99753441112115)]</t>
-  </si>
-  <si>
-    <t>[np.float64(774.5648003077152), np.float64(76.76418727978401)]</t>
-  </si>
-  <si>
-    <t>[np.float64(456.4636038941483), np.float64(40.65384775256874)]</t>
-  </si>
-  <si>
-    <t>[np.float64(237.8642458211221), np.float64(44.0528509387012)]</t>
-  </si>
-  <si>
-    <t>[np.float64(861.3437273916678), np.float64(-84.6297065901762)]</t>
-  </si>
-  <si>
-    <t>[np.float64(971.7390177952243), np.float64(-96.51337306319473)]</t>
-  </si>
-  <si>
-    <t>[np.float64(402.3031238386953), np.float64(-62.19337436785813)]</t>
-  </si>
-  <si>
-    <t>[np.float64(258.0017237558091), np.float64(-49.48908750638512)]</t>
-  </si>
-  <si>
-    <t>[np.float64(477.1975358351726), np.float64(66.87366022583726)]</t>
-  </si>
-  <si>
-    <t>[np.float64(205.60283813520886), np.float64(86.74695237385669)]</t>
-  </si>
-  <si>
-    <t>[np.float64(409.71963596290385), np.float64(45.34712242946057)]</t>
-  </si>
-  <si>
-    <t>[np.float64(266.21556830087), np.float64(-87.18080820169978)]</t>
-  </si>
-  <si>
-    <t>[np.float64(637.3404928083719), np.float64(-69.7233460639471)]</t>
-  </si>
-  <si>
-    <t>[np.float64(343.0846466757085), np.float64(96.40299633807132)]</t>
-  </si>
-  <si>
-    <t>[np.float64(23.65179343556878), np.float64(2.4910327063289373)]</t>
-  </si>
-  <si>
-    <t>[np.float64(713.3382121959465), np.float64(98.21477535721436)]</t>
-  </si>
-  <si>
-    <t>[np.float64(430.3761263494028), np.float64(10.664610074805168)]</t>
-  </si>
-  <si>
-    <t>[np.float64(690.4868256505449), np.float64(50.538377764145196)]</t>
-  </si>
-  <si>
-    <t>[np.float64(601.1559747789598), np.float64(18.57092814058238)]</t>
-  </si>
-  <si>
-    <t>[np.float64(685.1021993756166), np.float64(45.3584583175265)]</t>
-  </si>
-  <si>
-    <t>[np.float64(889.8303648338398), np.float64(-85.53686499554112)]</t>
-  </si>
-  <si>
-    <t>[np.float64(737.8962439616537), np.float64(91.81929096413975)]</t>
-  </si>
-  <si>
-    <t>[np.float64(282.5517103743599), np.float64(62.920492080466516)]</t>
-  </si>
-  <si>
-    <t>[np.float64(224.71019021871342), np.float64(33.954417477018524)]</t>
-  </si>
-  <si>
-    <t>[np.float64(832.8358794595201), np.float64(-73.26582262872488)]</t>
-  </si>
-  <si>
-    <t>[np.float64(693.7528678103133), np.float64(24.169647196263185)]</t>
-  </si>
-  <si>
-    <t>[np.float64(950.0184276198297), np.float64(-84.4963443227036)]</t>
-  </si>
-  <si>
-    <t>[np.float64(736.2426775194448), np.float64(65.83744582003516)]</t>
-  </si>
-  <si>
-    <t>[np.float64(828.1623341104994), np.float64(23.123123769821234)]</t>
-  </si>
-  <si>
-    <t>[np.float64(589.5579557788013), np.float64(17.67554998263337)]</t>
-  </si>
-  <si>
-    <t>[np.float64(522.6613325278861), np.float64(-96.3541372342821)]</t>
-  </si>
-  <si>
-    <t>[np.float64(351.45291256215086), np.float64(-72.18052714278917)]</t>
-  </si>
-  <si>
-    <t>[np.float64(885.2129214650936), np.float64(59.40304743928428)]</t>
-  </si>
-  <si>
-    <t>[np.float64(590.1660144300613), np.float64(19.044224613175118)]</t>
-  </si>
-  <si>
-    <t>[np.float64(558.3467547888552), np.float64(67.02837743187519)]</t>
-  </si>
-  <si>
-    <t>[np.float64(80.59545819956281), np.float64(14.273661028486345)]</t>
-  </si>
-  <si>
-    <t>[np.float64(977.5230310867952), np.float64(60.03670048700195)]</t>
-  </si>
-  <si>
-    <t>[np.float64(495.8666815657687), np.float64(47.17046100482983)]</t>
-  </si>
-  <si>
-    <t>[np.float64(198.0993221269547), np.float64(47.33877368556662)]</t>
-  </si>
-  <si>
-    <t>[np.float64(81.05023115508025), np.float64(36.40137817690453)]</t>
-  </si>
-  <si>
-    <t>[np.float64(37.47521734623693), np.float64(-13.546376733189575)]</t>
-  </si>
-  <si>
-    <t>[np.float64(690.2692123696214), np.float64(91.09963821836001)]</t>
-  </si>
-  <si>
-    <t>[np.float64(180.16377114919123), np.float64(80.2986445590598)]</t>
-  </si>
-  <si>
-    <t>[np.float64(538.4792732416454), np.float64(55.23364427439046)]</t>
-  </si>
-  <si>
-    <t>[np.float64(864.9413853176122), np.float64(57.03931063448496)]</t>
-  </si>
-  <si>
-    <t>[np.float64(710.6015489673173), np.float64(36.45980951109067)]</t>
-  </si>
-  <si>
-    <t>[np.float64(567.961197545273), np.float64(1.2204221995907716)]</t>
-  </si>
-  <si>
-    <t>[np.float64(576.6533522054417), np.float64(-33.95362607993111)]</t>
-  </si>
-  <si>
-    <t>[np.float64(794.8752528628357), np.float64(51.37025443996683)]</t>
-  </si>
-  <si>
-    <t>[np.float64(151.2147135181282), np.float64(53.90655872670311)]</t>
-  </si>
-  <si>
-    <t>[np.float64(599.6339862878567), np.float64(-78.4842184472075)]</t>
-  </si>
-  <si>
-    <t>[np.float64(362.51354448997273), np.float64(50.590210446506546)]</t>
-  </si>
-  <si>
-    <t>[np.float64(736.0020322510823), np.float64(40.1455352877411)]</t>
-  </si>
-  <si>
-    <t>[np.float64(189.28190631725394), np.float64(44.354608837520004)]</t>
-  </si>
-  <si>
-    <t>[np.float64(930.758170930426), np.float64(63.454715291628276)]</t>
-  </si>
-  <si>
-    <t>[np.float64(19.985867957566295), np.float64(-99.05244737862952)]</t>
-  </si>
-  <si>
-    <t>[np.float64(285.1071342810196), np.float64(38.992140852640176)]</t>
-  </si>
-  <si>
-    <t>[np.float64(299.15509827223883), np.float64(65.45451338937559)]</t>
-  </si>
-  <si>
-    <t>[np.float64(468.48568248283374), np.float64(35.70428764789014)]</t>
-  </si>
-  <si>
-    <t>[np.float64(921.1426397789403), np.float64(62.534977900287316)]</t>
-  </si>
-  <si>
-    <t>[np.float64(753.032109014234), np.float64(90.48197914718361)]</t>
-  </si>
-  <si>
-    <t>[np.float64(264.4930990199347), np.float64(27.22891641549363)]</t>
-  </si>
-  <si>
-    <t>[np.float64(838.963706517754), np.float64(-50.87839046231277)]</t>
-  </si>
-  <si>
-    <t>[np.float64(668.6325098343725), np.float64(-90.88751216341007)]</t>
-  </si>
-  <si>
-    <t>[np.float64(248.56491741527964), np.float64(-90.13584159507195)]</t>
-  </si>
-  <si>
-    <t>[np.float64(790.9099163259349), np.float64(85.35751810433959)]</t>
-  </si>
-  <si>
-    <t>[np.float64(834.9816706195787), np.float64(-97.17183434237087)]</t>
-  </si>
-  <si>
-    <t>[np.float64(758.9285864193909), np.float64(77.63964437184731)]</t>
-  </si>
-  <si>
-    <t>[np.float64(717.1022226275091), np.float64(-92.19547867515767)]</t>
-  </si>
-  <si>
-    <t>[np.float64(995.7563269431537), np.float64(-36.25638203367365)]</t>
-  </si>
-  <si>
-    <t>[np.float64(774.8247157934777), np.float64(4.49637717963094)]</t>
-  </si>
-  <si>
-    <t>[np.float64(884.5030697157092), np.float64(-73.80847256047167)]</t>
-  </si>
-  <si>
-    <t>[np.float64(400.95432275832576), np.float64(54.05560742699993)]</t>
-  </si>
-  <si>
-    <t>[np.float64(606.901092513093), np.float64(88.82536013360297)]</t>
-  </si>
-  <si>
-    <t>[np.float64(780.2278470853232), np.float64(-83.22441018913776)]</t>
-  </si>
-  <si>
-    <t>[np.float64(523.718288370592), np.float64(3.0345692565153115)]</t>
-  </si>
-  <si>
-    <t>[np.float64(273.4007487664373), np.float64(63.96470810292698)]</t>
-  </si>
-  <si>
-    <t>[np.float64(79.89549711633626), np.float64(-95.41307214057252)]</t>
-  </si>
-  <si>
-    <t>[np.float64(0.6281331959826497), np.float64(49.44384629357933)]</t>
-  </si>
-  <si>
-    <t>[np.float64(766.5584572446948), np.float64(61.18354902686855)]</t>
-  </si>
-  <si>
-    <t>[np.float64(487.2899876079231), np.float64(-81.76005450759736)]</t>
-  </si>
-  <si>
-    <t>[np.float64(909.5822341030727), np.float64(76.88774556188648)]</t>
-  </si>
-  <si>
-    <t>[np.float64(993.2318279886358), np.float64(11.189523745944612)]</t>
-  </si>
-  <si>
-    <t>[np.float64(672.9419666945747), np.float64(38.1551329014824)]</t>
-  </si>
-  <si>
-    <t>[np.float64(399.4771662966971), np.float64(29.185494193321006)]</t>
-  </si>
-  <si>
-    <t>[np.float64(755.6423286703765), np.float64(10.710341763243036)]</t>
-  </si>
-  <si>
-    <t>[np.float64(334.52238233061195), np.float64(37.548571748746184)]</t>
-  </si>
-  <si>
-    <t>[np.float64(711.9772653962867), np.float64(58.10599307522716)]</t>
-  </si>
-  <si>
-    <t>[np.float64(578.0242081187174), np.float64(-62.87781731906639)]</t>
-  </si>
-  <si>
-    <t>[np.float64(737.7255260643349), np.float64(8.108548270988905)]</t>
-  </si>
-  <si>
-    <t>[np.float64(100.38244060265656), np.float64(63.276710982591425)]</t>
-  </si>
-  <si>
-    <t>[np.float64(421.2022569721088), np.float64(54.125717622390596)]</t>
-  </si>
-  <si>
-    <t>[np.float64(355.10539587579615), np.float64(22.818588640192218)]</t>
-  </si>
-  <si>
-    <t>[np.float64(574.3662349640633), np.float64(-23.019083608598677)]</t>
-  </si>
-  <si>
-    <t>[np.float64(309.33358147352595), np.float64(-68.9035321011302)]</t>
-  </si>
-  <si>
-    <t>[np.float64(267.92446367304825), np.float64(-86.08212845525165)]</t>
-  </si>
-  <si>
-    <t>[np.float64(90.08796422307341), np.float64(15.973056618300348)]</t>
-  </si>
-  <si>
-    <t>[np.float64(255.83055500926378), np.float64(-59.05103204716602)]</t>
-  </si>
-  <si>
-    <t>[np.float64(106.56614225142714), np.float64(7.631917574952411)]</t>
-  </si>
-  <si>
-    <t>[np.float64(146.43124616188297), np.float64(30.143534727584324)]</t>
-  </si>
-  <si>
-    <t>[np.float64(410.30512530004114), np.float64(-95.78555766465561)]</t>
-  </si>
-  <si>
-    <t>[np.float64(127.05577149839054), np.float64(-90.7382960933241)]</t>
-  </si>
-  <si>
-    <t>[np.float64(531.6845037016744), np.float64(2.2511797230122994)]</t>
-  </si>
-  <si>
-    <t>[np.float64(212.19405271939985), np.float64(21.89368513633447)]</t>
-  </si>
-  <si>
-    <t>[np.float64(94.89495719660334), np.float64(82.99319218441016)]</t>
-  </si>
-  <si>
-    <t>[np.float64(469.50330028647835), np.float64(23.346519334607336)]</t>
-  </si>
-  <si>
-    <t>[np.float64(747.4196172334606), np.float64(39.68085373169629)]</t>
-  </si>
-  <si>
-    <t>[np.float64(614.232951641608), np.float64(58.70672754759741)]</t>
-  </si>
-  <si>
-    <t>[np.float64(266.03189764045055), np.float64(89.63477742670801)]</t>
-  </si>
-  <si>
-    <t>[np.float64(940.4088626374569), np.float64(76.69883670726557)]</t>
-  </si>
-  <si>
-    <t>[np.float64(738.6029513196507), np.float64(0.37462939463847533)]</t>
-  </si>
-  <si>
-    <t>[np.float64(412.7487363168602), np.float64(-58.656611046712804)]</t>
-  </si>
-  <si>
-    <t>[np.float64(292.2204576348829), np.float64(90.6828096960499)]</t>
-  </si>
-  <si>
-    <t>[np.float64(865.6700225261155), np.float64(52.35899571335432)]</t>
-  </si>
-  <si>
-    <t>[np.float64(607.7008675176061), np.float64(16.122292845656204)]</t>
-  </si>
-  <si>
-    <t>[np.float64(133.47423461756281), np.float64(53.97167354246744)]</t>
-  </si>
-  <si>
-    <t>[np.float64(230.61996982333653), np.float64(99.887668350161)]</t>
-  </si>
-  <si>
-    <t>[np.float64(736.0429150525246), np.float64(16.068070735216082)]</t>
-  </si>
-  <si>
-    <t>[np.float64(0.972006930989977), np.float64(6.466289313592611)]</t>
-  </si>
-  <si>
-    <t>[np.float64(105.27892369016523), np.float64(33.934214141419346)]</t>
-  </si>
-  <si>
-    <t>[np.float64(881.096924640154), np.float64(51.92369463239663)]</t>
-  </si>
-  <si>
-    <t>[np.float64(559.3535229310136), np.float64(-95.57131626360065)]</t>
-  </si>
-  <si>
-    <t>[np.float64(535.8187974252273), np.float64(76.17579444360385)]</t>
-  </si>
-  <si>
-    <t>[np.float64(234.3600165362626), np.float64(88.42793983079915)]</t>
-  </si>
-  <si>
-    <t>[np.float64(955.2297234333003), np.float64(50.56183710625356)]</t>
-  </si>
-  <si>
-    <t>[np.float64(811.0978469857175), np.float64(57.46874532376697)]</t>
-  </si>
-  <si>
-    <t>[np.float64(526.0540271661303), np.float64(37.68061668703439)]</t>
-  </si>
-  <si>
-    <t>[np.float64(557.5539316477032), np.float64(-72.9222883882723)]</t>
-  </si>
-  <si>
-    <t>[np.float64(424.4683363386906), np.float64(21.87355946100476)]</t>
-  </si>
-  <si>
-    <t>[np.float64(173.45836231059909), np.float64(-70.8794744935499)]</t>
-  </si>
-  <si>
-    <t>[np.float64(166.88326122044538), np.float64(4.918608336237298)]</t>
-  </si>
-  <si>
-    <t>[np.float64(171.13232613514418), np.float64(-79.22896976780848)]</t>
-  </si>
-  <si>
-    <t>[np.float64(172.85919781448445), np.float64(86.5029650470837)]</t>
-  </si>
-  <si>
-    <t>[np.float64(619.917231066804), np.float64(56.529729095079375)]</t>
-  </si>
-  <si>
-    <t>[np.float64(91.82463829654341), np.float64(-12.010244044651344)]</t>
-  </si>
-  <si>
-    <t>[np.float64(56.67408382325567), np.float64(-94.0890136964879)]</t>
-  </si>
-  <si>
-    <t>[np.float64(727.5251891275402), np.float64(50.986382062189364)]</t>
-  </si>
-  <si>
-    <t>[np.float64(490.6731477326748), np.float64(63.65199995540286)]</t>
-  </si>
-  <si>
-    <t>[np.float64(970.8919780320839), np.float64(53.541498439788)]</t>
-  </si>
-  <si>
-    <t>[np.float64(329.94840939200486), np.float64(61.81103502552551)]</t>
-  </si>
-  <si>
-    <t>[np.float64(683.1937481985457), np.float64(12.783509742014814)]</t>
-  </si>
-  <si>
-    <t>[np.float64(414.25871580416594), np.float64(62.26185877290942)]</t>
-  </si>
-  <si>
-    <t>[np.float64(977.0912704455758), np.float64(-80.30789422688913)]</t>
-  </si>
-  <si>
-    <t>[np.float64(128.04688410095156), np.float64(50.80389385176383)]</t>
-  </si>
-  <si>
-    <t>[np.float64(829.8937104385252), np.float64(48.911014402996216)]</t>
-  </si>
-  <si>
-    <t>[np.float64(229.98935537344155), np.float64(10.146894904525666)]</t>
-  </si>
-  <si>
-    <t>[np.float64(415.27479713227035), np.float64(73.20537624163836)]</t>
-  </si>
-  <si>
-    <t>[np.float64(905.2333378864349), np.float64(50.68013638416181)]</t>
-  </si>
-  <si>
-    <t>[np.float64(660.4091412766379), np.float64(90.38773898927363)]</t>
-  </si>
-  <si>
-    <t>[np.float64(391.93502730432573), np.float64(-76.92447906135389)]</t>
-  </si>
-  <si>
-    <t>[np.float64(590.6916894226293), np.float64(92.99071300741784)]</t>
-  </si>
-  <si>
-    <t>[np.float64(980.7512907929802), np.float64(-85.33653644784785)]</t>
-  </si>
-  <si>
-    <t>[np.float64(945.4415495884955), np.float64(5.713699526188606)]</t>
-  </si>
-  <si>
-    <t>[np.float64(556.5630990528814), np.float64(85.73316597830387)]</t>
-  </si>
-  <si>
-    <t>[np.float64(799.6470403138597), np.float64(-67.47526175269172)]</t>
-  </si>
-  <si>
-    <t>[np.float64(818.1768181610242), np.float64(8.118878400947978)]</t>
-  </si>
-  <si>
-    <t>[np.float64(639.6875448796643), np.float64(43.35751693013498)]</t>
-  </si>
-  <si>
-    <t>[np.float64(402.9655805070943), np.float64(12.953132239395742)]</t>
-  </si>
-  <si>
-    <t>[np.float64(381.11098396283995), np.float64(7.430054461493768)]</t>
-  </si>
-  <si>
-    <t>[np.float64(916.0198083749104), np.float64(88.31772183442271)]</t>
-  </si>
-  <si>
-    <t>[np.float64(785.8881893135882), np.float64(27.473089359007787)]</t>
-  </si>
-  <si>
-    <t>[np.float64(770.7410475151079), np.float64(-56.93361511357584)]</t>
-  </si>
-  <si>
-    <t>[np.float64(867.1782189657946), np.float64(29.60808237048215)]</t>
-  </si>
-  <si>
-    <t>[np.float64(217.6256423686471), np.float64(-40.33627800949622)]</t>
-  </si>
-  <si>
-    <t>[np.float64(910.0284973289682), np.float64(52.65168551437526)]</t>
-  </si>
-  <si>
-    <t>[np.float64(367.8952627667489), np.float64(40.37452976590333)]</t>
-  </si>
-  <si>
-    <t>[np.float64(224.8509769106436), np.float64(-76.71684540637145)]</t>
-  </si>
-  <si>
-    <t>[np.float64(729.2734225077246), np.float64(55.052535595368425)]</t>
-  </si>
-  <si>
-    <t>[np.float64(295.028455137782), np.float64(4.624124663613529)]</t>
-  </si>
-  <si>
-    <t>[np.float64(757.5329154385886), np.float64(-71.6605950392127)]</t>
-  </si>
-  <si>
-    <t>[np.float64(214.55148936831614), np.float64(75.69734808736956)]</t>
-  </si>
-  <si>
-    <t>[np.float64(781.0917740679353), np.float64(28.536855452878683)]</t>
-  </si>
-  <si>
-    <t>[np.float64(199.99412571587695), np.float64(33.02400111528448)]</t>
-  </si>
-  <si>
-    <t>[np.float64(943.350129896633), np.float64(47.45122820041175)]</t>
-  </si>
-  <si>
-    <t>[np.float64(548.7397193235421), np.float64(87.38557922395947)]</t>
-  </si>
-  <si>
-    <t>[np.float64(435.4307490654532), np.float64(52.52713971633497)]</t>
-  </si>
-  <si>
-    <t>[np.float64(709.5625981608749), np.float64(47.08304543225307)]</t>
-  </si>
-  <si>
-    <t>[np.float64(858.8854449837584), np.float64(22.807047942485)]</t>
-  </si>
-  <si>
-    <t>[np.float64(401.9666548023576), np.float64(29.422179667718154)]</t>
-  </si>
-  <si>
-    <t>[np.float64(932.8338202592797), np.float64(-54.46730150451926)]</t>
-  </si>
-  <si>
-    <t>[np.float64(525.6999412746051), np.float64(52.775517320990076)]</t>
-  </si>
-  <si>
-    <t>[np.float64(259.5743632117317), np.float64(-82.89802808712764)]</t>
-  </si>
-  <si>
-    <t>[np.float64(118.18143693867455), np.float64(26.821684352195433)]</t>
-  </si>
-  <si>
-    <t>[np.float64(859.4431658585676), np.float64(-79.14654046414367)]</t>
-  </si>
-  <si>
-    <t>[np.float64(31.928761513915994), np.float64(31.71895755680322)]</t>
-  </si>
-  <si>
-    <t>[np.float64(591.7462657080233), np.float64(-87.32321850957945)]</t>
-  </si>
-  <si>
-    <t>[np.float64(937.2246109541636), np.float64(46.47299319593006)]</t>
-  </si>
-  <si>
-    <t>[np.float64(337.91346890900854), np.float64(-80.99670839882336)]</t>
-  </si>
-  <si>
-    <t>[np.float64(306.75735719660355), np.float64(30.11068505336911)]</t>
-  </si>
-  <si>
-    <t>[np.float64(404.6276767097996), np.float64(96.22943521132584)]</t>
-  </si>
-  <si>
-    <t>[np.float64(113.32400269115317), np.float64(82.6022682902717)]</t>
-  </si>
-  <si>
-    <t>[np.float64(149.7091307094074), np.float64(12.629017981340638)]</t>
-  </si>
-  <si>
-    <t>[np.float64(427.2288045882322), np.float64(-76.28230677248375)]</t>
-  </si>
-  <si>
-    <t>[np.float64(184.03911997888122), np.float64(72.08716724806649)]</t>
-  </si>
-  <si>
-    <t>[np.float64(217.9861307584725), np.float64(92.5283029786641)]</t>
-  </si>
-  <si>
-    <t>[np.float64(419.5426786982172), np.float64(4.121039448779754)]</t>
-  </si>
-  <si>
-    <t>[np.float64(542.5382352687366), np.float64(60.94027706757197)]</t>
-  </si>
-  <si>
-    <t>[np.float64(463.36619600059817), np.float64(-96.02376972102262)]</t>
-  </si>
-  <si>
-    <t>[np.float64(520.9221479472753), np.float64(97.70755217482045)]</t>
-  </si>
-  <si>
-    <t>[np.float64(233.17783650022906), np.float64(93.42833180489563)]</t>
-  </si>
-  <si>
-    <t>[np.float64(737.1719953032745), np.float64(5.912388478059555)]</t>
-  </si>
-  <si>
-    <t>[np.float64(408.3522445822637), np.float64(-90.78267843728305)]</t>
-  </si>
-  <si>
-    <t>[np.float64(981.479291187402), np.float64(25.762613093262573)]</t>
-  </si>
-  <si>
-    <t>[np.float64(149.05277029373875), np.float64(77.38503315054203)]</t>
-  </si>
-  <si>
-    <t>[np.float64(405.05074318759927), np.float64(4.0099452063067815)]</t>
-  </si>
-  <si>
-    <t>[np.float64(141.60501676210814), np.float64(77.42901864716521)]</t>
-  </si>
-  <si>
-    <t>[np.float64(112.69101284977523), np.float64(27.946613617465047)]</t>
-  </si>
-  <si>
-    <t>[np.float64(732.1123617699501), np.float64(61.20283968333001)]</t>
-  </si>
-  <si>
-    <t>[np.float64(919.1716968292623), np.float64(76.26450740821099)]</t>
-  </si>
-  <si>
-    <t>[np.float64(170.21195793099554), np.float64(-76.93717729884708)]</t>
-  </si>
-  <si>
-    <t>[np.float64(711.4749569726016), np.float64(81.7564277275639)]</t>
-  </si>
-  <si>
-    <t>[np.float64(282.6828574807577), np.float64(-71.61701798709299)]</t>
-  </si>
-  <si>
-    <t>[np.float64(823.4842100860602), np.float64(85.20642426482706)]</t>
-  </si>
-  <si>
-    <t>[np.float64(785.9067706365497), np.float64(0.8618825769828504)]</t>
-  </si>
-  <si>
-    <t>[np.float64(937.3685094599408), np.float64(-6.9677464373159665)]</t>
-  </si>
-  <si>
-    <t>[np.float64(412.5034572930104), np.float64(4.821763407315018)]</t>
-  </si>
-  <si>
-    <t>[np.float64(512.7790498567033), np.float64(71.17155387565225)]</t>
-  </si>
-  <si>
-    <t>[np.float64(484.311706550707), np.float64(44.4858751086318)]</t>
-  </si>
-  <si>
-    <t>[np.float64(429.22368473104564), np.float64(51.64962318663521)]</t>
-  </si>
-  <si>
-    <t>[np.float64(252.80629194512727), np.float64(35.718770664906685)]</t>
-  </si>
-  <si>
-    <t>[np.float64(14.304381741207294), np.float64(81.74780550457683)]</t>
-  </si>
-  <si>
-    <t>[np.float64(618.9045228948434), np.float64(83.71541330716835)]</t>
-  </si>
-  <si>
-    <t>[np.float64(819.589142799627), np.float64(35.64517794445666)]</t>
-  </si>
-  <si>
-    <t>[np.float64(15.197705237342207), np.float64(72.40675484598833)]</t>
-  </si>
-  <si>
-    <t>[np.float64(352.67432102736217), np.float64(48.03788461996646)]</t>
-  </si>
-  <si>
-    <t>[np.float64(51.32822357559874), np.float64(31.059280050097584)]</t>
-  </si>
-  <si>
-    <t>[np.float64(126.54260827623898), np.float64(16.934863398482605)]</t>
-  </si>
-  <si>
-    <t>[np.float64(929.5921352885046), np.float64(43.28537552753488)]</t>
-  </si>
-  <si>
-    <t>[np.float64(201.9717214533746), np.float64(9.327390838043144)]</t>
-  </si>
-  <si>
-    <t>[np.float64(576.4397365627965), np.float64(22.989404471681937)]</t>
-  </si>
-  <si>
-    <t>[np.float64(457.19989747240453), np.float64(-56.163445293259514)]</t>
-  </si>
-  <si>
-    <t>[np.float64(739.6780137827228), np.float64(20.933815174319378)]</t>
-  </si>
-  <si>
-    <t>[np.float64(305.2616866442628), np.float64(-86.24115924413103)]</t>
-  </si>
-  <si>
-    <t>[np.float64(758.7390908719988), np.float64(-40.3780070428011)]</t>
-  </si>
-  <si>
-    <t>[np.float64(401.1210318639646), np.float64(61.180996017945944)]</t>
-  </si>
-  <si>
-    <t>[np.float64(702.7687574836249), np.float64(65.7197083817878)]</t>
-  </si>
-  <si>
-    <t>[np.float64(657.3551457020642), np.float64(-98.51518130269028)]</t>
-  </si>
-  <si>
-    <t>[np.float64(562.1247622802574), np.float64(60.50980573028488)]</t>
-  </si>
-  <si>
-    <t>[np.float64(856.1704923870907), np.float64(80.7326393170163)]</t>
-  </si>
-  <si>
-    <t>[np.float64(150.79251500638068), np.float64(91.25788930944861)]</t>
-  </si>
-  <si>
-    <t>[np.float64(757.4581090210235), np.float64(-91.0092245401771)]</t>
-  </si>
-  <si>
-    <t>[np.float64(863.1411899703239), np.float64(-76.82976265935596)]</t>
-  </si>
-  <si>
-    <t>[np.float64(246.13970621637583), np.float64(2.1893521048331337)]</t>
-  </si>
-  <si>
-    <t>[np.float64(450.7791184146482), np.float64(17.352812086009536)]</t>
-  </si>
-  <si>
-    <t>[np.float64(223.3660855519084), np.float64(11.315963364953845)]</t>
-  </si>
-  <si>
-    <t>[np.float64(664.5017122193077), np.float64(89.13831215139055)]</t>
-  </si>
-  <si>
-    <t>[np.float64(486.37402566865904), np.float64(60.23139307952883)]</t>
-  </si>
-  <si>
-    <t>[np.float64(269.00159096277855), np.float64(45.076132836087595)]</t>
-  </si>
-  <si>
-    <t>[np.float64(424.12778134680093), np.float64(71.51672321308885)]</t>
-  </si>
-  <si>
-    <t>[np.float64(361.02989447811984), np.float64(89.8849407308764)]</t>
-  </si>
-  <si>
-    <t>[np.float64(197.92299263228318), np.float64(-89.72514042873452)]</t>
-  </si>
-  <si>
-    <t>[np.float64(265.4352085234544), np.float64(20.044113739998465)]</t>
-  </si>
-  <si>
-    <t>[np.float64(657.7679084381869), np.float64(-88.94787504431112)]</t>
-  </si>
-  <si>
-    <t>[np.float64(880.9547948880356), np.float64(2.4704101707065433)]</t>
-  </si>
-  <si>
-    <t>[np.float64(598.2825351744086), np.float64(-77.85446413877067)]</t>
-  </si>
-  <si>
-    <t>[np.float64(157.97969975691618), np.float64(-90.69618160180289)]</t>
-  </si>
-  <si>
-    <t>[np.float64(229.2326951408271), np.float64(33.540401531095284)]</t>
-  </si>
-  <si>
-    <t>[np.float64(759.0555043885483), np.float64(-2.9033060946589444)]</t>
-  </si>
-  <si>
-    <t>[np.float64(639.3363928636134), np.float64(18.131470471994888)]</t>
-  </si>
-  <si>
-    <t>[np.float64(40.92240503011968), np.float64(25.064212411950066)]</t>
-  </si>
-  <si>
-    <t>[np.float64(89.67683590214493), np.float64(-0.48725193779846165)]</t>
-  </si>
-  <si>
-    <t>[np.float64(24.400985738499358), np.float64(49.372936122574174)]</t>
-  </si>
-  <si>
-    <t>[np.float64(881.1493217198536), np.float64(99.13114005947651)]</t>
-  </si>
-  <si>
-    <t>[np.float64(591.1480949791446), np.float64(3.491507006761907)]</t>
-  </si>
-  <si>
-    <t>[np.float64(413.95139534244674), np.float64(-68.03126601777842)]</t>
-  </si>
-  <si>
-    <t>[np.float64(671.3187869324223), np.float64(99.00360390776473)]</t>
-  </si>
-  <si>
-    <t>[np.float64(787.0113953010573), np.float64(88.8429712157454)]</t>
-  </si>
-  <si>
-    <t>[np.float64(30.028356232325248), np.float64(70.83621744390157)]</t>
-  </si>
-  <si>
-    <t>[np.float64(692.4252661844581), np.float64(-28.577389253415646)]</t>
-  </si>
-  <si>
-    <t>[np.float64(201.63437003671936), np.float64(23.072624602633823)]</t>
-  </si>
-  <si>
-    <t>[np.float64(32.14986402648889), np.float64(-66.55415375020657)]</t>
-  </si>
-  <si>
-    <t>[np.float64(151.91922496439304), np.float64(-83.66357515696058)]</t>
-  </si>
-  <si>
-    <t>[np.float64(237.57534898905053), np.float64(31.5548872840902)]</t>
-  </si>
-  <si>
-    <t>[np.float64(487.0553294846135), np.float64(74.79623456315579)]</t>
-  </si>
-  <si>
-    <t>[np.float64(673.9676502740757), np.float64(42.95517060588858)]</t>
-  </si>
-  <si>
-    <t>[np.float64(779.5071635307852), np.float64(54.34802804968828)]</t>
-  </si>
-  <si>
-    <t>[np.float64(520.8671009480645), np.float64(82.63830814309483)]</t>
-  </si>
-  <si>
-    <t>[np.float64(943.8756683317979), np.float64(-92.04503051540517)]</t>
-  </si>
-  <si>
-    <t>[np.float64(631.5705378577953), np.float64(-79.2596325024959)]</t>
-  </si>
-  <si>
-    <t>[np.float64(918.604561220947), np.float64(56.12231403730149)]</t>
-  </si>
-  <si>
-    <t>[np.float64(514.3303315213766), np.float64(65.910047290481)]</t>
-  </si>
-  <si>
-    <t>[np.float64(928.6285524931676), np.float64(23.93594537479993)]</t>
-  </si>
-  <si>
-    <t>[np.float64(928.9059704275064), np.float64(76.8071258073426)]</t>
-  </si>
-  <si>
-    <t>[np.float64(204.5147360521793), np.float64(32.972693089516895)]</t>
-  </si>
-  <si>
-    <t>[np.float64(319.64463775685346), np.float64(11.958244929522593)]</t>
-  </si>
-  <si>
-    <t>[np.float64(698.8300538716823), np.float64(56.09432736392864)]</t>
-  </si>
-  <si>
-    <t>[np.float64(845.019968861954), np.float64(53.138648936891144)]</t>
-  </si>
-  <si>
-    <t>[np.float64(37.41389192263156), np.float64(-81.4265042220201)]</t>
-  </si>
-  <si>
-    <t>[np.float64(501.01130356420254), np.float64(87.42496292217982)]</t>
-  </si>
-  <si>
-    <t>[np.float64(420.15563009967036), np.float64(26.47560419599995)]</t>
-  </si>
-  <si>
-    <t>[np.float64(975.1516059664706), np.float64(-80.45131444606106)]</t>
-  </si>
-  <si>
-    <t>[np.float64(345.94859975356553), np.float64(42.806636065024776)]</t>
-  </si>
-  <si>
-    <t>[np.float64(591.2216669116614), np.float64(-96.08872575478611)]</t>
-  </si>
-  <si>
-    <t>[np.float64(456.8906740586709), np.float64(-76.79932156693505)]</t>
-  </si>
-  <si>
-    <t>[np.float64(59.29189934340029), np.float64(91.27403855565285)]</t>
-  </si>
-  <si>
-    <t>[np.float64(206.74240868457227), np.float64(88.78143373517665)]</t>
-  </si>
-  <si>
-    <t>[np.float64(463.8577299172648), np.float64(79.5849186584395)]</t>
-  </si>
-  <si>
-    <t>[np.float64(358.3040764081857), np.float64(79.41285845706912)]</t>
-  </si>
-  <si>
-    <t>[np.float64(275.41851908195804), np.float64(-57.19964397616317)]</t>
-  </si>
-  <si>
-    <t>[np.float64(250.82902500850247), np.float64(90.653931423823)]</t>
-  </si>
-  <si>
-    <t>[np.float64(159.33843947636973), np.float64(-94.88049511228334)]</t>
-  </si>
-  <si>
-    <t>[np.float64(843.4004508268698), np.float64(23.463425293821103)]</t>
-  </si>
-  <si>
-    <t>[np.float64(542.3188427497101), np.float64(0.7809202083161324)]</t>
-  </si>
-  <si>
-    <t>[np.float64(691.697610921882), np.float64(87.72347675903279)]</t>
-  </si>
-  <si>
-    <t>[np.float64(12.668666898855596), np.float64(-64.59333588806864)]</t>
-  </si>
-  <si>
-    <t>[np.float64(634.9598035354372), np.float64(82.88142252490013)]</t>
-  </si>
-  <si>
-    <t>[np.float64(420.0479638439587), np.float64(-91.74558180203285)]</t>
-  </si>
-  <si>
-    <t>[np.float64(266.9410710353365), np.float64(87.79859296464235)]</t>
-  </si>
-  <si>
-    <t>[np.float64(878.580274802217), np.float64(11.26507691051026)]</t>
-  </si>
-  <si>
-    <t>[np.float64(8.478517247561989), np.float64(92.24326561206598)]</t>
-  </si>
-  <si>
-    <t>[np.float64(928.8012641130267), np.float64(37.157107751803466)]</t>
-  </si>
-  <si>
-    <t>[np.float64(678.8867918412868), np.float64(55.82242251750017)]</t>
-  </si>
-  <si>
-    <t>[np.float64(309.78796629253634), np.float64(-91.62512957889788)]</t>
-  </si>
-  <si>
-    <t>[np.float64(188.22629209214946), np.float64(26.217514479791532)]</t>
-  </si>
-  <si>
-    <t>[np.float64(769.7563669431343), np.float64(-92.69793506975725)]</t>
-  </si>
-  <si>
-    <t>[np.float64(919.9154894516441), np.float64(30.164884504321208)]</t>
-  </si>
-  <si>
-    <t>[np.float64(736.7339530792771), np.float64(67.05615869504672)]</t>
-  </si>
-  <si>
-    <t>[np.float64(797.0749307276899), np.float64(68.10992223860273)]</t>
-  </si>
-  <si>
-    <t>[np.float64(11.26137699095997), np.float64(75.15570429948673)]</t>
-  </si>
-  <si>
-    <t>[np.float64(423.42577911584567), np.float64(21.192824714832966)]</t>
-  </si>
-  <si>
-    <t>[np.float64(976.2812404324914), np.float64(91.31528623324078)]</t>
-  </si>
-  <si>
-    <t>[np.float64(369.372262975535), np.float64(30.776863592071038)]</t>
-  </si>
-  <si>
-    <t>[np.float64(170.2447308286783), np.float64(63.211097498654084)]</t>
-  </si>
-  <si>
-    <t>[np.float64(636.4623259960354), np.float64(-46.321224576649755)]</t>
-  </si>
-  <si>
-    <t>[np.float64(860.648766707796), np.float64(24.931309061088342)]</t>
-  </si>
-  <si>
-    <t>[np.float64(704.5874834640475), np.float64(42.60322624698327)]</t>
-  </si>
-  <si>
-    <t>[np.float64(175.61175906016013), np.float64(-64.893097894981)]</t>
-  </si>
-  <si>
-    <t>[np.float64(27.059712052157515), np.float64(21.676498962818712)]</t>
-  </si>
-  <si>
-    <t>[np.float64(56.3299384063497), np.float64(64.19037508971638)]</t>
-  </si>
-  <si>
-    <t>[np.float64(61.744007446712935), np.float64(5.859285285828662)]</t>
-  </si>
-  <si>
-    <t>[np.float64(164.68554777494748), np.float64(9.358521342263188)]</t>
-  </si>
-  <si>
-    <t>[np.float64(71.89581249592925), np.float64(75.61502629823843)]</t>
-  </si>
-  <si>
-    <t>[np.float64(662.7781550999304), np.float64(3.156655534393863)]</t>
-  </si>
-  <si>
-    <t>[np.float64(998.0740478487612), np.float64(48.81116825015616)]</t>
+    <t>[np.float64(973.4363607448389), np.float64(2.4217349122835685)]</t>
+  </si>
+  <si>
+    <t>[np.float64(220.7273968556427), np.float64(96.7098083483182)]</t>
+  </si>
+  <si>
+    <t>[np.float64(20.621332237053313), np.float64(-81.20271442698845)]</t>
+  </si>
+  <si>
+    <t>[np.float64(849.1171116947564), np.float64(23.577989924990675)]</t>
+  </si>
+  <si>
+    <t>[np.float64(105.91046187975562), np.float64(-88.22626930113364)]</t>
+  </si>
+  <si>
+    <t>[np.float64(499.2808611618721), np.float64(86.98879420499924)]</t>
+  </si>
+  <si>
+    <t>[np.float64(509.9115440620584), np.float64(45.2856171445346)]</t>
+  </si>
+  <si>
+    <t>[np.float64(946.8603522817564), np.float64(80.2687973248562)]</t>
+  </si>
+  <si>
+    <t>[np.float64(407.0664423537317), np.float64(29.010872562465096)]</t>
+  </si>
+  <si>
+    <t>[np.float64(967.4220604983602), np.float64(40.86130873659221)]</t>
+  </si>
+  <si>
+    <t>[np.float64(935.3153628082717), np.float64(-71.82524208487129)]</t>
+  </si>
+  <si>
+    <t>[np.float64(537.3031018656699), np.float64(-84.15795371026809)]</t>
+  </si>
+  <si>
+    <t>[np.float64(876.1248335546286), np.float64(70.20930429166731)]</t>
+  </si>
+  <si>
+    <t>[np.float64(900.7286693509297), np.float64(80.87257353534662)]</t>
+  </si>
+  <si>
+    <t>[np.float64(412.8912606314422), np.float64(-71.68771316642344)]</t>
+  </si>
+  <si>
+    <t>[np.float64(679.964407443432), np.float64(75.48324384764956)]</t>
+  </si>
+  <si>
+    <t>[np.float64(731.8714324598814), np.float64(97.72011851364829)]</t>
+  </si>
+  <si>
+    <t>[np.float64(889.6360992310415), np.float64(22.035296758003312)]</t>
+  </si>
+  <si>
+    <t>[np.float64(957.63054393257), np.float64(-98.94323281028761)]</t>
+  </si>
+  <si>
+    <t>[np.float64(53.65177467077675), np.float64(52.83069753226101)]</t>
+  </si>
+  <si>
+    <t>[np.float64(754.6919586567707), np.float64(-76.9786569601404)]</t>
+  </si>
+  <si>
+    <t>[np.float64(572.7797761128082), np.float64(88.36682688547145)]</t>
+  </si>
+  <si>
+    <t>[np.float64(694.1491231001163), np.float64(-87.81369842894544)]</t>
+  </si>
+  <si>
+    <t>[np.float64(153.8119527690146), np.float64(21.86829637019629)]</t>
+  </si>
+  <si>
+    <t>[np.float64(37.47149112400816), np.float64(16.985854103106107)]</t>
+  </si>
+  <si>
+    <t>[np.float64(819.0763334653254), np.float64(-85.11140169648803)]</t>
+  </si>
+  <si>
+    <t>[np.float64(58.82247020272713), np.float64(83.8999085444934)]</t>
+  </si>
+  <si>
+    <t>[np.float64(137.62278492138336), np.float64(89.46751128107536)]</t>
+  </si>
+  <si>
+    <t>[np.float64(868.6827118671522), np.float64(36.8970665208889)]</t>
+  </si>
+  <si>
+    <t>[np.float64(370.9482173387645), np.float64(-92.46723673847914)]</t>
+  </si>
+  <si>
+    <t>[np.float64(248.0005604614871), np.float64(61.06719355489426)]</t>
+  </si>
+  <si>
+    <t>[np.float64(937.1211646436338), np.float64(-41.76645835590631)]</t>
+  </si>
+  <si>
+    <t>[np.float64(629.1976714455025), np.float64(17.386062054753864)]</t>
+  </si>
+  <si>
+    <t>[np.float64(131.92859727383933), np.float64(-75.48849219567899)]</t>
+  </si>
+  <si>
+    <t>[np.float64(119.68554272498622), np.float64(69.58748122340523)]</t>
+  </si>
+  <si>
+    <t>[np.float64(617.7485811339394), np.float64(79.87223448776814)]</t>
+  </si>
+  <si>
+    <t>[np.float64(569.4896263232711), np.float64(-64.08212599860362)]</t>
+  </si>
+  <si>
+    <t>[np.float64(748.20615949158), np.float64(-91.02734783554982)]</t>
+  </si>
+  <si>
+    <t>[np.float64(595.9810914863523), np.float64(-89.0055139448616)]</t>
+  </si>
+  <si>
+    <t>[np.float64(892.0171290943636), np.float64(19.97856085395115)]</t>
+  </si>
+  <si>
+    <t>[np.float64(673.4615170169479), np.float64(97.41985096888635)]</t>
+  </si>
+  <si>
+    <t>[np.float64(156.1436775344417), np.float64(31.729434134650205)]</t>
+  </si>
+  <si>
+    <t>[np.float64(604.4100433067482), np.float64(-95.50968813336841)]</t>
+  </si>
+  <si>
+    <t>[np.float64(109.43206030305508), np.float64(49.48535298114268)]</t>
+  </si>
+  <si>
+    <t>[np.float64(339.935886691497), np.float64(98.97372377019312)]</t>
+  </si>
+  <si>
+    <t>[np.float64(622.0051885591507), np.float64(-94.24847832807242)]</t>
+  </si>
+  <si>
+    <t>[np.float64(756.7238012506566), np.float64(-0.9079069025193576)]</t>
+  </si>
+  <si>
+    <t>[np.float64(612.4183391072008), np.float64(8.840791980728909)]</t>
+  </si>
+  <si>
+    <t>[np.float64(980.3811614011219), np.float64(12.087734519806205)]</t>
+  </si>
+  <si>
+    <t>[np.float64(629.3187724586984), np.float64(92.66474917520222)]</t>
+  </si>
+  <si>
+    <t>[np.float64(519.5774505191459), np.float64(-55.52261799113858)]</t>
+  </si>
+  <si>
+    <t>[np.float64(58.88905534858313), np.float64(97.39684871366029)]</t>
+  </si>
+  <si>
+    <t>[np.float64(855.589111102049), np.float64(52.78651688953141)]</t>
+  </si>
+  <si>
+    <t>[np.float64(898.3789625502957), np.float64(99.16643727959305)]</t>
+  </si>
+  <si>
+    <t>[np.float64(628.4440378832013), np.float64(59.797058270977686)]</t>
+  </si>
+  <si>
+    <t>[np.float64(957.7310262227994), np.float64(80.24922546476105)]</t>
+  </si>
+  <si>
+    <t>[np.float64(51.90102395792706), np.float64(9.791531588481647)]</t>
+  </si>
+  <si>
+    <t>[np.float64(458.25519366960623), np.float64(90.75220045879524)]</t>
+  </si>
+  <si>
+    <t>[np.float64(507.35054235132895), np.float64(49.64339957433879)]</t>
+  </si>
+  <si>
+    <t>[np.float64(18.840600610778523), np.float64(51.36663226901595)]</t>
+  </si>
+  <si>
+    <t>[np.float64(351.0013891130419), np.float64(-55.75989794988148)]</t>
+  </si>
+  <si>
+    <t>[np.float64(135.7594081790001), np.float64(76.3476899997691)]</t>
+  </si>
+  <si>
+    <t>[np.float64(208.05523350993815), np.float64(-85.19036339021157)]</t>
+  </si>
+  <si>
+    <t>[np.float64(802.4880067918194), np.float64(-89.80550039952107)]</t>
+  </si>
+  <si>
+    <t>[np.float64(717.2573339691156), np.float64(35.55340719821751)]</t>
+  </si>
+  <si>
+    <t>[np.float64(876.2139852348698), np.float64(37.786159186818)]</t>
+  </si>
+  <si>
+    <t>[np.float64(732.8759518896875), np.float64(66.70205329770874)]</t>
+  </si>
+  <si>
+    <t>[np.float64(507.76328138313806), np.float64(5.284755945526598)]</t>
+  </si>
+  <si>
+    <t>[np.float64(203.85556734126976), np.float64(54.11489969880529)]</t>
+  </si>
+  <si>
+    <t>[np.float64(114.91640589374074), np.float64(96.86738104380214)]</t>
+  </si>
+  <si>
+    <t>[np.float64(942.5999527288908), np.float64(8.999348922260637)]</t>
+  </si>
+  <si>
+    <t>[np.float64(625.7933484337929), np.float64(66.54353979526442)]</t>
+  </si>
+  <si>
+    <t>[np.float64(381.3723279055601), np.float64(-94.85323255419857)]</t>
+  </si>
+  <si>
+    <t>[np.float64(855.1215037621749), np.float64(78.61330138962515)]</t>
+  </si>
+  <si>
+    <t>[np.float64(695.8119813901925), np.float64(88.3069667133536)]</t>
+  </si>
+  <si>
+    <t>[np.float64(324.64553237105366), np.float64(62.735510604601956)]</t>
+  </si>
+  <si>
+    <t>[np.float64(567.4010833117771), np.float64(25.1903903711344)]</t>
+  </si>
+  <si>
+    <t>[np.float64(212.93026046991938), np.float64(12.768138894765116)]</t>
+  </si>
+  <si>
+    <t>[np.float64(656.3537782622868), np.float64(-64.88165768203663)]</t>
+  </si>
+  <si>
+    <t>[np.float64(667.917636227347), np.float64(29.98375807627815)]</t>
+  </si>
+  <si>
+    <t>[np.float64(467.9546608162586), np.float64(79.43108362523532)]</t>
+  </si>
+  <si>
+    <t>[np.float64(989.4203901630007), np.float64(30.191760930181914)]</t>
+  </si>
+  <si>
+    <t>[np.float64(977.4573046689959), np.float64(-70.25306083706684)]</t>
+  </si>
+  <si>
+    <t>[np.float64(492.3568679408992), np.float64(7.619956786088906)]</t>
+  </si>
+  <si>
+    <t>[np.float64(993.824901593224), np.float64(46.50746479978994)]</t>
+  </si>
+  <si>
+    <t>[np.float64(541.6938807817959), np.float64(37.20912156431882)]</t>
+  </si>
+  <si>
+    <t>[np.float64(578.9177543259407), np.float64(28.552258727172358)]</t>
+  </si>
+  <si>
+    <t>[np.float64(994.7898534729919), np.float64(-40.327825331249215)]</t>
+  </si>
+  <si>
+    <t>[np.float64(943.6657119322341), np.float64(21.626197514097385)]</t>
+  </si>
+  <si>
+    <t>[np.float64(944.3465159339537), np.float64(-97.39062817688236)]</t>
+  </si>
+  <si>
+    <t>[np.float64(349.1757649421343), np.float64(-54.522994468530904)]</t>
+  </si>
+  <si>
+    <t>[np.float64(819.6874582942486), np.float64(71.5540510331349)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.337926563219737), np.float64(63.56532321878393)]</t>
+  </si>
+  <si>
+    <t>[np.float64(855.9597791198745), np.float64(-84.29378650547712)]</t>
+  </si>
+  <si>
+    <t>[np.float64(698.2322347586371), np.float64(-67.94051850364079)]</t>
+  </si>
+  <si>
+    <t>[np.float64(37.79034503446566), np.float64(70.66869086937052)]</t>
+  </si>
+  <si>
+    <t>[np.float64(960.8843490106918), np.float64(-80.5507750314112)]</t>
+  </si>
+  <si>
+    <t>[np.float64(266.26406632140356), np.float64(-88.88530053519712)]</t>
+  </si>
+  <si>
+    <t>[np.float64(645.3578074042226), np.float64(14.330055847357599)]</t>
+  </si>
+  <si>
+    <t>[np.float64(19.018328694297093), np.float64(31.50393782633816)]</t>
+  </si>
+  <si>
+    <t>[np.float64(796.3404591565351), np.float64(30.890877433210562)]</t>
+  </si>
+  <si>
+    <t>[np.float64(307.5350561854003), np.float64(84.66970433502448)]</t>
+  </si>
+  <si>
+    <t>[np.float64(385.05876234821756), np.float64(25.763603343534584)]</t>
+  </si>
+  <si>
+    <t>[np.float64(679.86839828577), np.float64(-86.01399917090784)]</t>
+  </si>
+  <si>
+    <t>[np.float64(388.0349509608506), np.float64(35.08327505256369)]</t>
+  </si>
+  <si>
+    <t>[np.float64(998.4412994463363), np.float64(61.49371400761436)]</t>
+  </si>
+  <si>
+    <t>[np.float64(98.05842490180162), np.float64(6.603335042302547)]</t>
+  </si>
+  <si>
+    <t>[np.float64(320.46058249732624), np.float64(8.140964686134325)]</t>
+  </si>
+  <si>
+    <t>[np.float64(177.2999139419369), np.float64(24.339630229261047)]</t>
+  </si>
+  <si>
+    <t>[np.float64(881.6427109488873), np.float64(10.225425481892287)]</t>
+  </si>
+  <si>
+    <t>[np.float64(284.2840170010371), np.float64(80.32580711629925)]</t>
+  </si>
+  <si>
+    <t>[np.float64(516.2852660439507), np.float64(-72.56026317330189)]</t>
+  </si>
+  <si>
+    <t>[np.float64(657.6191613351742), np.float64(84.80163818618587)]</t>
+  </si>
+  <si>
+    <t>[np.float64(642.1059989840523), np.float64(41.43891882893038)]</t>
+  </si>
+  <si>
+    <t>[np.float64(133.5054930643157), np.float64(-75.41002711132745)]</t>
+  </si>
+  <si>
+    <t>[np.float64(419.91821302537346), np.float64(-82.93706138517798)]</t>
+  </si>
+  <si>
+    <t>[np.float64(519.6542961581841), np.float64(-63.50729010712557)]</t>
+  </si>
+  <si>
+    <t>[np.float64(328.773126356191), np.float64(54.38770781483137)]</t>
+  </si>
+  <si>
+    <t>[np.float64(640.3067974895405), np.float64(74.20034298729755)]</t>
+  </si>
+  <si>
+    <t>[np.float64(70.23484866398466), np.float64(-92.14680833467229)]</t>
+  </si>
+  <si>
+    <t>[np.float64(487.2809098874439), np.float64(29.44344233337148)]</t>
+  </si>
+  <si>
+    <t>[np.float64(163.35262018842778), np.float64(14.928900215067856)]</t>
+  </si>
+  <si>
+    <t>[np.float64(494.16726761070487), np.float64(26.84790441739007)]</t>
+  </si>
+  <si>
+    <t>[np.float64(641.5957905815637), np.float64(-97.1772363078683)]</t>
+  </si>
+  <si>
+    <t>[np.float64(712.3311241921061), np.float64(87.20498750029196)]</t>
+  </si>
+  <si>
+    <t>[np.float64(119.94337634822571), np.float64(61.2801613234565)]</t>
+  </si>
+  <si>
+    <t>[np.float64(303.30004999995106), np.float64(-92.24881288168916)]</t>
+  </si>
+  <si>
+    <t>[np.float64(115.33583055663976), np.float64(92.73211824150178)]</t>
+  </si>
+  <si>
+    <t>[np.float64(650.5867996997817), np.float64(42.50468114431118)]</t>
+  </si>
+  <si>
+    <t>[np.float64(797.1921357026288), np.float64(23.183550198425593)]</t>
+  </si>
+  <si>
+    <t>[np.float64(511.85294397553184), np.float64(82.61288070177255)]</t>
+  </si>
+  <si>
+    <t>[np.float64(273.03537036900514), np.float64(-84.81040387545957)]</t>
+  </si>
+  <si>
+    <t>[np.float64(894.5338484120543), np.float64(68.93952305291958)]</t>
+  </si>
+  <si>
+    <t>[np.float64(876.1414620591219), np.float64(1.1413389612332736)]</t>
+  </si>
+  <si>
+    <t>[np.float64(88.96748511720808), np.float64(43.24618386821459)]</t>
+  </si>
+  <si>
+    <t>[np.float64(951.1410348448916), np.float64(48.83593856323674)]</t>
+  </si>
+  <si>
+    <t>[np.float64(549.6225714044656), np.float64(70.05972924564554)]</t>
+  </si>
+  <si>
+    <t>[np.float64(503.1593808962704), np.float64(70.92226923439867)]</t>
+  </si>
+  <si>
+    <t>[np.float64(916.6467441717546), np.float64(68.72004316711445)]</t>
+  </si>
+  <si>
+    <t>[np.float64(390.5983452542676), np.float64(-92.7847105376569)]</t>
+  </si>
+  <si>
+    <t>[np.float64(994.2487895143954), np.float64(4.320863923660866)]</t>
+  </si>
+  <si>
+    <t>[np.float64(709.8126221949393), np.float64(73.3900974338587)]</t>
+  </si>
+  <si>
+    <t>[np.float64(388.92760504719104), np.float64(60.137303660997304)]</t>
+  </si>
+  <si>
+    <t>[np.float64(316.1130377661806), np.float64(15.550461194458393)]</t>
+  </si>
+  <si>
+    <t>[np.float64(890.1900489316383), np.float64(19.105488294246626)]</t>
+  </si>
+  <si>
+    <t>[np.float64(554.0479250426914), np.float64(-94.23468910189044)]</t>
+  </si>
+  <si>
+    <t>[np.float64(314.4586897952016), np.float64(59.961170129087435)]</t>
+  </si>
+  <si>
+    <t>[np.float64(460.9222736600572), np.float64(-85.79084436040026)]</t>
+  </si>
+  <si>
+    <t>[np.float64(219.29390037142593), np.float64(16.345659890508983)]</t>
+  </si>
+  <si>
+    <t>[np.float64(636.3869956236739), np.float64(-35.466832487250954)]</t>
+  </si>
+  <si>
+    <t>[np.float64(931.4316678787104), np.float64(-90.50307315864575)]</t>
+  </si>
+  <si>
+    <t>[np.float64(563.3580460393416), np.float64(48.93567939563289)]</t>
+  </si>
+  <si>
+    <t>[np.float64(834.4758496480882), np.float64(21.616435677303826)]</t>
+  </si>
+  <si>
+    <t>[np.float64(406.9226671139199), np.float64(37.685291162205544)]</t>
+  </si>
+  <si>
+    <t>[np.float64(275.4930814961053), np.float64(-20.494783680711848)]</t>
+  </si>
+  <si>
+    <t>[np.float64(353.1230003882869), np.float64(39.62844578916861)]</t>
+  </si>
+  <si>
+    <t>[np.float64(197.00413594515774), np.float64(4.661656927286643)]</t>
+  </si>
+  <si>
+    <t>[np.float64(936.9288609495716), np.float64(-60.90593701200873)]</t>
+  </si>
+  <si>
+    <t>[np.float64(916.4882151957155), np.float64(-96.39159747093868)]</t>
+  </si>
+  <si>
+    <t>[np.float64(417.9084613535087), np.float64(-93.46321608302117)]</t>
+  </si>
+  <si>
+    <t>[np.float64(648.5415919699444), np.float64(40.60146714722654)]</t>
+  </si>
+  <si>
+    <t>[np.float64(884.2870763928136), np.float64(33.41696723702316)]</t>
+  </si>
+  <si>
+    <t>[np.float64(910.9691264318101), np.float64(49.73027845451182)]</t>
+  </si>
+  <si>
+    <t>[np.float64(225.1647678100459), np.float64(12.357924720725876)]</t>
+  </si>
+  <si>
+    <t>[np.float64(517.4018482822928), np.float64(90.44981911394126)]</t>
+  </si>
+  <si>
+    <t>[np.float64(391.0426491995337), np.float64(94.42868634833044)]</t>
+  </si>
+  <si>
+    <t>[np.float64(641.3516002963039), np.float64(61.143972143156844)]</t>
+  </si>
+  <si>
+    <t>[np.float64(748.8121209711737), np.float64(24.54886203674039)]</t>
+  </si>
+  <si>
+    <t>[np.float64(272.4609990577738), np.float64(27.61735616589796)]</t>
+  </si>
+  <si>
+    <t>[np.float64(936.4808987128584), np.float64(-72.96045496473332)]</t>
+  </si>
+  <si>
+    <t>[np.float64(60.43271189459843), np.float64(57.19227267753749)]</t>
+  </si>
+  <si>
+    <t>[np.float64(986.4579859913722), np.float64(-78.20457938630838)]</t>
+  </si>
+  <si>
+    <t>[np.float64(456.2675234961479), np.float64(-63.262022266830485)]</t>
+  </si>
+  <si>
+    <t>[np.float64(439.3919174161961), np.float64(47.278747583019)]</t>
+  </si>
+  <si>
+    <t>[np.float64(395.5022314376887), np.float64(89.50800111479538)]</t>
+  </si>
+  <si>
+    <t>[np.float64(13.9393935698231), np.float64(22.844722441088322)]</t>
+  </si>
+  <si>
+    <t>[np.float64(926.0046890644569), np.float64(77.4174465289259)]</t>
+  </si>
+  <si>
+    <t>[np.float64(70.19203115387963), np.float64(34.92267518683053)]</t>
+  </si>
+  <si>
+    <t>[np.float64(339.5568500986276), np.float64(-32.71022250840525)]</t>
+  </si>
+  <si>
+    <t>[np.float64(918.1980006285918), np.float64(28.39618301595192)]</t>
+  </si>
+  <si>
+    <t>[np.float64(326.04633311776973), np.float64(35.584798807241924)]</t>
+  </si>
+  <si>
+    <t>[np.float64(604.4019404004248), np.float64(33.72956540552988)]</t>
+  </si>
+  <si>
+    <t>[np.float64(189.30059884286288), np.float64(26.021505472498617)]</t>
+  </si>
+  <si>
+    <t>[np.float64(517.2098287144363), np.float64(90.83638247549658)]</t>
+  </si>
+  <si>
+    <t>[np.float64(778.7371606018261), np.float64(28.005329690004345)]</t>
+  </si>
+  <si>
+    <t>[np.float64(519.3595475544681), np.float64(-97.03630109172019)]</t>
+  </si>
+  <si>
+    <t>[np.float64(37.269622935867), np.float64(2.8733838476966582)]</t>
+  </si>
+  <si>
+    <t>[np.float64(567.531564700521), np.float64(7.243613211781479)]</t>
+  </si>
+  <si>
+    <t>[np.float64(103.4191874866065), np.float64(54.01578564839593)]</t>
+  </si>
+  <si>
+    <t>[np.float64(180.13980585121757), np.float64(64.58054243672063)]</t>
+  </si>
+  <si>
+    <t>[np.float64(70.86163539195877), np.float64(83.81054257317234)]</t>
+  </si>
+  <si>
+    <t>[np.float64(985.8458439795478), np.float64(-80.46927477916526)]</t>
+  </si>
+  <si>
+    <t>[np.float64(716.9281486661473), np.float64(-90.51305463666336)]</t>
+  </si>
+  <si>
+    <t>[np.float64(55.69770143005071), np.float64(62.66809742517307)]</t>
+  </si>
+  <si>
+    <t>[np.float64(38.688602746523195), np.float64(73.31412668001215)]</t>
+  </si>
+  <si>
+    <t>[np.float64(231.08208205297265), np.float64(2.876913155259416)]</t>
+  </si>
+  <si>
+    <t>[np.float64(95.83068636239022), np.float64(-63.42118988355663)]</t>
+  </si>
+  <si>
+    <t>[np.float64(511.1697351377488), np.float64(62.73765000452974)]</t>
+  </si>
+  <si>
+    <t>[np.float64(291.22173899553184), np.float64(-77.74437990061007)]</t>
+  </si>
+  <si>
+    <t>[np.float64(941.2498610989223), np.float64(76.44039220956967)]</t>
+  </si>
+  <si>
+    <t>[np.float64(354.2686915086853), np.float64(44.86620394739279)]</t>
+  </si>
+  <si>
+    <t>[np.float64(754.6589600862429), np.float64(-76.97719452290268)]</t>
+  </si>
+  <si>
+    <t>[np.float64(164.22980282757004), np.float64(-64.31549305313277)]</t>
+  </si>
+  <si>
+    <t>[np.float64(955.0915273266161), np.float64(-89.56032850026516)]</t>
+  </si>
+  <si>
+    <t>[np.float64(814.2954950608225), np.float64(-92.7285128798512)]</t>
+  </si>
+  <si>
+    <t>[np.float64(271.45695336903), np.float64(40.056087574329524)]</t>
+  </si>
+  <si>
+    <t>[np.float64(475.48492768487137), np.float64(64.71932578637333)]</t>
+  </si>
+  <si>
+    <t>[np.float64(322.2706558480734), np.float64(65.35735252519814)]</t>
+  </si>
+  <si>
+    <t>[np.float64(364.88706107936576), np.float64(43.40099635494772)]</t>
+  </si>
+  <si>
+    <t>[np.float64(369.8477711995962), np.float64(-89.61820879516969)]</t>
+  </si>
+  <si>
+    <t>[np.float64(83.12076878518471), np.float64(23.06618429275305)]</t>
+  </si>
+  <si>
+    <t>[np.float64(711.2196224970176), np.float64(-72.89839854837297)]</t>
+  </si>
+  <si>
+    <t>[np.float64(439.5497779364198), np.float64(-67.00190640520304)]</t>
+  </si>
+  <si>
+    <t>[np.float64(636.1421510369323), np.float64(64.27586199271863)]</t>
+  </si>
+  <si>
+    <t>[np.float64(935.3620521881153), np.float64(25.956592233355693)]</t>
+  </si>
+  <si>
+    <t>[np.float64(964.4613591756801), np.float64(31.990229272496094)]</t>
+  </si>
+  <si>
+    <t>[np.float64(655.1788525787143), np.float64(54.66983315934769)]</t>
+  </si>
+  <si>
+    <t>[np.float64(165.8778125666962), np.float64(-86.00912567515435)]</t>
+  </si>
+  <si>
+    <t>[np.float64(987.3026115688087), np.float64(45.64157371274297)]</t>
+  </si>
+  <si>
+    <t>[np.float64(392.05625287450107), np.float64(-56.922718493396296)]</t>
+  </si>
+  <si>
+    <t>[np.float64(234.65423246900176), np.float64(-96.81327165877636)]</t>
+  </si>
+  <si>
+    <t>[np.float64(699.9208084999558), np.float64(-8.807291803276044)]</t>
+  </si>
+  <si>
+    <t>[np.float64(199.54938867459217), np.float64(39.24856916952746)]</t>
+  </si>
+  <si>
+    <t>[np.float64(168.90348062254023), np.float64(-45.79881974235003)]</t>
+  </si>
+  <si>
+    <t>[np.float64(660.1120199908752), np.float64(31.368240263977697)]</t>
+  </si>
+  <si>
+    <t>[np.float64(536.1915507771375), np.float64(56.47023760604736)]</t>
+  </si>
+  <si>
+    <t>[np.float64(568.1724167455827), np.float64(39.80755181775842)]</t>
+  </si>
+  <si>
+    <t>[np.float64(722.2496237154352), np.float64(30.659100680104018)]</t>
+  </si>
+  <si>
+    <t>[np.float64(88.13608878977497), np.float64(97.83099752996614)]</t>
+  </si>
+  <si>
+    <t>[np.float64(672.9350882924774), np.float64(-71.34605120845006)]</t>
+  </si>
+  <si>
+    <t>[np.float64(551.1356308515798), np.float64(44.60085354006213)]</t>
+  </si>
+  <si>
+    <t>[np.float64(515.4020741546256), np.float64(93.89127560777183)]</t>
+  </si>
+  <si>
+    <t>[np.float64(99.73368525309867), np.float64(99.44069571980972)]</t>
+  </si>
+  <si>
+    <t>[np.float64(366.94134231415075), np.float64(39.57030179380533)]</t>
+  </si>
+  <si>
+    <t>[np.float64(854.4631779104034), np.float64(75.16951059463096)]</t>
+  </si>
+  <si>
+    <t>[np.float64(241.40528383286696), np.float64(89.34882087169382)]</t>
+  </si>
+  <si>
+    <t>[np.float64(253.61094343872338), np.float64(90.16554356468396)]</t>
+  </si>
+  <si>
+    <t>[np.float64(470.83067138093327), np.float64(60.9974377978113)]</t>
+  </si>
+  <si>
+    <t>[np.float64(420.43676093469276), np.float64(-84.03264154770085)]</t>
+  </si>
+  <si>
+    <t>[np.float64(731.6872140122333), np.float64(8.829943502540871)]</t>
+  </si>
+  <si>
+    <t>[np.float64(62.00946886274028), np.float64(72.20031466724609)]</t>
+  </si>
+  <si>
+    <t>[np.float64(307.72990157363745), np.float64(-49.0478203878834)]</t>
+  </si>
+  <si>
+    <t>[np.float64(586.1611857704054), np.float64(9.564033347811701)]</t>
+  </si>
+  <si>
+    <t>[np.float64(329.79432167965336), np.float64(97.960247823212)]</t>
+  </si>
+  <si>
+    <t>[np.float64(882.5759956316518), np.float64(41.84471718645085)]</t>
+  </si>
+  <si>
+    <t>[np.float64(122.34941154017964), np.float64(85.76603186999151)]</t>
+  </si>
+  <si>
+    <t>[np.float64(724.6481116788153), np.float64(95.42680988270922)]</t>
+  </si>
+  <si>
+    <t>[np.float64(40.0929714106828), np.float64(95.36413984400497)]</t>
+  </si>
+  <si>
+    <t>[np.float64(788.7894548384087), np.float64(29.568750261446837)]</t>
+  </si>
+  <si>
+    <t>[np.float64(596.0073573585039), np.float64(91.39104940877235)]</t>
+  </si>
+  <si>
+    <t>[np.float64(138.36329911854318), np.float64(-73.0644318799613)]</t>
+  </si>
+  <si>
+    <t>[np.float64(881.7874085614438), np.float64(68.10951726235749)]</t>
+  </si>
+  <si>
+    <t>[np.float64(662.825920931138), np.float64(-83.4540932011007)]</t>
+  </si>
+  <si>
+    <t>[np.float64(411.63627470769006), np.float64(-92.08356941926583)]</t>
+  </si>
+  <si>
+    <t>[np.float64(642.4019224770346), np.float64(46.55739014950194)]</t>
+  </si>
+  <si>
+    <t>[np.float64(509.07612486757967), np.float64(6.818592709584365)]</t>
+  </si>
+  <si>
+    <t>[np.float64(977.9965260374187), np.float64(8.046913046585487)]</t>
+  </si>
+  <si>
+    <t>[np.float64(979.1839350498487), np.float64(23.86410383290469)]</t>
+  </si>
+  <si>
+    <t>[np.float64(33.19648388049545), np.float64(-81.84908462273643)]</t>
+  </si>
+  <si>
+    <t>[np.float64(10.870144951764637), np.float64(95.60426083590116)]</t>
+  </si>
+  <si>
+    <t>[np.float64(497.5791167740666), np.float64(3.34061383532962)]</t>
+  </si>
+  <si>
+    <t>[np.float64(284.1774240124901), np.float64(4.455827877446225)]</t>
+  </si>
+  <si>
+    <t>[np.float64(891.3207686263704), np.float64(-73.50200583359717)]</t>
+  </si>
+  <si>
+    <t>[np.float64(436.9890642363231), np.float64(17.443393212897433)]</t>
+  </si>
+  <si>
+    <t>[np.float64(69.55444622639607), np.float64(-52.63513952870296)]</t>
+  </si>
+  <si>
+    <t>[np.float64(240.99858141632168), np.float64(74.79004087946868)]</t>
+  </si>
+  <si>
+    <t>[np.float64(889.724084252433), np.float64(35.25447519250059)]</t>
+  </si>
+  <si>
+    <t>[np.float64(268.87540397770437), np.float64(70.0061528877483)]</t>
+  </si>
+  <si>
+    <t>[np.float64(980.4381089629718), np.float64(83.35927122322971)]</t>
+  </si>
+  <si>
+    <t>[np.float64(835.8822266257741), np.float64(61.20017465863677)]</t>
+  </si>
+  <si>
+    <t>[np.float64(408.1246543523551), np.float64(76.78370376560645)]</t>
+  </si>
+  <si>
+    <t>[np.float64(988.5881462055632), np.float64(73.47584520354746)]</t>
+  </si>
+  <si>
+    <t>[np.float64(514.5865619493377), np.float64(-94.13341924629894)]</t>
+  </si>
+  <si>
+    <t>[np.float64(565.3278253383066), np.float64(75.18995139508039)]</t>
+  </si>
+  <si>
+    <t>[np.float64(465.6688837366426), np.float64(-99.35164189768845)]</t>
+  </si>
+  <si>
+    <t>[np.float64(484.51534245039187), np.float64(18.695234141006736)]</t>
+  </si>
+  <si>
+    <t>[np.float64(913.721873236967), np.float64(6.529370491589333)]</t>
+  </si>
+  <si>
+    <t>[np.float64(615.6356485930166), np.float64(89.69586708550099)]</t>
+  </si>
+  <si>
+    <t>[np.float64(59.45044375229824), np.float64(-93.9666803968964)]</t>
+  </si>
+  <si>
+    <t>[np.float64(681.8749681194214), np.float64(88.21394450836289)]</t>
+  </si>
+  <si>
+    <t>[np.float64(156.46831639730541), np.float64(-77.11909475536905)]</t>
+  </si>
+  <si>
+    <t>[np.float64(417.47038392262004), np.float64(6.206551233219827)]</t>
+  </si>
+  <si>
+    <t>[np.float64(676.0015228349876), np.float64(70.8562369889188)]</t>
+  </si>
+  <si>
+    <t>[np.float64(861.9114829527327), np.float64(69.66462289420531)]</t>
+  </si>
+  <si>
+    <t>[np.float64(406.104561344595), np.float64(91.92529476779598)]</t>
+  </si>
+  <si>
+    <t>[np.float64(519.4237612865901), np.float64(-47.73690287114607)]</t>
+  </si>
+  <si>
+    <t>[np.float64(445.3737744924957), np.float64(-42.35679204026566)]</t>
+  </si>
+  <si>
+    <t>[np.float64(649.4683935287788), np.float64(-91.23828155273732)]</t>
+  </si>
+  <si>
+    <t>[np.float64(596.2539841346193), np.float64(44.853808427308394)]</t>
+  </si>
+  <si>
+    <t>[np.float64(126.63732856635279), np.float64(43.20842178963346)]</t>
+  </si>
+  <si>
+    <t>[np.float64(882.933288261778), np.float64(29.200183091003396)]</t>
+  </si>
+  <si>
+    <t>[np.float64(68.59313326554218), np.float64(-93.3292836141774)]</t>
+  </si>
+  <si>
+    <t>[np.float64(396.4520341725992), np.float64(46.31416011476293)]</t>
+  </si>
+  <si>
+    <t>[np.float64(658.2849666628381), np.float64(32.44730477015827)]</t>
+  </si>
+  <si>
+    <t>[np.float64(428.2035417061516), np.float64(13.358113672033028)]</t>
+  </si>
+  <si>
+    <t>[np.float64(464.8734452427344), np.float64(-74.04954156615952)]</t>
+  </si>
+  <si>
+    <t>[np.float64(242.60554327116023), np.float64(69.35897121137117)]</t>
+  </si>
+  <si>
+    <t>[np.float64(929.8173397468682), np.float64(-72.66168082545059)]</t>
+  </si>
+  <si>
+    <t>[np.float64(430.24159773751757), np.float64(32.275723153262334)]</t>
+  </si>
+  <si>
+    <t>[np.float64(697.5772370335759), np.float64(94.55847509758038)]</t>
+  </si>
+  <si>
+    <t>[np.float64(46.9259172988683), np.float64(49.52261973916953)]</t>
+  </si>
+  <si>
+    <t>[np.float64(39.11450629923407), np.float64(15.982758704120087)]</t>
+  </si>
+  <si>
+    <t>[np.float64(197.64571876699577), np.float64(48.59148888598935)]</t>
+  </si>
+  <si>
+    <t>[np.float64(596.6385689298831), np.float64(-61.90848667379625)]</t>
+  </si>
+  <si>
+    <t>[np.float64(866.8827856675471), np.float64(13.756311075520074)]</t>
+  </si>
+  <si>
+    <t>[np.float64(638.7145222188361), np.float64(69.66153586698141)]</t>
+  </si>
+  <si>
+    <t>[np.float64(224.1697473146701), np.float64(27.972471844026956)]</t>
+  </si>
+  <si>
+    <t>[np.float64(365.359797601299), np.float64(-90.26938164146003)]</t>
+  </si>
+  <si>
+    <t>[np.float64(508.029947976409), np.float64(46.73024007995656)]</t>
+  </si>
+  <si>
+    <t>[np.float64(695.1165925499824), np.float64(-72.68831749409712)]</t>
+  </si>
+  <si>
+    <t>[np.float64(903.9874905995594), np.float64(61.87872573352837)]</t>
+  </si>
+  <si>
+    <t>[np.float64(627.2736414598), np.float64(37.494286925845415)]</t>
+  </si>
+  <si>
+    <t>[np.float64(907.6081342797842), np.float64(46.45780725798227)]</t>
+  </si>
+  <si>
+    <t>[np.float64(782.6084621947796), np.float64(50.514508225353154)]</t>
+  </si>
+  <si>
+    <t>[np.float64(462.22335026700733), np.float64(-71.46044636404113)]</t>
+  </si>
+  <si>
+    <t>[np.float64(884.9614820532913), np.float64(18.686584365224817)]</t>
+  </si>
+  <si>
+    <t>[np.float64(877.0607755847133), np.float64(-26.195421155041586)]</t>
+  </si>
+  <si>
+    <t>[np.float64(130.95126099210952), np.float64(27.746727469902922)]</t>
+  </si>
+  <si>
+    <t>[np.float64(62.85401072698193), np.float64(6.376146985911973)]</t>
+  </si>
+  <si>
+    <t>[np.float64(32.57148622938566), np.float64(62.122520646896106)]</t>
+  </si>
+  <si>
+    <t>[np.float64(649.6724836173105), np.float64(26.50526570755325)]</t>
+  </si>
+  <si>
+    <t>[np.float64(334.55754994919783), np.float64(91.10806832877344)]</t>
+  </si>
+  <si>
+    <t>[np.float64(648.2340730877758), np.float64(5.694260440164186)]</t>
+  </si>
+  <si>
+    <t>[np.float64(930.4784784920179), np.float64(-91.74974115919696)]</t>
+  </si>
+  <si>
+    <t>[np.float64(311.54397422962234), np.float64(40.70559607457142)]</t>
+  </si>
+  <si>
+    <t>[np.float64(968.7017073778962), np.float64(17.378099305323147)]</t>
+  </si>
+  <si>
+    <t>[np.float64(128.55096925066957), np.float64(78.33709511513806)]</t>
+  </si>
+  <si>
+    <t>[np.float64(753.8427665843346), np.float64(-61.81416911559317)]</t>
+  </si>
+  <si>
+    <t>[np.float64(124.88647076572413), np.float64(66.3355989407344)]</t>
+  </si>
+  <si>
+    <t>[np.float64(556.1050728858822), np.float64(64.68387441100265)]</t>
+  </si>
+  <si>
+    <t>[np.float64(590.4847031043373), np.float64(76.21376194794061)]</t>
+  </si>
+  <si>
+    <t>[np.float64(868.0998081077689), np.float64(18.706262501231237)]</t>
+  </si>
+  <si>
+    <t>[np.float64(943.6843807464899), np.float64(28.221500288554694)]</t>
+  </si>
+  <si>
+    <t>[np.float64(875.2642241455526), np.float64(-92.01161002554545)]</t>
+  </si>
+  <si>
+    <t>[np.float64(680.6432375982943), np.float64(35.680589238691454)]</t>
+  </si>
+  <si>
+    <t>[np.float64(478.6943638890758), np.float64(38.96871812415853)]</t>
+  </si>
+  <si>
+    <t>[np.float64(96.48203607894767), np.float64(-93.58337266856644)]</t>
+  </si>
+  <si>
+    <t>[np.float64(593.6223496125409), np.float64(24.980510394503995)]</t>
+  </si>
+  <si>
+    <t>[np.float64(779.7869692846874), np.float64(11.11841949438461)]</t>
+  </si>
+  <si>
+    <t>[np.float64(498.6853716800073), np.float64(57.345436502185834)]</t>
+  </si>
+  <si>
+    <t>[np.float64(267.4572074624246), np.float64(1.3645263521457025)]</t>
+  </si>
+  <si>
+    <t>[np.float64(733.8467021456448), np.float64(24.622456395074593)]</t>
+  </si>
+  <si>
+    <t>[np.float64(957.1039836977451), np.float64(38.40480597911258)]</t>
+  </si>
+  <si>
+    <t>[np.float64(544.027643892873), np.float64(-36.76445207122849)]</t>
+  </si>
+  <si>
+    <t>[np.float64(358.52009921772907), np.float64(62.38786058831448)]</t>
+  </si>
+  <si>
+    <t>[np.float64(703.651877338499), np.float64(60.89323593806958)]</t>
+  </si>
+  <si>
+    <t>[np.float64(353.60117251652423), np.float64(93.77081336091061)]</t>
+  </si>
+  <si>
+    <t>[np.float64(807.3272112206494), np.float64(-91.03534953221097)]</t>
+  </si>
+  <si>
+    <t>[np.float64(765.4569409515999), np.float64(54.43873197844553)]</t>
+  </si>
+  <si>
+    <t>[np.float64(410.9933550997531), np.float64(9.381448861653325)]</t>
+  </si>
+  <si>
+    <t>[np.float64(25.137514344145572), np.float64(10.543797195613422)]</t>
+  </si>
+  <si>
+    <t>[np.float64(281.17111516634), np.float64(53.29974591521548)]</t>
+  </si>
+  <si>
+    <t>[np.float64(861.6496506727585), np.float64(18.87761177138681)]</t>
+  </si>
+  <si>
+    <t>[np.float64(477.85139043764843), np.float64(46.44429669278418)]</t>
+  </si>
+  <si>
+    <t>[np.float64(126.2333688683267), np.float64(59.211093250701595)]</t>
+  </si>
+  <si>
+    <t>[np.float64(150.6422483033282), np.float64(97.54474858710472)]</t>
+  </si>
+  <si>
+    <t>[np.float64(129.42693661242077), np.float64(18.872833229773462)]</t>
+  </si>
+  <si>
+    <t>[np.float64(305.5503164553035), np.float64(16.652196170656055)]</t>
+  </si>
+  <si>
+    <t>[np.float64(799.5522561416907), np.float64(-99.23071447572534)]</t>
+  </si>
+  <si>
+    <t>[np.float64(479.89287949810966), np.float64(59.055039447173925)]</t>
+  </si>
+  <si>
+    <t>[np.float64(999.4968962757357), np.float64(-80.26772107105009)]</t>
+  </si>
+  <si>
+    <t>[np.float64(914.9077074815386), np.float64(50.12166398410031)]</t>
+  </si>
+  <si>
+    <t>[np.float64(399.72154826037365), np.float64(-84.43006380901943)]</t>
+  </si>
+  <si>
+    <t>[np.float64(601.0179078894666), np.float64(-73.9038514677853)]</t>
+  </si>
+  <si>
+    <t>[np.float64(90.8270200215383), np.float64(-71.25330975916899)]</t>
+  </si>
+  <si>
+    <t>[np.float64(348.79604987739674), np.float64(-69.24170606220268)]</t>
+  </si>
+  <si>
+    <t>[np.float64(220.31222732865675), np.float64(39.355518809991565)]</t>
+  </si>
+  <si>
+    <t>[np.float64(326.79847308181655), np.float64(-82.61418615857185)]</t>
+  </si>
+  <si>
+    <t>[np.float64(903.0688558332256), np.float64(48.12781299338823)]</t>
+  </si>
+  <si>
+    <t>[np.float64(357.98309871599434), np.float64(2.3400069107397883)]</t>
+  </si>
+  <si>
+    <t>[np.float64(123.30270525891318), np.float64(-99.83835549053939)]</t>
+  </si>
+  <si>
+    <t>[np.float64(974.166048956474), np.float64(6.397207922081648)]</t>
+  </si>
+  <si>
+    <t>[np.float64(715.7294567785323), np.float64(-75.1334947533725)]</t>
+  </si>
+  <si>
+    <t>[np.float64(996.3131715453565), np.float64(-93.85369456091637)]</t>
+  </si>
+  <si>
+    <t>[np.float64(264.10874601726607), np.float64(61.0668528937106)]</t>
+  </si>
+  <si>
+    <t>[np.float64(685.8432380292425), np.float64(86.84362575561411)]</t>
+  </si>
+  <si>
+    <t>[np.float64(554.3830831678323), np.float64(80.78345356567547)]</t>
+  </si>
+  <si>
+    <t>[np.float64(915.0890433708429), np.float64(70.57081129623398)]</t>
+  </si>
+  <si>
+    <t>[np.float64(817.9282046818394), np.float64(21.554832837509792)]</t>
+  </si>
+  <si>
+    <t>[np.float64(373.91771431497347), np.float64(44.40308960972558)]</t>
+  </si>
+  <si>
+    <t>[np.float64(155.55371513964843), np.float64(35.001982517662185)]</t>
+  </si>
+  <si>
+    <t>[np.float64(848.6409527899534), np.float64(-67.45932305220529)]</t>
+  </si>
+  <si>
+    <t>[np.float64(574.7779187873695), np.float64(-67.32837196841355)]</t>
+  </si>
+  <si>
+    <t>[np.float64(208.2817861978137), np.float64(53.94725314469434)]</t>
+  </si>
+  <si>
+    <t>[np.float64(53.738536016014415), np.float64(28.1533314591168)]</t>
+  </si>
+  <si>
+    <t>[np.float64(22.314328494724922), np.float64(-57.97681173571021)]</t>
+  </si>
+  <si>
+    <t>[np.float64(113.18956744101017), np.float64(-78.70699452140107)]</t>
+  </si>
+  <si>
+    <t>[np.float64(301.34276232360145), np.float64(-89.8500027614098)]</t>
+  </si>
+  <si>
+    <t>[np.float64(155.89573575090154), np.float64(-45.130436879942316)]</t>
+  </si>
+  <si>
+    <t>[np.float64(631.9622770724487), np.float64(-79.20152105341921)]</t>
+  </si>
+  <si>
+    <t>[np.float64(494.2666230840006), np.float64(99.0587692223217)]</t>
+  </si>
+  <si>
+    <t>[np.float64(375.27194913518), np.float64(49.57145040151008)]</t>
+  </si>
+  <si>
+    <t>[np.float64(834.711910096551), np.float64(96.73510438632002)]</t>
+  </si>
+  <si>
+    <t>[np.float64(669.2424983136585), np.float64(36.630752823869244)]</t>
+  </si>
+  <si>
+    <t>[np.float64(792.636998675927), np.float64(-81.7116859767139)]</t>
+  </si>
+  <si>
+    <t>[np.float64(994.5083103988185), np.float64(91.506030301974)]</t>
+  </si>
+  <si>
+    <t>[np.float64(699.5807242406448), np.float64(21.52472336169194)]</t>
+  </si>
+  <si>
+    <t>[np.float64(853.1665940841932), np.float64(12.19194492751059)]</t>
+  </si>
+  <si>
+    <t>[np.float64(50.16659535556711), np.float64(38.833463728447924)]</t>
+  </si>
+  <si>
+    <t>[np.float64(483.857709696046), np.float64(-29.3518510036958)]</t>
+  </si>
+  <si>
+    <t>[np.float64(120.64904253578356), np.float64(57.85664361658971)]</t>
+  </si>
+  <si>
+    <t>[np.float64(821.3715651780713), np.float64(49.223007188218105)]</t>
+  </si>
+  <si>
+    <t>[np.float64(995.5148000195635), np.float64(29.320507002294022)]</t>
+  </si>
+  <si>
+    <t>[np.float64(920.9016421892487), np.float64(56.876736315650476)]</t>
+  </si>
+  <si>
+    <t>[np.float64(837.70708558928), np.float64(68.62363354801147)]</t>
+  </si>
+  <si>
+    <t>[np.float64(517.6422196139023), np.float64(-55.707582553053015)]</t>
+  </si>
+  <si>
+    <t>[np.float64(866.2781383446329), np.float64(96.07044716365044)]</t>
+  </si>
+  <si>
+    <t>[np.float64(784.0211583291639), np.float64(-91.63321118112282)]</t>
+  </si>
+  <si>
+    <t>[np.float64(661.3071187713153), np.float64(94.49942773621359)]</t>
+  </si>
+  <si>
+    <t>[np.float64(448.1006662698196), np.float64(37.86711740965691)]</t>
+  </si>
+  <si>
+    <t>[np.float64(339.89720716045645), np.float64(-23.544070164072977)]</t>
+  </si>
+  <si>
+    <t>[np.float64(637.0852122109686), np.float64(-1.0105163651242322)]</t>
+  </si>
+  <si>
+    <t>[np.float64(804.9552730882823), np.float64(18.389886483315237)]</t>
+  </si>
+  <si>
+    <t>[np.float64(140.2071627594822), np.float64(27.557222202820824)]</t>
+  </si>
+  <si>
+    <t>[np.float64(158.55393510976478), np.float64(-35.118810991591644)]</t>
+  </si>
+  <si>
+    <t>[np.float64(146.0700328855271), np.float64(70.35010761378368)]</t>
+  </si>
+  <si>
+    <t>[np.float64(774.0481107653623), np.float64(-90.50818366940535)]</t>
+  </si>
+  <si>
+    <t>[np.float64(997.9322360834608), np.float64(38.15043170901441)]</t>
+  </si>
+  <si>
+    <t>[np.float64(85.67877378494282), np.float64(-53.22823821605829)]</t>
+  </si>
+  <si>
+    <t>[np.float64(130.06742429414143), np.float64(21.563998335643532)]</t>
+  </si>
+  <si>
+    <t>[np.float64(798.1792043489339), np.float64(87.07885022604177)]</t>
+  </si>
+  <si>
+    <t>[np.float64(15.54456862303133), np.float64(-60.82290432879649)]</t>
+  </si>
+  <si>
+    <t>[np.float64(314.56846505555893), np.float64(22.29055785531726)]</t>
+  </si>
+  <si>
+    <t>[np.float64(257.51885888627015), np.float64(-89.08198189590641)]</t>
+  </si>
+  <si>
+    <t>[np.float64(988.0373452874339), np.float64(47.063334182466434)]</t>
+  </si>
+  <si>
+    <t>[np.float64(276.47725110465507), np.float64(7.289223450940099)]</t>
+  </si>
+  <si>
+    <t>[np.float64(969.6449731633288), np.float64(69.05910682704089)]</t>
+  </si>
+  <si>
+    <t>[np.float64(240.905620594446), np.float64(-93.244601145068)]</t>
+  </si>
+  <si>
+    <t>[np.float64(233.82273393818775), np.float64(37.56174194388174)]</t>
+  </si>
+  <si>
+    <t>[np.float64(282.7697988342089), np.float64(32.07957402467369)]</t>
+  </si>
+  <si>
+    <t>[np.float64(95.26780958761671), np.float64(87.046226369364)]</t>
+  </si>
+  <si>
+    <t>[np.float64(738.7374577329622), np.float64(68.28956540548353)]</t>
+  </si>
+  <si>
+    <t>[np.float64(435.3704400737668), np.float64(43.212738103599264)]</t>
+  </si>
+  <si>
+    <t>[np.float64(151.58647092184097), np.float64(69.56158165842069)]</t>
+  </si>
+  <si>
+    <t>[np.float64(330.8421312030103), np.float64(68.22413297582972)]</t>
+  </si>
+  <si>
+    <t>[np.float64(316.6453208461266), np.float64(36.7337020630637)]</t>
+  </si>
+  <si>
+    <t>[np.float64(657.5272255274915), np.float64(-54.16912547440609)]</t>
+  </si>
+  <si>
+    <t>[np.float64(560.233307050822), np.float64(18.802907028977984)]</t>
+  </si>
+  <si>
+    <t>[np.float64(516.581986864741), np.float64(-60.150876180565895)]</t>
+  </si>
+  <si>
+    <t>[np.float64(521.2306032479956), np.float64(11.423620011033947)]</t>
+  </si>
+  <si>
+    <t>[np.float64(691.1530337268083), np.float64(32.54317765725901)]</t>
+  </si>
+  <si>
+    <t>[np.float64(184.68713048331585), np.float64(78.18361241813548)]</t>
+  </si>
+  <si>
+    <t>[np.float64(211.3385752230833), np.float64(14.74339700339597)]</t>
+  </si>
+  <si>
+    <t>[np.float64(825.6143951327563), np.float64(77.27889172111637)]</t>
+  </si>
+  <si>
+    <t>[np.float64(215.31085238142268), np.float64(55.58037447829304)]</t>
+  </si>
+  <si>
+    <t>[np.float64(628.4208001635325), np.float64(21.399695544585825)]</t>
+  </si>
+  <si>
+    <t>[np.float64(63.28572026639445), np.float64(75.83157634857596)]</t>
+  </si>
+  <si>
+    <t>[np.float64(523.8767486244498), np.float64(-93.50784055113725)]</t>
+  </si>
+  <si>
+    <t>[np.float64(997.1913473872122), np.float64(-88.9461866380054)]</t>
+  </si>
+  <si>
+    <t>[np.float64(101.75206067874353), np.float64(-76.80659345062517)]</t>
+  </si>
+  <si>
+    <t>[np.float64(763.4672682383674), np.float64(-82.4381307432867)]</t>
+  </si>
+  <si>
+    <t>[np.float64(147.23488372682348), np.float64(38.82572295680313)]</t>
+  </si>
+  <si>
+    <t>[np.float64(120.0803637448592), np.float64(65.58808452707689)]</t>
+  </si>
+  <si>
+    <t>[np.float64(34.208174726842785), np.float64(79.94722395633778)]</t>
+  </si>
+  <si>
+    <t>[np.float64(822.5875370193467), np.float64(87.9099905817746)]</t>
+  </si>
+  <si>
+    <t>[np.float64(591.2819317868577), np.float64(-94.323818574592)]</t>
+  </si>
+  <si>
+    <t>[np.float64(906.8856614556615), np.float64(90.44029782351905)]</t>
+  </si>
+  <si>
+    <t>[np.float64(137.62928600195423), np.float64(84.95571445574461)]</t>
+  </si>
+  <si>
+    <t>[np.float64(956.6785053362432), np.float64(82.68494587418209)]</t>
+  </si>
+  <si>
+    <t>[np.float64(246.42334032869772), np.float64(43.39466026520225)]</t>
+  </si>
+  <si>
+    <t>[np.float64(980.9375842029959), np.float64(66.8853468063331)]</t>
+  </si>
+  <si>
+    <t>[np.float64(870.1599417733754), np.float64(9.530641761513522)]</t>
+  </si>
+  <si>
+    <t>[np.float64(21.380558158124565), np.float64(81.21450585401374)]</t>
+  </si>
+  <si>
+    <t>[np.float64(293.45677035632644), np.float64(58.78349479800883)]</t>
+  </si>
+  <si>
+    <t>[np.float64(20.169506335026565), np.float64(-65.98095748777604)]</t>
+  </si>
+  <si>
+    <t>[np.float64(831.7406423820358), np.float64(-61.389153391174474)]</t>
+  </si>
+  <si>
+    <t>[np.float64(406.14386585729943), np.float64(7.983812160904165)]</t>
+  </si>
+  <si>
+    <t>[np.float64(606.9590033384072), np.float64(-58.92042471579468)]</t>
+  </si>
+  <si>
+    <t>[np.float64(361.69827062392676), np.float64(0.3525334272122649)]</t>
+  </si>
+  <si>
+    <t>[np.float64(230.9479776308949), np.float64(74.88667076699491)]</t>
+  </si>
+  <si>
+    <t>[np.float64(433.02864763661574), np.float64(-72.1952185372881)]</t>
+  </si>
+  <si>
+    <t>[np.float64(40.598210099470734), np.float64(59.866893349065066)]</t>
+  </si>
+  <si>
+    <t>[np.float64(872.0483606986655), np.float64(29.064666487201492)]</t>
+  </si>
+  <si>
+    <t>[np.float64(161.34762050623564), np.float64(52.750788366627006)]</t>
+  </si>
+  <si>
+    <t>[np.float64(341.22656177814383), np.float64(98.80058980937318)]</t>
+  </si>
+  <si>
+    <t>[np.float64(116.16898450757895), np.float64(-95.66558855640804)]</t>
+  </si>
+  <si>
+    <t>[np.float64(182.46215167729707), np.float64(-70.37845013895216)]</t>
+  </si>
+  <si>
+    <t>[np.float64(986.9806806252001), np.float64(5.422468724621623)]</t>
+  </si>
+  <si>
+    <t>[np.float64(324.91036040907784), np.float64(-75.1222925202006)]</t>
+  </si>
+  <si>
+    <t>[np.float64(865.2289620481127), np.float64(84.5731313265901)]</t>
+  </si>
+  <si>
+    <t>[np.float64(829.7271845683839), np.float64(40.90370844212461)]</t>
+  </si>
+  <si>
+    <t>[np.float64(187.80577299663526), np.float64(39.74628627281248)]</t>
+  </si>
+  <si>
+    <t>[np.float64(892.5042022815591), np.float64(76.18907717675859)]</t>
+  </si>
+  <si>
+    <t>[np.float64(648.2689855956392), np.float64(53.24291434213754)]</t>
+  </si>
+  <si>
+    <t>[np.float64(836.2182876010967), np.float64(60.765652515010856)]</t>
+  </si>
+  <si>
+    <t>[np.float64(864.6073409055357), np.float64(30.363529896443367)]</t>
+  </si>
+  <si>
+    <t>[np.float64(532.7757413086213), np.float64(67.62087576764614)]</t>
+  </si>
+  <si>
+    <t>[np.float64(495.03096782907), np.float64(-67.19420987955478)]</t>
+  </si>
+  <si>
+    <t>[np.float64(740.1495776800064), np.float64(-59.69327496474026)]</t>
+  </si>
+  <si>
+    <t>[np.float64(578.9331163188363), np.float64(87.89092909856825)]</t>
+  </si>
+  <si>
+    <t>[np.float64(360.0127392968472), np.float64(37.19716225371516)]</t>
+  </si>
+  <si>
+    <t>[np.float64(302.69461858561755), np.float64(28.09324184379605)]</t>
+  </si>
+  <si>
+    <t>[np.float64(993.0780333733424), np.float64(16.102190731963702)]</t>
+  </si>
+  <si>
+    <t>[np.float64(701.4284908822802), np.float64(42.22612620130366)]</t>
+  </si>
+  <si>
+    <t>[np.float64(156.52128841368375), np.float64(24.14476961018424)]</t>
+  </si>
+  <si>
+    <t>[np.float64(183.5928306683433), np.float64(98.51458378051547)]</t>
+  </si>
+  <si>
+    <t>[np.float64(8.339411196032763), np.float64(1.5813261162525265)]</t>
+  </si>
+  <si>
+    <t>[np.float64(743.6079998213072), np.float64(43.25482525550237)]</t>
+  </si>
+  <si>
+    <t>[np.float64(163.99303787358542), np.float64(45.84275473024985)]</t>
+  </si>
+  <si>
+    <t>[np.float64(451.69907690212284), np.float64(12.752739027890982)]</t>
+  </si>
+  <si>
+    <t>[np.float64(945.5898060845703), np.float64(76.65496827666038)]</t>
+  </si>
+  <si>
+    <t>[np.float64(683.1162891058673), np.float64(79.9339151648326)]</t>
+  </si>
+  <si>
+    <t>[np.float64(235.59935167310053), np.float64(50.95817690865073)]</t>
+  </si>
+  <si>
+    <t>[np.float64(240.41349638471087), np.float64(-82.16049563697463)]</t>
+  </si>
+  <si>
+    <t>[np.float64(824.3596915728235), np.float64(74.73076920596358)]</t>
+  </si>
+  <si>
+    <t>[np.float64(108.41376768376365), np.float64(41.556027498626605)]</t>
+  </si>
+  <si>
+    <t>[np.float64(971.4567683605778), np.float64(78.43606975710259)]</t>
+  </si>
+  <si>
+    <t>[np.float64(456.1257084975021), np.float64(30.45097875944373)]</t>
+  </si>
+  <si>
+    <t>[np.float64(169.4116246664391), np.float64(75.74162558470982)]</t>
+  </si>
+  <si>
+    <t>[np.float64(281.1477172618809), np.float64(82.14023269798574)]</t>
+  </si>
+  <si>
+    <t>[np.float64(400.93663788578215), np.float64(20.50436521222818)]</t>
+  </si>
+  <si>
+    <t>[np.float64(677.1279495006786), np.float64(10.355035261293352)]</t>
+  </si>
+  <si>
+    <t>[np.float64(33.70340736777566), np.float64(34.69709704821733)]</t>
+  </si>
+  <si>
+    <t>[np.float64(571.4116134813685), np.float64(1.8346998892412785)]</t>
+  </si>
+  <si>
+    <t>[np.float64(299.68548567842447), np.float64(64.53878497967415)]</t>
+  </si>
+  <si>
+    <t>[np.float64(52.03315246552498), np.float64(79.06043820764918)]</t>
+  </si>
+  <si>
+    <t>[np.float64(956.7898826205262), np.float64(28.24602465719113)]</t>
+  </si>
+  <si>
+    <t>[np.float64(515.5009985121225), np.float64(35.79761886915213)]</t>
+  </si>
+  <si>
+    <t>[np.float64(289.7242993206147), np.float64(92.68299524860868)]</t>
+  </si>
+  <si>
+    <t>[np.float64(740.4431518768947), np.float64(99.55950880543861)]</t>
+  </si>
+  <si>
+    <t>[np.float64(627.0687391205377), np.float64(79.92760887614273)]</t>
+  </si>
+  <si>
+    <t>[np.float64(376.3928629258342), np.float64(96.36826717252077)]</t>
+  </si>
+  <si>
+    <t>[np.float64(482.1539193734591), np.float64(-87.4155774658216)]</t>
+  </si>
+  <si>
+    <t>[np.float64(726.4283257011427), np.float64(-75.9342327102058)]</t>
+  </si>
+  <si>
+    <t>[np.float64(513.2053885665825), np.float64(-47.60466004856987)]</t>
+  </si>
+  <si>
+    <t>[np.float64(817.5059723648795), np.float64(-90.95504695055969)]</t>
+  </si>
+  <si>
+    <t>[np.float64(420.7731378924773), np.float64(-76.3467644034159)]</t>
+  </si>
+  <si>
+    <t>[np.float64(143.75031585806153), np.float64(39.715722172186815)]</t>
+  </si>
+  <si>
+    <t>[np.float64(634.5620007976805), np.float64(-57.15244661927641)]</t>
+  </si>
+  <si>
+    <t>[np.float64(264.18299129427857), np.float64(62.67416941792135)]</t>
+  </si>
+  <si>
+    <t>[np.float64(537.9315319086185), np.float64(21.156810866614336)]</t>
+  </si>
+  <si>
+    <t>[np.float64(658.7749097927029), np.float64(76.3219071714046)]</t>
+  </si>
+  <si>
+    <t>[np.float64(682.7219069652798), np.float64(26.400900033840728)]</t>
+  </si>
+  <si>
+    <t>[np.float64(423.24247183956464), np.float64(81.43277172855107)]</t>
+  </si>
+  <si>
+    <t>[np.float64(562.481126754411), np.float64(60.686404384757196)]</t>
+  </si>
+  <si>
+    <t>[np.float64(731.2953008010071), np.float64(-76.42359948650167)]</t>
+  </si>
+  <si>
+    <t>[np.float64(144.8114748223106), np.float64(17.901018220188945)]</t>
+  </si>
+  <si>
+    <t>[np.float64(415.4202158716829), np.float64(49.35363255809958)]</t>
+  </si>
+  <si>
+    <t>[np.float64(89.92941515316755), np.float64(22.621774940709784)]</t>
+  </si>
+  <si>
+    <t>[np.float64(943.7675975793223), np.float64(29.300572732942328)]</t>
+  </si>
+  <si>
+    <t>[np.float64(341.07686041545924), np.float64(-89.02088265825338)]</t>
+  </si>
+  <si>
+    <t>[np.float64(986.9402085552539), np.float64(59.64690033868959)]</t>
+  </si>
+  <si>
+    <t>[np.float64(872.9938120594998), np.float64(9.842233842226491)]</t>
+  </si>
+  <si>
+    <t>[np.float64(11.779089659882281), np.float64(33.70464446847643)]</t>
+  </si>
+  <si>
+    <t>[np.float64(796.9157649895881), np.float64(55.453894159772034)]</t>
+  </si>
+  <si>
+    <t>[np.float64(719.6926519061942), np.float64(-38.72078684618883)]</t>
+  </si>
+  <si>
+    <t>[np.float64(330.4051417568048), np.float64(56.47101075782027)]</t>
+  </si>
+  <si>
+    <t>[np.float64(98.74366586369376), np.float64(5.875815204412831)]</t>
+  </si>
+  <si>
+    <t>[np.float64(442.55794621604696), np.float64(75.04240950649174)]</t>
+  </si>
+  <si>
+    <t>[np.float64(238.82373715174953), np.float64(75.78905033090726)]</t>
+  </si>
+  <si>
+    <t>[np.float64(907.1265250363396), np.float64(97.58059656274986)]</t>
+  </si>
+  <si>
+    <t>[np.float64(686.2671837958499), np.float64(88.22488900901897)]</t>
+  </si>
+  <si>
+    <t>[np.float64(256.2327711459369), np.float64(80.65046979601175)]</t>
+  </si>
+  <si>
+    <t>[np.float64(836.0864239988498), np.float64(21.14823188233224)]</t>
+  </si>
+  <si>
+    <t>[np.float64(83.03509456594082), np.float64(34.54598741712792)]</t>
+  </si>
+  <si>
+    <t>[np.float64(983.2715000957512), np.float64(83.97831240311464)]</t>
+  </si>
+  <si>
+    <t>[np.float64(867.2560375892448), np.float64(39.9975580511086)]</t>
+  </si>
+  <si>
+    <t>[np.float64(795.5461627180628), np.float64(-94.7336117100932)]</t>
+  </si>
+  <si>
+    <t>[np.float64(677.2866088266978), np.float64(30.92260882040341)]</t>
+  </si>
+  <si>
+    <t>[np.float64(153.8355267519319), np.float64(59.113850943698736)]</t>
+  </si>
+  <si>
+    <t>[np.float64(941.9311587449546), np.float64(52.229886633024364)]</t>
+  </si>
+  <si>
+    <t>[np.float64(315.9907452023266), np.float64(72.56756057126975)]</t>
+  </si>
+  <si>
+    <t>[np.float64(101.32605572660968), np.float64(95.3805909858109)]</t>
+  </si>
+  <si>
+    <t>[np.float64(652.0780005501638), np.float64(22.664172669095947)]</t>
+  </si>
+  <si>
+    <t>[np.float64(173.78442739844678), np.float64(-66.85510856071988)]</t>
+  </si>
+  <si>
+    <t>[np.float64(464.5825704017403), np.float64(59.81902675640907)]</t>
+  </si>
+  <si>
+    <t>[np.float64(215.871217020836), np.float64(22.10483231851761)]</t>
+  </si>
+  <si>
+    <t>[np.float64(608.4088430401463), np.float64(59.483969820951955)]</t>
+  </si>
+  <si>
+    <t>[np.float64(219.89569816437515), np.float64(-48.96851642840703)]</t>
+  </si>
+  <si>
+    <t>[np.float64(966.586477495214), np.float64(5.817290557589843)]</t>
+  </si>
+  <si>
+    <t>[np.float64(912.9233027809854), np.float64(-51.40463396512245)]</t>
+  </si>
+  <si>
+    <t>[np.float64(85.07552034096588), np.float64(-73.553349685303)]</t>
+  </si>
+  <si>
+    <t>[np.float64(709.4589959250172), np.float64(18.297954803065124)]</t>
+  </si>
+  <si>
+    <t>[np.float64(824.1979198205767), np.float64(78.10913415584054)]</t>
+  </si>
+  <si>
+    <t>[np.float64(493.2866016966654), np.float64(59.79071013170977)]</t>
+  </si>
+  <si>
+    <t>[np.float64(230.24980521349957), np.float64(-93.92550950906164)]</t>
+  </si>
+  <si>
+    <t>[np.float64(38.45077264570796), np.float64(-54.10796174321033)]</t>
+  </si>
+  <si>
+    <t>[np.float64(414.3700617490619), np.float64(30.118853335867357)]</t>
+  </si>
+  <si>
+    <t>[np.float64(674.3126815994291), np.float64(25.235537316296558)]</t>
+  </si>
+  <si>
+    <t>[np.float64(570.1929261901746), np.float64(64.46705705111148)]</t>
+  </si>
+  <si>
+    <t>[np.float64(972.0295876456355), np.float64(44.887414006995016)]</t>
+  </si>
+  <si>
+    <t>[np.float64(450.689121308526), np.float64(71.7771840601626)]</t>
+  </si>
+  <si>
+    <t>[np.float64(475.6313823775156), np.float64(84.82638665439845)]</t>
+  </si>
+  <si>
+    <t>[np.float64(928.256347944841), np.float64(-55.12935254669078)]</t>
+  </si>
+  <si>
+    <t>[np.float64(659.6695858911253), np.float64(33.05431386434083)]</t>
+  </si>
+  <si>
+    <t>[np.float64(337.9594014133819), np.float64(78.4298236935362)]</t>
+  </si>
+  <si>
+    <t>[np.float64(629.3444993466161), np.float64(32.16470778001141)]</t>
+  </si>
+  <si>
+    <t>[np.float64(817.569656124406), np.float64(23.0022800582054)]</t>
+  </si>
+  <si>
+    <t>[np.float64(330.77580036114205), np.float64(-74.85864215068958)]</t>
+  </si>
+  <si>
+    <t>[np.float64(525.189084980981), np.float64(25.08687120823147)]</t>
+  </si>
+  <si>
+    <t>[np.float64(911.590631488878), np.float64(83.39326101652188)]</t>
+  </si>
+  <si>
+    <t>[np.float64(46.99584453557604), np.float64(82.09506471120577)]</t>
+  </si>
+  <si>
+    <t>[np.float64(105.6685811771757), np.float64(40.970755227216614)]</t>
+  </si>
+  <si>
+    <t>[np.float64(994.5529473397946), np.float64(34.886694752432504)]</t>
+  </si>
+  <si>
+    <t>[np.float64(521.4535780593774), np.float64(65.10192695256961)]</t>
+  </si>
+  <si>
+    <t>[np.float64(376.83488631021567), np.float64(-91.17986234271976)]</t>
+  </si>
+  <si>
+    <t>[np.float64(342.03606918851625), np.float64(6.993818319144296)]</t>
+  </si>
+  <si>
+    <t>[np.float64(563.5528663584095), np.float64(16.86693296817967)]</t>
+  </si>
+  <si>
+    <t>[np.float64(70.28343392954672), np.float64(79.87015504539045)]</t>
+  </si>
+  <si>
+    <t>[np.float64(362.5631746756872), np.float64(20.209809092892428)]</t>
+  </si>
+  <si>
+    <t>[np.float64(690.3938878750788), np.float64(6.097557622015785)]</t>
+  </si>
+  <si>
+    <t>[np.float64(332.29495988171), np.float64(39.80014955058266)]</t>
+  </si>
+  <si>
+    <t>[np.float64(63.15526461291232), np.float64(92.15024169335777)]</t>
+  </si>
+  <si>
+    <t>[np.float64(249.3089057392166), np.float64(-74.25901040901515)]</t>
+  </si>
+  <si>
+    <t>[np.float64(455.3003174358839), np.float64(-47.2602917278641)]</t>
+  </si>
+  <si>
+    <t>[np.float64(218.84275341510562), np.float64(-80.74809460828112)]</t>
+  </si>
+  <si>
+    <t>[np.float64(893.5995253965716), np.float64(33.759124866645436)]</t>
+  </si>
+  <si>
+    <t>[np.float64(477.973651707294), np.float64(30.991409782120115)]</t>
+  </si>
+  <si>
+    <t>[np.float64(882.3745178447343), np.float64(13.31941465784692)]</t>
+  </si>
+  <si>
+    <t>[np.float64(636.315695692104), np.float64(-38.96414401855084)]</t>
+  </si>
+  <si>
+    <t>[np.float64(744.3801169509255), np.float64(47.525705904629575)]</t>
+  </si>
+  <si>
+    <t>[np.float64(795.3634190443731), np.float64(59.90205958490705)]</t>
+  </si>
+  <si>
+    <t>[np.float64(867.505397025919), np.float64(85.56985862030228)]</t>
+  </si>
+  <si>
+    <t>[np.float64(764.2447520247607), np.float64(61.94473485133696)]</t>
+  </si>
+  <si>
+    <t>[np.float64(243.5491789665284), np.float64(91.19784185543148)]</t>
+  </si>
+  <si>
+    <t>[np.float64(252.76512553282882), np.float64(98.62134460393705)]</t>
+  </si>
+  <si>
+    <t>[np.float64(689.465102794218), np.float64(-95.92330579825502)]</t>
+  </si>
+  <si>
+    <t>[np.float64(431.24690295260706), np.float64(59.39443908504819)]</t>
+  </si>
+  <si>
+    <t>[np.float64(592.4781941927552), np.float64(28.522496217685813)]</t>
+  </si>
+  <si>
+    <t>[np.float64(33.09175123990538), np.float64(-60.64944004901105)]</t>
+  </si>
+  <si>
+    <t>[np.float64(599.6265254824787), np.float64(16.418526773795293)]</t>
+  </si>
+  <si>
+    <t>[np.float64(127.68252486957054), np.float64(58.86495554349352)]</t>
+  </si>
+  <si>
+    <t>[np.float64(431.0283766991025), np.float64(14.361411001454513)]</t>
+  </si>
+  <si>
+    <t>[np.float64(33.368456505288854), np.float64(18.49636861331065)]</t>
+  </si>
+  <si>
+    <t>[np.float64(457.55119979921375), np.float64(88.69173255152316)]</t>
+  </si>
+  <si>
+    <t>[np.float64(828.7401523529289), np.float64(67.8682540514479)]</t>
+  </si>
+  <si>
+    <t>[np.float64(19.80330911970274), np.float64(11.243732459017934)]</t>
+  </si>
+  <si>
+    <t>[np.float64(250.93310600558638), np.float64(59.57127664785901)]</t>
+  </si>
+  <si>
+    <t>[np.float64(476.3609024340418), np.float64(29.66385048666214)]</t>
+  </si>
+  <si>
+    <t>[np.float64(343.49219948533585), np.float64(-89.71739291126922)]</t>
+  </si>
+  <si>
+    <t>[np.float64(578.8675002819525), np.float64(58.346254519228125)]</t>
+  </si>
+  <si>
+    <t>[np.float64(190.78941339038613), np.float64(75.63693319527485)]</t>
+  </si>
+  <si>
+    <t>[np.float64(576.721301543993), np.float64(-48.79242526636218)]</t>
+  </si>
+  <si>
+    <t>[np.float64(638.5040975154825), np.float64(-93.98337870894471)]</t>
+  </si>
+  <si>
+    <t>[np.float64(972.7943682359266), np.float64(77.57727862685374)]</t>
+  </si>
+  <si>
+    <t>[np.float64(933.3594360023294), np.float64(79.04515209899162)]</t>
+  </si>
+  <si>
+    <t>[np.float64(350.2055182357294), np.float64(14.445618067259389)]</t>
+  </si>
+  <si>
+    <t>[np.float64(981.2008629089199), np.float64(19.280143979728635)]</t>
+  </si>
+  <si>
+    <t>[np.float64(970.4208170041204), np.float64(41.30572105462252)]</t>
+  </si>
+  <si>
+    <t>[np.float64(897.7726776797288), np.float64(-54.559464508036925)]</t>
+  </si>
+  <si>
+    <t>[np.float64(603.3042548285771), np.float64(69.73558854519598)]</t>
+  </si>
+  <si>
+    <t>[np.float64(528.9475822746086), np.float64(39.07484274501661)]</t>
+  </si>
+  <si>
+    <t>[np.float64(41.39447062497015), np.float64(21.83053357519063)]</t>
+  </si>
+  <si>
+    <t>[np.float64(188.3614057753058), np.float64(8.783564232435808)]</t>
+  </si>
+  <si>
+    <t>[np.float64(522.5716225811016), np.float64(99.76715167541906)]</t>
+  </si>
+  <si>
+    <t>[np.float64(754.9235146332471), np.float64(-4.896049294492585)]</t>
+  </si>
+  <si>
+    <t>[np.float64(626.405936576896), np.float64(98.6702652086386)]</t>
+  </si>
+  <si>
+    <t>[np.float64(905.0094871273452), np.float64(-96.88136231873187)]</t>
+  </si>
+  <si>
+    <t>[np.float64(393.1131318566875), np.float64(24.77154676239192)]</t>
+  </si>
+  <si>
+    <t>[np.float64(640.4197669820691), np.float64(-77.89910035834507)]</t>
+  </si>
+  <si>
+    <t>[np.float64(957.0225437035742), np.float64(34.85640599297719)]</t>
+  </si>
+  <si>
+    <t>[np.float64(185.38015911566174), np.float64(62.66763008397152)]</t>
+  </si>
+  <si>
+    <t>[np.float64(488.9217752520865), np.float64(53.76605873962134)]</t>
+  </si>
+  <si>
+    <t>[np.float64(455.5800538296475), np.float64(98.40656417110665)]</t>
+  </si>
+  <si>
+    <t>[np.float64(402.0003084951036), np.float64(-94.61545141796172)]</t>
+  </si>
+  <si>
+    <t>[np.float64(579.5174849226428), np.float64(-22.300021368359495)]</t>
+  </si>
+  <si>
+    <t>[np.float64(704.917454001521), np.float64(23.93232643804977)]</t>
+  </si>
+  <si>
+    <t>[np.float64(172.87379679341274), np.float64(70.48264639631313)]</t>
+  </si>
+  <si>
+    <t>[np.float64(86.62908375298085), np.float64(82.35918756812347)]</t>
+  </si>
+  <si>
+    <t>[np.float64(909.2911612236923), np.float64(22.607156754455644)]</t>
+  </si>
+  <si>
+    <t>[np.float64(932.2686506877823), np.float64(64.00385267041023)]</t>
+  </si>
+  <si>
+    <t>[np.float64(153.01665912828844), np.float64(39.54620681735338)]</t>
+  </si>
+  <si>
+    <t>[np.float64(288.55114850537547), np.float64(-88.9168162214686)]</t>
+  </si>
+  <si>
+    <t>[np.float64(196.24888886429594), np.float64(-87.3269148383392)]</t>
+  </si>
+  <si>
+    <t>[np.float64(367.84159645550704), np.float64(-97.58838049317167)]</t>
+  </si>
+  <si>
+    <t>[np.float64(400.62463592361576), np.float64(63.178145519151)]</t>
+  </si>
+  <si>
+    <t>[np.float64(235.87306135901554), np.float64(6.7554183962773635)]</t>
   </si>
 </sst>
 </file>
@@ -2444,7 +2405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I681"/>
+  <dimension ref="A1:I668"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -17817,305 +17778,6 @@
         <v>677</v>
       </c>
     </row>
-    <row r="669" spans="1:9">
-      <c r="A669" t="s">
-        <v>9</v>
-      </c>
-      <c r="B669">
-        <v>0</v>
-      </c>
-      <c r="D669" t="s">
-        <v>10</v>
-      </c>
-      <c r="E669" t="s">
-        <v>10</v>
-      </c>
-      <c r="F669" t="s">
-        <v>10</v>
-      </c>
-      <c r="H669" t="s">
-        <v>678</v>
-      </c>
-      <c r="I669" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="670" spans="1:9">
-      <c r="A670" t="s">
-        <v>9</v>
-      </c>
-      <c r="B670">
-        <v>0</v>
-      </c>
-      <c r="D670" t="s">
-        <v>10</v>
-      </c>
-      <c r="E670" t="s">
-        <v>10</v>
-      </c>
-      <c r="F670" t="s">
-        <v>10</v>
-      </c>
-      <c r="H670" t="s">
-        <v>679</v>
-      </c>
-      <c r="I670" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="671" spans="1:9">
-      <c r="A671" t="s">
-        <v>9</v>
-      </c>
-      <c r="B671">
-        <v>0</v>
-      </c>
-      <c r="D671" t="s">
-        <v>10</v>
-      </c>
-      <c r="E671" t="s">
-        <v>10</v>
-      </c>
-      <c r="F671" t="s">
-        <v>10</v>
-      </c>
-      <c r="H671" t="s">
-        <v>680</v>
-      </c>
-      <c r="I671" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="672" spans="1:9">
-      <c r="A672" t="s">
-        <v>9</v>
-      </c>
-      <c r="B672">
-        <v>0</v>
-      </c>
-      <c r="D672" t="s">
-        <v>10</v>
-      </c>
-      <c r="E672" t="s">
-        <v>10</v>
-      </c>
-      <c r="F672" t="s">
-        <v>10</v>
-      </c>
-      <c r="H672" t="s">
-        <v>681</v>
-      </c>
-      <c r="I672" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="673" spans="1:9">
-      <c r="A673" t="s">
-        <v>9</v>
-      </c>
-      <c r="B673">
-        <v>0</v>
-      </c>
-      <c r="D673" t="s">
-        <v>10</v>
-      </c>
-      <c r="E673" t="s">
-        <v>10</v>
-      </c>
-      <c r="F673" t="s">
-        <v>10</v>
-      </c>
-      <c r="H673" t="s">
-        <v>682</v>
-      </c>
-      <c r="I673" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="674" spans="1:9">
-      <c r="A674" t="s">
-        <v>9</v>
-      </c>
-      <c r="B674">
-        <v>0</v>
-      </c>
-      <c r="D674" t="s">
-        <v>10</v>
-      </c>
-      <c r="E674" t="s">
-        <v>10</v>
-      </c>
-      <c r="F674" t="s">
-        <v>10</v>
-      </c>
-      <c r="H674" t="s">
-        <v>683</v>
-      </c>
-      <c r="I674" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="675" spans="1:9">
-      <c r="A675" t="s">
-        <v>9</v>
-      </c>
-      <c r="B675">
-        <v>0</v>
-      </c>
-      <c r="D675" t="s">
-        <v>10</v>
-      </c>
-      <c r="E675" t="s">
-        <v>10</v>
-      </c>
-      <c r="F675" t="s">
-        <v>10</v>
-      </c>
-      <c r="H675" t="s">
-        <v>684</v>
-      </c>
-      <c r="I675" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="676" spans="1:9">
-      <c r="A676" t="s">
-        <v>9</v>
-      </c>
-      <c r="B676">
-        <v>0</v>
-      </c>
-      <c r="D676" t="s">
-        <v>10</v>
-      </c>
-      <c r="E676" t="s">
-        <v>10</v>
-      </c>
-      <c r="F676" t="s">
-        <v>10</v>
-      </c>
-      <c r="H676" t="s">
-        <v>685</v>
-      </c>
-      <c r="I676" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="677" spans="1:9">
-      <c r="A677" t="s">
-        <v>9</v>
-      </c>
-      <c r="B677">
-        <v>0</v>
-      </c>
-      <c r="D677" t="s">
-        <v>10</v>
-      </c>
-      <c r="E677" t="s">
-        <v>10</v>
-      </c>
-      <c r="F677" t="s">
-        <v>10</v>
-      </c>
-      <c r="H677" t="s">
-        <v>686</v>
-      </c>
-      <c r="I677" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="678" spans="1:9">
-      <c r="A678" t="s">
-        <v>9</v>
-      </c>
-      <c r="B678">
-        <v>0</v>
-      </c>
-      <c r="D678" t="s">
-        <v>10</v>
-      </c>
-      <c r="E678" t="s">
-        <v>10</v>
-      </c>
-      <c r="F678" t="s">
-        <v>10</v>
-      </c>
-      <c r="H678" t="s">
-        <v>687</v>
-      </c>
-      <c r="I678" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="679" spans="1:9">
-      <c r="A679" t="s">
-        <v>9</v>
-      </c>
-      <c r="B679">
-        <v>0</v>
-      </c>
-      <c r="D679" t="s">
-        <v>10</v>
-      </c>
-      <c r="E679" t="s">
-        <v>10</v>
-      </c>
-      <c r="F679" t="s">
-        <v>10</v>
-      </c>
-      <c r="H679" t="s">
-        <v>688</v>
-      </c>
-      <c r="I679" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="680" spans="1:9">
-      <c r="A680" t="s">
-        <v>9</v>
-      </c>
-      <c r="B680">
-        <v>0</v>
-      </c>
-      <c r="D680" t="s">
-        <v>10</v>
-      </c>
-      <c r="E680" t="s">
-        <v>10</v>
-      </c>
-      <c r="F680" t="s">
-        <v>10</v>
-      </c>
-      <c r="H680" t="s">
-        <v>689</v>
-      </c>
-      <c r="I680" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="681" spans="1:9">
-      <c r="A681" t="s">
-        <v>9</v>
-      </c>
-      <c r="B681">
-        <v>0</v>
-      </c>
-      <c r="D681" t="s">
-        <v>10</v>
-      </c>
-      <c r="E681" t="s">
-        <v>10</v>
-      </c>
-      <c r="F681" t="s">
-        <v>10</v>
-      </c>
-      <c r="H681" t="s">
-        <v>690</v>
-      </c>
-      <c r="I681" t="s">
-        <v>690</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Data/output/IND Stroke Position.xlsx
+++ b/Data/output/IND Stroke Position.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5607" uniqueCount="944">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5643" uniqueCount="950">
   <si>
     <t>Direct_or_Indirect</t>
   </si>
@@ -49,2803 +49,2821 @@
     <t>nan</t>
   </si>
   <si>
-    <t>[np.float64(389.12061678254827), np.float64(505.3094180803396)]</t>
-  </si>
-  <si>
-    <t>[np.float64(512.1904340396085), np.float64(10.971926381679395)]</t>
-  </si>
-  <si>
-    <t>[np.float64(166.61922893468463), np.float64(126.658453278754)]</t>
-  </si>
-  <si>
-    <t>[np.float64(957.3132954661894), np.float64(415.724449381343)]</t>
-  </si>
-  <si>
-    <t>[np.float64(519.5543743063323), np.float64(506.05373086184363)]</t>
-  </si>
-  <si>
-    <t>[np.float64(920.2191392250937), np.float64(-373.5399334017875)]</t>
-  </si>
-  <si>
-    <t>[np.float64(179.33372042968975), np.float64(-344.8695246710556)]</t>
-  </si>
-  <si>
-    <t>[np.float64(761.9958600823256), np.float64(-546.541860324725)]</t>
-  </si>
-  <si>
-    <t>[np.float64(901.0559107930497), np.float64(-117.14193940968289)]</t>
-  </si>
-  <si>
-    <t>[np.float64(587.7514543630665), np.float64(-185.9901133875938)]</t>
-  </si>
-  <si>
-    <t>[np.float64(160.01630953832026), np.float64(40.79970194859243)]</t>
-  </si>
-  <si>
-    <t>[np.float64(822.8421181515719), np.float64(516.3391619186436)]</t>
-  </si>
-  <si>
-    <t>[np.float64(375.2057667391444), np.float64(441.8879411733169)]</t>
-  </si>
-  <si>
-    <t>[np.float64(527.9580728497218), np.float64(-271.61557595020264)]</t>
-  </si>
-  <si>
-    <t>[np.float64(502.3860424750135), np.float64(-310.78868136703323)]</t>
-  </si>
-  <si>
-    <t>[np.float64(922.4927885600227), np.float64(-145.20431321878988)]</t>
-  </si>
-  <si>
-    <t>[np.float64(240.86349758588233), np.float64(-430.33376559298404)]</t>
-  </si>
-  <si>
-    <t>[np.float64(712.6461385877712), np.float64(-507.1834875027961)]</t>
-  </si>
-  <si>
-    <t>[np.float64(585.8414443755346), np.float64(23.488106985540412)]</t>
-  </si>
-  <si>
-    <t>[np.float64(814.7876985876659), np.float64(69.19330787131139)]</t>
-  </si>
-  <si>
-    <t>[np.float64(286.9166015503184), np.float64(-284.65531946393764)]</t>
-  </si>
-  <si>
-    <t>[np.float64(299.6263684223187), np.float64(334.0820153947967)]</t>
-  </si>
-  <si>
-    <t>[np.float64(39.178705548088224), np.float64(462.36883691210073)]</t>
-  </si>
-  <si>
-    <t>[np.float64(548.7995791438115), np.float64(14.120789114692911)]</t>
-  </si>
-  <si>
-    <t>[np.float64(56.73246833275736), np.float64(-210.21248153359443)]</t>
-  </si>
-  <si>
-    <t>[np.float64(639.6560407460922), np.float64(152.44376711765278)]</t>
-  </si>
-  <si>
-    <t>[np.float64(36.73173837551258), np.float64(-513.9396208249561)]</t>
-  </si>
-  <si>
-    <t>[np.float64(322.4042822333486), np.float64(-344.62058800491104)]</t>
-  </si>
-  <si>
-    <t>[np.float64(12.025047343841466), np.float64(318.6685861012919)]</t>
-  </si>
-  <si>
-    <t>[np.float64(782.0653195463035), np.float64(368.3088114304584)]</t>
-  </si>
-  <si>
-    <t>[np.float64(19.715534615780793), np.float64(0.9698428410443967)]</t>
-  </si>
-  <si>
-    <t>[np.float64(756.0076718093362), np.float64(-437.37555145222257)]</t>
-  </si>
-  <si>
-    <t>[np.float64(139.67631549783655), np.float64(302.4421560429862)]</t>
-  </si>
-  <si>
-    <t>[np.float64(721.78544866396), np.float64(-162.66917602520522)]</t>
-  </si>
-  <si>
-    <t>[np.float64(96.82552844242099), np.float64(-365.98844981256264)]</t>
-  </si>
-  <si>
-    <t>[np.float64(147.66073748947673), np.float64(-522.4102699843977)]</t>
-  </si>
-  <si>
-    <t>[np.float64(350.54288646603715), np.float64(357.844745899444)]</t>
-  </si>
-  <si>
-    <t>[np.float64(979.933478337416), np.float64(-210.58159518412543)]</t>
-  </si>
-  <si>
-    <t>[np.float64(92.68386111681981), np.float64(-124.94098177581475)]</t>
-  </si>
-  <si>
-    <t>[np.float64(657.1644763482374), np.float64(434.318165771811)]</t>
-  </si>
-  <si>
-    <t>[np.float64(451.23288392490434), np.float64(-407.74868167644735)]</t>
-  </si>
-  <si>
-    <t>[np.float64(110.64583173292952), np.float64(65.09332534314922)]</t>
-  </si>
-  <si>
-    <t>[np.float64(43.731132521996116), np.float64(72.74893309315769)]</t>
-  </si>
-  <si>
-    <t>[np.float64(684.2440199132468), np.float64(68.490344399116)]</t>
-  </si>
-  <si>
-    <t>[np.float64(582.9968660993558), np.float64(387.7917949671885)]</t>
-  </si>
-  <si>
-    <t>[np.float64(475.40746368371913), np.float64(141.43891915567167)]</t>
-  </si>
-  <si>
-    <t>[np.float64(542.8199682044769), np.float64(415.33735543726505)]</t>
-  </si>
-  <si>
-    <t>[np.float64(550.3551553184932), np.float64(-460.7825070649893)]</t>
-  </si>
-  <si>
-    <t>[np.float64(364.0924404885252), np.float64(-459.5992941429376)]</t>
-  </si>
-  <si>
-    <t>[np.float64(84.40946095883916), np.float64(-434.86968138792287)]</t>
-  </si>
-  <si>
-    <t>[np.float64(302.3903075094674), np.float64(-390.57281277756545)]</t>
-  </si>
-  <si>
-    <t>[np.float64(397.3629248083489), np.float64(-597.6999107283056)]</t>
-  </si>
-  <si>
-    <t>[np.float64(117.60600578713776), np.float64(-354.26173981916514)]</t>
-  </si>
-  <si>
-    <t>[np.float64(687.7061036327812), np.float64(271.1763139152896)]</t>
-  </si>
-  <si>
-    <t>[np.float64(796.6374885555429), np.float64(-102.52491691559993)]</t>
-  </si>
-  <si>
-    <t>[np.float64(690.2355074537232), np.float64(227.796608089164)]</t>
-  </si>
-  <si>
-    <t>[np.float64(152.73541576330229), np.float64(412.25214125528294)]</t>
-  </si>
-  <si>
-    <t>[np.float64(724.9458346959779), np.float64(-524.0119449776204)]</t>
-  </si>
-  <si>
-    <t>[np.float64(343.49535871175596), np.float64(37.87669001839379)]</t>
-  </si>
-  <si>
-    <t>[np.float64(171.61674723964825), np.float64(-410.51749278295154)]</t>
-  </si>
-  <si>
-    <t>[np.float64(289.91423258074224), np.float64(-326.6785313639146)]</t>
-  </si>
-  <si>
-    <t>[np.float64(703.177173877221), np.float64(561.8517076703602)]</t>
-  </si>
-  <si>
-    <t>[np.float64(538.5232897695203), np.float64(440.5076467496342)]</t>
-  </si>
-  <si>
-    <t>[np.float64(877.7954473976861), np.float64(-1.0432419947881044)]</t>
-  </si>
-  <si>
-    <t>[np.float64(70.77776453846107), np.float64(233.32490308471904)]</t>
-  </si>
-  <si>
-    <t>[np.float64(264.6647692477997), np.float64(-297.08649631558217)]</t>
-  </si>
-  <si>
-    <t>[np.float64(363.5839552503662), np.float64(-274.0548922450007)]</t>
-  </si>
-  <si>
-    <t>[np.float64(935.7224693680249), np.float64(27.07873006310581)]</t>
-  </si>
-  <si>
-    <t>[np.float64(506.9291424589618), np.float64(294.2960004630668)]</t>
-  </si>
-  <si>
-    <t>[np.float64(403.6080277721361), np.float64(-360.72889733102875)]</t>
-  </si>
-  <si>
-    <t>[np.float64(933.9286576176011), np.float64(385.05458861350996)]</t>
-  </si>
-  <si>
-    <t>[np.float64(354.99565357577876), np.float64(345.34146428342706)]</t>
-  </si>
-  <si>
-    <t>[np.float64(628.0320605006227), np.float64(-532.4277522022242)]</t>
-  </si>
-  <si>
-    <t>[np.float64(121.6861534029452), np.float64(-525.7388691321038)]</t>
-  </si>
-  <si>
-    <t>[np.float64(791.2836409256132), np.float64(522.5754433392854)]</t>
-  </si>
-  <si>
-    <t>[np.float64(555.8404737951743), np.float64(366.804291353626)]</t>
-  </si>
-  <si>
-    <t>[np.float64(655.928802479161), np.float64(-508.7843366102667)]</t>
-  </si>
-  <si>
-    <t>[np.float64(842.3093027105293), np.float64(331.7501223969631)]</t>
-  </si>
-  <si>
-    <t>[np.float64(20.240935594944332), np.float64(462.5359859890066)]</t>
-  </si>
-  <si>
-    <t>[np.float64(967.8898822467827), np.float64(-150.52120714452684)]</t>
-  </si>
-  <si>
-    <t>[np.float64(854.5363278635449), np.float64(-91.84211871883787)]</t>
-  </si>
-  <si>
-    <t>[np.float64(217.8509738705653), np.float64(-198.67140244929288)]</t>
-  </si>
-  <si>
-    <t>[np.float64(628.6732683149376), np.float64(24.494072678000293)]</t>
-  </si>
-  <si>
-    <t>[np.float64(854.25352923095), np.float64(244.24431711443845)]</t>
-  </si>
-  <si>
-    <t>[np.float64(706.7374443373731), np.float64(338.8517802206778)]</t>
-  </si>
-  <si>
-    <t>[np.float64(901.7352755766049), np.float64(125.22588181743845)]</t>
-  </si>
-  <si>
-    <t>[np.float64(653.3472491691883), np.float64(519.0685110360728)]</t>
-  </si>
-  <si>
-    <t>[np.float64(701.5744628299075), np.float64(-357.53679050019)]</t>
-  </si>
-  <si>
-    <t>[np.float64(903.0051548799282), np.float64(209.693288794502)]</t>
-  </si>
-  <si>
-    <t>[np.float64(46.846627571267675), np.float64(523.765792547081)]</t>
-  </si>
-  <si>
-    <t>[np.float64(938.5948718319992), np.float64(-162.6610570560232)]</t>
-  </si>
-  <si>
-    <t>[np.float64(381.34761443719367), np.float64(-220.40855210693832)]</t>
-  </si>
-  <si>
-    <t>[np.float64(892.7403229108901), np.float64(584.4352568213951)]</t>
-  </si>
-  <si>
-    <t>[np.float64(566.1151792920891), np.float64(-135.7968006743008)]</t>
-  </si>
-  <si>
-    <t>[np.float64(134.24346018963985), np.float64(146.48685992066044)]</t>
-  </si>
-  <si>
-    <t>[np.float64(3.1114504518300334), np.float64(289.4233823210568)]</t>
-  </si>
-  <si>
-    <t>[np.float64(485.45616521155574), np.float64(-442.00983181587935)]</t>
-  </si>
-  <si>
-    <t>[np.float64(533.8373080482419), np.float64(394.98644228129444)]</t>
-  </si>
-  <si>
-    <t>[np.float64(317.63322046424844), np.float64(-279.0058834813111)]</t>
-  </si>
-  <si>
-    <t>[np.float64(377.70329253701806), np.float64(546.460880213418)]</t>
-  </si>
-  <si>
-    <t>[np.float64(94.51635299058425), np.float64(303.86484551771366)]</t>
-  </si>
-  <si>
-    <t>[np.float64(805.769026825999), np.float64(196.96767743732084)]</t>
-  </si>
-  <si>
-    <t>[np.float64(186.1370556648979), np.float64(-161.24914207358785)]</t>
-  </si>
-  <si>
-    <t>[np.float64(559.0511529520471), np.float64(109.7382800437839)]</t>
-  </si>
-  <si>
-    <t>[np.float64(507.5357220608351), np.float64(92.97999732879862)]</t>
-  </si>
-  <si>
-    <t>[np.float64(44.63746198591267), np.float64(-553.7444285080807)]</t>
-  </si>
-  <si>
-    <t>[np.float64(800.2282027195114), np.float64(498.57538402436444)]</t>
-  </si>
-  <si>
-    <t>[np.float64(692.3119329427811), np.float64(403.5713553399162)]</t>
-  </si>
-  <si>
-    <t>[np.float64(70.8668903264118), np.float64(103.0355191397457)]</t>
-  </si>
-  <si>
-    <t>[np.float64(669.0052913960666), np.float64(-116.14879229655548)]</t>
-  </si>
-  <si>
-    <t>[np.float64(367.49036658986444), np.float64(579.1252735044427)]</t>
-  </si>
-  <si>
-    <t>[np.float64(751.6134456663274), np.float64(252.17639479603508)]</t>
-  </si>
-  <si>
-    <t>[np.float64(634.8821102613612), np.float64(260.22033173680245)]</t>
-  </si>
-  <si>
-    <t>[np.float64(910.0464602069053), np.float64(248.7961219006828)]</t>
-  </si>
-  <si>
-    <t>[np.float64(348.7543952900161), np.float64(-404.42567758039564)]</t>
-  </si>
-  <si>
-    <t>[np.float64(293.07661500152824), np.float64(108.93081568491834)]</t>
-  </si>
-  <si>
-    <t>[np.float64(96.80664846610532), np.float64(-86.23952619692454)]</t>
-  </si>
-  <si>
-    <t>[np.float64(43.773070259767735), np.float64(248.50241411909735)]</t>
-  </si>
-  <si>
-    <t>[np.float64(572.3692774744059), np.float64(201.90520960599986)]</t>
-  </si>
-  <si>
-    <t>[np.float64(787.8496382022753), np.float64(581.201985455652)]</t>
-  </si>
-  <si>
-    <t>[np.float64(325.10764407851144), np.float64(-279.10994652232006)]</t>
-  </si>
-  <si>
-    <t>[np.float64(438.67184425964524), np.float64(-550.3300020429275)]</t>
-  </si>
-  <si>
-    <t>[np.float64(786.3772229284372), np.float64(255.67804976267837)]</t>
-  </si>
-  <si>
-    <t>[np.float64(283.07885680307834), np.float64(-501.97701094617076)]</t>
-  </si>
-  <si>
-    <t>[np.float64(152.77501102091918), np.float64(-234.26414885865682)]</t>
-  </si>
-  <si>
-    <t>[np.float64(299.1750978258417), np.float64(370.13879118190164)]</t>
-  </si>
-  <si>
-    <t>[np.float64(583.6059682966844), np.float64(-457.2684988338144)]</t>
-  </si>
-  <si>
-    <t>[np.float64(768.8427260971334), np.float64(75.73489326558854)]</t>
-  </si>
-  <si>
-    <t>[np.float64(461.428786598858), np.float64(-343.68647742038235)]</t>
-  </si>
-  <si>
-    <t>[np.float64(335.20808914104725), np.float64(87.34005881579378)]</t>
-  </si>
-  <si>
-    <t>[np.float64(669.2174728029897), np.float64(-194.63302694302433)]</t>
-  </si>
-  <si>
-    <t>[np.float64(524.9039481282952), np.float64(339.0826764168986)]</t>
-  </si>
-  <si>
-    <t>[np.float64(32.171705772332196), np.float64(220.76310418236812)]</t>
-  </si>
-  <si>
-    <t>[np.float64(371.16194255988955), np.float64(499.10414441421676)]</t>
-  </si>
-  <si>
-    <t>[np.float64(160.29517508814405), np.float64(-581.6424709643449)]</t>
-  </si>
-  <si>
-    <t>[np.float64(693.7647723957301), np.float64(411.299635113382)]</t>
-  </si>
-  <si>
-    <t>[np.float64(900.4208722907889), np.float64(-593.0392105467325)]</t>
-  </si>
-  <si>
-    <t>[np.float64(785.8482938278534), np.float64(356.386545248325)]</t>
-  </si>
-  <si>
-    <t>[np.float64(406.631900830432), np.float64(-595.3975705831195)]</t>
-  </si>
-  <si>
-    <t>[np.float64(694.2494551890501), np.float64(594.8165791861695)]</t>
-  </si>
-  <si>
-    <t>[np.float64(61.28278997783077), np.float64(497.49061807291673)]</t>
-  </si>
-  <si>
-    <t>[np.float64(795.7896893875628), np.float64(-107.33047275322667)]</t>
-  </si>
-  <si>
-    <t>[np.float64(915.4474944035821), np.float64(-156.767960155759)]</t>
-  </si>
-  <si>
-    <t>[np.float64(99.3302433483414), np.float64(380.6723206758944)]</t>
-  </si>
-  <si>
-    <t>[np.float64(231.21888464422526), np.float64(292.9981218253671)]</t>
-  </si>
-  <si>
-    <t>[np.float64(300.6488815141892), np.float64(52.42740757122658)]</t>
-  </si>
-  <si>
-    <t>[np.float64(809.8522256906589), np.float64(-124.3827427642272)]</t>
-  </si>
-  <si>
-    <t>[np.float64(710.3502923423603), np.float64(-348.4311061601733)]</t>
-  </si>
-  <si>
-    <t>[np.float64(774.5138635740556), np.float64(-482.1621972729093)]</t>
-  </si>
-  <si>
-    <t>[np.float64(11.242530739084987), np.float64(269.3011951725913)]</t>
-  </si>
-  <si>
-    <t>[np.float64(797.6870770022072), np.float64(175.57972406001818)]</t>
-  </si>
-  <si>
-    <t>[np.float64(280.4301404482049), np.float64(62.444296309429205)]</t>
-  </si>
-  <si>
-    <t>[np.float64(999.8470475113438), np.float64(77.39495725224515)]</t>
-  </si>
-  <si>
-    <t>[np.float64(427.49989221559315), np.float64(-394.4982082071631)]</t>
-  </si>
-  <si>
-    <t>[np.float64(11.1818521409478), np.float64(320.25458901481636)]</t>
-  </si>
-  <si>
-    <t>[np.float64(203.89929838972577), np.float64(195.7116936020583)]</t>
-  </si>
-  <si>
-    <t>[np.float64(885.451044207389), np.float64(-387.9701305475326)]</t>
-  </si>
-  <si>
-    <t>[np.float64(84.10661526390706), np.float64(67.92129552167057)]</t>
-  </si>
-  <si>
-    <t>[np.float64(565.9355863605374), np.float64(256.68690640051364)]</t>
-  </si>
-  <si>
-    <t>[np.float64(936.9702398392058), np.float64(-299.102430293826)]</t>
-  </si>
-  <si>
-    <t>[np.float64(509.27867434340754), np.float64(382.4214706718451)]</t>
-  </si>
-  <si>
-    <t>[np.float64(935.9623497014475), np.float64(-508.4971866551607)]</t>
-  </si>
-  <si>
-    <t>[np.float64(660.0612878355055), np.float64(273.1196984992582)]</t>
-  </si>
-  <si>
-    <t>[np.float64(879.6952970690035), np.float64(-464.526401497792)]</t>
-  </si>
-  <si>
-    <t>[np.float64(468.42909441542446), np.float64(-313.94259399809624)]</t>
-  </si>
-  <si>
-    <t>[np.float64(383.1473044056679), np.float64(353.0677469408448)]</t>
-  </si>
-  <si>
-    <t>[np.float64(798.6976121917137), np.float64(253.92554341890923)]</t>
-  </si>
-  <si>
-    <t>[np.float64(152.6395518220963), np.float64(216.54452943847537)]</t>
-  </si>
-  <si>
-    <t>[np.float64(940.3328513577528), np.float64(434.2540147186596)]</t>
-  </si>
-  <si>
-    <t>[np.float64(950.6565495489672), np.float64(532.7171509607849)]</t>
-  </si>
-  <si>
-    <t>[np.float64(121.56114788597993), np.float64(284.1103282235539)]</t>
-  </si>
-  <si>
-    <t>[np.float64(527.6089251189856), np.float64(-441.55559074976975)]</t>
-  </si>
-  <si>
-    <t>[np.float64(466.4981599845175), np.float64(245.45907671506632)]</t>
-  </si>
-  <si>
-    <t>[np.float64(250.60676531489545), np.float64(-318.2721961628651)]</t>
-  </si>
-  <si>
-    <t>[np.float64(53.50801043403186), np.float64(-64.39219315643902)]</t>
-  </si>
-  <si>
-    <t>[np.float64(962.9135806439825), np.float64(-253.39511505767092)]</t>
-  </si>
-  <si>
-    <t>[np.float64(974.4529647335785), np.float64(397.92582992474775)]</t>
-  </si>
-  <si>
-    <t>[np.float64(451.9285362438056), np.float64(-416.6761765233822)]</t>
-  </si>
-  <si>
-    <t>[np.float64(472.3322095388005), np.float64(-344.8701854819059)]</t>
-  </si>
-  <si>
-    <t>[np.float64(408.03914016496213), np.float64(-87.94548076928777)]</t>
-  </si>
-  <si>
-    <t>[np.float64(865.9329964091718), np.float64(30.65639096163261)]</t>
-  </si>
-  <si>
-    <t>[np.float64(188.97731293977705), np.float64(-300.1721332661747)]</t>
-  </si>
-  <si>
-    <t>[np.float64(338.3877227366603), np.float64(-597.3505401550356)]</t>
-  </si>
-  <si>
-    <t>[np.float64(98.30433439870467), np.float64(-200.2960315484953)]</t>
-  </si>
-  <si>
-    <t>[np.float64(472.74412975337964), np.float64(-229.01141232932753)]</t>
-  </si>
-  <si>
-    <t>[np.float64(588.5784319803176), np.float64(-421.06662431346365)]</t>
-  </si>
-  <si>
-    <t>[np.float64(275.04697937835334), np.float64(-187.5676142113237)]</t>
-  </si>
-  <si>
-    <t>[np.float64(581.1540003360269), np.float64(538.3998604546246)]</t>
-  </si>
-  <si>
-    <t>[np.float64(869.6490955940526), np.float64(96.0943428471029)]</t>
-  </si>
-  <si>
-    <t>[np.float64(965.8475323037551), np.float64(376.2609032139744)]</t>
-  </si>
-  <si>
-    <t>[np.float64(852.6147084958037), np.float64(551.893716615265)]</t>
-  </si>
-  <si>
-    <t>[np.float64(82.40389965125505), np.float64(456.5959799903785)]</t>
-  </si>
-  <si>
-    <t>[np.float64(428.1761359885858), np.float64(516.5821312857345)]</t>
-  </si>
-  <si>
-    <t>[np.float64(328.1024613843862), np.float64(-407.922257390567)]</t>
-  </si>
-  <si>
-    <t>[np.float64(538.92993838178), np.float64(-114.42407815531283)]</t>
-  </si>
-  <si>
-    <t>[np.float64(297.66238203201146), np.float64(539.8600896376358)]</t>
-  </si>
-  <si>
-    <t>[np.float64(211.057804977568), np.float64(-594.2793898055061)]</t>
-  </si>
-  <si>
-    <t>[np.float64(961.042534744908), np.float64(-250.6319874045917)]</t>
-  </si>
-  <si>
-    <t>[np.float64(703.9187768322842), np.float64(-450.36447128958457)]</t>
-  </si>
-  <si>
-    <t>[np.float64(196.76965694006088), np.float64(-494.4145937603164)]</t>
-  </si>
-  <si>
-    <t>[np.float64(887.7630152948665), np.float64(-321.12644281560733)]</t>
-  </si>
-  <si>
-    <t>[np.float64(567.1825689987932), np.float64(-450.90477364734556)]</t>
-  </si>
-  <si>
-    <t>[np.float64(388.72263993699806), np.float64(-305.7957166748599)]</t>
-  </si>
-  <si>
-    <t>[np.float64(17.5839655782164), np.float64(63.07453245201657)]</t>
-  </si>
-  <si>
-    <t>[np.float64(316.6051743063293), np.float64(-281.2317997844248)]</t>
-  </si>
-  <si>
-    <t>[np.float64(427.43501139306005), np.float64(-544.7381648602355)]</t>
-  </si>
-  <si>
-    <t>[np.float64(321.7807836076414), np.float64(-156.03101863244086)]</t>
-  </si>
-  <si>
-    <t>[np.float64(874.2889997663183), np.float64(72.93813813168856)]</t>
-  </si>
-  <si>
-    <t>[np.float64(972.4787232912028), np.float64(553.0451853865591)]</t>
-  </si>
-  <si>
-    <t>[np.float64(868.4700756252317), np.float64(-564.7958472421724)]</t>
-  </si>
-  <si>
-    <t>[np.float64(490.7192686204703), np.float64(-377.04467734219156)]</t>
-  </si>
-  <si>
-    <t>[np.float64(288.77913714099236), np.float64(-400.49276273984026)]</t>
-  </si>
-  <si>
-    <t>[np.float64(130.329295485498), np.float64(515.5599676335396)]</t>
-  </si>
-  <si>
-    <t>[np.float64(100.76625318296529), np.float64(203.5151392780009)]</t>
-  </si>
-  <si>
-    <t>[np.float64(731.8903576215182), np.float64(-574.0892215454694)]</t>
-  </si>
-  <si>
-    <t>[np.float64(719.7995104114261), np.float64(-253.18983649829772)]</t>
-  </si>
-  <si>
-    <t>[np.float64(83.6740107599846), np.float64(550.148660417213)]</t>
-  </si>
-  <si>
-    <t>[np.float64(381.7909089514847), np.float64(44.371199898328996)]</t>
-  </si>
-  <si>
-    <t>[np.float64(391.42380017158797), np.float64(100.07472405829185)]</t>
-  </si>
-  <si>
-    <t>[np.float64(127.48867512056262), np.float64(525.9617133404151)]</t>
-  </si>
-  <si>
-    <t>[np.float64(235.37538206036558), np.float64(-128.35767624218715)]</t>
-  </si>
-  <si>
-    <t>[np.float64(821.8300010353023), np.float64(406.6736612212296)]</t>
-  </si>
-  <si>
-    <t>[np.float64(51.696047295996195), np.float64(304.6576163524526)]</t>
-  </si>
-  <si>
-    <t>[np.float64(822.3610116762156), np.float64(-279.2539799819113)]</t>
-  </si>
-  <si>
-    <t>[np.float64(572.4538214382943), np.float64(-193.573031467793)]</t>
-  </si>
-  <si>
-    <t>[np.float64(696.311493267718), np.float64(-562.542967933916)]</t>
-  </si>
-  <si>
-    <t>[np.float64(25.46076060143654), np.float64(28.034054634554536)]</t>
-  </si>
-  <si>
-    <t>[np.float64(294.6209894840457), np.float64(115.61230745225112)]</t>
-  </si>
-  <si>
-    <t>[np.float64(66.18119991833726), np.float64(157.9042509407916)]</t>
-  </si>
-  <si>
-    <t>[np.float64(704.8335936090795), np.float64(-146.60251648708163)]</t>
-  </si>
-  <si>
-    <t>[np.float64(463.0050089092341), np.float64(195.63423316217222)]</t>
-  </si>
-  <si>
-    <t>[np.float64(119.69806276504713), np.float64(-314.1024557245443)]</t>
-  </si>
-  <si>
-    <t>[np.float64(617.0143400476109), np.float64(-152.19237662307177)]</t>
-  </si>
-  <si>
-    <t>[np.float64(967.4990066352805), np.float64(-183.40640338718123)]</t>
-  </si>
-  <si>
-    <t>[np.float64(739.5166806379954), np.float64(360.2677175437699)]</t>
-  </si>
-  <si>
-    <t>[np.float64(431.69798549549034), np.float64(-321.2114334713351)]</t>
-  </si>
-  <si>
-    <t>[np.float64(140.79298764988025), np.float64(203.12375956112123)]</t>
-  </si>
-  <si>
-    <t>[np.float64(848.2924420377564), np.float64(242.99346165916438)]</t>
-  </si>
-  <si>
-    <t>[np.float64(467.35538195697546), np.float64(118.0616746382525)]</t>
-  </si>
-  <si>
-    <t>[np.float64(158.95096124832497), np.float64(-509.98783075076574)]</t>
-  </si>
-  <si>
-    <t>[np.float64(955.2125566890355), np.float64(340.76171487822455)]</t>
-  </si>
-  <si>
-    <t>[np.float64(103.83387642531672), np.float64(-509.92715480729004)]</t>
-  </si>
-  <si>
-    <t>[np.float64(862.789728649602), np.float64(-267.447548897364)]</t>
-  </si>
-  <si>
-    <t>[np.float64(859.9968732468324), np.float64(-383.96636729029524)]</t>
-  </si>
-  <si>
-    <t>[np.float64(117.93364726278833), np.float64(-481.3343902226824)]</t>
-  </si>
-  <si>
-    <t>[np.float64(23.028830414979605), np.float64(121.7467489399412)]</t>
-  </si>
-  <si>
-    <t>[np.float64(44.38644216130694), np.float64(181.94755028920235)]</t>
-  </si>
-  <si>
-    <t>[np.float64(388.16753405256645), np.float64(232.8260525215228)]</t>
-  </si>
-  <si>
-    <t>[np.float64(387.7669429491637), np.float64(128.997853897494)]</t>
-  </si>
-  <si>
-    <t>[np.float64(590.3570981538318), np.float64(-391.64277265959316)]</t>
-  </si>
-  <si>
-    <t>[np.float64(828.163549341764), np.float64(-307.0919993602858)]</t>
-  </si>
-  <si>
-    <t>[np.float64(93.41277391172953), np.float64(255.4655858695205)]</t>
-  </si>
-  <si>
-    <t>[np.float64(74.48071977660065), np.float64(277.93720642948654)]</t>
-  </si>
-  <si>
-    <t>[np.float64(237.89146604705547), np.float64(454.840100326775)]</t>
-  </si>
-  <si>
-    <t>[np.float64(255.37876620854237), np.float64(82.1201380482537)]</t>
-  </si>
-  <si>
-    <t>[np.float64(996.8629212686841), np.float64(-112.60767106967296)]</t>
-  </si>
-  <si>
-    <t>[np.float64(208.75239626963415), np.float64(-573.2745592417388)]</t>
-  </si>
-  <si>
-    <t>[np.float64(272.98159506322185), np.float64(-490.5917591901558)]</t>
-  </si>
-  <si>
-    <t>[np.float64(135.26372445939694), np.float64(-285.2659039794495)]</t>
-  </si>
-  <si>
-    <t>[np.float64(376.6623039318989), np.float64(-339.6258327880547)]</t>
-  </si>
-  <si>
-    <t>[np.float64(90.65135561195292), np.float64(416.5073470614077)]</t>
-  </si>
-  <si>
-    <t>[np.float64(19.40990533397691), np.float64(-72.17086311507921)]</t>
-  </si>
-  <si>
-    <t>[np.float64(274.56801773184435), np.float64(-173.65442362128903)]</t>
-  </si>
-  <si>
-    <t>[np.float64(268.82674428992124), np.float64(59.21384172177261)]</t>
-  </si>
-  <si>
-    <t>[np.float64(459.84237726780583), np.float64(-436.6874081653865)]</t>
-  </si>
-  <si>
-    <t>[np.float64(959.0430268248301), np.float64(403.7448064168407)]</t>
-  </si>
-  <si>
-    <t>[np.float64(785.9635209051684), np.float64(-433.90895423271536)]</t>
-  </si>
-  <si>
-    <t>[np.float64(691.533115367211), np.float64(-433.6775553648089)]</t>
-  </si>
-  <si>
-    <t>[np.float64(518.1886386783667), np.float64(135.39057462398216)]</t>
-  </si>
-  <si>
-    <t>[np.float64(207.87102656793166), np.float64(-365.64215741965916)]</t>
-  </si>
-  <si>
-    <t>[np.float64(277.7143070406093), np.float64(-24.084998715444726)]</t>
-  </si>
-  <si>
-    <t>[np.float64(543.4658750717925), np.float64(-148.78981932048004)]</t>
-  </si>
-  <si>
-    <t>[np.float64(123.6537457276079), np.float64(-293.98231949524785)]</t>
-  </si>
-  <si>
-    <t>[np.float64(576.4891323625483), np.float64(-77.30543946902287)]</t>
-  </si>
-  <si>
-    <t>[np.float64(867.2495858678325), np.float64(-226.77664301005365)]</t>
-  </si>
-  <si>
-    <t>[np.float64(458.2602503394084), np.float64(483.65683500391924)]</t>
-  </si>
-  <si>
-    <t>[np.float64(914.4280072736417), np.float64(31.655250524317466)]</t>
-  </si>
-  <si>
-    <t>[np.float64(361.6674202928514), np.float64(-251.8223092088083)]</t>
-  </si>
-  <si>
-    <t>[np.float64(563.6596814456578), np.float64(481.65591193282876)]</t>
-  </si>
-  <si>
-    <t>[np.float64(67.44372882428995), np.float64(-549.5667954240018)]</t>
-  </si>
-  <si>
-    <t>[np.float64(686.5800495421403), np.float64(262.3684514496456)]</t>
-  </si>
-  <si>
-    <t>[np.float64(418.115131978416), np.float64(52.268721467561704)]</t>
-  </si>
-  <si>
-    <t>[np.float64(667.0126977672712), np.float64(-196.54276409296858)]</t>
-  </si>
-  <si>
-    <t>[np.float64(689.3905526948162), np.float64(79.30846717627776)]</t>
-  </si>
-  <si>
-    <t>[np.float64(383.2287029055118), np.float64(466.7435971580287)]</t>
-  </si>
-  <si>
-    <t>[np.float64(741.4218004705842), np.float64(515.5076872693905)]</t>
-  </si>
-  <si>
-    <t>[np.float64(284.3350314730936), np.float64(227.7188664342225)]</t>
-  </si>
-  <si>
-    <t>[np.float64(283.075971692876), np.float64(-336.3287710360043)]</t>
-  </si>
-  <si>
-    <t>[np.float64(567.628588886251), np.float64(106.54965985426998)]</t>
-  </si>
-  <si>
-    <t>[np.float64(805.8191090369714), np.float64(550.5614893625145)]</t>
-  </si>
-  <si>
-    <t>[np.float64(161.02061312085436), np.float64(-179.1762127825903)]</t>
-  </si>
-  <si>
-    <t>[np.float64(222.15364567497343), np.float64(-578.4649172013036)]</t>
-  </si>
-  <si>
-    <t>[np.float64(744.4275636901274), np.float64(337.84964537673943)]</t>
-  </si>
-  <si>
-    <t>[np.float64(759.7521888180188), np.float64(293.2485204330602)]</t>
-  </si>
-  <si>
-    <t>[np.float64(34.42628088475941), np.float64(-153.15711449837215)]</t>
-  </si>
-  <si>
-    <t>[np.float64(344.70544007958506), np.float64(26.725762594855837)]</t>
-  </si>
-  <si>
-    <t>[np.float64(90.87906738331364), np.float64(-425.68620314738445)]</t>
-  </si>
-  <si>
-    <t>[np.float64(192.35767087598276), np.float64(-121.04202592956955)]</t>
-  </si>
-  <si>
-    <t>[np.float64(580.70713209263), np.float64(-421.0423721181704)]</t>
-  </si>
-  <si>
-    <t>[np.float64(735.6954965022519), np.float64(-459.8636249316179)]</t>
-  </si>
-  <si>
-    <t>[np.float64(896.5436603671187), np.float64(356.8713768325151)]</t>
-  </si>
-  <si>
-    <t>[np.float64(296.15329572254757), np.float64(359.2678317181385)]</t>
-  </si>
-  <si>
-    <t>[np.float64(154.08781124266648), np.float64(221.66362249857548)]</t>
-  </si>
-  <si>
-    <t>[np.float64(109.03605364599555), np.float64(312.9495009380321)]</t>
-  </si>
-  <si>
-    <t>[np.float64(932.5489313073149), np.float64(52.135026725818534)]</t>
-  </si>
-  <si>
-    <t>[np.float64(160.5960657576624), np.float64(-550.5430469154347)]</t>
-  </si>
-  <si>
-    <t>[np.float64(684.5188535893931), np.float64(-511.3599783975392)]</t>
-  </si>
-  <si>
-    <t>[np.float64(910.9098634912804), np.float64(202.1044882274424)]</t>
-  </si>
-  <si>
-    <t>[np.float64(319.09697760377344), np.float64(-225.34025815353147)]</t>
-  </si>
-  <si>
-    <t>[np.float64(509.37816769660094), np.float64(450.6922447261825)]</t>
-  </si>
-  <si>
-    <t>[np.float64(431.4733011890344), np.float64(134.68838629568688)]</t>
-  </si>
-  <si>
-    <t>[np.float64(510.57757797724565), np.float64(34.16159169003822)]</t>
-  </si>
-  <si>
-    <t>[np.float64(697.4803905957214), np.float64(-527.5863171928995)]</t>
-  </si>
-  <si>
-    <t>[np.float64(458.0529045110937), np.float64(-436.1394948423558)]</t>
-  </si>
-  <si>
-    <t>[np.float64(624.7411034000986), np.float64(459.43177276296365)]</t>
-  </si>
-  <si>
-    <t>[np.float64(33.68745068549273), np.float64(-94.01223530254612)]</t>
-  </si>
-  <si>
-    <t>[np.float64(581.5313425630158), np.float64(-481.1966630059561)]</t>
-  </si>
-  <si>
-    <t>[np.float64(207.68204127553423), np.float64(31.4737289759272)]</t>
-  </si>
-  <si>
-    <t>[np.float64(51.01961482907469), np.float64(467.2907424952132)]</t>
-  </si>
-  <si>
-    <t>[np.float64(736.9483750371453), np.float64(255.19248223472277)]</t>
-  </si>
-  <si>
-    <t>[np.float64(747.6826075188335), np.float64(-327.26851491408934)]</t>
-  </si>
-  <si>
-    <t>[np.float64(252.9285869695155), np.float64(412.99745872455344)]</t>
-  </si>
-  <si>
-    <t>[np.float64(830.5878990329346), np.float64(457.6897782204478)]</t>
-  </si>
-  <si>
-    <t>[np.float64(290.879814970341), np.float64(-226.81012682923046)]</t>
-  </si>
-  <si>
-    <t>[np.float64(687.7378183994907), np.float64(413.0094661512659)]</t>
-  </si>
-  <si>
-    <t>[np.float64(506.69835277504893), np.float64(-113.00062291579036)]</t>
-  </si>
-  <si>
-    <t>[np.float64(823.8417538751), np.float64(-564.0186022984079)]</t>
-  </si>
-  <si>
-    <t>[np.float64(255.6479596409361), np.float64(-396.2064730738838)]</t>
-  </si>
-  <si>
-    <t>[np.float64(245.51005248838896), np.float64(-412.251291391407)]</t>
-  </si>
-  <si>
-    <t>[np.float64(25.67157617750615), np.float64(255.04346901721215)]</t>
-  </si>
-  <si>
-    <t>[np.float64(336.8106385149221), np.float64(71.66703395771754)]</t>
-  </si>
-  <si>
-    <t>[np.float64(807.244571483276), np.float64(205.29267100928905)]</t>
-  </si>
-  <si>
-    <t>[np.float64(473.95473908722386), np.float64(152.36906360559544)]</t>
-  </si>
-  <si>
-    <t>[np.float64(924.0544763210372), np.float64(348.3586338790723)]</t>
-  </si>
-  <si>
-    <t>[np.float64(818.2599948838342), np.float64(-439.5935654326442)]</t>
-  </si>
-  <si>
-    <t>[np.float64(602.3685911391323), np.float64(-123.637170641019)]</t>
-  </si>
-  <si>
-    <t>[np.float64(320.1523035983256), np.float64(456.1348911409232)]</t>
-  </si>
-  <si>
-    <t>[np.float64(33.01855593044234), np.float64(142.54609321890734)]</t>
-  </si>
-  <si>
-    <t>[np.float64(515.7001077096504), np.float64(427.6467051651641)]</t>
-  </si>
-  <si>
-    <t>[np.float64(779.7627715404301), np.float64(-487.0451422397135)]</t>
-  </si>
-  <si>
-    <t>[np.float64(827.1417612275991), np.float64(-187.18540957659167)]</t>
-  </si>
-  <si>
-    <t>[np.float64(734.8527859253054), np.float64(-254.5850087582196)]</t>
-  </si>
-  <si>
-    <t>[np.float64(690.1706478586502), np.float64(183.60853162550904)]</t>
-  </si>
-  <si>
-    <t>[np.float64(367.5718631721517), np.float64(-128.72711995618403)]</t>
-  </si>
-  <si>
-    <t>[np.float64(995.2125776116206), np.float64(-311.5575770827041)]</t>
-  </si>
-  <si>
-    <t>[np.float64(998.2766927900809), np.float64(-316.4623237671606)]</t>
-  </si>
-  <si>
-    <t>[np.float64(309.03061804582876), np.float64(-549.4750825129674)]</t>
-  </si>
-  <si>
-    <t>[np.float64(730.7968250581686), np.float64(253.39447434614306)]</t>
-  </si>
-  <si>
-    <t>[np.float64(820.3507244040931), np.float64(-82.67826495327495)]</t>
-  </si>
-  <si>
-    <t>[np.float64(20.75885089308549), np.float64(-347.8087675668486)]</t>
-  </si>
-  <si>
-    <t>[np.float64(857.2491621211375), np.float64(506.2929469585458)]</t>
-  </si>
-  <si>
-    <t>[np.float64(849.7810315078387), np.float64(163.55514417279858)]</t>
-  </si>
-  <si>
-    <t>[np.float64(921.1488494498228), np.float64(570.2334174264593)]</t>
-  </si>
-  <si>
-    <t>[np.float64(438.96613404268635), np.float64(445.72767593444564)]</t>
-  </si>
-  <si>
-    <t>[np.float64(91.13074988937586), np.float64(512.3942238379632)]</t>
-  </si>
-  <si>
-    <t>[np.float64(191.5162161224716), np.float64(-497.8320496376621)]</t>
-  </si>
-  <si>
-    <t>[np.float64(209.3258776373782), np.float64(264.28049410188294)]</t>
-  </si>
-  <si>
-    <t>[np.float64(324.73244957982917), np.float64(-521.1995710448349)]</t>
-  </si>
-  <si>
-    <t>[np.float64(283.43886166245915), np.float64(-315.1133699860961)]</t>
-  </si>
-  <si>
-    <t>[np.float64(855.2705534398655), np.float64(-218.45106111111147)]</t>
-  </si>
-  <si>
-    <t>[np.float64(825.1664636189299), np.float64(485.5832022241541)]</t>
-  </si>
-  <si>
-    <t>[np.float64(77.59774136448495), np.float64(-380.46312541971633)]</t>
-  </si>
-  <si>
-    <t>[np.float64(79.7920847839837), np.float64(-267.53825226849193)]</t>
-  </si>
-  <si>
-    <t>[np.float64(365.2265156261797), np.float64(-341.26517553201785)]</t>
-  </si>
-  <si>
-    <t>[np.float64(331.2049820988738), np.float64(370.5535102833652)]</t>
-  </si>
-  <si>
-    <t>[np.float64(813.6702723884189), np.float64(45.91939163773634)]</t>
-  </si>
-  <si>
-    <t>[np.float64(109.8136529640783), np.float64(487.6428500057841)]</t>
-  </si>
-  <si>
-    <t>[np.float64(43.912477702750195), np.float64(-328.09935683936897)]</t>
-  </si>
-  <si>
-    <t>[np.float64(442.8961395080485), np.float64(-552.7136511242325)]</t>
-  </si>
-  <si>
-    <t>[np.float64(392.94800398204), np.float64(-334.40550438903784)]</t>
-  </si>
-  <si>
-    <t>[np.float64(73.88702981073425), np.float64(-290.03840397654386)]</t>
-  </si>
-  <si>
-    <t>[np.float64(849.1936436497499), np.float64(-531.314206043442)]</t>
-  </si>
-  <si>
-    <t>[np.float64(649.065102608522), np.float64(414.2705772660487)]</t>
-  </si>
-  <si>
-    <t>[np.float64(512.9854819231471), np.float64(276.898969858123)]</t>
-  </si>
-  <si>
-    <t>[np.float64(879.7405742101453), np.float64(-389.6869896093068)]</t>
-  </si>
-  <si>
-    <t>[np.float64(590.1344366468663), np.float64(115.99909149677353)]</t>
-  </si>
-  <si>
-    <t>[np.float64(215.62839086581997), np.float64(-257.41825470984605)]</t>
-  </si>
-  <si>
-    <t>[np.float64(233.431183349597), np.float64(24.999847371183023)]</t>
-  </si>
-  <si>
-    <t>[np.float64(886.4443800230059), np.float64(-495.62033940747324)]</t>
-  </si>
-  <si>
-    <t>[np.float64(214.5393440118215), np.float64(-573.5919301997501)]</t>
-  </si>
-  <si>
-    <t>[np.float64(285.4630698519033), np.float64(-359.3583874658592)]</t>
-  </si>
-  <si>
-    <t>[np.float64(901.7973284009262), np.float64(-431.76212517206847)]</t>
-  </si>
-  <si>
-    <t>[np.float64(373.3262008992558), np.float64(-257.166255721363)]</t>
-  </si>
-  <si>
-    <t>[np.float64(864.6585879410839), np.float64(192.70846392524913)]</t>
-  </si>
-  <si>
-    <t>[np.float64(518.1552338296899), np.float64(-218.1116529129335)]</t>
-  </si>
-  <si>
-    <t>[np.float64(620.8377563390636), np.float64(597.6720973516758)]</t>
-  </si>
-  <si>
-    <t>[np.float64(390.5679340286417), np.float64(463.63950202621527)]</t>
-  </si>
-  <si>
-    <t>[np.float64(777.1048225724749), np.float64(211.60904336188753)]</t>
-  </si>
-  <si>
-    <t>[np.float64(48.424121164693524), np.float64(-532.0450092143136)]</t>
-  </si>
-  <si>
-    <t>[np.float64(731.04945914408), np.float64(-242.86994425775845)]</t>
-  </si>
-  <si>
-    <t>[np.float64(415.41804066159347), np.float64(-465.7643390912366)]</t>
-  </si>
-  <si>
-    <t>[np.float64(354.6573539200225), np.float64(170.20507720707337)]</t>
-  </si>
-  <si>
-    <t>[np.float64(728.5128636027154), np.float64(194.81813737702782)]</t>
-  </si>
-  <si>
-    <t>[np.float64(691.909294669127), np.float64(-434.425158008864)]</t>
-  </si>
-  <si>
-    <t>[np.float64(105.33191436180023), np.float64(503.9984994946892)]</t>
-  </si>
-  <si>
-    <t>[np.float64(574.1224568012849), np.float64(313.0706061692189)]</t>
-  </si>
-  <si>
-    <t>[np.float64(286.9680530910731), np.float64(-167.70238401168064)]</t>
-  </si>
-  <si>
-    <t>[np.float64(168.86799804831787), np.float64(-467.82982915022774)]</t>
-  </si>
-  <si>
-    <t>[np.float64(592.2880613119024), np.float64(-373.5262921542927)]</t>
-  </si>
-  <si>
-    <t>[np.float64(479.65278813327103), np.float64(546.272782514026)]</t>
-  </si>
-  <si>
-    <t>[np.float64(969.3824087037136), np.float64(520.8162920021105)]</t>
-  </si>
-  <si>
-    <t>[np.float64(645.8829064507958), np.float64(122.61736041861991)]</t>
-  </si>
-  <si>
-    <t>[np.float64(691.7220964802694), np.float64(233.25162367207884)]</t>
-  </si>
-  <si>
-    <t>[np.float64(993.1259340057808), np.float64(-263.0525944257023)]</t>
-  </si>
-  <si>
-    <t>[np.float64(734.9195767928047), np.float64(-551.5279759106209)]</t>
-  </si>
-  <si>
-    <t>[np.float64(204.31097782044915), np.float64(-442.5306342125061)]</t>
-  </si>
-  <si>
-    <t>[np.float64(637.9520844370178), np.float64(566.5491024275702)]</t>
-  </si>
-  <si>
-    <t>[np.float64(915.2264814894597), np.float64(-467.08342075577156)]</t>
-  </si>
-  <si>
-    <t>[np.float64(78.45135370191181), np.float64(-201.06528850131963)]</t>
-  </si>
-  <si>
-    <t>[np.float64(458.8457082520678), np.float64(-212.86154101444953)]</t>
-  </si>
-  <si>
-    <t>[np.float64(305.38392980889085), np.float64(-325.0453011977239)]</t>
-  </si>
-  <si>
-    <t>[np.float64(837.5858917684013), np.float64(453.67752399028836)]</t>
-  </si>
-  <si>
-    <t>[np.float64(162.40742737779058), np.float64(203.91953090835466)]</t>
-  </si>
-  <si>
-    <t>[np.float64(222.13821287947343), np.float64(-440.59609224641565)]</t>
-  </si>
-  <si>
-    <t>[np.float64(652.8384227272857), np.float64(-75.55964728280264)]</t>
-  </si>
-  <si>
-    <t>[np.float64(960.6187700170896), np.float64(40.557530977613396)]</t>
-  </si>
-  <si>
-    <t>[np.float64(81.81586605255397), np.float64(-337.19724374234124)]</t>
-  </si>
-  <si>
-    <t>[np.float64(560.9674258251168), np.float64(-371.23892308082884)]</t>
-  </si>
-  <si>
-    <t>[np.float64(219.1310718619607), np.float64(-569.1032881697936)]</t>
-  </si>
-  <si>
-    <t>[np.float64(104.14579364339538), np.float64(42.545712186672176)]</t>
-  </si>
-  <si>
-    <t>[np.float64(212.9974590903152), np.float64(325.7979951968962)]</t>
-  </si>
-  <si>
-    <t>[np.float64(108.40440686049024), np.float64(295.7475516938555)]</t>
-  </si>
-  <si>
-    <t>[np.float64(8.557741183265133), np.float64(-499.17178825949753)]</t>
-  </si>
-  <si>
-    <t>[np.float64(112.42243411298081), np.float64(466.24526591802965)]</t>
-  </si>
-  <si>
-    <t>[np.float64(423.27580308993737), np.float64(151.62765827214628)]</t>
-  </si>
-  <si>
-    <t>[np.float64(717.0711001199213), np.float64(371.37056428854055)]</t>
-  </si>
-  <si>
-    <t>[np.float64(716.5891549785392), np.float64(-173.8379472773546)]</t>
-  </si>
-  <si>
-    <t>[np.float64(919.6205911401044), np.float64(455.6109127103093)]</t>
-  </si>
-  <si>
-    <t>[np.float64(658.0619696863616), np.float64(255.8022973170216)]</t>
-  </si>
-  <si>
-    <t>[np.float64(496.35925239499625), np.float64(517.4396822195315)]</t>
-  </si>
-  <si>
-    <t>[np.float64(89.37393503468782), np.float64(-230.0914428747244)]</t>
-  </si>
-  <si>
-    <t>[np.float64(882.9232324384078), np.float64(203.37668331616226)]</t>
-  </si>
-  <si>
-    <t>[np.float64(264.1807226783758), np.float64(563.0344670442712)]</t>
-  </si>
-  <si>
-    <t>[np.float64(523.4970022369497), np.float64(85.59276262468711)]</t>
-  </si>
-  <si>
-    <t>[np.float64(832.0662084277702), np.float64(536.4262506921966)]</t>
-  </si>
-  <si>
-    <t>[np.float64(911.3665685976406), np.float64(-412.32033307546885)]</t>
-  </si>
-  <si>
-    <t>[np.float64(800.8080315266373), np.float64(-503.9189032965061)]</t>
-  </si>
-  <si>
-    <t>[np.float64(623.3841992385762), np.float64(303.2203403356614)]</t>
-  </si>
-  <si>
-    <t>[np.float64(584.7087413108874), np.float64(228.9216178621573)]</t>
-  </si>
-  <si>
-    <t>[np.float64(313.5817175053386), np.float64(18.408806835868972)]</t>
-  </si>
-  <si>
-    <t>[np.float64(548.7216362654419), np.float64(68.72982205945891)]</t>
-  </si>
-  <si>
-    <t>[np.float64(401.3934186134455), np.float64(-110.77871697634941)]</t>
-  </si>
-  <si>
-    <t>[np.float64(296.6022295656355), np.float64(41.14429671250582)]</t>
-  </si>
-  <si>
-    <t>[np.float64(847.6021152779624), np.float64(-551.467887810823)]</t>
-  </si>
-  <si>
-    <t>[np.float64(928.2433386802934), np.float64(263.89125317375374)]</t>
-  </si>
-  <si>
-    <t>[np.float64(481.09726345312197), np.float64(-446.73097687368505)]</t>
-  </si>
-  <si>
-    <t>[np.float64(896.2099699601448), np.float64(-520.720542337106)]</t>
-  </si>
-  <si>
-    <t>[np.float64(306.36508859987543), np.float64(323.94206418051976)]</t>
-  </si>
-  <si>
-    <t>[np.float64(525.6726324544238), np.float64(-153.0625525032259)]</t>
-  </si>
-  <si>
-    <t>[np.float64(879.0698876936436), np.float64(-31.344486910914043)]</t>
-  </si>
-  <si>
-    <t>[np.float64(995.7639890118951), np.float64(-60.80313038033262)]</t>
-  </si>
-  <si>
-    <t>[np.float64(734.5571785665707), np.float64(9.3189509413711)]</t>
-  </si>
-  <si>
-    <t>[np.float64(295.492358336898), np.float64(384.81688846496957)]</t>
-  </si>
-  <si>
-    <t>[np.float64(134.54270963434624), np.float64(-455.697132843057)]</t>
-  </si>
-  <si>
-    <t>[np.float64(422.625046477991), np.float64(60.573106029327164)]</t>
-  </si>
-  <si>
-    <t>[np.float64(309.69127092277904), np.float64(459.32407775858724)]</t>
-  </si>
-  <si>
-    <t>[np.float64(144.19118537263142), np.float64(355.4160395227391)]</t>
-  </si>
-  <si>
-    <t>[np.float64(855.6421167834795), np.float64(-76.73821587902455)]</t>
-  </si>
-  <si>
-    <t>[np.float64(307.17620438807313), np.float64(562.621259019247)]</t>
-  </si>
-  <si>
-    <t>[np.float64(878.0600115198939), np.float64(165.9321012684469)]</t>
-  </si>
-  <si>
-    <t>[np.float64(459.79178206445727), np.float64(-480.0489814354935)]</t>
-  </si>
-  <si>
-    <t>[np.float64(405.4611282096544), np.float64(246.30273500002784)]</t>
-  </si>
-  <si>
-    <t>[np.float64(907.8171926205686), np.float64(-338.76195699256334)]</t>
-  </si>
-  <si>
-    <t>[np.float64(494.36007560573967), np.float64(415.8624497556725)]</t>
-  </si>
-  <si>
-    <t>[np.float64(218.56966560447822), np.float64(253.39108510697884)]</t>
-  </si>
-  <si>
-    <t>[np.float64(813.9167775523764), np.float64(556.8144841140913)]</t>
-  </si>
-  <si>
-    <t>[np.float64(772.3842044234145), np.float64(156.93607220443528)]</t>
-  </si>
-  <si>
-    <t>[np.float64(165.76796695602235), np.float64(424.8051042176967)]</t>
-  </si>
-  <si>
-    <t>[np.float64(208.53940600761177), np.float64(449.40371358603215)]</t>
-  </si>
-  <si>
-    <t>[np.float64(84.53956772205484), np.float64(71.97978236296012)]</t>
-  </si>
-  <si>
-    <t>[np.float64(709.1319653407267), np.float64(236.99698096700854)]</t>
-  </si>
-  <si>
-    <t>[np.float64(941.7660300232034), np.float64(-368.7202997313011)]</t>
-  </si>
-  <si>
-    <t>[np.float64(465.08459162755946), np.float64(-176.98030547752552)]</t>
-  </si>
-  <si>
-    <t>[np.float64(467.9152021071544), np.float64(236.0652270927617)]</t>
-  </si>
-  <si>
-    <t>[np.float64(109.93611054962116), np.float64(564.9546909849162)]</t>
-  </si>
-  <si>
-    <t>[np.float64(25.458436067775203), np.float64(-176.25323369306716)]</t>
-  </si>
-  <si>
-    <t>[np.float64(742.0670794879492), np.float64(102.54157449006539)]</t>
-  </si>
-  <si>
-    <t>[np.float64(975.8091748961699), np.float64(474.95513277146165)]</t>
-  </si>
-  <si>
-    <t>[np.float64(616.4329439225346), np.float64(358.18542095495945)]</t>
-  </si>
-  <si>
-    <t>[np.float64(797.3187771427758), np.float64(478.8383296120378)]</t>
-  </si>
-  <si>
-    <t>[np.float64(851.5005453074433), np.float64(146.61510364469075)]</t>
-  </si>
-  <si>
-    <t>[np.float64(803.4142657010842), np.float64(-508.1226418231974)]</t>
-  </si>
-  <si>
-    <t>[np.float64(554.9587620127531), np.float64(111.82048866003424)]</t>
-  </si>
-  <si>
-    <t>[np.float64(181.67250740616038), np.float64(439.3124543373408)]</t>
-  </si>
-  <si>
-    <t>[np.float64(608.5712516718695), np.float64(-558.6311509541531)]</t>
-  </si>
-  <si>
-    <t>[np.float64(476.90772075410473), np.float64(-85.25588157857214)]</t>
-  </si>
-  <si>
-    <t>[np.float64(201.02444783657702), np.float64(-191.02922589145493)]</t>
-  </si>
-  <si>
-    <t>[np.float64(334.9616661264252), np.float64(110.68236249563358)]</t>
-  </si>
-  <si>
-    <t>[np.float64(927.0152058171176), np.float64(-177.9624389308919)]</t>
-  </si>
-  <si>
-    <t>[np.float64(165.67894713016727), np.float64(-323.6963425206893)]</t>
-  </si>
-  <si>
-    <t>[np.float64(766.6365644903753), np.float64(-354.1644985987036)]</t>
-  </si>
-  <si>
-    <t>[np.float64(188.0753534579761), np.float64(455.9527999356335)]</t>
-  </si>
-  <si>
-    <t>[np.float64(389.32572980858447), np.float64(-197.59751283178417)]</t>
-  </si>
-  <si>
-    <t>[np.float64(874.8731285034391), np.float64(-123.05752220979394)]</t>
-  </si>
-  <si>
-    <t>[np.float64(149.0477849337737), np.float64(546.4539613713614)]</t>
-  </si>
-  <si>
-    <t>[np.float64(813.7652526784873), np.float64(62.134712238612565)]</t>
-  </si>
-  <si>
-    <t>[np.float64(37.54721891753632), np.float64(-357.83239216266793)]</t>
-  </si>
-  <si>
-    <t>[np.float64(10.743165508070973), np.float64(263.92853139813917)]</t>
-  </si>
-  <si>
-    <t>[np.float64(932.3786162331338), np.float64(-226.42293876744282)]</t>
-  </si>
-  <si>
-    <t>[np.float64(261.07016706102013), np.float64(-179.84655660900216)]</t>
-  </si>
-  <si>
-    <t>[np.float64(394.5342379063764), np.float64(305.7656469062516)]</t>
-  </si>
-  <si>
-    <t>[np.float64(921.4551237594565), np.float64(-287.9574934852172)]</t>
-  </si>
-  <si>
-    <t>[np.float64(743.3783518694506), np.float64(-234.8731351419425)]</t>
-  </si>
-  <si>
-    <t>[np.float64(241.3733345965383), np.float64(-552.1415724475278)]</t>
-  </si>
-  <si>
-    <t>[np.float64(871.4220081199812), np.float64(494.2658343119549)]</t>
-  </si>
-  <si>
-    <t>[np.float64(560.2508288485718), np.float64(468.83222546387015)]</t>
-  </si>
-  <si>
-    <t>[np.float64(474.55468677119086), np.float64(-214.16524911068893)]</t>
-  </si>
-  <si>
-    <t>[np.float64(103.74400285991747), np.float64(-264.04955684551095)]</t>
-  </si>
-  <si>
-    <t>[np.float64(363.01264004930334), np.float64(24.456559505271798)]</t>
-  </si>
-  <si>
-    <t>[np.float64(330.5237301319761), np.float64(-263.79938956557993)]</t>
-  </si>
-  <si>
-    <t>[np.float64(425.057051389928), np.float64(239.93117082822494)]</t>
-  </si>
-  <si>
-    <t>[np.float64(324.9587865073826), np.float64(-352.9971751823641)]</t>
-  </si>
-  <si>
-    <t>[np.float64(791.4121954486839), np.float64(-495.0853283969536)]</t>
-  </si>
-  <si>
-    <t>[np.float64(830.8405073789455), np.float64(-415.31653774606906)]</t>
-  </si>
-  <si>
-    <t>[np.float64(797.3845535065994), np.float64(-568.164415181078)]</t>
-  </si>
-  <si>
-    <t>[np.float64(967.8936476948656), np.float64(-471.05889181747233)]</t>
-  </si>
-  <si>
-    <t>[np.float64(602.1763976344313), np.float64(-250.55289321714696)]</t>
-  </si>
-  <si>
-    <t>[np.float64(720.6533044252941), np.float64(166.82611644780468)]</t>
-  </si>
-  <si>
-    <t>[np.float64(358.46890830342426), np.float64(-487.7642202439296)]</t>
-  </si>
-  <si>
-    <t>[np.float64(481.3542968157737), np.float64(414.0473348293467)]</t>
-  </si>
-  <si>
-    <t>[np.float64(489.867799289478), np.float64(561.3285307766705)]</t>
-  </si>
-  <si>
-    <t>[np.float64(565.7746948436048), np.float64(167.36814239446744)]</t>
-  </si>
-  <si>
-    <t>[np.float64(655.1708773454296), np.float64(-273.95138910622126)]</t>
-  </si>
-  <si>
-    <t>[np.float64(720.9585840681659), np.float64(110.50767819385521)]</t>
-  </si>
-  <si>
-    <t>[np.float64(731.9672137522957), np.float64(-575.0343588688155)]</t>
-  </si>
-  <si>
-    <t>[np.float64(947.3415042424086), np.float64(454.6751436927045)]</t>
-  </si>
-  <si>
-    <t>[np.float64(921.0349247564695), np.float64(327.35481711880016)]</t>
-  </si>
-  <si>
-    <t>[np.float64(675.526287834158), np.float64(402.74871282718675)]</t>
-  </si>
-  <si>
-    <t>[np.float64(280.7345300015732), np.float64(-242.44390466334858)]</t>
-  </si>
-  <si>
-    <t>[np.float64(729.1377867153439), np.float64(-236.24208166397864)]</t>
-  </si>
-  <si>
-    <t>[np.float64(896.1653263998661), np.float64(161.64574028571428)]</t>
-  </si>
-  <si>
-    <t>[np.float64(337.9011934370443), np.float64(290.6568227719556)]</t>
-  </si>
-  <si>
-    <t>[np.float64(791.1030543964829), np.float64(18.38418047049072)]</t>
-  </si>
-  <si>
-    <t>[np.float64(509.1362798373713), np.float64(545.9481997934483)]</t>
-  </si>
-  <si>
-    <t>[np.float64(166.13381078305045), np.float64(127.25448009518539)]</t>
-  </si>
-  <si>
-    <t>[np.float64(34.68463453379977), np.float64(-424.2295407315968)]</t>
-  </si>
-  <si>
-    <t>[np.float64(3.1797497480599013), np.float64(-245.17508444491307)]</t>
-  </si>
-  <si>
-    <t>[np.float64(24.462603319448164), np.float64(262.5124581289392)]</t>
-  </si>
-  <si>
-    <t>[np.float64(964.4287363285833), np.float64(569.1910726078688)]</t>
-  </si>
-  <si>
-    <t>[np.float64(739.8991048459329), np.float64(-310.7417146846835)]</t>
-  </si>
-  <si>
-    <t>[np.float64(916.4964531132227), np.float64(304.9531610725628)]</t>
-  </si>
-  <si>
-    <t>[np.float64(862.5265926484972), np.float64(-338.45821922857397)]</t>
-  </si>
-  <si>
-    <t>[np.float64(126.42719246427836), np.float64(-74.3746777182323)]</t>
-  </si>
-  <si>
-    <t>[np.float64(145.17587605695425), np.float64(333.06015923670986)]</t>
-  </si>
-  <si>
-    <t>[np.float64(716.4023586723662), np.float64(-488.91683029976116)]</t>
-  </si>
-  <si>
-    <t>[np.float64(721.7537532225093), np.float64(507.61641830438816)]</t>
-  </si>
-  <si>
-    <t>[np.float64(656.9491699330233), np.float64(-109.40134041415189)]</t>
-  </si>
-  <si>
-    <t>[np.float64(438.7430448157781), np.float64(310.09064366979544)]</t>
-  </si>
-  <si>
-    <t>[np.float64(708.5396399447973), np.float64(176.27378913492828)]</t>
-  </si>
-  <si>
-    <t>[np.float64(868.3421521885816), np.float64(-372.2622991675057)]</t>
-  </si>
-  <si>
-    <t>[np.float64(291.1069741674118), np.float64(-500.53366473613585)]</t>
-  </si>
-  <si>
-    <t>[np.float64(238.97669261773225), np.float64(-255.60595665208234)]</t>
-  </si>
-  <si>
-    <t>[np.float64(442.71675547322144), np.float64(-130.93003771991016)]</t>
-  </si>
-  <si>
-    <t>[np.float64(450.09678706954935), np.float64(-547.1320440479392)]</t>
-  </si>
-  <si>
-    <t>[np.float64(289.07725331059555), np.float64(208.19634959125506)]</t>
-  </si>
-  <si>
-    <t>[np.float64(462.202931201524), np.float64(-121.62322274437327)]</t>
-  </si>
-  <si>
-    <t>[np.float64(977.6262158182931), np.float64(476.0943389937918)]</t>
-  </si>
-  <si>
-    <t>[np.float64(87.73990236770568), np.float64(491.8029009907277)]</t>
-  </si>
-  <si>
-    <t>[np.float64(199.999268626725), np.float64(65.16521672149008)]</t>
-  </si>
-  <si>
-    <t>[np.float64(907.5913570730929), np.float64(-193.18420701570932)]</t>
-  </si>
-  <si>
-    <t>[np.float64(285.9659260510328), np.float64(359.395727335139)]</t>
-  </si>
-  <si>
-    <t>[np.float64(266.80359533733167), np.float64(564.979285825349)]</t>
-  </si>
-  <si>
-    <t>[np.float64(699.7408842324338), np.float64(-83.39390821676943)]</t>
-  </si>
-  <si>
-    <t>[np.float64(332.3822864291709), np.float64(491.77530503143566)]</t>
-  </si>
-  <si>
-    <t>[np.float64(194.38698716127956), np.float64(-535.2268698448468)]</t>
-  </si>
-  <si>
-    <t>[np.float64(706.7736293669874), np.float64(-150.69282657977476)]</t>
-  </si>
-  <si>
-    <t>[np.float64(123.76723537424206), np.float64(25.12987188277384)]</t>
-  </si>
-  <si>
-    <t>[np.float64(888.5511870051611), np.float64(361.8543845861195)]</t>
-  </si>
-  <si>
-    <t>[np.float64(463.2542463467709), np.float64(-405.85588619943934)]</t>
-  </si>
-  <si>
-    <t>[np.float64(352.8505769513632), np.float64(456.8768324131995)]</t>
-  </si>
-  <si>
-    <t>[np.float64(735.5424709463548), np.float64(208.98363060425004)]</t>
-  </si>
-  <si>
-    <t>[np.float64(191.24432221143783), np.float64(330.8562860198962)]</t>
-  </si>
-  <si>
-    <t>[np.float64(824.7288368454723), np.float64(-193.68559863943483)]</t>
-  </si>
-  <si>
-    <t>[np.float64(190.2501951023148), np.float64(451.05246658262126)]</t>
-  </si>
-  <si>
-    <t>[np.float64(633.7346603079626), np.float64(-102.1878851473025)]</t>
-  </si>
-  <si>
-    <t>[np.float64(399.6254243768995), np.float64(23.363727084837933)]</t>
-  </si>
-  <si>
-    <t>[np.float64(782.6664723469672), np.float64(-515.9241677670431)]</t>
-  </si>
-  <si>
-    <t>[np.float64(694.6377401538549), np.float64(577.9052995014706)]</t>
-  </si>
-  <si>
-    <t>[np.float64(581.9640370196329), np.float64(355.3829457964972)]</t>
-  </si>
-  <si>
-    <t>[np.float64(472.5310256436801), np.float64(589.462850794526)]</t>
-  </si>
-  <si>
-    <t>[np.float64(143.14770909209162), np.float64(-384.89908911427324)]</t>
-  </si>
-  <si>
-    <t>[np.float64(425.21568601064365), np.float64(-156.36275191661588)]</t>
-  </si>
-  <si>
-    <t>[np.float64(84.27244869217665), np.float64(-208.59117999613932)]</t>
-  </si>
-  <si>
-    <t>[np.float64(699.9588062314431), np.float64(-435.88737650919745)]</t>
-  </si>
-  <si>
-    <t>[np.float64(837.8953732973604), np.float64(-97.51384660670209)]</t>
-  </si>
-  <si>
-    <t>[np.float64(638.1547788936192), np.float64(471.5146879286842)]</t>
-  </si>
-  <si>
-    <t>[np.float64(508.30624973113856), np.float64(-563.1373501259461)]</t>
-  </si>
-  <si>
-    <t>[np.float64(374.1036904645869), np.float64(77.05058460391217)]</t>
-  </si>
-  <si>
-    <t>[np.float64(58.26547427760798), np.float64(100.12627150299124)]</t>
-  </si>
-  <si>
-    <t>[np.float64(556.2786873611842), np.float64(-160.43779466454794)]</t>
-  </si>
-  <si>
-    <t>[np.float64(354.35535585419797), np.float64(-273.4457938698799)]</t>
-  </si>
-  <si>
-    <t>[np.float64(485.98293781570914), np.float64(110.84297847577204)]</t>
-  </si>
-  <si>
-    <t>[np.float64(149.28634199897374), np.float64(-441.1551997756836)]</t>
-  </si>
-  <si>
-    <t>[np.float64(983.4765732533727), np.float64(317.6837161633257)]</t>
-  </si>
-  <si>
-    <t>[np.float64(658.2702379819061), np.float64(-435.40671484873303)]</t>
-  </si>
-  <si>
-    <t>[np.float64(362.49758533174014), np.float64(561.1085487455932)]</t>
-  </si>
-  <si>
-    <t>[np.float64(320.805956811641), np.float64(8.758594395997875)]</t>
-  </si>
-  <si>
-    <t>[np.float64(109.7118208525707), np.float64(-547.7523058271505)]</t>
-  </si>
-  <si>
-    <t>[np.float64(792.3569461724106), np.float64(11.351571069321608)]</t>
-  </si>
-  <si>
-    <t>[np.float64(201.54563297003014), np.float64(-430.6673604374635)]</t>
-  </si>
-  <si>
-    <t>[np.float64(150.4043538212636), np.float64(-334.9110980013799)]</t>
-  </si>
-  <si>
-    <t>[np.float64(588.6033020571019), np.float64(216.68843707988458)]</t>
-  </si>
-  <si>
-    <t>[np.float64(851.6538994014394), np.float64(-171.10441231826724)]</t>
-  </si>
-  <si>
-    <t>[np.float64(700.8381174787802), np.float64(-533.363029942796)]</t>
-  </si>
-  <si>
-    <t>[np.float64(568.1599556415108), np.float64(-410.9885328313345)]</t>
-  </si>
-  <si>
-    <t>[np.float64(722.4453623422886), np.float64(-394.37439300204323)]</t>
-  </si>
-  <si>
-    <t>[np.float64(94.57124244903225), np.float64(240.4838489076493)]</t>
-  </si>
-  <si>
-    <t>[np.float64(66.29039992242592), np.float64(-531.3894392996024)]</t>
-  </si>
-  <si>
-    <t>[np.float64(683.1586292828589), np.float64(402.4594100718077)]</t>
-  </si>
-  <si>
-    <t>[np.float64(903.789314765731), np.float64(-524.6393226836351)]</t>
-  </si>
-  <si>
-    <t>[np.float64(421.83732718407396), np.float64(-486.7562549692936)]</t>
-  </si>
-  <si>
-    <t>[np.float64(108.3727287748898), np.float64(-272.48235002063046)]</t>
-  </si>
-  <si>
-    <t>[np.float64(239.78777116948967), np.float64(194.09837867382794)]</t>
-  </si>
-  <si>
-    <t>[np.float64(913.6450194507629), np.float64(321.47948179753485)]</t>
-  </si>
-  <si>
-    <t>[np.float64(4.943394766643405), np.float64(-590.6680349441256)]</t>
-  </si>
-  <si>
-    <t>[np.float64(969.9076466205703), np.float64(-462.3006739786065)]</t>
-  </si>
-  <si>
-    <t>[np.float64(897.9317226297745), np.float64(231.97282574439862)]</t>
-  </si>
-  <si>
-    <t>[np.float64(943.148594088583), np.float64(241.49825176360264)]</t>
-  </si>
-  <si>
-    <t>[np.float64(117.32944501007414), np.float64(349.1298961106486)]</t>
-  </si>
-  <si>
-    <t>[np.float64(344.8442272776692), np.float64(171.3333840667376)]</t>
-  </si>
-  <si>
-    <t>[np.float64(895.3988408187348), np.float64(144.16442362410396)]</t>
-  </si>
-  <si>
-    <t>[np.float64(149.2866886751326), np.float64(-240.80628826036576)]</t>
-  </si>
-  <si>
-    <t>[np.float64(521.6426442567281), np.float64(-112.99030754507675)]</t>
-  </si>
-  <si>
-    <t>[np.float64(471.4998948006701), np.float64(576.2258082554256)]</t>
-  </si>
-  <si>
-    <t>[np.float64(769.6135746426671), np.float64(540.9818468970868)]</t>
-  </si>
-  <si>
-    <t>[np.float64(298.1277441146615), np.float64(-571.3302548903243)]</t>
-  </si>
-  <si>
-    <t>[np.float64(134.68973766144566), np.float64(-269.3814280907837)]</t>
-  </si>
-  <si>
-    <t>[np.float64(21.248859884796744), np.float64(-145.22703272970807)]</t>
-  </si>
-  <si>
-    <t>[np.float64(349.65142412386007), np.float64(592.957635172254)]</t>
-  </si>
-  <si>
-    <t>[np.float64(601.1790793145387), np.float64(318.75513268547)]</t>
-  </si>
-  <si>
-    <t>[np.float64(859.2675206346996), np.float64(358.8699727109263)]</t>
-  </si>
-  <si>
-    <t>[np.float64(724.3101331321973), np.float64(590.0686800854924)]</t>
-  </si>
-  <si>
-    <t>[np.float64(603.3899216554576), np.float64(177.66946756321022)]</t>
-  </si>
-  <si>
-    <t>[np.float64(865.3881139340457), np.float64(-377.7480945545385)]</t>
-  </si>
-  <si>
-    <t>[np.float64(864.5433849024045), np.float64(-450.68102335170397)]</t>
-  </si>
-  <si>
-    <t>[np.float64(84.81991104584895), np.float64(318.7842810148521)]</t>
-  </si>
-  <si>
-    <t>[np.float64(108.02882144320492), np.float64(273.7360323101202)]</t>
-  </si>
-  <si>
-    <t>[np.float64(966.9679295311256), np.float64(509.27639904588295)]</t>
-  </si>
-  <si>
-    <t>[np.float64(589.3985317090779), np.float64(-346.55087111518196)]</t>
-  </si>
-  <si>
-    <t>[np.float64(435.41292483065206), np.float64(153.82723765836852)]</t>
-  </si>
-  <si>
-    <t>[np.float64(625.9731188887537), np.float64(293.57395625186587)]</t>
-  </si>
-  <si>
-    <t>[np.float64(609.7666437348172), np.float64(-140.85580152569173)]</t>
-  </si>
-  <si>
-    <t>[np.float64(546.4530624365407), np.float64(230.68638516429098)]</t>
-  </si>
-  <si>
-    <t>[np.float64(422.22636221558673), np.float64(-585.7956651901345)]</t>
-  </si>
-  <si>
-    <t>[np.float64(254.15726324865085), np.float64(239.5212452529496)]</t>
-  </si>
-  <si>
-    <t>[np.float64(131.48941518681045), np.float64(390.4514440101526)]</t>
-  </si>
-  <si>
-    <t>[np.float64(199.03251698258984), np.float64(-574.698118746859)]</t>
-  </si>
-  <si>
-    <t>[np.float64(786.3017730806458), np.float64(326.2436388538165)]</t>
-  </si>
-  <si>
-    <t>[np.float64(561.321553161953), np.float64(-448.2251931412993)]</t>
-  </si>
-  <si>
-    <t>[np.float64(840.925294450463), np.float64(-262.55512595569996)]</t>
-  </si>
-  <si>
-    <t>[np.float64(399.1750154342255), np.float64(-135.3159627320038)]</t>
-  </si>
-  <si>
-    <t>[np.float64(19.882101786489415), np.float64(361.1779416663694)]</t>
-  </si>
-  <si>
-    <t>[np.float64(576.7540558794749), np.float64(593.6823800464088)]</t>
-  </si>
-  <si>
-    <t>[np.float64(31.164758390844092), np.float64(390.5752112434411)]</t>
-  </si>
-  <si>
-    <t>[np.float64(373.9456901348822), np.float64(-127.83843486837492)]</t>
-  </si>
-  <si>
-    <t>[np.float64(245.0148351686957), np.float64(-143.0708741495132)]</t>
-  </si>
-  <si>
-    <t>[np.float64(895.743541491091), np.float64(-524.2747789317308)]</t>
-  </si>
-  <si>
-    <t>[np.float64(188.9067078701939), np.float64(197.43575777372928)]</t>
-  </si>
-  <si>
-    <t>[np.float64(277.1229177510337), np.float64(412.73599937596646)]</t>
-  </si>
-  <si>
-    <t>[np.float64(925.968454644225), np.float64(240.7354580388801)]</t>
-  </si>
-  <si>
-    <t>[np.float64(50.94532359196246), np.float64(60.28514318261898)]</t>
-  </si>
-  <si>
-    <t>[np.float64(513.1469673162277), np.float64(-545.5900560781438)]</t>
-  </si>
-  <si>
-    <t>[np.float64(549.6505484209627), np.float64(553.2915434919332)]</t>
-  </si>
-  <si>
-    <t>[np.float64(744.8075618947917), np.float64(278.3931903122958)]</t>
-  </si>
-  <si>
-    <t>[np.float64(202.32750967953606), np.float64(-142.30420248455948)]</t>
-  </si>
-  <si>
-    <t>[np.float64(24.835174400220318), np.float64(401.89700837042017)]</t>
-  </si>
-  <si>
-    <t>[np.float64(150.41007243511183), np.float64(-401.7204130877908)]</t>
-  </si>
-  <si>
-    <t>[np.float64(137.76605315422196), np.float64(-169.34234271218543)]</t>
-  </si>
-  <si>
-    <t>[np.float64(911.3530973088338), np.float64(46.59701116167844)]</t>
-  </si>
-  <si>
-    <t>[np.float64(742.6447452627425), np.float64(441.43631550488203)]</t>
-  </si>
-  <si>
-    <t>[np.float64(46.72552270661456), np.float64(479.7121912191983)]</t>
-  </si>
-  <si>
-    <t>[np.float64(13.688263716932102), np.float64(327.9773949362649)]</t>
-  </si>
-  <si>
-    <t>[np.float64(415.46541782143953), np.float64(-511.59474673676493)]</t>
-  </si>
-  <si>
-    <t>[np.float64(836.1642893674988), np.float64(-482.0209349867252)]</t>
-  </si>
-  <si>
-    <t>[np.float64(280.47170666668484), np.float64(166.77267088769224)]</t>
-  </si>
-  <si>
-    <t>[np.float64(954.4147544447105), np.float64(-347.24878876196556)]</t>
-  </si>
-  <si>
-    <t>[np.float64(295.48669473750556), np.float64(-467.3216793837478)]</t>
-  </si>
-  <si>
-    <t>[np.float64(338.37213431273074), np.float64(-40.96780881070049)]</t>
-  </si>
-  <si>
-    <t>[np.float64(443.9224871874636), np.float64(-230.69663921830272)]</t>
-  </si>
-  <si>
-    <t>[np.float64(686.2245785396233), np.float64(68.48978706429034)]</t>
-  </si>
-  <si>
-    <t>[np.float64(584.2760705359758), np.float64(-186.0049779150911)]</t>
-  </si>
-  <si>
-    <t>[np.float64(816.487670167367), np.float64(-517.1260468593148)]</t>
-  </si>
-  <si>
-    <t>[np.float64(426.91689874863914), np.float64(315.8114642702352)]</t>
-  </si>
-  <si>
-    <t>[np.float64(987.295930234722), np.float64(356.07112191455553)]</t>
-  </si>
-  <si>
-    <t>[np.float64(465.03417872520913), np.float64(-229.1701809210897)]</t>
-  </si>
-  <si>
-    <t>[np.float64(454.4484795615237), np.float64(359.7775925662628)]</t>
-  </si>
-  <si>
-    <t>[np.float64(623.3879725999154), np.float64(-229.2229506650773)]</t>
-  </si>
-  <si>
-    <t>[np.float64(494.08688116129883), np.float64(213.2235649246761)]</t>
-  </si>
-  <si>
-    <t>[np.float64(59.09305782367225), np.float64(123.79294827048057)]</t>
-  </si>
-  <si>
-    <t>[np.float64(991.9699461078978), np.float64(-333.8229607438982)]</t>
-  </si>
-  <si>
-    <t>[np.float64(96.65932462955173), np.float64(163.92146080555574)]</t>
-  </si>
-  <si>
-    <t>[np.float64(764.1601879885734), np.float64(-554.2849737319813)]</t>
-  </si>
-  <si>
-    <t>[np.float64(198.0122780164494), np.float64(149.25263538536444)]</t>
-  </si>
-  <si>
-    <t>[np.float64(335.2452345064554), np.float64(26.01430836190434)]</t>
-  </si>
-  <si>
-    <t>[np.float64(110.98730346716879), np.float64(354.56721062056226)]</t>
-  </si>
-  <si>
-    <t>[np.float64(517.042683579776), np.float64(330.7974431002539)]</t>
-  </si>
-  <si>
-    <t>[np.float64(794.9241020046761), np.float64(1.8984824577147492)]</t>
-  </si>
-  <si>
-    <t>[np.float64(574.9887057143618), np.float64(158.44730115375683)]</t>
-  </si>
-  <si>
-    <t>[np.float64(256.37696446277994), np.float64(219.43174950272657)]</t>
-  </si>
-  <si>
-    <t>[np.float64(734.4368978685388), np.float64(479.41614497558544)]</t>
-  </si>
-  <si>
-    <t>[np.float64(901.6074219533235), np.float64(-183.24892581026563)]</t>
-  </si>
-  <si>
-    <t>[np.float64(491.9411191689886), np.float64(578.7417545495796)]</t>
-  </si>
-  <si>
-    <t>[np.float64(433.74032210423496), np.float64(340.19919547867755)]</t>
-  </si>
-  <si>
-    <t>[np.float64(780.7904683752733), np.float64(-566.1450461843265)]</t>
-  </si>
-  <si>
-    <t>[np.float64(718.9446031798611), np.float64(-500.9282974689202)]</t>
-  </si>
-  <si>
-    <t>[np.float64(456.2108009210197), np.float64(507.28368157027944)]</t>
-  </si>
-  <si>
-    <t>[np.float64(334.77031147761835), np.float64(384.5085525021998)]</t>
-  </si>
-  <si>
-    <t>[np.float64(726.7789071329959), np.float64(-294.9847868763905)]</t>
-  </si>
-  <si>
-    <t>[np.float64(698.2241006450325), np.float64(202.75782910669295)]</t>
-  </si>
-  <si>
-    <t>[np.float64(533.1778904953482), np.float64(105.11947763532248)]</t>
-  </si>
-  <si>
-    <t>[np.float64(250.69372763742803), np.float64(-405.2906758920496)]</t>
-  </si>
-  <si>
-    <t>[np.float64(313.7409157507693), np.float64(564.4847946963305)]</t>
-  </si>
-  <si>
-    <t>[np.float64(442.89830998907445), np.float64(221.37891561178276)]</t>
-  </si>
-  <si>
-    <t>[np.float64(801.4253098918402), np.float64(451.03313158882906)]</t>
-  </si>
-  <si>
-    <t>[np.float64(281.9584915305963), np.float64(467.6110573965525)]</t>
-  </si>
-  <si>
-    <t>[np.float64(810.4328881831506), np.float64(-78.98678137652178)]</t>
-  </si>
-  <si>
-    <t>[np.float64(160.20871097909873), np.float64(-232.71369754402855)]</t>
-  </si>
-  <si>
-    <t>[np.float64(135.34294090283106), np.float64(54.753414604490445)]</t>
-  </si>
-  <si>
-    <t>[np.float64(913.7819304448624), np.float64(-198.8380569089764)]</t>
-  </si>
-  <si>
-    <t>[np.float64(464.7149643430065), np.float64(-345.0166283192349)]</t>
-  </si>
-  <si>
-    <t>[np.float64(677.0938087112687), np.float64(-449.2597073487675)]</t>
-  </si>
-  <si>
-    <t>[np.float64(964.5362984002192), np.float64(149.4654321676619)]</t>
-  </si>
-  <si>
-    <t>[np.float64(6.36106177394391), np.float64(-320.91590137741036)]</t>
-  </si>
-  <si>
-    <t>[np.float64(603.3945458076921), np.float64(-511.13815584773624)]</t>
-  </si>
-  <si>
-    <t>[np.float64(558.6596786381806), np.float64(-555.8631431235368)]</t>
-  </si>
-  <si>
-    <t>[np.float64(738.1876056086348), np.float64(-368.84462191025)]</t>
-  </si>
-  <si>
-    <t>[np.float64(783.2883899018572), np.float64(544.5295650445403)]</t>
-  </si>
-  <si>
-    <t>[np.float64(725.5201328136202), np.float64(276.12663975416046)]</t>
-  </si>
-  <si>
-    <t>[np.float64(403.67683650052464), np.float64(-568.327604716678)]</t>
-  </si>
-  <si>
-    <t>[np.float64(188.050842591315), np.float64(-373.14319333100275)]</t>
-  </si>
-  <si>
-    <t>[np.float64(425.6687655748177), np.float64(87.33233019052909)]</t>
-  </si>
-  <si>
-    <t>[np.float64(881.8453468850237), np.float64(-320.7045574614336)]</t>
-  </si>
-  <si>
-    <t>[np.float64(194.21202788677428), np.float64(585.9689834824953)]</t>
-  </si>
-  <si>
-    <t>[np.float64(619.9028746432423), np.float64(-131.96222133545155)]</t>
-  </si>
-  <si>
-    <t>[np.float64(920.1943003024113), np.float64(215.80614397012323)]</t>
-  </si>
-  <si>
-    <t>[np.float64(956.729231316855), np.float64(524.86658544125)]</t>
-  </si>
-  <si>
-    <t>[np.float64(986.8250069499), np.float64(179.39021618658887)]</t>
-  </si>
-  <si>
-    <t>[np.float64(945.2399010718714), np.float64(487.35075824937826)]</t>
-  </si>
-  <si>
-    <t>[np.float64(543.8431871297939), np.float64(439.8341354622821)]</t>
-  </si>
-  <si>
-    <t>[np.float64(257.58105320531297), np.float64(-460.96662083659976)]</t>
-  </si>
-  <si>
-    <t>[np.float64(714.7814071276744), np.float64(-131.542396869745)]</t>
-  </si>
-  <si>
-    <t>[np.float64(703.8929989448682), np.float64(151.37491525333917)]</t>
-  </si>
-  <si>
-    <t>[np.float64(694.5081350516914), np.float64(-100.55684422474701)]</t>
-  </si>
-  <si>
-    <t>[np.float64(877.1862813743617), np.float64(397.51146312607113)]</t>
-  </si>
-  <si>
-    <t>[np.float64(340.7895439931704), np.float64(136.00950946835553)]</t>
-  </si>
-  <si>
-    <t>[np.float64(968.5913167940149), np.float64(228.0028355389769)]</t>
-  </si>
-  <si>
-    <t>[np.float64(566.9899920776645), np.float64(-210.951177234115)]</t>
-  </si>
-  <si>
-    <t>[np.float64(144.4237841497249), np.float64(352.4593022397222)]</t>
-  </si>
-  <si>
-    <t>[np.float64(634.3584483189147), np.float64(-395.7225179672216)]</t>
-  </si>
-  <si>
-    <t>[np.float64(314.96802421128547), np.float64(-397.6247609608821)]</t>
-  </si>
-  <si>
-    <t>[np.float64(187.68331898915247), np.float64(-472.89157339364306)]</t>
-  </si>
-  <si>
-    <t>[np.float64(183.4020901653154), np.float64(-434.3552844633945)]</t>
-  </si>
-  <si>
-    <t>[np.float64(667.8264878931986), np.float64(-216.0786318063233)]</t>
-  </si>
-  <si>
-    <t>[np.float64(760.2591550411126), np.float64(-211.19509417860962)]</t>
-  </si>
-  <si>
-    <t>[np.float64(345.3559537234073), np.float64(-586.1851696757808)]</t>
-  </si>
-  <si>
-    <t>[np.float64(17.448633193417272), np.float64(333.523001921538)]</t>
-  </si>
-  <si>
-    <t>[np.float64(79.0564482693782), np.float64(595.3834282310845)]</t>
-  </si>
-  <si>
-    <t>[np.float64(644.9034517856056), np.float64(-573.6110890303794)]</t>
-  </si>
-  <si>
-    <t>[np.float64(199.4048660563812), np.float64(-64.54093968292261)]</t>
-  </si>
-  <si>
-    <t>[np.float64(617.7363454141407), np.float64(260.9368402268484)]</t>
-  </si>
-  <si>
-    <t>[np.float64(882.6777885934456), np.float64(-450.4136144395154)]</t>
-  </si>
-  <si>
-    <t>[np.float64(380.76954714433754), np.float64(-350.52024014573135)]</t>
-  </si>
-  <si>
-    <t>[np.float64(720.7541957576675), np.float64(315.7404876537313)]</t>
-  </si>
-  <si>
-    <t>[np.float64(696.7801102936387), np.float64(77.6650041358206)]</t>
-  </si>
-  <si>
-    <t>[np.float64(853.9947303856768), np.float64(-267.2216305448911)]</t>
-  </si>
-  <si>
-    <t>[np.float64(767.232165321159), np.float64(495.41153028690223)]</t>
-  </si>
-  <si>
-    <t>[np.float64(168.45989847280063), np.float64(117.93833508242767)]</t>
-  </si>
-  <si>
-    <t>[np.float64(740.6064225123033), np.float64(-483.6916583312784)]</t>
-  </si>
-  <si>
-    <t>[np.float64(681.7187369754984), np.float64(353.0722306886238)]</t>
-  </si>
-  <si>
-    <t>[np.float64(62.521171128310016), np.float64(-323.5314362081729)]</t>
-  </si>
-  <si>
-    <t>[np.float64(613.3277127631845), np.float64(-575.0109263261731)]</t>
-  </si>
-  <si>
-    <t>[np.float64(208.47044561725735), np.float64(-334.1930410390333)]</t>
-  </si>
-  <si>
-    <t>[np.float64(784.7468524067586), np.float64(234.3579393061508)]</t>
-  </si>
-  <si>
-    <t>[np.float64(683.7335529868973), np.float64(-138.1837474572739)]</t>
-  </si>
-  <si>
-    <t>[np.float64(632.9011624081611), np.float64(297.7174566278078)]</t>
-  </si>
-  <si>
-    <t>[np.float64(996.0950905655357), np.float64(-359.39826646552615)]</t>
-  </si>
-  <si>
-    <t>[np.float64(790.1353703166141), np.float64(-303.18687688800526)]</t>
-  </si>
-  <si>
-    <t>[np.float64(238.19173783492965), np.float64(-202.56076791575077)]</t>
-  </si>
-  <si>
-    <t>[np.float64(82.47940649100849), np.float64(572.2224430819701)]</t>
-  </si>
-  <si>
-    <t>[np.float64(847.5581429456944), np.float64(261.1788498823414)]</t>
-  </si>
-  <si>
-    <t>[np.float64(818.8466876686972), np.float64(-128.16918222074122)]</t>
-  </si>
-  <si>
-    <t>[np.float64(611.9087485669401), np.float64(-145.4065133913063)]</t>
-  </si>
-  <si>
-    <t>[np.float64(671.474831543822), np.float64(31.425200281963498)]</t>
-  </si>
-  <si>
-    <t>[np.float64(269.0660169158036), np.float64(145.121347119083)]</t>
-  </si>
-  <si>
-    <t>[np.float64(921.684066650914), np.float64(-591.695024541416)]</t>
-  </si>
-  <si>
-    <t>[np.float64(108.00318254855168), np.float64(-316.4474513631171)]</t>
-  </si>
-  <si>
-    <t>[np.float64(869.6601961452252), np.float64(179.80200975099808)]</t>
-  </si>
-  <si>
-    <t>[np.float64(238.792973085462), np.float64(335.5265844340149)]</t>
-  </si>
-  <si>
-    <t>[np.float64(998.5145727683362), np.float64(505.7924275880175)]</t>
-  </si>
-  <si>
-    <t>[np.float64(313.98449634067936), np.float64(111.07607658491145)]</t>
-  </si>
-  <si>
-    <t>[np.float64(62.80236039216802), np.float64(278.17412804809237)]</t>
-  </si>
-  <si>
-    <t>[np.float64(175.47740046126935), np.float64(65.47956291100297)]</t>
-  </si>
-  <si>
-    <t>[np.float64(385.0538338410804), np.float64(-489.14227435697296)]</t>
-  </si>
-  <si>
-    <t>[np.float64(565.640283138595), np.float64(3.2976596241039715)]</t>
-  </si>
-  <si>
-    <t>[np.float64(203.65764145921793), np.float64(181.92161863484034)]</t>
-  </si>
-  <si>
-    <t>[np.float64(589.7640409000307), np.float64(50.92176682770537)]</t>
-  </si>
-  <si>
-    <t>[np.float64(270.76647227308916), np.float64(530.654643851773)]</t>
-  </si>
-  <si>
-    <t>[np.float64(891.8291073486173), np.float64(47.24113643427802)]</t>
-  </si>
-  <si>
-    <t>[np.float64(461.7677352487403), np.float64(519.0189804177298)]</t>
-  </si>
-  <si>
-    <t>[np.float64(159.62567917296255), np.float64(48.012715937531766)]</t>
-  </si>
-  <si>
-    <t>[np.float64(75.81235522625617), np.float64(-456.2480859331232)]</t>
-  </si>
-  <si>
-    <t>[np.float64(728.3999517672328), np.float64(-366.16506681667363)]</t>
-  </si>
-  <si>
-    <t>[np.float64(549.8364900061731), np.float64(-562.5055304031484)]</t>
-  </si>
-  <si>
-    <t>[np.float64(92.29628855850413), np.float64(464.5087206336432)]</t>
-  </si>
-  <si>
-    <t>[np.float64(940.4633212134544), np.float64(458.2571410667099)]</t>
-  </si>
-  <si>
-    <t>[np.float64(973.5154493336602), np.float64(-132.5150798111236)]</t>
-  </si>
-  <si>
-    <t>[np.float64(848.4316756398979), np.float64(-236.63128272445488)]</t>
-  </si>
-  <si>
-    <t>[np.float64(313.0001830639401), np.float64(400.80243305448664)]</t>
-  </si>
-  <si>
-    <t>[np.float64(430.1546354251069), np.float64(557.222708031074)]</t>
-  </si>
-  <si>
-    <t>[np.float64(67.07395302873142), np.float64(309.8484841315386)]</t>
-  </si>
-  <si>
-    <t>[np.float64(969.253044628029), np.float64(586.6459388563057)]</t>
-  </si>
-  <si>
-    <t>[np.float64(275.1006660148765), np.float64(125.70203425649095)]</t>
-  </si>
-  <si>
-    <t>[np.float64(819.7603326426057), np.float64(-250.30143475033162)]</t>
-  </si>
-  <si>
-    <t>[np.float64(711.7568661432229), np.float64(583.892282519424)]</t>
-  </si>
-  <si>
-    <t>[np.float64(281.7360399103441), np.float64(430.9142058042876)]</t>
-  </si>
-  <si>
-    <t>[np.float64(538.1377080605232), np.float64(341.39568593552735)]</t>
-  </si>
-  <si>
-    <t>[np.float64(638.8884922812513), np.float64(-268.81029368423884)]</t>
-  </si>
-  <si>
-    <t>[np.float64(569.0639436131582), np.float64(96.15930806971232)]</t>
-  </si>
-  <si>
-    <t>[np.float64(877.7392628658461), np.float64(265.28865880567355)]</t>
-  </si>
-  <si>
-    <t>[np.float64(278.70892197214937), np.float64(-509.83254126494955)]</t>
-  </si>
-  <si>
-    <t>[np.float64(750.3416285982178), np.float64(32.05120866527545)]</t>
-  </si>
-  <si>
-    <t>[np.float64(846.26590038978), np.float64(-193.1201928026997)]</t>
-  </si>
-  <si>
-    <t>[np.float64(443.3111261965135), np.float64(573.5803756149899)]</t>
-  </si>
-  <si>
-    <t>[np.float64(785.911079256451), np.float64(-517.8968776726401)]</t>
-  </si>
-  <si>
-    <t>[np.float64(334.33338333918005), np.float64(-290.52988260993453)]</t>
-  </si>
-  <si>
-    <t>[np.float64(883.7824195911694), np.float64(213.69555681314012)]</t>
-  </si>
-  <si>
-    <t>[np.float64(517.7309017609342), np.float64(-140.71099642722157)]</t>
-  </si>
-  <si>
-    <t>[np.float64(941.5328105113226), np.float64(-127.63386918114054)]</t>
-  </si>
-  <si>
-    <t>[np.float64(849.390013475023), np.float64(-167.21054006977226)]</t>
-  </si>
-  <si>
-    <t>[np.float64(388.99446017328586), np.float64(198.19623930268904)]</t>
-  </si>
-  <si>
-    <t>[np.float64(208.75530351181726), np.float64(-270.4395360966419)]</t>
-  </si>
-  <si>
-    <t>[np.float64(208.0154362534694), np.float64(-314.10886368113404)]</t>
-  </si>
-  <si>
-    <t>[np.float64(629.9701518989154), np.float64(431.9036300582213)]</t>
-  </si>
-  <si>
-    <t>[np.float64(685.0139833113121), np.float64(-131.632748804472)]</t>
-  </si>
-  <si>
-    <t>[np.float64(510.5593386190919), np.float64(-433.1809660255889)]</t>
-  </si>
-  <si>
-    <t>[np.float64(464.212831747128), np.float64(-62.263961033143005)]</t>
-  </si>
-  <si>
-    <t>[np.float64(983.7217742181632), np.float64(250.5967692462932)]</t>
-  </si>
-  <si>
-    <t>[np.float64(414.09247964279064), np.float64(-339.67488630204696)]</t>
-  </si>
-  <si>
-    <t>[np.float64(483.88969556736373), np.float64(91.23912372259099)]</t>
-  </si>
-  <si>
-    <t>[np.float64(229.8465930725112), np.float64(243.50530984962097)]</t>
-  </si>
-  <si>
-    <t>[np.float64(108.5613322211898), np.float64(-591.43313889813)]</t>
-  </si>
-  <si>
-    <t>[np.float64(66.14255408672621), np.float64(-385.02546905399333)]</t>
-  </si>
-  <si>
-    <t>[np.float64(833.4446173978507), np.float64(266.7052354015916)]</t>
-  </si>
-  <si>
-    <t>[np.float64(620.6444123854247), np.float64(121.89458166615009)]</t>
-  </si>
-  <si>
-    <t>[np.float64(791.9952672725968), np.float64(380.9361535819471)]</t>
-  </si>
-  <si>
-    <t>[np.float64(614.0498736017782), np.float64(-478.5517050526725)]</t>
-  </si>
-  <si>
-    <t>[np.float64(786.9955239708308), np.float64(-372.11862617454494)]</t>
-  </si>
-  <si>
-    <t>[np.float64(966.6784852662544), np.float64(519.5364601674155)]</t>
-  </si>
-  <si>
-    <t>[np.float64(34.99666300498061), np.float64(-102.94960898490734)]</t>
-  </si>
-  <si>
-    <t>[np.float64(363.64319394612863), np.float64(-304.73518995221326)]</t>
-  </si>
-  <si>
-    <t>[np.float64(901.0536760992333), np.float64(390.77303986548156)]</t>
-  </si>
-  <si>
-    <t>[np.float64(528.0790065733804), np.float64(-469.9820500832114)]</t>
-  </si>
-  <si>
-    <t>[np.float64(71.12073888177228), np.float64(544.5197957574842)]</t>
-  </si>
-  <si>
-    <t>[np.float64(678.8894651167542), np.float64(79.97774717241487)]</t>
-  </si>
-  <si>
-    <t>[np.float64(746.400052247101), np.float64(-326.0762700635963)]</t>
-  </si>
-  <si>
-    <t>[np.float64(114.48404100566611), np.float64(-457.3859303396139)]</t>
-  </si>
-  <si>
-    <t>[np.float64(511.9811825628946), np.float64(-589.9126202842745)]</t>
-  </si>
-  <si>
-    <t>[np.float64(387.7084634387434), np.float64(52.41940120562049)]</t>
-  </si>
-  <si>
-    <t>[np.float64(491.85694658959136), np.float64(16.65101706112887)]</t>
-  </si>
-  <si>
-    <t>[np.float64(377.38012099066486), np.float64(-305.8397645380364)]</t>
-  </si>
-  <si>
-    <t>[np.float64(71.0350638268149), np.float64(-301.64717923547795)]</t>
-  </si>
-  <si>
-    <t>[np.float64(396.50475604668435), np.float64(-20.67055962206382)]</t>
-  </si>
-  <si>
-    <t>[np.float64(861.3853077058388), np.float64(41.13720422921813)]</t>
-  </si>
-  <si>
-    <t>[np.float64(178.14238649200632), np.float64(426.38603159622744)]</t>
-  </si>
-  <si>
-    <t>[np.float64(276.63766712176596), np.float64(435.78942457913126)]</t>
-  </si>
-  <si>
-    <t>[np.float64(130.6979832229993), np.float64(350.03346269646215)]</t>
-  </si>
-  <si>
-    <t>[np.float64(288.23394936944834), np.float64(-256.86894889710663)]</t>
-  </si>
-  <si>
-    <t>[np.float64(534.3481396696127), np.float64(155.68133026173427)]</t>
-  </si>
-  <si>
-    <t>[np.float64(271.09058892184976), np.float64(539.4489158260255)]</t>
-  </si>
-  <si>
-    <t>[np.float64(364.4146867421155), np.float64(386.8705153312811)]</t>
-  </si>
-  <si>
-    <t>[np.float64(911.5339858510944), np.float64(-270.93578511046354)]</t>
-  </si>
-  <si>
-    <t>[np.float64(416.1976862789368), np.float64(-260.5287524565415)]</t>
-  </si>
-  <si>
-    <t>[np.float64(165.31092513020695), np.float64(-87.81165909218498)]</t>
-  </si>
-  <si>
-    <t>[np.float64(534.9397874429096), np.float64(83.1415639235388)]</t>
-  </si>
-  <si>
-    <t>[np.float64(404.51521481994047), np.float64(-405.9801319807465)]</t>
-  </si>
-  <si>
-    <t>[np.float64(451.9864487121114), np.float64(-216.38227220260677)]</t>
-  </si>
-  <si>
-    <t>[np.float64(879.0233759332896), np.float64(-197.58550140811076)]</t>
-  </si>
-  <si>
-    <t>[np.float64(865.7489131094102), np.float64(496.80580549301885)]</t>
-  </si>
-  <si>
-    <t>[np.float64(757.2368943579253), np.float64(-456.50680064191914)]</t>
-  </si>
-  <si>
-    <t>[np.float64(620.8635807202888), np.float64(-170.8493127153763)]</t>
-  </si>
-  <si>
-    <t>[np.float64(181.4547292267118), np.float64(22.768758500483614)]</t>
-  </si>
-  <si>
-    <t>[np.float64(220.91094883875317), np.float64(-463.4388443063403)]</t>
-  </si>
-  <si>
-    <t>[np.float64(241.32095076239622), np.float64(470.1967313286834)]</t>
-  </si>
-  <si>
-    <t>[np.float64(425.43248672337677), np.float64(-544.3269326643452)]</t>
-  </si>
-  <si>
-    <t>[np.float64(467.57072285572275), np.float64(-164.6369750086431)]</t>
-  </si>
-  <si>
-    <t>[np.float64(900.9792401254471), np.float64(212.30314045887178)]</t>
-  </si>
-  <si>
-    <t>[np.float64(473.3353936623359), np.float64(193.73869014833417)]</t>
-  </si>
-  <si>
-    <t>[np.float64(858.582075840736), np.float64(-192.92388766914763)]</t>
-  </si>
-  <si>
-    <t>[np.float64(86.07221186031478), np.float64(427.7677932085903)]</t>
-  </si>
-  <si>
-    <t>[np.float64(636.6217800166858), np.float64(374.97228045920724)]</t>
-  </si>
-  <si>
-    <t>[np.float64(855.5666240112926), np.float64(360.2214201472989)]</t>
-  </si>
-  <si>
-    <t>[np.float64(787.970250713375), np.float64(190.07880448851847)]</t>
-  </si>
-  <si>
-    <t>[np.float64(963.0421197445854), np.float64(599.3693885773544)]</t>
-  </si>
-  <si>
-    <t>[np.float64(921.3599927091717), np.float64(182.857131409236)]</t>
-  </si>
-  <si>
-    <t>[np.float64(163.4036607964865), np.float64(99.4863802547826)]</t>
-  </si>
-  <si>
-    <t>[np.float64(998.826105596409), np.float64(-451.42519226412594)]</t>
-  </si>
-  <si>
-    <t>[np.float64(500.1217307277778), np.float64(-217.06253449488617)]</t>
-  </si>
-  <si>
-    <t>[np.float64(596.5999084122438), np.float64(-199.75345060899963)]</t>
-  </si>
-  <si>
-    <t>[np.float64(156.1527930785025), np.float64(-506.1463106095274)]</t>
-  </si>
-  <si>
-    <t>[np.float64(59.52612845721794), np.float64(96.35316587732984)]</t>
-  </si>
-  <si>
-    <t>[np.float64(301.25860075343644), np.float64(-415.4546119597589)]</t>
-  </si>
-  <si>
-    <t>[np.float64(304.7348105619985), np.float64(10.889595427359495)]</t>
-  </si>
-  <si>
-    <t>[np.float64(334.9545166857444), np.float64(171.39804873053595)]</t>
-  </si>
-  <si>
-    <t>[np.float64(582.4588298986807), np.float64(-237.09672906196266)]</t>
-  </si>
-  <si>
-    <t>[np.float64(17.11628141265853), np.float64(506.77160641872933)]</t>
-  </si>
-  <si>
-    <t>[np.float64(707.3236801379303), np.float64(-146.06268866931777)]</t>
-  </si>
-  <si>
-    <t>[np.float64(58.0670600187817), np.float64(-515.2756494229727)]</t>
-  </si>
-  <si>
-    <t>[np.float64(467.6389304925802), np.float64(-353.0307062098733)]</t>
-  </si>
-  <si>
-    <t>[np.float64(282.6329987265941), np.float64(320.5653209754141)]</t>
-  </si>
-  <si>
-    <t>[np.float64(981.881894633957), np.float64(313.9983844765537)]</t>
-  </si>
-  <si>
-    <t>[np.float64(365.8787298166578), np.float64(-196.64272508415996)]</t>
-  </si>
-  <si>
-    <t>[np.float64(668.2554029318351), np.float64(-454.0633292380925)]</t>
-  </si>
-  <si>
-    <t>[np.float64(265.0981811589246), np.float64(477.40002626400155)]</t>
-  </si>
-  <si>
-    <t>[np.float64(82.56134270478942), np.float64(240.28651393877453)]</t>
-  </si>
-  <si>
-    <t>[np.float64(813.1878202959014), np.float64(-472.3274910455335)]</t>
-  </si>
-  <si>
-    <t>[np.float64(521.2104542548167), np.float64(345.7032732840073)]</t>
-  </si>
-  <si>
-    <t>[np.float64(451.9992614830181), np.float64(378.67129845593365)]</t>
-  </si>
-  <si>
-    <t>[np.float64(122.25951083776788), np.float64(-496.25822166997074)]</t>
-  </si>
-  <si>
-    <t>[np.float64(925.3403537524591), np.float64(-444.7175016508734)]</t>
-  </si>
-  <si>
-    <t>[np.float64(383.7830645987973), np.float64(333.1829986291035)]</t>
-  </si>
-  <si>
-    <t>[np.float64(935.085127035598), np.float64(464.06524601673414)]</t>
-  </si>
-  <si>
-    <t>[np.float64(66.77916516427985), np.float64(-66.80067624283868)]</t>
-  </si>
-  <si>
-    <t>[np.float64(491.2630693526546), np.float64(274.45631679671794)]</t>
-  </si>
-  <si>
-    <t>[np.float64(798.6166868947139), np.float64(-254.98977513156836)]</t>
-  </si>
-  <si>
-    <t>[np.float64(578.6014322813835), np.float64(11.657615288054558)]</t>
-  </si>
-  <si>
-    <t>[np.float64(652.8135065770076), np.float64(568.540627613057)]</t>
-  </si>
-  <si>
-    <t>[np.float64(561.2355367770455), np.float64(109.36404630358675)]</t>
-  </si>
-  <si>
-    <t>[np.float64(60.038352082209315), np.float64(427.38404368286433)]</t>
-  </si>
-  <si>
-    <t>[np.float64(989.9832817366764), np.float64(-391.0002580651339)]</t>
-  </si>
-  <si>
-    <t>[np.float64(394.42609707510655), np.float64(504.0236970416938)]</t>
-  </si>
-  <si>
-    <t>[np.float64(814.9770312514805), np.float64(-546.8621482353284)]</t>
-  </si>
-  <si>
-    <t>[np.float64(628.2085331517555), np.float64(556.7408130579843)]</t>
-  </si>
-  <si>
-    <t>[np.float64(528.6770428784772), np.float64(-542.9157554644221)]</t>
+    <t>[np.float64(698.0572177656861), np.float64(571.1659745989821)]</t>
+  </si>
+  <si>
+    <t>[np.float64(345.9889108157832), np.float64(-403.6040787588984)]</t>
+  </si>
+  <si>
+    <t>[np.float64(580.1129574787238), np.float64(272.82133423589414)]</t>
+  </si>
+  <si>
+    <t>[np.float64(673.8227654716696), np.float64(-92.60985242468587)]</t>
+  </si>
+  <si>
+    <t>[np.float64(893.9797016930522), np.float64(158.546201827088)]</t>
+  </si>
+  <si>
+    <t>[np.float64(830.47363664844), np.float64(-140.16348146680167)]</t>
+  </si>
+  <si>
+    <t>[np.float64(353.45860721954705), np.float64(-471.3965495185956)]</t>
+  </si>
+  <si>
+    <t>[np.float64(805.2810754916198), np.float64(-87.70987358170873)]</t>
+  </si>
+  <si>
+    <t>[np.float64(626.034430943751), np.float64(435.176244444591)]</t>
+  </si>
+  <si>
+    <t>[np.float64(888.5089578083835), np.float64(-548.2623998987458)]</t>
+  </si>
+  <si>
+    <t>[np.float64(10.094054085015403), np.float64(-263.2398268260607)]</t>
+  </si>
+  <si>
+    <t>[np.float64(787.0770431987471), np.float64(279.3447446079015)]</t>
+  </si>
+  <si>
+    <t>[np.float64(160.96640159364907), np.float64(-517.8268973974157)]</t>
+  </si>
+  <si>
+    <t>[np.float64(799.3179187366843), np.float64(105.6322763472615)]</t>
+  </si>
+  <si>
+    <t>[np.float64(204.733287016856), np.float64(84.0321899674301)]</t>
+  </si>
+  <si>
+    <t>[np.float64(416.45561922189034), np.float64(565.9143500640082)]</t>
+  </si>
+  <si>
+    <t>[np.float64(437.5061939278503), np.float64(41.02753325263575)]</t>
+  </si>
+  <si>
+    <t>[np.float64(8.414622356146428), np.float64(558.597373379225)]</t>
+  </si>
+  <si>
+    <t>[np.float64(241.53843304614153), np.float64(404.8801120970463)]</t>
+  </si>
+  <si>
+    <t>[np.float64(609.6792477164349), np.float64(-498.30582350182397)]</t>
+  </si>
+  <si>
+    <t>[np.float64(866.8663556193897), np.float64(518.6718041795245)]</t>
+  </si>
+  <si>
+    <t>[np.float64(176.90960062449435), np.float64(-477.51348655390876)]</t>
+  </si>
+  <si>
+    <t>[np.float64(971.2802432150864), np.float64(-361.11605601525184)]</t>
+  </si>
+  <si>
+    <t>[np.float64(367.6798154928853), np.float64(54.397686191477646)]</t>
+  </si>
+  <si>
+    <t>[np.float64(593.4639360640138), np.float64(343.19699577166875)]</t>
+  </si>
+  <si>
+    <t>[np.float64(185.111562182927), np.float64(401.5986531593471)]</t>
+  </si>
+  <si>
+    <t>[np.float64(369.33590574656273), np.float64(-485.48064281774805)]</t>
+  </si>
+  <si>
+    <t>[np.float64(834.814939673131), np.float64(-126.06962460724543)]</t>
+  </si>
+  <si>
+    <t>[np.float64(628.9875703134472), np.float64(217.2193344170014)]</t>
+  </si>
+  <si>
+    <t>[np.float64(835.9858246859238), np.float64(425.2990088989602)]</t>
+  </si>
+  <si>
+    <t>[np.float64(454.30579676489333), np.float64(258.9705069374975)]</t>
+  </si>
+  <si>
+    <t>[np.float64(224.5525557880398), np.float64(241.51690643043196)]</t>
+  </si>
+  <si>
+    <t>[np.float64(931.4820739926421), np.float64(-209.29522205758985)]</t>
+  </si>
+  <si>
+    <t>[np.float64(507.4268451954793), np.float64(349.41297575539454)]</t>
+  </si>
+  <si>
+    <t>[np.float64(495.7208497055718), np.float64(462.605842129183)]</t>
+  </si>
+  <si>
+    <t>[np.float64(368.8810851440106), np.float64(527.3670004111741)]</t>
+  </si>
+  <si>
+    <t>[np.float64(549.8550822332736), np.float64(-206.46321341088304)]</t>
+  </si>
+  <si>
+    <t>[np.float64(656.0655695386904), np.float64(477.1209546335897)]</t>
+  </si>
+  <si>
+    <t>[np.float64(795.4617914245316), np.float64(15.876295462239)]</t>
+  </si>
+  <si>
+    <t>[np.float64(560.0882569146124), np.float64(-461.24262011707197)]</t>
+  </si>
+  <si>
+    <t>[np.float64(367.08563282612306), np.float64(-105.31609437360288)]</t>
+  </si>
+  <si>
+    <t>[np.float64(420.5981986971924), np.float64(164.10061795005424)]</t>
+  </si>
+  <si>
+    <t>[np.float64(96.88166553279243), np.float64(281.54321714383843)]</t>
+  </si>
+  <si>
+    <t>[np.float64(694.55112895971), np.float64(366.6269467791742)]</t>
+  </si>
+  <si>
+    <t>[np.float64(78.84693380801544), np.float64(213.95410688431252)]</t>
+  </si>
+  <si>
+    <t>[np.float64(342.6730646954426), np.float64(-113.48034370754203)]</t>
+  </si>
+  <si>
+    <t>[np.float64(864.0824056304607), np.float64(54.072412564958086)]</t>
+  </si>
+  <si>
+    <t>[np.float64(943.0093555693406), np.float64(157.93182972605098)]</t>
+  </si>
+  <si>
+    <t>[np.float64(68.99991568916298), np.float64(159.86771316978684)]</t>
+  </si>
+  <si>
+    <t>[np.float64(55.68021581296412), np.float64(-476.3672589536286)]</t>
+  </si>
+  <si>
+    <t>[np.float64(414.1935342645553), np.float64(-480.62651646989616)]</t>
+  </si>
+  <si>
+    <t>[np.float64(69.01294670357305), np.float64(42.59544638009845)]</t>
+  </si>
+  <si>
+    <t>[np.float64(517.2422287423005), np.float64(-380.9166332103895)]</t>
+  </si>
+  <si>
+    <t>[np.float64(30.354901491942087), np.float64(162.95165445645864)]</t>
+  </si>
+  <si>
+    <t>[np.float64(202.96322136051592), np.float64(-357.3466088742493)]</t>
+  </si>
+  <si>
+    <t>[np.float64(581.7237004115266), np.float64(234.34946227819034)]</t>
+  </si>
+  <si>
+    <t>[np.float64(413.87716596933575), np.float64(180.43387969256526)]</t>
+  </si>
+  <si>
+    <t>[np.float64(229.1312927171232), np.float64(-360.26874100521525)]</t>
+  </si>
+  <si>
+    <t>[np.float64(799.5790299438767), np.float64(277.81707819894507)]</t>
+  </si>
+  <si>
+    <t>[np.float64(35.31001996053406), np.float64(300.1127571923512)]</t>
+  </si>
+  <si>
+    <t>[np.float64(589.9335440710985), np.float64(-388.02475603923244)]</t>
+  </si>
+  <si>
+    <t>[np.float64(502.28733169337727), np.float64(553.749630677605)]</t>
+  </si>
+  <si>
+    <t>[np.float64(49.6168384359823), np.float64(553.2454462139615)]</t>
+  </si>
+  <si>
+    <t>[np.float64(564.8517662656781), np.float64(178.4648916994521)]</t>
+  </si>
+  <si>
+    <t>[np.float64(843.9354932761628), np.float64(129.02068703099633)]</t>
+  </si>
+  <si>
+    <t>[np.float64(633.2617970634207), np.float64(-312.18709418008166)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.981187770424889), np.float64(230.79886434606965)]</t>
+  </si>
+  <si>
+    <t>[np.float64(465.1577943978301), np.float64(589.7747516807522)]</t>
+  </si>
+  <si>
+    <t>[np.float64(681.4454927861359), np.float64(29.919891194357774)]</t>
+  </si>
+  <si>
+    <t>[np.float64(595.7001461313403), np.float64(-362.10542833243323)]</t>
+  </si>
+  <si>
+    <t>[np.float64(870.9893557383559), np.float64(497.3662400207518)]</t>
+  </si>
+  <si>
+    <t>[np.float64(406.21410136556125), np.float64(362.8180562760126)]</t>
+  </si>
+  <si>
+    <t>[np.float64(76.14063244987335), np.float64(219.57038322517155)]</t>
+  </si>
+  <si>
+    <t>[np.float64(734.5494619375314), np.float64(211.76812155071332)]</t>
+  </si>
+  <si>
+    <t>[np.float64(181.9712350753876), np.float64(-510.761497188962)]</t>
+  </si>
+  <si>
+    <t>[np.float64(21.180620629885794), np.float64(106.51734005855144)]</t>
+  </si>
+  <si>
+    <t>[np.float64(204.34928669217712), np.float64(224.33601693668152)]</t>
+  </si>
+  <si>
+    <t>[np.float64(116.6443093154359), np.float64(187.26204864035515)]</t>
+  </si>
+  <si>
+    <t>[np.float64(866.0265445001355), np.float64(-494.7293753823064)]</t>
+  </si>
+  <si>
+    <t>[np.float64(860.4537808117702), np.float64(-246.4022746163336)]</t>
+  </si>
+  <si>
+    <t>[np.float64(934.7525224938466), np.float64(-201.27312133282743)]</t>
+  </si>
+  <si>
+    <t>[np.float64(183.59534768784468), np.float64(-486.3172622974376)]</t>
+  </si>
+  <si>
+    <t>[np.float64(718.8367600366686), np.float64(-235.15160760656187)]</t>
+  </si>
+  <si>
+    <t>[np.float64(686.8457385283558), np.float64(-134.75761092566995)]</t>
+  </si>
+  <si>
+    <t>[np.float64(277.66119386126655), np.float64(560.80696587947)]</t>
+  </si>
+  <si>
+    <t>[np.float64(233.34758207762707), np.float64(-212.81094966025103)]</t>
+  </si>
+  <si>
+    <t>[np.float64(591.1865784685683), np.float64(350.5433753816558)]</t>
+  </si>
+  <si>
+    <t>[np.float64(400.7712974948171), np.float64(-363.45803614322955)]</t>
+  </si>
+  <si>
+    <t>[np.float64(334.70371179421323), np.float64(-325.79785504732115)]</t>
+  </si>
+  <si>
+    <t>[np.float64(527.5573981513054), np.float64(208.86321791691682)]</t>
+  </si>
+  <si>
+    <t>[np.float64(809.0316826391094), np.float64(566.7785379272643)]</t>
+  </si>
+  <si>
+    <t>[np.float64(979.5145294455426), np.float64(-527.596890031289)]</t>
+  </si>
+  <si>
+    <t>[np.float64(784.3826897132357), np.float64(316.7154477917204)]</t>
+  </si>
+  <si>
+    <t>[np.float64(67.13043086414605), np.float64(-306.1990449261689)]</t>
+  </si>
+  <si>
+    <t>[np.float64(200.9807754022125), np.float64(-589.4980550346683)]</t>
+  </si>
+  <si>
+    <t>[np.float64(45.9477307452203), np.float64(-321.7703870744495)]</t>
+  </si>
+  <si>
+    <t>[np.float64(601.7735939061511), np.float64(43.97582560374451)]</t>
+  </si>
+  <si>
+    <t>[np.float64(506.4115512427154), np.float64(-431.71740576471154)]</t>
+  </si>
+  <si>
+    <t>[np.float64(709.2270633230795), np.float64(378.652422332819)]</t>
+  </si>
+  <si>
+    <t>[np.float64(72.91950992637585), np.float64(348.7404559877107)]</t>
+  </si>
+  <si>
+    <t>[np.float64(499.4331996602548), np.float64(12.780007569934583)]</t>
+  </si>
+  <si>
+    <t>[np.float64(390.50102287600964), np.float64(-255.96153620561995)]</t>
+  </si>
+  <si>
+    <t>[np.float64(124.10584836499905), np.float64(203.68830894144878)]</t>
+  </si>
+  <si>
+    <t>[np.float64(580.1959876507624), np.float64(-76.17500462557575)]</t>
+  </si>
+  <si>
+    <t>[np.float64(397.58272444877565), np.float64(-507.1253336849911)]</t>
+  </si>
+  <si>
+    <t>[np.float64(389.9196988684649), np.float64(471.86857351955064)]</t>
+  </si>
+  <si>
+    <t>[np.float64(244.6389351585162), np.float64(-346.96338455176993)]</t>
+  </si>
+  <si>
+    <t>[np.float64(891.36043391206), np.float64(-206.29537247417113)]</t>
+  </si>
+  <si>
+    <t>[np.float64(434.173403872118), np.float64(350.459123087331)]</t>
+  </si>
+  <si>
+    <t>[np.float64(856.947689800199), np.float64(507.10759801507766)]</t>
+  </si>
+  <si>
+    <t>[np.float64(585.3040369852014), np.float64(79.85839438448215)]</t>
+  </si>
+  <si>
+    <t>[np.float64(654.2070098153233), np.float64(-88.33305604901074)]</t>
+  </si>
+  <si>
+    <t>[np.float64(507.22842642654774), np.float64(-481.9411710794075)]</t>
+  </si>
+  <si>
+    <t>[np.float64(471.3996179696139), np.float64(438.02073986266623)]</t>
+  </si>
+  <si>
+    <t>[np.float64(733.931475906315), np.float64(-238.73524289767641)]</t>
+  </si>
+  <si>
+    <t>[np.float64(121.09422600009967), np.float64(289.11692026700257)]</t>
+  </si>
+  <si>
+    <t>[np.float64(200.88506398777983), np.float64(-212.83112102960524)]</t>
+  </si>
+  <si>
+    <t>[np.float64(807.2714826959648), np.float64(-406.64612130740784)]</t>
+  </si>
+  <si>
+    <t>[np.float64(151.95328410427567), np.float64(152.0278261820996)]</t>
+  </si>
+  <si>
+    <t>[np.float64(121.8458726699434), np.float64(-289.39651022146154)]</t>
+  </si>
+  <si>
+    <t>[np.float64(496.4336382366982), np.float64(8.30075688846614)]</t>
+  </si>
+  <si>
+    <t>[np.float64(141.5966127703372), np.float64(-308.51320893365005)]</t>
+  </si>
+  <si>
+    <t>[np.float64(995.4150630229874), np.float64(4.385400924730334)]</t>
+  </si>
+  <si>
+    <t>[np.float64(907.0832893101935), np.float64(596.6269851265092)]</t>
+  </si>
+  <si>
+    <t>[np.float64(763.6536880147103), np.float64(380.82922255528536)]</t>
+  </si>
+  <si>
+    <t>[np.float64(637.5339192857509), np.float64(-474.3171212586934)]</t>
+  </si>
+  <si>
+    <t>[np.float64(84.93492462682295), np.float64(-187.37592020850246)]</t>
+  </si>
+  <si>
+    <t>[np.float64(328.03664678717206), np.float64(-228.5147751809763)]</t>
+  </si>
+  <si>
+    <t>[np.float64(597.9031224237042), np.float64(324.7834914633206)]</t>
+  </si>
+  <si>
+    <t>[np.float64(59.80851212252147), np.float64(369.2912013264016)]</t>
+  </si>
+  <si>
+    <t>[np.float64(835.0224219388359), np.float64(-67.4951557594062)]</t>
+  </si>
+  <si>
+    <t>[np.float64(990.7445502709977), np.float64(168.98365403011962)]</t>
+  </si>
+  <si>
+    <t>[np.float64(146.2587328917041), np.float64(325.82867878619584)]</t>
+  </si>
+  <si>
+    <t>[np.float64(362.5775837706512), np.float64(64.42261354609082)]</t>
+  </si>
+  <si>
+    <t>[np.float64(522.0450863419958), np.float64(86.60228249364866)]</t>
+  </si>
+  <si>
+    <t>[np.float64(555.4690420264326), np.float64(105.06025047540254)]</t>
+  </si>
+  <si>
+    <t>[np.float64(457.99392735636457), np.float64(158.600515158211)]</t>
+  </si>
+  <si>
+    <t>[np.float64(981.0052983520675), np.float64(66.65726759931636)]</t>
+  </si>
+  <si>
+    <t>[np.float64(976.8467513476282), np.float64(-264.02011897250793)]</t>
+  </si>
+  <si>
+    <t>[np.float64(810.3213028683132), np.float64(-366.4000961950859)]</t>
+  </si>
+  <si>
+    <t>[np.float64(633.4395376442702), np.float64(269.0321139932711)]</t>
+  </si>
+  <si>
+    <t>[np.float64(69.21319807377147), np.float64(-374.67925411508753)]</t>
+  </si>
+  <si>
+    <t>[np.float64(646.0737667476733), np.float64(-543.9124867074959)]</t>
+  </si>
+  <si>
+    <t>[np.float64(980.580609139414), np.float64(-342.22022234413737)]</t>
+  </si>
+  <si>
+    <t>[np.float64(217.29201151974152), np.float64(231.85507577946635)]</t>
+  </si>
+  <si>
+    <t>[np.float64(858.0911812742595), np.float64(264.50585591495553)]</t>
+  </si>
+  <si>
+    <t>[np.float64(777.1779748249476), np.float64(-170.7709407813262)]</t>
+  </si>
+  <si>
+    <t>[np.float64(466.3919536782829), np.float64(-227.73843703307261)]</t>
+  </si>
+  <si>
+    <t>[np.float64(419.31204790628675), np.float64(169.4088895262654)]</t>
+  </si>
+  <si>
+    <t>[np.float64(742.9377858043019), np.float64(-545.3808121884751)]</t>
+  </si>
+  <si>
+    <t>[np.float64(716.5237908477357), np.float64(-343.4567395432577)]</t>
+  </si>
+  <si>
+    <t>[np.float64(779.4289143664565), np.float64(-589.5385810426767)]</t>
+  </si>
+  <si>
+    <t>[np.float64(41.466069894546045), np.float64(-140.04786911419484)]</t>
+  </si>
+  <si>
+    <t>[np.float64(15.210421816310937), np.float64(98.86334614395139)]</t>
+  </si>
+  <si>
+    <t>[np.float64(492.0943714238428), np.float64(-457.6979837094144)]</t>
+  </si>
+  <si>
+    <t>[np.float64(317.4597126991805), np.float64(167.34077924622977)]</t>
+  </si>
+  <si>
+    <t>[np.float64(182.86892547550627), np.float64(-118.16507377753283)]</t>
+  </si>
+  <si>
+    <t>[np.float64(481.038463570171), np.float64(-66.95460236887368)]</t>
+  </si>
+  <si>
+    <t>[np.float64(386.15964209963784), np.float64(-531.7288075816158)]</t>
+  </si>
+  <si>
+    <t>[np.float64(557.0652982419105), np.float64(47.339574002598056)]</t>
+  </si>
+  <si>
+    <t>[np.float64(977.5804354001614), np.float64(-142.68885572662242)]</t>
+  </si>
+  <si>
+    <t>[np.float64(744.6037892591884), np.float64(573.6719054799487)]</t>
+  </si>
+  <si>
+    <t>[np.float64(856.3406388638708), np.float64(105.40466181370971)]</t>
+  </si>
+  <si>
+    <t>[np.float64(822.1495252669099), np.float64(419.35819452207386)]</t>
+  </si>
+  <si>
+    <t>[np.float64(913.8583616033329), np.float64(335.5441886249289)]</t>
+  </si>
+  <si>
+    <t>[np.float64(571.050208867908), np.float64(-426.85170493542586)]</t>
+  </si>
+  <si>
+    <t>[np.float64(46.93639730422139), np.float64(-511.7116986308042)]</t>
+  </si>
+  <si>
+    <t>[np.float64(117.53736444629604), np.float64(-432.71746263660714)]</t>
+  </si>
+  <si>
+    <t>[np.float64(84.85790042469165), np.float64(-197.09221386763397)]</t>
+  </si>
+  <si>
+    <t>[np.float64(917.2002870492647), np.float64(488.08072316771745)]</t>
+  </si>
+  <si>
+    <t>[np.float64(649.6992777723827), np.float64(-358.10986876000186)]</t>
+  </si>
+  <si>
+    <t>[np.float64(716.3527253026289), np.float64(-473.5548044615609)]</t>
+  </si>
+  <si>
+    <t>[np.float64(557.936808115316), np.float64(507.87289538173604)]</t>
+  </si>
+  <si>
+    <t>[np.float64(613.984509314424), np.float64(43.39728308519466)]</t>
+  </si>
+  <si>
+    <t>[np.float64(214.1805409815588), np.float64(-448.31823188155107)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.759638121272003), np.float64(-511.40432565081386)]</t>
+  </si>
+  <si>
+    <t>[np.float64(24.093336435723643), np.float64(-539.4793103932062)]</t>
+  </si>
+  <si>
+    <t>[np.float64(493.28364523493775), np.float64(55.37348891096326)]</t>
+  </si>
+  <si>
+    <t>[np.float64(893.6635578680725), np.float64(-439.8951802780548)]</t>
+  </si>
+  <si>
+    <t>[np.float64(219.36585190826742), np.float64(294.85464174317235)]</t>
+  </si>
+  <si>
+    <t>[np.float64(130.99437694194137), np.float64(298.6346193303415)]</t>
+  </si>
+  <si>
+    <t>[np.float64(788.2863356741608), np.float64(-426.3159296870727)]</t>
+  </si>
+  <si>
+    <t>[np.float64(58.75451575036949), np.float64(445.2438534200546)]</t>
+  </si>
+  <si>
+    <t>[np.float64(346.16392696819844), np.float64(267.3611633569968)]</t>
+  </si>
+  <si>
+    <t>[np.float64(433.98104609916743), np.float64(356.7910691291595)]</t>
+  </si>
+  <si>
+    <t>[np.float64(866.617474293325), np.float64(511.8347679656199)]</t>
+  </si>
+  <si>
+    <t>[np.float64(716.9046220085736), np.float64(269.9057128210088)]</t>
+  </si>
+  <si>
+    <t>[np.float64(320.0091869656837), np.float64(354.3586338344569)]</t>
+  </si>
+  <si>
+    <t>[np.float64(430.66504314775455), np.float64(311.2388667886529)]</t>
+  </si>
+  <si>
+    <t>[np.float64(254.0343633703903), np.float64(303.78558280260995)]</t>
+  </si>
+  <si>
+    <t>[np.float64(78.56135757957594), np.float64(144.13275558650184)]</t>
+  </si>
+  <si>
+    <t>[np.float64(950.3682760144609), np.float64(-166.42801715671084)]</t>
+  </si>
+  <si>
+    <t>[np.float64(378.4109273666154), np.float64(183.05540962622763)]</t>
+  </si>
+  <si>
+    <t>[np.float64(957.1505180847495), np.float64(572.3449942231571)]</t>
+  </si>
+  <si>
+    <t>[np.float64(981.0220606403262), np.float64(57.61283800296337)]</t>
+  </si>
+  <si>
+    <t>[np.float64(297.99946069199245), np.float64(-343.4170250281509)]</t>
+  </si>
+  <si>
+    <t>[np.float64(47.68805598328241), np.float64(-313.0686133069837)]</t>
+  </si>
+  <si>
+    <t>[np.float64(60.78272830703047), np.float64(532.6898764760708)]</t>
+  </si>
+  <si>
+    <t>[np.float64(495.15956680546714), np.float64(-52.263311224070776)]</t>
+  </si>
+  <si>
+    <t>[np.float64(559.4921491772486), np.float64(-568.789753430986)]</t>
+  </si>
+  <si>
+    <t>[np.float64(442.1446299043261), np.float64(583.5144829339613)]</t>
+  </si>
+  <si>
+    <t>[np.float64(738.5073264714154), np.float64(21.99680810410348)]</t>
+  </si>
+  <si>
+    <t>[np.float64(583.4168723362135), np.float64(147.25303785109747)]</t>
+  </si>
+  <si>
+    <t>[np.float64(607.2495815798824), np.float64(187.08931479054854)]</t>
+  </si>
+  <si>
+    <t>[np.float64(823.4393323091634), np.float64(-421.33513937134103)]</t>
+  </si>
+  <si>
+    <t>[np.float64(537.6718162981259), np.float64(-440.3280505520306)]</t>
+  </si>
+  <si>
+    <t>[np.float64(350.26137965730817), np.float64(-196.6179258282637)]</t>
+  </si>
+  <si>
+    <t>[np.float64(612.8486446751932), np.float64(567.554424862087)]</t>
+  </si>
+  <si>
+    <t>[np.float64(513.6265794984878), np.float64(406.8377206007317)]</t>
+  </si>
+  <si>
+    <t>[np.float64(40.248404693390086), np.float64(201.62177559044903)]</t>
+  </si>
+  <si>
+    <t>[np.float64(132.25883091969925), np.float64(242.7313140718246)]</t>
+  </si>
+  <si>
+    <t>[np.float64(63.810373613860214), np.float64(-165.8796487252523)]</t>
+  </si>
+  <si>
+    <t>[np.float64(309.91977374744215), np.float64(76.27782072150819)]</t>
+  </si>
+  <si>
+    <t>[np.float64(863.7710971857762), np.float64(114.20671420928568)]</t>
+  </si>
+  <si>
+    <t>[np.float64(168.1262389706626), np.float64(59.920698053985916)]</t>
+  </si>
+  <si>
+    <t>[np.float64(525.1179298493082), np.float64(473.34495778055157)]</t>
+  </si>
+  <si>
+    <t>[np.float64(611.474122461386), np.float64(-296.04279885115926)]</t>
+  </si>
+  <si>
+    <t>[np.float64(807.5322072746287), np.float64(-502.6112308790086)]</t>
+  </si>
+  <si>
+    <t>[np.float64(334.70116157973405), np.float64(343.8712882126714)]</t>
+  </si>
+  <si>
+    <t>[np.float64(915.6949105857718), np.float64(-181.5983386372518)]</t>
+  </si>
+  <si>
+    <t>[np.float64(697.7297899747772), np.float64(479.0079795725651)]</t>
+  </si>
+  <si>
+    <t>[np.float64(936.4549978610563), np.float64(77.62878269781811)]</t>
+  </si>
+  <si>
+    <t>[np.float64(336.82031836300763), np.float64(194.61776745863585)]</t>
+  </si>
+  <si>
+    <t>[np.float64(773.2938173259321), np.float64(33.58510555489738)]</t>
+  </si>
+  <si>
+    <t>[np.float64(390.73951551409914), np.float64(-162.80962967749053)]</t>
+  </si>
+  <si>
+    <t>[np.float64(253.53240818520538), np.float64(352.53506564038037)]</t>
+  </si>
+  <si>
+    <t>[np.float64(263.11782360807155), np.float64(-525.8036958340481)]</t>
+  </si>
+  <si>
+    <t>[np.float64(828.8240279235683), np.float64(-362.3249758944347)]</t>
+  </si>
+  <si>
+    <t>[np.float64(840.3451812577624), np.float64(8.326652666975178)]</t>
+  </si>
+  <si>
+    <t>[np.float64(387.6406340842169), np.float64(396.81733740529955)]</t>
+  </si>
+  <si>
+    <t>[np.float64(508.6693236452333), np.float64(273.7859904158852)]</t>
+  </si>
+  <si>
+    <t>[np.float64(633.7743632647195), np.float64(-268.76490118896027)]</t>
+  </si>
+  <si>
+    <t>[np.float64(431.3805578477087), np.float64(-54.309849500032556)]</t>
+  </si>
+  <si>
+    <t>[np.float64(897.3547086529918), np.float64(-401.66350023090297)]</t>
+  </si>
+  <si>
+    <t>[np.float64(964.1367260283744), np.float64(-186.57050767656682)]</t>
+  </si>
+  <si>
+    <t>[np.float64(295.3317592111401), np.float64(99.69315254997423)]</t>
+  </si>
+  <si>
+    <t>[np.float64(538.644476741743), np.float64(-407.1750895790374)]</t>
+  </si>
+  <si>
+    <t>[np.float64(745.7627733783443), np.float64(-385.48710583360787)]</t>
+  </si>
+  <si>
+    <t>[np.float64(749.6329709141263), np.float64(-193.48791536120393)]</t>
+  </si>
+  <si>
+    <t>[np.float64(737.0240194042037), np.float64(583.1345503588893)]</t>
+  </si>
+  <si>
+    <t>[np.float64(378.67260654553024), np.float64(-87.61401437173026)]</t>
+  </si>
+  <si>
+    <t>[np.float64(862.7825914808706), np.float64(247.79481920346961)]</t>
+  </si>
+  <si>
+    <t>[np.float64(574.749513835702), np.float64(-384.24921327909385)]</t>
+  </si>
+  <si>
+    <t>[np.float64(867.2969339287042), np.float64(-250.503976326501)]</t>
+  </si>
+  <si>
+    <t>[np.float64(633.6214606586684), np.float64(472.209491327259)]</t>
+  </si>
+  <si>
+    <t>[np.float64(252.42772379105816), np.float64(-431.28059656937467)]</t>
+  </si>
+  <si>
+    <t>[np.float64(929.5609358382758), np.float64(-72.10088552131288)]</t>
+  </si>
+  <si>
+    <t>[np.float64(843.4130774939538), np.float64(-581.6678559943642)]</t>
+  </si>
+  <si>
+    <t>[np.float64(766.3040702919949), np.float64(-553.5481427516987)]</t>
+  </si>
+  <si>
+    <t>[np.float64(965.1686856136821), np.float64(324.59671252171484)]</t>
+  </si>
+  <si>
+    <t>[np.float64(363.61172816700014), np.float64(299.8546213025743)]</t>
+  </si>
+  <si>
+    <t>[np.float64(928.0718335912943), np.float64(-395.52595165985247)]</t>
+  </si>
+  <si>
+    <t>[np.float64(754.7567964783997), np.float64(-83.02643501984289)]</t>
+  </si>
+  <si>
+    <t>[np.float64(571.8283964057758), np.float64(-452.55634197110646)]</t>
+  </si>
+  <si>
+    <t>[np.float64(530.8113512641937), np.float64(-390.9073348092618)]</t>
+  </si>
+  <si>
+    <t>[np.float64(138.57336125678677), np.float64(312.38706034503184)]</t>
+  </si>
+  <si>
+    <t>[np.float64(479.15288351545405), np.float64(-194.59098357608798)]</t>
+  </si>
+  <si>
+    <t>[np.float64(293.14153166857113), np.float64(70.42900733809711)]</t>
+  </si>
+  <si>
+    <t>[np.float64(397.17268335995357), np.float64(-43.93438002750645)]</t>
+  </si>
+  <si>
+    <t>[np.float64(580.8662969103565), np.float64(-152.587409204155)]</t>
+  </si>
+  <si>
+    <t>[np.float64(122.8970235190624), np.float64(136.1761934838553)]</t>
+  </si>
+  <si>
+    <t>[np.float64(768.8796919778038), np.float64(-571.4213855628859)]</t>
+  </si>
+  <si>
+    <t>[np.float64(282.6025480633764), np.float64(499.230066878318)]</t>
+  </si>
+  <si>
+    <t>[np.float64(30.12884121376136), np.float64(-455.0332895635156)]</t>
+  </si>
+  <si>
+    <t>[np.float64(28.483058661174066), np.float64(178.4741194350063)]</t>
+  </si>
+  <si>
+    <t>[np.float64(177.86389184480544), np.float64(224.96620721298677)]</t>
+  </si>
+  <si>
+    <t>[np.float64(910.8000886488223), np.float64(488.1076022950647)]</t>
+  </si>
+  <si>
+    <t>[np.float64(936.9649621684769), np.float64(-485.1713286019433)]</t>
+  </si>
+  <si>
+    <t>[np.float64(57.632675077133435), np.float64(49.6103333404119)]</t>
+  </si>
+  <si>
+    <t>[np.float64(584.8722772356675), np.float64(356.76262745938084)]</t>
+  </si>
+  <si>
+    <t>[np.float64(648.9001692139309), np.float64(-382.1024040405243)]</t>
+  </si>
+  <si>
+    <t>[np.float64(996.654880515963), np.float64(131.94297375950225)]</t>
+  </si>
+  <si>
+    <t>[np.float64(82.04680274785248), np.float64(-333.7559129659588)]</t>
+  </si>
+  <si>
+    <t>[np.float64(39.40966536003187), np.float64(-485.1795412092879)]</t>
+  </si>
+  <si>
+    <t>[np.float64(845.092462574819), np.float64(-437.01832658567923)]</t>
+  </si>
+  <si>
+    <t>[np.float64(696.686545182387), np.float64(-400.6769283294599)]</t>
+  </si>
+  <si>
+    <t>[np.float64(785.6816595561789), np.float64(-169.43383442081267)]</t>
+  </si>
+  <si>
+    <t>[np.float64(747.0161966735294), np.float64(469.2714074978287)]</t>
+  </si>
+  <si>
+    <t>[np.float64(42.353394435224786), np.float64(192.7445665523161)]</t>
+  </si>
+  <si>
+    <t>[np.float64(247.46100742384337), np.float64(519.4611752621156)]</t>
+  </si>
+  <si>
+    <t>[np.float64(491.09679706762245), np.float64(244.39471256823242)]</t>
+  </si>
+  <si>
+    <t>[np.float64(968.9071796511311), np.float64(255.0991090585146)]</t>
+  </si>
+  <si>
+    <t>[np.float64(424.48407807534625), np.float64(-439.7853395769524)]</t>
+  </si>
+  <si>
+    <t>[np.float64(205.15977326557123), np.float64(281.7596723417415)]</t>
+  </si>
+  <si>
+    <t>[np.float64(925.380046451214), np.float64(185.7212946042648)]</t>
+  </si>
+  <si>
+    <t>[np.float64(478.3322540381986), np.float64(232.0134618209587)]</t>
+  </si>
+  <si>
+    <t>[np.float64(263.5225026742144), np.float64(-264.6414518773276)]</t>
+  </si>
+  <si>
+    <t>[np.float64(626.7575127906117), np.float64(0.7456000995317709)]</t>
+  </si>
+  <si>
+    <t>[np.float64(894.941821338751), np.float64(513.5982868235033)]</t>
+  </si>
+  <si>
+    <t>[np.float64(917.5405085203355), np.float64(386.3258900994207)]</t>
+  </si>
+  <si>
+    <t>[np.float64(874.73102873986), np.float64(-260.3854325160427)]</t>
+  </si>
+  <si>
+    <t>[np.float64(8.261405235476914), np.float64(592.2112328391165)]</t>
+  </si>
+  <si>
+    <t>[np.float64(936.657201229372), np.float64(-172.66968757162027)]</t>
+  </si>
+  <si>
+    <t>[np.float64(249.57034597446048), np.float64(64.01975129751588)]</t>
+  </si>
+  <si>
+    <t>[np.float64(719.9575898347119), np.float64(174.0850119403791)]</t>
+  </si>
+  <si>
+    <t>[np.float64(279.2421521779981), np.float64(-394.52582548617147)]</t>
+  </si>
+  <si>
+    <t>[np.float64(547.0021897621975), np.float64(120.71093973818472)]</t>
+  </si>
+  <si>
+    <t>[np.float64(322.05491008485376), np.float64(-175.08236076843014)]</t>
+  </si>
+  <si>
+    <t>[np.float64(569.2750539466535), np.float64(228.77763623069427)]</t>
+  </si>
+  <si>
+    <t>[np.float64(315.92729021975964), np.float64(493.0006093441591)]</t>
+  </si>
+  <si>
+    <t>[np.float64(84.59376408095554), np.float64(-498.7284923774515)]</t>
+  </si>
+  <si>
+    <t>[np.float64(849.2259360134276), np.float64(324.7334741027664)]</t>
+  </si>
+  <si>
+    <t>[np.float64(572.7501639033884), np.float64(331.65451807154056)]</t>
+  </si>
+  <si>
+    <t>[np.float64(981.8319895027951), np.float64(453.93086818187476)]</t>
+  </si>
+  <si>
+    <t>[np.float64(234.45748127441578), np.float64(-338.04561485411506)]</t>
+  </si>
+  <si>
+    <t>[np.float64(816.1441951472435), np.float64(-332.0367855069687)]</t>
+  </si>
+  <si>
+    <t>[np.float64(712.775480006518), np.float64(-391.2164160885041)]</t>
+  </si>
+  <si>
+    <t>[np.float64(45.374361154842724), np.float64(-431.614996269878)]</t>
+  </si>
+  <si>
+    <t>[np.float64(331.0246895324416), np.float64(582.9532779844149)]</t>
+  </si>
+  <si>
+    <t>[np.float64(379.00088456006256), np.float64(-298.37424381050005)]</t>
+  </si>
+  <si>
+    <t>[np.float64(681.0210947336344), np.float64(512.4622095147572)]</t>
+  </si>
+  <si>
+    <t>[np.float64(196.75631474455923), np.float64(483.89657514646206)]</t>
+  </si>
+  <si>
+    <t>[np.float64(502.1412071501893), np.float64(-215.00191347298517)]</t>
+  </si>
+  <si>
+    <t>[np.float64(124.9131590731245), np.float64(41.98928815000488)]</t>
+  </si>
+  <si>
+    <t>[np.float64(142.47964216073981), np.float64(121.0725778820422)]</t>
+  </si>
+  <si>
+    <t>[np.float64(44.48649900226931), np.float64(-126.94785184380356)]</t>
+  </si>
+  <si>
+    <t>[np.float64(30.35585888553516), np.float64(242.75809825037425)]</t>
+  </si>
+  <si>
+    <t>[np.float64(496.87884496660774), np.float64(338.6773271981068)]</t>
+  </si>
+  <si>
+    <t>[np.float64(518.661673546288), np.float64(570.6123896907504)]</t>
+  </si>
+  <si>
+    <t>[np.float64(484.80493470111674), np.float64(-148.13668668212227)]</t>
+  </si>
+  <si>
+    <t>[np.float64(842.0109953731011), np.float64(-227.58699098250713)]</t>
+  </si>
+  <si>
+    <t>[np.float64(43.70235957607016), np.float64(-416.68663275962507)]</t>
+  </si>
+  <si>
+    <t>[np.float64(294.12577926924854), np.float64(396.4549665066414)]</t>
+  </si>
+  <si>
+    <t>[np.float64(627.4810777843854), np.float64(-66.40624602711443)]</t>
+  </si>
+  <si>
+    <t>[np.float64(264.6690144211168), np.float64(328.6026827976474)]</t>
+  </si>
+  <si>
+    <t>[np.float64(677.8349651374821), np.float64(548.876089667805)]</t>
+  </si>
+  <si>
+    <t>[np.float64(975.5985365881643), np.float64(468.0962372063202)]</t>
+  </si>
+  <si>
+    <t>[np.float64(799.9000326162455), np.float64(-217.23746711491026)]</t>
+  </si>
+  <si>
+    <t>[np.float64(910.856209142404), np.float64(165.61963466913835)]</t>
+  </si>
+  <si>
+    <t>[np.float64(532.7534679764804), np.float64(-414.493882683066)]</t>
+  </si>
+  <si>
+    <t>[np.float64(33.89268926793398), np.float64(-108.3143402881164)]</t>
+  </si>
+  <si>
+    <t>[np.float64(420.7551086734434), np.float64(-531.829409037883)]</t>
+  </si>
+  <si>
+    <t>[np.float64(319.10235432790034), np.float64(317.4395096137911)]</t>
+  </si>
+  <si>
+    <t>[np.float64(502.4126883429103), np.float64(236.69745909268158)]</t>
+  </si>
+  <si>
+    <t>[np.float64(14.317636454983074), np.float64(-379.0041009228971)]</t>
+  </si>
+  <si>
+    <t>[np.float64(899.1662659581934), np.float64(-361.92591077908935)]</t>
+  </si>
+  <si>
+    <t>[np.float64(300.1450063417047), np.float64(-358.65869203513165)]</t>
+  </si>
+  <si>
+    <t>[np.float64(351.7984113187201), np.float64(-361.2564610456514)]</t>
+  </si>
+  <si>
+    <t>[np.float64(947.3472455571233), np.float64(397.0844702525627)]</t>
+  </si>
+  <si>
+    <t>[np.float64(539.0887632262545), np.float64(-424.7746323156251)]</t>
+  </si>
+  <si>
+    <t>[np.float64(717.4326691412145), np.float64(398.305953389253)]</t>
+  </si>
+  <si>
+    <t>[np.float64(853.4068122931574), np.float64(240.09142145928206)]</t>
+  </si>
+  <si>
+    <t>[np.float64(654.7500803060423), np.float64(521.3380920306663)]</t>
+  </si>
+  <si>
+    <t>[np.float64(867.6390052236992), np.float64(578.0598444035088)]</t>
+  </si>
+  <si>
+    <t>[np.float64(226.36835354392792), np.float64(-279.5652396045297)]</t>
+  </si>
+  <si>
+    <t>[np.float64(966.8390865110497), np.float64(-465.18202877898995)]</t>
+  </si>
+  <si>
+    <t>[np.float64(572.7364030730431), np.float64(418.9190654319865)]</t>
+  </si>
+  <si>
+    <t>[np.float64(982.6513857769495), np.float64(-110.09647318746516)]</t>
+  </si>
+  <si>
+    <t>[np.float64(623.1458836702649), np.float64(447.86946826122085)]</t>
+  </si>
+  <si>
+    <t>[np.float64(178.48184017250733), np.float64(356.16449377912)]</t>
+  </si>
+  <si>
+    <t>[np.float64(320.83157398210284), np.float64(463.876577301261)]</t>
+  </si>
+  <si>
+    <t>[np.float64(998.8738438767477), np.float64(-274.5875538252716)]</t>
+  </si>
+  <si>
+    <t>[np.float64(982.7063982039671), np.float64(161.91031249074365)]</t>
+  </si>
+  <si>
+    <t>[np.float64(40.93790009392628), np.float64(-135.19413763191397)]</t>
+  </si>
+  <si>
+    <t>[np.float64(790.9894852042146), np.float64(543.4555750245302)]</t>
+  </si>
+  <si>
+    <t>[np.float64(804.6805868156841), np.float64(-512.629880828662)]</t>
+  </si>
+  <si>
+    <t>[np.float64(337.5829854283073), np.float64(-441.8827812747958)]</t>
+  </si>
+  <si>
+    <t>[np.float64(450.1989150395298), np.float64(-509.1109079194064)]</t>
+  </si>
+  <si>
+    <t>[np.float64(576.9947062956725), np.float64(-149.12733765941925)]</t>
+  </si>
+  <si>
+    <t>[np.float64(462.25302732268744), np.float64(-191.830001607658)]</t>
+  </si>
+  <si>
+    <t>[np.float64(34.35096471696486), np.float64(-393.00152802183345)]</t>
+  </si>
+  <si>
+    <t>[np.float64(90.60614348329798), np.float64(-502.69379842563706)]</t>
+  </si>
+  <si>
+    <t>[np.float64(688.8839944531295), np.float64(-483.59243996025754)]</t>
+  </si>
+  <si>
+    <t>[np.float64(562.9324625583513), np.float64(-326.47979646863786)]</t>
+  </si>
+  <si>
+    <t>[np.float64(512.3455605242918), np.float64(-483.14806572320754)]</t>
+  </si>
+  <si>
+    <t>[np.float64(498.0008205780082), np.float64(-535.3263526742666)]</t>
+  </si>
+  <si>
+    <t>[np.float64(307.60270252682886), np.float64(-213.47400414434452)]</t>
+  </si>
+  <si>
+    <t>[np.float64(907.074230771901), np.float64(-449.54266179624506)]</t>
+  </si>
+  <si>
+    <t>[np.float64(410.6544569736488), np.float64(254.07740844292812)]</t>
+  </si>
+  <si>
+    <t>[np.float64(920.1933294685118), np.float64(160.11050447858997)]</t>
+  </si>
+  <si>
+    <t>[np.float64(800.4344181987896), np.float64(537.4562091493813)]</t>
+  </si>
+  <si>
+    <t>[np.float64(477.0538814567465), np.float64(248.50428909870425)]</t>
+  </si>
+  <si>
+    <t>[np.float64(203.2416204839721), np.float64(117.0565701742762)]</t>
+  </si>
+  <si>
+    <t>[np.float64(151.0994879071721), np.float64(559.331397704691)]</t>
+  </si>
+  <si>
+    <t>[np.float64(989.0897255259052), np.float64(-297.74383638887804)]</t>
+  </si>
+  <si>
+    <t>[np.float64(326.45888012681223), np.float64(182.05449820425122)]</t>
+  </si>
+  <si>
+    <t>[np.float64(306.50717252878104), np.float64(-204.3855323504094)]</t>
+  </si>
+  <si>
+    <t>[np.float64(304.53044799882576), np.float64(-559.7173622210483)]</t>
+  </si>
+  <si>
+    <t>[np.float64(146.71687798331666), np.float64(457.05148241089023)]</t>
+  </si>
+  <si>
+    <t>[np.float64(951.1558695714625), np.float64(-483.79088681753217)]</t>
+  </si>
+  <si>
+    <t>[np.float64(962.6984231821966), np.float64(-204.90386731168894)]</t>
+  </si>
+  <si>
+    <t>[np.float64(404.97581695225347), np.float64(-385.8958611745604)]</t>
+  </si>
+  <si>
+    <t>[np.float64(200.1937759699527), np.float64(-563.1828283186105)]</t>
+  </si>
+  <si>
+    <t>[np.float64(104.74358524682181), np.float64(421.0448678122805)]</t>
+  </si>
+  <si>
+    <t>[np.float64(322.86637337275715), np.float64(272.06030343518273)]</t>
+  </si>
+  <si>
+    <t>[np.float64(659.8914491430279), np.float64(431.2571600939157)]</t>
+  </si>
+  <si>
+    <t>[np.float64(899.2370218914411), np.float64(332.9737364412565)]</t>
+  </si>
+  <si>
+    <t>[np.float64(603.0167817968608), np.float64(134.74966952863383)]</t>
+  </si>
+  <si>
+    <t>[np.float64(611.5113026257252), np.float64(-368.73730711646203)]</t>
+  </si>
+  <si>
+    <t>[np.float64(196.85314938636444), np.float64(22.069375707727318)]</t>
+  </si>
+  <si>
+    <t>[np.float64(239.91232443110744), np.float64(531.3658604200523)]</t>
+  </si>
+  <si>
+    <t>[np.float64(933.4568350031417), np.float64(290.02493167915566)]</t>
+  </si>
+  <si>
+    <t>[np.float64(936.5889663143829), np.float64(-85.04334852412319)]</t>
+  </si>
+  <si>
+    <t>[np.float64(741.376530076691), np.float64(-410.2417844629391)]</t>
+  </si>
+  <si>
+    <t>[np.float64(644.8538121965473), np.float64(-480.15992869187727)]</t>
+  </si>
+  <si>
+    <t>[np.float64(351.8838625694692), np.float64(-230.68060318358124)]</t>
+  </si>
+  <si>
+    <t>[np.float64(963.8264509231278), np.float64(-526.66273969601)]</t>
+  </si>
+  <si>
+    <t>[np.float64(586.9094950362603), np.float64(79.12218515628547)]</t>
+  </si>
+  <si>
+    <t>[np.float64(722.5856104954469), np.float64(-476.82950944699274)]</t>
+  </si>
+  <si>
+    <t>[np.float64(826.6451124434649), np.float64(-76.43592732502168)]</t>
+  </si>
+  <si>
+    <t>[np.float64(402.5880418331811), np.float64(56.616709150736824)]</t>
+  </si>
+  <si>
+    <t>[np.float64(709.780265401891), np.float64(451.9793719484944)]</t>
+  </si>
+  <si>
+    <t>[np.float64(613.8266656651001), np.float64(-597.8536666912954)]</t>
+  </si>
+  <si>
+    <t>[np.float64(478.23391392430494), np.float64(-241.97406369480404)]</t>
+  </si>
+  <si>
+    <t>[np.float64(488.73426196745794), np.float64(-503.46453212204324)]</t>
+  </si>
+  <si>
+    <t>[np.float64(201.08961312173912), np.float64(175.3313396709882)]</t>
+  </si>
+  <si>
+    <t>[np.float64(716.2453495559314), np.float64(87.97465746565422)]</t>
+  </si>
+  <si>
+    <t>[np.float64(658.0967066602991), np.float64(-129.02198648363282)]</t>
+  </si>
+  <si>
+    <t>[np.float64(166.04324642230438), np.float64(-326.00747939683475)]</t>
+  </si>
+  <si>
+    <t>[np.float64(448.4726316423788), np.float64(470.60476265149487)]</t>
+  </si>
+  <si>
+    <t>[np.float64(533.5174765895531), np.float64(425.7987362970821)]</t>
+  </si>
+  <si>
+    <t>[np.float64(593.7409369907805), np.float64(124.62359096887656)]</t>
+  </si>
+  <si>
+    <t>[np.float64(808.741434699215), np.float64(-345.63436701941566)]</t>
+  </si>
+  <si>
+    <t>[np.float64(111.35573126573573), np.float64(534.7301281302518)]</t>
+  </si>
+  <si>
+    <t>[np.float64(969.9435356660357), np.float64(-278.1668804821279)]</t>
+  </si>
+  <si>
+    <t>[np.float64(181.49689801826253), np.float64(-314.7511985967712)]</t>
+  </si>
+  <si>
+    <t>[np.float64(849.0745197470737), np.float64(218.42635904381427)]</t>
+  </si>
+  <si>
+    <t>[np.float64(174.42737299647115), np.float64(-104.88245809709088)]</t>
+  </si>
+  <si>
+    <t>[np.float64(586.8002454978607), np.float64(293.4784113043994)]</t>
+  </si>
+  <si>
+    <t>[np.float64(35.931987805097876), np.float64(113.50039580224359)]</t>
+  </si>
+  <si>
+    <t>[np.float64(942.0795060936316), np.float64(-137.3291111622666)]</t>
+  </si>
+  <si>
+    <t>[np.float64(108.64385982336266), np.float64(533.0649439964602)]</t>
+  </si>
+  <si>
+    <t>[np.float64(530.698286537769), np.float64(277.2245750880013)]</t>
+  </si>
+  <si>
+    <t>[np.float64(533.7659961571004), np.float64(302.4357051610823)]</t>
+  </si>
+  <si>
+    <t>[np.float64(508.0027106686088), np.float64(544.8992990165987)]</t>
+  </si>
+  <si>
+    <t>[np.float64(901.2143484944819), np.float64(248.192485302794)]</t>
+  </si>
+  <si>
+    <t>[np.float64(332.15187551081846), np.float64(129.313513149939)]</t>
+  </si>
+  <si>
+    <t>[np.float64(427.96956900740923), np.float64(-206.418754417132)]</t>
+  </si>
+  <si>
+    <t>[np.float64(611.8864755002925), np.float64(-295.4512063549722)]</t>
+  </si>
+  <si>
+    <t>[np.float64(914.8000631689704), np.float64(188.1132438205425)]</t>
+  </si>
+  <si>
+    <t>[np.float64(625.7863337298347), np.float64(306.5038811937894)]</t>
+  </si>
+  <si>
+    <t>[np.float64(342.19255780304593), np.float64(452.8894043636992)]</t>
+  </si>
+  <si>
+    <t>[np.float64(940.1457681593367), np.float64(-96.2844229109433)]</t>
+  </si>
+  <si>
+    <t>[np.float64(891.8675645184726), np.float64(285.3722626157712)]</t>
+  </si>
+  <si>
+    <t>[np.float64(96.189275800998), np.float64(-109.16937976792673)]</t>
+  </si>
+  <si>
+    <t>[np.float64(76.05023442400538), np.float64(365.53041502234987)]</t>
+  </si>
+  <si>
+    <t>[np.float64(170.88751819503722), np.float64(-151.67862166494427)]</t>
+  </si>
+  <si>
+    <t>[np.float64(252.530854326108), np.float64(73.98569152106211)]</t>
+  </si>
+  <si>
+    <t>[np.float64(791.0508718380784), np.float64(101.29993454568819)]</t>
+  </si>
+  <si>
+    <t>[np.float64(816.2809355565129), np.float64(274.11846034627297)]</t>
+  </si>
+  <si>
+    <t>[np.float64(798.3562026475576), np.float64(-359.211492022724)]</t>
+  </si>
+  <si>
+    <t>[np.float64(370.55941875808765), np.float64(-500.57001485743365)]</t>
+  </si>
+  <si>
+    <t>[np.float64(126.60044976619167), np.float64(100.66609525043486)]</t>
+  </si>
+  <si>
+    <t>[np.float64(782.0989501977365), np.float64(-437.70292493894203)]</t>
+  </si>
+  <si>
+    <t>[np.float64(536.4831055031565), np.float64(-366.5949704774233)]</t>
+  </si>
+  <si>
+    <t>[np.float64(877.9471062324288), np.float64(-268.0498652960924)]</t>
+  </si>
+  <si>
+    <t>[np.float64(569.852741009405), np.float64(500.5893808811313)]</t>
+  </si>
+  <si>
+    <t>[np.float64(943.2829504742125), np.float64(433.9425875472393)]</t>
+  </si>
+  <si>
+    <t>[np.float64(847.0784382887493), np.float64(24.82749592711923)]</t>
+  </si>
+  <si>
+    <t>[np.float64(817.8273872619123), np.float64(170.2195628281072)]</t>
+  </si>
+  <si>
+    <t>[np.float64(296.402305352436), np.float64(200.44464369800153)]</t>
+  </si>
+  <si>
+    <t>[np.float64(21.68615295526033), np.float64(349.11199775601995)]</t>
+  </si>
+  <si>
+    <t>[np.float64(43.441864801957664), np.float64(-392.58719773610653)]</t>
+  </si>
+  <si>
+    <t>[np.float64(298.7421287969515), np.float64(-237.0002012600646)]</t>
+  </si>
+  <si>
+    <t>[np.float64(497.95493059376463), np.float64(-367.3122345973817)]</t>
+  </si>
+  <si>
+    <t>[np.float64(55.77924112417077), np.float64(-556.3667747759721)]</t>
+  </si>
+  <si>
+    <t>[np.float64(641.1069193795714), np.float64(-131.61397525668315)]</t>
+  </si>
+  <si>
+    <t>[np.float64(828.4414531751199), np.float64(-210.08880107780618)]</t>
+  </si>
+  <si>
+    <t>[np.float64(859.6971455165781), np.float64(-126.96413718810396)]</t>
+  </si>
+  <si>
+    <t>[np.float64(336.3973154071993), np.float64(412.922899594614)]</t>
+  </si>
+  <si>
+    <t>[np.float64(638.3359813432866), np.float64(286.00861162979174)]</t>
+  </si>
+  <si>
+    <t>[np.float64(692.2653963481083), np.float64(-208.02638371847968)]</t>
+  </si>
+  <si>
+    <t>[np.float64(280.33971662266066), np.float64(-127.99761698906224)]</t>
+  </si>
+  <si>
+    <t>[np.float64(704.1375298263495), np.float64(542.7045975595609)]</t>
+  </si>
+  <si>
+    <t>[np.float64(966.2462264023037), np.float64(-184.43708295036316)]</t>
+  </si>
+  <si>
+    <t>[np.float64(603.9706960878783), np.float64(65.1535656703071)]</t>
+  </si>
+  <si>
+    <t>[np.float64(898.3965205333124), np.float64(112.90206175500884)]</t>
+  </si>
+  <si>
+    <t>[np.float64(704.5540711256614), np.float64(-239.42904307194556)]</t>
+  </si>
+  <si>
+    <t>[np.float64(788.9008711683908), np.float64(-212.2954804733418)]</t>
+  </si>
+  <si>
+    <t>[np.float64(596.1516010626348), np.float64(-571.4621772213873)]</t>
+  </si>
+  <si>
+    <t>[np.float64(98.32661761997397), np.float64(-162.81028098629275)]</t>
+  </si>
+  <si>
+    <t>[np.float64(998.4792616085754), np.float64(-578.3372508190316)]</t>
+  </si>
+  <si>
+    <t>[np.float64(254.51330777884007), np.float64(-512.7482609315745)]</t>
+  </si>
+  <si>
+    <t>[np.float64(803.0858591114865), np.float64(317.91807692075236)]</t>
+  </si>
+  <si>
+    <t>[np.float64(162.50381210066323), np.float64(176.81677772070202)]</t>
+  </si>
+  <si>
+    <t>[np.float64(501.27168296876556), np.float64(-119.99877951551781)]</t>
+  </si>
+  <si>
+    <t>[np.float64(71.03242887551143), np.float64(233.80693092042577)]</t>
+  </si>
+  <si>
+    <t>[np.float64(402.2520985133242), np.float64(430.700854908413)]</t>
+  </si>
+  <si>
+    <t>[np.float64(267.18947403598594), np.float64(576.3690602760373)]</t>
+  </si>
+  <si>
+    <t>[np.float64(582.2811524333684), np.float64(-416.5782010197031)]</t>
+  </si>
+  <si>
+    <t>[np.float64(584.4711371020022), np.float64(-198.04130177708123)]</t>
+  </si>
+  <si>
+    <t>[np.float64(159.62115242218022), np.float64(-10.733275692216239)]</t>
+  </si>
+  <si>
+    <t>[np.float64(446.81958712867566), np.float64(5.577168225637479)]</t>
+  </si>
+  <si>
+    <t>[np.float64(982.3935616717356), np.float64(184.77741485313516)]</t>
+  </si>
+  <si>
+    <t>[np.float64(820.9910032359346), np.float64(-520.5839275854454)]</t>
+  </si>
+  <si>
+    <t>[np.float64(580.6571413499377), np.float64(350.89211797978544)]</t>
+  </si>
+  <si>
+    <t>[np.float64(925.1622374803575), np.float64(364.24343573065516)]</t>
+  </si>
+  <si>
+    <t>[np.float64(353.40733326466477), np.float64(-182.0881001675903)]</t>
+  </si>
+  <si>
+    <t>[np.float64(713.3899551472188), np.float64(263.9937949914208)]</t>
+  </si>
+  <si>
+    <t>[np.float64(469.7734532691998), np.float64(96.12934852622516)]</t>
+  </si>
+  <si>
+    <t>[np.float64(485.26499495325805), np.float64(-290.07510115022006)]</t>
+  </si>
+  <si>
+    <t>[np.float64(923.7326488278245), np.float64(-315.24362638385844)]</t>
+  </si>
+  <si>
+    <t>[np.float64(237.53886809625692), np.float64(474.1095961289807)]</t>
+  </si>
+  <si>
+    <t>[np.float64(512.4309503758404), np.float64(-424.64619162912925)]</t>
+  </si>
+  <si>
+    <t>[np.float64(777.9240700362375), np.float64(-372.33040798481693)]</t>
+  </si>
+  <si>
+    <t>[np.float64(518.9721375148439), np.float64(-301.60186670829773)]</t>
+  </si>
+  <si>
+    <t>[np.float64(502.7208067428324), np.float64(55.54906813759976)]</t>
+  </si>
+  <si>
+    <t>[np.float64(243.65425562443787), np.float64(-113.68056727115936)]</t>
+  </si>
+  <si>
+    <t>[np.float64(765.0920187051164), np.float64(-176.89771315681116)]</t>
+  </si>
+  <si>
+    <t>[np.float64(535.3262884882529), np.float64(170.88536519028855)]</t>
+  </si>
+  <si>
+    <t>[np.float64(182.57157798328427), np.float64(-485.320827080758)]</t>
+  </si>
+  <si>
+    <t>[np.float64(356.5273418436831), np.float64(-267.67108835869533)]</t>
+  </si>
+  <si>
+    <t>[np.float64(865.995230559085), np.float64(459.28544791076047)]</t>
+  </si>
+  <si>
+    <t>[np.float64(272.2300343185209), np.float64(-215.19790528973795)]</t>
+  </si>
+  <si>
+    <t>[np.float64(629.137379469192), np.float64(-561.1113619569007)]</t>
+  </si>
+  <si>
+    <t>[np.float64(190.6582924547996), np.float64(-427.29702802844736)]</t>
+  </si>
+  <si>
+    <t>[np.float64(272.97717467548676), np.float64(253.63345520256553)]</t>
+  </si>
+  <si>
+    <t>[np.float64(132.76466398434295), np.float64(598.4109561371972)]</t>
+  </si>
+  <si>
+    <t>[np.float64(583.832994212183), np.float64(482.3899908493422)]</t>
+  </si>
+  <si>
+    <t>[np.float64(9.184116210422367), np.float64(588.8126883556358)]</t>
+  </si>
+  <si>
+    <t>[np.float64(45.95209347724838), np.float64(297.6418400990468)]</t>
+  </si>
+  <si>
+    <t>[np.float64(511.1080092551473), np.float64(231.3058901076497)]</t>
+  </si>
+  <si>
+    <t>[np.float64(129.63438767172363), np.float64(206.61267202281658)]</t>
+  </si>
+  <si>
+    <t>[np.float64(793.5200066661343), np.float64(558.0132026754634)]</t>
+  </si>
+  <si>
+    <t>[np.float64(95.10010141402935), np.float64(-218.04211184953283)]</t>
+  </si>
+  <si>
+    <t>[np.float64(557.0891169316166), np.float64(15.83416712791768)]</t>
+  </si>
+  <si>
+    <t>[np.float64(784.7777524341774), np.float64(555.7517462010171)]</t>
+  </si>
+  <si>
+    <t>[np.float64(502.9761854832259), np.float64(297.0389091693063)]</t>
+  </si>
+  <si>
+    <t>[np.float64(808.3878463216786), np.float64(-173.40926888241887)]</t>
+  </si>
+  <si>
+    <t>[np.float64(641.8301750977375), np.float64(-259.40728674502117)]</t>
+  </si>
+  <si>
+    <t>[np.float64(935.7908790019404), np.float64(-200.44685972874453)]</t>
+  </si>
+  <si>
+    <t>[np.float64(932.224749789966), np.float64(327.64618309153)]</t>
+  </si>
+  <si>
+    <t>[np.float64(999.7899435291852), np.float64(-186.20731783538952)]</t>
+  </si>
+  <si>
+    <t>[np.float64(420.40592869236224), np.float64(-558.7995380133956)]</t>
+  </si>
+  <si>
+    <t>[np.float64(267.27467142669883), np.float64(313.86036631667264)]</t>
+  </si>
+  <si>
+    <t>[np.float64(392.0046643403765), np.float64(318.92667802220876)]</t>
+  </si>
+  <si>
+    <t>[np.float64(407.40423483071663), np.float64(591.3827204155286)]</t>
+  </si>
+  <si>
+    <t>[np.float64(179.31883515299808), np.float64(-517.1457788219616)]</t>
+  </si>
+  <si>
+    <t>[np.float64(76.46839069906486), np.float64(-449.0693678812024)]</t>
+  </si>
+  <si>
+    <t>[np.float64(109.69083795152446), np.float64(361.9657314963332)]</t>
+  </si>
+  <si>
+    <t>[np.float64(751.4305585486169), np.float64(556.7561518436012)]</t>
+  </si>
+  <si>
+    <t>[np.float64(841.3771100792022), np.float64(9.407327842836821)]</t>
+  </si>
+  <si>
+    <t>[np.float64(699.4856443639372), np.float64(279.5273585724392)]</t>
+  </si>
+  <si>
+    <t>[np.float64(671.6162785715434), np.float64(-488.19865428283754)]</t>
+  </si>
+  <si>
+    <t>[np.float64(652.2870262808342), np.float64(-260.71229472688117)]</t>
+  </si>
+  <si>
+    <t>[np.float64(660.0420920559899), np.float64(-392.29250355318464)]</t>
+  </si>
+  <si>
+    <t>[np.float64(545.3020421639761), np.float64(-486.9976765423691)]</t>
+  </si>
+  <si>
+    <t>[np.float64(814.7070375101584), np.float64(-587.0513043477254)]</t>
+  </si>
+  <si>
+    <t>[np.float64(22.88253428920928), np.float64(-526.1410776318787)]</t>
+  </si>
+  <si>
+    <t>[np.float64(265.7470344006765), np.float64(311.6916741676009)]</t>
+  </si>
+  <si>
+    <t>[np.float64(798.4575105507711), np.float64(76.74917727670856)]</t>
+  </si>
+  <si>
+    <t>[np.float64(187.9010862984941), np.float64(-593.967917229921)]</t>
+  </si>
+  <si>
+    <t>[np.float64(136.2982766492471), np.float64(-406.3309880977389)]</t>
+  </si>
+  <si>
+    <t>[np.float64(777.0865869382196), np.float64(130.7452048399108)]</t>
+  </si>
+  <si>
+    <t>[np.float64(644.5354351668519), np.float64(67.56488665646827)]</t>
+  </si>
+  <si>
+    <t>[np.float64(180.99701528992952), np.float64(-186.16413850899056)]</t>
+  </si>
+  <si>
+    <t>[np.float64(552.106721440518), np.float64(-141.84317831284778)]</t>
+  </si>
+  <si>
+    <t>[np.float64(204.69296299743178), np.float64(529.0501404612746)]</t>
+  </si>
+  <si>
+    <t>[np.float64(493.2739948529645), np.float64(-490.70234886892445)]</t>
+  </si>
+  <si>
+    <t>[np.float64(85.10893111850105), np.float64(-97.24276203720558)]</t>
+  </si>
+  <si>
+    <t>[np.float64(361.9787320354286), np.float64(0.8275469895820606)]</t>
+  </si>
+  <si>
+    <t>[np.float64(220.65824734064444), np.float64(442.59148916543063)]</t>
+  </si>
+  <si>
+    <t>[np.float64(921.3245123127954), np.float64(-260.88832001930075)]</t>
+  </si>
+  <si>
+    <t>[np.float64(69.76085157343704), np.float64(480.3205378740786)]</t>
+  </si>
+  <si>
+    <t>[np.float64(646.6878314614036), np.float64(-79.79155694817996)]</t>
+  </si>
+  <si>
+    <t>[np.float64(946.3923160700576), np.float64(574.4804429936557)]</t>
+  </si>
+  <si>
+    <t>[np.float64(320.4010525597273), np.float64(-394.7855321376944)]</t>
+  </si>
+  <si>
+    <t>[np.float64(317.6390686620776), np.float64(-310.1094097763987)]</t>
+  </si>
+  <si>
+    <t>[np.float64(523.6592039286477), np.float64(-569.8522063094274)]</t>
+  </si>
+  <si>
+    <t>[np.float64(173.7561066082498), np.float64(139.6099258053547)]</t>
+  </si>
+  <si>
+    <t>[np.float64(665.8629255435021), np.float64(512.4705683355783)]</t>
+  </si>
+  <si>
+    <t>[np.float64(149.1239370898324), np.float64(-355.9576588715415)]</t>
+  </si>
+  <si>
+    <t>[np.float64(45.7826215984285), np.float64(-310.631673947013)]</t>
+  </si>
+  <si>
+    <t>[np.float64(979.4273607436921), np.float64(-213.70999256704863)]</t>
+  </si>
+  <si>
+    <t>[np.float64(249.27855722103988), np.float64(255.22001406810045)]</t>
+  </si>
+  <si>
+    <t>[np.float64(617.8584317367563), np.float64(303.7155454706947)]</t>
+  </si>
+  <si>
+    <t>[np.float64(220.20246411109125), np.float64(86.03623329696916)]</t>
+  </si>
+  <si>
+    <t>[np.float64(656.1916513185673), np.float64(143.7319090120368)]</t>
+  </si>
+  <si>
+    <t>[np.float64(201.7206226366226), np.float64(-596.9629054371782)]</t>
+  </si>
+  <si>
+    <t>[np.float64(327.33196991784655), np.float64(-588.0289251232031)]</t>
+  </si>
+  <si>
+    <t>[np.float64(895.8363751481418), np.float64(-142.9691890811044)]</t>
+  </si>
+  <si>
+    <t>[np.float64(876.2968670453945), np.float64(555.8212535249661)]</t>
+  </si>
+  <si>
+    <t>[np.float64(919.3414025075214), np.float64(-298.29087205267274)]</t>
+  </si>
+  <si>
+    <t>[np.float64(27.450767176823156), np.float64(486.9593919446495)]</t>
+  </si>
+  <si>
+    <t>[np.float64(601.0924868007208), np.float64(428.7530995704176)]</t>
+  </si>
+  <si>
+    <t>[np.float64(230.27127151427595), np.float64(206.3665791634827)]</t>
+  </si>
+  <si>
+    <t>[np.float64(283.56032718175607), np.float64(-496.54957548496196)]</t>
+  </si>
+  <si>
+    <t>[np.float64(929.1765369979183), np.float64(-515.4819504991847)]</t>
+  </si>
+  <si>
+    <t>[np.float64(551.0390578112343), np.float64(365.74181365439904)]</t>
+  </si>
+  <si>
+    <t>[np.float64(574.8733750535367), np.float64(-526.8983984383176)]</t>
+  </si>
+  <si>
+    <t>[np.float64(709.4341230425114), np.float64(-396.0725038126143)]</t>
+  </si>
+  <si>
+    <t>[np.float64(178.94513513190768), np.float64(126.83577031777577)]</t>
+  </si>
+  <si>
+    <t>[np.float64(409.39760449207785), np.float64(-138.44174617254623)]</t>
+  </si>
+  <si>
+    <t>[np.float64(180.34452811191903), np.float64(478.5334190172987)]</t>
+  </si>
+  <si>
+    <t>[np.float64(987.18826726983), np.float64(90.34380819412797)]</t>
+  </si>
+  <si>
+    <t>[np.float64(495.6513696688164), np.float64(165.04694818170276)]</t>
+  </si>
+  <si>
+    <t>[np.float64(923.2886791863842), np.float64(527.9178780524398)]</t>
+  </si>
+  <si>
+    <t>[np.float64(97.5600449449845), np.float64(56.80430302962566)]</t>
+  </si>
+  <si>
+    <t>[np.float64(696.4065784355374), np.float64(75.63015034552393)]</t>
+  </si>
+  <si>
+    <t>[np.float64(520.2826420304926), np.float64(342.48252345823903)]</t>
+  </si>
+  <si>
+    <t>[np.float64(494.63972341005837), np.float64(-335.183021068504)]</t>
+  </si>
+  <si>
+    <t>[np.float64(810.6431855826607), np.float64(-457.18661924526964)]</t>
+  </si>
+  <si>
+    <t>[np.float64(402.5037538828762), np.float64(-360.69825457869234)]</t>
+  </si>
+  <si>
+    <t>[np.float64(416.3879676753839), np.float64(-106.143082860952)]</t>
+  </si>
+  <si>
+    <t>[np.float64(937.8543063638692), np.float64(-1.9062569438085575)]</t>
+  </si>
+  <si>
+    <t>[np.float64(120.55692232389926), np.float64(-167.02841700867054)]</t>
+  </si>
+  <si>
+    <t>[np.float64(793.5257376942358), np.float64(508.3568180996567)]</t>
+  </si>
+  <si>
+    <t>[np.float64(7.583500413738897), np.float64(-126.18058856626487)]</t>
+  </si>
+  <si>
+    <t>[np.float64(714.0103132710052), np.float64(123.34155128470593)]</t>
+  </si>
+  <si>
+    <t>[np.float64(11.523974430708627), np.float64(138.70542485402314)]</t>
+  </si>
+  <si>
+    <t>[np.float64(307.18673527240094), np.float64(581.05788814369)]</t>
+  </si>
+  <si>
+    <t>[np.float64(548.255019096402), np.float64(373.8090667425997)]</t>
+  </si>
+  <si>
+    <t>[np.float64(425.59945731341077), np.float64(-126.42066040736444)]</t>
+  </si>
+  <si>
+    <t>[np.float64(724.1188584425079), np.float64(-588.0861531506088)]</t>
+  </si>
+  <si>
+    <t>[np.float64(541.9027140567872), np.float64(-109.16982886826844)]</t>
+  </si>
+  <si>
+    <t>[np.float64(234.63626549265615), np.float64(-363.31605637909877)]</t>
+  </si>
+  <si>
+    <t>[np.float64(964.0917622028444), np.float64(-141.61227399477536)]</t>
+  </si>
+  <si>
+    <t>[np.float64(793.7767724904589), np.float64(-262.37691344373826)]</t>
+  </si>
+  <si>
+    <t>[np.float64(124.10133979700755), np.float64(523.0201165601238)]</t>
+  </si>
+  <si>
+    <t>[np.float64(802.0471934463227), np.float64(435.3311378517442)]</t>
+  </si>
+  <si>
+    <t>[np.float64(156.46470788449184), np.float64(427.7095940961192)]</t>
+  </si>
+  <si>
+    <t>[np.float64(955.2419311223724), np.float64(-489.3738050378877)]</t>
+  </si>
+  <si>
+    <t>[np.float64(193.9589279607803), np.float64(-282.29674297621887)]</t>
+  </si>
+  <si>
+    <t>[np.float64(659.3854686033745), np.float64(383.5902325219729)]</t>
+  </si>
+  <si>
+    <t>[np.float64(501.5790888091598), np.float64(527.7593761092637)]</t>
+  </si>
+  <si>
+    <t>[np.float64(124.92733335979322), np.float64(405.47758417325974)]</t>
+  </si>
+  <si>
+    <t>[np.float64(563.2376932642173), np.float64(454.6139649315812)]</t>
+  </si>
+  <si>
+    <t>[np.float64(335.03770124041364), np.float64(-308.821681464059)]</t>
+  </si>
+  <si>
+    <t>[np.float64(783.5924622696623), np.float64(336.7654430182504)]</t>
+  </si>
+  <si>
+    <t>[np.float64(875.3903000573733), np.float64(-535.8575116353247)]</t>
+  </si>
+  <si>
+    <t>[np.float64(864.7318960069008), np.float64(434.9882007691215)]</t>
+  </si>
+  <si>
+    <t>[np.float64(492.64515297981535), np.float64(366.2059982003134)]</t>
+  </si>
+  <si>
+    <t>[np.float64(119.6616514279566), np.float64(-199.02905471674075)]</t>
+  </si>
+  <si>
+    <t>[np.float64(159.81740020686686), np.float64(43.92429955553769)]</t>
+  </si>
+  <si>
+    <t>[np.float64(717.5684689963649), np.float64(-512.5068064406622)]</t>
+  </si>
+  <si>
+    <t>[np.float64(66.82343866651819), np.float64(-342.1088363017069)]</t>
+  </si>
+  <si>
+    <t>[np.float64(284.1041457057114), np.float64(-411.30356498530193)]</t>
+  </si>
+  <si>
+    <t>[np.float64(709.6952077811641), np.float64(406.7079904896848)]</t>
+  </si>
+  <si>
+    <t>[np.float64(467.5847410057451), np.float64(472.5035766614394)]</t>
+  </si>
+  <si>
+    <t>[np.float64(176.2588631357197), np.float64(-193.06685304435535)]</t>
+  </si>
+  <si>
+    <t>[np.float64(928.0985389340647), np.float64(70.9392030693765)]</t>
+  </si>
+  <si>
+    <t>[np.float64(382.30649028973176), np.float64(63.892394755988676)]</t>
+  </si>
+  <si>
+    <t>[np.float64(977.6928841052583), np.float64(266.3700070501344)]</t>
+  </si>
+  <si>
+    <t>[np.float64(695.568240186256), np.float64(192.79549217992735)]</t>
+  </si>
+  <si>
+    <t>[np.float64(658.5189961772656), np.float64(-283.3979682612487)]</t>
+  </si>
+  <si>
+    <t>[np.float64(350.81377995288085), np.float64(306.960601203976)]</t>
+  </si>
+  <si>
+    <t>[np.float64(457.14730481838404), np.float64(-471.28107569921616)]</t>
+  </si>
+  <si>
+    <t>[np.float64(440.5099446628202), np.float64(-313.62807185739257)]</t>
+  </si>
+  <si>
+    <t>[np.float64(374.4740316499794), np.float64(-335.9377823327413)]</t>
+  </si>
+  <si>
+    <t>[np.float64(337.92214347797335), np.float64(526.0130022555904)]</t>
+  </si>
+  <si>
+    <t>[np.float64(913.7588597059291), np.float64(-445.1367649786108)]</t>
+  </si>
+  <si>
+    <t>[np.float64(766.4925075545452), np.float64(-563.1604187912958)]</t>
+  </si>
+  <si>
+    <t>[np.float64(346.4417885871202), np.float64(143.9564955722567)]</t>
+  </si>
+  <si>
+    <t>[np.float64(443.6775997444078), np.float64(-277.51875245930614)]</t>
+  </si>
+  <si>
+    <t>[np.float64(599.9289840536051), np.float64(346.27917863756466)]</t>
+  </si>
+  <si>
+    <t>[np.float64(243.5139746142907), np.float64(-391.04419233575544)]</t>
+  </si>
+  <si>
+    <t>[np.float64(560.9882960331133), np.float64(65.11026053677313)]</t>
+  </si>
+  <si>
+    <t>[np.float64(684.5575646758156), np.float64(-587.3064125663614)]</t>
+  </si>
+  <si>
+    <t>[np.float64(143.6615202068211), np.float64(-168.95655240507585)]</t>
+  </si>
+  <si>
+    <t>[np.float64(499.68027268282054), np.float64(319.13092646921166)]</t>
+  </si>
+  <si>
+    <t>[np.float64(483.3107790590258), np.float64(141.64279193123923)]</t>
+  </si>
+  <si>
+    <t>[np.float64(506.48554944918357), np.float64(-137.21028866225157)]</t>
+  </si>
+  <si>
+    <t>[np.float64(68.754880162197), np.float64(39.67361181415242)]</t>
+  </si>
+  <si>
+    <t>[np.float64(213.4756380500148), np.float64(-247.4937803406777)]</t>
+  </si>
+  <si>
+    <t>[np.float64(134.55441259631485), np.float64(-454.44623766634027)]</t>
+  </si>
+  <si>
+    <t>[np.float64(919.035018774724), np.float64(123.13585326685734)]</t>
+  </si>
+  <si>
+    <t>[np.float64(35.120395902414224), np.float64(-268.90437257321264)]</t>
+  </si>
+  <si>
+    <t>[np.float64(390.9581274038667), np.float64(-221.80749673771322)]</t>
+  </si>
+  <si>
+    <t>[np.float64(20.162533486528854), np.float64(512.6309870483838)]</t>
+  </si>
+  <si>
+    <t>[np.float64(758.0636307294949), np.float64(-513.8878932700477)]</t>
+  </si>
+  <si>
+    <t>[np.float64(538.2327592042751), np.float64(-514.247980012849)]</t>
+  </si>
+  <si>
+    <t>[np.float64(160.02832906260102), np.float64(215.79421977143272)]</t>
+  </si>
+  <si>
+    <t>[np.float64(644.9616731628989), np.float64(116.34065764515537)]</t>
+  </si>
+  <si>
+    <t>[np.float64(519.5849235901899), np.float64(24.387933852053038)]</t>
+  </si>
+  <si>
+    <t>[np.float64(493.9501569714548), np.float64(69.48878066027407)]</t>
+  </si>
+  <si>
+    <t>[np.float64(871.4250350780251), np.float64(54.031818114321254)]</t>
+  </si>
+  <si>
+    <t>[np.float64(867.3240974863598), np.float64(-343.04362016263065)]</t>
+  </si>
+  <si>
+    <t>[np.float64(175.9014507897406), np.float64(536.5870247157868)]</t>
+  </si>
+  <si>
+    <t>[np.float64(498.8718109906052), np.float64(-469.4361505492393)]</t>
+  </si>
+  <si>
+    <t>[np.float64(247.9921987380187), np.float64(278.7587929694064)]</t>
+  </si>
+  <si>
+    <t>[np.float64(556.5477940488819), np.float64(98.1777161728819)]</t>
+  </si>
+  <si>
+    <t>[np.float64(468.9157775390155), np.float64(308.06405580993044)]</t>
+  </si>
+  <si>
+    <t>[np.float64(215.34343766064435), np.float64(-235.58052739595536)]</t>
+  </si>
+  <si>
+    <t>[np.float64(515.7513188743999), np.float64(578.869278208271)]</t>
+  </si>
+  <si>
+    <t>[np.float64(363.17370687445947), np.float64(-155.59570110718352)]</t>
+  </si>
+  <si>
+    <t>[np.float64(379.52627575118146), np.float64(-102.22926599853122)]</t>
+  </si>
+  <si>
+    <t>[np.float64(758.1750129930465), np.float64(-143.32284839211928)]</t>
+  </si>
+  <si>
+    <t>[np.float64(587.85840526039), np.float64(554.5473122624905)]</t>
+  </si>
+  <si>
+    <t>[np.float64(469.41988644408264), np.float64(574.1768835939997)]</t>
+  </si>
+  <si>
+    <t>[np.float64(809.279549163873), np.float64(-565.3045650153846)]</t>
+  </si>
+  <si>
+    <t>[np.float64(88.30724045834137), np.float64(367.93992469472744)]</t>
+  </si>
+  <si>
+    <t>[np.float64(576.0719301611283), np.float64(568.2825090095089)]</t>
+  </si>
+  <si>
+    <t>[np.float64(384.9603881583209), np.float64(-200.5468919636092)]</t>
+  </si>
+  <si>
+    <t>[np.float64(604.8195485525487), np.float64(436.76626125507846)]</t>
+  </si>
+  <si>
+    <t>[np.float64(800.5543546949793), np.float64(18.12959176115885)]</t>
+  </si>
+  <si>
+    <t>[np.float64(127.30104497338569), np.float64(178.0721086038492)]</t>
+  </si>
+  <si>
+    <t>[np.float64(164.87215101018492), np.float64(548.2479120766347)]</t>
+  </si>
+  <si>
+    <t>[np.float64(350.9244260563117), np.float64(-393.0996222186169)]</t>
+  </si>
+  <si>
+    <t>[np.float64(37.30381217869383), np.float64(261.6117546060524)]</t>
+  </si>
+  <si>
+    <t>[np.float64(761.1135929436024), np.float64(-244.18498865866206)]</t>
+  </si>
+  <si>
+    <t>[np.float64(254.16473890908264), np.float64(595.6017920243628)]</t>
+  </si>
+  <si>
+    <t>[np.float64(642.2061493486749), np.float64(-238.36491481426435)]</t>
+  </si>
+  <si>
+    <t>[np.float64(382.9813674829614), np.float64(12.633908728272445)]</t>
+  </si>
+  <si>
+    <t>[np.float64(531.2971661687865), np.float64(3.860744859509964)]</t>
+  </si>
+  <si>
+    <t>[np.float64(983.6138916687086), np.float64(119.31202039283733)]</t>
+  </si>
+  <si>
+    <t>[np.float64(601.0462747117633), np.float64(-556.8250213264442)]</t>
+  </si>
+  <si>
+    <t>[np.float64(507.8653089866115), np.float64(-361.1676402211113)]</t>
+  </si>
+  <si>
+    <t>[np.float64(953.1113497082445), np.float64(-386.2006959925237)]</t>
+  </si>
+  <si>
+    <t>[np.float64(231.96422215993906), np.float64(-546.9469126927575)]</t>
+  </si>
+  <si>
+    <t>[np.float64(100.58742739161231), np.float64(214.8838937096084)]</t>
+  </si>
+  <si>
+    <t>[np.float64(716.3463852385651), np.float64(510.4512926011423)]</t>
+  </si>
+  <si>
+    <t>[np.float64(465.76896776869137), np.float64(-187.06353938162488)]</t>
+  </si>
+  <si>
+    <t>[np.float64(480.69852585236606), np.float64(53.506338058096844)]</t>
+  </si>
+  <si>
+    <t>[np.float64(395.4516669987528), np.float64(-587.2828674684376)]</t>
+  </si>
+  <si>
+    <t>[np.float64(904.6965029094853), np.float64(65.03893008510067)]</t>
+  </si>
+  <si>
+    <t>[np.float64(509.35544854508953), np.float64(-302.88666778120097)]</t>
+  </si>
+  <si>
+    <t>[np.float64(352.66715882306454), np.float64(93.6146107839113)]</t>
+  </si>
+  <si>
+    <t>[np.float64(13.496287097121694), np.float64(263.5260777843288)]</t>
+  </si>
+  <si>
+    <t>[np.float64(761.2779537947957), np.float64(-106.43529765219819)]</t>
+  </si>
+  <si>
+    <t>[np.float64(373.74599756446423), np.float64(56.8044535502255)]</t>
+  </si>
+  <si>
+    <t>[np.float64(327.9696392543201), np.float64(94.73527264610198)]</t>
+  </si>
+  <si>
+    <t>[np.float64(392.4708753599615), np.float64(27.9631867242756)]</t>
+  </si>
+  <si>
+    <t>[np.float64(68.27069225344995), np.float64(-538.042997886838)]</t>
+  </si>
+  <si>
+    <t>[np.float64(516.3019416361133), np.float64(-527.9014324043849)]</t>
+  </si>
+  <si>
+    <t>[np.float64(223.07017386720352), np.float64(-452.819390046739)]</t>
+  </si>
+  <si>
+    <t>[np.float64(84.95172600383493), np.float64(284.7057607676318)]</t>
+  </si>
+  <si>
+    <t>[np.float64(473.08213639357075), np.float64(-383.17569938267417)]</t>
+  </si>
+  <si>
+    <t>[np.float64(467.2802648938622), np.float64(144.0726327014777)]</t>
+  </si>
+  <si>
+    <t>[np.float64(129.55208503735582), np.float64(226.10556260273006)]</t>
+  </si>
+  <si>
+    <t>[np.float64(119.7112822097972), np.float64(-218.19016741983404)]</t>
+  </si>
+  <si>
+    <t>[np.float64(483.2621905655873), np.float64(332.34601242262386)]</t>
+  </si>
+  <si>
+    <t>[np.float64(866.2028631161907), np.float64(371.6982018234837)]</t>
+  </si>
+  <si>
+    <t>[np.float64(596.099543366851), np.float64(479.67470869819863)]</t>
+  </si>
+  <si>
+    <t>[np.float64(456.83583676316687), np.float64(516.0869083952473)]</t>
+  </si>
+  <si>
+    <t>[np.float64(682.1283734830056), np.float64(176.5740536756848)]</t>
+  </si>
+  <si>
+    <t>[np.float64(327.69399162114496), np.float64(-374.0088111347136)]</t>
+  </si>
+  <si>
+    <t>[np.float64(43.89525147509465), np.float64(-266.52153087721683)]</t>
+  </si>
+  <si>
+    <t>[np.float64(917.8483476865031), np.float64(456.616511721302)]</t>
+  </si>
+  <si>
+    <t>[np.float64(648.0117535585761), np.float64(-493.4201672397695)]</t>
+  </si>
+  <si>
+    <t>[np.float64(583.0518829128913), np.float64(-321.22177366992884)]</t>
+  </si>
+  <si>
+    <t>[np.float64(353.41949251436), np.float64(515.9574312867696)]</t>
+  </si>
+  <si>
+    <t>[np.float64(399.5118279377724), np.float64(-167.73896245102782)]</t>
+  </si>
+  <si>
+    <t>[np.float64(652.4533657725307), np.float64(192.25274679560948)]</t>
+  </si>
+  <si>
+    <t>[np.float64(672.1951179300331), np.float64(43.02251431706486)]</t>
+  </si>
+  <si>
+    <t>[np.float64(923.7728574488593), np.float64(275.97143716715436)]</t>
+  </si>
+  <si>
+    <t>[np.float64(111.28283373668025), np.float64(-65.33470862729541)]</t>
+  </si>
+  <si>
+    <t>[np.float64(311.9535996465018), np.float64(139.25383187435432)]</t>
+  </si>
+  <si>
+    <t>[np.float64(947.7345471048116), np.float64(-164.27081387901399)]</t>
+  </si>
+  <si>
+    <t>[np.float64(966.4824883263599), np.float64(-599.738291898646)]</t>
+  </si>
+  <si>
+    <t>[np.float64(243.31576628914985), np.float64(-306.2573567352421)]</t>
+  </si>
+  <si>
+    <t>[np.float64(320.1722920267737), np.float64(346.6861046032001)]</t>
+  </si>
+  <si>
+    <t>[np.float64(718.5884760727276), np.float64(-186.36800655024985)]</t>
+  </si>
+  <si>
+    <t>[np.float64(840.4296101406059), np.float64(-396.06296058570547)]</t>
+  </si>
+  <si>
+    <t>[np.float64(540.3970096618494), np.float64(474.1939432695781)]</t>
+  </si>
+  <si>
+    <t>[np.float64(892.2636639139623), np.float64(351.17314942906944)]</t>
+  </si>
+  <si>
+    <t>[np.float64(948.6690762821084), np.float64(32.89741047220548)]</t>
+  </si>
+  <si>
+    <t>[np.float64(796.0988418247972), np.float64(527.4391714053841)]</t>
+  </si>
+  <si>
+    <t>[np.float64(510.75292194320764), np.float64(-140.44896327215713)]</t>
+  </si>
+  <si>
+    <t>[np.float64(786.1237460961868), np.float64(-94.74525700762786)]</t>
+  </si>
+  <si>
+    <t>[np.float64(537.4773440147081), np.float64(507.8598192686345)]</t>
+  </si>
+  <si>
+    <t>[np.float64(302.7036172417622), np.float64(67.11408473949666)]</t>
+  </si>
+  <si>
+    <t>[np.float64(446.4001544498398), np.float64(-493.2874689861688)]</t>
+  </si>
+  <si>
+    <t>[np.float64(308.1179067632671), np.float64(473.0389495635591)]</t>
+  </si>
+  <si>
+    <t>[np.float64(323.34267042466024), np.float64(532.5756892784257)]</t>
+  </si>
+  <si>
+    <t>[np.float64(731.9172916526031), np.float64(341.77059492614967)]</t>
+  </si>
+  <si>
+    <t>[np.float64(587.1006661096458), np.float64(172.1328306934713)]</t>
+  </si>
+  <si>
+    <t>[np.float64(258.07326688310474), np.float64(436.6588278066199)]</t>
+  </si>
+  <si>
+    <t>[np.float64(179.31704549823968), np.float64(-374.4761423016986)]</t>
+  </si>
+  <si>
+    <t>[np.float64(289.8501884950007), np.float64(125.40793287409895)]</t>
+  </si>
+  <si>
+    <t>[np.float64(166.41213045063697), np.float64(267.64384589660847)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.705106769811838), np.float64(18.611916180331377)]</t>
+  </si>
+  <si>
+    <t>[np.float64(20.946997686844604), np.float64(-567.6932413827728)]</t>
+  </si>
+  <si>
+    <t>[np.float64(562.7203426638196), np.float64(-453.9148736312884)]</t>
+  </si>
+  <si>
+    <t>[np.float64(457.1839953975788), np.float64(505.950783857988)]</t>
+  </si>
+  <si>
+    <t>[np.float64(108.6734855507704), np.float64(54.77728846532705)]</t>
+  </si>
+  <si>
+    <t>[np.float64(694.1559033590903), np.float64(77.16227294436726)]</t>
+  </si>
+  <si>
+    <t>[np.float64(626.0122784011635), np.float64(551.5838151297728)]</t>
+  </si>
+  <si>
+    <t>[np.float64(250.401610611079), np.float64(172.93620833795637)]</t>
+  </si>
+  <si>
+    <t>[np.float64(279.4998072755599), np.float64(58.92149422424757)]</t>
+  </si>
+  <si>
+    <t>[np.float64(450.5735984067104), np.float64(-348.19855532902307)]</t>
+  </si>
+  <si>
+    <t>[np.float64(298.4412486093039), np.float64(597.7088549954917)]</t>
+  </si>
+  <si>
+    <t>[np.float64(844.5170555714263), np.float64(256.5689580277491)]</t>
+  </si>
+  <si>
+    <t>[np.float64(731.7219985439704), np.float64(-554.1770425887808)]</t>
+  </si>
+  <si>
+    <t>[np.float64(833.7981727961499), np.float64(528.4898322344884)]</t>
+  </si>
+  <si>
+    <t>[np.float64(259.21720975717034), np.float64(-558.5306203766036)]</t>
+  </si>
+  <si>
+    <t>[np.float64(108.70169507675853), np.float64(299.1403819682756)]</t>
+  </si>
+  <si>
+    <t>[np.float64(404.8338305330609), np.float64(394.544549034489)]</t>
+  </si>
+  <si>
+    <t>[np.float64(796.3544941058894), np.float64(171.5534327962299)]</t>
+  </si>
+  <si>
+    <t>[np.float64(147.28706150278737), np.float64(505.00839510826813)]</t>
+  </si>
+  <si>
+    <t>[np.float64(333.69069870151134), np.float64(460.5553275243717)]</t>
+  </si>
+  <si>
+    <t>[np.float64(844.9351547632153), np.float64(6.37309297766285)]</t>
+  </si>
+  <si>
+    <t>[np.float64(852.8749342905828), np.float64(466.50166004846596)]</t>
+  </si>
+  <si>
+    <t>[np.float64(674.7343582576134), np.float64(389.82189755441925)]</t>
+  </si>
+  <si>
+    <t>[np.float64(253.86111524216437), np.float64(-127.0736160203399)]</t>
+  </si>
+  <si>
+    <t>[np.float64(161.29945971939975), np.float64(-413.3032441127598)]</t>
+  </si>
+  <si>
+    <t>[np.float64(410.85785263648233), np.float64(457.3602480635002)]</t>
+  </si>
+  <si>
+    <t>[np.float64(811.2283944901067), np.float64(228.07519258138473)]</t>
+  </si>
+  <si>
+    <t>[np.float64(277.9208632733018), np.float64(366.5261143084575)]</t>
+  </si>
+  <si>
+    <t>[np.float64(281.07586883151725), np.float64(391.8031001740716)]</t>
+  </si>
+  <si>
+    <t>[np.float64(373.34825991637786), np.float64(-281.3135470996856)]</t>
+  </si>
+  <si>
+    <t>[np.float64(746.6664196562573), np.float64(597.4357282577662)]</t>
+  </si>
+  <si>
+    <t>[np.float64(731.3730484275577), np.float64(23.786240820286025)]</t>
+  </si>
+  <si>
+    <t>[np.float64(544.3829481131052), np.float64(347.1917456343525)]</t>
+  </si>
+  <si>
+    <t>[np.float64(212.8184271701733), np.float64(110.73251490420137)]</t>
+  </si>
+  <si>
+    <t>[np.float64(204.12698232122207), np.float64(-283.63322330463336)]</t>
+  </si>
+  <si>
+    <t>[np.float64(811.7450010055848), np.float64(-97.71468845499032)]</t>
+  </si>
+  <si>
+    <t>[np.float64(380.6826687407683), np.float64(213.53362588764764)]</t>
+  </si>
+  <si>
+    <t>[np.float64(739.1180493595058), np.float64(526.1698510876925)]</t>
+  </si>
+  <si>
+    <t>[np.float64(306.1191409946488), np.float64(-109.17972791555661)]</t>
+  </si>
+  <si>
+    <t>[np.float64(287.7449185016386), np.float64(-484.06538670051805)]</t>
+  </si>
+  <si>
+    <t>[np.float64(948.6033860420818), np.float64(-410.84013680587015)]</t>
+  </si>
+  <si>
+    <t>[np.float64(581.0718418535313), np.float64(399.97409444639015)]</t>
+  </si>
+  <si>
+    <t>[np.float64(99.15317960320291), np.float64(-106.7141777715326)]</t>
+  </si>
+  <si>
+    <t>[np.float64(444.41617864054336), np.float64(418.2421312768797)]</t>
+  </si>
+  <si>
+    <t>[np.float64(524.7642405438747), np.float64(-490.9958262085221)]</t>
+  </si>
+  <si>
+    <t>[np.float64(884.6371017259912), np.float64(39.44153959471896)]</t>
+  </si>
+  <si>
+    <t>[np.float64(778.790153558071), np.float64(63.440111144831576)]</t>
+  </si>
+  <si>
+    <t>[np.float64(362.9214032797091), np.float64(543.6526918567235)]</t>
+  </si>
+  <si>
+    <t>[np.float64(870.3823146865868), np.float64(141.32988840853636)]</t>
+  </si>
+  <si>
+    <t>[np.float64(276.6967776047489), np.float64(-124.08833047268428)]</t>
+  </si>
+  <si>
+    <t>[np.float64(735.9697974513206), np.float64(80.36834546572368)]</t>
+  </si>
+  <si>
+    <t>[np.float64(65.31170412919218), np.float64(-266.5505104855441)]</t>
+  </si>
+  <si>
+    <t>[np.float64(945.4154306893462), np.float64(392.5423110406732)]</t>
+  </si>
+  <si>
+    <t>[np.float64(114.77341722839263), np.float64(-293.93451619002894)]</t>
+  </si>
+  <si>
+    <t>[np.float64(160.50355617487233), np.float64(-539.174581334644)]</t>
+  </si>
+  <si>
+    <t>[np.float64(665.716157622877), np.float64(-576.2669792186864)]</t>
+  </si>
+  <si>
+    <t>[np.float64(807.3392518211552), np.float64(-126.48642540124285)]</t>
+  </si>
+  <si>
+    <t>[np.float64(611.6478949076143), np.float64(178.57583005824847)]</t>
+  </si>
+  <si>
+    <t>[np.float64(241.5892074629211), np.float64(63.9718656591366)]</t>
+  </si>
+  <si>
+    <t>[np.float64(746.4627593224616), np.float64(-517.3258249976396)]</t>
+  </si>
+  <si>
+    <t>[np.float64(523.1228160931912), np.float64(-123.2973256132044)]</t>
+  </si>
+  <si>
+    <t>[np.float64(900.4026501186227), np.float64(114.7578295659298)]</t>
+  </si>
+  <si>
+    <t>[np.float64(633.3459830909451), np.float64(435.581859350061)]</t>
+  </si>
+  <si>
+    <t>[np.float64(289.6233206919713), np.float64(126.02530273404807)]</t>
+  </si>
+  <si>
+    <t>[np.float64(111.93234108425432), np.float64(261.9034389725881)]</t>
+  </si>
+  <si>
+    <t>[np.float64(721.8074184635058), np.float64(43.99418694763824)]</t>
+  </si>
+  <si>
+    <t>[np.float64(58.27666481672522), np.float64(187.14990651915173)]</t>
+  </si>
+  <si>
+    <t>[np.float64(361.9911041409458), np.float64(485.94506511663485)]</t>
+  </si>
+  <si>
+    <t>[np.float64(196.9488537973919), np.float64(-313.6935508019473)]</t>
+  </si>
+  <si>
+    <t>[np.float64(26.27439084878469), np.float64(-302.5947011080329)]</t>
+  </si>
+  <si>
+    <t>[np.float64(113.21226281730334), np.float64(530.5144921770705)]</t>
+  </si>
+  <si>
+    <t>[np.float64(71.42705738899512), np.float64(-298.634882737259)]</t>
+  </si>
+  <si>
+    <t>[np.float64(985.5101463180649), np.float64(533.198423847437)]</t>
+  </si>
+  <si>
+    <t>[np.float64(623.9228477798196), np.float64(12.051683735373217)]</t>
+  </si>
+  <si>
+    <t>[np.float64(813.9824862521451), np.float64(422.7227500015042)]</t>
+  </si>
+  <si>
+    <t>[np.float64(432.36913836741996), np.float64(-224.7717009613949)]</t>
+  </si>
+  <si>
+    <t>[np.float64(308.9124297988299), np.float64(-276.7895737355437)]</t>
+  </si>
+  <si>
+    <t>[np.float64(712.253309571553), np.float64(141.48666369916464)]</t>
+  </si>
+  <si>
+    <t>[np.float64(296.5709774670301), np.float64(18.629953407995004)]</t>
+  </si>
+  <si>
+    <t>[np.float64(253.7859072782781), np.float64(-194.13907960072964)]</t>
+  </si>
+  <si>
+    <t>[np.float64(926.3943370007989), np.float64(-404.6748337609065)]</t>
+  </si>
+  <si>
+    <t>[np.float64(382.98938253554894), np.float64(176.96057120582896)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.4035805487413455), np.float64(-124.34328727798652)]</t>
+  </si>
+  <si>
+    <t>[np.float64(18.296109295348973), np.float64(132.43448883384258)]</t>
+  </si>
+  <si>
+    <t>[np.float64(730.361163124811), np.float64(288.71056033931677)]</t>
+  </si>
+  <si>
+    <t>[np.float64(183.76689246183574), np.float64(109.3198195259115)]</t>
+  </si>
+  <si>
+    <t>[np.float64(956.0029128037154), np.float64(251.9801771457885)]</t>
+  </si>
+  <si>
+    <t>[np.float64(679.7357944239045), np.float64(580.8986771378197)]</t>
+  </si>
+  <si>
+    <t>[np.float64(859.0601969593376), np.float64(-471.6992706267189)]</t>
+  </si>
+  <si>
+    <t>[np.float64(995.4229442438498), np.float64(570.4031324739271)]</t>
+  </si>
+  <si>
+    <t>[np.float64(747.8819162096462), np.float64(184.26710363067377)]</t>
+  </si>
+  <si>
+    <t>[np.float64(539.899796997458), np.float64(60.74605625313211)]</t>
+  </si>
+  <si>
+    <t>[np.float64(897.356539536285), np.float64(-196.9725455465716)]</t>
+  </si>
+  <si>
+    <t>[np.float64(970.9995227230902), np.float64(-127.4319860522645)]</t>
+  </si>
+  <si>
+    <t>[np.float64(305.8654819960199), np.float64(-409.61574280135255)]</t>
+  </si>
+  <si>
+    <t>[np.float64(948.0541588533172), np.float64(314.50046974068846)]</t>
+  </si>
+  <si>
+    <t>[np.float64(591.9179405445307), np.float64(302.60078228798113)]</t>
+  </si>
+  <si>
+    <t>[np.float64(878.4068510049618), np.float64(-463.55131061279997)]</t>
+  </si>
+  <si>
+    <t>[np.float64(994.3867680310182), np.float64(-519.0422334523231)]</t>
+  </si>
+  <si>
+    <t>[np.float64(457.1751743285871), np.float64(-69.46559432019353)]</t>
+  </si>
+  <si>
+    <t>[np.float64(279.21725747315264), np.float64(540.2269970533912)]</t>
+  </si>
+  <si>
+    <t>[np.float64(799.9472764216484), np.float64(-516.5482245849493)]</t>
+  </si>
+  <si>
+    <t>[np.float64(277.7747696313283), np.float64(-477.985127015137)]</t>
+  </si>
+  <si>
+    <t>[np.float64(897.9988764501242), np.float64(-310.5609306839185)]</t>
+  </si>
+  <si>
+    <t>[np.float64(681.024927843037), np.float64(-376.848863682093)]</t>
+  </si>
+  <si>
+    <t>[np.float64(20.989828918203667), np.float64(161.7581978910555)]</t>
+  </si>
+  <si>
+    <t>[np.float64(504.4014138884193), np.float64(368.51035467120096)]</t>
+  </si>
+  <si>
+    <t>[np.float64(438.6082630543377), np.float64(221.25933397767471)]</t>
+  </si>
+  <si>
+    <t>[np.float64(979.9801783961153), np.float64(236.4295520965867)]</t>
+  </si>
+  <si>
+    <t>[np.float64(312.3102120147153), np.float64(445.90024139804996)]</t>
+  </si>
+  <si>
+    <t>[np.float64(992.2963667048085), np.float64(592.7647936435228)]</t>
+  </si>
+  <si>
+    <t>[np.float64(560.2790914291911), np.float64(-217.09613683947578)]</t>
+  </si>
+  <si>
+    <t>[np.float64(885.162643230648), np.float64(587.0798348758185)]</t>
+  </si>
+  <si>
+    <t>[np.float64(575.8593102913532), np.float64(-478.05973786121183)]</t>
+  </si>
+  <si>
+    <t>[np.float64(907.79138533838), np.float64(-113.19289209312842)]</t>
+  </si>
+  <si>
+    <t>[np.float64(442.32852352232885), np.float64(-482.8799776460352)]</t>
+  </si>
+  <si>
+    <t>[np.float64(597.3207452448704), np.float64(-360.45607095826125)]</t>
+  </si>
+  <si>
+    <t>[np.float64(227.95728059805433), np.float64(-346.0915239249979)]</t>
+  </si>
+  <si>
+    <t>[np.float64(370.3735914710425), np.float64(425.2430117299623)]</t>
+  </si>
+  <si>
+    <t>[np.float64(749.0475242029455), np.float64(-552.9442097073141)]</t>
+  </si>
+  <si>
+    <t>[np.float64(126.54473924653675), np.float64(-404.3269474575579)]</t>
+  </si>
+  <si>
+    <t>[np.float64(189.4276380369122), np.float64(-310.78812420039765)]</t>
+  </si>
+  <si>
+    <t>[np.float64(511.81776425967274), np.float64(21.01383789995907)]</t>
+  </si>
+  <si>
+    <t>[np.float64(796.1784930929019), np.float64(-170.35063135049586)]</t>
+  </si>
+  <si>
+    <t>[np.float64(33.9155199790957), np.float64(48.0988638085463)]</t>
+  </si>
+  <si>
+    <t>[np.float64(979.5374755256112), np.float64(-370.4796822053611)]</t>
+  </si>
+  <si>
+    <t>[np.float64(715.941268008362), np.float64(-362.17530943973867)]</t>
+  </si>
+  <si>
+    <t>[np.float64(907.6000340519784), np.float64(237.94657807531735)]</t>
+  </si>
+  <si>
+    <t>[np.float64(678.3369570795378), np.float64(-339.7529088227879)]</t>
+  </si>
+  <si>
+    <t>[np.float64(524.4292139842728), np.float64(79.78280359396763)]</t>
+  </si>
+  <si>
+    <t>[np.float64(882.6617134748128), np.float64(-205.29705488186613)]</t>
+  </si>
+  <si>
+    <t>[np.float64(810.4082673655993), np.float64(-404.1583286274989)]</t>
+  </si>
+  <si>
+    <t>[np.float64(771.14330897072), np.float64(-466.3400572089905)]</t>
+  </si>
+  <si>
+    <t>[np.float64(856.2646026255126), np.float64(-414.39582786701055)]</t>
+  </si>
+  <si>
+    <t>[np.float64(87.94151021677344), np.float64(-425.03236013391364)]</t>
+  </si>
+  <si>
+    <t>[np.float64(123.50448149038229), np.float64(192.39614114987523)]</t>
+  </si>
+  <si>
+    <t>[np.float64(765.1100495529369), np.float64(225.16851539499737)]</t>
+  </si>
+  <si>
+    <t>[np.float64(188.1812025021541), np.float64(-492.50897764430607)]</t>
+  </si>
+  <si>
+    <t>[np.float64(606.0469180631205), np.float64(-258.16679900171505)]</t>
+  </si>
+  <si>
+    <t>[np.float64(401.91043035435405), np.float64(469.07698353094634)]</t>
+  </si>
+  <si>
+    <t>[np.float64(473.8566954611317), np.float64(89.39087413052266)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.3871717172528877), np.float64(284.9100591101028)]</t>
+  </si>
+  <si>
+    <t>[np.float64(721.9943566171557), np.float64(132.2692784016184)]</t>
+  </si>
+  <si>
+    <t>[np.float64(435.28201446084734), np.float64(-454.25016072596884)]</t>
+  </si>
+  <si>
+    <t>[np.float64(623.2090161579788), np.float64(209.02638819510764)]</t>
+  </si>
+  <si>
+    <t>[np.float64(212.35064580606644), np.float64(-536.6419126148689)]</t>
+  </si>
+  <si>
+    <t>[np.float64(704.9485953320376), np.float64(-436.54108685798644)]</t>
+  </si>
+  <si>
+    <t>[np.float64(735.2476424424316), np.float64(-392.96364035775366)]</t>
+  </si>
+  <si>
+    <t>[np.float64(335.2311780327927), np.float64(145.39772569404204)]</t>
+  </si>
+  <si>
+    <t>[np.float64(965.3754044418878), np.float64(-387.48823760915997)]</t>
+  </si>
+  <si>
+    <t>[np.float64(266.6807247778328), np.float64(-112.6449101507589)]</t>
+  </si>
+  <si>
+    <t>[np.float64(246.21859683997138), np.float64(268.8037302611041)]</t>
+  </si>
+  <si>
+    <t>[np.float64(373.29194105528006), np.float64(-292.31155643155455)]</t>
+  </si>
+  <si>
+    <t>[np.float64(495.709544856057), np.float64(-561.2944617391262)]</t>
+  </si>
+  <si>
+    <t>[np.float64(707.7175651641011), np.float64(538.493569792121)]</t>
+  </si>
+  <si>
+    <t>[np.float64(902.3041812261017), np.float64(545.7226765586777)]</t>
+  </si>
+  <si>
+    <t>[np.float64(581.8613781150401), np.float64(-580.9160753792999)]</t>
+  </si>
+  <si>
+    <t>[np.float64(788.9681744668471), np.float64(-171.22381154392758)]</t>
+  </si>
+  <si>
+    <t>[np.float64(623.9279816814476), np.float64(531.8268000606879)]</t>
+  </si>
+  <si>
+    <t>[np.float64(93.89912531132916), np.float64(331.45543800867915)]</t>
+  </si>
+  <si>
+    <t>[np.float64(680.8764541439119), np.float64(-407.7636045332716)]</t>
+  </si>
+  <si>
+    <t>[np.float64(407.9344211164894), np.float64(447.17049046431316)]</t>
+  </si>
+  <si>
+    <t>[np.float64(317.4680052989205), np.float64(454.90215115719457)]</t>
+  </si>
+  <si>
+    <t>[np.float64(25.276007365235607), np.float64(-376.4364224563616)]</t>
+  </si>
+  <si>
+    <t>[np.float64(350.4819395462315), np.float64(198.21538742628263)]</t>
+  </si>
+  <si>
+    <t>[np.float64(472.08185060708286), np.float64(567.9305483946675)]</t>
+  </si>
+  <si>
+    <t>[np.float64(221.59944093561344), np.float64(206.76563875994248)]</t>
+  </si>
+  <si>
+    <t>[np.float64(685.8725121511858), np.float64(376.4810411956437)]</t>
+  </si>
+  <si>
+    <t>[np.float64(982.6765485578557), np.float64(-287.74100358083217)]</t>
+  </si>
+  <si>
+    <t>[np.float64(195.9883820617987), np.float64(253.45465757154295)]</t>
+  </si>
+  <si>
+    <t>[np.float64(817.4306637741706), np.float64(-88.88640852464806)]</t>
+  </si>
+  <si>
+    <t>[np.float64(19.060020038457417), np.float64(-310.6618278062079)]</t>
+  </si>
+  <si>
+    <t>[np.float64(986.8136146844108), np.float64(433.285662932263)]</t>
+  </si>
+  <si>
+    <t>[np.float64(887.8115370619211), np.float64(49.270005678453686)]</t>
+  </si>
+  <si>
+    <t>[np.float64(473.52314169704954), np.float64(475.6509932181541)]</t>
+  </si>
+  <si>
+    <t>[np.float64(991.5462339019352), np.float64(-586.5440917996549)]</t>
+  </si>
+  <si>
+    <t>[np.float64(564.0181782522064), np.float64(114.95139313703703)]</t>
+  </si>
+  <si>
+    <t>[np.float64(682.3670404064202), np.float64(-512.4851186627074)]</t>
+  </si>
+  <si>
+    <t>[np.float64(42.80411888109947), np.float64(-196.09216901433552)]</t>
   </si>
 </sst>
 </file>
@@ -3203,7 +3221,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I934"/>
+  <dimension ref="A1:I940"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -24694,6 +24712,144 @@
         <v>943</v>
       </c>
     </row>
+    <row r="935" spans="1:9">
+      <c r="A935" t="s">
+        <v>9</v>
+      </c>
+      <c r="B935">
+        <v>0</v>
+      </c>
+      <c r="D935" t="s">
+        <v>10</v>
+      </c>
+      <c r="E935" t="s">
+        <v>10</v>
+      </c>
+      <c r="F935" t="s">
+        <v>10</v>
+      </c>
+      <c r="H935" t="s">
+        <v>944</v>
+      </c>
+      <c r="I935" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="936" spans="1:9">
+      <c r="A936" t="s">
+        <v>9</v>
+      </c>
+      <c r="B936">
+        <v>0</v>
+      </c>
+      <c r="D936" t="s">
+        <v>10</v>
+      </c>
+      <c r="E936" t="s">
+        <v>10</v>
+      </c>
+      <c r="F936" t="s">
+        <v>10</v>
+      </c>
+      <c r="H936" t="s">
+        <v>945</v>
+      </c>
+      <c r="I936" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="937" spans="1:9">
+      <c r="A937" t="s">
+        <v>9</v>
+      </c>
+      <c r="B937">
+        <v>0</v>
+      </c>
+      <c r="D937" t="s">
+        <v>10</v>
+      </c>
+      <c r="E937" t="s">
+        <v>10</v>
+      </c>
+      <c r="F937" t="s">
+        <v>10</v>
+      </c>
+      <c r="H937" t="s">
+        <v>946</v>
+      </c>
+      <c r="I937" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="938" spans="1:9">
+      <c r="A938" t="s">
+        <v>9</v>
+      </c>
+      <c r="B938">
+        <v>0</v>
+      </c>
+      <c r="D938" t="s">
+        <v>10</v>
+      </c>
+      <c r="E938" t="s">
+        <v>10</v>
+      </c>
+      <c r="F938" t="s">
+        <v>10</v>
+      </c>
+      <c r="H938" t="s">
+        <v>947</v>
+      </c>
+      <c r="I938" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="939" spans="1:9">
+      <c r="A939" t="s">
+        <v>9</v>
+      </c>
+      <c r="B939">
+        <v>0</v>
+      </c>
+      <c r="D939" t="s">
+        <v>10</v>
+      </c>
+      <c r="E939" t="s">
+        <v>10</v>
+      </c>
+      <c r="F939" t="s">
+        <v>10</v>
+      </c>
+      <c r="H939" t="s">
+        <v>948</v>
+      </c>
+      <c r="I939" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="940" spans="1:9">
+      <c r="A940" t="s">
+        <v>9</v>
+      </c>
+      <c r="B940">
+        <v>0</v>
+      </c>
+      <c r="D940" t="s">
+        <v>10</v>
+      </c>
+      <c r="E940" t="s">
+        <v>10</v>
+      </c>
+      <c r="F940" t="s">
+        <v>10</v>
+      </c>
+      <c r="H940" t="s">
+        <v>949</v>
+      </c>
+      <c r="I940" t="s">
+        <v>949</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Data/output/IND Stroke Position.xlsx
+++ b/Data/output/IND Stroke Position.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5643" uniqueCount="950">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5583" uniqueCount="940">
   <si>
     <t>Direct_or_Indirect</t>
   </si>
@@ -49,2821 +49,2791 @@
     <t>nan</t>
   </si>
   <si>
-    <t>[np.float64(698.0572177656861), np.float64(571.1659745989821)]</t>
-  </si>
-  <si>
-    <t>[np.float64(345.9889108157832), np.float64(-403.6040787588984)]</t>
-  </si>
-  <si>
-    <t>[np.float64(580.1129574787238), np.float64(272.82133423589414)]</t>
-  </si>
-  <si>
-    <t>[np.float64(673.8227654716696), np.float64(-92.60985242468587)]</t>
-  </si>
-  <si>
-    <t>[np.float64(893.9797016930522), np.float64(158.546201827088)]</t>
-  </si>
-  <si>
-    <t>[np.float64(830.47363664844), np.float64(-140.16348146680167)]</t>
-  </si>
-  <si>
-    <t>[np.float64(353.45860721954705), np.float64(-471.3965495185956)]</t>
-  </si>
-  <si>
-    <t>[np.float64(805.2810754916198), np.float64(-87.70987358170873)]</t>
-  </si>
-  <si>
-    <t>[np.float64(626.034430943751), np.float64(435.176244444591)]</t>
-  </si>
-  <si>
-    <t>[np.float64(888.5089578083835), np.float64(-548.2623998987458)]</t>
-  </si>
-  <si>
-    <t>[np.float64(10.094054085015403), np.float64(-263.2398268260607)]</t>
-  </si>
-  <si>
-    <t>[np.float64(787.0770431987471), np.float64(279.3447446079015)]</t>
-  </si>
-  <si>
-    <t>[np.float64(160.96640159364907), np.float64(-517.8268973974157)]</t>
-  </si>
-  <si>
-    <t>[np.float64(799.3179187366843), np.float64(105.6322763472615)]</t>
-  </si>
-  <si>
-    <t>[np.float64(204.733287016856), np.float64(84.0321899674301)]</t>
-  </si>
-  <si>
-    <t>[np.float64(416.45561922189034), np.float64(565.9143500640082)]</t>
-  </si>
-  <si>
-    <t>[np.float64(437.5061939278503), np.float64(41.02753325263575)]</t>
-  </si>
-  <si>
-    <t>[np.float64(8.414622356146428), np.float64(558.597373379225)]</t>
-  </si>
-  <si>
-    <t>[np.float64(241.53843304614153), np.float64(404.8801120970463)]</t>
-  </si>
-  <si>
-    <t>[np.float64(609.6792477164349), np.float64(-498.30582350182397)]</t>
-  </si>
-  <si>
-    <t>[np.float64(866.8663556193897), np.float64(518.6718041795245)]</t>
-  </si>
-  <si>
-    <t>[np.float64(176.90960062449435), np.float64(-477.51348655390876)]</t>
-  </si>
-  <si>
-    <t>[np.float64(971.2802432150864), np.float64(-361.11605601525184)]</t>
-  </si>
-  <si>
-    <t>[np.float64(367.6798154928853), np.float64(54.397686191477646)]</t>
-  </si>
-  <si>
-    <t>[np.float64(593.4639360640138), np.float64(343.19699577166875)]</t>
-  </si>
-  <si>
-    <t>[np.float64(185.111562182927), np.float64(401.5986531593471)]</t>
-  </si>
-  <si>
-    <t>[np.float64(369.33590574656273), np.float64(-485.48064281774805)]</t>
-  </si>
-  <si>
-    <t>[np.float64(834.814939673131), np.float64(-126.06962460724543)]</t>
-  </si>
-  <si>
-    <t>[np.float64(628.9875703134472), np.float64(217.2193344170014)]</t>
-  </si>
-  <si>
-    <t>[np.float64(835.9858246859238), np.float64(425.2990088989602)]</t>
-  </si>
-  <si>
-    <t>[np.float64(454.30579676489333), np.float64(258.9705069374975)]</t>
-  </si>
-  <si>
-    <t>[np.float64(224.5525557880398), np.float64(241.51690643043196)]</t>
-  </si>
-  <si>
-    <t>[np.float64(931.4820739926421), np.float64(-209.29522205758985)]</t>
-  </si>
-  <si>
-    <t>[np.float64(507.4268451954793), np.float64(349.41297575539454)]</t>
-  </si>
-  <si>
-    <t>[np.float64(495.7208497055718), np.float64(462.605842129183)]</t>
-  </si>
-  <si>
-    <t>[np.float64(368.8810851440106), np.float64(527.3670004111741)]</t>
-  </si>
-  <si>
-    <t>[np.float64(549.8550822332736), np.float64(-206.46321341088304)]</t>
-  </si>
-  <si>
-    <t>[np.float64(656.0655695386904), np.float64(477.1209546335897)]</t>
-  </si>
-  <si>
-    <t>[np.float64(795.4617914245316), np.float64(15.876295462239)]</t>
-  </si>
-  <si>
-    <t>[np.float64(560.0882569146124), np.float64(-461.24262011707197)]</t>
-  </si>
-  <si>
-    <t>[np.float64(367.08563282612306), np.float64(-105.31609437360288)]</t>
-  </si>
-  <si>
-    <t>[np.float64(420.5981986971924), np.float64(164.10061795005424)]</t>
-  </si>
-  <si>
-    <t>[np.float64(96.88166553279243), np.float64(281.54321714383843)]</t>
-  </si>
-  <si>
-    <t>[np.float64(694.55112895971), np.float64(366.6269467791742)]</t>
-  </si>
-  <si>
-    <t>[np.float64(78.84693380801544), np.float64(213.95410688431252)]</t>
-  </si>
-  <si>
-    <t>[np.float64(342.6730646954426), np.float64(-113.48034370754203)]</t>
-  </si>
-  <si>
-    <t>[np.float64(864.0824056304607), np.float64(54.072412564958086)]</t>
-  </si>
-  <si>
-    <t>[np.float64(943.0093555693406), np.float64(157.93182972605098)]</t>
-  </si>
-  <si>
-    <t>[np.float64(68.99991568916298), np.float64(159.86771316978684)]</t>
-  </si>
-  <si>
-    <t>[np.float64(55.68021581296412), np.float64(-476.3672589536286)]</t>
-  </si>
-  <si>
-    <t>[np.float64(414.1935342645553), np.float64(-480.62651646989616)]</t>
-  </si>
-  <si>
-    <t>[np.float64(69.01294670357305), np.float64(42.59544638009845)]</t>
-  </si>
-  <si>
-    <t>[np.float64(517.2422287423005), np.float64(-380.9166332103895)]</t>
-  </si>
-  <si>
-    <t>[np.float64(30.354901491942087), np.float64(162.95165445645864)]</t>
-  </si>
-  <si>
-    <t>[np.float64(202.96322136051592), np.float64(-357.3466088742493)]</t>
-  </si>
-  <si>
-    <t>[np.float64(581.7237004115266), np.float64(234.34946227819034)]</t>
-  </si>
-  <si>
-    <t>[np.float64(413.87716596933575), np.float64(180.43387969256526)]</t>
-  </si>
-  <si>
-    <t>[np.float64(229.1312927171232), np.float64(-360.26874100521525)]</t>
-  </si>
-  <si>
-    <t>[np.float64(799.5790299438767), np.float64(277.81707819894507)]</t>
-  </si>
-  <si>
-    <t>[np.float64(35.31001996053406), np.float64(300.1127571923512)]</t>
-  </si>
-  <si>
-    <t>[np.float64(589.9335440710985), np.float64(-388.02475603923244)]</t>
-  </si>
-  <si>
-    <t>[np.float64(502.28733169337727), np.float64(553.749630677605)]</t>
-  </si>
-  <si>
-    <t>[np.float64(49.6168384359823), np.float64(553.2454462139615)]</t>
-  </si>
-  <si>
-    <t>[np.float64(564.8517662656781), np.float64(178.4648916994521)]</t>
-  </si>
-  <si>
-    <t>[np.float64(843.9354932761628), np.float64(129.02068703099633)]</t>
-  </si>
-  <si>
-    <t>[np.float64(633.2617970634207), np.float64(-312.18709418008166)]</t>
-  </si>
-  <si>
-    <t>[np.float64(4.981187770424889), np.float64(230.79886434606965)]</t>
-  </si>
-  <si>
-    <t>[np.float64(465.1577943978301), np.float64(589.7747516807522)]</t>
-  </si>
-  <si>
-    <t>[np.float64(681.4454927861359), np.float64(29.919891194357774)]</t>
-  </si>
-  <si>
-    <t>[np.float64(595.7001461313403), np.float64(-362.10542833243323)]</t>
-  </si>
-  <si>
-    <t>[np.float64(870.9893557383559), np.float64(497.3662400207518)]</t>
-  </si>
-  <si>
-    <t>[np.float64(406.21410136556125), np.float64(362.8180562760126)]</t>
-  </si>
-  <si>
-    <t>[np.float64(76.14063244987335), np.float64(219.57038322517155)]</t>
-  </si>
-  <si>
-    <t>[np.float64(734.5494619375314), np.float64(211.76812155071332)]</t>
-  </si>
-  <si>
-    <t>[np.float64(181.9712350753876), np.float64(-510.761497188962)]</t>
-  </si>
-  <si>
-    <t>[np.float64(21.180620629885794), np.float64(106.51734005855144)]</t>
-  </si>
-  <si>
-    <t>[np.float64(204.34928669217712), np.float64(224.33601693668152)]</t>
-  </si>
-  <si>
-    <t>[np.float64(116.6443093154359), np.float64(187.26204864035515)]</t>
-  </si>
-  <si>
-    <t>[np.float64(866.0265445001355), np.float64(-494.7293753823064)]</t>
-  </si>
-  <si>
-    <t>[np.float64(860.4537808117702), np.float64(-246.4022746163336)]</t>
-  </si>
-  <si>
-    <t>[np.float64(934.7525224938466), np.float64(-201.27312133282743)]</t>
-  </si>
-  <si>
-    <t>[np.float64(183.59534768784468), np.float64(-486.3172622974376)]</t>
-  </si>
-  <si>
-    <t>[np.float64(718.8367600366686), np.float64(-235.15160760656187)]</t>
-  </si>
-  <si>
-    <t>[np.float64(686.8457385283558), np.float64(-134.75761092566995)]</t>
-  </si>
-  <si>
-    <t>[np.float64(277.66119386126655), np.float64(560.80696587947)]</t>
-  </si>
-  <si>
-    <t>[np.float64(233.34758207762707), np.float64(-212.81094966025103)]</t>
-  </si>
-  <si>
-    <t>[np.float64(591.1865784685683), np.float64(350.5433753816558)]</t>
-  </si>
-  <si>
-    <t>[np.float64(400.7712974948171), np.float64(-363.45803614322955)]</t>
-  </si>
-  <si>
-    <t>[np.float64(334.70371179421323), np.float64(-325.79785504732115)]</t>
-  </si>
-  <si>
-    <t>[np.float64(527.5573981513054), np.float64(208.86321791691682)]</t>
-  </si>
-  <si>
-    <t>[np.float64(809.0316826391094), np.float64(566.7785379272643)]</t>
-  </si>
-  <si>
-    <t>[np.float64(979.5145294455426), np.float64(-527.596890031289)]</t>
-  </si>
-  <si>
-    <t>[np.float64(784.3826897132357), np.float64(316.7154477917204)]</t>
-  </si>
-  <si>
-    <t>[np.float64(67.13043086414605), np.float64(-306.1990449261689)]</t>
-  </si>
-  <si>
-    <t>[np.float64(200.9807754022125), np.float64(-589.4980550346683)]</t>
-  </si>
-  <si>
-    <t>[np.float64(45.9477307452203), np.float64(-321.7703870744495)]</t>
-  </si>
-  <si>
-    <t>[np.float64(601.7735939061511), np.float64(43.97582560374451)]</t>
-  </si>
-  <si>
-    <t>[np.float64(506.4115512427154), np.float64(-431.71740576471154)]</t>
-  </si>
-  <si>
-    <t>[np.float64(709.2270633230795), np.float64(378.652422332819)]</t>
-  </si>
-  <si>
-    <t>[np.float64(72.91950992637585), np.float64(348.7404559877107)]</t>
-  </si>
-  <si>
-    <t>[np.float64(499.4331996602548), np.float64(12.780007569934583)]</t>
-  </si>
-  <si>
-    <t>[np.float64(390.50102287600964), np.float64(-255.96153620561995)]</t>
-  </si>
-  <si>
-    <t>[np.float64(124.10584836499905), np.float64(203.68830894144878)]</t>
-  </si>
-  <si>
-    <t>[np.float64(580.1959876507624), np.float64(-76.17500462557575)]</t>
-  </si>
-  <si>
-    <t>[np.float64(397.58272444877565), np.float64(-507.1253336849911)]</t>
-  </si>
-  <si>
-    <t>[np.float64(389.9196988684649), np.float64(471.86857351955064)]</t>
-  </si>
-  <si>
-    <t>[np.float64(244.6389351585162), np.float64(-346.96338455176993)]</t>
-  </si>
-  <si>
-    <t>[np.float64(891.36043391206), np.float64(-206.29537247417113)]</t>
-  </si>
-  <si>
-    <t>[np.float64(434.173403872118), np.float64(350.459123087331)]</t>
-  </si>
-  <si>
-    <t>[np.float64(856.947689800199), np.float64(507.10759801507766)]</t>
-  </si>
-  <si>
-    <t>[np.float64(585.3040369852014), np.float64(79.85839438448215)]</t>
-  </si>
-  <si>
-    <t>[np.float64(654.2070098153233), np.float64(-88.33305604901074)]</t>
-  </si>
-  <si>
-    <t>[np.float64(507.22842642654774), np.float64(-481.9411710794075)]</t>
-  </si>
-  <si>
-    <t>[np.float64(471.3996179696139), np.float64(438.02073986266623)]</t>
-  </si>
-  <si>
-    <t>[np.float64(733.931475906315), np.float64(-238.73524289767641)]</t>
-  </si>
-  <si>
-    <t>[np.float64(121.09422600009967), np.float64(289.11692026700257)]</t>
-  </si>
-  <si>
-    <t>[np.float64(200.88506398777983), np.float64(-212.83112102960524)]</t>
-  </si>
-  <si>
-    <t>[np.float64(807.2714826959648), np.float64(-406.64612130740784)]</t>
-  </si>
-  <si>
-    <t>[np.float64(151.95328410427567), np.float64(152.0278261820996)]</t>
-  </si>
-  <si>
-    <t>[np.float64(121.8458726699434), np.float64(-289.39651022146154)]</t>
-  </si>
-  <si>
-    <t>[np.float64(496.4336382366982), np.float64(8.30075688846614)]</t>
-  </si>
-  <si>
-    <t>[np.float64(141.5966127703372), np.float64(-308.51320893365005)]</t>
-  </si>
-  <si>
-    <t>[np.float64(995.4150630229874), np.float64(4.385400924730334)]</t>
-  </si>
-  <si>
-    <t>[np.float64(907.0832893101935), np.float64(596.6269851265092)]</t>
-  </si>
-  <si>
-    <t>[np.float64(763.6536880147103), np.float64(380.82922255528536)]</t>
-  </si>
-  <si>
-    <t>[np.float64(637.5339192857509), np.float64(-474.3171212586934)]</t>
-  </si>
-  <si>
-    <t>[np.float64(84.93492462682295), np.float64(-187.37592020850246)]</t>
-  </si>
-  <si>
-    <t>[np.float64(328.03664678717206), np.float64(-228.5147751809763)]</t>
-  </si>
-  <si>
-    <t>[np.float64(597.9031224237042), np.float64(324.7834914633206)]</t>
-  </si>
-  <si>
-    <t>[np.float64(59.80851212252147), np.float64(369.2912013264016)]</t>
-  </si>
-  <si>
-    <t>[np.float64(835.0224219388359), np.float64(-67.4951557594062)]</t>
-  </si>
-  <si>
-    <t>[np.float64(990.7445502709977), np.float64(168.98365403011962)]</t>
-  </si>
-  <si>
-    <t>[np.float64(146.2587328917041), np.float64(325.82867878619584)]</t>
-  </si>
-  <si>
-    <t>[np.float64(362.5775837706512), np.float64(64.42261354609082)]</t>
-  </si>
-  <si>
-    <t>[np.float64(522.0450863419958), np.float64(86.60228249364866)]</t>
-  </si>
-  <si>
-    <t>[np.float64(555.4690420264326), np.float64(105.06025047540254)]</t>
-  </si>
-  <si>
-    <t>[np.float64(457.99392735636457), np.float64(158.600515158211)]</t>
-  </si>
-  <si>
-    <t>[np.float64(981.0052983520675), np.float64(66.65726759931636)]</t>
-  </si>
-  <si>
-    <t>[np.float64(976.8467513476282), np.float64(-264.02011897250793)]</t>
-  </si>
-  <si>
-    <t>[np.float64(810.3213028683132), np.float64(-366.4000961950859)]</t>
-  </si>
-  <si>
-    <t>[np.float64(633.4395376442702), np.float64(269.0321139932711)]</t>
-  </si>
-  <si>
-    <t>[np.float64(69.21319807377147), np.float64(-374.67925411508753)]</t>
-  </si>
-  <si>
-    <t>[np.float64(646.0737667476733), np.float64(-543.9124867074959)]</t>
-  </si>
-  <si>
-    <t>[np.float64(980.580609139414), np.float64(-342.22022234413737)]</t>
-  </si>
-  <si>
-    <t>[np.float64(217.29201151974152), np.float64(231.85507577946635)]</t>
-  </si>
-  <si>
-    <t>[np.float64(858.0911812742595), np.float64(264.50585591495553)]</t>
-  </si>
-  <si>
-    <t>[np.float64(777.1779748249476), np.float64(-170.7709407813262)]</t>
-  </si>
-  <si>
-    <t>[np.float64(466.3919536782829), np.float64(-227.73843703307261)]</t>
-  </si>
-  <si>
-    <t>[np.float64(419.31204790628675), np.float64(169.4088895262654)]</t>
-  </si>
-  <si>
-    <t>[np.float64(742.9377858043019), np.float64(-545.3808121884751)]</t>
-  </si>
-  <si>
-    <t>[np.float64(716.5237908477357), np.float64(-343.4567395432577)]</t>
-  </si>
-  <si>
-    <t>[np.float64(779.4289143664565), np.float64(-589.5385810426767)]</t>
-  </si>
-  <si>
-    <t>[np.float64(41.466069894546045), np.float64(-140.04786911419484)]</t>
-  </si>
-  <si>
-    <t>[np.float64(15.210421816310937), np.float64(98.86334614395139)]</t>
-  </si>
-  <si>
-    <t>[np.float64(492.0943714238428), np.float64(-457.6979837094144)]</t>
-  </si>
-  <si>
-    <t>[np.float64(317.4597126991805), np.float64(167.34077924622977)]</t>
-  </si>
-  <si>
-    <t>[np.float64(182.86892547550627), np.float64(-118.16507377753283)]</t>
-  </si>
-  <si>
-    <t>[np.float64(481.038463570171), np.float64(-66.95460236887368)]</t>
-  </si>
-  <si>
-    <t>[np.float64(386.15964209963784), np.float64(-531.7288075816158)]</t>
-  </si>
-  <si>
-    <t>[np.float64(557.0652982419105), np.float64(47.339574002598056)]</t>
-  </si>
-  <si>
-    <t>[np.float64(977.5804354001614), np.float64(-142.68885572662242)]</t>
-  </si>
-  <si>
-    <t>[np.float64(744.6037892591884), np.float64(573.6719054799487)]</t>
-  </si>
-  <si>
-    <t>[np.float64(856.3406388638708), np.float64(105.40466181370971)]</t>
-  </si>
-  <si>
-    <t>[np.float64(822.1495252669099), np.float64(419.35819452207386)]</t>
-  </si>
-  <si>
-    <t>[np.float64(913.8583616033329), np.float64(335.5441886249289)]</t>
-  </si>
-  <si>
-    <t>[np.float64(571.050208867908), np.float64(-426.85170493542586)]</t>
-  </si>
-  <si>
-    <t>[np.float64(46.93639730422139), np.float64(-511.7116986308042)]</t>
-  </si>
-  <si>
-    <t>[np.float64(117.53736444629604), np.float64(-432.71746263660714)]</t>
-  </si>
-  <si>
-    <t>[np.float64(84.85790042469165), np.float64(-197.09221386763397)]</t>
-  </si>
-  <si>
-    <t>[np.float64(917.2002870492647), np.float64(488.08072316771745)]</t>
-  </si>
-  <si>
-    <t>[np.float64(649.6992777723827), np.float64(-358.10986876000186)]</t>
-  </si>
-  <si>
-    <t>[np.float64(716.3527253026289), np.float64(-473.5548044615609)]</t>
-  </si>
-  <si>
-    <t>[np.float64(557.936808115316), np.float64(507.87289538173604)]</t>
-  </si>
-  <si>
-    <t>[np.float64(613.984509314424), np.float64(43.39728308519466)]</t>
-  </si>
-  <si>
-    <t>[np.float64(214.1805409815588), np.float64(-448.31823188155107)]</t>
-  </si>
-  <si>
-    <t>[np.float64(4.759638121272003), np.float64(-511.40432565081386)]</t>
-  </si>
-  <si>
-    <t>[np.float64(24.093336435723643), np.float64(-539.4793103932062)]</t>
-  </si>
-  <si>
-    <t>[np.float64(493.28364523493775), np.float64(55.37348891096326)]</t>
-  </si>
-  <si>
-    <t>[np.float64(893.6635578680725), np.float64(-439.8951802780548)]</t>
-  </si>
-  <si>
-    <t>[np.float64(219.36585190826742), np.float64(294.85464174317235)]</t>
-  </si>
-  <si>
-    <t>[np.float64(130.99437694194137), np.float64(298.6346193303415)]</t>
-  </si>
-  <si>
-    <t>[np.float64(788.2863356741608), np.float64(-426.3159296870727)]</t>
-  </si>
-  <si>
-    <t>[np.float64(58.75451575036949), np.float64(445.2438534200546)]</t>
-  </si>
-  <si>
-    <t>[np.float64(346.16392696819844), np.float64(267.3611633569968)]</t>
-  </si>
-  <si>
-    <t>[np.float64(433.98104609916743), np.float64(356.7910691291595)]</t>
-  </si>
-  <si>
-    <t>[np.float64(866.617474293325), np.float64(511.8347679656199)]</t>
-  </si>
-  <si>
-    <t>[np.float64(716.9046220085736), np.float64(269.9057128210088)]</t>
-  </si>
-  <si>
-    <t>[np.float64(320.0091869656837), np.float64(354.3586338344569)]</t>
-  </si>
-  <si>
-    <t>[np.float64(430.66504314775455), np.float64(311.2388667886529)]</t>
-  </si>
-  <si>
-    <t>[np.float64(254.0343633703903), np.float64(303.78558280260995)]</t>
-  </si>
-  <si>
-    <t>[np.float64(78.56135757957594), np.float64(144.13275558650184)]</t>
-  </si>
-  <si>
-    <t>[np.float64(950.3682760144609), np.float64(-166.42801715671084)]</t>
-  </si>
-  <si>
-    <t>[np.float64(378.4109273666154), np.float64(183.05540962622763)]</t>
-  </si>
-  <si>
-    <t>[np.float64(957.1505180847495), np.float64(572.3449942231571)]</t>
-  </si>
-  <si>
-    <t>[np.float64(981.0220606403262), np.float64(57.61283800296337)]</t>
-  </si>
-  <si>
-    <t>[np.float64(297.99946069199245), np.float64(-343.4170250281509)]</t>
-  </si>
-  <si>
-    <t>[np.float64(47.68805598328241), np.float64(-313.0686133069837)]</t>
-  </si>
-  <si>
-    <t>[np.float64(60.78272830703047), np.float64(532.6898764760708)]</t>
-  </si>
-  <si>
-    <t>[np.float64(495.15956680546714), np.float64(-52.263311224070776)]</t>
-  </si>
-  <si>
-    <t>[np.float64(559.4921491772486), np.float64(-568.789753430986)]</t>
-  </si>
-  <si>
-    <t>[np.float64(442.1446299043261), np.float64(583.5144829339613)]</t>
-  </si>
-  <si>
-    <t>[np.float64(738.5073264714154), np.float64(21.99680810410348)]</t>
-  </si>
-  <si>
-    <t>[np.float64(583.4168723362135), np.float64(147.25303785109747)]</t>
-  </si>
-  <si>
-    <t>[np.float64(607.2495815798824), np.float64(187.08931479054854)]</t>
-  </si>
-  <si>
-    <t>[np.float64(823.4393323091634), np.float64(-421.33513937134103)]</t>
-  </si>
-  <si>
-    <t>[np.float64(537.6718162981259), np.float64(-440.3280505520306)]</t>
-  </si>
-  <si>
-    <t>[np.float64(350.26137965730817), np.float64(-196.6179258282637)]</t>
-  </si>
-  <si>
-    <t>[np.float64(612.8486446751932), np.float64(567.554424862087)]</t>
-  </si>
-  <si>
-    <t>[np.float64(513.6265794984878), np.float64(406.8377206007317)]</t>
-  </si>
-  <si>
-    <t>[np.float64(40.248404693390086), np.float64(201.62177559044903)]</t>
-  </si>
-  <si>
-    <t>[np.float64(132.25883091969925), np.float64(242.7313140718246)]</t>
-  </si>
-  <si>
-    <t>[np.float64(63.810373613860214), np.float64(-165.8796487252523)]</t>
-  </si>
-  <si>
-    <t>[np.float64(309.91977374744215), np.float64(76.27782072150819)]</t>
-  </si>
-  <si>
-    <t>[np.float64(863.7710971857762), np.float64(114.20671420928568)]</t>
-  </si>
-  <si>
-    <t>[np.float64(168.1262389706626), np.float64(59.920698053985916)]</t>
-  </si>
-  <si>
-    <t>[np.float64(525.1179298493082), np.float64(473.34495778055157)]</t>
-  </si>
-  <si>
-    <t>[np.float64(611.474122461386), np.float64(-296.04279885115926)]</t>
-  </si>
-  <si>
-    <t>[np.float64(807.5322072746287), np.float64(-502.6112308790086)]</t>
-  </si>
-  <si>
-    <t>[np.float64(334.70116157973405), np.float64(343.8712882126714)]</t>
-  </si>
-  <si>
-    <t>[np.float64(915.6949105857718), np.float64(-181.5983386372518)]</t>
-  </si>
-  <si>
-    <t>[np.float64(697.7297899747772), np.float64(479.0079795725651)]</t>
-  </si>
-  <si>
-    <t>[np.float64(936.4549978610563), np.float64(77.62878269781811)]</t>
-  </si>
-  <si>
-    <t>[np.float64(336.82031836300763), np.float64(194.61776745863585)]</t>
-  </si>
-  <si>
-    <t>[np.float64(773.2938173259321), np.float64(33.58510555489738)]</t>
-  </si>
-  <si>
-    <t>[np.float64(390.73951551409914), np.float64(-162.80962967749053)]</t>
-  </si>
-  <si>
-    <t>[np.float64(253.53240818520538), np.float64(352.53506564038037)]</t>
-  </si>
-  <si>
-    <t>[np.float64(263.11782360807155), np.float64(-525.8036958340481)]</t>
-  </si>
-  <si>
-    <t>[np.float64(828.8240279235683), np.float64(-362.3249758944347)]</t>
-  </si>
-  <si>
-    <t>[np.float64(840.3451812577624), np.float64(8.326652666975178)]</t>
-  </si>
-  <si>
-    <t>[np.float64(387.6406340842169), np.float64(396.81733740529955)]</t>
-  </si>
-  <si>
-    <t>[np.float64(508.6693236452333), np.float64(273.7859904158852)]</t>
-  </si>
-  <si>
-    <t>[np.float64(633.7743632647195), np.float64(-268.76490118896027)]</t>
-  </si>
-  <si>
-    <t>[np.float64(431.3805578477087), np.float64(-54.309849500032556)]</t>
-  </si>
-  <si>
-    <t>[np.float64(897.3547086529918), np.float64(-401.66350023090297)]</t>
-  </si>
-  <si>
-    <t>[np.float64(964.1367260283744), np.float64(-186.57050767656682)]</t>
-  </si>
-  <si>
-    <t>[np.float64(295.3317592111401), np.float64(99.69315254997423)]</t>
-  </si>
-  <si>
-    <t>[np.float64(538.644476741743), np.float64(-407.1750895790374)]</t>
-  </si>
-  <si>
-    <t>[np.float64(745.7627733783443), np.float64(-385.48710583360787)]</t>
-  </si>
-  <si>
-    <t>[np.float64(749.6329709141263), np.float64(-193.48791536120393)]</t>
-  </si>
-  <si>
-    <t>[np.float64(737.0240194042037), np.float64(583.1345503588893)]</t>
-  </si>
-  <si>
-    <t>[np.float64(378.67260654553024), np.float64(-87.61401437173026)]</t>
-  </si>
-  <si>
-    <t>[np.float64(862.7825914808706), np.float64(247.79481920346961)]</t>
-  </si>
-  <si>
-    <t>[np.float64(574.749513835702), np.float64(-384.24921327909385)]</t>
-  </si>
-  <si>
-    <t>[np.float64(867.2969339287042), np.float64(-250.503976326501)]</t>
-  </si>
-  <si>
-    <t>[np.float64(633.6214606586684), np.float64(472.209491327259)]</t>
-  </si>
-  <si>
-    <t>[np.float64(252.42772379105816), np.float64(-431.28059656937467)]</t>
-  </si>
-  <si>
-    <t>[np.float64(929.5609358382758), np.float64(-72.10088552131288)]</t>
-  </si>
-  <si>
-    <t>[np.float64(843.4130774939538), np.float64(-581.6678559943642)]</t>
-  </si>
-  <si>
-    <t>[np.float64(766.3040702919949), np.float64(-553.5481427516987)]</t>
-  </si>
-  <si>
-    <t>[np.float64(965.1686856136821), np.float64(324.59671252171484)]</t>
-  </si>
-  <si>
-    <t>[np.float64(363.61172816700014), np.float64(299.8546213025743)]</t>
-  </si>
-  <si>
-    <t>[np.float64(928.0718335912943), np.float64(-395.52595165985247)]</t>
-  </si>
-  <si>
-    <t>[np.float64(754.7567964783997), np.float64(-83.02643501984289)]</t>
-  </si>
-  <si>
-    <t>[np.float64(571.8283964057758), np.float64(-452.55634197110646)]</t>
-  </si>
-  <si>
-    <t>[np.float64(530.8113512641937), np.float64(-390.9073348092618)]</t>
-  </si>
-  <si>
-    <t>[np.float64(138.57336125678677), np.float64(312.38706034503184)]</t>
-  </si>
-  <si>
-    <t>[np.float64(479.15288351545405), np.float64(-194.59098357608798)]</t>
-  </si>
-  <si>
-    <t>[np.float64(293.14153166857113), np.float64(70.42900733809711)]</t>
-  </si>
-  <si>
-    <t>[np.float64(397.17268335995357), np.float64(-43.93438002750645)]</t>
-  </si>
-  <si>
-    <t>[np.float64(580.8662969103565), np.float64(-152.587409204155)]</t>
-  </si>
-  <si>
-    <t>[np.float64(122.8970235190624), np.float64(136.1761934838553)]</t>
-  </si>
-  <si>
-    <t>[np.float64(768.8796919778038), np.float64(-571.4213855628859)]</t>
-  </si>
-  <si>
-    <t>[np.float64(282.6025480633764), np.float64(499.230066878318)]</t>
-  </si>
-  <si>
-    <t>[np.float64(30.12884121376136), np.float64(-455.0332895635156)]</t>
-  </si>
-  <si>
-    <t>[np.float64(28.483058661174066), np.float64(178.4741194350063)]</t>
-  </si>
-  <si>
-    <t>[np.float64(177.86389184480544), np.float64(224.96620721298677)]</t>
-  </si>
-  <si>
-    <t>[np.float64(910.8000886488223), np.float64(488.1076022950647)]</t>
-  </si>
-  <si>
-    <t>[np.float64(936.9649621684769), np.float64(-485.1713286019433)]</t>
-  </si>
-  <si>
-    <t>[np.float64(57.632675077133435), np.float64(49.6103333404119)]</t>
-  </si>
-  <si>
-    <t>[np.float64(584.8722772356675), np.float64(356.76262745938084)]</t>
-  </si>
-  <si>
-    <t>[np.float64(648.9001692139309), np.float64(-382.1024040405243)]</t>
-  </si>
-  <si>
-    <t>[np.float64(996.654880515963), np.float64(131.94297375950225)]</t>
-  </si>
-  <si>
-    <t>[np.float64(82.04680274785248), np.float64(-333.7559129659588)]</t>
-  </si>
-  <si>
-    <t>[np.float64(39.40966536003187), np.float64(-485.1795412092879)]</t>
-  </si>
-  <si>
-    <t>[np.float64(845.092462574819), np.float64(-437.01832658567923)]</t>
-  </si>
-  <si>
-    <t>[np.float64(696.686545182387), np.float64(-400.6769283294599)]</t>
-  </si>
-  <si>
-    <t>[np.float64(785.6816595561789), np.float64(-169.43383442081267)]</t>
-  </si>
-  <si>
-    <t>[np.float64(747.0161966735294), np.float64(469.2714074978287)]</t>
-  </si>
-  <si>
-    <t>[np.float64(42.353394435224786), np.float64(192.7445665523161)]</t>
-  </si>
-  <si>
-    <t>[np.float64(247.46100742384337), np.float64(519.4611752621156)]</t>
-  </si>
-  <si>
-    <t>[np.float64(491.09679706762245), np.float64(244.39471256823242)]</t>
-  </si>
-  <si>
-    <t>[np.float64(968.9071796511311), np.float64(255.0991090585146)]</t>
-  </si>
-  <si>
-    <t>[np.float64(424.48407807534625), np.float64(-439.7853395769524)]</t>
-  </si>
-  <si>
-    <t>[np.float64(205.15977326557123), np.float64(281.7596723417415)]</t>
-  </si>
-  <si>
-    <t>[np.float64(925.380046451214), np.float64(185.7212946042648)]</t>
-  </si>
-  <si>
-    <t>[np.float64(478.3322540381986), np.float64(232.0134618209587)]</t>
-  </si>
-  <si>
-    <t>[np.float64(263.5225026742144), np.float64(-264.6414518773276)]</t>
-  </si>
-  <si>
-    <t>[np.float64(626.7575127906117), np.float64(0.7456000995317709)]</t>
-  </si>
-  <si>
-    <t>[np.float64(894.941821338751), np.float64(513.5982868235033)]</t>
-  </si>
-  <si>
-    <t>[np.float64(917.5405085203355), np.float64(386.3258900994207)]</t>
-  </si>
-  <si>
-    <t>[np.float64(874.73102873986), np.float64(-260.3854325160427)]</t>
-  </si>
-  <si>
-    <t>[np.float64(8.261405235476914), np.float64(592.2112328391165)]</t>
-  </si>
-  <si>
-    <t>[np.float64(936.657201229372), np.float64(-172.66968757162027)]</t>
-  </si>
-  <si>
-    <t>[np.float64(249.57034597446048), np.float64(64.01975129751588)]</t>
-  </si>
-  <si>
-    <t>[np.float64(719.9575898347119), np.float64(174.0850119403791)]</t>
-  </si>
-  <si>
-    <t>[np.float64(279.2421521779981), np.float64(-394.52582548617147)]</t>
-  </si>
-  <si>
-    <t>[np.float64(547.0021897621975), np.float64(120.71093973818472)]</t>
-  </si>
-  <si>
-    <t>[np.float64(322.05491008485376), np.float64(-175.08236076843014)]</t>
-  </si>
-  <si>
-    <t>[np.float64(569.2750539466535), np.float64(228.77763623069427)]</t>
-  </si>
-  <si>
-    <t>[np.float64(315.92729021975964), np.float64(493.0006093441591)]</t>
-  </si>
-  <si>
-    <t>[np.float64(84.59376408095554), np.float64(-498.7284923774515)]</t>
-  </si>
-  <si>
-    <t>[np.float64(849.2259360134276), np.float64(324.7334741027664)]</t>
-  </si>
-  <si>
-    <t>[np.float64(572.7501639033884), np.float64(331.65451807154056)]</t>
-  </si>
-  <si>
-    <t>[np.float64(981.8319895027951), np.float64(453.93086818187476)]</t>
-  </si>
-  <si>
-    <t>[np.float64(234.45748127441578), np.float64(-338.04561485411506)]</t>
-  </si>
-  <si>
-    <t>[np.float64(816.1441951472435), np.float64(-332.0367855069687)]</t>
-  </si>
-  <si>
-    <t>[np.float64(712.775480006518), np.float64(-391.2164160885041)]</t>
-  </si>
-  <si>
-    <t>[np.float64(45.374361154842724), np.float64(-431.614996269878)]</t>
-  </si>
-  <si>
-    <t>[np.float64(331.0246895324416), np.float64(582.9532779844149)]</t>
-  </si>
-  <si>
-    <t>[np.float64(379.00088456006256), np.float64(-298.37424381050005)]</t>
-  </si>
-  <si>
-    <t>[np.float64(681.0210947336344), np.float64(512.4622095147572)]</t>
-  </si>
-  <si>
-    <t>[np.float64(196.75631474455923), np.float64(483.89657514646206)]</t>
-  </si>
-  <si>
-    <t>[np.float64(502.1412071501893), np.float64(-215.00191347298517)]</t>
-  </si>
-  <si>
-    <t>[np.float64(124.9131590731245), np.float64(41.98928815000488)]</t>
-  </si>
-  <si>
-    <t>[np.float64(142.47964216073981), np.float64(121.0725778820422)]</t>
-  </si>
-  <si>
-    <t>[np.float64(44.48649900226931), np.float64(-126.94785184380356)]</t>
-  </si>
-  <si>
-    <t>[np.float64(30.35585888553516), np.float64(242.75809825037425)]</t>
-  </si>
-  <si>
-    <t>[np.float64(496.87884496660774), np.float64(338.6773271981068)]</t>
-  </si>
-  <si>
-    <t>[np.float64(518.661673546288), np.float64(570.6123896907504)]</t>
-  </si>
-  <si>
-    <t>[np.float64(484.80493470111674), np.float64(-148.13668668212227)]</t>
-  </si>
-  <si>
-    <t>[np.float64(842.0109953731011), np.float64(-227.58699098250713)]</t>
-  </si>
-  <si>
-    <t>[np.float64(43.70235957607016), np.float64(-416.68663275962507)]</t>
-  </si>
-  <si>
-    <t>[np.float64(294.12577926924854), np.float64(396.4549665066414)]</t>
-  </si>
-  <si>
-    <t>[np.float64(627.4810777843854), np.float64(-66.40624602711443)]</t>
-  </si>
-  <si>
-    <t>[np.float64(264.6690144211168), np.float64(328.6026827976474)]</t>
-  </si>
-  <si>
-    <t>[np.float64(677.8349651374821), np.float64(548.876089667805)]</t>
-  </si>
-  <si>
-    <t>[np.float64(975.5985365881643), np.float64(468.0962372063202)]</t>
-  </si>
-  <si>
-    <t>[np.float64(799.9000326162455), np.float64(-217.23746711491026)]</t>
-  </si>
-  <si>
-    <t>[np.float64(910.856209142404), np.float64(165.61963466913835)]</t>
-  </si>
-  <si>
-    <t>[np.float64(532.7534679764804), np.float64(-414.493882683066)]</t>
-  </si>
-  <si>
-    <t>[np.float64(33.89268926793398), np.float64(-108.3143402881164)]</t>
-  </si>
-  <si>
-    <t>[np.float64(420.7551086734434), np.float64(-531.829409037883)]</t>
-  </si>
-  <si>
-    <t>[np.float64(319.10235432790034), np.float64(317.4395096137911)]</t>
-  </si>
-  <si>
-    <t>[np.float64(502.4126883429103), np.float64(236.69745909268158)]</t>
-  </si>
-  <si>
-    <t>[np.float64(14.317636454983074), np.float64(-379.0041009228971)]</t>
-  </si>
-  <si>
-    <t>[np.float64(899.1662659581934), np.float64(-361.92591077908935)]</t>
-  </si>
-  <si>
-    <t>[np.float64(300.1450063417047), np.float64(-358.65869203513165)]</t>
-  </si>
-  <si>
-    <t>[np.float64(351.7984113187201), np.float64(-361.2564610456514)]</t>
-  </si>
-  <si>
-    <t>[np.float64(947.3472455571233), np.float64(397.0844702525627)]</t>
-  </si>
-  <si>
-    <t>[np.float64(539.0887632262545), np.float64(-424.7746323156251)]</t>
-  </si>
-  <si>
-    <t>[np.float64(717.4326691412145), np.float64(398.305953389253)]</t>
-  </si>
-  <si>
-    <t>[np.float64(853.4068122931574), np.float64(240.09142145928206)]</t>
-  </si>
-  <si>
-    <t>[np.float64(654.7500803060423), np.float64(521.3380920306663)]</t>
-  </si>
-  <si>
-    <t>[np.float64(867.6390052236992), np.float64(578.0598444035088)]</t>
-  </si>
-  <si>
-    <t>[np.float64(226.36835354392792), np.float64(-279.5652396045297)]</t>
-  </si>
-  <si>
-    <t>[np.float64(966.8390865110497), np.float64(-465.18202877898995)]</t>
-  </si>
-  <si>
-    <t>[np.float64(572.7364030730431), np.float64(418.9190654319865)]</t>
-  </si>
-  <si>
-    <t>[np.float64(982.6513857769495), np.float64(-110.09647318746516)]</t>
-  </si>
-  <si>
-    <t>[np.float64(623.1458836702649), np.float64(447.86946826122085)]</t>
-  </si>
-  <si>
-    <t>[np.float64(178.48184017250733), np.float64(356.16449377912)]</t>
-  </si>
-  <si>
-    <t>[np.float64(320.83157398210284), np.float64(463.876577301261)]</t>
-  </si>
-  <si>
-    <t>[np.float64(998.8738438767477), np.float64(-274.5875538252716)]</t>
-  </si>
-  <si>
-    <t>[np.float64(982.7063982039671), np.float64(161.91031249074365)]</t>
-  </si>
-  <si>
-    <t>[np.float64(40.93790009392628), np.float64(-135.19413763191397)]</t>
-  </si>
-  <si>
-    <t>[np.float64(790.9894852042146), np.float64(543.4555750245302)]</t>
-  </si>
-  <si>
-    <t>[np.float64(804.6805868156841), np.float64(-512.629880828662)]</t>
-  </si>
-  <si>
-    <t>[np.float64(337.5829854283073), np.float64(-441.8827812747958)]</t>
-  </si>
-  <si>
-    <t>[np.float64(450.1989150395298), np.float64(-509.1109079194064)]</t>
-  </si>
-  <si>
-    <t>[np.float64(576.9947062956725), np.float64(-149.12733765941925)]</t>
-  </si>
-  <si>
-    <t>[np.float64(462.25302732268744), np.float64(-191.830001607658)]</t>
-  </si>
-  <si>
-    <t>[np.float64(34.35096471696486), np.float64(-393.00152802183345)]</t>
-  </si>
-  <si>
-    <t>[np.float64(90.60614348329798), np.float64(-502.69379842563706)]</t>
-  </si>
-  <si>
-    <t>[np.float64(688.8839944531295), np.float64(-483.59243996025754)]</t>
-  </si>
-  <si>
-    <t>[np.float64(562.9324625583513), np.float64(-326.47979646863786)]</t>
-  </si>
-  <si>
-    <t>[np.float64(512.3455605242918), np.float64(-483.14806572320754)]</t>
-  </si>
-  <si>
-    <t>[np.float64(498.0008205780082), np.float64(-535.3263526742666)]</t>
-  </si>
-  <si>
-    <t>[np.float64(307.60270252682886), np.float64(-213.47400414434452)]</t>
-  </si>
-  <si>
-    <t>[np.float64(907.074230771901), np.float64(-449.54266179624506)]</t>
-  </si>
-  <si>
-    <t>[np.float64(410.6544569736488), np.float64(254.07740844292812)]</t>
-  </si>
-  <si>
-    <t>[np.float64(920.1933294685118), np.float64(160.11050447858997)]</t>
-  </si>
-  <si>
-    <t>[np.float64(800.4344181987896), np.float64(537.4562091493813)]</t>
-  </si>
-  <si>
-    <t>[np.float64(477.0538814567465), np.float64(248.50428909870425)]</t>
-  </si>
-  <si>
-    <t>[np.float64(203.2416204839721), np.float64(117.0565701742762)]</t>
-  </si>
-  <si>
-    <t>[np.float64(151.0994879071721), np.float64(559.331397704691)]</t>
-  </si>
-  <si>
-    <t>[np.float64(989.0897255259052), np.float64(-297.74383638887804)]</t>
-  </si>
-  <si>
-    <t>[np.float64(326.45888012681223), np.float64(182.05449820425122)]</t>
-  </si>
-  <si>
-    <t>[np.float64(306.50717252878104), np.float64(-204.3855323504094)]</t>
-  </si>
-  <si>
-    <t>[np.float64(304.53044799882576), np.float64(-559.7173622210483)]</t>
-  </si>
-  <si>
-    <t>[np.float64(146.71687798331666), np.float64(457.05148241089023)]</t>
-  </si>
-  <si>
-    <t>[np.float64(951.1558695714625), np.float64(-483.79088681753217)]</t>
-  </si>
-  <si>
-    <t>[np.float64(962.6984231821966), np.float64(-204.90386731168894)]</t>
-  </si>
-  <si>
-    <t>[np.float64(404.97581695225347), np.float64(-385.8958611745604)]</t>
-  </si>
-  <si>
-    <t>[np.float64(200.1937759699527), np.float64(-563.1828283186105)]</t>
-  </si>
-  <si>
-    <t>[np.float64(104.74358524682181), np.float64(421.0448678122805)]</t>
-  </si>
-  <si>
-    <t>[np.float64(322.86637337275715), np.float64(272.06030343518273)]</t>
-  </si>
-  <si>
-    <t>[np.float64(659.8914491430279), np.float64(431.2571600939157)]</t>
-  </si>
-  <si>
-    <t>[np.float64(899.2370218914411), np.float64(332.9737364412565)]</t>
-  </si>
-  <si>
-    <t>[np.float64(603.0167817968608), np.float64(134.74966952863383)]</t>
-  </si>
-  <si>
-    <t>[np.float64(611.5113026257252), np.float64(-368.73730711646203)]</t>
-  </si>
-  <si>
-    <t>[np.float64(196.85314938636444), np.float64(22.069375707727318)]</t>
-  </si>
-  <si>
-    <t>[np.float64(239.91232443110744), np.float64(531.3658604200523)]</t>
-  </si>
-  <si>
-    <t>[np.float64(933.4568350031417), np.float64(290.02493167915566)]</t>
-  </si>
-  <si>
-    <t>[np.float64(936.5889663143829), np.float64(-85.04334852412319)]</t>
-  </si>
-  <si>
-    <t>[np.float64(741.376530076691), np.float64(-410.2417844629391)]</t>
-  </si>
-  <si>
-    <t>[np.float64(644.8538121965473), np.float64(-480.15992869187727)]</t>
-  </si>
-  <si>
-    <t>[np.float64(351.8838625694692), np.float64(-230.68060318358124)]</t>
-  </si>
-  <si>
-    <t>[np.float64(963.8264509231278), np.float64(-526.66273969601)]</t>
-  </si>
-  <si>
-    <t>[np.float64(586.9094950362603), np.float64(79.12218515628547)]</t>
-  </si>
-  <si>
-    <t>[np.float64(722.5856104954469), np.float64(-476.82950944699274)]</t>
-  </si>
-  <si>
-    <t>[np.float64(826.6451124434649), np.float64(-76.43592732502168)]</t>
-  </si>
-  <si>
-    <t>[np.float64(402.5880418331811), np.float64(56.616709150736824)]</t>
-  </si>
-  <si>
-    <t>[np.float64(709.780265401891), np.float64(451.9793719484944)]</t>
-  </si>
-  <si>
-    <t>[np.float64(613.8266656651001), np.float64(-597.8536666912954)]</t>
-  </si>
-  <si>
-    <t>[np.float64(478.23391392430494), np.float64(-241.97406369480404)]</t>
-  </si>
-  <si>
-    <t>[np.float64(488.73426196745794), np.float64(-503.46453212204324)]</t>
-  </si>
-  <si>
-    <t>[np.float64(201.08961312173912), np.float64(175.3313396709882)]</t>
-  </si>
-  <si>
-    <t>[np.float64(716.2453495559314), np.float64(87.97465746565422)]</t>
-  </si>
-  <si>
-    <t>[np.float64(658.0967066602991), np.float64(-129.02198648363282)]</t>
-  </si>
-  <si>
-    <t>[np.float64(166.04324642230438), np.float64(-326.00747939683475)]</t>
-  </si>
-  <si>
-    <t>[np.float64(448.4726316423788), np.float64(470.60476265149487)]</t>
-  </si>
-  <si>
-    <t>[np.float64(533.5174765895531), np.float64(425.7987362970821)]</t>
-  </si>
-  <si>
-    <t>[np.float64(593.7409369907805), np.float64(124.62359096887656)]</t>
-  </si>
-  <si>
-    <t>[np.float64(808.741434699215), np.float64(-345.63436701941566)]</t>
-  </si>
-  <si>
-    <t>[np.float64(111.35573126573573), np.float64(534.7301281302518)]</t>
-  </si>
-  <si>
-    <t>[np.float64(969.9435356660357), np.float64(-278.1668804821279)]</t>
-  </si>
-  <si>
-    <t>[np.float64(181.49689801826253), np.float64(-314.7511985967712)]</t>
-  </si>
-  <si>
-    <t>[np.float64(849.0745197470737), np.float64(218.42635904381427)]</t>
-  </si>
-  <si>
-    <t>[np.float64(174.42737299647115), np.float64(-104.88245809709088)]</t>
-  </si>
-  <si>
-    <t>[np.float64(586.8002454978607), np.float64(293.4784113043994)]</t>
-  </si>
-  <si>
-    <t>[np.float64(35.931987805097876), np.float64(113.50039580224359)]</t>
-  </si>
-  <si>
-    <t>[np.float64(942.0795060936316), np.float64(-137.3291111622666)]</t>
-  </si>
-  <si>
-    <t>[np.float64(108.64385982336266), np.float64(533.0649439964602)]</t>
-  </si>
-  <si>
-    <t>[np.float64(530.698286537769), np.float64(277.2245750880013)]</t>
-  </si>
-  <si>
-    <t>[np.float64(533.7659961571004), np.float64(302.4357051610823)]</t>
-  </si>
-  <si>
-    <t>[np.float64(508.0027106686088), np.float64(544.8992990165987)]</t>
-  </si>
-  <si>
-    <t>[np.float64(901.2143484944819), np.float64(248.192485302794)]</t>
-  </si>
-  <si>
-    <t>[np.float64(332.15187551081846), np.float64(129.313513149939)]</t>
-  </si>
-  <si>
-    <t>[np.float64(427.96956900740923), np.float64(-206.418754417132)]</t>
-  </si>
-  <si>
-    <t>[np.float64(611.8864755002925), np.float64(-295.4512063549722)]</t>
-  </si>
-  <si>
-    <t>[np.float64(914.8000631689704), np.float64(188.1132438205425)]</t>
-  </si>
-  <si>
-    <t>[np.float64(625.7863337298347), np.float64(306.5038811937894)]</t>
-  </si>
-  <si>
-    <t>[np.float64(342.19255780304593), np.float64(452.8894043636992)]</t>
-  </si>
-  <si>
-    <t>[np.float64(940.1457681593367), np.float64(-96.2844229109433)]</t>
-  </si>
-  <si>
-    <t>[np.float64(891.8675645184726), np.float64(285.3722626157712)]</t>
-  </si>
-  <si>
-    <t>[np.float64(96.189275800998), np.float64(-109.16937976792673)]</t>
-  </si>
-  <si>
-    <t>[np.float64(76.05023442400538), np.float64(365.53041502234987)]</t>
-  </si>
-  <si>
-    <t>[np.float64(170.88751819503722), np.float64(-151.67862166494427)]</t>
-  </si>
-  <si>
-    <t>[np.float64(252.530854326108), np.float64(73.98569152106211)]</t>
-  </si>
-  <si>
-    <t>[np.float64(791.0508718380784), np.float64(101.29993454568819)]</t>
-  </si>
-  <si>
-    <t>[np.float64(816.2809355565129), np.float64(274.11846034627297)]</t>
-  </si>
-  <si>
-    <t>[np.float64(798.3562026475576), np.float64(-359.211492022724)]</t>
-  </si>
-  <si>
-    <t>[np.float64(370.55941875808765), np.float64(-500.57001485743365)]</t>
-  </si>
-  <si>
-    <t>[np.float64(126.60044976619167), np.float64(100.66609525043486)]</t>
-  </si>
-  <si>
-    <t>[np.float64(782.0989501977365), np.float64(-437.70292493894203)]</t>
-  </si>
-  <si>
-    <t>[np.float64(536.4831055031565), np.float64(-366.5949704774233)]</t>
-  </si>
-  <si>
-    <t>[np.float64(877.9471062324288), np.float64(-268.0498652960924)]</t>
-  </si>
-  <si>
-    <t>[np.float64(569.852741009405), np.float64(500.5893808811313)]</t>
-  </si>
-  <si>
-    <t>[np.float64(943.2829504742125), np.float64(433.9425875472393)]</t>
-  </si>
-  <si>
-    <t>[np.float64(847.0784382887493), np.float64(24.82749592711923)]</t>
-  </si>
-  <si>
-    <t>[np.float64(817.8273872619123), np.float64(170.2195628281072)]</t>
-  </si>
-  <si>
-    <t>[np.float64(296.402305352436), np.float64(200.44464369800153)]</t>
-  </si>
-  <si>
-    <t>[np.float64(21.68615295526033), np.float64(349.11199775601995)]</t>
-  </si>
-  <si>
-    <t>[np.float64(43.441864801957664), np.float64(-392.58719773610653)]</t>
-  </si>
-  <si>
-    <t>[np.float64(298.7421287969515), np.float64(-237.0002012600646)]</t>
-  </si>
-  <si>
-    <t>[np.float64(497.95493059376463), np.float64(-367.3122345973817)]</t>
-  </si>
-  <si>
-    <t>[np.float64(55.77924112417077), np.float64(-556.3667747759721)]</t>
-  </si>
-  <si>
-    <t>[np.float64(641.1069193795714), np.float64(-131.61397525668315)]</t>
-  </si>
-  <si>
-    <t>[np.float64(828.4414531751199), np.float64(-210.08880107780618)]</t>
-  </si>
-  <si>
-    <t>[np.float64(859.6971455165781), np.float64(-126.96413718810396)]</t>
-  </si>
-  <si>
-    <t>[np.float64(336.3973154071993), np.float64(412.922899594614)]</t>
-  </si>
-  <si>
-    <t>[np.float64(638.3359813432866), np.float64(286.00861162979174)]</t>
-  </si>
-  <si>
-    <t>[np.float64(692.2653963481083), np.float64(-208.02638371847968)]</t>
-  </si>
-  <si>
-    <t>[np.float64(280.33971662266066), np.float64(-127.99761698906224)]</t>
-  </si>
-  <si>
-    <t>[np.float64(704.1375298263495), np.float64(542.7045975595609)]</t>
-  </si>
-  <si>
-    <t>[np.float64(966.2462264023037), np.float64(-184.43708295036316)]</t>
-  </si>
-  <si>
-    <t>[np.float64(603.9706960878783), np.float64(65.1535656703071)]</t>
-  </si>
-  <si>
-    <t>[np.float64(898.3965205333124), np.float64(112.90206175500884)]</t>
-  </si>
-  <si>
-    <t>[np.float64(704.5540711256614), np.float64(-239.42904307194556)]</t>
-  </si>
-  <si>
-    <t>[np.float64(788.9008711683908), np.float64(-212.2954804733418)]</t>
-  </si>
-  <si>
-    <t>[np.float64(596.1516010626348), np.float64(-571.4621772213873)]</t>
-  </si>
-  <si>
-    <t>[np.float64(98.32661761997397), np.float64(-162.81028098629275)]</t>
-  </si>
-  <si>
-    <t>[np.float64(998.4792616085754), np.float64(-578.3372508190316)]</t>
-  </si>
-  <si>
-    <t>[np.float64(254.51330777884007), np.float64(-512.7482609315745)]</t>
-  </si>
-  <si>
-    <t>[np.float64(803.0858591114865), np.float64(317.91807692075236)]</t>
-  </si>
-  <si>
-    <t>[np.float64(162.50381210066323), np.float64(176.81677772070202)]</t>
-  </si>
-  <si>
-    <t>[np.float64(501.27168296876556), np.float64(-119.99877951551781)]</t>
-  </si>
-  <si>
-    <t>[np.float64(71.03242887551143), np.float64(233.80693092042577)]</t>
-  </si>
-  <si>
-    <t>[np.float64(402.2520985133242), np.float64(430.700854908413)]</t>
-  </si>
-  <si>
-    <t>[np.float64(267.18947403598594), np.float64(576.3690602760373)]</t>
-  </si>
-  <si>
-    <t>[np.float64(582.2811524333684), np.float64(-416.5782010197031)]</t>
-  </si>
-  <si>
-    <t>[np.float64(584.4711371020022), np.float64(-198.04130177708123)]</t>
-  </si>
-  <si>
-    <t>[np.float64(159.62115242218022), np.float64(-10.733275692216239)]</t>
-  </si>
-  <si>
-    <t>[np.float64(446.81958712867566), np.float64(5.577168225637479)]</t>
-  </si>
-  <si>
-    <t>[np.float64(982.3935616717356), np.float64(184.77741485313516)]</t>
-  </si>
-  <si>
-    <t>[np.float64(820.9910032359346), np.float64(-520.5839275854454)]</t>
-  </si>
-  <si>
-    <t>[np.float64(580.6571413499377), np.float64(350.89211797978544)]</t>
-  </si>
-  <si>
-    <t>[np.float64(925.1622374803575), np.float64(364.24343573065516)]</t>
-  </si>
-  <si>
-    <t>[np.float64(353.40733326466477), np.float64(-182.0881001675903)]</t>
-  </si>
-  <si>
-    <t>[np.float64(713.3899551472188), np.float64(263.9937949914208)]</t>
-  </si>
-  <si>
-    <t>[np.float64(469.7734532691998), np.float64(96.12934852622516)]</t>
-  </si>
-  <si>
-    <t>[np.float64(485.26499495325805), np.float64(-290.07510115022006)]</t>
-  </si>
-  <si>
-    <t>[np.float64(923.7326488278245), np.float64(-315.24362638385844)]</t>
-  </si>
-  <si>
-    <t>[np.float64(237.53886809625692), np.float64(474.1095961289807)]</t>
-  </si>
-  <si>
-    <t>[np.float64(512.4309503758404), np.float64(-424.64619162912925)]</t>
-  </si>
-  <si>
-    <t>[np.float64(777.9240700362375), np.float64(-372.33040798481693)]</t>
-  </si>
-  <si>
-    <t>[np.float64(518.9721375148439), np.float64(-301.60186670829773)]</t>
-  </si>
-  <si>
-    <t>[np.float64(502.7208067428324), np.float64(55.54906813759976)]</t>
-  </si>
-  <si>
-    <t>[np.float64(243.65425562443787), np.float64(-113.68056727115936)]</t>
-  </si>
-  <si>
-    <t>[np.float64(765.0920187051164), np.float64(-176.89771315681116)]</t>
-  </si>
-  <si>
-    <t>[np.float64(535.3262884882529), np.float64(170.88536519028855)]</t>
-  </si>
-  <si>
-    <t>[np.float64(182.57157798328427), np.float64(-485.320827080758)]</t>
-  </si>
-  <si>
-    <t>[np.float64(356.5273418436831), np.float64(-267.67108835869533)]</t>
-  </si>
-  <si>
-    <t>[np.float64(865.995230559085), np.float64(459.28544791076047)]</t>
-  </si>
-  <si>
-    <t>[np.float64(272.2300343185209), np.float64(-215.19790528973795)]</t>
-  </si>
-  <si>
-    <t>[np.float64(629.137379469192), np.float64(-561.1113619569007)]</t>
-  </si>
-  <si>
-    <t>[np.float64(190.6582924547996), np.float64(-427.29702802844736)]</t>
-  </si>
-  <si>
-    <t>[np.float64(272.97717467548676), np.float64(253.63345520256553)]</t>
-  </si>
-  <si>
-    <t>[np.float64(132.76466398434295), np.float64(598.4109561371972)]</t>
-  </si>
-  <si>
-    <t>[np.float64(583.832994212183), np.float64(482.3899908493422)]</t>
-  </si>
-  <si>
-    <t>[np.float64(9.184116210422367), np.float64(588.8126883556358)]</t>
-  </si>
-  <si>
-    <t>[np.float64(45.95209347724838), np.float64(297.6418400990468)]</t>
-  </si>
-  <si>
-    <t>[np.float64(511.1080092551473), np.float64(231.3058901076497)]</t>
-  </si>
-  <si>
-    <t>[np.float64(129.63438767172363), np.float64(206.61267202281658)]</t>
-  </si>
-  <si>
-    <t>[np.float64(793.5200066661343), np.float64(558.0132026754634)]</t>
-  </si>
-  <si>
-    <t>[np.float64(95.10010141402935), np.float64(-218.04211184953283)]</t>
-  </si>
-  <si>
-    <t>[np.float64(557.0891169316166), np.float64(15.83416712791768)]</t>
-  </si>
-  <si>
-    <t>[np.float64(784.7777524341774), np.float64(555.7517462010171)]</t>
-  </si>
-  <si>
-    <t>[np.float64(502.9761854832259), np.float64(297.0389091693063)]</t>
-  </si>
-  <si>
-    <t>[np.float64(808.3878463216786), np.float64(-173.40926888241887)]</t>
-  </si>
-  <si>
-    <t>[np.float64(641.8301750977375), np.float64(-259.40728674502117)]</t>
-  </si>
-  <si>
-    <t>[np.float64(935.7908790019404), np.float64(-200.44685972874453)]</t>
-  </si>
-  <si>
-    <t>[np.float64(932.224749789966), np.float64(327.64618309153)]</t>
-  </si>
-  <si>
-    <t>[np.float64(999.7899435291852), np.float64(-186.20731783538952)]</t>
-  </si>
-  <si>
-    <t>[np.float64(420.40592869236224), np.float64(-558.7995380133956)]</t>
-  </si>
-  <si>
-    <t>[np.float64(267.27467142669883), np.float64(313.86036631667264)]</t>
-  </si>
-  <si>
-    <t>[np.float64(392.0046643403765), np.float64(318.92667802220876)]</t>
-  </si>
-  <si>
-    <t>[np.float64(407.40423483071663), np.float64(591.3827204155286)]</t>
-  </si>
-  <si>
-    <t>[np.float64(179.31883515299808), np.float64(-517.1457788219616)]</t>
-  </si>
-  <si>
-    <t>[np.float64(76.46839069906486), np.float64(-449.0693678812024)]</t>
-  </si>
-  <si>
-    <t>[np.float64(109.69083795152446), np.float64(361.9657314963332)]</t>
-  </si>
-  <si>
-    <t>[np.float64(751.4305585486169), np.float64(556.7561518436012)]</t>
-  </si>
-  <si>
-    <t>[np.float64(841.3771100792022), np.float64(9.407327842836821)]</t>
-  </si>
-  <si>
-    <t>[np.float64(699.4856443639372), np.float64(279.5273585724392)]</t>
-  </si>
-  <si>
-    <t>[np.float64(671.6162785715434), np.float64(-488.19865428283754)]</t>
-  </si>
-  <si>
-    <t>[np.float64(652.2870262808342), np.float64(-260.71229472688117)]</t>
-  </si>
-  <si>
-    <t>[np.float64(660.0420920559899), np.float64(-392.29250355318464)]</t>
-  </si>
-  <si>
-    <t>[np.float64(545.3020421639761), np.float64(-486.9976765423691)]</t>
-  </si>
-  <si>
-    <t>[np.float64(814.7070375101584), np.float64(-587.0513043477254)]</t>
-  </si>
-  <si>
-    <t>[np.float64(22.88253428920928), np.float64(-526.1410776318787)]</t>
-  </si>
-  <si>
-    <t>[np.float64(265.7470344006765), np.float64(311.6916741676009)]</t>
-  </si>
-  <si>
-    <t>[np.float64(798.4575105507711), np.float64(76.74917727670856)]</t>
-  </si>
-  <si>
-    <t>[np.float64(187.9010862984941), np.float64(-593.967917229921)]</t>
-  </si>
-  <si>
-    <t>[np.float64(136.2982766492471), np.float64(-406.3309880977389)]</t>
-  </si>
-  <si>
-    <t>[np.float64(777.0865869382196), np.float64(130.7452048399108)]</t>
-  </si>
-  <si>
-    <t>[np.float64(644.5354351668519), np.float64(67.56488665646827)]</t>
-  </si>
-  <si>
-    <t>[np.float64(180.99701528992952), np.float64(-186.16413850899056)]</t>
-  </si>
-  <si>
-    <t>[np.float64(552.106721440518), np.float64(-141.84317831284778)]</t>
-  </si>
-  <si>
-    <t>[np.float64(204.69296299743178), np.float64(529.0501404612746)]</t>
-  </si>
-  <si>
-    <t>[np.float64(493.2739948529645), np.float64(-490.70234886892445)]</t>
-  </si>
-  <si>
-    <t>[np.float64(85.10893111850105), np.float64(-97.24276203720558)]</t>
-  </si>
-  <si>
-    <t>[np.float64(361.9787320354286), np.float64(0.8275469895820606)]</t>
-  </si>
-  <si>
-    <t>[np.float64(220.65824734064444), np.float64(442.59148916543063)]</t>
-  </si>
-  <si>
-    <t>[np.float64(921.3245123127954), np.float64(-260.88832001930075)]</t>
-  </si>
-  <si>
-    <t>[np.float64(69.76085157343704), np.float64(480.3205378740786)]</t>
-  </si>
-  <si>
-    <t>[np.float64(646.6878314614036), np.float64(-79.79155694817996)]</t>
-  </si>
-  <si>
-    <t>[np.float64(946.3923160700576), np.float64(574.4804429936557)]</t>
-  </si>
-  <si>
-    <t>[np.float64(320.4010525597273), np.float64(-394.7855321376944)]</t>
-  </si>
-  <si>
-    <t>[np.float64(317.6390686620776), np.float64(-310.1094097763987)]</t>
-  </si>
-  <si>
-    <t>[np.float64(523.6592039286477), np.float64(-569.8522063094274)]</t>
-  </si>
-  <si>
-    <t>[np.float64(173.7561066082498), np.float64(139.6099258053547)]</t>
-  </si>
-  <si>
-    <t>[np.float64(665.8629255435021), np.float64(512.4705683355783)]</t>
-  </si>
-  <si>
-    <t>[np.float64(149.1239370898324), np.float64(-355.9576588715415)]</t>
-  </si>
-  <si>
-    <t>[np.float64(45.7826215984285), np.float64(-310.631673947013)]</t>
-  </si>
-  <si>
-    <t>[np.float64(979.4273607436921), np.float64(-213.70999256704863)]</t>
-  </si>
-  <si>
-    <t>[np.float64(249.27855722103988), np.float64(255.22001406810045)]</t>
-  </si>
-  <si>
-    <t>[np.float64(617.8584317367563), np.float64(303.7155454706947)]</t>
-  </si>
-  <si>
-    <t>[np.float64(220.20246411109125), np.float64(86.03623329696916)]</t>
-  </si>
-  <si>
-    <t>[np.float64(656.1916513185673), np.float64(143.7319090120368)]</t>
-  </si>
-  <si>
-    <t>[np.float64(201.7206226366226), np.float64(-596.9629054371782)]</t>
-  </si>
-  <si>
-    <t>[np.float64(327.33196991784655), np.float64(-588.0289251232031)]</t>
-  </si>
-  <si>
-    <t>[np.float64(895.8363751481418), np.float64(-142.9691890811044)]</t>
-  </si>
-  <si>
-    <t>[np.float64(876.2968670453945), np.float64(555.8212535249661)]</t>
-  </si>
-  <si>
-    <t>[np.float64(919.3414025075214), np.float64(-298.29087205267274)]</t>
-  </si>
-  <si>
-    <t>[np.float64(27.450767176823156), np.float64(486.9593919446495)]</t>
-  </si>
-  <si>
-    <t>[np.float64(601.0924868007208), np.float64(428.7530995704176)]</t>
-  </si>
-  <si>
-    <t>[np.float64(230.27127151427595), np.float64(206.3665791634827)]</t>
-  </si>
-  <si>
-    <t>[np.float64(283.56032718175607), np.float64(-496.54957548496196)]</t>
-  </si>
-  <si>
-    <t>[np.float64(929.1765369979183), np.float64(-515.4819504991847)]</t>
-  </si>
-  <si>
-    <t>[np.float64(551.0390578112343), np.float64(365.74181365439904)]</t>
-  </si>
-  <si>
-    <t>[np.float64(574.8733750535367), np.float64(-526.8983984383176)]</t>
-  </si>
-  <si>
-    <t>[np.float64(709.4341230425114), np.float64(-396.0725038126143)]</t>
-  </si>
-  <si>
-    <t>[np.float64(178.94513513190768), np.float64(126.83577031777577)]</t>
-  </si>
-  <si>
-    <t>[np.float64(409.39760449207785), np.float64(-138.44174617254623)]</t>
-  </si>
-  <si>
-    <t>[np.float64(180.34452811191903), np.float64(478.5334190172987)]</t>
-  </si>
-  <si>
-    <t>[np.float64(987.18826726983), np.float64(90.34380819412797)]</t>
-  </si>
-  <si>
-    <t>[np.float64(495.6513696688164), np.float64(165.04694818170276)]</t>
-  </si>
-  <si>
-    <t>[np.float64(923.2886791863842), np.float64(527.9178780524398)]</t>
-  </si>
-  <si>
-    <t>[np.float64(97.5600449449845), np.float64(56.80430302962566)]</t>
-  </si>
-  <si>
-    <t>[np.float64(696.4065784355374), np.float64(75.63015034552393)]</t>
-  </si>
-  <si>
-    <t>[np.float64(520.2826420304926), np.float64(342.48252345823903)]</t>
-  </si>
-  <si>
-    <t>[np.float64(494.63972341005837), np.float64(-335.183021068504)]</t>
-  </si>
-  <si>
-    <t>[np.float64(810.6431855826607), np.float64(-457.18661924526964)]</t>
-  </si>
-  <si>
-    <t>[np.float64(402.5037538828762), np.float64(-360.69825457869234)]</t>
-  </si>
-  <si>
-    <t>[np.float64(416.3879676753839), np.float64(-106.143082860952)]</t>
-  </si>
-  <si>
-    <t>[np.float64(937.8543063638692), np.float64(-1.9062569438085575)]</t>
-  </si>
-  <si>
-    <t>[np.float64(120.55692232389926), np.float64(-167.02841700867054)]</t>
-  </si>
-  <si>
-    <t>[np.float64(793.5257376942358), np.float64(508.3568180996567)]</t>
-  </si>
-  <si>
-    <t>[np.float64(7.583500413738897), np.float64(-126.18058856626487)]</t>
-  </si>
-  <si>
-    <t>[np.float64(714.0103132710052), np.float64(123.34155128470593)]</t>
-  </si>
-  <si>
-    <t>[np.float64(11.523974430708627), np.float64(138.70542485402314)]</t>
-  </si>
-  <si>
-    <t>[np.float64(307.18673527240094), np.float64(581.05788814369)]</t>
-  </si>
-  <si>
-    <t>[np.float64(548.255019096402), np.float64(373.8090667425997)]</t>
-  </si>
-  <si>
-    <t>[np.float64(425.59945731341077), np.float64(-126.42066040736444)]</t>
-  </si>
-  <si>
-    <t>[np.float64(724.1188584425079), np.float64(-588.0861531506088)]</t>
-  </si>
-  <si>
-    <t>[np.float64(541.9027140567872), np.float64(-109.16982886826844)]</t>
-  </si>
-  <si>
-    <t>[np.float64(234.63626549265615), np.float64(-363.31605637909877)]</t>
-  </si>
-  <si>
-    <t>[np.float64(964.0917622028444), np.float64(-141.61227399477536)]</t>
-  </si>
-  <si>
-    <t>[np.float64(793.7767724904589), np.float64(-262.37691344373826)]</t>
-  </si>
-  <si>
-    <t>[np.float64(124.10133979700755), np.float64(523.0201165601238)]</t>
-  </si>
-  <si>
-    <t>[np.float64(802.0471934463227), np.float64(435.3311378517442)]</t>
-  </si>
-  <si>
-    <t>[np.float64(156.46470788449184), np.float64(427.7095940961192)]</t>
-  </si>
-  <si>
-    <t>[np.float64(955.2419311223724), np.float64(-489.3738050378877)]</t>
-  </si>
-  <si>
-    <t>[np.float64(193.9589279607803), np.float64(-282.29674297621887)]</t>
-  </si>
-  <si>
-    <t>[np.float64(659.3854686033745), np.float64(383.5902325219729)]</t>
-  </si>
-  <si>
-    <t>[np.float64(501.5790888091598), np.float64(527.7593761092637)]</t>
-  </si>
-  <si>
-    <t>[np.float64(124.92733335979322), np.float64(405.47758417325974)]</t>
-  </si>
-  <si>
-    <t>[np.float64(563.2376932642173), np.float64(454.6139649315812)]</t>
-  </si>
-  <si>
-    <t>[np.float64(335.03770124041364), np.float64(-308.821681464059)]</t>
-  </si>
-  <si>
-    <t>[np.float64(783.5924622696623), np.float64(336.7654430182504)]</t>
-  </si>
-  <si>
-    <t>[np.float64(875.3903000573733), np.float64(-535.8575116353247)]</t>
-  </si>
-  <si>
-    <t>[np.float64(864.7318960069008), np.float64(434.9882007691215)]</t>
-  </si>
-  <si>
-    <t>[np.float64(492.64515297981535), np.float64(366.2059982003134)]</t>
-  </si>
-  <si>
-    <t>[np.float64(119.6616514279566), np.float64(-199.02905471674075)]</t>
-  </si>
-  <si>
-    <t>[np.float64(159.81740020686686), np.float64(43.92429955553769)]</t>
-  </si>
-  <si>
-    <t>[np.float64(717.5684689963649), np.float64(-512.5068064406622)]</t>
-  </si>
-  <si>
-    <t>[np.float64(66.82343866651819), np.float64(-342.1088363017069)]</t>
-  </si>
-  <si>
-    <t>[np.float64(284.1041457057114), np.float64(-411.30356498530193)]</t>
-  </si>
-  <si>
-    <t>[np.float64(709.6952077811641), np.float64(406.7079904896848)]</t>
-  </si>
-  <si>
-    <t>[np.float64(467.5847410057451), np.float64(472.5035766614394)]</t>
-  </si>
-  <si>
-    <t>[np.float64(176.2588631357197), np.float64(-193.06685304435535)]</t>
-  </si>
-  <si>
-    <t>[np.float64(928.0985389340647), np.float64(70.9392030693765)]</t>
-  </si>
-  <si>
-    <t>[np.float64(382.30649028973176), np.float64(63.892394755988676)]</t>
-  </si>
-  <si>
-    <t>[np.float64(977.6928841052583), np.float64(266.3700070501344)]</t>
-  </si>
-  <si>
-    <t>[np.float64(695.568240186256), np.float64(192.79549217992735)]</t>
-  </si>
-  <si>
-    <t>[np.float64(658.5189961772656), np.float64(-283.3979682612487)]</t>
-  </si>
-  <si>
-    <t>[np.float64(350.81377995288085), np.float64(306.960601203976)]</t>
-  </si>
-  <si>
-    <t>[np.float64(457.14730481838404), np.float64(-471.28107569921616)]</t>
-  </si>
-  <si>
-    <t>[np.float64(440.5099446628202), np.float64(-313.62807185739257)]</t>
-  </si>
-  <si>
-    <t>[np.float64(374.4740316499794), np.float64(-335.9377823327413)]</t>
-  </si>
-  <si>
-    <t>[np.float64(337.92214347797335), np.float64(526.0130022555904)]</t>
-  </si>
-  <si>
-    <t>[np.float64(913.7588597059291), np.float64(-445.1367649786108)]</t>
-  </si>
-  <si>
-    <t>[np.float64(766.4925075545452), np.float64(-563.1604187912958)]</t>
-  </si>
-  <si>
-    <t>[np.float64(346.4417885871202), np.float64(143.9564955722567)]</t>
-  </si>
-  <si>
-    <t>[np.float64(443.6775997444078), np.float64(-277.51875245930614)]</t>
-  </si>
-  <si>
-    <t>[np.float64(599.9289840536051), np.float64(346.27917863756466)]</t>
-  </si>
-  <si>
-    <t>[np.float64(243.5139746142907), np.float64(-391.04419233575544)]</t>
-  </si>
-  <si>
-    <t>[np.float64(560.9882960331133), np.float64(65.11026053677313)]</t>
-  </si>
-  <si>
-    <t>[np.float64(684.5575646758156), np.float64(-587.3064125663614)]</t>
-  </si>
-  <si>
-    <t>[np.float64(143.6615202068211), np.float64(-168.95655240507585)]</t>
-  </si>
-  <si>
-    <t>[np.float64(499.68027268282054), np.float64(319.13092646921166)]</t>
-  </si>
-  <si>
-    <t>[np.float64(483.3107790590258), np.float64(141.64279193123923)]</t>
-  </si>
-  <si>
-    <t>[np.float64(506.48554944918357), np.float64(-137.21028866225157)]</t>
-  </si>
-  <si>
-    <t>[np.float64(68.754880162197), np.float64(39.67361181415242)]</t>
-  </si>
-  <si>
-    <t>[np.float64(213.4756380500148), np.float64(-247.4937803406777)]</t>
-  </si>
-  <si>
-    <t>[np.float64(134.55441259631485), np.float64(-454.44623766634027)]</t>
-  </si>
-  <si>
-    <t>[np.float64(919.035018774724), np.float64(123.13585326685734)]</t>
-  </si>
-  <si>
-    <t>[np.float64(35.120395902414224), np.float64(-268.90437257321264)]</t>
-  </si>
-  <si>
-    <t>[np.float64(390.9581274038667), np.float64(-221.80749673771322)]</t>
-  </si>
-  <si>
-    <t>[np.float64(20.162533486528854), np.float64(512.6309870483838)]</t>
-  </si>
-  <si>
-    <t>[np.float64(758.0636307294949), np.float64(-513.8878932700477)]</t>
-  </si>
-  <si>
-    <t>[np.float64(538.2327592042751), np.float64(-514.247980012849)]</t>
-  </si>
-  <si>
-    <t>[np.float64(160.02832906260102), np.float64(215.79421977143272)]</t>
-  </si>
-  <si>
-    <t>[np.float64(644.9616731628989), np.float64(116.34065764515537)]</t>
-  </si>
-  <si>
-    <t>[np.float64(519.5849235901899), np.float64(24.387933852053038)]</t>
-  </si>
-  <si>
-    <t>[np.float64(493.9501569714548), np.float64(69.48878066027407)]</t>
-  </si>
-  <si>
-    <t>[np.float64(871.4250350780251), np.float64(54.031818114321254)]</t>
-  </si>
-  <si>
-    <t>[np.float64(867.3240974863598), np.float64(-343.04362016263065)]</t>
-  </si>
-  <si>
-    <t>[np.float64(175.9014507897406), np.float64(536.5870247157868)]</t>
-  </si>
-  <si>
-    <t>[np.float64(498.8718109906052), np.float64(-469.4361505492393)]</t>
-  </si>
-  <si>
-    <t>[np.float64(247.9921987380187), np.float64(278.7587929694064)]</t>
-  </si>
-  <si>
-    <t>[np.float64(556.5477940488819), np.float64(98.1777161728819)]</t>
-  </si>
-  <si>
-    <t>[np.float64(468.9157775390155), np.float64(308.06405580993044)]</t>
-  </si>
-  <si>
-    <t>[np.float64(215.34343766064435), np.float64(-235.58052739595536)]</t>
-  </si>
-  <si>
-    <t>[np.float64(515.7513188743999), np.float64(578.869278208271)]</t>
-  </si>
-  <si>
-    <t>[np.float64(363.17370687445947), np.float64(-155.59570110718352)]</t>
-  </si>
-  <si>
-    <t>[np.float64(379.52627575118146), np.float64(-102.22926599853122)]</t>
-  </si>
-  <si>
-    <t>[np.float64(758.1750129930465), np.float64(-143.32284839211928)]</t>
-  </si>
-  <si>
-    <t>[np.float64(587.85840526039), np.float64(554.5473122624905)]</t>
-  </si>
-  <si>
-    <t>[np.float64(469.41988644408264), np.float64(574.1768835939997)]</t>
-  </si>
-  <si>
-    <t>[np.float64(809.279549163873), np.float64(-565.3045650153846)]</t>
-  </si>
-  <si>
-    <t>[np.float64(88.30724045834137), np.float64(367.93992469472744)]</t>
-  </si>
-  <si>
-    <t>[np.float64(576.0719301611283), np.float64(568.2825090095089)]</t>
-  </si>
-  <si>
-    <t>[np.float64(384.9603881583209), np.float64(-200.5468919636092)]</t>
-  </si>
-  <si>
-    <t>[np.float64(604.8195485525487), np.float64(436.76626125507846)]</t>
-  </si>
-  <si>
-    <t>[np.float64(800.5543546949793), np.float64(18.12959176115885)]</t>
-  </si>
-  <si>
-    <t>[np.float64(127.30104497338569), np.float64(178.0721086038492)]</t>
-  </si>
-  <si>
-    <t>[np.float64(164.87215101018492), np.float64(548.2479120766347)]</t>
-  </si>
-  <si>
-    <t>[np.float64(350.9244260563117), np.float64(-393.0996222186169)]</t>
-  </si>
-  <si>
-    <t>[np.float64(37.30381217869383), np.float64(261.6117546060524)]</t>
-  </si>
-  <si>
-    <t>[np.float64(761.1135929436024), np.float64(-244.18498865866206)]</t>
-  </si>
-  <si>
-    <t>[np.float64(254.16473890908264), np.float64(595.6017920243628)]</t>
-  </si>
-  <si>
-    <t>[np.float64(642.2061493486749), np.float64(-238.36491481426435)]</t>
-  </si>
-  <si>
-    <t>[np.float64(382.9813674829614), np.float64(12.633908728272445)]</t>
-  </si>
-  <si>
-    <t>[np.float64(531.2971661687865), np.float64(3.860744859509964)]</t>
-  </si>
-  <si>
-    <t>[np.float64(983.6138916687086), np.float64(119.31202039283733)]</t>
-  </si>
-  <si>
-    <t>[np.float64(601.0462747117633), np.float64(-556.8250213264442)]</t>
-  </si>
-  <si>
-    <t>[np.float64(507.8653089866115), np.float64(-361.1676402211113)]</t>
-  </si>
-  <si>
-    <t>[np.float64(953.1113497082445), np.float64(-386.2006959925237)]</t>
-  </si>
-  <si>
-    <t>[np.float64(231.96422215993906), np.float64(-546.9469126927575)]</t>
-  </si>
-  <si>
-    <t>[np.float64(100.58742739161231), np.float64(214.8838937096084)]</t>
-  </si>
-  <si>
-    <t>[np.float64(716.3463852385651), np.float64(510.4512926011423)]</t>
-  </si>
-  <si>
-    <t>[np.float64(465.76896776869137), np.float64(-187.06353938162488)]</t>
-  </si>
-  <si>
-    <t>[np.float64(480.69852585236606), np.float64(53.506338058096844)]</t>
-  </si>
-  <si>
-    <t>[np.float64(395.4516669987528), np.float64(-587.2828674684376)]</t>
-  </si>
-  <si>
-    <t>[np.float64(904.6965029094853), np.float64(65.03893008510067)]</t>
-  </si>
-  <si>
-    <t>[np.float64(509.35544854508953), np.float64(-302.88666778120097)]</t>
-  </si>
-  <si>
-    <t>[np.float64(352.66715882306454), np.float64(93.6146107839113)]</t>
-  </si>
-  <si>
-    <t>[np.float64(13.496287097121694), np.float64(263.5260777843288)]</t>
-  </si>
-  <si>
-    <t>[np.float64(761.2779537947957), np.float64(-106.43529765219819)]</t>
-  </si>
-  <si>
-    <t>[np.float64(373.74599756446423), np.float64(56.8044535502255)]</t>
-  </si>
-  <si>
-    <t>[np.float64(327.9696392543201), np.float64(94.73527264610198)]</t>
-  </si>
-  <si>
-    <t>[np.float64(392.4708753599615), np.float64(27.9631867242756)]</t>
-  </si>
-  <si>
-    <t>[np.float64(68.27069225344995), np.float64(-538.042997886838)]</t>
-  </si>
-  <si>
-    <t>[np.float64(516.3019416361133), np.float64(-527.9014324043849)]</t>
-  </si>
-  <si>
-    <t>[np.float64(223.07017386720352), np.float64(-452.819390046739)]</t>
-  </si>
-  <si>
-    <t>[np.float64(84.95172600383493), np.float64(284.7057607676318)]</t>
-  </si>
-  <si>
-    <t>[np.float64(473.08213639357075), np.float64(-383.17569938267417)]</t>
-  </si>
-  <si>
-    <t>[np.float64(467.2802648938622), np.float64(144.0726327014777)]</t>
-  </si>
-  <si>
-    <t>[np.float64(129.55208503735582), np.float64(226.10556260273006)]</t>
-  </si>
-  <si>
-    <t>[np.float64(119.7112822097972), np.float64(-218.19016741983404)]</t>
-  </si>
-  <si>
-    <t>[np.float64(483.2621905655873), np.float64(332.34601242262386)]</t>
-  </si>
-  <si>
-    <t>[np.float64(866.2028631161907), np.float64(371.6982018234837)]</t>
-  </si>
-  <si>
-    <t>[np.float64(596.099543366851), np.float64(479.67470869819863)]</t>
-  </si>
-  <si>
-    <t>[np.float64(456.83583676316687), np.float64(516.0869083952473)]</t>
-  </si>
-  <si>
-    <t>[np.float64(682.1283734830056), np.float64(176.5740536756848)]</t>
-  </si>
-  <si>
-    <t>[np.float64(327.69399162114496), np.float64(-374.0088111347136)]</t>
-  </si>
-  <si>
-    <t>[np.float64(43.89525147509465), np.float64(-266.52153087721683)]</t>
-  </si>
-  <si>
-    <t>[np.float64(917.8483476865031), np.float64(456.616511721302)]</t>
-  </si>
-  <si>
-    <t>[np.float64(648.0117535585761), np.float64(-493.4201672397695)]</t>
-  </si>
-  <si>
-    <t>[np.float64(583.0518829128913), np.float64(-321.22177366992884)]</t>
-  </si>
-  <si>
-    <t>[np.float64(353.41949251436), np.float64(515.9574312867696)]</t>
-  </si>
-  <si>
-    <t>[np.float64(399.5118279377724), np.float64(-167.73896245102782)]</t>
-  </si>
-  <si>
-    <t>[np.float64(652.4533657725307), np.float64(192.25274679560948)]</t>
-  </si>
-  <si>
-    <t>[np.float64(672.1951179300331), np.float64(43.02251431706486)]</t>
-  </si>
-  <si>
-    <t>[np.float64(923.7728574488593), np.float64(275.97143716715436)]</t>
-  </si>
-  <si>
-    <t>[np.float64(111.28283373668025), np.float64(-65.33470862729541)]</t>
-  </si>
-  <si>
-    <t>[np.float64(311.9535996465018), np.float64(139.25383187435432)]</t>
-  </si>
-  <si>
-    <t>[np.float64(947.7345471048116), np.float64(-164.27081387901399)]</t>
-  </si>
-  <si>
-    <t>[np.float64(966.4824883263599), np.float64(-599.738291898646)]</t>
-  </si>
-  <si>
-    <t>[np.float64(243.31576628914985), np.float64(-306.2573567352421)]</t>
-  </si>
-  <si>
-    <t>[np.float64(320.1722920267737), np.float64(346.6861046032001)]</t>
-  </si>
-  <si>
-    <t>[np.float64(718.5884760727276), np.float64(-186.36800655024985)]</t>
-  </si>
-  <si>
-    <t>[np.float64(840.4296101406059), np.float64(-396.06296058570547)]</t>
-  </si>
-  <si>
-    <t>[np.float64(540.3970096618494), np.float64(474.1939432695781)]</t>
-  </si>
-  <si>
-    <t>[np.float64(892.2636639139623), np.float64(351.17314942906944)]</t>
-  </si>
-  <si>
-    <t>[np.float64(948.6690762821084), np.float64(32.89741047220548)]</t>
-  </si>
-  <si>
-    <t>[np.float64(796.0988418247972), np.float64(527.4391714053841)]</t>
-  </si>
-  <si>
-    <t>[np.float64(510.75292194320764), np.float64(-140.44896327215713)]</t>
-  </si>
-  <si>
-    <t>[np.float64(786.1237460961868), np.float64(-94.74525700762786)]</t>
-  </si>
-  <si>
-    <t>[np.float64(537.4773440147081), np.float64(507.8598192686345)]</t>
-  </si>
-  <si>
-    <t>[np.float64(302.7036172417622), np.float64(67.11408473949666)]</t>
-  </si>
-  <si>
-    <t>[np.float64(446.4001544498398), np.float64(-493.2874689861688)]</t>
-  </si>
-  <si>
-    <t>[np.float64(308.1179067632671), np.float64(473.0389495635591)]</t>
-  </si>
-  <si>
-    <t>[np.float64(323.34267042466024), np.float64(532.5756892784257)]</t>
-  </si>
-  <si>
-    <t>[np.float64(731.9172916526031), np.float64(341.77059492614967)]</t>
-  </si>
-  <si>
-    <t>[np.float64(587.1006661096458), np.float64(172.1328306934713)]</t>
-  </si>
-  <si>
-    <t>[np.float64(258.07326688310474), np.float64(436.6588278066199)]</t>
-  </si>
-  <si>
-    <t>[np.float64(179.31704549823968), np.float64(-374.4761423016986)]</t>
-  </si>
-  <si>
-    <t>[np.float64(289.8501884950007), np.float64(125.40793287409895)]</t>
-  </si>
-  <si>
-    <t>[np.float64(166.41213045063697), np.float64(267.64384589660847)]</t>
-  </si>
-  <si>
-    <t>[np.float64(2.705106769811838), np.float64(18.611916180331377)]</t>
-  </si>
-  <si>
-    <t>[np.float64(20.946997686844604), np.float64(-567.6932413827728)]</t>
-  </si>
-  <si>
-    <t>[np.float64(562.7203426638196), np.float64(-453.9148736312884)]</t>
-  </si>
-  <si>
-    <t>[np.float64(457.1839953975788), np.float64(505.950783857988)]</t>
-  </si>
-  <si>
-    <t>[np.float64(108.6734855507704), np.float64(54.77728846532705)]</t>
-  </si>
-  <si>
-    <t>[np.float64(694.1559033590903), np.float64(77.16227294436726)]</t>
-  </si>
-  <si>
-    <t>[np.float64(626.0122784011635), np.float64(551.5838151297728)]</t>
-  </si>
-  <si>
-    <t>[np.float64(250.401610611079), np.float64(172.93620833795637)]</t>
-  </si>
-  <si>
-    <t>[np.float64(279.4998072755599), np.float64(58.92149422424757)]</t>
-  </si>
-  <si>
-    <t>[np.float64(450.5735984067104), np.float64(-348.19855532902307)]</t>
-  </si>
-  <si>
-    <t>[np.float64(298.4412486093039), np.float64(597.7088549954917)]</t>
-  </si>
-  <si>
-    <t>[np.float64(844.5170555714263), np.float64(256.5689580277491)]</t>
-  </si>
-  <si>
-    <t>[np.float64(731.7219985439704), np.float64(-554.1770425887808)]</t>
-  </si>
-  <si>
-    <t>[np.float64(833.7981727961499), np.float64(528.4898322344884)]</t>
-  </si>
-  <si>
-    <t>[np.float64(259.21720975717034), np.float64(-558.5306203766036)]</t>
-  </si>
-  <si>
-    <t>[np.float64(108.70169507675853), np.float64(299.1403819682756)]</t>
-  </si>
-  <si>
-    <t>[np.float64(404.8338305330609), np.float64(394.544549034489)]</t>
-  </si>
-  <si>
-    <t>[np.float64(796.3544941058894), np.float64(171.5534327962299)]</t>
-  </si>
-  <si>
-    <t>[np.float64(147.28706150278737), np.float64(505.00839510826813)]</t>
-  </si>
-  <si>
-    <t>[np.float64(333.69069870151134), np.float64(460.5553275243717)]</t>
-  </si>
-  <si>
-    <t>[np.float64(844.9351547632153), np.float64(6.37309297766285)]</t>
-  </si>
-  <si>
-    <t>[np.float64(852.8749342905828), np.float64(466.50166004846596)]</t>
-  </si>
-  <si>
-    <t>[np.float64(674.7343582576134), np.float64(389.82189755441925)]</t>
-  </si>
-  <si>
-    <t>[np.float64(253.86111524216437), np.float64(-127.0736160203399)]</t>
-  </si>
-  <si>
-    <t>[np.float64(161.29945971939975), np.float64(-413.3032441127598)]</t>
-  </si>
-  <si>
-    <t>[np.float64(410.85785263648233), np.float64(457.3602480635002)]</t>
-  </si>
-  <si>
-    <t>[np.float64(811.2283944901067), np.float64(228.07519258138473)]</t>
-  </si>
-  <si>
-    <t>[np.float64(277.9208632733018), np.float64(366.5261143084575)]</t>
-  </si>
-  <si>
-    <t>[np.float64(281.07586883151725), np.float64(391.8031001740716)]</t>
-  </si>
-  <si>
-    <t>[np.float64(373.34825991637786), np.float64(-281.3135470996856)]</t>
-  </si>
-  <si>
-    <t>[np.float64(746.6664196562573), np.float64(597.4357282577662)]</t>
-  </si>
-  <si>
-    <t>[np.float64(731.3730484275577), np.float64(23.786240820286025)]</t>
-  </si>
-  <si>
-    <t>[np.float64(544.3829481131052), np.float64(347.1917456343525)]</t>
-  </si>
-  <si>
-    <t>[np.float64(212.8184271701733), np.float64(110.73251490420137)]</t>
-  </si>
-  <si>
-    <t>[np.float64(204.12698232122207), np.float64(-283.63322330463336)]</t>
-  </si>
-  <si>
-    <t>[np.float64(811.7450010055848), np.float64(-97.71468845499032)]</t>
-  </si>
-  <si>
-    <t>[np.float64(380.6826687407683), np.float64(213.53362588764764)]</t>
-  </si>
-  <si>
-    <t>[np.float64(739.1180493595058), np.float64(526.1698510876925)]</t>
-  </si>
-  <si>
-    <t>[np.float64(306.1191409946488), np.float64(-109.17972791555661)]</t>
-  </si>
-  <si>
-    <t>[np.float64(287.7449185016386), np.float64(-484.06538670051805)]</t>
-  </si>
-  <si>
-    <t>[np.float64(948.6033860420818), np.float64(-410.84013680587015)]</t>
-  </si>
-  <si>
-    <t>[np.float64(581.0718418535313), np.float64(399.97409444639015)]</t>
-  </si>
-  <si>
-    <t>[np.float64(99.15317960320291), np.float64(-106.7141777715326)]</t>
-  </si>
-  <si>
-    <t>[np.float64(444.41617864054336), np.float64(418.2421312768797)]</t>
-  </si>
-  <si>
-    <t>[np.float64(524.7642405438747), np.float64(-490.9958262085221)]</t>
-  </si>
-  <si>
-    <t>[np.float64(884.6371017259912), np.float64(39.44153959471896)]</t>
-  </si>
-  <si>
-    <t>[np.float64(778.790153558071), np.float64(63.440111144831576)]</t>
-  </si>
-  <si>
-    <t>[np.float64(362.9214032797091), np.float64(543.6526918567235)]</t>
-  </si>
-  <si>
-    <t>[np.float64(870.3823146865868), np.float64(141.32988840853636)]</t>
-  </si>
-  <si>
-    <t>[np.float64(276.6967776047489), np.float64(-124.08833047268428)]</t>
-  </si>
-  <si>
-    <t>[np.float64(735.9697974513206), np.float64(80.36834546572368)]</t>
-  </si>
-  <si>
-    <t>[np.float64(65.31170412919218), np.float64(-266.5505104855441)]</t>
-  </si>
-  <si>
-    <t>[np.float64(945.4154306893462), np.float64(392.5423110406732)]</t>
-  </si>
-  <si>
-    <t>[np.float64(114.77341722839263), np.float64(-293.93451619002894)]</t>
-  </si>
-  <si>
-    <t>[np.float64(160.50355617487233), np.float64(-539.174581334644)]</t>
-  </si>
-  <si>
-    <t>[np.float64(665.716157622877), np.float64(-576.2669792186864)]</t>
-  </si>
-  <si>
-    <t>[np.float64(807.3392518211552), np.float64(-126.48642540124285)]</t>
-  </si>
-  <si>
-    <t>[np.float64(611.6478949076143), np.float64(178.57583005824847)]</t>
-  </si>
-  <si>
-    <t>[np.float64(241.5892074629211), np.float64(63.9718656591366)]</t>
-  </si>
-  <si>
-    <t>[np.float64(746.4627593224616), np.float64(-517.3258249976396)]</t>
-  </si>
-  <si>
-    <t>[np.float64(523.1228160931912), np.float64(-123.2973256132044)]</t>
-  </si>
-  <si>
-    <t>[np.float64(900.4026501186227), np.float64(114.7578295659298)]</t>
-  </si>
-  <si>
-    <t>[np.float64(633.3459830909451), np.float64(435.581859350061)]</t>
-  </si>
-  <si>
-    <t>[np.float64(289.6233206919713), np.float64(126.02530273404807)]</t>
-  </si>
-  <si>
-    <t>[np.float64(111.93234108425432), np.float64(261.9034389725881)]</t>
-  </si>
-  <si>
-    <t>[np.float64(721.8074184635058), np.float64(43.99418694763824)]</t>
-  </si>
-  <si>
-    <t>[np.float64(58.27666481672522), np.float64(187.14990651915173)]</t>
-  </si>
-  <si>
-    <t>[np.float64(361.9911041409458), np.float64(485.94506511663485)]</t>
-  </si>
-  <si>
-    <t>[np.float64(196.9488537973919), np.float64(-313.6935508019473)]</t>
-  </si>
-  <si>
-    <t>[np.float64(26.27439084878469), np.float64(-302.5947011080329)]</t>
-  </si>
-  <si>
-    <t>[np.float64(113.21226281730334), np.float64(530.5144921770705)]</t>
-  </si>
-  <si>
-    <t>[np.float64(71.42705738899512), np.float64(-298.634882737259)]</t>
-  </si>
-  <si>
-    <t>[np.float64(985.5101463180649), np.float64(533.198423847437)]</t>
-  </si>
-  <si>
-    <t>[np.float64(623.9228477798196), np.float64(12.051683735373217)]</t>
-  </si>
-  <si>
-    <t>[np.float64(813.9824862521451), np.float64(422.7227500015042)]</t>
-  </si>
-  <si>
-    <t>[np.float64(432.36913836741996), np.float64(-224.7717009613949)]</t>
-  </si>
-  <si>
-    <t>[np.float64(308.9124297988299), np.float64(-276.7895737355437)]</t>
-  </si>
-  <si>
-    <t>[np.float64(712.253309571553), np.float64(141.48666369916464)]</t>
-  </si>
-  <si>
-    <t>[np.float64(296.5709774670301), np.float64(18.629953407995004)]</t>
-  </si>
-  <si>
-    <t>[np.float64(253.7859072782781), np.float64(-194.13907960072964)]</t>
-  </si>
-  <si>
-    <t>[np.float64(926.3943370007989), np.float64(-404.6748337609065)]</t>
-  </si>
-  <si>
-    <t>[np.float64(382.98938253554894), np.float64(176.96057120582896)]</t>
-  </si>
-  <si>
-    <t>[np.float64(1.4035805487413455), np.float64(-124.34328727798652)]</t>
-  </si>
-  <si>
-    <t>[np.float64(18.296109295348973), np.float64(132.43448883384258)]</t>
-  </si>
-  <si>
-    <t>[np.float64(730.361163124811), np.float64(288.71056033931677)]</t>
-  </si>
-  <si>
-    <t>[np.float64(183.76689246183574), np.float64(109.3198195259115)]</t>
-  </si>
-  <si>
-    <t>[np.float64(956.0029128037154), np.float64(251.9801771457885)]</t>
-  </si>
-  <si>
-    <t>[np.float64(679.7357944239045), np.float64(580.8986771378197)]</t>
-  </si>
-  <si>
-    <t>[np.float64(859.0601969593376), np.float64(-471.6992706267189)]</t>
-  </si>
-  <si>
-    <t>[np.float64(995.4229442438498), np.float64(570.4031324739271)]</t>
-  </si>
-  <si>
-    <t>[np.float64(747.8819162096462), np.float64(184.26710363067377)]</t>
-  </si>
-  <si>
-    <t>[np.float64(539.899796997458), np.float64(60.74605625313211)]</t>
-  </si>
-  <si>
-    <t>[np.float64(897.356539536285), np.float64(-196.9725455465716)]</t>
-  </si>
-  <si>
-    <t>[np.float64(970.9995227230902), np.float64(-127.4319860522645)]</t>
-  </si>
-  <si>
-    <t>[np.float64(305.8654819960199), np.float64(-409.61574280135255)]</t>
-  </si>
-  <si>
-    <t>[np.float64(948.0541588533172), np.float64(314.50046974068846)]</t>
-  </si>
-  <si>
-    <t>[np.float64(591.9179405445307), np.float64(302.60078228798113)]</t>
-  </si>
-  <si>
-    <t>[np.float64(878.4068510049618), np.float64(-463.55131061279997)]</t>
-  </si>
-  <si>
-    <t>[np.float64(994.3867680310182), np.float64(-519.0422334523231)]</t>
-  </si>
-  <si>
-    <t>[np.float64(457.1751743285871), np.float64(-69.46559432019353)]</t>
-  </si>
-  <si>
-    <t>[np.float64(279.21725747315264), np.float64(540.2269970533912)]</t>
-  </si>
-  <si>
-    <t>[np.float64(799.9472764216484), np.float64(-516.5482245849493)]</t>
-  </si>
-  <si>
-    <t>[np.float64(277.7747696313283), np.float64(-477.985127015137)]</t>
-  </si>
-  <si>
-    <t>[np.float64(897.9988764501242), np.float64(-310.5609306839185)]</t>
-  </si>
-  <si>
-    <t>[np.float64(681.024927843037), np.float64(-376.848863682093)]</t>
-  </si>
-  <si>
-    <t>[np.float64(20.989828918203667), np.float64(161.7581978910555)]</t>
-  </si>
-  <si>
-    <t>[np.float64(504.4014138884193), np.float64(368.51035467120096)]</t>
-  </si>
-  <si>
-    <t>[np.float64(438.6082630543377), np.float64(221.25933397767471)]</t>
-  </si>
-  <si>
-    <t>[np.float64(979.9801783961153), np.float64(236.4295520965867)]</t>
-  </si>
-  <si>
-    <t>[np.float64(312.3102120147153), np.float64(445.90024139804996)]</t>
-  </si>
-  <si>
-    <t>[np.float64(992.2963667048085), np.float64(592.7647936435228)]</t>
-  </si>
-  <si>
-    <t>[np.float64(560.2790914291911), np.float64(-217.09613683947578)]</t>
-  </si>
-  <si>
-    <t>[np.float64(885.162643230648), np.float64(587.0798348758185)]</t>
-  </si>
-  <si>
-    <t>[np.float64(575.8593102913532), np.float64(-478.05973786121183)]</t>
-  </si>
-  <si>
-    <t>[np.float64(907.79138533838), np.float64(-113.19289209312842)]</t>
-  </si>
-  <si>
-    <t>[np.float64(442.32852352232885), np.float64(-482.8799776460352)]</t>
-  </si>
-  <si>
-    <t>[np.float64(597.3207452448704), np.float64(-360.45607095826125)]</t>
-  </si>
-  <si>
-    <t>[np.float64(227.95728059805433), np.float64(-346.0915239249979)]</t>
-  </si>
-  <si>
-    <t>[np.float64(370.3735914710425), np.float64(425.2430117299623)]</t>
-  </si>
-  <si>
-    <t>[np.float64(749.0475242029455), np.float64(-552.9442097073141)]</t>
-  </si>
-  <si>
-    <t>[np.float64(126.54473924653675), np.float64(-404.3269474575579)]</t>
-  </si>
-  <si>
-    <t>[np.float64(189.4276380369122), np.float64(-310.78812420039765)]</t>
-  </si>
-  <si>
-    <t>[np.float64(511.81776425967274), np.float64(21.01383789995907)]</t>
-  </si>
-  <si>
-    <t>[np.float64(796.1784930929019), np.float64(-170.35063135049586)]</t>
-  </si>
-  <si>
-    <t>[np.float64(33.9155199790957), np.float64(48.0988638085463)]</t>
-  </si>
-  <si>
-    <t>[np.float64(979.5374755256112), np.float64(-370.4796822053611)]</t>
-  </si>
-  <si>
-    <t>[np.float64(715.941268008362), np.float64(-362.17530943973867)]</t>
-  </si>
-  <si>
-    <t>[np.float64(907.6000340519784), np.float64(237.94657807531735)]</t>
-  </si>
-  <si>
-    <t>[np.float64(678.3369570795378), np.float64(-339.7529088227879)]</t>
-  </si>
-  <si>
-    <t>[np.float64(524.4292139842728), np.float64(79.78280359396763)]</t>
-  </si>
-  <si>
-    <t>[np.float64(882.6617134748128), np.float64(-205.29705488186613)]</t>
-  </si>
-  <si>
-    <t>[np.float64(810.4082673655993), np.float64(-404.1583286274989)]</t>
-  </si>
-  <si>
-    <t>[np.float64(771.14330897072), np.float64(-466.3400572089905)]</t>
-  </si>
-  <si>
-    <t>[np.float64(856.2646026255126), np.float64(-414.39582786701055)]</t>
-  </si>
-  <si>
-    <t>[np.float64(87.94151021677344), np.float64(-425.03236013391364)]</t>
-  </si>
-  <si>
-    <t>[np.float64(123.50448149038229), np.float64(192.39614114987523)]</t>
-  </si>
-  <si>
-    <t>[np.float64(765.1100495529369), np.float64(225.16851539499737)]</t>
-  </si>
-  <si>
-    <t>[np.float64(188.1812025021541), np.float64(-492.50897764430607)]</t>
-  </si>
-  <si>
-    <t>[np.float64(606.0469180631205), np.float64(-258.16679900171505)]</t>
-  </si>
-  <si>
-    <t>[np.float64(401.91043035435405), np.float64(469.07698353094634)]</t>
-  </si>
-  <si>
-    <t>[np.float64(473.8566954611317), np.float64(89.39087413052266)]</t>
-  </si>
-  <si>
-    <t>[np.float64(0.3871717172528877), np.float64(284.9100591101028)]</t>
-  </si>
-  <si>
-    <t>[np.float64(721.9943566171557), np.float64(132.2692784016184)]</t>
-  </si>
-  <si>
-    <t>[np.float64(435.28201446084734), np.float64(-454.25016072596884)]</t>
-  </si>
-  <si>
-    <t>[np.float64(623.2090161579788), np.float64(209.02638819510764)]</t>
-  </si>
-  <si>
-    <t>[np.float64(212.35064580606644), np.float64(-536.6419126148689)]</t>
-  </si>
-  <si>
-    <t>[np.float64(704.9485953320376), np.float64(-436.54108685798644)]</t>
-  </si>
-  <si>
-    <t>[np.float64(735.2476424424316), np.float64(-392.96364035775366)]</t>
-  </si>
-  <si>
-    <t>[np.float64(335.2311780327927), np.float64(145.39772569404204)]</t>
-  </si>
-  <si>
-    <t>[np.float64(965.3754044418878), np.float64(-387.48823760915997)]</t>
-  </si>
-  <si>
-    <t>[np.float64(266.6807247778328), np.float64(-112.6449101507589)]</t>
-  </si>
-  <si>
-    <t>[np.float64(246.21859683997138), np.float64(268.8037302611041)]</t>
-  </si>
-  <si>
-    <t>[np.float64(373.29194105528006), np.float64(-292.31155643155455)]</t>
-  </si>
-  <si>
-    <t>[np.float64(495.709544856057), np.float64(-561.2944617391262)]</t>
-  </si>
-  <si>
-    <t>[np.float64(707.7175651641011), np.float64(538.493569792121)]</t>
-  </si>
-  <si>
-    <t>[np.float64(902.3041812261017), np.float64(545.7226765586777)]</t>
-  </si>
-  <si>
-    <t>[np.float64(581.8613781150401), np.float64(-580.9160753792999)]</t>
-  </si>
-  <si>
-    <t>[np.float64(788.9681744668471), np.float64(-171.22381154392758)]</t>
-  </si>
-  <si>
-    <t>[np.float64(623.9279816814476), np.float64(531.8268000606879)]</t>
-  </si>
-  <si>
-    <t>[np.float64(93.89912531132916), np.float64(331.45543800867915)]</t>
-  </si>
-  <si>
-    <t>[np.float64(680.8764541439119), np.float64(-407.7636045332716)]</t>
-  </si>
-  <si>
-    <t>[np.float64(407.9344211164894), np.float64(447.17049046431316)]</t>
-  </si>
-  <si>
-    <t>[np.float64(317.4680052989205), np.float64(454.90215115719457)]</t>
-  </si>
-  <si>
-    <t>[np.float64(25.276007365235607), np.float64(-376.4364224563616)]</t>
-  </si>
-  <si>
-    <t>[np.float64(350.4819395462315), np.float64(198.21538742628263)]</t>
-  </si>
-  <si>
-    <t>[np.float64(472.08185060708286), np.float64(567.9305483946675)]</t>
-  </si>
-  <si>
-    <t>[np.float64(221.59944093561344), np.float64(206.76563875994248)]</t>
-  </si>
-  <si>
-    <t>[np.float64(685.8725121511858), np.float64(376.4810411956437)]</t>
-  </si>
-  <si>
-    <t>[np.float64(982.6765485578557), np.float64(-287.74100358083217)]</t>
-  </si>
-  <si>
-    <t>[np.float64(195.9883820617987), np.float64(253.45465757154295)]</t>
-  </si>
-  <si>
-    <t>[np.float64(817.4306637741706), np.float64(-88.88640852464806)]</t>
-  </si>
-  <si>
-    <t>[np.float64(19.060020038457417), np.float64(-310.6618278062079)]</t>
-  </si>
-  <si>
-    <t>[np.float64(986.8136146844108), np.float64(433.285662932263)]</t>
-  </si>
-  <si>
-    <t>[np.float64(887.8115370619211), np.float64(49.270005678453686)]</t>
-  </si>
-  <si>
-    <t>[np.float64(473.52314169704954), np.float64(475.6509932181541)]</t>
-  </si>
-  <si>
-    <t>[np.float64(991.5462339019352), np.float64(-586.5440917996549)]</t>
-  </si>
-  <si>
-    <t>[np.float64(564.0181782522064), np.float64(114.95139313703703)]</t>
-  </si>
-  <si>
-    <t>[np.float64(682.3670404064202), np.float64(-512.4851186627074)]</t>
-  </si>
-  <si>
-    <t>[np.float64(42.80411888109947), np.float64(-196.09216901433552)]</t>
+    <t>[np.float64(509.11804267826676), np.float64(416.9433683544478)]</t>
+  </si>
+  <si>
+    <t>[np.float64(524.458069935949), np.float64(-457.2629279149801)]</t>
+  </si>
+  <si>
+    <t>[np.float64(251.1826640608519), np.float64(-149.4911013632306)]</t>
+  </si>
+  <si>
+    <t>[np.float64(560.567653272777), np.float64(391.07188634466206)]</t>
+  </si>
+  <si>
+    <t>[np.float64(290.0714565517266), np.float64(57.004848800975765)]</t>
+  </si>
+  <si>
+    <t>[np.float64(390.61856165642337), np.float64(146.40713489975553)]</t>
+  </si>
+  <si>
+    <t>[np.float64(124.47913034510638), np.float64(-414.2384142367572)]</t>
+  </si>
+  <si>
+    <t>[np.float64(117.74275798765765), np.float64(-133.88552955000432)]</t>
+  </si>
+  <si>
+    <t>[np.float64(90.45500153408526), np.float64(121.78627995703175)]</t>
+  </si>
+  <si>
+    <t>[np.float64(257.167147549606), np.float64(-189.4185135451374)]</t>
+  </si>
+  <si>
+    <t>[np.float64(790.7727434844476), np.float64(-425.12669635136604)]</t>
+  </si>
+  <si>
+    <t>[np.float64(34.05974720589955), np.float64(-11.624219225867137)]</t>
+  </si>
+  <si>
+    <t>[np.float64(42.549832384600975), np.float64(-370.86560069338793)]</t>
+  </si>
+  <si>
+    <t>[np.float64(833.3904124312427), np.float64(495.1080564399424)]</t>
+  </si>
+  <si>
+    <t>[np.float64(502.15468923686), np.float64(-539.1033378447395)]</t>
+  </si>
+  <si>
+    <t>[np.float64(933.1485932333355), np.float64(570.6307344768611)]</t>
+  </si>
+  <si>
+    <t>[np.float64(467.8834404033992), np.float64(-318.20177920280173)]</t>
+  </si>
+  <si>
+    <t>[np.float64(231.00528524649556), np.float64(201.04173763877202)]</t>
+  </si>
+  <si>
+    <t>[np.float64(748.8988198551256), np.float64(59.7086697044889)]</t>
+  </si>
+  <si>
+    <t>[np.float64(523.7135577280368), np.float64(-512.1903906004736)]</t>
+  </si>
+  <si>
+    <t>[np.float64(52.16444979002988), np.float64(-177.82097696552074)]</t>
+  </si>
+  <si>
+    <t>[np.float64(519.3702576273151), np.float64(-277.8813302007665)]</t>
+  </si>
+  <si>
+    <t>[np.float64(419.6382939577236), np.float64(114.81357193639758)]</t>
+  </si>
+  <si>
+    <t>[np.float64(152.36662146343016), np.float64(-68.8276701256325)]</t>
+  </si>
+  <si>
+    <t>[np.float64(135.77037534659985), np.float64(426.152419338104)]</t>
+  </si>
+  <si>
+    <t>[np.float64(918.0026130832581), np.float64(231.6622960184601)]</t>
+  </si>
+  <si>
+    <t>[np.float64(130.35373674280726), np.float64(-485.2571110726028)]</t>
+  </si>
+  <si>
+    <t>[np.float64(18.292915818781008), np.float64(-442.34377151212504)]</t>
+  </si>
+  <si>
+    <t>[np.float64(25.424387448188313), np.float64(433.3481032965526)]</t>
+  </si>
+  <si>
+    <t>[np.float64(336.7904835922724), np.float64(166.98429125067946)]</t>
+  </si>
+  <si>
+    <t>[np.float64(43.00908401631276), np.float64(-439.2172437869441)]</t>
+  </si>
+  <si>
+    <t>[np.float64(707.5654621265643), np.float64(-199.11454107527726)]</t>
+  </si>
+  <si>
+    <t>[np.float64(348.1577065794582), np.float64(-353.84379912504596)]</t>
+  </si>
+  <si>
+    <t>[np.float64(23.151435815215613), np.float64(-310.5792050217019)]</t>
+  </si>
+  <si>
+    <t>[np.float64(546.8042554739294), np.float64(-183.14156927748553)]</t>
+  </si>
+  <si>
+    <t>[np.float64(721.7855077870446), np.float64(455.0069592246716)]</t>
+  </si>
+  <si>
+    <t>[np.float64(931.4786795079638), np.float64(278.4971311756026)]</t>
+  </si>
+  <si>
+    <t>[np.float64(678.4343062333828), np.float64(297.41560912199714)]</t>
+  </si>
+  <si>
+    <t>[np.float64(243.23525992434392), np.float64(-262.81578093279194)]</t>
+  </si>
+  <si>
+    <t>[np.float64(958.5051575095782), np.float64(-225.47626088076373)]</t>
+  </si>
+  <si>
+    <t>[np.float64(498.8639875489587), np.float64(8.275514629918007)]</t>
+  </si>
+  <si>
+    <t>[np.float64(267.05518712902534), np.float64(-283.5677952156043)]</t>
+  </si>
+  <si>
+    <t>[np.float64(736.6877338325312), np.float64(305.36974903415216)]</t>
+  </si>
+  <si>
+    <t>[np.float64(879.4049009481591), np.float64(198.05949250615697)]</t>
+  </si>
+  <si>
+    <t>[np.float64(176.88358973011776), np.float64(152.24520387564712)]</t>
+  </si>
+  <si>
+    <t>[np.float64(659.8978493230042), np.float64(430.61965543526617)]</t>
+  </si>
+  <si>
+    <t>[np.float64(753.5260979701279), np.float64(581.0293097641654)]</t>
+  </si>
+  <si>
+    <t>[np.float64(245.87894820921207), np.float64(463.72087240149585)]</t>
+  </si>
+  <si>
+    <t>[np.float64(65.29745022000755), np.float64(441.5181667773636)]</t>
+  </si>
+  <si>
+    <t>[np.float64(163.7267736652004), np.float64(-327.2105690685403)]</t>
+  </si>
+  <si>
+    <t>[np.float64(445.25065974995573), np.float64(265.1723296728301)]</t>
+  </si>
+  <si>
+    <t>[np.float64(485.7875855543969), np.float64(-108.6379614250609)]</t>
+  </si>
+  <si>
+    <t>[np.float64(477.34925824418315), np.float64(-76.16121186307407)]</t>
+  </si>
+  <si>
+    <t>[np.float64(344.03940443200787), np.float64(176.58391078607963)]</t>
+  </si>
+  <si>
+    <t>[np.float64(348.3318084942542), np.float64(-100.28750458083772)]</t>
+  </si>
+  <si>
+    <t>[np.float64(30.373155256539054), np.float64(343.35460398605767)]</t>
+  </si>
+  <si>
+    <t>[np.float64(363.38862179417987), np.float64(351.63006994921557)]</t>
+  </si>
+  <si>
+    <t>[np.float64(14.15149862925924), np.float64(561.6182191020889)]</t>
+  </si>
+  <si>
+    <t>[np.float64(185.98428336827732), np.float64(-167.27377016506495)]</t>
+  </si>
+  <si>
+    <t>[np.float64(434.3361891655353), np.float64(-530.6628080310528)]</t>
+  </si>
+  <si>
+    <t>[np.float64(463.7112470566021), np.float64(191.98098256165406)]</t>
+  </si>
+  <si>
+    <t>[np.float64(215.59217587425005), np.float64(-350.03527906935886)]</t>
+  </si>
+  <si>
+    <t>[np.float64(652.3821692749924), np.float64(77.83386727267452)]</t>
+  </si>
+  <si>
+    <t>[np.float64(701.043395891005), np.float64(-97.34271592356106)]</t>
+  </si>
+  <si>
+    <t>[np.float64(119.146407964278), np.float64(222.75115437612897)]</t>
+  </si>
+  <si>
+    <t>[np.float64(976.0202464464084), np.float64(533.5817985761246)]</t>
+  </si>
+  <si>
+    <t>[np.float64(664.2152869399958), np.float64(284.7709096098687)]</t>
+  </si>
+  <si>
+    <t>[np.float64(945.1237845025562), np.float64(-120.99246761456914)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.4831479646665304), np.float64(236.34612259990354)]</t>
+  </si>
+  <si>
+    <t>[np.float64(583.6288344730552), np.float64(525.5419082005646)]</t>
+  </si>
+  <si>
+    <t>[np.float64(501.22224504983626), np.float64(-155.22616193538005)]</t>
+  </si>
+  <si>
+    <t>[np.float64(477.32634085617667), np.float64(304.1558796181548)]</t>
+  </si>
+  <si>
+    <t>[np.float64(373.51558745755244), np.float64(-209.7879333868085)]</t>
+  </si>
+  <si>
+    <t>[np.float64(20.165553704077798), np.float64(-171.9502064594853)]</t>
+  </si>
+  <si>
+    <t>[np.float64(219.39488631405612), np.float64(22.99419158305591)]</t>
+  </si>
+  <si>
+    <t>[np.float64(837.8228542350686), np.float64(354.53975318118626)]</t>
+  </si>
+  <si>
+    <t>[np.float64(945.0921907506014), np.float64(146.87860377459435)]</t>
+  </si>
+  <si>
+    <t>[np.float64(131.0191961733035), np.float64(-109.90390567679532)]</t>
+  </si>
+  <si>
+    <t>[np.float64(203.28315202613024), np.float64(360.64334282188315)]</t>
+  </si>
+  <si>
+    <t>[np.float64(93.12312073733963), np.float64(280.02310658317754)]</t>
+  </si>
+  <si>
+    <t>[np.float64(200.3382841131043), np.float64(407.75082134015497)]</t>
+  </si>
+  <si>
+    <t>[np.float64(812.4187107246698), np.float64(-273.50413445744397)]</t>
+  </si>
+  <si>
+    <t>[np.float64(538.222279562979), np.float64(-257.7520605999871)]</t>
+  </si>
+  <si>
+    <t>[np.float64(189.6705020001933), np.float64(-166.34860145959345)]</t>
+  </si>
+  <si>
+    <t>[np.float64(26.83097450594707), np.float64(567.9342054749329)]</t>
+  </si>
+  <si>
+    <t>[np.float64(700.6844692526505), np.float64(558.8912137048005)]</t>
+  </si>
+  <si>
+    <t>[np.float64(794.6145983685136), np.float64(594.6621591198004)]</t>
+  </si>
+  <si>
+    <t>[np.float64(393.0478761988554), np.float64(-364.0460220202237)]</t>
+  </si>
+  <si>
+    <t>[np.float64(90.59024119140224), np.float64(250.8369821924149)]</t>
+  </si>
+  <si>
+    <t>[np.float64(820.4424317519472), np.float64(-417.4213837507958)]</t>
+  </si>
+  <si>
+    <t>[np.float64(555.4782476768544), np.float64(567.2287832629629)]</t>
+  </si>
+  <si>
+    <t>[np.float64(984.3995061556554), np.float64(-208.2806657420793)]</t>
+  </si>
+  <si>
+    <t>[np.float64(282.5561055104099), np.float64(-446.23735027539385)]</t>
+  </si>
+  <si>
+    <t>[np.float64(70.20428195548567), np.float64(559.9209360094858)]</t>
+  </si>
+  <si>
+    <t>[np.float64(203.96756225391155), np.float64(322.4779090818481)]</t>
+  </si>
+  <si>
+    <t>[np.float64(687.5589972699532), np.float64(434.0493632563862)]</t>
+  </si>
+  <si>
+    <t>[np.float64(755.4131998647512), np.float64(326.3786508609219)]</t>
+  </si>
+  <si>
+    <t>[np.float64(461.1636194676646), np.float64(535.4081029403446)]</t>
+  </si>
+  <si>
+    <t>[np.float64(454.2559485288654), np.float64(573.5031292963997)]</t>
+  </si>
+  <si>
+    <t>[np.float64(872.4307416701099), np.float64(530.4393528257685)]</t>
+  </si>
+  <si>
+    <t>[np.float64(908.9036474078899), np.float64(-551.8742799959218)]</t>
+  </si>
+  <si>
+    <t>[np.float64(215.69571359075067), np.float64(310.14369679152503)]</t>
+  </si>
+  <si>
+    <t>[np.float64(395.98461500448735), np.float64(-341.2824935905836)]</t>
+  </si>
+  <si>
+    <t>[np.float64(983.7731102592232), np.float64(-451.2735629211129)]</t>
+  </si>
+  <si>
+    <t>[np.float64(342.2093764302422), np.float64(321.2705183923397)]</t>
+  </si>
+  <si>
+    <t>[np.float64(93.74425227320859), np.float64(281.26872299301203)]</t>
+  </si>
+  <si>
+    <t>[np.float64(263.80069020060427), np.float64(385.38132621918544)]</t>
+  </si>
+  <si>
+    <t>[np.float64(556.628318435453), np.float64(237.19367670164615)]</t>
+  </si>
+  <si>
+    <t>[np.float64(635.4367704829464), np.float64(-79.59210828431446)]</t>
+  </si>
+  <si>
+    <t>[np.float64(177.99090514399074), np.float64(571.550951596872)]</t>
+  </si>
+  <si>
+    <t>[np.float64(180.2285758014044), np.float64(408.7155267650827)]</t>
+  </si>
+  <si>
+    <t>[np.float64(549.2168840305562), np.float64(118.3262019173369)]</t>
+  </si>
+  <si>
+    <t>[np.float64(395.95147885276504), np.float64(276.3934710165746)]</t>
+  </si>
+  <si>
+    <t>[np.float64(546.6457775481873), np.float64(-139.5321805713042)]</t>
+  </si>
+  <si>
+    <t>[np.float64(381.5496052711397), np.float64(143.30963545904626)]</t>
+  </si>
+  <si>
+    <t>[np.float64(324.5417649856772), np.float64(415.4339435435613)]</t>
+  </si>
+  <si>
+    <t>[np.float64(840.1044437790956), np.float64(-472.22990267787924)]</t>
+  </si>
+  <si>
+    <t>[np.float64(742.4527578394044), np.float64(123.98068629787167)]</t>
+  </si>
+  <si>
+    <t>[np.float64(630.5368077975503), np.float64(-305.5406203547234)]</t>
+  </si>
+  <si>
+    <t>[np.float64(718.045446161898), np.float64(-476.83728723625677)]</t>
+  </si>
+  <si>
+    <t>[np.float64(575.7630932211287), np.float64(275.248930121159)]</t>
+  </si>
+  <si>
+    <t>[np.float64(534.7486419538845), np.float64(535.8865958961583)]</t>
+  </si>
+  <si>
+    <t>[np.float64(413.60710427635615), np.float64(239.2543065183287)]</t>
+  </si>
+  <si>
+    <t>[np.float64(813.2512524546144), np.float64(-141.49806253292735)]</t>
+  </si>
+  <si>
+    <t>[np.float64(597.0991603049581), np.float64(-236.7633813427409)]</t>
+  </si>
+  <si>
+    <t>[np.float64(527.5271319971441), np.float64(-561.7651696333845)]</t>
+  </si>
+  <si>
+    <t>[np.float64(540.565419854791), np.float64(545.7635922628274)]</t>
+  </si>
+  <si>
+    <t>[np.float64(41.35386974078514), np.float64(-274.2023024763479)]</t>
+  </si>
+  <si>
+    <t>[np.float64(246.5804916876043), np.float64(-484.1552051909571)]</t>
+  </si>
+  <si>
+    <t>[np.float64(998.2804144402019), np.float64(42.96424887775288)]</t>
+  </si>
+  <si>
+    <t>[np.float64(708.7504662707112), np.float64(61.68220896639764)]</t>
+  </si>
+  <si>
+    <t>[np.float64(13.386382931062313), np.float64(-585.0323066862605)]</t>
+  </si>
+  <si>
+    <t>[np.float64(634.261500987582), np.float64(-588.6002304327116)]</t>
+  </si>
+  <si>
+    <t>[np.float64(141.8086371450966), np.float64(-348.70340582036545)]</t>
+  </si>
+  <si>
+    <t>[np.float64(238.52781526687772), np.float64(135.8340461911945)]</t>
+  </si>
+  <si>
+    <t>[np.float64(212.9925280022873), np.float64(129.88891946723174)]</t>
+  </si>
+  <si>
+    <t>[np.float64(674.6545226093768), np.float64(-590.7328373847735)]</t>
+  </si>
+  <si>
+    <t>[np.float64(145.88843630260985), np.float64(21.84550716816068)]</t>
+  </si>
+  <si>
+    <t>[np.float64(295.8512517470392), np.float64(-554.9047902263467)]</t>
+  </si>
+  <si>
+    <t>[np.float64(645.8259883631439), np.float64(439.823697461507)]</t>
+  </si>
+  <si>
+    <t>[np.float64(658.0121524689508), np.float64(130.50863799297065)]</t>
+  </si>
+  <si>
+    <t>[np.float64(807.532577714892), np.float64(507.3924482344014)]</t>
+  </si>
+  <si>
+    <t>[np.float64(414.8982462245701), np.float64(-236.88925488590155)]</t>
+  </si>
+  <si>
+    <t>[np.float64(684.6997883632429), np.float64(290.0677274987843)]</t>
+  </si>
+  <si>
+    <t>[np.float64(191.62042150187642), np.float64(96.0271607522551)]</t>
+  </si>
+  <si>
+    <t>[np.float64(744.9602263992206), np.float64(341.47128047324134)]</t>
+  </si>
+  <si>
+    <t>[np.float64(258.4881635097559), np.float64(371.77091214128325)]</t>
+  </si>
+  <si>
+    <t>[np.float64(888.0557656048121), np.float64(582.2488637074443)]</t>
+  </si>
+  <si>
+    <t>[np.float64(134.42743980636095), np.float64(461.57438885721035)]</t>
+  </si>
+  <si>
+    <t>[np.float64(505.30442008283984), np.float64(-551.466583199825)]</t>
+  </si>
+  <si>
+    <t>[np.float64(723.8724542766154), np.float64(-140.73485373948915)]</t>
+  </si>
+  <si>
+    <t>[np.float64(87.45394088363668), np.float64(333.2766932219156)]</t>
+  </si>
+  <si>
+    <t>[np.float64(154.1421828642241), np.float64(-479.28678064814386)]</t>
+  </si>
+  <si>
+    <t>[np.float64(488.282258940006), np.float64(-456.4386335857541)]</t>
+  </si>
+  <si>
+    <t>[np.float64(941.046495454798), np.float64(-464.2137251970977)]</t>
+  </si>
+  <si>
+    <t>[np.float64(726.151560975386), np.float64(509.1323948347447)]</t>
+  </si>
+  <si>
+    <t>[np.float64(339.49493875467994), np.float64(-314.53700028059177)]</t>
+  </si>
+  <si>
+    <t>[np.float64(401.5653848510008), np.float64(126.5026742808642)]</t>
+  </si>
+  <si>
+    <t>[np.float64(489.50422980449895), np.float64(289.03060931396215)]</t>
+  </si>
+  <si>
+    <t>[np.float64(628.5628192192663), np.float64(130.66471556885688)]</t>
+  </si>
+  <si>
+    <t>[np.float64(859.5799102150958), np.float64(-362.79779686469743)]</t>
+  </si>
+  <si>
+    <t>[np.float64(896.288491885017), np.float64(233.99028949884428)]</t>
+  </si>
+  <si>
+    <t>[np.float64(348.23404802893464), np.float64(271.8292243042639)]</t>
+  </si>
+  <si>
+    <t>[np.float64(288.22367627840606), np.float64(-203.62700321867493)]</t>
+  </si>
+  <si>
+    <t>[np.float64(15.681125431087573), np.float64(128.6039582949959)]</t>
+  </si>
+  <si>
+    <t>[np.float64(140.6762702950952), np.float64(197.53632316883693)]</t>
+  </si>
+  <si>
+    <t>[np.float64(470.6106821766565), np.float64(-340.0380347875002)]</t>
+  </si>
+  <si>
+    <t>[np.float64(261.8222215029332), np.float64(138.6381101963184)]</t>
+  </si>
+  <si>
+    <t>[np.float64(426.6432047403864), np.float64(157.17453673833836)]</t>
+  </si>
+  <si>
+    <t>[np.float64(177.543829653541), np.float64(-84.50073113770839)]</t>
+  </si>
+  <si>
+    <t>[np.float64(150.43337708507164), np.float64(-557.5122202320804)]</t>
+  </si>
+  <si>
+    <t>[np.float64(817.7010469805003), np.float64(488.9754696713385)]</t>
+  </si>
+  <si>
+    <t>[np.float64(496.48926864692834), np.float64(-551.9282110982845)]</t>
+  </si>
+  <si>
+    <t>[np.float64(690.6827322662942), np.float64(-251.40206076743618)]</t>
+  </si>
+  <si>
+    <t>[np.float64(470.4777261047447), np.float64(201.8717187023666)]</t>
+  </si>
+  <si>
+    <t>[np.float64(937.3836382381124), np.float64(82.59930503673047)]</t>
+  </si>
+  <si>
+    <t>[np.float64(895.7529506866114), np.float64(111.40527799285724)]</t>
+  </si>
+  <si>
+    <t>[np.float64(879.8471093567106), np.float64(-271.15833389141994)]</t>
+  </si>
+  <si>
+    <t>[np.float64(338.74970161846505), np.float64(539.5200583987782)]</t>
+  </si>
+  <si>
+    <t>[np.float64(401.37501405648214), np.float64(513.8282621304686)]</t>
+  </si>
+  <si>
+    <t>[np.float64(139.63616653680467), np.float64(-532.9879119743633)]</t>
+  </si>
+  <si>
+    <t>[np.float64(765.9653667637916), np.float64(272.482248178334)]</t>
+  </si>
+  <si>
+    <t>[np.float64(563.2156639282946), np.float64(-129.31885357023515)]</t>
+  </si>
+  <si>
+    <t>[np.float64(442.99409766318973), np.float64(410.41840477774895)]</t>
+  </si>
+  <si>
+    <t>[np.float64(209.8911298790932), np.float64(-417.84333933603085)]</t>
+  </si>
+  <si>
+    <t>[np.float64(182.2493119931007), np.float64(165.13120246278697)]</t>
+  </si>
+  <si>
+    <t>[np.float64(851.689877787838), np.float64(-360.84237213255886)]</t>
+  </si>
+  <si>
+    <t>[np.float64(103.19533044620476), np.float64(278.30702705577335)]</t>
+  </si>
+  <si>
+    <t>[np.float64(481.7431632141387), np.float64(-406.27185781066487)]</t>
+  </si>
+  <si>
+    <t>[np.float64(298.25405272246064), np.float64(-490.36614509295123)]</t>
+  </si>
+  <si>
+    <t>[np.float64(767.0409270493069), np.float64(421.37224865942574)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.172776786383724), np.float64(-327.2513035778614)]</t>
+  </si>
+  <si>
+    <t>[np.float64(247.28072194537276), np.float64(-186.51647615454038)]</t>
+  </si>
+  <si>
+    <t>[np.float64(708.892299484124), np.float64(156.5736003969149)]</t>
+  </si>
+  <si>
+    <t>[np.float64(194.78227692569206), np.float64(424.5773520194816)]</t>
+  </si>
+  <si>
+    <t>[np.float64(607.4554131844488), np.float64(244.44709677542357)]</t>
+  </si>
+  <si>
+    <t>[np.float64(266.4032517805803), np.float64(68.29380820399854)]</t>
+  </si>
+  <si>
+    <t>[np.float64(897.3212526953962), np.float64(-153.44684016543636)]</t>
+  </si>
+  <si>
+    <t>[np.float64(998.412394307856), np.float64(277.46882689379845)]</t>
+  </si>
+  <si>
+    <t>[np.float64(942.2701058317155), np.float64(-228.30351036097858)]</t>
+  </si>
+  <si>
+    <t>[np.float64(173.39249748494413), np.float64(-158.20781201551677)]</t>
+  </si>
+  <si>
+    <t>[np.float64(433.64129026601995), np.float64(500.0560350220708)]</t>
+  </si>
+  <si>
+    <t>[np.float64(714.0126470852368), np.float64(169.88830674300038)]</t>
+  </si>
+  <si>
+    <t>[np.float64(350.3420086079129), np.float64(3.6145602282333584)]</t>
+  </si>
+  <si>
+    <t>[np.float64(841.0045347371265), np.float64(426.14637331756035)]</t>
+  </si>
+  <si>
+    <t>[np.float64(554.2982338504763), np.float64(576.7987618388329)]</t>
+  </si>
+  <si>
+    <t>[np.float64(595.8310807136836), np.float64(179.25790108995636)]</t>
+  </si>
+  <si>
+    <t>[np.float64(904.9364597710526), np.float64(-287.810426903992)]</t>
+  </si>
+  <si>
+    <t>[np.float64(88.32960259151767), np.float64(-465.90062426460105)]</t>
+  </si>
+  <si>
+    <t>[np.float64(900.0438359943789), np.float64(-315.912235737523)]</t>
+  </si>
+  <si>
+    <t>[np.float64(911.9639949786273), np.float64(-338.23908787764736)]</t>
+  </si>
+  <si>
+    <t>[np.float64(959.3316696144321), np.float64(-544.6331616933871)]</t>
+  </si>
+  <si>
+    <t>[np.float64(444.7336635594851), np.float64(156.8816993282952)]</t>
+  </si>
+  <si>
+    <t>[np.float64(894.4103505242356), np.float64(35.18026141860753)]</t>
+  </si>
+  <si>
+    <t>[np.float64(643.4177757210625), np.float64(504.9422094204897)]</t>
+  </si>
+  <si>
+    <t>[np.float64(634.3839397724964), np.float64(53.313991578627906)]</t>
+  </si>
+  <si>
+    <t>[np.float64(855.384910216074), np.float64(326.0204129896007)]</t>
+  </si>
+  <si>
+    <t>[np.float64(665.396711258507), np.float64(501.8492055075185)]</t>
+  </si>
+  <si>
+    <t>[np.float64(44.833928684685716), np.float64(448.39750643994284)]</t>
+  </si>
+  <si>
+    <t>[np.float64(288.0882640453397), np.float64(-424.66463797304186)]</t>
+  </si>
+  <si>
+    <t>[np.float64(9.304571966347375), np.float64(-171.29436841578138)]</t>
+  </si>
+  <si>
+    <t>[np.float64(460.9182981489225), np.float64(273.19460073190305)]</t>
+  </si>
+  <si>
+    <t>[np.float64(254.9157998221423), np.float64(-549.8762255249433)]</t>
+  </si>
+  <si>
+    <t>[np.float64(597.54277811349), np.float64(449.2281904053839)]</t>
+  </si>
+  <si>
+    <t>[np.float64(150.75858872860204), np.float64(179.27539301485353)]</t>
+  </si>
+  <si>
+    <t>[np.float64(441.6683287516231), np.float64(-102.9943138979549)]</t>
+  </si>
+  <si>
+    <t>[np.float64(947.3145974279182), np.float64(247.3557299703574)]</t>
+  </si>
+  <si>
+    <t>[np.float64(271.7010180551106), np.float64(50.74748664093045)]</t>
+  </si>
+  <si>
+    <t>[np.float64(334.16398515921765), np.float64(-403.47067345250963)]</t>
+  </si>
+  <si>
+    <t>[np.float64(772.6170335733326), np.float64(-327.39600020927463)]</t>
+  </si>
+  <si>
+    <t>[np.float64(794.9549504954423), np.float64(383.61921763469934)]</t>
+  </si>
+  <si>
+    <t>[np.float64(290.17519777212976), np.float64(100.89405901126588)]</t>
+  </si>
+  <si>
+    <t>[np.float64(275.68337792572527), np.float64(-550.881064930546)]</t>
+  </si>
+  <si>
+    <t>[np.float64(373.6517611386747), np.float64(420.84190038275665)]</t>
+  </si>
+  <si>
+    <t>[np.float64(952.1754704414918), np.float64(494.3993204532269)]</t>
+  </si>
+  <si>
+    <t>[np.float64(617.0759747812268), np.float64(-164.23356948166702)]</t>
+  </si>
+  <si>
+    <t>[np.float64(795.1601219451871), np.float64(-349.96679709093235)]</t>
+  </si>
+  <si>
+    <t>[np.float64(151.63224490522842), np.float64(56.21290717765112)]</t>
+  </si>
+  <si>
+    <t>[np.float64(692.5158930806858), np.float64(146.11959004306232)]</t>
+  </si>
+  <si>
+    <t>[np.float64(89.84948370985579), np.float64(421.1263779005353)]</t>
+  </si>
+  <si>
+    <t>[np.float64(104.2856691738837), np.float64(-193.9337152271769)]</t>
+  </si>
+  <si>
+    <t>[np.float64(752.8115471006482), np.float64(-370.0477396572057)]</t>
+  </si>
+  <si>
+    <t>[np.float64(863.2932275158705), np.float64(21.32478990187451)]</t>
+  </si>
+  <si>
+    <t>[np.float64(25.226366430430858), np.float64(152.9953349663026)]</t>
+  </si>
+  <si>
+    <t>[np.float64(541.8352469752075), np.float64(94.35487119062122)]</t>
+  </si>
+  <si>
+    <t>[np.float64(312.3461290003624), np.float64(456.8681701479022)]</t>
+  </si>
+  <si>
+    <t>[np.float64(376.4938238485204), np.float64(223.10671968457416)]</t>
+  </si>
+  <si>
+    <t>[np.float64(865.321988288673), np.float64(-164.22157247552263)]</t>
+  </si>
+  <si>
+    <t>[np.float64(70.02856347945064), np.float64(177.56119209479368)]</t>
+  </si>
+  <si>
+    <t>[np.float64(565.0448594768139), np.float64(-247.39998477869574)]</t>
+  </si>
+  <si>
+    <t>[np.float64(341.5099863919603), np.float64(142.10433912760368)]</t>
+  </si>
+  <si>
+    <t>[np.float64(214.36165715001988), np.float64(265.4601822578728)]</t>
+  </si>
+  <si>
+    <t>[np.float64(398.4622625934269), np.float64(131.25020212320783)]</t>
+  </si>
+  <si>
+    <t>[np.float64(107.37242131813962), np.float64(-163.89198236839718)]</t>
+  </si>
+  <si>
+    <t>[np.float64(567.5680317521994), np.float64(-178.31834976958083)]</t>
+  </si>
+  <si>
+    <t>[np.float64(992.0514314738123), np.float64(76.15448680196221)]</t>
+  </si>
+  <si>
+    <t>[np.float64(627.0457757302673), np.float64(316.8945016979279)]</t>
+  </si>
+  <si>
+    <t>[np.float64(434.8025138188032), np.float64(554.1910539320884)]</t>
+  </si>
+  <si>
+    <t>[np.float64(89.71560795722111), np.float64(56.17526251434572)]</t>
+  </si>
+  <si>
+    <t>[np.float64(613.028034987524), np.float64(327.92801166670415)]</t>
+  </si>
+  <si>
+    <t>[np.float64(616.8558823658472), np.float64(-272.55634165841883)]</t>
+  </si>
+  <si>
+    <t>[np.float64(201.07043107823452), np.float64(323.0529057682827)]</t>
+  </si>
+  <si>
+    <t>[np.float64(914.3651490644684), np.float64(-70.32077907583187)]</t>
+  </si>
+  <si>
+    <t>[np.float64(498.9940456972365), np.float64(530.9735077158414)]</t>
+  </si>
+  <si>
+    <t>[np.float64(187.87619002770083), np.float64(-197.40151842576682)]</t>
+  </si>
+  <si>
+    <t>[np.float64(547.5862141732126), np.float64(-224.94073907968703)]</t>
+  </si>
+  <si>
+    <t>[np.float64(64.50802339465234), np.float64(-238.6940860254158)]</t>
+  </si>
+  <si>
+    <t>[np.float64(731.7655160271025), np.float64(190.03679519214575)]</t>
+  </si>
+  <si>
+    <t>[np.float64(643.5759256343068), np.float64(-516.5150533806275)]</t>
+  </si>
+  <si>
+    <t>[np.float64(809.7757979166374), np.float64(-543.5580030633662)]</t>
+  </si>
+  <si>
+    <t>[np.float64(49.166774335870244), np.float64(-518.0631493142158)]</t>
+  </si>
+  <si>
+    <t>[np.float64(229.83962675853653), np.float64(-445.02625219697217)]</t>
+  </si>
+  <si>
+    <t>[np.float64(328.58268167487626), np.float64(-428.82462163977186)]</t>
+  </si>
+  <si>
+    <t>[np.float64(641.3559413434709), np.float64(-195.0710121862968)]</t>
+  </si>
+  <si>
+    <t>[np.float64(788.0967662701823), np.float64(-104.66745987417806)]</t>
+  </si>
+  <si>
+    <t>[np.float64(360.2717371299985), np.float64(-498.2688621645741)]</t>
+  </si>
+  <si>
+    <t>[np.float64(904.6268933988368), np.float64(95.90094636820595)]</t>
+  </si>
+  <si>
+    <t>[np.float64(451.7108243317712), np.float64(586.8092794300696)]</t>
+  </si>
+  <si>
+    <t>[np.float64(248.67057618009682), np.float64(471.1802354101653)]</t>
+  </si>
+  <si>
+    <t>[np.float64(77.96270590008503), np.float64(-486.3194073910133)]</t>
+  </si>
+  <si>
+    <t>[np.float64(499.64424827191846), np.float64(536.5217187470566)]</t>
+  </si>
+  <si>
+    <t>[np.float64(557.6299732540651), np.float64(95.42619595854921)]</t>
+  </si>
+  <si>
+    <t>[np.float64(391.64534279501373), np.float64(596.4451013198914)]</t>
+  </si>
+  <si>
+    <t>[np.float64(555.485781267054), np.float64(554.1771595993766)]</t>
+  </si>
+  <si>
+    <t>[np.float64(328.92152787069506), np.float64(-565.3154966093891)]</t>
+  </si>
+  <si>
+    <t>[np.float64(673.480366598161), np.float64(-168.87500428076947)]</t>
+  </si>
+  <si>
+    <t>[np.float64(151.5862708468434), np.float64(-494.57555824971314)]</t>
+  </si>
+  <si>
+    <t>[np.float64(845.67801248341), np.float64(75.48855488041693)]</t>
+  </si>
+  <si>
+    <t>[np.float64(404.36484646216775), np.float64(346.32728679695526)]</t>
+  </si>
+  <si>
+    <t>[np.float64(774.145346900322), np.float64(-201.62410647786476)]</t>
+  </si>
+  <si>
+    <t>[np.float64(63.00221153387231), np.float64(397.77180700677866)]</t>
+  </si>
+  <si>
+    <t>[np.float64(725.1557366727909), np.float64(-379.4179946160509)]</t>
+  </si>
+  <si>
+    <t>[np.float64(165.76303114725033), np.float64(-253.6361910548971)]</t>
+  </si>
+  <si>
+    <t>[np.float64(159.70366469744246), np.float64(-469.17846724190395)]</t>
+  </si>
+  <si>
+    <t>[np.float64(818.5506318317293), np.float64(501.7960769079057)]</t>
+  </si>
+  <si>
+    <t>[np.float64(760.0766507268971), np.float64(481.20873831918175)]</t>
+  </si>
+  <si>
+    <t>[np.float64(221.99294447040586), np.float64(-224.22739868191945)]</t>
+  </si>
+  <si>
+    <t>[np.float64(985.2732302619306), np.float64(135.80331186109618)]</t>
+  </si>
+  <si>
+    <t>[np.float64(665.6184403003178), np.float64(442.7056017373652)]</t>
+  </si>
+  <si>
+    <t>[np.float64(82.10670848974289), np.float64(420.86625309968485)]</t>
+  </si>
+  <si>
+    <t>[np.float64(811.040118952639), np.float64(336.0808958589315)]</t>
+  </si>
+  <si>
+    <t>[np.float64(626.4893114231055), np.float64(-311.6273256971647)]</t>
+  </si>
+  <si>
+    <t>[np.float64(665.0360296861982), np.float64(-469.19672805133735)]</t>
+  </si>
+  <si>
+    <t>[np.float64(719.8039872871703), np.float64(165.24420357720862)]</t>
+  </si>
+  <si>
+    <t>[np.float64(575.6689167493246), np.float64(-280.35335576131104)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.279239774592212), np.float64(-206.26249098859785)]</t>
+  </si>
+  <si>
+    <t>[np.float64(397.64292082753207), np.float64(136.89879902918415)]</t>
+  </si>
+  <si>
+    <t>[np.float64(383.276904958322), np.float64(145.71338202517063)]</t>
+  </si>
+  <si>
+    <t>[np.float64(209.41015149723597), np.float64(-533.4120479843538)]</t>
+  </si>
+  <si>
+    <t>[np.float64(857.1940108122375), np.float64(481.4145011244343)]</t>
+  </si>
+  <si>
+    <t>[np.float64(853.047902807916), np.float64(-261.19318732988864)]</t>
+  </si>
+  <si>
+    <t>[np.float64(73.01139171929837), np.float64(482.21187657323344)]</t>
+  </si>
+  <si>
+    <t>[np.float64(755.8487296539059), np.float64(-198.10234301808254)]</t>
+  </si>
+  <si>
+    <t>[np.float64(900.6456049925168), np.float64(301.45042768199096)]</t>
+  </si>
+  <si>
+    <t>[np.float64(809.2977614581133), np.float64(358.5512898305258)]</t>
+  </si>
+  <si>
+    <t>[np.float64(414.86090613822824), np.float64(525.9672627628254)]</t>
+  </si>
+  <si>
+    <t>[np.float64(881.6757691889454), np.float64(89.56366815585568)]</t>
+  </si>
+  <si>
+    <t>[np.float64(428.4252833476638), np.float64(-463.5695259156404)]</t>
+  </si>
+  <si>
+    <t>[np.float64(98.05536508439295), np.float64(-224.95002791446467)]</t>
+  </si>
+  <si>
+    <t>[np.float64(456.8121653890188), np.float64(524.6832390436962)]</t>
+  </si>
+  <si>
+    <t>[np.float64(136.17221188978323), np.float64(207.7070642953878)]</t>
+  </si>
+  <si>
+    <t>[np.float64(57.563915345893115), np.float64(500.2353339646727)]</t>
+  </si>
+  <si>
+    <t>[np.float64(293.18554830200793), np.float64(358.46167144859953)]</t>
+  </si>
+  <si>
+    <t>[np.float64(325.5710390715171), np.float64(-316.0128323790581)]</t>
+  </si>
+  <si>
+    <t>[np.float64(168.7108949176882), np.float64(142.5946880242583)]</t>
+  </si>
+  <si>
+    <t>[np.float64(948.0819889864953), np.float64(-426.8307957671822)]</t>
+  </si>
+  <si>
+    <t>[np.float64(275.77087165807967), np.float64(454.6360140436293)]</t>
+  </si>
+  <si>
+    <t>[np.float64(398.39684133154185), np.float64(412.75637254759874)]</t>
+  </si>
+  <si>
+    <t>[np.float64(885.4155195023803), np.float64(273.3955170738775)]</t>
+  </si>
+  <si>
+    <t>[np.float64(353.6828867807162), np.float64(17.63063047689286)]</t>
+  </si>
+  <si>
+    <t>[np.float64(892.5830079125583), np.float64(499.04910345383496)]</t>
+  </si>
+  <si>
+    <t>[np.float64(598.465799035888), np.float64(335.2192095585773)]</t>
+  </si>
+  <si>
+    <t>[np.float64(815.5407805045319), np.float64(-505.70371023041264)]</t>
+  </si>
+  <si>
+    <t>[np.float64(314.22275324506876), np.float64(255.4402889362991)]</t>
+  </si>
+  <si>
+    <t>[np.float64(131.1492869388544), np.float64(456.9734125763566)]</t>
+  </si>
+  <si>
+    <t>[np.float64(777.6874860034784), np.float64(71.7647275600458)]</t>
+  </si>
+  <si>
+    <t>[np.float64(175.01388560368304), np.float64(-586.4091842231044)]</t>
+  </si>
+  <si>
+    <t>[np.float64(347.7735187174409), np.float64(417.8189442469653)]</t>
+  </si>
+  <si>
+    <t>[np.float64(42.88666192993129), np.float64(378.5422250885698)]</t>
+  </si>
+  <si>
+    <t>[np.float64(826.3953634706803), np.float64(501.9731399757734)]</t>
+  </si>
+  <si>
+    <t>[np.float64(155.93850559922052), np.float64(8.090287182983616)]</t>
+  </si>
+  <si>
+    <t>[np.float64(117.67727425982433), np.float64(-115.43711921731807)]</t>
+  </si>
+  <si>
+    <t>[np.float64(862.1326671776791), np.float64(-363.9903536628707)]</t>
+  </si>
+  <si>
+    <t>[np.float64(693.366389923262), np.float64(347.1666375123043)]</t>
+  </si>
+  <si>
+    <t>[np.float64(773.3428903977476), np.float64(44.08359188512327)]</t>
+  </si>
+  <si>
+    <t>[np.float64(457.5461273391336), np.float64(-500.3187301938556)]</t>
+  </si>
+  <si>
+    <t>[np.float64(666.2621512887866), np.float64(235.4997356629409)]</t>
+  </si>
+  <si>
+    <t>[np.float64(945.2053789070698), np.float64(-508.5647511603946)]</t>
+  </si>
+  <si>
+    <t>[np.float64(104.61461624056578), np.float64(565.7909184657235)]</t>
+  </si>
+  <si>
+    <t>[np.float64(354.50372691497813), np.float64(-458.96253212986244)]</t>
+  </si>
+  <si>
+    <t>[np.float64(993.8160274453535), np.float64(174.66101673983485)]</t>
+  </si>
+  <si>
+    <t>[np.float64(198.54030793369492), np.float64(-154.70656451439646)]</t>
+  </si>
+  <si>
+    <t>[np.float64(897.5556140672627), np.float64(-328.98475250707986)]</t>
+  </si>
+  <si>
+    <t>[np.float64(254.9604841674642), np.float64(-403.04492850341563)]</t>
+  </si>
+  <si>
+    <t>[np.float64(642.2616984863259), np.float64(-416.3965499280961)]</t>
+  </si>
+  <si>
+    <t>[np.float64(186.2293582232306), np.float64(581.4746168327681)]</t>
+  </si>
+  <si>
+    <t>[np.float64(171.11098528857337), np.float64(-579.5702857080532)]</t>
+  </si>
+  <si>
+    <t>[np.float64(334.9469924607317), np.float64(286.65004631075453)]</t>
+  </si>
+  <si>
+    <t>[np.float64(696.4755775295139), np.float64(-514.0714782628168)]</t>
+  </si>
+  <si>
+    <t>[np.float64(191.55785727211781), np.float64(481.5250810715322)]</t>
+  </si>
+  <si>
+    <t>[np.float64(83.65943379514972), np.float64(-107.65893823330225)]</t>
+  </si>
+  <si>
+    <t>[np.float64(102.16115659501635), np.float64(75.54042846939603)]</t>
+  </si>
+  <si>
+    <t>[np.float64(872.3353983792802), np.float64(-472.75587265295536)]</t>
+  </si>
+  <si>
+    <t>[np.float64(686.3366164585367), np.float64(-121.70669234580623)]</t>
+  </si>
+  <si>
+    <t>[np.float64(803.2140004850611), np.float64(-266.36069705961665)]</t>
+  </si>
+  <si>
+    <t>[np.float64(852.6364417831876), np.float64(-403.6429417349681)]</t>
+  </si>
+  <si>
+    <t>[np.float64(885.7957124301291), np.float64(272.1248162512877)]</t>
+  </si>
+  <si>
+    <t>[np.float64(317.0272911157026), np.float64(577.9668357418298)]</t>
+  </si>
+  <si>
+    <t>[np.float64(830.1937884644108), np.float64(-244.19891743076164)]</t>
+  </si>
+  <si>
+    <t>[np.float64(614.3929997869701), np.float64(-548.7259350466153)]</t>
+  </si>
+  <si>
+    <t>[np.float64(618.6154083854487), np.float64(512.3415465392197)]</t>
+  </si>
+  <si>
+    <t>[np.float64(612.6345357997698), np.float64(557.9924307827596)]</t>
+  </si>
+  <si>
+    <t>[np.float64(801.6567891443281), np.float64(252.75092312865922)]</t>
+  </si>
+  <si>
+    <t>[np.float64(180.38685001818533), np.float64(-189.40754359370015)]</t>
+  </si>
+  <si>
+    <t>[np.float64(308.13769871568974), np.float64(-481.9088829693183)]</t>
+  </si>
+  <si>
+    <t>[np.float64(281.7815410498634), np.float64(538.0593377003888)]</t>
+  </si>
+  <si>
+    <t>[np.float64(904.0315862696029), np.float64(24.46575997203695)]</t>
+  </si>
+  <si>
+    <t>[np.float64(6.877933343942488), np.float64(-224.4304209955227)]</t>
+  </si>
+  <si>
+    <t>[np.float64(108.39002774521822), np.float64(308.3727547061013)]</t>
+  </si>
+  <si>
+    <t>[np.float64(455.14691382768314), np.float64(586.4533995628135)]</t>
+  </si>
+  <si>
+    <t>[np.float64(225.6139393916391), np.float64(226.88430203031498)]</t>
+  </si>
+  <si>
+    <t>[np.float64(596.5682773362287), np.float64(459.61893083948803)]</t>
+  </si>
+  <si>
+    <t>[np.float64(269.3128121208026), np.float64(438.4038296479828)]</t>
+  </si>
+  <si>
+    <t>[np.float64(898.6456936882755), np.float64(-87.1082743564316)]</t>
+  </si>
+  <si>
+    <t>[np.float64(35.05899596481721), np.float64(185.74230321967673)]</t>
+  </si>
+  <si>
+    <t>[np.float64(223.1919541025058), np.float64(395.710714263402)]</t>
+  </si>
+  <si>
+    <t>[np.float64(495.0579270609906), np.float64(359.7952513023487)]</t>
+  </si>
+  <si>
+    <t>[np.float64(421.64511575608964), np.float64(252.96472391266627)]</t>
+  </si>
+  <si>
+    <t>[np.float64(850.8744681763507), np.float64(361.5062768963114)]</t>
+  </si>
+  <si>
+    <t>[np.float64(606.5552740267345), np.float64(-306.7404895346928)]</t>
+  </si>
+  <si>
+    <t>[np.float64(846.4685695853875), np.float64(-328.8975302262332)]</t>
+  </si>
+  <si>
+    <t>[np.float64(925.0007975498845), np.float64(-282.7410860982977)]</t>
+  </si>
+  <si>
+    <t>[np.float64(199.01917233580468), np.float64(-194.86967875858085)]</t>
+  </si>
+  <si>
+    <t>[np.float64(147.21796843667923), np.float64(168.8329122300803)]</t>
+  </si>
+  <si>
+    <t>[np.float64(672.2600072992946), np.float64(498.06943658508726)]</t>
+  </si>
+  <si>
+    <t>[np.float64(786.1898190599867), np.float64(419.1730353601017)]</t>
+  </si>
+  <si>
+    <t>[np.float64(417.585075442512), np.float64(80.77969677922204)]</t>
+  </si>
+  <si>
+    <t>[np.float64(666.8972009023792), np.float64(372.09590836577866)]</t>
+  </si>
+  <si>
+    <t>[np.float64(719.417170291803), np.float64(501.26073859436383)]</t>
+  </si>
+  <si>
+    <t>[np.float64(415.28453212436887), np.float64(-216.80918146748894)]</t>
+  </si>
+  <si>
+    <t>[np.float64(897.3130351909143), np.float64(289.6413361071134)]</t>
+  </si>
+  <si>
+    <t>[np.float64(475.5636504051841), np.float64(-230.8113558087523)]</t>
+  </si>
+  <si>
+    <t>[np.float64(134.04062210162093), np.float64(130.68328617309373)]</t>
+  </si>
+  <si>
+    <t>[np.float64(293.06017319669843), np.float64(-379.8390667918816)]</t>
+  </si>
+  <si>
+    <t>[np.float64(878.8626408358267), np.float64(52.580509074318)]</t>
+  </si>
+  <si>
+    <t>[np.float64(100.82717220953074), np.float64(-83.74403354452033)]</t>
+  </si>
+  <si>
+    <t>[np.float64(484.49865089122125), np.float64(-488.22412437428494)]</t>
+  </si>
+  <si>
+    <t>[np.float64(490.1440485557356), np.float64(-401.51638240637334)]</t>
+  </si>
+  <si>
+    <t>[np.float64(942.8952126819504), np.float64(-520.8268394964585)]</t>
+  </si>
+  <si>
+    <t>[np.float64(862.6283249154034), np.float64(284.90865957365736)]</t>
+  </si>
+  <si>
+    <t>[np.float64(895.9896151293317), np.float64(509.8871321343704)]</t>
+  </si>
+  <si>
+    <t>[np.float64(165.6363079310983), np.float64(52.27277662736765)]</t>
+  </si>
+  <si>
+    <t>[np.float64(83.08283875374667), np.float64(-364.7589253581199)]</t>
+  </si>
+  <si>
+    <t>[np.float64(227.03683467787982), np.float64(-341.8447630874894)]</t>
+  </si>
+  <si>
+    <t>[np.float64(677.848016564996), np.float64(-449.8410303922177)]</t>
+  </si>
+  <si>
+    <t>[np.float64(879.9276907423919), np.float64(454.4234040675117)]</t>
+  </si>
+  <si>
+    <t>[np.float64(994.5099833026043), np.float64(-546.410103963047)]</t>
+  </si>
+  <si>
+    <t>[np.float64(466.4435885667434), np.float64(365.25774444631406)]</t>
+  </si>
+  <si>
+    <t>[np.float64(895.5019828682791), np.float64(-201.02447300268784)]</t>
+  </si>
+  <si>
+    <t>[np.float64(942.3078255020844), np.float64(190.478437144998)]</t>
+  </si>
+  <si>
+    <t>[np.float64(671.5060100606352), np.float64(-274.23653153388545)]</t>
+  </si>
+  <si>
+    <t>[np.float64(945.6208447346685), np.float64(89.6870569269289)]</t>
+  </si>
+  <si>
+    <t>[np.float64(429.43108731059556), np.float64(386.1700613301613)]</t>
+  </si>
+  <si>
+    <t>[np.float64(617.071197618564), np.float64(439.9350943256195)]</t>
+  </si>
+  <si>
+    <t>[np.float64(487.571607394514), np.float64(-373.80871041078615)]</t>
+  </si>
+  <si>
+    <t>[np.float64(619.6904861691116), np.float64(-480.66028637095394)]</t>
+  </si>
+  <si>
+    <t>[np.float64(898.1145055971177), np.float64(178.75492581130356)]</t>
+  </si>
+  <si>
+    <t>[np.float64(802.7253759559368), np.float64(210.6843067758499)]</t>
+  </si>
+  <si>
+    <t>[np.float64(885.8388203655737), np.float64(-94.25623592304817)]</t>
+  </si>
+  <si>
+    <t>[np.float64(646.7515512027185), np.float64(-531.2558272480351)]</t>
+  </si>
+  <si>
+    <t>[np.float64(575.9587405697678), np.float64(-302.41036003012994)]</t>
+  </si>
+  <si>
+    <t>[np.float64(568.6831131612491), np.float64(472.8787381301129)]</t>
+  </si>
+  <si>
+    <t>[np.float64(91.7481023417167), np.float64(244.17513416848897)]</t>
+  </si>
+  <si>
+    <t>[np.float64(952.4827208612303), np.float64(415.6730099675676)]</t>
+  </si>
+  <si>
+    <t>[np.float64(697.7973131983433), np.float64(-589.1143972548892)]</t>
+  </si>
+  <si>
+    <t>[np.float64(491.88920651254875), np.float64(188.36243554415876)]</t>
+  </si>
+  <si>
+    <t>[np.float64(881.6906378564968), np.float64(191.39537267535104)]</t>
+  </si>
+  <si>
+    <t>[np.float64(612.4206652998912), np.float64(-591.8218230929646)]</t>
+  </si>
+  <si>
+    <t>[np.float64(964.6181914892935), np.float64(-466.4334990213817)]</t>
+  </si>
+  <si>
+    <t>[np.float64(96.45142493103442), np.float64(-395.1492713741454)]</t>
+  </si>
+  <si>
+    <t>[np.float64(482.09607472306794), np.float64(-407.5647833561131)]</t>
+  </si>
+  <si>
+    <t>[np.float64(325.1027950942967), np.float64(-97.64222591015812)]</t>
+  </si>
+  <si>
+    <t>[np.float64(678.3598059312216), np.float64(-154.8088828224183)]</t>
+  </si>
+  <si>
+    <t>[np.float64(371.784329566671), np.float64(-135.11294365680203)]</t>
+  </si>
+  <si>
+    <t>[np.float64(614.9284392360983), np.float64(-184.8898347341476)]</t>
+  </si>
+  <si>
+    <t>[np.float64(906.9720259174428), np.float64(19.285121239813066)]</t>
+  </si>
+  <si>
+    <t>[np.float64(522.1481068306748), np.float64(-358.8653403885349)]</t>
+  </si>
+  <si>
+    <t>[np.float64(190.07778982311086), np.float64(365.1891879712455)]</t>
+  </si>
+  <si>
+    <t>[np.float64(785.5870981280106), np.float64(-498.7927409387369)]</t>
+  </si>
+  <si>
+    <t>[np.float64(255.57141775657232), np.float64(-425.1432525319399)]</t>
+  </si>
+  <si>
+    <t>[np.float64(441.52868081258333), np.float64(573.8159040345245)]</t>
+  </si>
+  <si>
+    <t>[np.float64(121.74387794073593), np.float64(21.215763839619058)]</t>
+  </si>
+  <si>
+    <t>[np.float64(167.6277640616609), np.float64(579.1814202258345)]</t>
+  </si>
+  <si>
+    <t>[np.float64(102.70309773392717), np.float64(-503.97277332159945)]</t>
+  </si>
+  <si>
+    <t>[np.float64(953.35184762691), np.float64(285.2291729295953)]</t>
+  </si>
+  <si>
+    <t>[np.float64(113.60934372784625), np.float64(-568.2749411427855)]</t>
+  </si>
+  <si>
+    <t>[np.float64(353.3320499308058), np.float64(485.44994228804285)]</t>
+  </si>
+  <si>
+    <t>[np.float64(616.372176220192), np.float64(25.948827712159073)]</t>
+  </si>
+  <si>
+    <t>[np.float64(828.9264100897443), np.float64(346.0913200303596)]</t>
+  </si>
+  <si>
+    <t>[np.float64(870.9565763965485), np.float64(581.9800542696134)]</t>
+  </si>
+  <si>
+    <t>[np.float64(280.8884375490697), np.float64(245.25425975090752)]</t>
+  </si>
+  <si>
+    <t>[np.float64(400.6815152877512), np.float64(-217.8031068999448)]</t>
+  </si>
+  <si>
+    <t>[np.float64(873.3359296596118), np.float64(389.14872543526667)]</t>
+  </si>
+  <si>
+    <t>[np.float64(548.0632575218974), np.float64(-383.96377215442584)]</t>
+  </si>
+  <si>
+    <t>[np.float64(425.7187827119322), np.float64(519.874844314123)]</t>
+  </si>
+  <si>
+    <t>[np.float64(507.03390134711765), np.float64(218.6691323529983)]</t>
+  </si>
+  <si>
+    <t>[np.float64(465.9225067374381), np.float64(318.6473692799051)]</t>
+  </si>
+  <si>
+    <t>[np.float64(959.136980051234), np.float64(445.1711756245718)]</t>
+  </si>
+  <si>
+    <t>[np.float64(485.083973502445), np.float64(500.38798193802154)]</t>
+  </si>
+  <si>
+    <t>[np.float64(282.48504664839925), np.float64(-341.74611370266604)]</t>
+  </si>
+  <si>
+    <t>[np.float64(805.627798295162), np.float64(-466.7468823217453)]</t>
+  </si>
+  <si>
+    <t>[np.float64(517.0803944828712), np.float64(113.92789714796652)]</t>
+  </si>
+  <si>
+    <t>[np.float64(843.8743008706937), np.float64(-332.8376002040379)]</t>
+  </si>
+  <si>
+    <t>[np.float64(591.4904149011921), np.float64(449.3851573834563)]</t>
+  </si>
+  <si>
+    <t>[np.float64(343.9701973563027), np.float64(144.77688384992337)]</t>
+  </si>
+  <si>
+    <t>[np.float64(344.0695058110189), np.float64(475.0600395835547)]</t>
+  </si>
+  <si>
+    <t>[np.float64(700.6888458570652), np.float64(115.82970746568003)]</t>
+  </si>
+  <si>
+    <t>[np.float64(70.8547207257998), np.float64(296.1402399682057)]</t>
+  </si>
+  <si>
+    <t>[np.float64(893.9735070367467), np.float64(74.08726234556218)]</t>
+  </si>
+  <si>
+    <t>[np.float64(237.14583762172668), np.float64(-422.926807728574)]</t>
+  </si>
+  <si>
+    <t>[np.float64(251.2971788291869), np.float64(220.72790708913897)]</t>
+  </si>
+  <si>
+    <t>[np.float64(707.6261899757739), np.float64(-583.9294272020611)]</t>
+  </si>
+  <si>
+    <t>[np.float64(749.5505730071142), np.float64(357.87145633232626)]</t>
+  </si>
+  <si>
+    <t>[np.float64(882.8659459124643), np.float64(529.5239819108763)]</t>
+  </si>
+  <si>
+    <t>[np.float64(267.02343879345415), np.float64(-555.5242505984074)]</t>
+  </si>
+  <si>
+    <t>[np.float64(616.7149580735014), np.float64(34.025712572612406)]</t>
+  </si>
+  <si>
+    <t>[np.float64(880.4379537216665), np.float64(-288.2748991856356)]</t>
+  </si>
+  <si>
+    <t>[np.float64(50.76674038147111), np.float64(-483.90057854574115)]</t>
+  </si>
+  <si>
+    <t>[np.float64(929.6758430761632), np.float64(564.7340248980381)]</t>
+  </si>
+  <si>
+    <t>[np.float64(626.7183130940018), np.float64(-279.72606645804615)]</t>
+  </si>
+  <si>
+    <t>[np.float64(490.42316376298334), np.float64(360.52559522104616)]</t>
+  </si>
+  <si>
+    <t>[np.float64(660.2407540372827), np.float64(565.085075010071)]</t>
+  </si>
+  <si>
+    <t>[np.float64(103.70301545136829), np.float64(-330.6036129798723)]</t>
+  </si>
+  <si>
+    <t>[np.float64(945.4248106625057), np.float64(298.57412281262543)]</t>
+  </si>
+  <si>
+    <t>[np.float64(305.9891250514277), np.float64(-305.7694118195952)]</t>
+  </si>
+  <si>
+    <t>[np.float64(898.1193106535386), np.float64(-557.6302630464611)]</t>
+  </si>
+  <si>
+    <t>[np.float64(216.55842241003242), np.float64(239.98010286563317)]</t>
+  </si>
+  <si>
+    <t>[np.float64(530.1708028349394), np.float64(-177.91600296474616)]</t>
+  </si>
+  <si>
+    <t>[np.float64(485.9790905960849), np.float64(152.03656114935131)]</t>
+  </si>
+  <si>
+    <t>[np.float64(517.1068949915824), np.float64(-341.066931651036)]</t>
+  </si>
+  <si>
+    <t>[np.float64(863.5869987562495), np.float64(-321.7163309688003)]</t>
+  </si>
+  <si>
+    <t>[np.float64(480.50495120544014), np.float64(69.04766033992689)]</t>
+  </si>
+  <si>
+    <t>[np.float64(509.4301080841671), np.float64(-274.8951845680209)]</t>
+  </si>
+  <si>
+    <t>[np.float64(746.1889066426828), np.float64(19.035090571227897)]</t>
+  </si>
+  <si>
+    <t>[np.float64(190.00366796653424), np.float64(442.5247555719502)]</t>
+  </si>
+  <si>
+    <t>[np.float64(778.1643593536498), np.float64(464.56853137272174)]</t>
+  </si>
+  <si>
+    <t>[np.float64(466.10465672394463), np.float64(-315.39223906833524)]</t>
+  </si>
+  <si>
+    <t>[np.float64(285.3207321572502), np.float64(385.8841101820009)]</t>
+  </si>
+  <si>
+    <t>[np.float64(158.54472197513593), np.float64(388.43840490899595)]</t>
+  </si>
+  <si>
+    <t>[np.float64(984.2833379877269), np.float64(594.7874781222583)]</t>
+  </si>
+  <si>
+    <t>[np.float64(562.0122365115816), np.float64(-468.2895756493116)]</t>
+  </si>
+  <si>
+    <t>[np.float64(713.9375853108561), np.float64(205.37983300246378)]</t>
+  </si>
+  <si>
+    <t>[np.float64(116.48962279022057), np.float64(462.93029783486077)]</t>
+  </si>
+  <si>
+    <t>[np.float64(981.8671880646939), np.float64(-227.9099216485776)]</t>
+  </si>
+  <si>
+    <t>[np.float64(113.76650713697734), np.float64(-189.64839871662008)]</t>
+  </si>
+  <si>
+    <t>[np.float64(330.1329544686238), np.float64(210.8375336957739)]</t>
+  </si>
+  <si>
+    <t>[np.float64(640.2918787491391), np.float64(208.58158502833317)]</t>
+  </si>
+  <si>
+    <t>[np.float64(466.8584005121983), np.float64(-239.13854863364043)]</t>
+  </si>
+  <si>
+    <t>[np.float64(774.8054429248759), np.float64(-201.93772489177115)]</t>
+  </si>
+  <si>
+    <t>[np.float64(226.85704386471116), np.float64(69.8592707416949)]</t>
+  </si>
+  <si>
+    <t>[np.float64(809.0546132046544), np.float64(455.3257887206571)]</t>
+  </si>
+  <si>
+    <t>[np.float64(419.5365269469358), np.float64(-270.46029013773494)]</t>
+  </si>
+  <si>
+    <t>[np.float64(132.28021298181224), np.float64(-264.59781015517166)]</t>
+  </si>
+  <si>
+    <t>[np.float64(535.7874434564201), np.float64(-598.7942052494714)]</t>
+  </si>
+  <si>
+    <t>[np.float64(749.642840455673), np.float64(-326.2972772963592)]</t>
+  </si>
+  <si>
+    <t>[np.float64(812.6315451479334), np.float64(199.41671522320394)]</t>
+  </si>
+  <si>
+    <t>[np.float64(969.2171125308606), np.float64(-524.1784645726993)]</t>
+  </si>
+  <si>
+    <t>[np.float64(938.1206701436683), np.float64(-567.7524684242901)]</t>
+  </si>
+  <si>
+    <t>[np.float64(618.2131182335414), np.float64(170.2602948962866)]</t>
+  </si>
+  <si>
+    <t>[np.float64(678.9943058581391), np.float64(274.68327221956054)]</t>
+  </si>
+  <si>
+    <t>[np.float64(61.510376472671105), np.float64(-292.74889032144034)]</t>
+  </si>
+  <si>
+    <t>[np.float64(720.7479040989625), np.float64(-114.91178798016279)]</t>
+  </si>
+  <si>
+    <t>[np.float64(998.799330576446), np.float64(-471.55453814297016)]</t>
+  </si>
+  <si>
+    <t>[np.float64(199.46329085289972), np.float64(82.9929790018466)]</t>
+  </si>
+  <si>
+    <t>[np.float64(920.1119163629334), np.float64(-162.21337070391326)]</t>
+  </si>
+  <si>
+    <t>[np.float64(659.2004330495812), np.float64(-76.68154753940871)]</t>
+  </si>
+  <si>
+    <t>[np.float64(978.5160432236306), np.float64(159.22362592246714)]</t>
+  </si>
+  <si>
+    <t>[np.float64(935.1836941929992), np.float64(-62.654833087394536)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.5578768930454308), np.float64(-338.13901195375365)]</t>
+  </si>
+  <si>
+    <t>[np.float64(25.683952312629653), np.float64(208.81668410104237)]</t>
+  </si>
+  <si>
+    <t>[np.float64(444.74330970812935), np.float64(-160.4172178559882)]</t>
+  </si>
+  <si>
+    <t>[np.float64(212.10611573758587), np.float64(-588.6707441487191)]</t>
+  </si>
+  <si>
+    <t>[np.float64(971.1804850640756), np.float64(-101.67619469719978)]</t>
+  </si>
+  <si>
+    <t>[np.float64(121.60248374149995), np.float64(-405.84322270226977)]</t>
+  </si>
+  <si>
+    <t>[np.float64(487.4722799794897), np.float64(-328.0809300354005)]</t>
+  </si>
+  <si>
+    <t>[np.float64(286.1556388939124), np.float64(468.62107569172304)]</t>
+  </si>
+  <si>
+    <t>[np.float64(830.2927905116732), np.float64(-513.2900298208907)]</t>
+  </si>
+  <si>
+    <t>[np.float64(130.20773093969206), np.float64(-132.85740746103744)]</t>
+  </si>
+  <si>
+    <t>[np.float64(313.91495988528675), np.float64(-447.6237072719834)]</t>
+  </si>
+  <si>
+    <t>[np.float64(931.4340249308749), np.float64(-164.11093192542893)]</t>
+  </si>
+  <si>
+    <t>[np.float64(541.5253473293664), np.float64(-329.92563912817377)]</t>
+  </si>
+  <si>
+    <t>[np.float64(556.8817089318667), np.float64(124.19482055950823)]</t>
+  </si>
+  <si>
+    <t>[np.float64(502.199339578398), np.float64(-248.2820673113025)]</t>
+  </si>
+  <si>
+    <t>[np.float64(675.6146009480836), np.float64(129.6211927025821)]</t>
+  </si>
+  <si>
+    <t>[np.float64(27.408986887103914), np.float64(34.02446382265339)]</t>
+  </si>
+  <si>
+    <t>[np.float64(320.75288544113255), np.float64(434.32929882646295)]</t>
+  </si>
+  <si>
+    <t>[np.float64(146.63511100154537), np.float64(210.13590397508142)]</t>
+  </si>
+  <si>
+    <t>[np.float64(344.6704273918486), np.float64(-296.56744815990004)]</t>
+  </si>
+  <si>
+    <t>[np.float64(672.6831804705797), np.float64(506.84812915613475)]</t>
+  </si>
+  <si>
+    <t>[np.float64(680.5343500651236), np.float64(303.58899201883025)]</t>
+  </si>
+  <si>
+    <t>[np.float64(293.61293503540173), np.float64(-117.5427548984797)]</t>
+  </si>
+  <si>
+    <t>[np.float64(918.5966931690328), np.float64(-262.29245324156506)]</t>
+  </si>
+  <si>
+    <t>[np.float64(708.8262644623363), np.float64(-596.8011092340336)]</t>
+  </si>
+  <si>
+    <t>[np.float64(398.580680759565), np.float64(64.17780362450185)]</t>
+  </si>
+  <si>
+    <t>[np.float64(234.0901093657155), np.float64(217.58818220368903)]</t>
+  </si>
+  <si>
+    <t>[np.float64(389.5673372660788), np.float64(464.4183183606599)]</t>
+  </si>
+  <si>
+    <t>[np.float64(940.0758979955673), np.float64(-236.34085209322262)]</t>
+  </si>
+  <si>
+    <t>[np.float64(156.17498691060362), np.float64(-398.3877803663114)]</t>
+  </si>
+  <si>
+    <t>[np.float64(291.5145752064392), np.float64(98.24720959607862)]</t>
+  </si>
+  <si>
+    <t>[np.float64(496.3561696124577), np.float64(-425.3131430768718)]</t>
+  </si>
+  <si>
+    <t>[np.float64(946.089486564237), np.float64(525.8919874580827)]</t>
+  </si>
+  <si>
+    <t>[np.float64(17.64875672308186), np.float64(-428.7197059448316)]</t>
+  </si>
+  <si>
+    <t>[np.float64(135.71850122654982), np.float64(-138.91043726764377)]</t>
+  </si>
+  <si>
+    <t>[np.float64(663.3654720713595), np.float64(-465.00688145201843)]</t>
+  </si>
+  <si>
+    <t>[np.float64(297.09029605843904), np.float64(-427.39277946723973)]</t>
+  </si>
+  <si>
+    <t>[np.float64(159.37062230939625), np.float64(384.236944568739)]</t>
+  </si>
+  <si>
+    <t>[np.float64(206.34696827818456), np.float64(86.41906458934)]</t>
+  </si>
+  <si>
+    <t>[np.float64(676.2558238242398), np.float64(465.44903347378613)]</t>
+  </si>
+  <si>
+    <t>[np.float64(149.05482068720676), np.float64(-370.59530777816235)]</t>
+  </si>
+  <si>
+    <t>[np.float64(887.1089093501723), np.float64(64.6941904382353)]</t>
+  </si>
+  <si>
+    <t>[np.float64(146.6382669187819), np.float64(-316.7496369651595)]</t>
+  </si>
+  <si>
+    <t>[np.float64(485.73570816985176), np.float64(-206.44218629498374)]</t>
+  </si>
+  <si>
+    <t>[np.float64(879.2703244525541), np.float64(-163.21213434297192)]</t>
+  </si>
+  <si>
+    <t>[np.float64(539.3804971414315), np.float64(-379.43856164267436)]</t>
+  </si>
+  <si>
+    <t>[np.float64(75.2726154787634), np.float64(-295.5428382318029)]</t>
+  </si>
+  <si>
+    <t>[np.float64(825.4007585333608), np.float64(172.2657440926996)]</t>
+  </si>
+  <si>
+    <t>[np.float64(170.39437402117485), np.float64(205.09747235153782)]</t>
+  </si>
+  <si>
+    <t>[np.float64(607.8368954550942), np.float64(-135.4091267309763)]</t>
+  </si>
+  <si>
+    <t>[np.float64(895.7176120025049), np.float64(260.22493394808384)]</t>
+  </si>
+  <si>
+    <t>[np.float64(870.1445457370778), np.float64(77.45623681172151)]</t>
+  </si>
+  <si>
+    <t>[np.float64(72.73259315828207), np.float64(183.03586873340396)]</t>
+  </si>
+  <si>
+    <t>[np.float64(6.563103184586305), np.float64(-357.9763758187356)]</t>
+  </si>
+  <si>
+    <t>[np.float64(901.7657250748616), np.float64(-321.9036606191672)]</t>
+  </si>
+  <si>
+    <t>[np.float64(535.9999765309487), np.float64(-218.28900012434627)]</t>
+  </si>
+  <si>
+    <t>[np.float64(544.5463703034476), np.float64(-568.9872234008295)]</t>
+  </si>
+  <si>
+    <t>[np.float64(566.624897317688), np.float64(564.6984523657218)]</t>
+  </si>
+  <si>
+    <t>[np.float64(316.04282625575763), np.float64(473.1161754554496)]</t>
+  </si>
+  <si>
+    <t>[np.float64(628.6852480763226), np.float64(-465.42636296359683)]</t>
+  </si>
+  <si>
+    <t>[np.float64(762.1965575494556), np.float64(-495.07681797159626)]</t>
+  </si>
+  <si>
+    <t>[np.float64(956.4602909339873), np.float64(233.27994665796973)]</t>
+  </si>
+  <si>
+    <t>[np.float64(297.4419237028979), np.float64(190.37580055529554)]</t>
+  </si>
+  <si>
+    <t>[np.float64(873.8636157534929), np.float64(-498.7486886005794)]</t>
+  </si>
+  <si>
+    <t>[np.float64(289.57264003166136), np.float64(259.8417359948364)]</t>
+  </si>
+  <si>
+    <t>[np.float64(443.31560552955983), np.float64(-567.7792402639055)]</t>
+  </si>
+  <si>
+    <t>[np.float64(489.3352486842234), np.float64(-187.04264669121903)]</t>
+  </si>
+  <si>
+    <t>[np.float64(507.30311793065664), np.float64(491.647222059418)]</t>
+  </si>
+  <si>
+    <t>[np.float64(543.2027739693038), np.float64(429.00896552217)]</t>
+  </si>
+  <si>
+    <t>[np.float64(896.7206763844321), np.float64(456.95800207618095)]</t>
+  </si>
+  <si>
+    <t>[np.float64(115.56128885591666), np.float64(328.0910641959465)]</t>
+  </si>
+  <si>
+    <t>[np.float64(852.9484173974178), np.float64(-487.9889753219011)]</t>
+  </si>
+  <si>
+    <t>[np.float64(87.2650472633959), np.float64(63.13216633869092)]</t>
+  </si>
+  <si>
+    <t>[np.float64(351.36941315072033), np.float64(237.28219192938286)]</t>
+  </si>
+  <si>
+    <t>[np.float64(334.4291867798469), np.float64(508.2302214691051)]</t>
+  </si>
+  <si>
+    <t>[np.float64(43.99708108179079), np.float64(-410.76625587258013)]</t>
+  </si>
+  <si>
+    <t>[np.float64(541.5057025750864), np.float64(5.61517521082294)]</t>
+  </si>
+  <si>
+    <t>[np.float64(133.5233160878495), np.float64(-124.60348854794694)]</t>
+  </si>
+  <si>
+    <t>[np.float64(258.5170128752262), np.float64(125.9413292352441)]</t>
+  </si>
+  <si>
+    <t>[np.float64(167.75118074905336), np.float64(-555.924896600992)]</t>
+  </si>
+  <si>
+    <t>[np.float64(225.76684186459516), np.float64(-329.4588224828042)]</t>
+  </si>
+  <si>
+    <t>[np.float64(389.84201658080417), np.float64(-298.8918329226653)]</t>
+  </si>
+  <si>
+    <t>[np.float64(735.2160477038038), np.float64(425.6859580863081)]</t>
+  </si>
+  <si>
+    <t>[np.float64(167.78022869830212), np.float64(-126.45966774988091)]</t>
+  </si>
+  <si>
+    <t>[np.float64(468.285635808294), np.float64(432.994877155302)]</t>
+  </si>
+  <si>
+    <t>[np.float64(410.77041533486045), np.float64(430.23910433404967)]</t>
+  </si>
+  <si>
+    <t>[np.float64(374.19735439236234), np.float64(-401.2636282838971)]</t>
+  </si>
+  <si>
+    <t>[np.float64(669.6087906975233), np.float64(138.86374233664878)]</t>
+  </si>
+  <si>
+    <t>[np.float64(47.206733103894784), np.float64(433.8479704114777)]</t>
+  </si>
+  <si>
+    <t>[np.float64(662.9103645611108), np.float64(-576.0783559952665)]</t>
+  </si>
+  <si>
+    <t>[np.float64(29.692852604423337), np.float64(44.30191255456316)]</t>
+  </si>
+  <si>
+    <t>[np.float64(243.95183796738795), np.float64(-318.09825644436893)]</t>
+  </si>
+  <si>
+    <t>[np.float64(204.18938544860853), np.float64(353.5837646686773)]</t>
+  </si>
+  <si>
+    <t>[np.float64(910.7967624339074), np.float64(-318.0549584037655)]</t>
+  </si>
+  <si>
+    <t>[np.float64(640.6620931505516), np.float64(-507.46233595542265)]</t>
+  </si>
+  <si>
+    <t>[np.float64(47.55849666091583), np.float64(512.7521069546376)]</t>
+  </si>
+  <si>
+    <t>[np.float64(756.1254416420646), np.float64(48.863696045934034)]</t>
+  </si>
+  <si>
+    <t>[np.float64(373.47913677714286), np.float64(238.9509420821206)]</t>
+  </si>
+  <si>
+    <t>[np.float64(224.52014610230998), np.float64(286.32142749838636)]</t>
+  </si>
+  <si>
+    <t>[np.float64(522.0015453855145), np.float64(96.02011796048168)]</t>
+  </si>
+  <si>
+    <t>[np.float64(993.6641289215303), np.float64(543.5913524788991)]</t>
+  </si>
+  <si>
+    <t>[np.float64(973.5433393670143), np.float64(386.9133604575047)]</t>
+  </si>
+  <si>
+    <t>[np.float64(335.65196742738965), np.float64(508.54814034600713)]</t>
+  </si>
+  <si>
+    <t>[np.float64(998.852244940348), np.float64(264.20838449951566)]</t>
+  </si>
+  <si>
+    <t>[np.float64(375.24975659517844), np.float64(-410.69752448159073)]</t>
+  </si>
+  <si>
+    <t>[np.float64(82.14095932005183), np.float64(543.3730098614776)]</t>
+  </si>
+  <si>
+    <t>[np.float64(398.6749874187759), np.float64(-280.91393971902784)]</t>
+  </si>
+  <si>
+    <t>[np.float64(898.5902355746955), np.float64(-550.1297699164634)]</t>
+  </si>
+  <si>
+    <t>[np.float64(244.92738704608607), np.float64(182.73603686286754)]</t>
+  </si>
+  <si>
+    <t>[np.float64(462.6682585284234), np.float64(211.4646142304531)]</t>
+  </si>
+  <si>
+    <t>[np.float64(535.7326974155536), np.float64(127.87273702259426)]</t>
+  </si>
+  <si>
+    <t>[np.float64(732.1987555631569), np.float64(133.2628051106252)]</t>
+  </si>
+  <si>
+    <t>[np.float64(887.5006386398435), np.float64(-242.87179344577413)]</t>
+  </si>
+  <si>
+    <t>[np.float64(292.3974008938438), np.float64(-64.97889278343564)]</t>
+  </si>
+  <si>
+    <t>[np.float64(615.6774592179736), np.float64(-147.49514105329263)]</t>
+  </si>
+  <si>
+    <t>[np.float64(986.211582268212), np.float64(-343.55250744785116)]</t>
+  </si>
+  <si>
+    <t>[np.float64(222.64674819260665), np.float64(-174.99815582683067)]</t>
+  </si>
+  <si>
+    <t>[np.float64(109.36796129938564), np.float64(370.04378229722147)]</t>
+  </si>
+  <si>
+    <t>[np.float64(952.4925647903021), np.float64(527.2385221582447)]</t>
+  </si>
+  <si>
+    <t>[np.float64(418.01129032439246), np.float64(445.35516798732147)]</t>
+  </si>
+  <si>
+    <t>[np.float64(691.8792829045337), np.float64(451.8469363348943)]</t>
+  </si>
+  <si>
+    <t>[np.float64(452.8561068495782), np.float64(-457.3730830676415)]</t>
+  </si>
+  <si>
+    <t>[np.float64(98.36967090784721), np.float64(-120.58805934341962)]</t>
+  </si>
+  <si>
+    <t>[np.float64(656.5548204030027), np.float64(-359.2395979592843)]</t>
+  </si>
+  <si>
+    <t>[np.float64(154.48912483701616), np.float64(-91.75855780863691)]</t>
+  </si>
+  <si>
+    <t>[np.float64(897.9680875423416), np.float64(184.25528512848223)]</t>
+  </si>
+  <si>
+    <t>[np.float64(405.26191554487735), np.float64(-264.2252871440909)]</t>
+  </si>
+  <si>
+    <t>[np.float64(510.7098601398756), np.float64(-433.2570363525965)]</t>
+  </si>
+  <si>
+    <t>[np.float64(231.0590013900844), np.float64(499.77252138305266)]</t>
+  </si>
+  <si>
+    <t>[np.float64(840.2766371868946), np.float64(-284.25463350323173)]</t>
+  </si>
+  <si>
+    <t>[np.float64(990.6192860652452), np.float64(-197.54830759905343)]</t>
+  </si>
+  <si>
+    <t>[np.float64(627.593378253012), np.float64(-591.0516020040126)]</t>
+  </si>
+  <si>
+    <t>[np.float64(345.7456303242875), np.float64(-586.9189985829834)]</t>
+  </si>
+  <si>
+    <t>[np.float64(117.07943693005119), np.float64(383.44017167873585)]</t>
+  </si>
+  <si>
+    <t>[np.float64(108.1798132767029), np.float64(331.240162033754)]</t>
+  </si>
+  <si>
+    <t>[np.float64(453.41866658617425), np.float64(396.37693596263523)]</t>
+  </si>
+  <si>
+    <t>[np.float64(434.18822009245196), np.float64(421.7761684886732)]</t>
+  </si>
+  <si>
+    <t>[np.float64(891.8645195279877), np.float64(-223.88696374251754)]</t>
+  </si>
+  <si>
+    <t>[np.float64(523.0703294896617), np.float64(249.6226918085457)]</t>
+  </si>
+  <si>
+    <t>[np.float64(18.779454529016306), np.float64(482.2172993299416)]</t>
+  </si>
+  <si>
+    <t>[np.float64(590.0809946521535), np.float64(-278.21115411367776)]</t>
+  </si>
+  <si>
+    <t>[np.float64(312.9695425946386), np.float64(-275.2295631230238)]</t>
+  </si>
+  <si>
+    <t>[np.float64(920.4518039990319), np.float64(278.5804771195677)]</t>
+  </si>
+  <si>
+    <t>[np.float64(448.21727071773654), np.float64(-129.89736480918322)]</t>
+  </si>
+  <si>
+    <t>[np.float64(469.10239993113646), np.float64(-458.3154412060503)]</t>
+  </si>
+  <si>
+    <t>[np.float64(105.87494793003071), np.float64(574.3685575365241)]</t>
+  </si>
+  <si>
+    <t>[np.float64(710.4499946547743), np.float64(-590.2886807471539)]</t>
+  </si>
+  <si>
+    <t>[np.float64(568.6859329887668), np.float64(408.09039837153523)]</t>
+  </si>
+  <si>
+    <t>[np.float64(844.2248943187573), np.float64(337.1119113950807)]</t>
+  </si>
+  <si>
+    <t>[np.float64(749.8012450008025), np.float64(597.1711403599313)]</t>
+  </si>
+  <si>
+    <t>[np.float64(37.637686008414775), np.float64(240.90375786489506)]</t>
+  </si>
+  <si>
+    <t>[np.float64(458.0377727834103), np.float64(-539.5701191068861)]</t>
+  </si>
+  <si>
+    <t>[np.float64(405.61907473738114), np.float64(414.4482021756718)]</t>
+  </si>
+  <si>
+    <t>[np.float64(868.1773708012248), np.float64(-124.04704952245612)]</t>
+  </si>
+  <si>
+    <t>[np.float64(54.85584960690149), np.float64(-385.39226279934974)]</t>
+  </si>
+  <si>
+    <t>[np.float64(520.2903266541985), np.float64(-491.5044787492616)]</t>
+  </si>
+  <si>
+    <t>[np.float64(675.1098316522667), np.float64(-150.83800248023948)]</t>
+  </si>
+  <si>
+    <t>[np.float64(549.9127039312853), np.float64(416.33734348802)]</t>
+  </si>
+  <si>
+    <t>[np.float64(53.57856010795714), np.float64(-291.14969922912763)]</t>
+  </si>
+  <si>
+    <t>[np.float64(752.8654021121234), np.float64(392.5607813858534)]</t>
+  </si>
+  <si>
+    <t>[np.float64(557.867139818635), np.float64(135.0556043579802)]</t>
+  </si>
+  <si>
+    <t>[np.float64(941.6816299262503), np.float64(-222.88326116442994)]</t>
+  </si>
+  <si>
+    <t>[np.float64(118.20500305590187), np.float64(-151.36705571775553)]</t>
+  </si>
+  <si>
+    <t>[np.float64(165.59938308765766), np.float64(299.32944932357213)]</t>
+  </si>
+  <si>
+    <t>[np.float64(326.51688995786765), np.float64(-213.6498255733738)]</t>
+  </si>
+  <si>
+    <t>[np.float64(863.5064170808661), np.float64(318.2569989292007)]</t>
+  </si>
+  <si>
+    <t>[np.float64(824.1241930521368), np.float64(-218.43485868506815)]</t>
+  </si>
+  <si>
+    <t>[np.float64(511.0615963085229), np.float64(-110.7797292994108)]</t>
+  </si>
+  <si>
+    <t>[np.float64(449.22576656836435), np.float64(431.5602099158996)]</t>
+  </si>
+  <si>
+    <t>[np.float64(282.19655402513433), np.float64(576.0167928700057)]</t>
+  </si>
+  <si>
+    <t>[np.float64(824.0183707256693), np.float64(-214.39938884027845)]</t>
+  </si>
+  <si>
+    <t>[np.float64(129.27712981694395), np.float64(-375.1498373431449)]</t>
+  </si>
+  <si>
+    <t>[np.float64(258.1398941897162), np.float64(187.04834746264612)]</t>
+  </si>
+  <si>
+    <t>[np.float64(189.70605050425237), np.float64(461.25222131357896)]</t>
+  </si>
+  <si>
+    <t>[np.float64(864.2844442033263), np.float64(-479.35668935479214)]</t>
+  </si>
+  <si>
+    <t>[np.float64(974.6865514390879), np.float64(590.9956597891064)]</t>
+  </si>
+  <si>
+    <t>[np.float64(900.3860392754913), np.float64(-514.0414504235923)]</t>
+  </si>
+  <si>
+    <t>[np.float64(583.0293605240014), np.float64(-171.21409681536534)]</t>
+  </si>
+  <si>
+    <t>[np.float64(307.3943391635422), np.float64(-116.15332299761621)]</t>
+  </si>
+  <si>
+    <t>[np.float64(282.65369872742184), np.float64(342.4585670143123)]</t>
+  </si>
+  <si>
+    <t>[np.float64(533.0848395595481), np.float64(556.0841175819473)]</t>
+  </si>
+  <si>
+    <t>[np.float64(361.8692255541878), np.float64(516.1418892055051)]</t>
+  </si>
+  <si>
+    <t>[np.float64(249.52763415893742), np.float64(-321.74675906804435)]</t>
+  </si>
+  <si>
+    <t>[np.float64(682.2371115759665), np.float64(-152.60640895538427)]</t>
+  </si>
+  <si>
+    <t>[np.float64(322.524297677494), np.float64(228.62917590477764)]</t>
+  </si>
+  <si>
+    <t>[np.float64(315.9605763727935), np.float64(-288.17682876502266)]</t>
+  </si>
+  <si>
+    <t>[np.float64(412.38398561114866), np.float64(16.33545731208153)]</t>
+  </si>
+  <si>
+    <t>[np.float64(752.6698879816245), np.float64(-391.9529003531321)]</t>
+  </si>
+  <si>
+    <t>[np.float64(450.1732091858832), np.float64(-335.0727031015777)]</t>
+  </si>
+  <si>
+    <t>[np.float64(552.8865855905034), np.float64(-350.5267204370987)]</t>
+  </si>
+  <si>
+    <t>[np.float64(679.3121243409158), np.float64(11.998366421240917)]</t>
+  </si>
+  <si>
+    <t>[np.float64(427.81993984840597), np.float64(544.4914663143063)]</t>
+  </si>
+  <si>
+    <t>[np.float64(616.640832293276), np.float64(-114.20437186391592)]</t>
+  </si>
+  <si>
+    <t>[np.float64(963.8546546537748), np.float64(-454.818104795028)]</t>
+  </si>
+  <si>
+    <t>[np.float64(904.4253388379298), np.float64(-302.2208813007427)]</t>
+  </si>
+  <si>
+    <t>[np.float64(261.7058299930596), np.float64(-478.945033822048)]</t>
+  </si>
+  <si>
+    <t>[np.float64(638.9771378240459), np.float64(85.7895705200491)]</t>
+  </si>
+  <si>
+    <t>[np.float64(393.50682702522465), np.float64(152.53953162334426)]</t>
+  </si>
+  <si>
+    <t>[np.float64(98.34625717059609), np.float64(392.50893445071665)]</t>
+  </si>
+  <si>
+    <t>[np.float64(646.2462636814112), np.float64(-380.2499021476261)]</t>
+  </si>
+  <si>
+    <t>[np.float64(437.91158849233716), np.float64(79.47161404002804)]</t>
+  </si>
+  <si>
+    <t>[np.float64(865.6177691068174), np.float64(582.064024677825)]</t>
+  </si>
+  <si>
+    <t>[np.float64(270.0409770517803), np.float64(-571.1735407420455)]</t>
+  </si>
+  <si>
+    <t>[np.float64(314.6051267903803), np.float64(-158.69959443953223)]</t>
+  </si>
+  <si>
+    <t>[np.float64(758.3423644171537), np.float64(-554.8819590058538)]</t>
+  </si>
+  <si>
+    <t>[np.float64(693.2115736652739), np.float64(-186.7410637674517)]</t>
+  </si>
+  <si>
+    <t>[np.float64(632.2010928969972), np.float64(-77.9451069573953)]</t>
+  </si>
+  <si>
+    <t>[np.float64(738.741492118725), np.float64(-239.2515005605053)]</t>
+  </si>
+  <si>
+    <t>[np.float64(495.32389850467075), np.float64(-250.43653668406677)]</t>
+  </si>
+  <si>
+    <t>[np.float64(668.7868623581124), np.float64(459.167081048138)]</t>
+  </si>
+  <si>
+    <t>[np.float64(402.2150453724952), np.float64(420.24198297141356)]</t>
+  </si>
+  <si>
+    <t>[np.float64(541.241523376205), np.float64(559.6997883423828)]</t>
+  </si>
+  <si>
+    <t>[np.float64(229.16358798705872), np.float64(-550.8247775759146)]</t>
+  </si>
+  <si>
+    <t>[np.float64(97.62580748435856), np.float64(74.47001253729195)]</t>
+  </si>
+  <si>
+    <t>[np.float64(784.2173212703527), np.float64(96.10318728986203)]</t>
+  </si>
+  <si>
+    <t>[np.float64(322.24024930872184), np.float64(-447.2759520464863)]</t>
+  </si>
+  <si>
+    <t>[np.float64(928.3236174002508), np.float64(547.512786925799)]</t>
+  </si>
+  <si>
+    <t>[np.float64(204.7259843904784), np.float64(301.44749370870045)]</t>
+  </si>
+  <si>
+    <t>[np.float64(301.71653455578274), np.float64(-246.6260614944112)]</t>
+  </si>
+  <si>
+    <t>[np.float64(833.4181709207614), np.float64(-455.400095601122)]</t>
+  </si>
+  <si>
+    <t>[np.float64(348.80378251639763), np.float64(262.32141329032197)]</t>
+  </si>
+  <si>
+    <t>[np.float64(461.4172831957115), np.float64(-314.8387423919384)]</t>
+  </si>
+  <si>
+    <t>[np.float64(900.3135863268747), np.float64(414.5762638324152)]</t>
+  </si>
+  <si>
+    <t>[np.float64(203.5127150757723), np.float64(-540.9224576073564)]</t>
+  </si>
+  <si>
+    <t>[np.float64(684.6580962792842), np.float64(-435.15818689185744)]</t>
+  </si>
+  <si>
+    <t>[np.float64(754.275662709616), np.float64(411.1940485501866)]</t>
+  </si>
+  <si>
+    <t>[np.float64(399.2269546969737), np.float64(-460.84306822167457)]</t>
+  </si>
+  <si>
+    <t>[np.float64(46.00955239334237), np.float64(-395.43775319198346)]</t>
+  </si>
+  <si>
+    <t>[np.float64(753.2639564842534), np.float64(-127.41917383469405)]</t>
+  </si>
+  <si>
+    <t>[np.float64(160.26551317568493), np.float64(261.24144628828446)]</t>
+  </si>
+  <si>
+    <t>[np.float64(98.83979669918497), np.float64(-488.21182418244246)]</t>
+  </si>
+  <si>
+    <t>[np.float64(982.0078630333392), np.float64(287.820394208274)]</t>
+  </si>
+  <si>
+    <t>[np.float64(697.989956500689), np.float64(226.1506528158094)]</t>
+  </si>
+  <si>
+    <t>[np.float64(997.2723997713023), np.float64(109.41088039478348)]</t>
+  </si>
+  <si>
+    <t>[np.float64(103.15995589441773), np.float64(294.48405379936776)]</t>
+  </si>
+  <si>
+    <t>[np.float64(148.27906133480707), np.float64(484.74414698058035)]</t>
+  </si>
+  <si>
+    <t>[np.float64(360.3386075027759), np.float64(-476.390810609826)]</t>
+  </si>
+  <si>
+    <t>[np.float64(800.5061991992204), np.float64(-248.01595712678142)]</t>
+  </si>
+  <si>
+    <t>[np.float64(214.88056960014023), np.float64(403.0836835785209)]</t>
+  </si>
+  <si>
+    <t>[np.float64(661.3050777293762), np.float64(-500.5800427218634)]</t>
+  </si>
+  <si>
+    <t>[np.float64(687.4415171224576), np.float64(-427.5154828799206)]</t>
+  </si>
+  <si>
+    <t>[np.float64(707.035205597997), np.float64(-147.58522922331633)]</t>
+  </si>
+  <si>
+    <t>[np.float64(968.009986326557), np.float64(-371.3138513109384)]</t>
+  </si>
+  <si>
+    <t>[np.float64(296.5871157738339), np.float64(485.60531664518135)]</t>
+  </si>
+  <si>
+    <t>[np.float64(640.4530010260264), np.float64(284.0802586869188)]</t>
+  </si>
+  <si>
+    <t>[np.float64(35.45724185995813), np.float64(165.65562583089684)]</t>
+  </si>
+  <si>
+    <t>[np.float64(838.8026972714238), np.float64(189.42596978916458)]</t>
+  </si>
+  <si>
+    <t>[np.float64(651.3563749065212), np.float64(-165.35309590971832)]</t>
+  </si>
+  <si>
+    <t>[np.float64(209.95210083323246), np.float64(443.49438468814606)]</t>
+  </si>
+  <si>
+    <t>[np.float64(196.65639200003017), np.float64(-496.35168857625644)]</t>
+  </si>
+  <si>
+    <t>[np.float64(336.8653929713422), np.float64(-101.64014690268988)]</t>
+  </si>
+  <si>
+    <t>[np.float64(387.57088406666475), np.float64(494.7406934106343)]</t>
+  </si>
+  <si>
+    <t>[np.float64(51.58677999061312), np.float64(46.82119764607785)]</t>
+  </si>
+  <si>
+    <t>[np.float64(220.20509719731828), np.float64(337.6280622852172)]</t>
+  </si>
+  <si>
+    <t>[np.float64(843.6894930044224), np.float64(-294.1682165965919)]</t>
+  </si>
+  <si>
+    <t>[np.float64(497.8915387899512), np.float64(-213.0374658383929)]</t>
+  </si>
+  <si>
+    <t>[np.float64(828.364322080178), np.float64(-442.4470789678334)]</t>
+  </si>
+  <si>
+    <t>[np.float64(158.90725507806192), np.float64(-291.8963059724757)]</t>
+  </si>
+  <si>
+    <t>[np.float64(161.4709181564945), np.float64(491.5539944279403)]</t>
+  </si>
+  <si>
+    <t>[np.float64(618.3210032759399), np.float64(-233.76206573479277)]</t>
+  </si>
+  <si>
+    <t>[np.float64(422.9984316620837), np.float64(-253.96165581175427)]</t>
+  </si>
+  <si>
+    <t>[np.float64(696.0223215808024), np.float64(252.36125010968374)]</t>
+  </si>
+  <si>
+    <t>[np.float64(236.49556553671815), np.float64(-332.1351498405545)]</t>
+  </si>
+  <si>
+    <t>[np.float64(30.87585587333086), np.float64(-172.79855668318862)]</t>
+  </si>
+  <si>
+    <t>[np.float64(366.40227103550984), np.float64(377.6983926528595)]</t>
+  </si>
+  <si>
+    <t>[np.float64(678.1427833901558), np.float64(-598.8709392602229)]</t>
+  </si>
+  <si>
+    <t>[np.float64(144.97649350708642), np.float64(429.5176036877722)]</t>
+  </si>
+  <si>
+    <t>[np.float64(157.24805225040828), np.float64(459.671643023604)]</t>
+  </si>
+  <si>
+    <t>[np.float64(317.15271852460916), np.float64(224.30311195785976)]</t>
+  </si>
+  <si>
+    <t>[np.float64(618.9438506396731), np.float64(-456.35101769987523)]</t>
+  </si>
+  <si>
+    <t>[np.float64(491.58457746103056), np.float64(592.9292135842038)]</t>
+  </si>
+  <si>
+    <t>[np.float64(792.3065770499304), np.float64(280.35443707633704)]</t>
+  </si>
+  <si>
+    <t>[np.float64(127.80696913951861), np.float64(128.31285662011396)]</t>
+  </si>
+  <si>
+    <t>[np.float64(774.0761792429532), np.float64(-269.1568037140147)]</t>
+  </si>
+  <si>
+    <t>[np.float64(771.6131999184978), np.float64(539.867855562981)]</t>
+  </si>
+  <si>
+    <t>[np.float64(655.7169979003687), np.float64(-564.2820029616496)]</t>
+  </si>
+  <si>
+    <t>[np.float64(580.8567639745957), np.float64(268.8498114201436)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.3574884076981153), np.float64(-393.2977536376063)]</t>
+  </si>
+  <si>
+    <t>[np.float64(766.0871705266571), np.float64(-95.43991174993687)]</t>
+  </si>
+  <si>
+    <t>[np.float64(611.4109241265002), np.float64(-330.62334322129254)]</t>
+  </si>
+  <si>
+    <t>[np.float64(49.77236571889099), np.float64(-442.18309929552424)]</t>
+  </si>
+  <si>
+    <t>[np.float64(359.91570941179305), np.float64(-363.7523584959384)]</t>
+  </si>
+  <si>
+    <t>[np.float64(988.4001946014605), np.float64(-123.3382762016526)]</t>
+  </si>
+  <si>
+    <t>[np.float64(908.1584373552921), np.float64(-300.35134621510116)]</t>
+  </si>
+  <si>
+    <t>[np.float64(933.1593233211099), np.float64(-305.63409587716103)]</t>
+  </si>
+  <si>
+    <t>[np.float64(914.6847573258913), np.float64(105.56545797179331)]</t>
+  </si>
+  <si>
+    <t>[np.float64(605.8885060725502), np.float64(509.52391260037894)]</t>
+  </si>
+  <si>
+    <t>[np.float64(571.0050928727863), np.float64(-470.7245057352728)]</t>
+  </si>
+  <si>
+    <t>[np.float64(240.2464070036322), np.float64(285.3546370332979)]</t>
+  </si>
+  <si>
+    <t>[np.float64(984.4265215249283), np.float64(576.7871873975616)]</t>
+  </si>
+  <si>
+    <t>[np.float64(630.8978884286879), np.float64(0.1388496755592996)]</t>
+  </si>
+  <si>
+    <t>[np.float64(682.8631737704403), np.float64(60.731765127901326)]</t>
+  </si>
+  <si>
+    <t>[np.float64(915.7547514687359), np.float64(-572.4152768099605)]</t>
+  </si>
+  <si>
+    <t>[np.float64(482.1277558588737), np.float64(-414.02057786653353)]</t>
+  </si>
+  <si>
+    <t>[np.float64(272.3134895359035), np.float64(390.9236766018836)]</t>
+  </si>
+  <si>
+    <t>[np.float64(425.8856637470584), np.float64(210.7064281094847)]</t>
+  </si>
+  <si>
+    <t>[np.float64(331.4287814566932), np.float64(40.19687471844691)]</t>
+  </si>
+  <si>
+    <t>[np.float64(472.22703928682506), np.float64(225.23342209001157)]</t>
+  </si>
+  <si>
+    <t>[np.float64(345.4859690106278), np.float64(114.84939308830212)]</t>
+  </si>
+  <si>
+    <t>[np.float64(755.0805254859679), np.float64(-102.64515673150822)]</t>
+  </si>
+  <si>
+    <t>[np.float64(476.7670844485117), np.float64(292.076209692062)]</t>
+  </si>
+  <si>
+    <t>[np.float64(367.8618485422014), np.float64(-562.1801797773967)]</t>
+  </si>
+  <si>
+    <t>[np.float64(596.2975445957585), np.float64(182.19384571831722)]</t>
+  </si>
+  <si>
+    <t>[np.float64(547.2658400899057), np.float64(-405.5875965213602)]</t>
+  </si>
+  <si>
+    <t>[np.float64(577.0410843932585), np.float64(308.09223884524374)]</t>
+  </si>
+  <si>
+    <t>[np.float64(673.4728787438331), np.float64(383.4828039622139)]</t>
+  </si>
+  <si>
+    <t>[np.float64(695.7735047796331), np.float64(-3.0974400206547443)]</t>
+  </si>
+  <si>
+    <t>[np.float64(213.68870898048021), np.float64(532.9041911578627)]</t>
+  </si>
+  <si>
+    <t>[np.float64(197.85759577192485), np.float64(296.00164419620785)]</t>
+  </si>
+  <si>
+    <t>[np.float64(695.4616852296374), np.float64(-110.20042223332615)]</t>
+  </si>
+  <si>
+    <t>[np.float64(491.3026631258343), np.float64(495.69756459756013)]</t>
+  </si>
+  <si>
+    <t>[np.float64(738.6434016801971), np.float64(-190.20876383368085)]</t>
+  </si>
+  <si>
+    <t>[np.float64(767.7169867058722), np.float64(-454.1782019504122)]</t>
+  </si>
+  <si>
+    <t>[np.float64(941.6867976778603), np.float64(-114.64044047306419)]</t>
+  </si>
+  <si>
+    <t>[np.float64(248.8718304615465), np.float64(436.80213228754405)]</t>
+  </si>
+  <si>
+    <t>[np.float64(758.6759595726713), np.float64(421.20073231409947)]</t>
+  </si>
+  <si>
+    <t>[np.float64(141.9297559496313), np.float64(366.76996913107007)]</t>
+  </si>
+  <si>
+    <t>[np.float64(151.19056457589076), np.float64(268.3359243641464)]</t>
+  </si>
+  <si>
+    <t>[np.float64(555.8318319504364), np.float64(298.26709001698157)]</t>
+  </si>
+  <si>
+    <t>[np.float64(408.42622545968277), np.float64(422.48045353910345)]</t>
+  </si>
+  <si>
+    <t>[np.float64(30.519643154443333), np.float64(-406.6189969372608)]</t>
+  </si>
+  <si>
+    <t>[np.float64(54.226164987034586), np.float64(480.22188960863446)]</t>
+  </si>
+  <si>
+    <t>[np.float64(882.1034811137428), np.float64(90.61032794517973)]</t>
+  </si>
+  <si>
+    <t>[np.float64(178.5940922347632), np.float64(-218.63319009961072)]</t>
+  </si>
+  <si>
+    <t>[np.float64(412.1143095763475), np.float64(-419.390566586997)]</t>
+  </si>
+  <si>
+    <t>[np.float64(47.25103135105746), np.float64(27.1639883479304)]</t>
+  </si>
+  <si>
+    <t>[np.float64(108.29648555817096), np.float64(-597.9021405423841)]</t>
+  </si>
+  <si>
+    <t>[np.float64(824.6238887614454), np.float64(-160.2487813703724)]</t>
+  </si>
+  <si>
+    <t>[np.float64(869.0657542786801), np.float64(232.23831156623623)]</t>
+  </si>
+  <si>
+    <t>[np.float64(661.9033913004681), np.float64(-328.37469558422293)]</t>
+  </si>
+  <si>
+    <t>[np.float64(568.0280311405578), np.float64(-126.985030553635)]</t>
+  </si>
+  <si>
+    <t>[np.float64(892.5987639780022), np.float64(-245.07302212313306)]</t>
+  </si>
+  <si>
+    <t>[np.float64(584.4102360437981), np.float64(-87.57983761868672)]</t>
+  </si>
+  <si>
+    <t>[np.float64(648.9204632976107), np.float64(-363.41773429356374)]</t>
+  </si>
+  <si>
+    <t>[np.float64(516.2684377252816), np.float64(-473.1292955689729)]</t>
+  </si>
+  <si>
+    <t>[np.float64(258.7573990472061), np.float64(-317.87500563301234)]</t>
+  </si>
+  <si>
+    <t>[np.float64(916.8032708434225), np.float64(-533.9067636442259)]</t>
+  </si>
+  <si>
+    <t>[np.float64(271.8766685050883), np.float64(-233.76470849227684)]</t>
+  </si>
+  <si>
+    <t>[np.float64(85.34157490679894), np.float64(288.87547808042825)]</t>
+  </si>
+  <si>
+    <t>[np.float64(440.7610512338216), np.float64(558.566371008854)]</t>
+  </si>
+  <si>
+    <t>[np.float64(261.3355244940172), np.float64(16.956574436567394)]</t>
+  </si>
+  <si>
+    <t>[np.float64(913.2979072861878), np.float64(-369.46135593516794)]</t>
+  </si>
+  <si>
+    <t>[np.float64(145.191305779941), np.float64(279.3168368954763)]</t>
+  </si>
+  <si>
+    <t>[np.float64(118.98158857871488), np.float64(-212.04630636017657)]</t>
+  </si>
+  <si>
+    <t>[np.float64(751.479345328952), np.float64(482.81222638952545)]</t>
+  </si>
+  <si>
+    <t>[np.float64(952.0932012703946), np.float64(90.40945543601515)]</t>
+  </si>
+  <si>
+    <t>[np.float64(527.6205491061451), np.float64(184.04822235080462)]</t>
+  </si>
+  <si>
+    <t>[np.float64(391.1399677539915), np.float64(-457.8288554771888)]</t>
+  </si>
+  <si>
+    <t>[np.float64(664.924371102959), np.float64(339.64739899173185)]</t>
+  </si>
+  <si>
+    <t>[np.float64(52.965750356518186), np.float64(463.7093832781634)]</t>
+  </si>
+  <si>
+    <t>[np.float64(403.8861256588475), np.float64(-524.09470883466)]</t>
+  </si>
+  <si>
+    <t>[np.float64(947.6077087439955), np.float64(196.9886061046609)]</t>
+  </si>
+  <si>
+    <t>[np.float64(414.5301125470422), np.float64(451.61373358277615)]</t>
+  </si>
+  <si>
+    <t>[np.float64(162.88280886791262), np.float64(-162.50888086883282)]</t>
+  </si>
+  <si>
+    <t>[np.float64(707.0438277839912), np.float64(203.127989967624)]</t>
+  </si>
+  <si>
+    <t>[np.float64(841.7821023696439), np.float64(-146.82012036825012)]</t>
+  </si>
+  <si>
+    <t>[np.float64(70.22031748192093), np.float64(58.90286898633951)]</t>
+  </si>
+  <si>
+    <t>[np.float64(799.4170460127841), np.float64(47.79668835720577)]</t>
+  </si>
+  <si>
+    <t>[np.float64(608.2148796634959), np.float64(107.3073597344835)]</t>
+  </si>
+  <si>
+    <t>[np.float64(693.4616817256381), np.float64(177.83564224985003)]</t>
+  </si>
+  <si>
+    <t>[np.float64(633.4376901401391), np.float64(398.12406613421103)]</t>
+  </si>
+  <si>
+    <t>[np.float64(182.84304126548446), np.float64(210.4493963397515)]</t>
+  </si>
+  <si>
+    <t>[np.float64(161.4797158968593), np.float64(91.48527625609825)]</t>
+  </si>
+  <si>
+    <t>[np.float64(199.95971479294784), np.float64(78.48036778746905)]</t>
+  </si>
+  <si>
+    <t>[np.float64(167.80960171738823), np.float64(346.5511409127812)]</t>
+  </si>
+  <si>
+    <t>[np.float64(990.1745755061116), np.float64(307.02567079842197)]</t>
+  </si>
+  <si>
+    <t>[np.float64(840.0214535713911), np.float64(-480.36544489426797)]</t>
+  </si>
+  <si>
+    <t>[np.float64(8.673365235482343), np.float64(88.33818085608459)]</t>
+  </si>
+  <si>
+    <t>[np.float64(861.3588129571563), np.float64(-355.38122366607263)]</t>
+  </si>
+  <si>
+    <t>[np.float64(940.5673702409281), np.float64(542.3026804262097)]</t>
+  </si>
+  <si>
+    <t>[np.float64(206.9097856829064), np.float64(-549.7169751681477)]</t>
+  </si>
+  <si>
+    <t>[np.float64(514.2600081504908), np.float64(-89.65086814513944)]</t>
+  </si>
+  <si>
+    <t>[np.float64(961.1569278014337), np.float64(0.634807493933522)]</t>
+  </si>
+  <si>
+    <t>[np.float64(495.11488553620984), np.float64(-383.84596012195436)]</t>
+  </si>
+  <si>
+    <t>[np.float64(637.2940652107269), np.float64(285.4977804524501)]</t>
+  </si>
+  <si>
+    <t>[np.float64(803.4019020026763), np.float64(434.82338589968526)]</t>
+  </si>
+  <si>
+    <t>[np.float64(8.526835080587048), np.float64(-129.52519564542723)]</t>
+  </si>
+  <si>
+    <t>[np.float64(348.71580093969146), np.float64(-369.7220293994657)]</t>
+  </si>
+  <si>
+    <t>[np.float64(487.1765277361395), np.float64(455.3515748805196)]</t>
+  </si>
+  <si>
+    <t>[np.float64(825.6028665575199), np.float64(-497.1770133946775)]</t>
+  </si>
+  <si>
+    <t>[np.float64(941.0251260104336), np.float64(-502.65091132496946)]</t>
+  </si>
+  <si>
+    <t>[np.float64(627.3796856604346), np.float64(-487.1300049510928)]</t>
+  </si>
+  <si>
+    <t>[np.float64(7.608261181741738), np.float64(-219.23439821766652)]</t>
+  </si>
+  <si>
+    <t>[np.float64(896.3570316887535), np.float64(105.13059077276398)]</t>
+  </si>
+  <si>
+    <t>[np.float64(293.34812335858675), np.float64(-275.5010528505245)]</t>
+  </si>
+  <si>
+    <t>[np.float64(417.89175957608325), np.float64(200.910540615581)]</t>
+  </si>
+  <si>
+    <t>[np.float64(575.7509927722118), np.float64(167.9862649836075)]</t>
+  </si>
+  <si>
+    <t>[np.float64(640.6018180050128), np.float64(-546.4112601291174)]</t>
+  </si>
+  <si>
+    <t>[np.float64(236.02690732823328), np.float64(127.4637808666439)]</t>
+  </si>
+  <si>
+    <t>[np.float64(959.8450045891017), np.float64(270.90878374134127)]</t>
+  </si>
+  <si>
+    <t>[np.float64(124.75057886775708), np.float64(-504.3721170952439)]</t>
   </si>
 </sst>
 </file>
@@ -3221,7 +3191,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I940"/>
+  <dimension ref="A1:I930"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -24620,236 +24590,6 @@
         <v>939</v>
       </c>
     </row>
-    <row r="931" spans="1:9">
-      <c r="A931" t="s">
-        <v>9</v>
-      </c>
-      <c r="B931">
-        <v>0</v>
-      </c>
-      <c r="D931" t="s">
-        <v>10</v>
-      </c>
-      <c r="E931" t="s">
-        <v>10</v>
-      </c>
-      <c r="F931" t="s">
-        <v>10</v>
-      </c>
-      <c r="H931" t="s">
-        <v>940</v>
-      </c>
-      <c r="I931" t="s">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="932" spans="1:9">
-      <c r="A932" t="s">
-        <v>9</v>
-      </c>
-      <c r="B932">
-        <v>0</v>
-      </c>
-      <c r="D932" t="s">
-        <v>10</v>
-      </c>
-      <c r="E932" t="s">
-        <v>10</v>
-      </c>
-      <c r="F932" t="s">
-        <v>10</v>
-      </c>
-      <c r="H932" t="s">
-        <v>941</v>
-      </c>
-      <c r="I932" t="s">
-        <v>941</v>
-      </c>
-    </row>
-    <row r="933" spans="1:9">
-      <c r="A933" t="s">
-        <v>9</v>
-      </c>
-      <c r="B933">
-        <v>0</v>
-      </c>
-      <c r="D933" t="s">
-        <v>10</v>
-      </c>
-      <c r="E933" t="s">
-        <v>10</v>
-      </c>
-      <c r="F933" t="s">
-        <v>10</v>
-      </c>
-      <c r="H933" t="s">
-        <v>942</v>
-      </c>
-      <c r="I933" t="s">
-        <v>942</v>
-      </c>
-    </row>
-    <row r="934" spans="1:9">
-      <c r="A934" t="s">
-        <v>9</v>
-      </c>
-      <c r="B934">
-        <v>0</v>
-      </c>
-      <c r="D934" t="s">
-        <v>10</v>
-      </c>
-      <c r="E934" t="s">
-        <v>10</v>
-      </c>
-      <c r="F934" t="s">
-        <v>10</v>
-      </c>
-      <c r="H934" t="s">
-        <v>943</v>
-      </c>
-      <c r="I934" t="s">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="935" spans="1:9">
-      <c r="A935" t="s">
-        <v>9</v>
-      </c>
-      <c r="B935">
-        <v>0</v>
-      </c>
-      <c r="D935" t="s">
-        <v>10</v>
-      </c>
-      <c r="E935" t="s">
-        <v>10</v>
-      </c>
-      <c r="F935" t="s">
-        <v>10</v>
-      </c>
-      <c r="H935" t="s">
-        <v>944</v>
-      </c>
-      <c r="I935" t="s">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="936" spans="1:9">
-      <c r="A936" t="s">
-        <v>9</v>
-      </c>
-      <c r="B936">
-        <v>0</v>
-      </c>
-      <c r="D936" t="s">
-        <v>10</v>
-      </c>
-      <c r="E936" t="s">
-        <v>10</v>
-      </c>
-      <c r="F936" t="s">
-        <v>10</v>
-      </c>
-      <c r="H936" t="s">
-        <v>945</v>
-      </c>
-      <c r="I936" t="s">
-        <v>945</v>
-      </c>
-    </row>
-    <row r="937" spans="1:9">
-      <c r="A937" t="s">
-        <v>9</v>
-      </c>
-      <c r="B937">
-        <v>0</v>
-      </c>
-      <c r="D937" t="s">
-        <v>10</v>
-      </c>
-      <c r="E937" t="s">
-        <v>10</v>
-      </c>
-      <c r="F937" t="s">
-        <v>10</v>
-      </c>
-      <c r="H937" t="s">
-        <v>946</v>
-      </c>
-      <c r="I937" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="938" spans="1:9">
-      <c r="A938" t="s">
-        <v>9</v>
-      </c>
-      <c r="B938">
-        <v>0</v>
-      </c>
-      <c r="D938" t="s">
-        <v>10</v>
-      </c>
-      <c r="E938" t="s">
-        <v>10</v>
-      </c>
-      <c r="F938" t="s">
-        <v>10</v>
-      </c>
-      <c r="H938" t="s">
-        <v>947</v>
-      </c>
-      <c r="I938" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="939" spans="1:9">
-      <c r="A939" t="s">
-        <v>9</v>
-      </c>
-      <c r="B939">
-        <v>0</v>
-      </c>
-      <c r="D939" t="s">
-        <v>10</v>
-      </c>
-      <c r="E939" t="s">
-        <v>10</v>
-      </c>
-      <c r="F939" t="s">
-        <v>10</v>
-      </c>
-      <c r="H939" t="s">
-        <v>948</v>
-      </c>
-      <c r="I939" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="940" spans="1:9">
-      <c r="A940" t="s">
-        <v>9</v>
-      </c>
-      <c r="B940">
-        <v>0</v>
-      </c>
-      <c r="D940" t="s">
-        <v>10</v>
-      </c>
-      <c r="E940" t="s">
-        <v>10</v>
-      </c>
-      <c r="F940" t="s">
-        <v>10</v>
-      </c>
-      <c r="H940" t="s">
-        <v>949</v>
-      </c>
-      <c r="I940" t="s">
-        <v>949</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Data/output/IND Stroke Position.xlsx
+++ b/Data/output/IND Stroke Position.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5583" uniqueCount="940">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5709" uniqueCount="961">
   <si>
     <t>Direct_or_Indirect</t>
   </si>
@@ -49,2791 +49,2854 @@
     <t>nan</t>
   </si>
   <si>
-    <t>[np.float64(509.11804267826676), np.float64(416.9433683544478)]</t>
-  </si>
-  <si>
-    <t>[np.float64(524.458069935949), np.float64(-457.2629279149801)]</t>
-  </si>
-  <si>
-    <t>[np.float64(251.1826640608519), np.float64(-149.4911013632306)]</t>
-  </si>
-  <si>
-    <t>[np.float64(560.567653272777), np.float64(391.07188634466206)]</t>
-  </si>
-  <si>
-    <t>[np.float64(290.0714565517266), np.float64(57.004848800975765)]</t>
-  </si>
-  <si>
-    <t>[np.float64(390.61856165642337), np.float64(146.40713489975553)]</t>
-  </si>
-  <si>
-    <t>[np.float64(124.47913034510638), np.float64(-414.2384142367572)]</t>
-  </si>
-  <si>
-    <t>[np.float64(117.74275798765765), np.float64(-133.88552955000432)]</t>
-  </si>
-  <si>
-    <t>[np.float64(90.45500153408526), np.float64(121.78627995703175)]</t>
-  </si>
-  <si>
-    <t>[np.float64(257.167147549606), np.float64(-189.4185135451374)]</t>
-  </si>
-  <si>
-    <t>[np.float64(790.7727434844476), np.float64(-425.12669635136604)]</t>
-  </si>
-  <si>
-    <t>[np.float64(34.05974720589955), np.float64(-11.624219225867137)]</t>
-  </si>
-  <si>
-    <t>[np.float64(42.549832384600975), np.float64(-370.86560069338793)]</t>
-  </si>
-  <si>
-    <t>[np.float64(833.3904124312427), np.float64(495.1080564399424)]</t>
-  </si>
-  <si>
-    <t>[np.float64(502.15468923686), np.float64(-539.1033378447395)]</t>
-  </si>
-  <si>
-    <t>[np.float64(933.1485932333355), np.float64(570.6307344768611)]</t>
-  </si>
-  <si>
-    <t>[np.float64(467.8834404033992), np.float64(-318.20177920280173)]</t>
-  </si>
-  <si>
-    <t>[np.float64(231.00528524649556), np.float64(201.04173763877202)]</t>
-  </si>
-  <si>
-    <t>[np.float64(748.8988198551256), np.float64(59.7086697044889)]</t>
-  </si>
-  <si>
-    <t>[np.float64(523.7135577280368), np.float64(-512.1903906004736)]</t>
-  </si>
-  <si>
-    <t>[np.float64(52.16444979002988), np.float64(-177.82097696552074)]</t>
-  </si>
-  <si>
-    <t>[np.float64(519.3702576273151), np.float64(-277.8813302007665)]</t>
-  </si>
-  <si>
-    <t>[np.float64(419.6382939577236), np.float64(114.81357193639758)]</t>
-  </si>
-  <si>
-    <t>[np.float64(152.36662146343016), np.float64(-68.8276701256325)]</t>
-  </si>
-  <si>
-    <t>[np.float64(135.77037534659985), np.float64(426.152419338104)]</t>
-  </si>
-  <si>
-    <t>[np.float64(918.0026130832581), np.float64(231.6622960184601)]</t>
-  </si>
-  <si>
-    <t>[np.float64(130.35373674280726), np.float64(-485.2571110726028)]</t>
-  </si>
-  <si>
-    <t>[np.float64(18.292915818781008), np.float64(-442.34377151212504)]</t>
-  </si>
-  <si>
-    <t>[np.float64(25.424387448188313), np.float64(433.3481032965526)]</t>
-  </si>
-  <si>
-    <t>[np.float64(336.7904835922724), np.float64(166.98429125067946)]</t>
-  </si>
-  <si>
-    <t>[np.float64(43.00908401631276), np.float64(-439.2172437869441)]</t>
-  </si>
-  <si>
-    <t>[np.float64(707.5654621265643), np.float64(-199.11454107527726)]</t>
-  </si>
-  <si>
-    <t>[np.float64(348.1577065794582), np.float64(-353.84379912504596)]</t>
-  </si>
-  <si>
-    <t>[np.float64(23.151435815215613), np.float64(-310.5792050217019)]</t>
-  </si>
-  <si>
-    <t>[np.float64(546.8042554739294), np.float64(-183.14156927748553)]</t>
-  </si>
-  <si>
-    <t>[np.float64(721.7855077870446), np.float64(455.0069592246716)]</t>
-  </si>
-  <si>
-    <t>[np.float64(931.4786795079638), np.float64(278.4971311756026)]</t>
-  </si>
-  <si>
-    <t>[np.float64(678.4343062333828), np.float64(297.41560912199714)]</t>
-  </si>
-  <si>
-    <t>[np.float64(243.23525992434392), np.float64(-262.81578093279194)]</t>
-  </si>
-  <si>
-    <t>[np.float64(958.5051575095782), np.float64(-225.47626088076373)]</t>
-  </si>
-  <si>
-    <t>[np.float64(498.8639875489587), np.float64(8.275514629918007)]</t>
-  </si>
-  <si>
-    <t>[np.float64(267.05518712902534), np.float64(-283.5677952156043)]</t>
-  </si>
-  <si>
-    <t>[np.float64(736.6877338325312), np.float64(305.36974903415216)]</t>
-  </si>
-  <si>
-    <t>[np.float64(879.4049009481591), np.float64(198.05949250615697)]</t>
-  </si>
-  <si>
-    <t>[np.float64(176.88358973011776), np.float64(152.24520387564712)]</t>
-  </si>
-  <si>
-    <t>[np.float64(659.8978493230042), np.float64(430.61965543526617)]</t>
-  </si>
-  <si>
-    <t>[np.float64(753.5260979701279), np.float64(581.0293097641654)]</t>
-  </si>
-  <si>
-    <t>[np.float64(245.87894820921207), np.float64(463.72087240149585)]</t>
-  </si>
-  <si>
-    <t>[np.float64(65.29745022000755), np.float64(441.5181667773636)]</t>
-  </si>
-  <si>
-    <t>[np.float64(163.7267736652004), np.float64(-327.2105690685403)]</t>
-  </si>
-  <si>
-    <t>[np.float64(445.25065974995573), np.float64(265.1723296728301)]</t>
-  </si>
-  <si>
-    <t>[np.float64(485.7875855543969), np.float64(-108.6379614250609)]</t>
-  </si>
-  <si>
-    <t>[np.float64(477.34925824418315), np.float64(-76.16121186307407)]</t>
-  </si>
-  <si>
-    <t>[np.float64(344.03940443200787), np.float64(176.58391078607963)]</t>
-  </si>
-  <si>
-    <t>[np.float64(348.3318084942542), np.float64(-100.28750458083772)]</t>
-  </si>
-  <si>
-    <t>[np.float64(30.373155256539054), np.float64(343.35460398605767)]</t>
-  </si>
-  <si>
-    <t>[np.float64(363.38862179417987), np.float64(351.63006994921557)]</t>
-  </si>
-  <si>
-    <t>[np.float64(14.15149862925924), np.float64(561.6182191020889)]</t>
-  </si>
-  <si>
-    <t>[np.float64(185.98428336827732), np.float64(-167.27377016506495)]</t>
-  </si>
-  <si>
-    <t>[np.float64(434.3361891655353), np.float64(-530.6628080310528)]</t>
-  </si>
-  <si>
-    <t>[np.float64(463.7112470566021), np.float64(191.98098256165406)]</t>
-  </si>
-  <si>
-    <t>[np.float64(215.59217587425005), np.float64(-350.03527906935886)]</t>
-  </si>
-  <si>
-    <t>[np.float64(652.3821692749924), np.float64(77.83386727267452)]</t>
-  </si>
-  <si>
-    <t>[np.float64(701.043395891005), np.float64(-97.34271592356106)]</t>
-  </si>
-  <si>
-    <t>[np.float64(119.146407964278), np.float64(222.75115437612897)]</t>
-  </si>
-  <si>
-    <t>[np.float64(976.0202464464084), np.float64(533.5817985761246)]</t>
-  </si>
-  <si>
-    <t>[np.float64(664.2152869399958), np.float64(284.7709096098687)]</t>
-  </si>
-  <si>
-    <t>[np.float64(945.1237845025562), np.float64(-120.99246761456914)]</t>
-  </si>
-  <si>
-    <t>[np.float64(0.4831479646665304), np.float64(236.34612259990354)]</t>
-  </si>
-  <si>
-    <t>[np.float64(583.6288344730552), np.float64(525.5419082005646)]</t>
-  </si>
-  <si>
-    <t>[np.float64(501.22224504983626), np.float64(-155.22616193538005)]</t>
-  </si>
-  <si>
-    <t>[np.float64(477.32634085617667), np.float64(304.1558796181548)]</t>
-  </si>
-  <si>
-    <t>[np.float64(373.51558745755244), np.float64(-209.7879333868085)]</t>
-  </si>
-  <si>
-    <t>[np.float64(20.165553704077798), np.float64(-171.9502064594853)]</t>
-  </si>
-  <si>
-    <t>[np.float64(219.39488631405612), np.float64(22.99419158305591)]</t>
-  </si>
-  <si>
-    <t>[np.float64(837.8228542350686), np.float64(354.53975318118626)]</t>
-  </si>
-  <si>
-    <t>[np.float64(945.0921907506014), np.float64(146.87860377459435)]</t>
-  </si>
-  <si>
-    <t>[np.float64(131.0191961733035), np.float64(-109.90390567679532)]</t>
-  </si>
-  <si>
-    <t>[np.float64(203.28315202613024), np.float64(360.64334282188315)]</t>
-  </si>
-  <si>
-    <t>[np.float64(93.12312073733963), np.float64(280.02310658317754)]</t>
-  </si>
-  <si>
-    <t>[np.float64(200.3382841131043), np.float64(407.75082134015497)]</t>
-  </si>
-  <si>
-    <t>[np.float64(812.4187107246698), np.float64(-273.50413445744397)]</t>
-  </si>
-  <si>
-    <t>[np.float64(538.222279562979), np.float64(-257.7520605999871)]</t>
-  </si>
-  <si>
-    <t>[np.float64(189.6705020001933), np.float64(-166.34860145959345)]</t>
-  </si>
-  <si>
-    <t>[np.float64(26.83097450594707), np.float64(567.9342054749329)]</t>
-  </si>
-  <si>
-    <t>[np.float64(700.6844692526505), np.float64(558.8912137048005)]</t>
-  </si>
-  <si>
-    <t>[np.float64(794.6145983685136), np.float64(594.6621591198004)]</t>
-  </si>
-  <si>
-    <t>[np.float64(393.0478761988554), np.float64(-364.0460220202237)]</t>
-  </si>
-  <si>
-    <t>[np.float64(90.59024119140224), np.float64(250.8369821924149)]</t>
-  </si>
-  <si>
-    <t>[np.float64(820.4424317519472), np.float64(-417.4213837507958)]</t>
-  </si>
-  <si>
-    <t>[np.float64(555.4782476768544), np.float64(567.2287832629629)]</t>
-  </si>
-  <si>
-    <t>[np.float64(984.3995061556554), np.float64(-208.2806657420793)]</t>
-  </si>
-  <si>
-    <t>[np.float64(282.5561055104099), np.float64(-446.23735027539385)]</t>
-  </si>
-  <si>
-    <t>[np.float64(70.20428195548567), np.float64(559.9209360094858)]</t>
-  </si>
-  <si>
-    <t>[np.float64(203.96756225391155), np.float64(322.4779090818481)]</t>
-  </si>
-  <si>
-    <t>[np.float64(687.5589972699532), np.float64(434.0493632563862)]</t>
-  </si>
-  <si>
-    <t>[np.float64(755.4131998647512), np.float64(326.3786508609219)]</t>
-  </si>
-  <si>
-    <t>[np.float64(461.1636194676646), np.float64(535.4081029403446)]</t>
-  </si>
-  <si>
-    <t>[np.float64(454.2559485288654), np.float64(573.5031292963997)]</t>
-  </si>
-  <si>
-    <t>[np.float64(872.4307416701099), np.float64(530.4393528257685)]</t>
-  </si>
-  <si>
-    <t>[np.float64(908.9036474078899), np.float64(-551.8742799959218)]</t>
-  </si>
-  <si>
-    <t>[np.float64(215.69571359075067), np.float64(310.14369679152503)]</t>
-  </si>
-  <si>
-    <t>[np.float64(395.98461500448735), np.float64(-341.2824935905836)]</t>
-  </si>
-  <si>
-    <t>[np.float64(983.7731102592232), np.float64(-451.2735629211129)]</t>
-  </si>
-  <si>
-    <t>[np.float64(342.2093764302422), np.float64(321.2705183923397)]</t>
-  </si>
-  <si>
-    <t>[np.float64(93.74425227320859), np.float64(281.26872299301203)]</t>
-  </si>
-  <si>
-    <t>[np.float64(263.80069020060427), np.float64(385.38132621918544)]</t>
-  </si>
-  <si>
-    <t>[np.float64(556.628318435453), np.float64(237.19367670164615)]</t>
-  </si>
-  <si>
-    <t>[np.float64(635.4367704829464), np.float64(-79.59210828431446)]</t>
-  </si>
-  <si>
-    <t>[np.float64(177.99090514399074), np.float64(571.550951596872)]</t>
-  </si>
-  <si>
-    <t>[np.float64(180.2285758014044), np.float64(408.7155267650827)]</t>
-  </si>
-  <si>
-    <t>[np.float64(549.2168840305562), np.float64(118.3262019173369)]</t>
-  </si>
-  <si>
-    <t>[np.float64(395.95147885276504), np.float64(276.3934710165746)]</t>
-  </si>
-  <si>
-    <t>[np.float64(546.6457775481873), np.float64(-139.5321805713042)]</t>
-  </si>
-  <si>
-    <t>[np.float64(381.5496052711397), np.float64(143.30963545904626)]</t>
-  </si>
-  <si>
-    <t>[np.float64(324.5417649856772), np.float64(415.4339435435613)]</t>
-  </si>
-  <si>
-    <t>[np.float64(840.1044437790956), np.float64(-472.22990267787924)]</t>
-  </si>
-  <si>
-    <t>[np.float64(742.4527578394044), np.float64(123.98068629787167)]</t>
-  </si>
-  <si>
-    <t>[np.float64(630.5368077975503), np.float64(-305.5406203547234)]</t>
-  </si>
-  <si>
-    <t>[np.float64(718.045446161898), np.float64(-476.83728723625677)]</t>
-  </si>
-  <si>
-    <t>[np.float64(575.7630932211287), np.float64(275.248930121159)]</t>
-  </si>
-  <si>
-    <t>[np.float64(534.7486419538845), np.float64(535.8865958961583)]</t>
-  </si>
-  <si>
-    <t>[np.float64(413.60710427635615), np.float64(239.2543065183287)]</t>
-  </si>
-  <si>
-    <t>[np.float64(813.2512524546144), np.float64(-141.49806253292735)]</t>
-  </si>
-  <si>
-    <t>[np.float64(597.0991603049581), np.float64(-236.7633813427409)]</t>
-  </si>
-  <si>
-    <t>[np.float64(527.5271319971441), np.float64(-561.7651696333845)]</t>
-  </si>
-  <si>
-    <t>[np.float64(540.565419854791), np.float64(545.7635922628274)]</t>
-  </si>
-  <si>
-    <t>[np.float64(41.35386974078514), np.float64(-274.2023024763479)]</t>
-  </si>
-  <si>
-    <t>[np.float64(246.5804916876043), np.float64(-484.1552051909571)]</t>
-  </si>
-  <si>
-    <t>[np.float64(998.2804144402019), np.float64(42.96424887775288)]</t>
-  </si>
-  <si>
-    <t>[np.float64(708.7504662707112), np.float64(61.68220896639764)]</t>
-  </si>
-  <si>
-    <t>[np.float64(13.386382931062313), np.float64(-585.0323066862605)]</t>
-  </si>
-  <si>
-    <t>[np.float64(634.261500987582), np.float64(-588.6002304327116)]</t>
-  </si>
-  <si>
-    <t>[np.float64(141.8086371450966), np.float64(-348.70340582036545)]</t>
-  </si>
-  <si>
-    <t>[np.float64(238.52781526687772), np.float64(135.8340461911945)]</t>
-  </si>
-  <si>
-    <t>[np.float64(212.9925280022873), np.float64(129.88891946723174)]</t>
-  </si>
-  <si>
-    <t>[np.float64(674.6545226093768), np.float64(-590.7328373847735)]</t>
-  </si>
-  <si>
-    <t>[np.float64(145.88843630260985), np.float64(21.84550716816068)]</t>
-  </si>
-  <si>
-    <t>[np.float64(295.8512517470392), np.float64(-554.9047902263467)]</t>
-  </si>
-  <si>
-    <t>[np.float64(645.8259883631439), np.float64(439.823697461507)]</t>
-  </si>
-  <si>
-    <t>[np.float64(658.0121524689508), np.float64(130.50863799297065)]</t>
-  </si>
-  <si>
-    <t>[np.float64(807.532577714892), np.float64(507.3924482344014)]</t>
-  </si>
-  <si>
-    <t>[np.float64(414.8982462245701), np.float64(-236.88925488590155)]</t>
-  </si>
-  <si>
-    <t>[np.float64(684.6997883632429), np.float64(290.0677274987843)]</t>
-  </si>
-  <si>
-    <t>[np.float64(191.62042150187642), np.float64(96.0271607522551)]</t>
-  </si>
-  <si>
-    <t>[np.float64(744.9602263992206), np.float64(341.47128047324134)]</t>
-  </si>
-  <si>
-    <t>[np.float64(258.4881635097559), np.float64(371.77091214128325)]</t>
-  </si>
-  <si>
-    <t>[np.float64(888.0557656048121), np.float64(582.2488637074443)]</t>
-  </si>
-  <si>
-    <t>[np.float64(134.42743980636095), np.float64(461.57438885721035)]</t>
-  </si>
-  <si>
-    <t>[np.float64(505.30442008283984), np.float64(-551.466583199825)]</t>
-  </si>
-  <si>
-    <t>[np.float64(723.8724542766154), np.float64(-140.73485373948915)]</t>
-  </si>
-  <si>
-    <t>[np.float64(87.45394088363668), np.float64(333.2766932219156)]</t>
-  </si>
-  <si>
-    <t>[np.float64(154.1421828642241), np.float64(-479.28678064814386)]</t>
-  </si>
-  <si>
-    <t>[np.float64(488.282258940006), np.float64(-456.4386335857541)]</t>
-  </si>
-  <si>
-    <t>[np.float64(941.046495454798), np.float64(-464.2137251970977)]</t>
-  </si>
-  <si>
-    <t>[np.float64(726.151560975386), np.float64(509.1323948347447)]</t>
-  </si>
-  <si>
-    <t>[np.float64(339.49493875467994), np.float64(-314.53700028059177)]</t>
-  </si>
-  <si>
-    <t>[np.float64(401.5653848510008), np.float64(126.5026742808642)]</t>
-  </si>
-  <si>
-    <t>[np.float64(489.50422980449895), np.float64(289.03060931396215)]</t>
-  </si>
-  <si>
-    <t>[np.float64(628.5628192192663), np.float64(130.66471556885688)]</t>
-  </si>
-  <si>
-    <t>[np.float64(859.5799102150958), np.float64(-362.79779686469743)]</t>
-  </si>
-  <si>
-    <t>[np.float64(896.288491885017), np.float64(233.99028949884428)]</t>
-  </si>
-  <si>
-    <t>[np.float64(348.23404802893464), np.float64(271.8292243042639)]</t>
-  </si>
-  <si>
-    <t>[np.float64(288.22367627840606), np.float64(-203.62700321867493)]</t>
-  </si>
-  <si>
-    <t>[np.float64(15.681125431087573), np.float64(128.6039582949959)]</t>
-  </si>
-  <si>
-    <t>[np.float64(140.6762702950952), np.float64(197.53632316883693)]</t>
-  </si>
-  <si>
-    <t>[np.float64(470.6106821766565), np.float64(-340.0380347875002)]</t>
-  </si>
-  <si>
-    <t>[np.float64(261.8222215029332), np.float64(138.6381101963184)]</t>
-  </si>
-  <si>
-    <t>[np.float64(426.6432047403864), np.float64(157.17453673833836)]</t>
-  </si>
-  <si>
-    <t>[np.float64(177.543829653541), np.float64(-84.50073113770839)]</t>
-  </si>
-  <si>
-    <t>[np.float64(150.43337708507164), np.float64(-557.5122202320804)]</t>
-  </si>
-  <si>
-    <t>[np.float64(817.7010469805003), np.float64(488.9754696713385)]</t>
-  </si>
-  <si>
-    <t>[np.float64(496.48926864692834), np.float64(-551.9282110982845)]</t>
-  </si>
-  <si>
-    <t>[np.float64(690.6827322662942), np.float64(-251.40206076743618)]</t>
-  </si>
-  <si>
-    <t>[np.float64(470.4777261047447), np.float64(201.8717187023666)]</t>
-  </si>
-  <si>
-    <t>[np.float64(937.3836382381124), np.float64(82.59930503673047)]</t>
-  </si>
-  <si>
-    <t>[np.float64(895.7529506866114), np.float64(111.40527799285724)]</t>
-  </si>
-  <si>
-    <t>[np.float64(879.8471093567106), np.float64(-271.15833389141994)]</t>
-  </si>
-  <si>
-    <t>[np.float64(338.74970161846505), np.float64(539.5200583987782)]</t>
-  </si>
-  <si>
-    <t>[np.float64(401.37501405648214), np.float64(513.8282621304686)]</t>
-  </si>
-  <si>
-    <t>[np.float64(139.63616653680467), np.float64(-532.9879119743633)]</t>
-  </si>
-  <si>
-    <t>[np.float64(765.9653667637916), np.float64(272.482248178334)]</t>
-  </si>
-  <si>
-    <t>[np.float64(563.2156639282946), np.float64(-129.31885357023515)]</t>
-  </si>
-  <si>
-    <t>[np.float64(442.99409766318973), np.float64(410.41840477774895)]</t>
-  </si>
-  <si>
-    <t>[np.float64(209.8911298790932), np.float64(-417.84333933603085)]</t>
-  </si>
-  <si>
-    <t>[np.float64(182.2493119931007), np.float64(165.13120246278697)]</t>
-  </si>
-  <si>
-    <t>[np.float64(851.689877787838), np.float64(-360.84237213255886)]</t>
-  </si>
-  <si>
-    <t>[np.float64(103.19533044620476), np.float64(278.30702705577335)]</t>
-  </si>
-  <si>
-    <t>[np.float64(481.7431632141387), np.float64(-406.27185781066487)]</t>
-  </si>
-  <si>
-    <t>[np.float64(298.25405272246064), np.float64(-490.36614509295123)]</t>
-  </si>
-  <si>
-    <t>[np.float64(767.0409270493069), np.float64(421.37224865942574)]</t>
-  </si>
-  <si>
-    <t>[np.float64(3.172776786383724), np.float64(-327.2513035778614)]</t>
-  </si>
-  <si>
-    <t>[np.float64(247.28072194537276), np.float64(-186.51647615454038)]</t>
-  </si>
-  <si>
-    <t>[np.float64(708.892299484124), np.float64(156.5736003969149)]</t>
-  </si>
-  <si>
-    <t>[np.float64(194.78227692569206), np.float64(424.5773520194816)]</t>
-  </si>
-  <si>
-    <t>[np.float64(607.4554131844488), np.float64(244.44709677542357)]</t>
-  </si>
-  <si>
-    <t>[np.float64(266.4032517805803), np.float64(68.29380820399854)]</t>
-  </si>
-  <si>
-    <t>[np.float64(897.3212526953962), np.float64(-153.44684016543636)]</t>
-  </si>
-  <si>
-    <t>[np.float64(998.412394307856), np.float64(277.46882689379845)]</t>
-  </si>
-  <si>
-    <t>[np.float64(942.2701058317155), np.float64(-228.30351036097858)]</t>
-  </si>
-  <si>
-    <t>[np.float64(173.39249748494413), np.float64(-158.20781201551677)]</t>
-  </si>
-  <si>
-    <t>[np.float64(433.64129026601995), np.float64(500.0560350220708)]</t>
-  </si>
-  <si>
-    <t>[np.float64(714.0126470852368), np.float64(169.88830674300038)]</t>
-  </si>
-  <si>
-    <t>[np.float64(350.3420086079129), np.float64(3.6145602282333584)]</t>
-  </si>
-  <si>
-    <t>[np.float64(841.0045347371265), np.float64(426.14637331756035)]</t>
-  </si>
-  <si>
-    <t>[np.float64(554.2982338504763), np.float64(576.7987618388329)]</t>
-  </si>
-  <si>
-    <t>[np.float64(595.8310807136836), np.float64(179.25790108995636)]</t>
-  </si>
-  <si>
-    <t>[np.float64(904.9364597710526), np.float64(-287.810426903992)]</t>
-  </si>
-  <si>
-    <t>[np.float64(88.32960259151767), np.float64(-465.90062426460105)]</t>
-  </si>
-  <si>
-    <t>[np.float64(900.0438359943789), np.float64(-315.912235737523)]</t>
-  </si>
-  <si>
-    <t>[np.float64(911.9639949786273), np.float64(-338.23908787764736)]</t>
-  </si>
-  <si>
-    <t>[np.float64(959.3316696144321), np.float64(-544.6331616933871)]</t>
-  </si>
-  <si>
-    <t>[np.float64(444.7336635594851), np.float64(156.8816993282952)]</t>
-  </si>
-  <si>
-    <t>[np.float64(894.4103505242356), np.float64(35.18026141860753)]</t>
-  </si>
-  <si>
-    <t>[np.float64(643.4177757210625), np.float64(504.9422094204897)]</t>
-  </si>
-  <si>
-    <t>[np.float64(634.3839397724964), np.float64(53.313991578627906)]</t>
-  </si>
-  <si>
-    <t>[np.float64(855.384910216074), np.float64(326.0204129896007)]</t>
-  </si>
-  <si>
-    <t>[np.float64(665.396711258507), np.float64(501.8492055075185)]</t>
-  </si>
-  <si>
-    <t>[np.float64(44.833928684685716), np.float64(448.39750643994284)]</t>
-  </si>
-  <si>
-    <t>[np.float64(288.0882640453397), np.float64(-424.66463797304186)]</t>
-  </si>
-  <si>
-    <t>[np.float64(9.304571966347375), np.float64(-171.29436841578138)]</t>
-  </si>
-  <si>
-    <t>[np.float64(460.9182981489225), np.float64(273.19460073190305)]</t>
-  </si>
-  <si>
-    <t>[np.float64(254.9157998221423), np.float64(-549.8762255249433)]</t>
-  </si>
-  <si>
-    <t>[np.float64(597.54277811349), np.float64(449.2281904053839)]</t>
-  </si>
-  <si>
-    <t>[np.float64(150.75858872860204), np.float64(179.27539301485353)]</t>
-  </si>
-  <si>
-    <t>[np.float64(441.6683287516231), np.float64(-102.9943138979549)]</t>
-  </si>
-  <si>
-    <t>[np.float64(947.3145974279182), np.float64(247.3557299703574)]</t>
-  </si>
-  <si>
-    <t>[np.float64(271.7010180551106), np.float64(50.74748664093045)]</t>
-  </si>
-  <si>
-    <t>[np.float64(334.16398515921765), np.float64(-403.47067345250963)]</t>
-  </si>
-  <si>
-    <t>[np.float64(772.6170335733326), np.float64(-327.39600020927463)]</t>
-  </si>
-  <si>
-    <t>[np.float64(794.9549504954423), np.float64(383.61921763469934)]</t>
-  </si>
-  <si>
-    <t>[np.float64(290.17519777212976), np.float64(100.89405901126588)]</t>
-  </si>
-  <si>
-    <t>[np.float64(275.68337792572527), np.float64(-550.881064930546)]</t>
-  </si>
-  <si>
-    <t>[np.float64(373.6517611386747), np.float64(420.84190038275665)]</t>
-  </si>
-  <si>
-    <t>[np.float64(952.1754704414918), np.float64(494.3993204532269)]</t>
-  </si>
-  <si>
-    <t>[np.float64(617.0759747812268), np.float64(-164.23356948166702)]</t>
-  </si>
-  <si>
-    <t>[np.float64(795.1601219451871), np.float64(-349.96679709093235)]</t>
-  </si>
-  <si>
-    <t>[np.float64(151.63224490522842), np.float64(56.21290717765112)]</t>
-  </si>
-  <si>
-    <t>[np.float64(692.5158930806858), np.float64(146.11959004306232)]</t>
-  </si>
-  <si>
-    <t>[np.float64(89.84948370985579), np.float64(421.1263779005353)]</t>
-  </si>
-  <si>
-    <t>[np.float64(104.2856691738837), np.float64(-193.9337152271769)]</t>
-  </si>
-  <si>
-    <t>[np.float64(752.8115471006482), np.float64(-370.0477396572057)]</t>
-  </si>
-  <si>
-    <t>[np.float64(863.2932275158705), np.float64(21.32478990187451)]</t>
-  </si>
-  <si>
-    <t>[np.float64(25.226366430430858), np.float64(152.9953349663026)]</t>
-  </si>
-  <si>
-    <t>[np.float64(541.8352469752075), np.float64(94.35487119062122)]</t>
-  </si>
-  <si>
-    <t>[np.float64(312.3461290003624), np.float64(456.8681701479022)]</t>
-  </si>
-  <si>
-    <t>[np.float64(376.4938238485204), np.float64(223.10671968457416)]</t>
-  </si>
-  <si>
-    <t>[np.float64(865.321988288673), np.float64(-164.22157247552263)]</t>
-  </si>
-  <si>
-    <t>[np.float64(70.02856347945064), np.float64(177.56119209479368)]</t>
-  </si>
-  <si>
-    <t>[np.float64(565.0448594768139), np.float64(-247.39998477869574)]</t>
-  </si>
-  <si>
-    <t>[np.float64(341.5099863919603), np.float64(142.10433912760368)]</t>
-  </si>
-  <si>
-    <t>[np.float64(214.36165715001988), np.float64(265.4601822578728)]</t>
-  </si>
-  <si>
-    <t>[np.float64(398.4622625934269), np.float64(131.25020212320783)]</t>
-  </si>
-  <si>
-    <t>[np.float64(107.37242131813962), np.float64(-163.89198236839718)]</t>
-  </si>
-  <si>
-    <t>[np.float64(567.5680317521994), np.float64(-178.31834976958083)]</t>
-  </si>
-  <si>
-    <t>[np.float64(992.0514314738123), np.float64(76.15448680196221)]</t>
-  </si>
-  <si>
-    <t>[np.float64(627.0457757302673), np.float64(316.8945016979279)]</t>
-  </si>
-  <si>
-    <t>[np.float64(434.8025138188032), np.float64(554.1910539320884)]</t>
-  </si>
-  <si>
-    <t>[np.float64(89.71560795722111), np.float64(56.17526251434572)]</t>
-  </si>
-  <si>
-    <t>[np.float64(613.028034987524), np.float64(327.92801166670415)]</t>
-  </si>
-  <si>
-    <t>[np.float64(616.8558823658472), np.float64(-272.55634165841883)]</t>
-  </si>
-  <si>
-    <t>[np.float64(201.07043107823452), np.float64(323.0529057682827)]</t>
-  </si>
-  <si>
-    <t>[np.float64(914.3651490644684), np.float64(-70.32077907583187)]</t>
-  </si>
-  <si>
-    <t>[np.float64(498.9940456972365), np.float64(530.9735077158414)]</t>
-  </si>
-  <si>
-    <t>[np.float64(187.87619002770083), np.float64(-197.40151842576682)]</t>
-  </si>
-  <si>
-    <t>[np.float64(547.5862141732126), np.float64(-224.94073907968703)]</t>
-  </si>
-  <si>
-    <t>[np.float64(64.50802339465234), np.float64(-238.6940860254158)]</t>
-  </si>
-  <si>
-    <t>[np.float64(731.7655160271025), np.float64(190.03679519214575)]</t>
-  </si>
-  <si>
-    <t>[np.float64(643.5759256343068), np.float64(-516.5150533806275)]</t>
-  </si>
-  <si>
-    <t>[np.float64(809.7757979166374), np.float64(-543.5580030633662)]</t>
-  </si>
-  <si>
-    <t>[np.float64(49.166774335870244), np.float64(-518.0631493142158)]</t>
-  </si>
-  <si>
-    <t>[np.float64(229.83962675853653), np.float64(-445.02625219697217)]</t>
-  </si>
-  <si>
-    <t>[np.float64(328.58268167487626), np.float64(-428.82462163977186)]</t>
-  </si>
-  <si>
-    <t>[np.float64(641.3559413434709), np.float64(-195.0710121862968)]</t>
-  </si>
-  <si>
-    <t>[np.float64(788.0967662701823), np.float64(-104.66745987417806)]</t>
-  </si>
-  <si>
-    <t>[np.float64(360.2717371299985), np.float64(-498.2688621645741)]</t>
-  </si>
-  <si>
-    <t>[np.float64(904.6268933988368), np.float64(95.90094636820595)]</t>
-  </si>
-  <si>
-    <t>[np.float64(451.7108243317712), np.float64(586.8092794300696)]</t>
-  </si>
-  <si>
-    <t>[np.float64(248.67057618009682), np.float64(471.1802354101653)]</t>
-  </si>
-  <si>
-    <t>[np.float64(77.96270590008503), np.float64(-486.3194073910133)]</t>
-  </si>
-  <si>
-    <t>[np.float64(499.64424827191846), np.float64(536.5217187470566)]</t>
-  </si>
-  <si>
-    <t>[np.float64(557.6299732540651), np.float64(95.42619595854921)]</t>
-  </si>
-  <si>
-    <t>[np.float64(391.64534279501373), np.float64(596.4451013198914)]</t>
-  </si>
-  <si>
-    <t>[np.float64(555.485781267054), np.float64(554.1771595993766)]</t>
-  </si>
-  <si>
-    <t>[np.float64(328.92152787069506), np.float64(-565.3154966093891)]</t>
-  </si>
-  <si>
-    <t>[np.float64(673.480366598161), np.float64(-168.87500428076947)]</t>
-  </si>
-  <si>
-    <t>[np.float64(151.5862708468434), np.float64(-494.57555824971314)]</t>
-  </si>
-  <si>
-    <t>[np.float64(845.67801248341), np.float64(75.48855488041693)]</t>
-  </si>
-  <si>
-    <t>[np.float64(404.36484646216775), np.float64(346.32728679695526)]</t>
-  </si>
-  <si>
-    <t>[np.float64(774.145346900322), np.float64(-201.62410647786476)]</t>
-  </si>
-  <si>
-    <t>[np.float64(63.00221153387231), np.float64(397.77180700677866)]</t>
-  </si>
-  <si>
-    <t>[np.float64(725.1557366727909), np.float64(-379.4179946160509)]</t>
-  </si>
-  <si>
-    <t>[np.float64(165.76303114725033), np.float64(-253.6361910548971)]</t>
-  </si>
-  <si>
-    <t>[np.float64(159.70366469744246), np.float64(-469.17846724190395)]</t>
-  </si>
-  <si>
-    <t>[np.float64(818.5506318317293), np.float64(501.7960769079057)]</t>
-  </si>
-  <si>
-    <t>[np.float64(760.0766507268971), np.float64(481.20873831918175)]</t>
-  </si>
-  <si>
-    <t>[np.float64(221.99294447040586), np.float64(-224.22739868191945)]</t>
-  </si>
-  <si>
-    <t>[np.float64(985.2732302619306), np.float64(135.80331186109618)]</t>
-  </si>
-  <si>
-    <t>[np.float64(665.6184403003178), np.float64(442.7056017373652)]</t>
-  </si>
-  <si>
-    <t>[np.float64(82.10670848974289), np.float64(420.86625309968485)]</t>
-  </si>
-  <si>
-    <t>[np.float64(811.040118952639), np.float64(336.0808958589315)]</t>
-  </si>
-  <si>
-    <t>[np.float64(626.4893114231055), np.float64(-311.6273256971647)]</t>
-  </si>
-  <si>
-    <t>[np.float64(665.0360296861982), np.float64(-469.19672805133735)]</t>
-  </si>
-  <si>
-    <t>[np.float64(719.8039872871703), np.float64(165.24420357720862)]</t>
-  </si>
-  <si>
-    <t>[np.float64(575.6689167493246), np.float64(-280.35335576131104)]</t>
-  </si>
-  <si>
-    <t>[np.float64(2.279239774592212), np.float64(-206.26249098859785)]</t>
-  </si>
-  <si>
-    <t>[np.float64(397.64292082753207), np.float64(136.89879902918415)]</t>
-  </si>
-  <si>
-    <t>[np.float64(383.276904958322), np.float64(145.71338202517063)]</t>
-  </si>
-  <si>
-    <t>[np.float64(209.41015149723597), np.float64(-533.4120479843538)]</t>
-  </si>
-  <si>
-    <t>[np.float64(857.1940108122375), np.float64(481.4145011244343)]</t>
-  </si>
-  <si>
-    <t>[np.float64(853.047902807916), np.float64(-261.19318732988864)]</t>
-  </si>
-  <si>
-    <t>[np.float64(73.01139171929837), np.float64(482.21187657323344)]</t>
-  </si>
-  <si>
-    <t>[np.float64(755.8487296539059), np.float64(-198.10234301808254)]</t>
-  </si>
-  <si>
-    <t>[np.float64(900.6456049925168), np.float64(301.45042768199096)]</t>
-  </si>
-  <si>
-    <t>[np.float64(809.2977614581133), np.float64(358.5512898305258)]</t>
-  </si>
-  <si>
-    <t>[np.float64(414.86090613822824), np.float64(525.9672627628254)]</t>
-  </si>
-  <si>
-    <t>[np.float64(881.6757691889454), np.float64(89.56366815585568)]</t>
-  </si>
-  <si>
-    <t>[np.float64(428.4252833476638), np.float64(-463.5695259156404)]</t>
-  </si>
-  <si>
-    <t>[np.float64(98.05536508439295), np.float64(-224.95002791446467)]</t>
-  </si>
-  <si>
-    <t>[np.float64(456.8121653890188), np.float64(524.6832390436962)]</t>
-  </si>
-  <si>
-    <t>[np.float64(136.17221188978323), np.float64(207.7070642953878)]</t>
-  </si>
-  <si>
-    <t>[np.float64(57.563915345893115), np.float64(500.2353339646727)]</t>
-  </si>
-  <si>
-    <t>[np.float64(293.18554830200793), np.float64(358.46167144859953)]</t>
-  </si>
-  <si>
-    <t>[np.float64(325.5710390715171), np.float64(-316.0128323790581)]</t>
-  </si>
-  <si>
-    <t>[np.float64(168.7108949176882), np.float64(142.5946880242583)]</t>
-  </si>
-  <si>
-    <t>[np.float64(948.0819889864953), np.float64(-426.8307957671822)]</t>
-  </si>
-  <si>
-    <t>[np.float64(275.77087165807967), np.float64(454.6360140436293)]</t>
-  </si>
-  <si>
-    <t>[np.float64(398.39684133154185), np.float64(412.75637254759874)]</t>
-  </si>
-  <si>
-    <t>[np.float64(885.4155195023803), np.float64(273.3955170738775)]</t>
-  </si>
-  <si>
-    <t>[np.float64(353.6828867807162), np.float64(17.63063047689286)]</t>
-  </si>
-  <si>
-    <t>[np.float64(892.5830079125583), np.float64(499.04910345383496)]</t>
-  </si>
-  <si>
-    <t>[np.float64(598.465799035888), np.float64(335.2192095585773)]</t>
-  </si>
-  <si>
-    <t>[np.float64(815.5407805045319), np.float64(-505.70371023041264)]</t>
-  </si>
-  <si>
-    <t>[np.float64(314.22275324506876), np.float64(255.4402889362991)]</t>
-  </si>
-  <si>
-    <t>[np.float64(131.1492869388544), np.float64(456.9734125763566)]</t>
-  </si>
-  <si>
-    <t>[np.float64(777.6874860034784), np.float64(71.7647275600458)]</t>
-  </si>
-  <si>
-    <t>[np.float64(175.01388560368304), np.float64(-586.4091842231044)]</t>
-  </si>
-  <si>
-    <t>[np.float64(347.7735187174409), np.float64(417.8189442469653)]</t>
-  </si>
-  <si>
-    <t>[np.float64(42.88666192993129), np.float64(378.5422250885698)]</t>
-  </si>
-  <si>
-    <t>[np.float64(826.3953634706803), np.float64(501.9731399757734)]</t>
-  </si>
-  <si>
-    <t>[np.float64(155.93850559922052), np.float64(8.090287182983616)]</t>
-  </si>
-  <si>
-    <t>[np.float64(117.67727425982433), np.float64(-115.43711921731807)]</t>
-  </si>
-  <si>
-    <t>[np.float64(862.1326671776791), np.float64(-363.9903536628707)]</t>
-  </si>
-  <si>
-    <t>[np.float64(693.366389923262), np.float64(347.1666375123043)]</t>
-  </si>
-  <si>
-    <t>[np.float64(773.3428903977476), np.float64(44.08359188512327)]</t>
-  </si>
-  <si>
-    <t>[np.float64(457.5461273391336), np.float64(-500.3187301938556)]</t>
-  </si>
-  <si>
-    <t>[np.float64(666.2621512887866), np.float64(235.4997356629409)]</t>
-  </si>
-  <si>
-    <t>[np.float64(945.2053789070698), np.float64(-508.5647511603946)]</t>
-  </si>
-  <si>
-    <t>[np.float64(104.61461624056578), np.float64(565.7909184657235)]</t>
-  </si>
-  <si>
-    <t>[np.float64(354.50372691497813), np.float64(-458.96253212986244)]</t>
-  </si>
-  <si>
-    <t>[np.float64(993.8160274453535), np.float64(174.66101673983485)]</t>
-  </si>
-  <si>
-    <t>[np.float64(198.54030793369492), np.float64(-154.70656451439646)]</t>
-  </si>
-  <si>
-    <t>[np.float64(897.5556140672627), np.float64(-328.98475250707986)]</t>
-  </si>
-  <si>
-    <t>[np.float64(254.9604841674642), np.float64(-403.04492850341563)]</t>
-  </si>
-  <si>
-    <t>[np.float64(642.2616984863259), np.float64(-416.3965499280961)]</t>
-  </si>
-  <si>
-    <t>[np.float64(186.2293582232306), np.float64(581.4746168327681)]</t>
-  </si>
-  <si>
-    <t>[np.float64(171.11098528857337), np.float64(-579.5702857080532)]</t>
-  </si>
-  <si>
-    <t>[np.float64(334.9469924607317), np.float64(286.65004631075453)]</t>
-  </si>
-  <si>
-    <t>[np.float64(696.4755775295139), np.float64(-514.0714782628168)]</t>
-  </si>
-  <si>
-    <t>[np.float64(191.55785727211781), np.float64(481.5250810715322)]</t>
-  </si>
-  <si>
-    <t>[np.float64(83.65943379514972), np.float64(-107.65893823330225)]</t>
-  </si>
-  <si>
-    <t>[np.float64(102.16115659501635), np.float64(75.54042846939603)]</t>
-  </si>
-  <si>
-    <t>[np.float64(872.3353983792802), np.float64(-472.75587265295536)]</t>
-  </si>
-  <si>
-    <t>[np.float64(686.3366164585367), np.float64(-121.70669234580623)]</t>
-  </si>
-  <si>
-    <t>[np.float64(803.2140004850611), np.float64(-266.36069705961665)]</t>
-  </si>
-  <si>
-    <t>[np.float64(852.6364417831876), np.float64(-403.6429417349681)]</t>
-  </si>
-  <si>
-    <t>[np.float64(885.7957124301291), np.float64(272.1248162512877)]</t>
-  </si>
-  <si>
-    <t>[np.float64(317.0272911157026), np.float64(577.9668357418298)]</t>
-  </si>
-  <si>
-    <t>[np.float64(830.1937884644108), np.float64(-244.19891743076164)]</t>
-  </si>
-  <si>
-    <t>[np.float64(614.3929997869701), np.float64(-548.7259350466153)]</t>
-  </si>
-  <si>
-    <t>[np.float64(618.6154083854487), np.float64(512.3415465392197)]</t>
-  </si>
-  <si>
-    <t>[np.float64(612.6345357997698), np.float64(557.9924307827596)]</t>
-  </si>
-  <si>
-    <t>[np.float64(801.6567891443281), np.float64(252.75092312865922)]</t>
-  </si>
-  <si>
-    <t>[np.float64(180.38685001818533), np.float64(-189.40754359370015)]</t>
-  </si>
-  <si>
-    <t>[np.float64(308.13769871568974), np.float64(-481.9088829693183)]</t>
-  </si>
-  <si>
-    <t>[np.float64(281.7815410498634), np.float64(538.0593377003888)]</t>
-  </si>
-  <si>
-    <t>[np.float64(904.0315862696029), np.float64(24.46575997203695)]</t>
-  </si>
-  <si>
-    <t>[np.float64(6.877933343942488), np.float64(-224.4304209955227)]</t>
-  </si>
-  <si>
-    <t>[np.float64(108.39002774521822), np.float64(308.3727547061013)]</t>
-  </si>
-  <si>
-    <t>[np.float64(455.14691382768314), np.float64(586.4533995628135)]</t>
-  </si>
-  <si>
-    <t>[np.float64(225.6139393916391), np.float64(226.88430203031498)]</t>
-  </si>
-  <si>
-    <t>[np.float64(596.5682773362287), np.float64(459.61893083948803)]</t>
-  </si>
-  <si>
-    <t>[np.float64(269.3128121208026), np.float64(438.4038296479828)]</t>
-  </si>
-  <si>
-    <t>[np.float64(898.6456936882755), np.float64(-87.1082743564316)]</t>
-  </si>
-  <si>
-    <t>[np.float64(35.05899596481721), np.float64(185.74230321967673)]</t>
-  </si>
-  <si>
-    <t>[np.float64(223.1919541025058), np.float64(395.710714263402)]</t>
-  </si>
-  <si>
-    <t>[np.float64(495.0579270609906), np.float64(359.7952513023487)]</t>
-  </si>
-  <si>
-    <t>[np.float64(421.64511575608964), np.float64(252.96472391266627)]</t>
-  </si>
-  <si>
-    <t>[np.float64(850.8744681763507), np.float64(361.5062768963114)]</t>
-  </si>
-  <si>
-    <t>[np.float64(606.5552740267345), np.float64(-306.7404895346928)]</t>
-  </si>
-  <si>
-    <t>[np.float64(846.4685695853875), np.float64(-328.8975302262332)]</t>
-  </si>
-  <si>
-    <t>[np.float64(925.0007975498845), np.float64(-282.7410860982977)]</t>
-  </si>
-  <si>
-    <t>[np.float64(199.01917233580468), np.float64(-194.86967875858085)]</t>
-  </si>
-  <si>
-    <t>[np.float64(147.21796843667923), np.float64(168.8329122300803)]</t>
-  </si>
-  <si>
-    <t>[np.float64(672.2600072992946), np.float64(498.06943658508726)]</t>
-  </si>
-  <si>
-    <t>[np.float64(786.1898190599867), np.float64(419.1730353601017)]</t>
-  </si>
-  <si>
-    <t>[np.float64(417.585075442512), np.float64(80.77969677922204)]</t>
-  </si>
-  <si>
-    <t>[np.float64(666.8972009023792), np.float64(372.09590836577866)]</t>
-  </si>
-  <si>
-    <t>[np.float64(719.417170291803), np.float64(501.26073859436383)]</t>
-  </si>
-  <si>
-    <t>[np.float64(415.28453212436887), np.float64(-216.80918146748894)]</t>
-  </si>
-  <si>
-    <t>[np.float64(897.3130351909143), np.float64(289.6413361071134)]</t>
-  </si>
-  <si>
-    <t>[np.float64(475.5636504051841), np.float64(-230.8113558087523)]</t>
-  </si>
-  <si>
-    <t>[np.float64(134.04062210162093), np.float64(130.68328617309373)]</t>
-  </si>
-  <si>
-    <t>[np.float64(293.06017319669843), np.float64(-379.8390667918816)]</t>
-  </si>
-  <si>
-    <t>[np.float64(878.8626408358267), np.float64(52.580509074318)]</t>
-  </si>
-  <si>
-    <t>[np.float64(100.82717220953074), np.float64(-83.74403354452033)]</t>
-  </si>
-  <si>
-    <t>[np.float64(484.49865089122125), np.float64(-488.22412437428494)]</t>
-  </si>
-  <si>
-    <t>[np.float64(490.1440485557356), np.float64(-401.51638240637334)]</t>
-  </si>
-  <si>
-    <t>[np.float64(942.8952126819504), np.float64(-520.8268394964585)]</t>
-  </si>
-  <si>
-    <t>[np.float64(862.6283249154034), np.float64(284.90865957365736)]</t>
-  </si>
-  <si>
-    <t>[np.float64(895.9896151293317), np.float64(509.8871321343704)]</t>
-  </si>
-  <si>
-    <t>[np.float64(165.6363079310983), np.float64(52.27277662736765)]</t>
-  </si>
-  <si>
-    <t>[np.float64(83.08283875374667), np.float64(-364.7589253581199)]</t>
-  </si>
-  <si>
-    <t>[np.float64(227.03683467787982), np.float64(-341.8447630874894)]</t>
-  </si>
-  <si>
-    <t>[np.float64(677.848016564996), np.float64(-449.8410303922177)]</t>
-  </si>
-  <si>
-    <t>[np.float64(879.9276907423919), np.float64(454.4234040675117)]</t>
-  </si>
-  <si>
-    <t>[np.float64(994.5099833026043), np.float64(-546.410103963047)]</t>
-  </si>
-  <si>
-    <t>[np.float64(466.4435885667434), np.float64(365.25774444631406)]</t>
-  </si>
-  <si>
-    <t>[np.float64(895.5019828682791), np.float64(-201.02447300268784)]</t>
-  </si>
-  <si>
-    <t>[np.float64(942.3078255020844), np.float64(190.478437144998)]</t>
-  </si>
-  <si>
-    <t>[np.float64(671.5060100606352), np.float64(-274.23653153388545)]</t>
-  </si>
-  <si>
-    <t>[np.float64(945.6208447346685), np.float64(89.6870569269289)]</t>
-  </si>
-  <si>
-    <t>[np.float64(429.43108731059556), np.float64(386.1700613301613)]</t>
-  </si>
-  <si>
-    <t>[np.float64(617.071197618564), np.float64(439.9350943256195)]</t>
-  </si>
-  <si>
-    <t>[np.float64(487.571607394514), np.float64(-373.80871041078615)]</t>
-  </si>
-  <si>
-    <t>[np.float64(619.6904861691116), np.float64(-480.66028637095394)]</t>
-  </si>
-  <si>
-    <t>[np.float64(898.1145055971177), np.float64(178.75492581130356)]</t>
-  </si>
-  <si>
-    <t>[np.float64(802.7253759559368), np.float64(210.6843067758499)]</t>
-  </si>
-  <si>
-    <t>[np.float64(885.8388203655737), np.float64(-94.25623592304817)]</t>
-  </si>
-  <si>
-    <t>[np.float64(646.7515512027185), np.float64(-531.2558272480351)]</t>
-  </si>
-  <si>
-    <t>[np.float64(575.9587405697678), np.float64(-302.41036003012994)]</t>
-  </si>
-  <si>
-    <t>[np.float64(568.6831131612491), np.float64(472.8787381301129)]</t>
-  </si>
-  <si>
-    <t>[np.float64(91.7481023417167), np.float64(244.17513416848897)]</t>
-  </si>
-  <si>
-    <t>[np.float64(952.4827208612303), np.float64(415.6730099675676)]</t>
-  </si>
-  <si>
-    <t>[np.float64(697.7973131983433), np.float64(-589.1143972548892)]</t>
-  </si>
-  <si>
-    <t>[np.float64(491.88920651254875), np.float64(188.36243554415876)]</t>
-  </si>
-  <si>
-    <t>[np.float64(881.6906378564968), np.float64(191.39537267535104)]</t>
-  </si>
-  <si>
-    <t>[np.float64(612.4206652998912), np.float64(-591.8218230929646)]</t>
-  </si>
-  <si>
-    <t>[np.float64(964.6181914892935), np.float64(-466.4334990213817)]</t>
-  </si>
-  <si>
-    <t>[np.float64(96.45142493103442), np.float64(-395.1492713741454)]</t>
-  </si>
-  <si>
-    <t>[np.float64(482.09607472306794), np.float64(-407.5647833561131)]</t>
-  </si>
-  <si>
-    <t>[np.float64(325.1027950942967), np.float64(-97.64222591015812)]</t>
-  </si>
-  <si>
-    <t>[np.float64(678.3598059312216), np.float64(-154.8088828224183)]</t>
-  </si>
-  <si>
-    <t>[np.float64(371.784329566671), np.float64(-135.11294365680203)]</t>
-  </si>
-  <si>
-    <t>[np.float64(614.9284392360983), np.float64(-184.8898347341476)]</t>
-  </si>
-  <si>
-    <t>[np.float64(906.9720259174428), np.float64(19.285121239813066)]</t>
-  </si>
-  <si>
-    <t>[np.float64(522.1481068306748), np.float64(-358.8653403885349)]</t>
-  </si>
-  <si>
-    <t>[np.float64(190.07778982311086), np.float64(365.1891879712455)]</t>
-  </si>
-  <si>
-    <t>[np.float64(785.5870981280106), np.float64(-498.7927409387369)]</t>
-  </si>
-  <si>
-    <t>[np.float64(255.57141775657232), np.float64(-425.1432525319399)]</t>
-  </si>
-  <si>
-    <t>[np.float64(441.52868081258333), np.float64(573.8159040345245)]</t>
-  </si>
-  <si>
-    <t>[np.float64(121.74387794073593), np.float64(21.215763839619058)]</t>
-  </si>
-  <si>
-    <t>[np.float64(167.6277640616609), np.float64(579.1814202258345)]</t>
-  </si>
-  <si>
-    <t>[np.float64(102.70309773392717), np.float64(-503.97277332159945)]</t>
-  </si>
-  <si>
-    <t>[np.float64(953.35184762691), np.float64(285.2291729295953)]</t>
-  </si>
-  <si>
-    <t>[np.float64(113.60934372784625), np.float64(-568.2749411427855)]</t>
-  </si>
-  <si>
-    <t>[np.float64(353.3320499308058), np.float64(485.44994228804285)]</t>
-  </si>
-  <si>
-    <t>[np.float64(616.372176220192), np.float64(25.948827712159073)]</t>
-  </si>
-  <si>
-    <t>[np.float64(828.9264100897443), np.float64(346.0913200303596)]</t>
-  </si>
-  <si>
-    <t>[np.float64(870.9565763965485), np.float64(581.9800542696134)]</t>
-  </si>
-  <si>
-    <t>[np.float64(280.8884375490697), np.float64(245.25425975090752)]</t>
-  </si>
-  <si>
-    <t>[np.float64(400.6815152877512), np.float64(-217.8031068999448)]</t>
-  </si>
-  <si>
-    <t>[np.float64(873.3359296596118), np.float64(389.14872543526667)]</t>
-  </si>
-  <si>
-    <t>[np.float64(548.0632575218974), np.float64(-383.96377215442584)]</t>
-  </si>
-  <si>
-    <t>[np.float64(425.7187827119322), np.float64(519.874844314123)]</t>
-  </si>
-  <si>
-    <t>[np.float64(507.03390134711765), np.float64(218.6691323529983)]</t>
-  </si>
-  <si>
-    <t>[np.float64(465.9225067374381), np.float64(318.6473692799051)]</t>
-  </si>
-  <si>
-    <t>[np.float64(959.136980051234), np.float64(445.1711756245718)]</t>
-  </si>
-  <si>
-    <t>[np.float64(485.083973502445), np.float64(500.38798193802154)]</t>
-  </si>
-  <si>
-    <t>[np.float64(282.48504664839925), np.float64(-341.74611370266604)]</t>
-  </si>
-  <si>
-    <t>[np.float64(805.627798295162), np.float64(-466.7468823217453)]</t>
-  </si>
-  <si>
-    <t>[np.float64(517.0803944828712), np.float64(113.92789714796652)]</t>
-  </si>
-  <si>
-    <t>[np.float64(843.8743008706937), np.float64(-332.8376002040379)]</t>
-  </si>
-  <si>
-    <t>[np.float64(591.4904149011921), np.float64(449.3851573834563)]</t>
-  </si>
-  <si>
-    <t>[np.float64(343.9701973563027), np.float64(144.77688384992337)]</t>
-  </si>
-  <si>
-    <t>[np.float64(344.0695058110189), np.float64(475.0600395835547)]</t>
-  </si>
-  <si>
-    <t>[np.float64(700.6888458570652), np.float64(115.82970746568003)]</t>
-  </si>
-  <si>
-    <t>[np.float64(70.8547207257998), np.float64(296.1402399682057)]</t>
-  </si>
-  <si>
-    <t>[np.float64(893.9735070367467), np.float64(74.08726234556218)]</t>
-  </si>
-  <si>
-    <t>[np.float64(237.14583762172668), np.float64(-422.926807728574)]</t>
-  </si>
-  <si>
-    <t>[np.float64(251.2971788291869), np.float64(220.72790708913897)]</t>
-  </si>
-  <si>
-    <t>[np.float64(707.6261899757739), np.float64(-583.9294272020611)]</t>
-  </si>
-  <si>
-    <t>[np.float64(749.5505730071142), np.float64(357.87145633232626)]</t>
-  </si>
-  <si>
-    <t>[np.float64(882.8659459124643), np.float64(529.5239819108763)]</t>
-  </si>
-  <si>
-    <t>[np.float64(267.02343879345415), np.float64(-555.5242505984074)]</t>
-  </si>
-  <si>
-    <t>[np.float64(616.7149580735014), np.float64(34.025712572612406)]</t>
-  </si>
-  <si>
-    <t>[np.float64(880.4379537216665), np.float64(-288.2748991856356)]</t>
-  </si>
-  <si>
-    <t>[np.float64(50.76674038147111), np.float64(-483.90057854574115)]</t>
-  </si>
-  <si>
-    <t>[np.float64(929.6758430761632), np.float64(564.7340248980381)]</t>
-  </si>
-  <si>
-    <t>[np.float64(626.7183130940018), np.float64(-279.72606645804615)]</t>
-  </si>
-  <si>
-    <t>[np.float64(490.42316376298334), np.float64(360.52559522104616)]</t>
-  </si>
-  <si>
-    <t>[np.float64(660.2407540372827), np.float64(565.085075010071)]</t>
-  </si>
-  <si>
-    <t>[np.float64(103.70301545136829), np.float64(-330.6036129798723)]</t>
-  </si>
-  <si>
-    <t>[np.float64(945.4248106625057), np.float64(298.57412281262543)]</t>
-  </si>
-  <si>
-    <t>[np.float64(305.9891250514277), np.float64(-305.7694118195952)]</t>
-  </si>
-  <si>
-    <t>[np.float64(898.1193106535386), np.float64(-557.6302630464611)]</t>
-  </si>
-  <si>
-    <t>[np.float64(216.55842241003242), np.float64(239.98010286563317)]</t>
-  </si>
-  <si>
-    <t>[np.float64(530.1708028349394), np.float64(-177.91600296474616)]</t>
-  </si>
-  <si>
-    <t>[np.float64(485.9790905960849), np.float64(152.03656114935131)]</t>
-  </si>
-  <si>
-    <t>[np.float64(517.1068949915824), np.float64(-341.066931651036)]</t>
-  </si>
-  <si>
-    <t>[np.float64(863.5869987562495), np.float64(-321.7163309688003)]</t>
-  </si>
-  <si>
-    <t>[np.float64(480.50495120544014), np.float64(69.04766033992689)]</t>
-  </si>
-  <si>
-    <t>[np.float64(509.4301080841671), np.float64(-274.8951845680209)]</t>
-  </si>
-  <si>
-    <t>[np.float64(746.1889066426828), np.float64(19.035090571227897)]</t>
-  </si>
-  <si>
-    <t>[np.float64(190.00366796653424), np.float64(442.5247555719502)]</t>
-  </si>
-  <si>
-    <t>[np.float64(778.1643593536498), np.float64(464.56853137272174)]</t>
-  </si>
-  <si>
-    <t>[np.float64(466.10465672394463), np.float64(-315.39223906833524)]</t>
-  </si>
-  <si>
-    <t>[np.float64(285.3207321572502), np.float64(385.8841101820009)]</t>
-  </si>
-  <si>
-    <t>[np.float64(158.54472197513593), np.float64(388.43840490899595)]</t>
-  </si>
-  <si>
-    <t>[np.float64(984.2833379877269), np.float64(594.7874781222583)]</t>
-  </si>
-  <si>
-    <t>[np.float64(562.0122365115816), np.float64(-468.2895756493116)]</t>
-  </si>
-  <si>
-    <t>[np.float64(713.9375853108561), np.float64(205.37983300246378)]</t>
-  </si>
-  <si>
-    <t>[np.float64(116.48962279022057), np.float64(462.93029783486077)]</t>
-  </si>
-  <si>
-    <t>[np.float64(981.8671880646939), np.float64(-227.9099216485776)]</t>
-  </si>
-  <si>
-    <t>[np.float64(113.76650713697734), np.float64(-189.64839871662008)]</t>
-  </si>
-  <si>
-    <t>[np.float64(330.1329544686238), np.float64(210.8375336957739)]</t>
-  </si>
-  <si>
-    <t>[np.float64(640.2918787491391), np.float64(208.58158502833317)]</t>
-  </si>
-  <si>
-    <t>[np.float64(466.8584005121983), np.float64(-239.13854863364043)]</t>
-  </si>
-  <si>
-    <t>[np.float64(774.8054429248759), np.float64(-201.93772489177115)]</t>
-  </si>
-  <si>
-    <t>[np.float64(226.85704386471116), np.float64(69.8592707416949)]</t>
-  </si>
-  <si>
-    <t>[np.float64(809.0546132046544), np.float64(455.3257887206571)]</t>
-  </si>
-  <si>
-    <t>[np.float64(419.5365269469358), np.float64(-270.46029013773494)]</t>
-  </si>
-  <si>
-    <t>[np.float64(132.28021298181224), np.float64(-264.59781015517166)]</t>
-  </si>
-  <si>
-    <t>[np.float64(535.7874434564201), np.float64(-598.7942052494714)]</t>
-  </si>
-  <si>
-    <t>[np.float64(749.642840455673), np.float64(-326.2972772963592)]</t>
-  </si>
-  <si>
-    <t>[np.float64(812.6315451479334), np.float64(199.41671522320394)]</t>
-  </si>
-  <si>
-    <t>[np.float64(969.2171125308606), np.float64(-524.1784645726993)]</t>
-  </si>
-  <si>
-    <t>[np.float64(938.1206701436683), np.float64(-567.7524684242901)]</t>
-  </si>
-  <si>
-    <t>[np.float64(618.2131182335414), np.float64(170.2602948962866)]</t>
-  </si>
-  <si>
-    <t>[np.float64(678.9943058581391), np.float64(274.68327221956054)]</t>
-  </si>
-  <si>
-    <t>[np.float64(61.510376472671105), np.float64(-292.74889032144034)]</t>
-  </si>
-  <si>
-    <t>[np.float64(720.7479040989625), np.float64(-114.91178798016279)]</t>
-  </si>
-  <si>
-    <t>[np.float64(998.799330576446), np.float64(-471.55453814297016)]</t>
-  </si>
-  <si>
-    <t>[np.float64(199.46329085289972), np.float64(82.9929790018466)]</t>
-  </si>
-  <si>
-    <t>[np.float64(920.1119163629334), np.float64(-162.21337070391326)]</t>
-  </si>
-  <si>
-    <t>[np.float64(659.2004330495812), np.float64(-76.68154753940871)]</t>
-  </si>
-  <si>
-    <t>[np.float64(978.5160432236306), np.float64(159.22362592246714)]</t>
-  </si>
-  <si>
-    <t>[np.float64(935.1836941929992), np.float64(-62.654833087394536)]</t>
-  </si>
-  <si>
-    <t>[np.float64(3.5578768930454308), np.float64(-338.13901195375365)]</t>
-  </si>
-  <si>
-    <t>[np.float64(25.683952312629653), np.float64(208.81668410104237)]</t>
-  </si>
-  <si>
-    <t>[np.float64(444.74330970812935), np.float64(-160.4172178559882)]</t>
-  </si>
-  <si>
-    <t>[np.float64(212.10611573758587), np.float64(-588.6707441487191)]</t>
-  </si>
-  <si>
-    <t>[np.float64(971.1804850640756), np.float64(-101.67619469719978)]</t>
-  </si>
-  <si>
-    <t>[np.float64(121.60248374149995), np.float64(-405.84322270226977)]</t>
-  </si>
-  <si>
-    <t>[np.float64(487.4722799794897), np.float64(-328.0809300354005)]</t>
-  </si>
-  <si>
-    <t>[np.float64(286.1556388939124), np.float64(468.62107569172304)]</t>
-  </si>
-  <si>
-    <t>[np.float64(830.2927905116732), np.float64(-513.2900298208907)]</t>
-  </si>
-  <si>
-    <t>[np.float64(130.20773093969206), np.float64(-132.85740746103744)]</t>
-  </si>
-  <si>
-    <t>[np.float64(313.91495988528675), np.float64(-447.6237072719834)]</t>
-  </si>
-  <si>
-    <t>[np.float64(931.4340249308749), np.float64(-164.11093192542893)]</t>
-  </si>
-  <si>
-    <t>[np.float64(541.5253473293664), np.float64(-329.92563912817377)]</t>
-  </si>
-  <si>
-    <t>[np.float64(556.8817089318667), np.float64(124.19482055950823)]</t>
-  </si>
-  <si>
-    <t>[np.float64(502.199339578398), np.float64(-248.2820673113025)]</t>
-  </si>
-  <si>
-    <t>[np.float64(675.6146009480836), np.float64(129.6211927025821)]</t>
-  </si>
-  <si>
-    <t>[np.float64(27.408986887103914), np.float64(34.02446382265339)]</t>
-  </si>
-  <si>
-    <t>[np.float64(320.75288544113255), np.float64(434.32929882646295)]</t>
-  </si>
-  <si>
-    <t>[np.float64(146.63511100154537), np.float64(210.13590397508142)]</t>
-  </si>
-  <si>
-    <t>[np.float64(344.6704273918486), np.float64(-296.56744815990004)]</t>
-  </si>
-  <si>
-    <t>[np.float64(672.6831804705797), np.float64(506.84812915613475)]</t>
-  </si>
-  <si>
-    <t>[np.float64(680.5343500651236), np.float64(303.58899201883025)]</t>
-  </si>
-  <si>
-    <t>[np.float64(293.61293503540173), np.float64(-117.5427548984797)]</t>
-  </si>
-  <si>
-    <t>[np.float64(918.5966931690328), np.float64(-262.29245324156506)]</t>
-  </si>
-  <si>
-    <t>[np.float64(708.8262644623363), np.float64(-596.8011092340336)]</t>
-  </si>
-  <si>
-    <t>[np.float64(398.580680759565), np.float64(64.17780362450185)]</t>
-  </si>
-  <si>
-    <t>[np.float64(234.0901093657155), np.float64(217.58818220368903)]</t>
-  </si>
-  <si>
-    <t>[np.float64(389.5673372660788), np.float64(464.4183183606599)]</t>
-  </si>
-  <si>
-    <t>[np.float64(940.0758979955673), np.float64(-236.34085209322262)]</t>
-  </si>
-  <si>
-    <t>[np.float64(156.17498691060362), np.float64(-398.3877803663114)]</t>
-  </si>
-  <si>
-    <t>[np.float64(291.5145752064392), np.float64(98.24720959607862)]</t>
-  </si>
-  <si>
-    <t>[np.float64(496.3561696124577), np.float64(-425.3131430768718)]</t>
-  </si>
-  <si>
-    <t>[np.float64(946.089486564237), np.float64(525.8919874580827)]</t>
-  </si>
-  <si>
-    <t>[np.float64(17.64875672308186), np.float64(-428.7197059448316)]</t>
-  </si>
-  <si>
-    <t>[np.float64(135.71850122654982), np.float64(-138.91043726764377)]</t>
-  </si>
-  <si>
-    <t>[np.float64(663.3654720713595), np.float64(-465.00688145201843)]</t>
-  </si>
-  <si>
-    <t>[np.float64(297.09029605843904), np.float64(-427.39277946723973)]</t>
-  </si>
-  <si>
-    <t>[np.float64(159.37062230939625), np.float64(384.236944568739)]</t>
-  </si>
-  <si>
-    <t>[np.float64(206.34696827818456), np.float64(86.41906458934)]</t>
-  </si>
-  <si>
-    <t>[np.float64(676.2558238242398), np.float64(465.44903347378613)]</t>
-  </si>
-  <si>
-    <t>[np.float64(149.05482068720676), np.float64(-370.59530777816235)]</t>
-  </si>
-  <si>
-    <t>[np.float64(887.1089093501723), np.float64(64.6941904382353)]</t>
-  </si>
-  <si>
-    <t>[np.float64(146.6382669187819), np.float64(-316.7496369651595)]</t>
-  </si>
-  <si>
-    <t>[np.float64(485.73570816985176), np.float64(-206.44218629498374)]</t>
-  </si>
-  <si>
-    <t>[np.float64(879.2703244525541), np.float64(-163.21213434297192)]</t>
-  </si>
-  <si>
-    <t>[np.float64(539.3804971414315), np.float64(-379.43856164267436)]</t>
-  </si>
-  <si>
-    <t>[np.float64(75.2726154787634), np.float64(-295.5428382318029)]</t>
-  </si>
-  <si>
-    <t>[np.float64(825.4007585333608), np.float64(172.2657440926996)]</t>
-  </si>
-  <si>
-    <t>[np.float64(170.39437402117485), np.float64(205.09747235153782)]</t>
-  </si>
-  <si>
-    <t>[np.float64(607.8368954550942), np.float64(-135.4091267309763)]</t>
-  </si>
-  <si>
-    <t>[np.float64(895.7176120025049), np.float64(260.22493394808384)]</t>
-  </si>
-  <si>
-    <t>[np.float64(870.1445457370778), np.float64(77.45623681172151)]</t>
-  </si>
-  <si>
-    <t>[np.float64(72.73259315828207), np.float64(183.03586873340396)]</t>
-  </si>
-  <si>
-    <t>[np.float64(6.563103184586305), np.float64(-357.9763758187356)]</t>
-  </si>
-  <si>
-    <t>[np.float64(901.7657250748616), np.float64(-321.9036606191672)]</t>
-  </si>
-  <si>
-    <t>[np.float64(535.9999765309487), np.float64(-218.28900012434627)]</t>
-  </si>
-  <si>
-    <t>[np.float64(544.5463703034476), np.float64(-568.9872234008295)]</t>
-  </si>
-  <si>
-    <t>[np.float64(566.624897317688), np.float64(564.6984523657218)]</t>
-  </si>
-  <si>
-    <t>[np.float64(316.04282625575763), np.float64(473.1161754554496)]</t>
-  </si>
-  <si>
-    <t>[np.float64(628.6852480763226), np.float64(-465.42636296359683)]</t>
-  </si>
-  <si>
-    <t>[np.float64(762.1965575494556), np.float64(-495.07681797159626)]</t>
-  </si>
-  <si>
-    <t>[np.float64(956.4602909339873), np.float64(233.27994665796973)]</t>
-  </si>
-  <si>
-    <t>[np.float64(297.4419237028979), np.float64(190.37580055529554)]</t>
-  </si>
-  <si>
-    <t>[np.float64(873.8636157534929), np.float64(-498.7486886005794)]</t>
-  </si>
-  <si>
-    <t>[np.float64(289.57264003166136), np.float64(259.8417359948364)]</t>
-  </si>
-  <si>
-    <t>[np.float64(443.31560552955983), np.float64(-567.7792402639055)]</t>
-  </si>
-  <si>
-    <t>[np.float64(489.3352486842234), np.float64(-187.04264669121903)]</t>
-  </si>
-  <si>
-    <t>[np.float64(507.30311793065664), np.float64(491.647222059418)]</t>
-  </si>
-  <si>
-    <t>[np.float64(543.2027739693038), np.float64(429.00896552217)]</t>
-  </si>
-  <si>
-    <t>[np.float64(896.7206763844321), np.float64(456.95800207618095)]</t>
-  </si>
-  <si>
-    <t>[np.float64(115.56128885591666), np.float64(328.0910641959465)]</t>
-  </si>
-  <si>
-    <t>[np.float64(852.9484173974178), np.float64(-487.9889753219011)]</t>
-  </si>
-  <si>
-    <t>[np.float64(87.2650472633959), np.float64(63.13216633869092)]</t>
-  </si>
-  <si>
-    <t>[np.float64(351.36941315072033), np.float64(237.28219192938286)]</t>
-  </si>
-  <si>
-    <t>[np.float64(334.4291867798469), np.float64(508.2302214691051)]</t>
-  </si>
-  <si>
-    <t>[np.float64(43.99708108179079), np.float64(-410.76625587258013)]</t>
-  </si>
-  <si>
-    <t>[np.float64(541.5057025750864), np.float64(5.61517521082294)]</t>
-  </si>
-  <si>
-    <t>[np.float64(133.5233160878495), np.float64(-124.60348854794694)]</t>
-  </si>
-  <si>
-    <t>[np.float64(258.5170128752262), np.float64(125.9413292352441)]</t>
-  </si>
-  <si>
-    <t>[np.float64(167.75118074905336), np.float64(-555.924896600992)]</t>
-  </si>
-  <si>
-    <t>[np.float64(225.76684186459516), np.float64(-329.4588224828042)]</t>
-  </si>
-  <si>
-    <t>[np.float64(389.84201658080417), np.float64(-298.8918329226653)]</t>
-  </si>
-  <si>
-    <t>[np.float64(735.2160477038038), np.float64(425.6859580863081)]</t>
-  </si>
-  <si>
-    <t>[np.float64(167.78022869830212), np.float64(-126.45966774988091)]</t>
-  </si>
-  <si>
-    <t>[np.float64(468.285635808294), np.float64(432.994877155302)]</t>
-  </si>
-  <si>
-    <t>[np.float64(410.77041533486045), np.float64(430.23910433404967)]</t>
-  </si>
-  <si>
-    <t>[np.float64(374.19735439236234), np.float64(-401.2636282838971)]</t>
-  </si>
-  <si>
-    <t>[np.float64(669.6087906975233), np.float64(138.86374233664878)]</t>
-  </si>
-  <si>
-    <t>[np.float64(47.206733103894784), np.float64(433.8479704114777)]</t>
-  </si>
-  <si>
-    <t>[np.float64(662.9103645611108), np.float64(-576.0783559952665)]</t>
-  </si>
-  <si>
-    <t>[np.float64(29.692852604423337), np.float64(44.30191255456316)]</t>
-  </si>
-  <si>
-    <t>[np.float64(243.95183796738795), np.float64(-318.09825644436893)]</t>
-  </si>
-  <si>
-    <t>[np.float64(204.18938544860853), np.float64(353.5837646686773)]</t>
-  </si>
-  <si>
-    <t>[np.float64(910.7967624339074), np.float64(-318.0549584037655)]</t>
-  </si>
-  <si>
-    <t>[np.float64(640.6620931505516), np.float64(-507.46233595542265)]</t>
-  </si>
-  <si>
-    <t>[np.float64(47.55849666091583), np.float64(512.7521069546376)]</t>
-  </si>
-  <si>
-    <t>[np.float64(756.1254416420646), np.float64(48.863696045934034)]</t>
-  </si>
-  <si>
-    <t>[np.float64(373.47913677714286), np.float64(238.9509420821206)]</t>
-  </si>
-  <si>
-    <t>[np.float64(224.52014610230998), np.float64(286.32142749838636)]</t>
-  </si>
-  <si>
-    <t>[np.float64(522.0015453855145), np.float64(96.02011796048168)]</t>
-  </si>
-  <si>
-    <t>[np.float64(993.6641289215303), np.float64(543.5913524788991)]</t>
-  </si>
-  <si>
-    <t>[np.float64(973.5433393670143), np.float64(386.9133604575047)]</t>
-  </si>
-  <si>
-    <t>[np.float64(335.65196742738965), np.float64(508.54814034600713)]</t>
-  </si>
-  <si>
-    <t>[np.float64(998.852244940348), np.float64(264.20838449951566)]</t>
-  </si>
-  <si>
-    <t>[np.float64(375.24975659517844), np.float64(-410.69752448159073)]</t>
-  </si>
-  <si>
-    <t>[np.float64(82.14095932005183), np.float64(543.3730098614776)]</t>
-  </si>
-  <si>
-    <t>[np.float64(398.6749874187759), np.float64(-280.91393971902784)]</t>
-  </si>
-  <si>
-    <t>[np.float64(898.5902355746955), np.float64(-550.1297699164634)]</t>
-  </si>
-  <si>
-    <t>[np.float64(244.92738704608607), np.float64(182.73603686286754)]</t>
-  </si>
-  <si>
-    <t>[np.float64(462.6682585284234), np.float64(211.4646142304531)]</t>
-  </si>
-  <si>
-    <t>[np.float64(535.7326974155536), np.float64(127.87273702259426)]</t>
-  </si>
-  <si>
-    <t>[np.float64(732.1987555631569), np.float64(133.2628051106252)]</t>
-  </si>
-  <si>
-    <t>[np.float64(887.5006386398435), np.float64(-242.87179344577413)]</t>
-  </si>
-  <si>
-    <t>[np.float64(292.3974008938438), np.float64(-64.97889278343564)]</t>
-  </si>
-  <si>
-    <t>[np.float64(615.6774592179736), np.float64(-147.49514105329263)]</t>
-  </si>
-  <si>
-    <t>[np.float64(986.211582268212), np.float64(-343.55250744785116)]</t>
-  </si>
-  <si>
-    <t>[np.float64(222.64674819260665), np.float64(-174.99815582683067)]</t>
-  </si>
-  <si>
-    <t>[np.float64(109.36796129938564), np.float64(370.04378229722147)]</t>
-  </si>
-  <si>
-    <t>[np.float64(952.4925647903021), np.float64(527.2385221582447)]</t>
-  </si>
-  <si>
-    <t>[np.float64(418.01129032439246), np.float64(445.35516798732147)]</t>
-  </si>
-  <si>
-    <t>[np.float64(691.8792829045337), np.float64(451.8469363348943)]</t>
-  </si>
-  <si>
-    <t>[np.float64(452.8561068495782), np.float64(-457.3730830676415)]</t>
-  </si>
-  <si>
-    <t>[np.float64(98.36967090784721), np.float64(-120.58805934341962)]</t>
-  </si>
-  <si>
-    <t>[np.float64(656.5548204030027), np.float64(-359.2395979592843)]</t>
-  </si>
-  <si>
-    <t>[np.float64(154.48912483701616), np.float64(-91.75855780863691)]</t>
-  </si>
-  <si>
-    <t>[np.float64(897.9680875423416), np.float64(184.25528512848223)]</t>
-  </si>
-  <si>
-    <t>[np.float64(405.26191554487735), np.float64(-264.2252871440909)]</t>
-  </si>
-  <si>
-    <t>[np.float64(510.7098601398756), np.float64(-433.2570363525965)]</t>
-  </si>
-  <si>
-    <t>[np.float64(231.0590013900844), np.float64(499.77252138305266)]</t>
-  </si>
-  <si>
-    <t>[np.float64(840.2766371868946), np.float64(-284.25463350323173)]</t>
-  </si>
-  <si>
-    <t>[np.float64(990.6192860652452), np.float64(-197.54830759905343)]</t>
-  </si>
-  <si>
-    <t>[np.float64(627.593378253012), np.float64(-591.0516020040126)]</t>
-  </si>
-  <si>
-    <t>[np.float64(345.7456303242875), np.float64(-586.9189985829834)]</t>
-  </si>
-  <si>
-    <t>[np.float64(117.07943693005119), np.float64(383.44017167873585)]</t>
-  </si>
-  <si>
-    <t>[np.float64(108.1798132767029), np.float64(331.240162033754)]</t>
-  </si>
-  <si>
-    <t>[np.float64(453.41866658617425), np.float64(396.37693596263523)]</t>
-  </si>
-  <si>
-    <t>[np.float64(434.18822009245196), np.float64(421.7761684886732)]</t>
-  </si>
-  <si>
-    <t>[np.float64(891.8645195279877), np.float64(-223.88696374251754)]</t>
-  </si>
-  <si>
-    <t>[np.float64(523.0703294896617), np.float64(249.6226918085457)]</t>
-  </si>
-  <si>
-    <t>[np.float64(18.779454529016306), np.float64(482.2172993299416)]</t>
-  </si>
-  <si>
-    <t>[np.float64(590.0809946521535), np.float64(-278.21115411367776)]</t>
-  </si>
-  <si>
-    <t>[np.float64(312.9695425946386), np.float64(-275.2295631230238)]</t>
-  </si>
-  <si>
-    <t>[np.float64(920.4518039990319), np.float64(278.5804771195677)]</t>
-  </si>
-  <si>
-    <t>[np.float64(448.21727071773654), np.float64(-129.89736480918322)]</t>
-  </si>
-  <si>
-    <t>[np.float64(469.10239993113646), np.float64(-458.3154412060503)]</t>
-  </si>
-  <si>
-    <t>[np.float64(105.87494793003071), np.float64(574.3685575365241)]</t>
-  </si>
-  <si>
-    <t>[np.float64(710.4499946547743), np.float64(-590.2886807471539)]</t>
-  </si>
-  <si>
-    <t>[np.float64(568.6859329887668), np.float64(408.09039837153523)]</t>
-  </si>
-  <si>
-    <t>[np.float64(844.2248943187573), np.float64(337.1119113950807)]</t>
-  </si>
-  <si>
-    <t>[np.float64(749.8012450008025), np.float64(597.1711403599313)]</t>
-  </si>
-  <si>
-    <t>[np.float64(37.637686008414775), np.float64(240.90375786489506)]</t>
-  </si>
-  <si>
-    <t>[np.float64(458.0377727834103), np.float64(-539.5701191068861)]</t>
-  </si>
-  <si>
-    <t>[np.float64(405.61907473738114), np.float64(414.4482021756718)]</t>
-  </si>
-  <si>
-    <t>[np.float64(868.1773708012248), np.float64(-124.04704952245612)]</t>
-  </si>
-  <si>
-    <t>[np.float64(54.85584960690149), np.float64(-385.39226279934974)]</t>
-  </si>
-  <si>
-    <t>[np.float64(520.2903266541985), np.float64(-491.5044787492616)]</t>
-  </si>
-  <si>
-    <t>[np.float64(675.1098316522667), np.float64(-150.83800248023948)]</t>
-  </si>
-  <si>
-    <t>[np.float64(549.9127039312853), np.float64(416.33734348802)]</t>
-  </si>
-  <si>
-    <t>[np.float64(53.57856010795714), np.float64(-291.14969922912763)]</t>
-  </si>
-  <si>
-    <t>[np.float64(752.8654021121234), np.float64(392.5607813858534)]</t>
-  </si>
-  <si>
-    <t>[np.float64(557.867139818635), np.float64(135.0556043579802)]</t>
-  </si>
-  <si>
-    <t>[np.float64(941.6816299262503), np.float64(-222.88326116442994)]</t>
-  </si>
-  <si>
-    <t>[np.float64(118.20500305590187), np.float64(-151.36705571775553)]</t>
-  </si>
-  <si>
-    <t>[np.float64(165.59938308765766), np.float64(299.32944932357213)]</t>
-  </si>
-  <si>
-    <t>[np.float64(326.51688995786765), np.float64(-213.6498255733738)]</t>
-  </si>
-  <si>
-    <t>[np.float64(863.5064170808661), np.float64(318.2569989292007)]</t>
-  </si>
-  <si>
-    <t>[np.float64(824.1241930521368), np.float64(-218.43485868506815)]</t>
-  </si>
-  <si>
-    <t>[np.float64(511.0615963085229), np.float64(-110.7797292994108)]</t>
-  </si>
-  <si>
-    <t>[np.float64(449.22576656836435), np.float64(431.5602099158996)]</t>
-  </si>
-  <si>
-    <t>[np.float64(282.19655402513433), np.float64(576.0167928700057)]</t>
-  </si>
-  <si>
-    <t>[np.float64(824.0183707256693), np.float64(-214.39938884027845)]</t>
-  </si>
-  <si>
-    <t>[np.float64(129.27712981694395), np.float64(-375.1498373431449)]</t>
-  </si>
-  <si>
-    <t>[np.float64(258.1398941897162), np.float64(187.04834746264612)]</t>
-  </si>
-  <si>
-    <t>[np.float64(189.70605050425237), np.float64(461.25222131357896)]</t>
-  </si>
-  <si>
-    <t>[np.float64(864.2844442033263), np.float64(-479.35668935479214)]</t>
-  </si>
-  <si>
-    <t>[np.float64(974.6865514390879), np.float64(590.9956597891064)]</t>
-  </si>
-  <si>
-    <t>[np.float64(900.3860392754913), np.float64(-514.0414504235923)]</t>
-  </si>
-  <si>
-    <t>[np.float64(583.0293605240014), np.float64(-171.21409681536534)]</t>
-  </si>
-  <si>
-    <t>[np.float64(307.3943391635422), np.float64(-116.15332299761621)]</t>
-  </si>
-  <si>
-    <t>[np.float64(282.65369872742184), np.float64(342.4585670143123)]</t>
-  </si>
-  <si>
-    <t>[np.float64(533.0848395595481), np.float64(556.0841175819473)]</t>
-  </si>
-  <si>
-    <t>[np.float64(361.8692255541878), np.float64(516.1418892055051)]</t>
-  </si>
-  <si>
-    <t>[np.float64(249.52763415893742), np.float64(-321.74675906804435)]</t>
-  </si>
-  <si>
-    <t>[np.float64(682.2371115759665), np.float64(-152.60640895538427)]</t>
-  </si>
-  <si>
-    <t>[np.float64(322.524297677494), np.float64(228.62917590477764)]</t>
-  </si>
-  <si>
-    <t>[np.float64(315.9605763727935), np.float64(-288.17682876502266)]</t>
-  </si>
-  <si>
-    <t>[np.float64(412.38398561114866), np.float64(16.33545731208153)]</t>
-  </si>
-  <si>
-    <t>[np.float64(752.6698879816245), np.float64(-391.9529003531321)]</t>
-  </si>
-  <si>
-    <t>[np.float64(450.1732091858832), np.float64(-335.0727031015777)]</t>
-  </si>
-  <si>
-    <t>[np.float64(552.8865855905034), np.float64(-350.5267204370987)]</t>
-  </si>
-  <si>
-    <t>[np.float64(679.3121243409158), np.float64(11.998366421240917)]</t>
-  </si>
-  <si>
-    <t>[np.float64(427.81993984840597), np.float64(544.4914663143063)]</t>
-  </si>
-  <si>
-    <t>[np.float64(616.640832293276), np.float64(-114.20437186391592)]</t>
-  </si>
-  <si>
-    <t>[np.float64(963.8546546537748), np.float64(-454.818104795028)]</t>
-  </si>
-  <si>
-    <t>[np.float64(904.4253388379298), np.float64(-302.2208813007427)]</t>
-  </si>
-  <si>
-    <t>[np.float64(261.7058299930596), np.float64(-478.945033822048)]</t>
-  </si>
-  <si>
-    <t>[np.float64(638.9771378240459), np.float64(85.7895705200491)]</t>
-  </si>
-  <si>
-    <t>[np.float64(393.50682702522465), np.float64(152.53953162334426)]</t>
-  </si>
-  <si>
-    <t>[np.float64(98.34625717059609), np.float64(392.50893445071665)]</t>
-  </si>
-  <si>
-    <t>[np.float64(646.2462636814112), np.float64(-380.2499021476261)]</t>
-  </si>
-  <si>
-    <t>[np.float64(437.91158849233716), np.float64(79.47161404002804)]</t>
-  </si>
-  <si>
-    <t>[np.float64(865.6177691068174), np.float64(582.064024677825)]</t>
-  </si>
-  <si>
-    <t>[np.float64(270.0409770517803), np.float64(-571.1735407420455)]</t>
-  </si>
-  <si>
-    <t>[np.float64(314.6051267903803), np.float64(-158.69959443953223)]</t>
-  </si>
-  <si>
-    <t>[np.float64(758.3423644171537), np.float64(-554.8819590058538)]</t>
-  </si>
-  <si>
-    <t>[np.float64(693.2115736652739), np.float64(-186.7410637674517)]</t>
-  </si>
-  <si>
-    <t>[np.float64(632.2010928969972), np.float64(-77.9451069573953)]</t>
-  </si>
-  <si>
-    <t>[np.float64(738.741492118725), np.float64(-239.2515005605053)]</t>
-  </si>
-  <si>
-    <t>[np.float64(495.32389850467075), np.float64(-250.43653668406677)]</t>
-  </si>
-  <si>
-    <t>[np.float64(668.7868623581124), np.float64(459.167081048138)]</t>
-  </si>
-  <si>
-    <t>[np.float64(402.2150453724952), np.float64(420.24198297141356)]</t>
-  </si>
-  <si>
-    <t>[np.float64(541.241523376205), np.float64(559.6997883423828)]</t>
-  </si>
-  <si>
-    <t>[np.float64(229.16358798705872), np.float64(-550.8247775759146)]</t>
-  </si>
-  <si>
-    <t>[np.float64(97.62580748435856), np.float64(74.47001253729195)]</t>
-  </si>
-  <si>
-    <t>[np.float64(784.2173212703527), np.float64(96.10318728986203)]</t>
-  </si>
-  <si>
-    <t>[np.float64(322.24024930872184), np.float64(-447.2759520464863)]</t>
-  </si>
-  <si>
-    <t>[np.float64(928.3236174002508), np.float64(547.512786925799)]</t>
-  </si>
-  <si>
-    <t>[np.float64(204.7259843904784), np.float64(301.44749370870045)]</t>
-  </si>
-  <si>
-    <t>[np.float64(301.71653455578274), np.float64(-246.6260614944112)]</t>
-  </si>
-  <si>
-    <t>[np.float64(833.4181709207614), np.float64(-455.400095601122)]</t>
-  </si>
-  <si>
-    <t>[np.float64(348.80378251639763), np.float64(262.32141329032197)]</t>
-  </si>
-  <si>
-    <t>[np.float64(461.4172831957115), np.float64(-314.8387423919384)]</t>
-  </si>
-  <si>
-    <t>[np.float64(900.3135863268747), np.float64(414.5762638324152)]</t>
-  </si>
-  <si>
-    <t>[np.float64(203.5127150757723), np.float64(-540.9224576073564)]</t>
-  </si>
-  <si>
-    <t>[np.float64(684.6580962792842), np.float64(-435.15818689185744)]</t>
-  </si>
-  <si>
-    <t>[np.float64(754.275662709616), np.float64(411.1940485501866)]</t>
-  </si>
-  <si>
-    <t>[np.float64(399.2269546969737), np.float64(-460.84306822167457)]</t>
-  </si>
-  <si>
-    <t>[np.float64(46.00955239334237), np.float64(-395.43775319198346)]</t>
-  </si>
-  <si>
-    <t>[np.float64(753.2639564842534), np.float64(-127.41917383469405)]</t>
-  </si>
-  <si>
-    <t>[np.float64(160.26551317568493), np.float64(261.24144628828446)]</t>
-  </si>
-  <si>
-    <t>[np.float64(98.83979669918497), np.float64(-488.21182418244246)]</t>
-  </si>
-  <si>
-    <t>[np.float64(982.0078630333392), np.float64(287.820394208274)]</t>
-  </si>
-  <si>
-    <t>[np.float64(697.989956500689), np.float64(226.1506528158094)]</t>
-  </si>
-  <si>
-    <t>[np.float64(997.2723997713023), np.float64(109.41088039478348)]</t>
-  </si>
-  <si>
-    <t>[np.float64(103.15995589441773), np.float64(294.48405379936776)]</t>
-  </si>
-  <si>
-    <t>[np.float64(148.27906133480707), np.float64(484.74414698058035)]</t>
-  </si>
-  <si>
-    <t>[np.float64(360.3386075027759), np.float64(-476.390810609826)]</t>
-  </si>
-  <si>
-    <t>[np.float64(800.5061991992204), np.float64(-248.01595712678142)]</t>
-  </si>
-  <si>
-    <t>[np.float64(214.88056960014023), np.float64(403.0836835785209)]</t>
-  </si>
-  <si>
-    <t>[np.float64(661.3050777293762), np.float64(-500.5800427218634)]</t>
-  </si>
-  <si>
-    <t>[np.float64(687.4415171224576), np.float64(-427.5154828799206)]</t>
-  </si>
-  <si>
-    <t>[np.float64(707.035205597997), np.float64(-147.58522922331633)]</t>
-  </si>
-  <si>
-    <t>[np.float64(968.009986326557), np.float64(-371.3138513109384)]</t>
-  </si>
-  <si>
-    <t>[np.float64(296.5871157738339), np.float64(485.60531664518135)]</t>
-  </si>
-  <si>
-    <t>[np.float64(640.4530010260264), np.float64(284.0802586869188)]</t>
-  </si>
-  <si>
-    <t>[np.float64(35.45724185995813), np.float64(165.65562583089684)]</t>
-  </si>
-  <si>
-    <t>[np.float64(838.8026972714238), np.float64(189.42596978916458)]</t>
-  </si>
-  <si>
-    <t>[np.float64(651.3563749065212), np.float64(-165.35309590971832)]</t>
-  </si>
-  <si>
-    <t>[np.float64(209.95210083323246), np.float64(443.49438468814606)]</t>
-  </si>
-  <si>
-    <t>[np.float64(196.65639200003017), np.float64(-496.35168857625644)]</t>
-  </si>
-  <si>
-    <t>[np.float64(336.8653929713422), np.float64(-101.64014690268988)]</t>
-  </si>
-  <si>
-    <t>[np.float64(387.57088406666475), np.float64(494.7406934106343)]</t>
-  </si>
-  <si>
-    <t>[np.float64(51.58677999061312), np.float64(46.82119764607785)]</t>
-  </si>
-  <si>
-    <t>[np.float64(220.20509719731828), np.float64(337.6280622852172)]</t>
-  </si>
-  <si>
-    <t>[np.float64(843.6894930044224), np.float64(-294.1682165965919)]</t>
-  </si>
-  <si>
-    <t>[np.float64(497.8915387899512), np.float64(-213.0374658383929)]</t>
-  </si>
-  <si>
-    <t>[np.float64(828.364322080178), np.float64(-442.4470789678334)]</t>
-  </si>
-  <si>
-    <t>[np.float64(158.90725507806192), np.float64(-291.8963059724757)]</t>
-  </si>
-  <si>
-    <t>[np.float64(161.4709181564945), np.float64(491.5539944279403)]</t>
-  </si>
-  <si>
-    <t>[np.float64(618.3210032759399), np.float64(-233.76206573479277)]</t>
-  </si>
-  <si>
-    <t>[np.float64(422.9984316620837), np.float64(-253.96165581175427)]</t>
-  </si>
-  <si>
-    <t>[np.float64(696.0223215808024), np.float64(252.36125010968374)]</t>
-  </si>
-  <si>
-    <t>[np.float64(236.49556553671815), np.float64(-332.1351498405545)]</t>
-  </si>
-  <si>
-    <t>[np.float64(30.87585587333086), np.float64(-172.79855668318862)]</t>
-  </si>
-  <si>
-    <t>[np.float64(366.40227103550984), np.float64(377.6983926528595)]</t>
-  </si>
-  <si>
-    <t>[np.float64(678.1427833901558), np.float64(-598.8709392602229)]</t>
-  </si>
-  <si>
-    <t>[np.float64(144.97649350708642), np.float64(429.5176036877722)]</t>
-  </si>
-  <si>
-    <t>[np.float64(157.24805225040828), np.float64(459.671643023604)]</t>
-  </si>
-  <si>
-    <t>[np.float64(317.15271852460916), np.float64(224.30311195785976)]</t>
-  </si>
-  <si>
-    <t>[np.float64(618.9438506396731), np.float64(-456.35101769987523)]</t>
-  </si>
-  <si>
-    <t>[np.float64(491.58457746103056), np.float64(592.9292135842038)]</t>
-  </si>
-  <si>
-    <t>[np.float64(792.3065770499304), np.float64(280.35443707633704)]</t>
-  </si>
-  <si>
-    <t>[np.float64(127.80696913951861), np.float64(128.31285662011396)]</t>
-  </si>
-  <si>
-    <t>[np.float64(774.0761792429532), np.float64(-269.1568037140147)]</t>
-  </si>
-  <si>
-    <t>[np.float64(771.6131999184978), np.float64(539.867855562981)]</t>
-  </si>
-  <si>
-    <t>[np.float64(655.7169979003687), np.float64(-564.2820029616496)]</t>
-  </si>
-  <si>
-    <t>[np.float64(580.8567639745957), np.float64(268.8498114201436)]</t>
-  </si>
-  <si>
-    <t>[np.float64(1.3574884076981153), np.float64(-393.2977536376063)]</t>
-  </si>
-  <si>
-    <t>[np.float64(766.0871705266571), np.float64(-95.43991174993687)]</t>
-  </si>
-  <si>
-    <t>[np.float64(611.4109241265002), np.float64(-330.62334322129254)]</t>
-  </si>
-  <si>
-    <t>[np.float64(49.77236571889099), np.float64(-442.18309929552424)]</t>
-  </si>
-  <si>
-    <t>[np.float64(359.91570941179305), np.float64(-363.7523584959384)]</t>
-  </si>
-  <si>
-    <t>[np.float64(988.4001946014605), np.float64(-123.3382762016526)]</t>
-  </si>
-  <si>
-    <t>[np.float64(908.1584373552921), np.float64(-300.35134621510116)]</t>
-  </si>
-  <si>
-    <t>[np.float64(933.1593233211099), np.float64(-305.63409587716103)]</t>
-  </si>
-  <si>
-    <t>[np.float64(914.6847573258913), np.float64(105.56545797179331)]</t>
-  </si>
-  <si>
-    <t>[np.float64(605.8885060725502), np.float64(509.52391260037894)]</t>
-  </si>
-  <si>
-    <t>[np.float64(571.0050928727863), np.float64(-470.7245057352728)]</t>
-  </si>
-  <si>
-    <t>[np.float64(240.2464070036322), np.float64(285.3546370332979)]</t>
-  </si>
-  <si>
-    <t>[np.float64(984.4265215249283), np.float64(576.7871873975616)]</t>
-  </si>
-  <si>
-    <t>[np.float64(630.8978884286879), np.float64(0.1388496755592996)]</t>
-  </si>
-  <si>
-    <t>[np.float64(682.8631737704403), np.float64(60.731765127901326)]</t>
-  </si>
-  <si>
-    <t>[np.float64(915.7547514687359), np.float64(-572.4152768099605)]</t>
-  </si>
-  <si>
-    <t>[np.float64(482.1277558588737), np.float64(-414.02057786653353)]</t>
-  </si>
-  <si>
-    <t>[np.float64(272.3134895359035), np.float64(390.9236766018836)]</t>
-  </si>
-  <si>
-    <t>[np.float64(425.8856637470584), np.float64(210.7064281094847)]</t>
-  </si>
-  <si>
-    <t>[np.float64(331.4287814566932), np.float64(40.19687471844691)]</t>
-  </si>
-  <si>
-    <t>[np.float64(472.22703928682506), np.float64(225.23342209001157)]</t>
-  </si>
-  <si>
-    <t>[np.float64(345.4859690106278), np.float64(114.84939308830212)]</t>
-  </si>
-  <si>
-    <t>[np.float64(755.0805254859679), np.float64(-102.64515673150822)]</t>
-  </si>
-  <si>
-    <t>[np.float64(476.7670844485117), np.float64(292.076209692062)]</t>
-  </si>
-  <si>
-    <t>[np.float64(367.8618485422014), np.float64(-562.1801797773967)]</t>
-  </si>
-  <si>
-    <t>[np.float64(596.2975445957585), np.float64(182.19384571831722)]</t>
-  </si>
-  <si>
-    <t>[np.float64(547.2658400899057), np.float64(-405.5875965213602)]</t>
-  </si>
-  <si>
-    <t>[np.float64(577.0410843932585), np.float64(308.09223884524374)]</t>
-  </si>
-  <si>
-    <t>[np.float64(673.4728787438331), np.float64(383.4828039622139)]</t>
-  </si>
-  <si>
-    <t>[np.float64(695.7735047796331), np.float64(-3.0974400206547443)]</t>
-  </si>
-  <si>
-    <t>[np.float64(213.68870898048021), np.float64(532.9041911578627)]</t>
-  </si>
-  <si>
-    <t>[np.float64(197.85759577192485), np.float64(296.00164419620785)]</t>
-  </si>
-  <si>
-    <t>[np.float64(695.4616852296374), np.float64(-110.20042223332615)]</t>
-  </si>
-  <si>
-    <t>[np.float64(491.3026631258343), np.float64(495.69756459756013)]</t>
-  </si>
-  <si>
-    <t>[np.float64(738.6434016801971), np.float64(-190.20876383368085)]</t>
-  </si>
-  <si>
-    <t>[np.float64(767.7169867058722), np.float64(-454.1782019504122)]</t>
-  </si>
-  <si>
-    <t>[np.float64(941.6867976778603), np.float64(-114.64044047306419)]</t>
-  </si>
-  <si>
-    <t>[np.float64(248.8718304615465), np.float64(436.80213228754405)]</t>
-  </si>
-  <si>
-    <t>[np.float64(758.6759595726713), np.float64(421.20073231409947)]</t>
-  </si>
-  <si>
-    <t>[np.float64(141.9297559496313), np.float64(366.76996913107007)]</t>
-  </si>
-  <si>
-    <t>[np.float64(151.19056457589076), np.float64(268.3359243641464)]</t>
-  </si>
-  <si>
-    <t>[np.float64(555.8318319504364), np.float64(298.26709001698157)]</t>
-  </si>
-  <si>
-    <t>[np.float64(408.42622545968277), np.float64(422.48045353910345)]</t>
-  </si>
-  <si>
-    <t>[np.float64(30.519643154443333), np.float64(-406.6189969372608)]</t>
-  </si>
-  <si>
-    <t>[np.float64(54.226164987034586), np.float64(480.22188960863446)]</t>
-  </si>
-  <si>
-    <t>[np.float64(882.1034811137428), np.float64(90.61032794517973)]</t>
-  </si>
-  <si>
-    <t>[np.float64(178.5940922347632), np.float64(-218.63319009961072)]</t>
-  </si>
-  <si>
-    <t>[np.float64(412.1143095763475), np.float64(-419.390566586997)]</t>
-  </si>
-  <si>
-    <t>[np.float64(47.25103135105746), np.float64(27.1639883479304)]</t>
-  </si>
-  <si>
-    <t>[np.float64(108.29648555817096), np.float64(-597.9021405423841)]</t>
-  </si>
-  <si>
-    <t>[np.float64(824.6238887614454), np.float64(-160.2487813703724)]</t>
-  </si>
-  <si>
-    <t>[np.float64(869.0657542786801), np.float64(232.23831156623623)]</t>
-  </si>
-  <si>
-    <t>[np.float64(661.9033913004681), np.float64(-328.37469558422293)]</t>
-  </si>
-  <si>
-    <t>[np.float64(568.0280311405578), np.float64(-126.985030553635)]</t>
-  </si>
-  <si>
-    <t>[np.float64(892.5987639780022), np.float64(-245.07302212313306)]</t>
-  </si>
-  <si>
-    <t>[np.float64(584.4102360437981), np.float64(-87.57983761868672)]</t>
-  </si>
-  <si>
-    <t>[np.float64(648.9204632976107), np.float64(-363.41773429356374)]</t>
-  </si>
-  <si>
-    <t>[np.float64(516.2684377252816), np.float64(-473.1292955689729)]</t>
-  </si>
-  <si>
-    <t>[np.float64(258.7573990472061), np.float64(-317.87500563301234)]</t>
-  </si>
-  <si>
-    <t>[np.float64(916.8032708434225), np.float64(-533.9067636442259)]</t>
-  </si>
-  <si>
-    <t>[np.float64(271.8766685050883), np.float64(-233.76470849227684)]</t>
-  </si>
-  <si>
-    <t>[np.float64(85.34157490679894), np.float64(288.87547808042825)]</t>
-  </si>
-  <si>
-    <t>[np.float64(440.7610512338216), np.float64(558.566371008854)]</t>
-  </si>
-  <si>
-    <t>[np.float64(261.3355244940172), np.float64(16.956574436567394)]</t>
-  </si>
-  <si>
-    <t>[np.float64(913.2979072861878), np.float64(-369.46135593516794)]</t>
-  </si>
-  <si>
-    <t>[np.float64(145.191305779941), np.float64(279.3168368954763)]</t>
-  </si>
-  <si>
-    <t>[np.float64(118.98158857871488), np.float64(-212.04630636017657)]</t>
-  </si>
-  <si>
-    <t>[np.float64(751.479345328952), np.float64(482.81222638952545)]</t>
-  </si>
-  <si>
-    <t>[np.float64(952.0932012703946), np.float64(90.40945543601515)]</t>
-  </si>
-  <si>
-    <t>[np.float64(527.6205491061451), np.float64(184.04822235080462)]</t>
-  </si>
-  <si>
-    <t>[np.float64(391.1399677539915), np.float64(-457.8288554771888)]</t>
-  </si>
-  <si>
-    <t>[np.float64(664.924371102959), np.float64(339.64739899173185)]</t>
-  </si>
-  <si>
-    <t>[np.float64(52.965750356518186), np.float64(463.7093832781634)]</t>
-  </si>
-  <si>
-    <t>[np.float64(403.8861256588475), np.float64(-524.09470883466)]</t>
-  </si>
-  <si>
-    <t>[np.float64(947.6077087439955), np.float64(196.9886061046609)]</t>
-  </si>
-  <si>
-    <t>[np.float64(414.5301125470422), np.float64(451.61373358277615)]</t>
-  </si>
-  <si>
-    <t>[np.float64(162.88280886791262), np.float64(-162.50888086883282)]</t>
-  </si>
-  <si>
-    <t>[np.float64(707.0438277839912), np.float64(203.127989967624)]</t>
-  </si>
-  <si>
-    <t>[np.float64(841.7821023696439), np.float64(-146.82012036825012)]</t>
-  </si>
-  <si>
-    <t>[np.float64(70.22031748192093), np.float64(58.90286898633951)]</t>
-  </si>
-  <si>
-    <t>[np.float64(799.4170460127841), np.float64(47.79668835720577)]</t>
-  </si>
-  <si>
-    <t>[np.float64(608.2148796634959), np.float64(107.3073597344835)]</t>
-  </si>
-  <si>
-    <t>[np.float64(693.4616817256381), np.float64(177.83564224985003)]</t>
-  </si>
-  <si>
-    <t>[np.float64(633.4376901401391), np.float64(398.12406613421103)]</t>
-  </si>
-  <si>
-    <t>[np.float64(182.84304126548446), np.float64(210.4493963397515)]</t>
-  </si>
-  <si>
-    <t>[np.float64(161.4797158968593), np.float64(91.48527625609825)]</t>
-  </si>
-  <si>
-    <t>[np.float64(199.95971479294784), np.float64(78.48036778746905)]</t>
-  </si>
-  <si>
-    <t>[np.float64(167.80960171738823), np.float64(346.5511409127812)]</t>
-  </si>
-  <si>
-    <t>[np.float64(990.1745755061116), np.float64(307.02567079842197)]</t>
-  </si>
-  <si>
-    <t>[np.float64(840.0214535713911), np.float64(-480.36544489426797)]</t>
-  </si>
-  <si>
-    <t>[np.float64(8.673365235482343), np.float64(88.33818085608459)]</t>
-  </si>
-  <si>
-    <t>[np.float64(861.3588129571563), np.float64(-355.38122366607263)]</t>
-  </si>
-  <si>
-    <t>[np.float64(940.5673702409281), np.float64(542.3026804262097)]</t>
-  </si>
-  <si>
-    <t>[np.float64(206.9097856829064), np.float64(-549.7169751681477)]</t>
-  </si>
-  <si>
-    <t>[np.float64(514.2600081504908), np.float64(-89.65086814513944)]</t>
-  </si>
-  <si>
-    <t>[np.float64(961.1569278014337), np.float64(0.634807493933522)]</t>
-  </si>
-  <si>
-    <t>[np.float64(495.11488553620984), np.float64(-383.84596012195436)]</t>
-  </si>
-  <si>
-    <t>[np.float64(637.2940652107269), np.float64(285.4977804524501)]</t>
-  </si>
-  <si>
-    <t>[np.float64(803.4019020026763), np.float64(434.82338589968526)]</t>
-  </si>
-  <si>
-    <t>[np.float64(8.526835080587048), np.float64(-129.52519564542723)]</t>
-  </si>
-  <si>
-    <t>[np.float64(348.71580093969146), np.float64(-369.7220293994657)]</t>
-  </si>
-  <si>
-    <t>[np.float64(487.1765277361395), np.float64(455.3515748805196)]</t>
-  </si>
-  <si>
-    <t>[np.float64(825.6028665575199), np.float64(-497.1770133946775)]</t>
-  </si>
-  <si>
-    <t>[np.float64(941.0251260104336), np.float64(-502.65091132496946)]</t>
-  </si>
-  <si>
-    <t>[np.float64(627.3796856604346), np.float64(-487.1300049510928)]</t>
-  </si>
-  <si>
-    <t>[np.float64(7.608261181741738), np.float64(-219.23439821766652)]</t>
-  </si>
-  <si>
-    <t>[np.float64(896.3570316887535), np.float64(105.13059077276398)]</t>
-  </si>
-  <si>
-    <t>[np.float64(293.34812335858675), np.float64(-275.5010528505245)]</t>
-  </si>
-  <si>
-    <t>[np.float64(417.89175957608325), np.float64(200.910540615581)]</t>
-  </si>
-  <si>
-    <t>[np.float64(575.7509927722118), np.float64(167.9862649836075)]</t>
-  </si>
-  <si>
-    <t>[np.float64(640.6018180050128), np.float64(-546.4112601291174)]</t>
-  </si>
-  <si>
-    <t>[np.float64(236.02690732823328), np.float64(127.4637808666439)]</t>
-  </si>
-  <si>
-    <t>[np.float64(959.8450045891017), np.float64(270.90878374134127)]</t>
-  </si>
-  <si>
-    <t>[np.float64(124.75057886775708), np.float64(-504.3721170952439)]</t>
+    <t>[np.float64(931.2519084802718), np.float64(-288.4440492734075)]</t>
+  </si>
+  <si>
+    <t>[np.float64(302.25052577237955), np.float64(523.8873751036115)]</t>
+  </si>
+  <si>
+    <t>[np.float64(864.9752141885864), np.float64(548.8857783688325)]</t>
+  </si>
+  <si>
+    <t>[np.float64(457.2540942068966), np.float64(249.13977306157403)]</t>
+  </si>
+  <si>
+    <t>[np.float64(245.2977211079147), np.float64(-181.14059042797146)]</t>
+  </si>
+  <si>
+    <t>[np.float64(633.8613350392184), np.float64(572.3131259313036)]</t>
+  </si>
+  <si>
+    <t>[np.float64(324.9561724143043), np.float64(-466.3195861426045)]</t>
+  </si>
+  <si>
+    <t>[np.float64(135.04330035279867), np.float64(-78.8343481032291)]</t>
+  </si>
+  <si>
+    <t>[np.float64(978.0079008432675), np.float64(-184.9694036306579)]</t>
+  </si>
+  <si>
+    <t>[np.float64(225.90090021121756), np.float64(-424.58265987450346)]</t>
+  </si>
+  <si>
+    <t>[np.float64(939.4964750454843), np.float64(-3.3455050626386083)]</t>
+  </si>
+  <si>
+    <t>[np.float64(516.218761530275), np.float64(-457.0139693261636)]</t>
+  </si>
+  <si>
+    <t>[np.float64(670.1378091500104), np.float64(360.04875840511784)]</t>
+  </si>
+  <si>
+    <t>[np.float64(889.0230783538842), np.float64(525.9963650818811)]</t>
+  </si>
+  <si>
+    <t>[np.float64(403.925083946541), np.float64(-502.7215036368997)]</t>
+  </si>
+  <si>
+    <t>[np.float64(380.5585637362673), np.float64(243.00897690916088)]</t>
+  </si>
+  <si>
+    <t>[np.float64(826.3858843470084), np.float64(-334.49415308435323)]</t>
+  </si>
+  <si>
+    <t>[np.float64(235.1610857573403), np.float64(350.7139883666272)]</t>
+  </si>
+  <si>
+    <t>[np.float64(972.6143951952989), np.float64(194.00021485863374)]</t>
+  </si>
+  <si>
+    <t>[np.float64(402.3504572775157), np.float64(-139.7641440246186)]</t>
+  </si>
+  <si>
+    <t>[np.float64(494.3171006017334), np.float64(-361.47636880887706)]</t>
+  </si>
+  <si>
+    <t>[np.float64(351.0737922329662), np.float64(553.7855711352565)]</t>
+  </si>
+  <si>
+    <t>[np.float64(41.118485309361354), np.float64(-572.9240595684491)]</t>
+  </si>
+  <si>
+    <t>[np.float64(356.07441180601154), np.float64(38.560297959292825)]</t>
+  </si>
+  <si>
+    <t>[np.float64(236.81601459057822), np.float64(107.9200621835663)]</t>
+  </si>
+  <si>
+    <t>[np.float64(398.05447740341094), np.float64(519.2736986953148)]</t>
+  </si>
+  <si>
+    <t>[np.float64(439.83086157432126), np.float64(-343.00432070599226)]</t>
+  </si>
+  <si>
+    <t>[np.float64(137.59609303713893), np.float64(264.1660035675412)]</t>
+  </si>
+  <si>
+    <t>[np.float64(533.1755978410577), np.float64(416.75092164924763)]</t>
+  </si>
+  <si>
+    <t>[np.float64(786.480987440336), np.float64(343.37825243254804)]</t>
+  </si>
+  <si>
+    <t>[np.float64(408.64533006786394), np.float64(-60.32255382455355)]</t>
+  </si>
+  <si>
+    <t>[np.float64(601.1125300726276), np.float64(146.9803251832102)]</t>
+  </si>
+  <si>
+    <t>[np.float64(424.72476912290756), np.float64(-182.66157922953658)]</t>
+  </si>
+  <si>
+    <t>[np.float64(295.27030988322787), np.float64(-515.5309793705653)]</t>
+  </si>
+  <si>
+    <t>[np.float64(355.5280289147551), np.float64(346.32085050227545)]</t>
+  </si>
+  <si>
+    <t>[np.float64(936.5387685933697), np.float64(-392.14502745371453)]</t>
+  </si>
+  <si>
+    <t>[np.float64(966.0381093152292), np.float64(50.949729332194806)]</t>
+  </si>
+  <si>
+    <t>[np.float64(167.369615131167), np.float64(527.6607910984328)]</t>
+  </si>
+  <si>
+    <t>[np.float64(172.19621003318107), np.float64(-346.12622087975876)]</t>
+  </si>
+  <si>
+    <t>[np.float64(238.39137899414953), np.float64(371.7576385763971)]</t>
+  </si>
+  <si>
+    <t>[np.float64(142.6050616367892), np.float64(94.64938579904685)]</t>
+  </si>
+  <si>
+    <t>[np.float64(298.42214113932295), np.float64(-443.72334946396194)]</t>
+  </si>
+  <si>
+    <t>[np.float64(250.90339209428535), np.float64(110.67698259238989)]</t>
+  </si>
+  <si>
+    <t>[np.float64(952.9967156208156), np.float64(-489.30964824486017)]</t>
+  </si>
+  <si>
+    <t>[np.float64(833.9984437622417), np.float64(-418.3805400281276)]</t>
+  </si>
+  <si>
+    <t>[np.float64(980.2187566829026), np.float64(522.5261985065254)]</t>
+  </si>
+  <si>
+    <t>[np.float64(944.9820822509342), np.float64(79.40780452466163)]</t>
+  </si>
+  <si>
+    <t>[np.float64(689.4222328107293), np.float64(454.13285326997106)]</t>
+  </si>
+  <si>
+    <t>[np.float64(830.6731685417886), np.float64(568.3612293692031)]</t>
+  </si>
+  <si>
+    <t>[np.float64(72.35091557809048), np.float64(264.3783647723908)]</t>
+  </si>
+  <si>
+    <t>[np.float64(196.17680556547035), np.float64(17.329612623629487)]</t>
+  </si>
+  <si>
+    <t>[np.float64(207.33441731790558), np.float64(-294.6852430033743)]</t>
+  </si>
+  <si>
+    <t>[np.float64(305.186722242446), np.float64(-186.88846957032047)]</t>
+  </si>
+  <si>
+    <t>[np.float64(809.8108930106698), np.float64(444.7015479205088)]</t>
+  </si>
+  <si>
+    <t>[np.float64(154.39518692942167), np.float64(410.9857304396221)]</t>
+  </si>
+  <si>
+    <t>[np.float64(576.0033227091311), np.float64(-463.3629550499445)]</t>
+  </si>
+  <si>
+    <t>[np.float64(763.9123278040468), np.float64(128.43883934695998)]</t>
+  </si>
+  <si>
+    <t>[np.float64(8.277095569743874), np.float64(-222.64575345553988)]</t>
+  </si>
+  <si>
+    <t>[np.float64(193.17457519958748), np.float64(-562.8657302372881)]</t>
+  </si>
+  <si>
+    <t>[np.float64(664.1908540907127), np.float64(144.5534889259759)]</t>
+  </si>
+  <si>
+    <t>[np.float64(992.7864932713876), np.float64(-201.25619610689557)]</t>
+  </si>
+  <si>
+    <t>[np.float64(22.83083840541178), np.float64(31.288508879810138)]</t>
+  </si>
+  <si>
+    <t>[np.float64(141.07473019615114), np.float64(-185.84215697292632)]</t>
+  </si>
+  <si>
+    <t>[np.float64(443.07970904850424), np.float64(-278.4142301008743)]</t>
+  </si>
+  <si>
+    <t>[np.float64(336.4201040585182), np.float64(-249.93546645934464)]</t>
+  </si>
+  <si>
+    <t>[np.float64(670.1308032801509), np.float64(58.45018440237072)]</t>
+  </si>
+  <si>
+    <t>[np.float64(492.9937244802648), np.float64(216.47652836878262)]</t>
+  </si>
+  <si>
+    <t>[np.float64(964.0276211243828), np.float64(-422.9552496408264)]</t>
+  </si>
+  <si>
+    <t>[np.float64(83.99410687597909), np.float64(-358.20287417745163)]</t>
+  </si>
+  <si>
+    <t>[np.float64(833.2631699013612), np.float64(242.40345371699277)]</t>
+  </si>
+  <si>
+    <t>[np.float64(58.350779972014436), np.float64(-234.27625108942914)]</t>
+  </si>
+  <si>
+    <t>[np.float64(349.81784616030166), np.float64(593.7369925482742)]</t>
+  </si>
+  <si>
+    <t>[np.float64(271.5716567068017), np.float64(512.6782012756319)]</t>
+  </si>
+  <si>
+    <t>[np.float64(868.1120055778954), np.float64(-375.8361642665625)]</t>
+  </si>
+  <si>
+    <t>[np.float64(690.3861830069031), np.float64(-444.4318746222397)]</t>
+  </si>
+  <si>
+    <t>[np.float64(839.4348029731337), np.float64(249.30564897848012)]</t>
+  </si>
+  <si>
+    <t>[np.float64(417.9885412873745), np.float64(-281.9377973566957)]</t>
+  </si>
+  <si>
+    <t>[np.float64(975.8436137963284), np.float64(-454.7135898100645)]</t>
+  </si>
+  <si>
+    <t>[np.float64(445.99664691428273), np.float64(161.67562434974514)]</t>
+  </si>
+  <si>
+    <t>[np.float64(733.0946183311385), np.float64(-374.42407109615465)]</t>
+  </si>
+  <si>
+    <t>[np.float64(658.4877297392235), np.float64(504.672166408546)]</t>
+  </si>
+  <si>
+    <t>[np.float64(145.91911564654114), np.float64(-494.22163504894695)]</t>
+  </si>
+  <si>
+    <t>[np.float64(823.5988184352187), np.float64(369.02219434138874)]</t>
+  </si>
+  <si>
+    <t>[np.float64(926.3699438339537), np.float64(495.99309002793257)]</t>
+  </si>
+  <si>
+    <t>[np.float64(925.3227172583577), np.float64(284.14770463738125)]</t>
+  </si>
+  <si>
+    <t>[np.float64(143.32745847326157), np.float64(265.36928552909944)]</t>
+  </si>
+  <si>
+    <t>[np.float64(20.661147320808926), np.float64(-215.20336830791194)]</t>
+  </si>
+  <si>
+    <t>[np.float64(659.5776040309706), np.float64(543.6729057696475)]</t>
+  </si>
+  <si>
+    <t>[np.float64(837.6413262033972), np.float64(-260.0602787333419)]</t>
+  </si>
+  <si>
+    <t>[np.float64(375.42630040390367), np.float64(-342.735970914313)]</t>
+  </si>
+  <si>
+    <t>[np.float64(783.8123812876248), np.float64(370.12433895880133)]</t>
+  </si>
+  <si>
+    <t>[np.float64(871.3071578640572), np.float64(238.62639589637195)]</t>
+  </si>
+  <si>
+    <t>[np.float64(720.1486530014076), np.float64(306.3433032670563)]</t>
+  </si>
+  <si>
+    <t>[np.float64(615.1610986546553), np.float64(-132.89233729459954)]</t>
+  </si>
+  <si>
+    <t>[np.float64(327.3335865848017), np.float64(523.7686463525747)]</t>
+  </si>
+  <si>
+    <t>[np.float64(351.0428750170972), np.float64(514.4190683223294)]</t>
+  </si>
+  <si>
+    <t>[np.float64(436.6784867242532), np.float64(-112.01903101839895)]</t>
+  </si>
+  <si>
+    <t>[np.float64(68.94018598206885), np.float64(185.94527266001717)]</t>
+  </si>
+  <si>
+    <t>[np.float64(565.9339954078166), np.float64(-584.461583645543)]</t>
+  </si>
+  <si>
+    <t>[np.float64(110.08394331758198), np.float64(166.38268813841603)]</t>
+  </si>
+  <si>
+    <t>[np.float64(276.27273560335817), np.float64(-386.08454820457735)]</t>
+  </si>
+  <si>
+    <t>[np.float64(853.5689338403683), np.float64(237.636081471097)]</t>
+  </si>
+  <si>
+    <t>[np.float64(392.0246486770873), np.float64(6.615524177688144)]</t>
+  </si>
+  <si>
+    <t>[np.float64(13.820475146184119), np.float64(-320.0164788582571)]</t>
+  </si>
+  <si>
+    <t>[np.float64(496.9940410436029), np.float64(-94.2929176588562)]</t>
+  </si>
+  <si>
+    <t>[np.float64(703.408660837366), np.float64(6.6424563399239105)]</t>
+  </si>
+  <si>
+    <t>[np.float64(565.8221604910009), np.float64(367.59052222696016)]</t>
+  </si>
+  <si>
+    <t>[np.float64(330.0869988654159), np.float64(-96.17905569955758)]</t>
+  </si>
+  <si>
+    <t>[np.float64(570.0620397633071), np.float64(66.21997502376519)]</t>
+  </si>
+  <si>
+    <t>[np.float64(232.0288229173656), np.float64(-449.25807126418647)]</t>
+  </si>
+  <si>
+    <t>[np.float64(445.9269291413423), np.float64(308.1870932773229)]</t>
+  </si>
+  <si>
+    <t>[np.float64(940.5876727294808), np.float64(192.406724386708)]</t>
+  </si>
+  <si>
+    <t>[np.float64(363.5981701070526), np.float64(-345.8342797209653)]</t>
+  </si>
+  <si>
+    <t>[np.float64(341.46591306279385), np.float64(-436.13744055829704)]</t>
+  </si>
+  <si>
+    <t>[np.float64(460.4731453288825), np.float64(124.22538780224329)]</t>
+  </si>
+  <si>
+    <t>[np.float64(160.3824933332243), np.float64(111.20487208456188)]</t>
+  </si>
+  <si>
+    <t>[np.float64(460.9397279620359), np.float64(-530.5011623744097)]</t>
+  </si>
+  <si>
+    <t>[np.float64(701.3775607477215), np.float64(467.99703028355384)]</t>
+  </si>
+  <si>
+    <t>[np.float64(153.51615236074534), np.float64(168.20277626423592)]</t>
+  </si>
+  <si>
+    <t>[np.float64(100.48158573757627), np.float64(-266.36264577603276)]</t>
+  </si>
+  <si>
+    <t>[np.float64(224.38205584273064), np.float64(-516.663463293795)]</t>
+  </si>
+  <si>
+    <t>[np.float64(130.08096224064258), np.float64(-201.89379858983142)]</t>
+  </si>
+  <si>
+    <t>[np.float64(727.9397731848793), np.float64(524.853611923204)]</t>
+  </si>
+  <si>
+    <t>[np.float64(993.5976353714601), np.float64(-272.5957375575628)]</t>
+  </si>
+  <si>
+    <t>[np.float64(131.25359315022033), np.float64(182.61488383551978)]</t>
+  </si>
+  <si>
+    <t>[np.float64(545.6101992529937), np.float64(-282.10638541089065)]</t>
+  </si>
+  <si>
+    <t>[np.float64(535.5457499472051), np.float64(-523.6027409344796)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.638546256247489), np.float64(-438.1998188484213)]</t>
+  </si>
+  <si>
+    <t>[np.float64(168.7663801681547), np.float64(-528.696403409804)]</t>
+  </si>
+  <si>
+    <t>[np.float64(498.4692268974169), np.float64(223.04583187746357)]</t>
+  </si>
+  <si>
+    <t>[np.float64(592.7607711794067), np.float64(499.14012189761047)]</t>
+  </si>
+  <si>
+    <t>[np.float64(225.29615483018682), np.float64(300.99368358063543)]</t>
+  </si>
+  <si>
+    <t>[np.float64(35.19642955083613), np.float64(-261.47139900469296)]</t>
+  </si>
+  <si>
+    <t>[np.float64(369.22257641661696), np.float64(3.9827795872568004)]</t>
+  </si>
+  <si>
+    <t>[np.float64(484.6095209947078), np.float64(229.65773003887944)]</t>
+  </si>
+  <si>
+    <t>[np.float64(297.30933602456656), np.float64(53.70259144214333)]</t>
+  </si>
+  <si>
+    <t>[np.float64(686.2425663573406), np.float64(-463.68825868860426)]</t>
+  </si>
+  <si>
+    <t>[np.float64(542.7743123566627), np.float64(260.05354933118315)]</t>
+  </si>
+  <si>
+    <t>[np.float64(679.5993826661089), np.float64(-510.2863854900478)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.135465073522136), np.float64(-120.12603624219872)]</t>
+  </si>
+  <si>
+    <t>[np.float64(356.68829196451725), np.float64(-94.81061406291866)]</t>
+  </si>
+  <si>
+    <t>[np.float64(456.9441745102414), np.float64(41.471594309323336)]</t>
+  </si>
+  <si>
+    <t>[np.float64(140.7741884659698), np.float64(312.18069026766545)]</t>
+  </si>
+  <si>
+    <t>[np.float64(412.0744569287804), np.float64(-557.8113439675119)]</t>
+  </si>
+  <si>
+    <t>[np.float64(757.2094830306053), np.float64(-135.95505056033875)]</t>
+  </si>
+  <si>
+    <t>[np.float64(436.81762327963025), np.float64(-247.3991364781703)]</t>
+  </si>
+  <si>
+    <t>[np.float64(504.40672406801457), np.float64(371.0642026547723)]</t>
+  </si>
+  <si>
+    <t>[np.float64(83.76770717372261), np.float64(440.8095653077198)]</t>
+  </si>
+  <si>
+    <t>[np.float64(410.2129616556647), np.float64(431.730318072867)]</t>
+  </si>
+  <si>
+    <t>[np.float64(205.1985980623061), np.float64(261.27028990366205)]</t>
+  </si>
+  <si>
+    <t>[np.float64(685.1677563067359), np.float64(-95.14816620795227)]</t>
+  </si>
+  <si>
+    <t>[np.float64(613.2164872944971), np.float64(288.25318009302043)]</t>
+  </si>
+  <si>
+    <t>[np.float64(545.9476501686604), np.float64(386.9636277130551)]</t>
+  </si>
+  <si>
+    <t>[np.float64(696.5659757402158), np.float64(32.6872666753078)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.717470406793267), np.float64(-221.789267350668)]</t>
+  </si>
+  <si>
+    <t>[np.float64(167.13069301543925), np.float64(541.5012788239835)]</t>
+  </si>
+  <si>
+    <t>[np.float64(512.055148746956), np.float64(527.7231653887245)]</t>
+  </si>
+  <si>
+    <t>[np.float64(60.740594405386815), np.float64(177.04675986532277)]</t>
+  </si>
+  <si>
+    <t>[np.float64(627.9004579150882), np.float64(-240.24602396972205)]</t>
+  </si>
+  <si>
+    <t>[np.float64(583.2115125446113), np.float64(583.2733041502927)]</t>
+  </si>
+  <si>
+    <t>[np.float64(87.35176557257208), np.float64(210.32860785382377)]</t>
+  </si>
+  <si>
+    <t>[np.float64(171.5388929896784), np.float64(-174.450870738344)]</t>
+  </si>
+  <si>
+    <t>[np.float64(552.1223721947111), np.float64(-455.4090142723005)]</t>
+  </si>
+  <si>
+    <t>[np.float64(463.53162851876016), np.float64(276.8851490184778)]</t>
+  </si>
+  <si>
+    <t>[np.float64(860.9985915305413), np.float64(412.23964562613276)]</t>
+  </si>
+  <si>
+    <t>[np.float64(435.11651337495096), np.float64(469.1513520740855)]</t>
+  </si>
+  <si>
+    <t>[np.float64(72.05732017550326), np.float64(-278.5013806060559)]</t>
+  </si>
+  <si>
+    <t>[np.float64(633.0461474524326), np.float64(523.2175786488358)]</t>
+  </si>
+  <si>
+    <t>[np.float64(520.2496259397619), np.float64(56.82337988673396)]</t>
+  </si>
+  <si>
+    <t>[np.float64(934.8216992897266), np.float64(237.75825610863217)]</t>
+  </si>
+  <si>
+    <t>[np.float64(942.8662583575907), np.float64(-506.7405220913952)]</t>
+  </si>
+  <si>
+    <t>[np.float64(886.458081682897), np.float64(-79.18687105609831)]</t>
+  </si>
+  <si>
+    <t>[np.float64(640.2309415861794), np.float64(-549.0603023160976)]</t>
+  </si>
+  <si>
+    <t>[np.float64(326.39264510741515), np.float64(540.2298003702247)]</t>
+  </si>
+  <si>
+    <t>[np.float64(20.147321146029242), np.float64(-466.4540829823578)]</t>
+  </si>
+  <si>
+    <t>[np.float64(717.4110213075601), np.float64(243.29494724395113)]</t>
+  </si>
+  <si>
+    <t>[np.float64(110.03988235440687), np.float64(502.8499683189534)]</t>
+  </si>
+  <si>
+    <t>[np.float64(274.6579818515674), np.float64(-320.4515331531252)]</t>
+  </si>
+  <si>
+    <t>[np.float64(498.6607036839147), np.float64(-533.0205535660821)]</t>
+  </si>
+  <si>
+    <t>[np.float64(992.7135175249083), np.float64(-450.78255145407036)]</t>
+  </si>
+  <si>
+    <t>[np.float64(977.6054315719208), np.float64(49.905281092709856)]</t>
+  </si>
+  <si>
+    <t>[np.float64(52.085452421379294), np.float64(-88.65254524721382)]</t>
+  </si>
+  <si>
+    <t>[np.float64(939.0767254981756), np.float64(-6.899973234594995)]</t>
+  </si>
+  <si>
+    <t>[np.float64(350.8163886998075), np.float64(-325.9917213003569)]</t>
+  </si>
+  <si>
+    <t>[np.float64(928.9009164047922), np.float64(-325.96696279048945)]</t>
+  </si>
+  <si>
+    <t>[np.float64(687.0522433802773), np.float64(250.93803469713282)]</t>
+  </si>
+  <si>
+    <t>[np.float64(573.0629165867521), np.float64(589.7022883856866)]</t>
+  </si>
+  <si>
+    <t>[np.float64(350.8786052091296), np.float64(-497.12377688845106)]</t>
+  </si>
+  <si>
+    <t>[np.float64(949.8597487049575), np.float64(248.64159585488267)]</t>
+  </si>
+  <si>
+    <t>[np.float64(256.22700946804), np.float64(283.18626600646553)]</t>
+  </si>
+  <si>
+    <t>[np.float64(403.00048612888315), np.float64(169.50940676682671)]</t>
+  </si>
+  <si>
+    <t>[np.float64(559.5319240898799), np.float64(-173.23328231073617)]</t>
+  </si>
+  <si>
+    <t>[np.float64(935.2011985250758), np.float64(-587.5138431492638)]</t>
+  </si>
+  <si>
+    <t>[np.float64(466.40678655538215), np.float64(468.0658607662292)]</t>
+  </si>
+  <si>
+    <t>[np.float64(368.54335411252316), np.float64(-413.5167358337102)]</t>
+  </si>
+  <si>
+    <t>[np.float64(357.61013989697733), np.float64(514.7082240761933)]</t>
+  </si>
+  <si>
+    <t>[np.float64(985.8856054663692), np.float64(407.05821404707615)]</t>
+  </si>
+  <si>
+    <t>[np.float64(814.8762840160176), np.float64(392.30203383001356)]</t>
+  </si>
+  <si>
+    <t>[np.float64(313.9969576968377), np.float64(-551.6072192621085)]</t>
+  </si>
+  <si>
+    <t>[np.float64(648.8280407859625), np.float64(-247.50453164254577)]</t>
+  </si>
+  <si>
+    <t>[np.float64(687.8106849566318), np.float64(-385.51570011654405)]</t>
+  </si>
+  <si>
+    <t>[np.float64(119.55771833416429), np.float64(254.24532913253108)]</t>
+  </si>
+  <si>
+    <t>[np.float64(610.381451776966), np.float64(-214.30723749998464)]</t>
+  </si>
+  <si>
+    <t>[np.float64(13.222867286976303), np.float64(-191.079197538776)]</t>
+  </si>
+  <si>
+    <t>[np.float64(731.7620041773403), np.float64(-291.8052301805751)]</t>
+  </si>
+  <si>
+    <t>[np.float64(610.5722559239133), np.float64(-165.74489727877773)]</t>
+  </si>
+  <si>
+    <t>[np.float64(98.82930429755189), np.float64(-439.0129756669749)]</t>
+  </si>
+  <si>
+    <t>[np.float64(24.735859037187225), np.float64(-365.6699398139559)]</t>
+  </si>
+  <si>
+    <t>[np.float64(992.7152989966135), np.float64(-148.65706470204663)]</t>
+  </si>
+  <si>
+    <t>[np.float64(385.04085148676694), np.float64(-319.27077354980776)]</t>
+  </si>
+  <si>
+    <t>[np.float64(345.43616570432636), np.float64(376.82582940987777)]</t>
+  </si>
+  <si>
+    <t>[np.float64(668.0285586175735), np.float64(137.26651275703716)]</t>
+  </si>
+  <si>
+    <t>[np.float64(878.7236953118302), np.float64(230.28075632773084)]</t>
+  </si>
+  <si>
+    <t>[np.float64(663.3336243698558), np.float64(455.5980723261548)]</t>
+  </si>
+  <si>
+    <t>[np.float64(334.888394187681), np.float64(278.7704783408951)]</t>
+  </si>
+  <si>
+    <t>[np.float64(189.59325376254566), np.float64(450.7151513770825)]</t>
+  </si>
+  <si>
+    <t>[np.float64(88.84839761962537), np.float64(-278.4447957892069)]</t>
+  </si>
+  <si>
+    <t>[np.float64(982.9648003199741), np.float64(28.693711968551952)]</t>
+  </si>
+  <si>
+    <t>[np.float64(512.107570666644), np.float64(-453.60856068959015)]</t>
+  </si>
+  <si>
+    <t>[np.float64(332.81586737937073), np.float64(-422.3980676187651)]</t>
+  </si>
+  <si>
+    <t>[np.float64(746.3360983799538), np.float64(91.6798204118561)]</t>
+  </si>
+  <si>
+    <t>[np.float64(74.6342995050584), np.float64(185.61669785279094)]</t>
+  </si>
+  <si>
+    <t>[np.float64(562.3375405223248), np.float64(31.616946662413852)]</t>
+  </si>
+  <si>
+    <t>[np.float64(413.041301160192), np.float64(-489.22593980754107)]</t>
+  </si>
+  <si>
+    <t>[np.float64(187.85071367054974), np.float64(-256.612444607007)]</t>
+  </si>
+  <si>
+    <t>[np.float64(609.1846702885499), np.float64(14.220036627968511)]</t>
+  </si>
+  <si>
+    <t>[np.float64(393.57201752042823), np.float64(253.79993320975984)]</t>
+  </si>
+  <si>
+    <t>[np.float64(759.5035221043242), np.float64(-285.86658244351344)]</t>
+  </si>
+  <si>
+    <t>[np.float64(280.68055941500256), np.float64(204.83226843678221)]</t>
+  </si>
+  <si>
+    <t>[np.float64(999.1568175989997), np.float64(-28.348803450444052)]</t>
+  </si>
+  <si>
+    <t>[np.float64(567.4716820067142), np.float64(560.3401539552815)]</t>
+  </si>
+  <si>
+    <t>[np.float64(950.1435782790887), np.float64(488.27028665063654)]</t>
+  </si>
+  <si>
+    <t>[np.float64(905.7907787155686), np.float64(-452.89710788466994)]</t>
+  </si>
+  <si>
+    <t>[np.float64(602.9592138014372), np.float64(417.00925673831273)]</t>
+  </si>
+  <si>
+    <t>[np.float64(767.4392967865243), np.float64(-104.98209440244193)]</t>
+  </si>
+  <si>
+    <t>[np.float64(616.4690769765764), np.float64(91.80932584076174)]</t>
+  </si>
+  <si>
+    <t>[np.float64(696.4074980313686), np.float64(-348.8429763953332)]</t>
+  </si>
+  <si>
+    <t>[np.float64(479.47670237130677), np.float64(62.731071677528575)]</t>
+  </si>
+  <si>
+    <t>[np.float64(471.08614411754223), np.float64(298.18969302931816)]</t>
+  </si>
+  <si>
+    <t>[np.float64(45.723693357087704), np.float64(346.40940400366196)]</t>
+  </si>
+  <si>
+    <t>[np.float64(14.856174641483367), np.float64(-377.06961001047773)]</t>
+  </si>
+  <si>
+    <t>[np.float64(483.0568904054701), np.float64(117.66195248587144)]</t>
+  </si>
+  <si>
+    <t>[np.float64(615.7761485030644), np.float64(-114.77567844191424)]</t>
+  </si>
+  <si>
+    <t>[np.float64(685.124402477457), np.float64(-338.3323526983305)]</t>
+  </si>
+  <si>
+    <t>[np.float64(518.0644366765289), np.float64(-103.62930428205726)]</t>
+  </si>
+  <si>
+    <t>[np.float64(806.9271247393755), np.float64(230.65205816341177)]</t>
+  </si>
+  <si>
+    <t>[np.float64(644.0571301345019), np.float64(263.28038620821667)]</t>
+  </si>
+  <si>
+    <t>[np.float64(885.099422096345), np.float64(496.9537903211851)]</t>
+  </si>
+  <si>
+    <t>[np.float64(491.0909122623248), np.float64(389.51619863337896)]</t>
+  </si>
+  <si>
+    <t>[np.float64(969.9821555942104), np.float64(-448.04548865665447)]</t>
+  </si>
+  <si>
+    <t>[np.float64(40.435490842354646), np.float64(200.32809981378864)]</t>
+  </si>
+  <si>
+    <t>[np.float64(43.37025195639954), np.float64(182.58725272120978)]</t>
+  </si>
+  <si>
+    <t>[np.float64(825.6634062317336), np.float64(523.5345422628868)]</t>
+  </si>
+  <si>
+    <t>[np.float64(614.0457106809234), np.float64(449.0955148202904)]</t>
+  </si>
+  <si>
+    <t>[np.float64(848.6370449447766), np.float64(-257.1194721347178)]</t>
+  </si>
+  <si>
+    <t>[np.float64(841.8807435026813), np.float64(135.29173743835577)]</t>
+  </si>
+  <si>
+    <t>[np.float64(310.4308447946178), np.float64(-561.1524869687095)]</t>
+  </si>
+  <si>
+    <t>[np.float64(986.7590757170235), np.float64(-412.15329193640264)]</t>
+  </si>
+  <si>
+    <t>[np.float64(550.2461775753475), np.float64(407.599688904676)]</t>
+  </si>
+  <si>
+    <t>[np.float64(50.10141138624613), np.float64(-291.3167720433314)]</t>
+  </si>
+  <si>
+    <t>[np.float64(111.64296498687033), np.float64(37.33375203182993)]</t>
+  </si>
+  <si>
+    <t>[np.float64(100.22906410411869), np.float64(-440.5998835893165)]</t>
+  </si>
+  <si>
+    <t>[np.float64(839.7366625980628), np.float64(338.0425107009187)]</t>
+  </si>
+  <si>
+    <t>[np.float64(443.594670794607), np.float64(564.6305099333745)]</t>
+  </si>
+  <si>
+    <t>[np.float64(252.4101369293924), np.float64(-82.98790819940814)]</t>
+  </si>
+  <si>
+    <t>[np.float64(37.55931111548361), np.float64(-427.5273395919019)]</t>
+  </si>
+  <si>
+    <t>[np.float64(972.2169105619009), np.float64(537.3021157764254)]</t>
+  </si>
+  <si>
+    <t>[np.float64(90.88333417339211), np.float64(-221.97275410968535)]</t>
+  </si>
+  <si>
+    <t>[np.float64(60.41558444026074), np.float64(-514.980895651453)]</t>
+  </si>
+  <si>
+    <t>[np.float64(284.53905591939156), np.float64(-533.8919666345307)]</t>
+  </si>
+  <si>
+    <t>[np.float64(444.6576360644241), np.float64(460.39793305358717)]</t>
+  </si>
+  <si>
+    <t>[np.float64(519.548590951873), np.float64(-347.15862948258655)]</t>
+  </si>
+  <si>
+    <t>[np.float64(591.2146728954607), np.float64(-567.6376880895086)]</t>
+  </si>
+  <si>
+    <t>[np.float64(53.02483145662728), np.float64(218.81963864800707)]</t>
+  </si>
+  <si>
+    <t>[np.float64(120.4761183405818), np.float64(-508.6126045045054)]</t>
+  </si>
+  <si>
+    <t>[np.float64(237.6334885599265), np.float64(297.17709414842716)]</t>
+  </si>
+  <si>
+    <t>[np.float64(725.8483172140682), np.float64(92.55769800640849)]</t>
+  </si>
+  <si>
+    <t>[np.float64(98.52337370195308), np.float64(267.32928550835925)]</t>
+  </si>
+  <si>
+    <t>[np.float64(846.2721588734775), np.float64(563.4947677925188)]</t>
+  </si>
+  <si>
+    <t>[np.float64(728.1054423370372), np.float64(-473.0570712196757)]</t>
+  </si>
+  <si>
+    <t>[np.float64(982.7860833342111), np.float64(97.04215376531204)]</t>
+  </si>
+  <si>
+    <t>[np.float64(10.085573742943943), np.float64(478.303410788905)]</t>
+  </si>
+  <si>
+    <t>[np.float64(505.0820955198676), np.float64(136.5760440347841)]</t>
+  </si>
+  <si>
+    <t>[np.float64(544.8689827061721), np.float64(523.4909958431838)]</t>
+  </si>
+  <si>
+    <t>[np.float64(7.3488908000448605), np.float64(-149.88493928657027)]</t>
+  </si>
+  <si>
+    <t>[np.float64(543.9164398079713), np.float64(-456.75359466384845)]</t>
+  </si>
+  <si>
+    <t>[np.float64(592.4147091514521), np.float64(514.3064785935974)]</t>
+  </si>
+  <si>
+    <t>[np.float64(969.3873223250998), np.float64(-292.0034682318767)]</t>
+  </si>
+  <si>
+    <t>[np.float64(851.9408242555243), np.float64(-318.0742634800945)]</t>
+  </si>
+  <si>
+    <t>[np.float64(975.9610864342579), np.float64(-386.69792747101496)]</t>
+  </si>
+  <si>
+    <t>[np.float64(60.826004350358346), np.float64(419.3348670071164)]</t>
+  </si>
+  <si>
+    <t>[np.float64(78.57184882733715), np.float64(-343.17839555838594)]</t>
+  </si>
+  <si>
+    <t>[np.float64(106.15107135047708), np.float64(-92.76594551570167)]</t>
+  </si>
+  <si>
+    <t>[np.float64(177.24749286000176), np.float64(198.79120983070266)]</t>
+  </si>
+  <si>
+    <t>[np.float64(801.1251971559883), np.float64(321.8977599836171)]</t>
+  </si>
+  <si>
+    <t>[np.float64(542.2457923918175), np.float64(-527.6531815165426)]</t>
+  </si>
+  <si>
+    <t>[np.float64(65.0605654488099), np.float64(-424.5523880762055)]</t>
+  </si>
+  <si>
+    <t>[np.float64(228.80911326921228), np.float64(-357.50798661006655)]</t>
+  </si>
+  <si>
+    <t>[np.float64(335.99644832337736), np.float64(-57.63357952154183)]</t>
+  </si>
+  <si>
+    <t>[np.float64(537.8015784476881), np.float64(-584.4370684403235)]</t>
+  </si>
+  <si>
+    <t>[np.float64(435.298063559745), np.float64(587.021413259936)]</t>
+  </si>
+  <si>
+    <t>[np.float64(299.9211817284547), np.float64(189.75505006551293)]</t>
+  </si>
+  <si>
+    <t>[np.float64(162.9295904610073), np.float64(357.0064568870972)]</t>
+  </si>
+  <si>
+    <t>[np.float64(431.07291716303354), np.float64(-138.53468400232975)]</t>
+  </si>
+  <si>
+    <t>[np.float64(885.1899872298172), np.float64(245.27182319778194)]</t>
+  </si>
+  <si>
+    <t>[np.float64(776.7418871223531), np.float64(30.485087131778073)]</t>
+  </si>
+  <si>
+    <t>[np.float64(330.4028529580275), np.float64(179.08439364642618)]</t>
+  </si>
+  <si>
+    <t>[np.float64(651.9900925345427), np.float64(-76.35442648642118)]</t>
+  </si>
+  <si>
+    <t>[np.float64(625.2837536603148), np.float64(-510.0085575193047)]</t>
+  </si>
+  <si>
+    <t>[np.float64(132.0138752193384), np.float64(-552.1215522686269)]</t>
+  </si>
+  <si>
+    <t>[np.float64(942.0155687711895), np.float64(-77.87021993111534)]</t>
+  </si>
+  <si>
+    <t>[np.float64(579.5632868615627), np.float64(273.31110045866285)]</t>
+  </si>
+  <si>
+    <t>[np.float64(936.9267267114899), np.float64(-570.923740299295)]</t>
+  </si>
+  <si>
+    <t>[np.float64(246.1805269174644), np.float64(-508.4008557221222)]</t>
+  </si>
+  <si>
+    <t>[np.float64(458.59798670439875), np.float64(26.410318526055903)]</t>
+  </si>
+  <si>
+    <t>[np.float64(161.03075250285082), np.float64(-215.8558939946858)]</t>
+  </si>
+  <si>
+    <t>[np.float64(975.5538743595766), np.float64(-517.9320528747011)]</t>
+  </si>
+  <si>
+    <t>[np.float64(729.584959999488), np.float64(-335.1312948739525)]</t>
+  </si>
+  <si>
+    <t>[np.float64(408.33476794275015), np.float64(162.70157365002285)]</t>
+  </si>
+  <si>
+    <t>[np.float64(926.6686711559892), np.float64(421.5659722461378)]</t>
+  </si>
+  <si>
+    <t>[np.float64(889.385946928445), np.float64(496.12675220512415)]</t>
+  </si>
+  <si>
+    <t>[np.float64(624.3762675501977), np.float64(496.2276762763461)]</t>
+  </si>
+  <si>
+    <t>[np.float64(36.128248294869934), np.float64(-224.72941689460322)]</t>
+  </si>
+  <si>
+    <t>[np.float64(398.08259162218707), np.float64(526.5518504522897)]</t>
+  </si>
+  <si>
+    <t>[np.float64(22.343621599479), np.float64(521.9982837537477)]</t>
+  </si>
+  <si>
+    <t>[np.float64(177.65967126642823), np.float64(377.99185451541564)]</t>
+  </si>
+  <si>
+    <t>[np.float64(701.3385964413944), np.float64(-478.3529564130947)]</t>
+  </si>
+  <si>
+    <t>[np.float64(263.14477191794884), np.float64(194.43881250123673)]</t>
+  </si>
+  <si>
+    <t>[np.float64(478.07603032179213), np.float64(250.86412062408897)]</t>
+  </si>
+  <si>
+    <t>[np.float64(984.5827451175097), np.float64(-215.83492297339734)]</t>
+  </si>
+  <si>
+    <t>[np.float64(431.3444719841601), np.float64(349.1071135177184)]</t>
+  </si>
+  <si>
+    <t>[np.float64(237.37747565043543), np.float64(-468.741673906536)]</t>
+  </si>
+  <si>
+    <t>[np.float64(510.17273973286314), np.float64(420.96387323822444)]</t>
+  </si>
+  <si>
+    <t>[np.float64(763.6808950720795), np.float64(-581.047447455577)]</t>
+  </si>
+  <si>
+    <t>[np.float64(520.4871773887128), np.float64(-427.23055489083333)]</t>
+  </si>
+  <si>
+    <t>[np.float64(849.1364107685165), np.float64(516.5380986782698)]</t>
+  </si>
+  <si>
+    <t>[np.float64(866.6258839597716), np.float64(400.9828331002153)]</t>
+  </si>
+  <si>
+    <t>[np.float64(610.3762475322798), np.float64(174.8238496928767)]</t>
+  </si>
+  <si>
+    <t>[np.float64(471.2316414532048), np.float64(-495.26173722663117)]</t>
+  </si>
+  <si>
+    <t>[np.float64(64.15249015683943), np.float64(567.2667360857188)]</t>
+  </si>
+  <si>
+    <t>[np.float64(975.1385245671862), np.float64(-548.7929375277683)]</t>
+  </si>
+  <si>
+    <t>[np.float64(694.5314361306331), np.float64(-178.70658233506572)]</t>
+  </si>
+  <si>
+    <t>[np.float64(36.21428724881959), np.float64(-34.54328998335109)]</t>
+  </si>
+  <si>
+    <t>[np.float64(118.26113843011655), np.float64(358.3721389344936)]</t>
+  </si>
+  <si>
+    <t>[np.float64(47.29478870358861), np.float64(56.61470783782863)]</t>
+  </si>
+  <si>
+    <t>[np.float64(564.3882323667337), np.float64(-487.6706589270591)]</t>
+  </si>
+  <si>
+    <t>[np.float64(974.1365381685247), np.float64(-241.56451844207692)]</t>
+  </si>
+  <si>
+    <t>[np.float64(922.1629972308634), np.float64(525.2393229941438)]</t>
+  </si>
+  <si>
+    <t>[np.float64(853.6691886034424), np.float64(-93.81457090316917)]</t>
+  </si>
+  <si>
+    <t>[np.float64(603.0422447802732), np.float64(537.0326250199557)]</t>
+  </si>
+  <si>
+    <t>[np.float64(856.9530780129862), np.float64(-357.78550524591463)]</t>
+  </si>
+  <si>
+    <t>[np.float64(228.1521776542268), np.float64(-532.8471785684043)]</t>
+  </si>
+  <si>
+    <t>[np.float64(22.352334318267996), np.float64(152.3499288262417)]</t>
+  </si>
+  <si>
+    <t>[np.float64(519.3663927717477), np.float64(558.2148425423004)]</t>
+  </si>
+  <si>
+    <t>[np.float64(975.9421817238544), np.float64(432.86557798053605)]</t>
+  </si>
+  <si>
+    <t>[np.float64(19.812396619515617), np.float64(223.62932224296742)]</t>
+  </si>
+  <si>
+    <t>[np.float64(257.72061518415757), np.float64(234.98807789378907)]</t>
+  </si>
+  <si>
+    <t>[np.float64(271.3713628417267), np.float64(-315.67880965713215)]</t>
+  </si>
+  <si>
+    <t>[np.float64(999.3871951529745), np.float64(-344.61140447591595)]</t>
+  </si>
+  <si>
+    <t>[np.float64(647.0635266833851), np.float64(-242.087991711036)]</t>
+  </si>
+  <si>
+    <t>[np.float64(10.437777649282554), np.float64(46.133312750421624)]</t>
+  </si>
+  <si>
+    <t>[np.float64(390.5869165408761), np.float64(330.88109327058964)]</t>
+  </si>
+  <si>
+    <t>[np.float64(159.89386687778273), np.float64(416.1804535559155)]</t>
+  </si>
+  <si>
+    <t>[np.float64(824.4052030879047), np.float64(-356.92027764305186)]</t>
+  </si>
+  <si>
+    <t>[np.float64(774.4833419334789), np.float64(542.3996531407438)]</t>
+  </si>
+  <si>
+    <t>[np.float64(415.91164705195894), np.float64(166.20438647537514)]</t>
+  </si>
+  <si>
+    <t>[np.float64(560.0223332073798), np.float64(346.16101327403635)]</t>
+  </si>
+  <si>
+    <t>[np.float64(693.8491732358766), np.float64(-446.12524134013194)]</t>
+  </si>
+  <si>
+    <t>[np.float64(378.14711606309356), np.float64(283.79964654343155)]</t>
+  </si>
+  <si>
+    <t>[np.float64(815.7829707025528), np.float64(-492.564287699302)]</t>
+  </si>
+  <si>
+    <t>[np.float64(440.6605865277687), np.float64(508.42110540120757)]</t>
+  </si>
+  <si>
+    <t>[np.float64(519.200428513481), np.float64(-184.0041387432617)]</t>
+  </si>
+  <si>
+    <t>[np.float64(925.7190982431255), np.float64(-247.42577569455761)]</t>
+  </si>
+  <si>
+    <t>[np.float64(794.3838777636056), np.float64(79.4361696695147)]</t>
+  </si>
+  <si>
+    <t>[np.float64(919.4391334396253), np.float64(273.0366070464662)]</t>
+  </si>
+  <si>
+    <t>[np.float64(775.503233896183), np.float64(-561.563845634285)]</t>
+  </si>
+  <si>
+    <t>[np.float64(982.0232223815441), np.float64(-154.73528885474985)]</t>
+  </si>
+  <si>
+    <t>[np.float64(794.8835003728003), np.float64(410.53182775032803)]</t>
+  </si>
+  <si>
+    <t>[np.float64(825.1450472282477), np.float64(310.9686198847737)]</t>
+  </si>
+  <si>
+    <t>[np.float64(137.98088522534746), np.float64(-196.65314080833048)]</t>
+  </si>
+  <si>
+    <t>[np.float64(37.9823738743601), np.float64(-213.54951673472777)]</t>
+  </si>
+  <si>
+    <t>[np.float64(514.3898399479907), np.float64(249.23314608642409)]</t>
+  </si>
+  <si>
+    <t>[np.float64(349.52823613840013), np.float64(-111.99535738815854)]</t>
+  </si>
+  <si>
+    <t>[np.float64(46.98519872302575), np.float64(-524.2126119200882)]</t>
+  </si>
+  <si>
+    <t>[np.float64(707.7154093920918), np.float64(-184.4322556744973)]</t>
+  </si>
+  <si>
+    <t>[np.float64(456.86041454487537), np.float64(-347.7455835137115)]</t>
+  </si>
+  <si>
+    <t>[np.float64(990.275514145552), np.float64(-193.48638213276377)]</t>
+  </si>
+  <si>
+    <t>[np.float64(881.2918605347104), np.float64(-325.52387167308945)]</t>
+  </si>
+  <si>
+    <t>[np.float64(926.327047685708), np.float64(26.152870987305732)]</t>
+  </si>
+  <si>
+    <t>[np.float64(94.66514505938362), np.float64(-377.14679617364055)]</t>
+  </si>
+  <si>
+    <t>[np.float64(327.4475021270227), np.float64(468.36107783029865)]</t>
+  </si>
+  <si>
+    <t>[np.float64(247.55659716799215), np.float64(585.6665207233302)]</t>
+  </si>
+  <si>
+    <t>[np.float64(786.3898893412661), np.float64(564.0493385813545)]</t>
+  </si>
+  <si>
+    <t>[np.float64(587.5920019854669), np.float64(-502.62165746760337)]</t>
+  </si>
+  <si>
+    <t>[np.float64(793.737610341531), np.float64(6.841402403158327)]</t>
+  </si>
+  <si>
+    <t>[np.float64(44.867066712095834), np.float64(341.1016639039549)]</t>
+  </si>
+  <si>
+    <t>[np.float64(341.86250848992506), np.float64(522.8533945967404)]</t>
+  </si>
+  <si>
+    <t>[np.float64(243.90128051199355), np.float64(-224.81252035678762)]</t>
+  </si>
+  <si>
+    <t>[np.float64(640.9794477437322), np.float64(-473.82528820715993)]</t>
+  </si>
+  <si>
+    <t>[np.float64(624.1812925309856), np.float64(398.6143433560518)]</t>
+  </si>
+  <si>
+    <t>[np.float64(895.1614150194379), np.float64(223.66514698577384)]</t>
+  </si>
+  <si>
+    <t>[np.float64(298.9924833509512), np.float64(-433.2382890860459)]</t>
+  </si>
+  <si>
+    <t>[np.float64(953.3616363929689), np.float64(385.54263506375685)]</t>
+  </si>
+  <si>
+    <t>[np.float64(985.7568784900787), np.float64(423.1360550209382)]</t>
+  </si>
+  <si>
+    <t>[np.float64(496.94552238274116), np.float64(-242.27857458427093)]</t>
+  </si>
+  <si>
+    <t>[np.float64(955.0443442472164), np.float64(-321.23382561642336)]</t>
+  </si>
+  <si>
+    <t>[np.float64(433.9866440820055), np.float64(-254.49232642229907)]</t>
+  </si>
+  <si>
+    <t>[np.float64(394.35661919219353), np.float64(-342.3423227052332)]</t>
+  </si>
+  <si>
+    <t>[np.float64(247.82841098674058), np.float64(468.1209109005533)]</t>
+  </si>
+  <si>
+    <t>[np.float64(527.3010554734783), np.float64(551.3762866570187)]</t>
+  </si>
+  <si>
+    <t>[np.float64(64.65750130127779), np.float64(-570.8819112875661)]</t>
+  </si>
+  <si>
+    <t>[np.float64(47.28772131227244), np.float64(-405.32873020916065)]</t>
+  </si>
+  <si>
+    <t>[np.float64(618.8144852005655), np.float64(82.87742683290435)]</t>
+  </si>
+  <si>
+    <t>[np.float64(396.27207764211715), np.float64(-127.68441211038606)]</t>
+  </si>
+  <si>
+    <t>[np.float64(525.3113997091098), np.float64(118.02407858827848)]</t>
+  </si>
+  <si>
+    <t>[np.float64(719.2986190698298), np.float64(-353.763060956697)]</t>
+  </si>
+  <si>
+    <t>[np.float64(567.5920358764641), np.float64(-228.58111747427432)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.4862323476577668), np.float64(167.65145969615537)]</t>
+  </si>
+  <si>
+    <t>[np.float64(358.63027425007834), np.float64(356.40747037166716)]</t>
+  </si>
+  <si>
+    <t>[np.float64(575.8298247151856), np.float64(79.12754082006722)]</t>
+  </si>
+  <si>
+    <t>[np.float64(564.8971997710292), np.float64(-394.8161913245152)]</t>
+  </si>
+  <si>
+    <t>[np.float64(978.4445051265359), np.float64(379.18258513299224)]</t>
+  </si>
+  <si>
+    <t>[np.float64(298.63339680727273), np.float64(83.82405807705925)]</t>
+  </si>
+  <si>
+    <t>[np.float64(947.730789688553), np.float64(274.27829211130575)]</t>
+  </si>
+  <si>
+    <t>[np.float64(24.968633313939172), np.float64(581.2993171110975)]</t>
+  </si>
+  <si>
+    <t>[np.float64(335.50779085692227), np.float64(573.7717324038729)]</t>
+  </si>
+  <si>
+    <t>[np.float64(141.76471469177176), np.float64(-204.3726726038106)]</t>
+  </si>
+  <si>
+    <t>[np.float64(201.65199652927944), np.float64(-433.91191712275025)]</t>
+  </si>
+  <si>
+    <t>[np.float64(152.1721559606961), np.float64(-166.3935139114501)]</t>
+  </si>
+  <si>
+    <t>[np.float64(204.5684765489044), np.float64(-279.84090453348114)]</t>
+  </si>
+  <si>
+    <t>[np.float64(123.80051583319151), np.float64(-108.38055097264237)]</t>
+  </si>
+  <si>
+    <t>[np.float64(325.2007708265696), np.float64(260.3332418200189)]</t>
+  </si>
+  <si>
+    <t>[np.float64(980.6886392696696), np.float64(-115.94855239847078)]</t>
+  </si>
+  <si>
+    <t>[np.float64(684.5564519465856), np.float64(463.32471793325976)]</t>
+  </si>
+  <si>
+    <t>[np.float64(901.8648205682409), np.float64(423.71960146974993)]</t>
+  </si>
+  <si>
+    <t>[np.float64(393.3677705273646), np.float64(-202.10354375101127)]</t>
+  </si>
+  <si>
+    <t>[np.float64(750.2275129032759), np.float64(-271.3026541104763)]</t>
+  </si>
+  <si>
+    <t>[np.float64(659.0694876728322), np.float64(-377.5056973139547)]</t>
+  </si>
+  <si>
+    <t>[np.float64(875.619472611741), np.float64(87.0446578317825)]</t>
+  </si>
+  <si>
+    <t>[np.float64(63.74193950157747), np.float64(362.80606765598645)]</t>
+  </si>
+  <si>
+    <t>[np.float64(699.3430436677904), np.float64(-361.8027538604509)]</t>
+  </si>
+  <si>
+    <t>[np.float64(869.9885035647796), np.float64(526.5191324085663)]</t>
+  </si>
+  <si>
+    <t>[np.float64(137.33137745572688), np.float64(-444.99748122584435)]</t>
+  </si>
+  <si>
+    <t>[np.float64(709.1403653079441), np.float64(594.6171160106126)]</t>
+  </si>
+  <si>
+    <t>[np.float64(354.9582419073978), np.float64(35.92936611374944)]</t>
+  </si>
+  <si>
+    <t>[np.float64(688.0449555041441), np.float64(-416.1720991813059)]</t>
+  </si>
+  <si>
+    <t>[np.float64(273.06915281998477), np.float64(344.64465624224715)]</t>
+  </si>
+  <si>
+    <t>[np.float64(282.59875155666083), np.float64(-298.4429489516672)]</t>
+  </si>
+  <si>
+    <t>[np.float64(419.9123939992203), np.float64(-536.5607356922485)]</t>
+  </si>
+  <si>
+    <t>[np.float64(938.0664190006488), np.float64(-321.4088279707093)]</t>
+  </si>
+  <si>
+    <t>[np.float64(533.2323429979987), np.float64(-437.3484492858261)]</t>
+  </si>
+  <si>
+    <t>[np.float64(486.9268594525229), np.float64(442.9005298578554)]</t>
+  </si>
+  <si>
+    <t>[np.float64(538.7163005325297), np.float64(-399.143814036652)]</t>
+  </si>
+  <si>
+    <t>[np.float64(622.3025250496975), np.float64(215.67840928801854)]</t>
+  </si>
+  <si>
+    <t>[np.float64(273.9740104005309), np.float64(167.94201930723193)]</t>
+  </si>
+  <si>
+    <t>[np.float64(593.2299798221304), np.float64(518.3019091916035)]</t>
+  </si>
+  <si>
+    <t>[np.float64(240.86061344057265), np.float64(-435.2040552680252)]</t>
+  </si>
+  <si>
+    <t>[np.float64(352.5479153880683), np.float64(-255.9310381240823)]</t>
+  </si>
+  <si>
+    <t>[np.float64(995.139264378809), np.float64(567.6151608179346)]</t>
+  </si>
+  <si>
+    <t>[np.float64(431.21418935973566), np.float64(-397.0872026943325)]</t>
+  </si>
+  <si>
+    <t>[np.float64(618.1423352600763), np.float64(-244.38769586796502)]</t>
+  </si>
+  <si>
+    <t>[np.float64(700.1220676812137), np.float64(252.65044853548454)]</t>
+  </si>
+  <si>
+    <t>[np.float64(406.1360645479882), np.float64(542.9788454548657)]</t>
+  </si>
+  <si>
+    <t>[np.float64(301.48393400069216), np.float64(197.9748777874288)]</t>
+  </si>
+  <si>
+    <t>[np.float64(365.5497456419182), np.float64(188.96482928149055)]</t>
+  </si>
+  <si>
+    <t>[np.float64(379.648966450196), np.float64(-497.47904829830156)]</t>
+  </si>
+  <si>
+    <t>[np.float64(996.4823485666268), np.float64(-360.20675693727947)]</t>
+  </si>
+  <si>
+    <t>[np.float64(983.6418634312063), np.float64(317.30168086889114)]</t>
+  </si>
+  <si>
+    <t>[np.float64(952.0606654193499), np.float64(5.917080597385279)]</t>
+  </si>
+  <si>
+    <t>[np.float64(94.96572041927276), np.float64(-259.57634920700826)]</t>
+  </si>
+  <si>
+    <t>[np.float64(949.5606349067315), np.float64(-531.6261564396397)]</t>
+  </si>
+  <si>
+    <t>[np.float64(804.3537240877266), np.float64(-278.69497232179884)]</t>
+  </si>
+  <si>
+    <t>[np.float64(303.36265658585415), np.float64(332.72916753891957)]</t>
+  </si>
+  <si>
+    <t>[np.float64(47.05799307650382), np.float64(363.11386952363193)]</t>
+  </si>
+  <si>
+    <t>[np.float64(471.0455933305901), np.float64(353.3774972981562)]</t>
+  </si>
+  <si>
+    <t>[np.float64(398.15944899359), np.float64(295.2551585837916)]</t>
+  </si>
+  <si>
+    <t>[np.float64(108.8945662471028), np.float64(537.1006756689687)]</t>
+  </si>
+  <si>
+    <t>[np.float64(122.8089372115202), np.float64(-160.4714086991849)]</t>
+  </si>
+  <si>
+    <t>[np.float64(624.3713666510522), np.float64(-376.1104271932944)]</t>
+  </si>
+  <si>
+    <t>[np.float64(343.0228692300987), np.float64(486.5498728153116)]</t>
+  </si>
+  <si>
+    <t>[np.float64(894.5788891288403), np.float64(-383.57613870317573)]</t>
+  </si>
+  <si>
+    <t>[np.float64(458.41812599915346), np.float64(318.0237449426419)]</t>
+  </si>
+  <si>
+    <t>[np.float64(989.875036394596), np.float64(510.11256893730797)]</t>
+  </si>
+  <si>
+    <t>[np.float64(473.83317017136386), np.float64(95.71098228973972)]</t>
+  </si>
+  <si>
+    <t>[np.float64(785.104028164197), np.float64(223.02838696806418)]</t>
+  </si>
+  <si>
+    <t>[np.float64(714.2470061557054), np.float64(415.94522012918776)]</t>
+  </si>
+  <si>
+    <t>[np.float64(722.6536456887529), np.float64(-271.7945665028289)]</t>
+  </si>
+  <si>
+    <t>[np.float64(736.1553014069688), np.float64(407.75127127556584)]</t>
+  </si>
+  <si>
+    <t>[np.float64(971.6218214030062), np.float64(235.26527768723895)]</t>
+  </si>
+  <si>
+    <t>[np.float64(352.94583628611855), np.float64(143.24397755643736)]</t>
+  </si>
+  <si>
+    <t>[np.float64(11.637375538077531), np.float64(-429.5278121455931)]</t>
+  </si>
+  <si>
+    <t>[np.float64(126.13007627128825), np.float64(374.98153472916727)]</t>
+  </si>
+  <si>
+    <t>[np.float64(457.42021026186154), np.float64(340.7737574422222)]</t>
+  </si>
+  <si>
+    <t>[np.float64(732.754017396203), np.float64(-488.05993713357014)]</t>
+  </si>
+  <si>
+    <t>[np.float64(405.05432727429525), np.float64(-522.4086358167672)]</t>
+  </si>
+  <si>
+    <t>[np.float64(147.54434317526244), np.float64(303.36916874425515)]</t>
+  </si>
+  <si>
+    <t>[np.float64(674.7865348370698), np.float64(-301.04319625463404)]</t>
+  </si>
+  <si>
+    <t>[np.float64(49.25859540328581), np.float64(263.85236939268407)]</t>
+  </si>
+  <si>
+    <t>[np.float64(683.2823552006702), np.float64(-166.12021368459745)]</t>
+  </si>
+  <si>
+    <t>[np.float64(193.73567139010817), np.float64(449.9128870385939)]</t>
+  </si>
+  <si>
+    <t>[np.float64(718.8095484599286), np.float64(-423.68793556609967)]</t>
+  </si>
+  <si>
+    <t>[np.float64(316.3712087538837), np.float64(-449.9795699787144)]</t>
+  </si>
+  <si>
+    <t>[np.float64(849.7131786657652), np.float64(543.7087834836918)]</t>
+  </si>
+  <si>
+    <t>[np.float64(956.0254480247984), np.float64(-238.85152584904512)]</t>
+  </si>
+  <si>
+    <t>[np.float64(330.99000894100385), np.float64(64.51603306070876)]</t>
+  </si>
+  <si>
+    <t>[np.float64(159.98114270460383), np.float64(-524.1611090429332)]</t>
+  </si>
+  <si>
+    <t>[np.float64(910.7223259157873), np.float64(198.09410547044104)]</t>
+  </si>
+  <si>
+    <t>[np.float64(588.724299408092), np.float64(-509.4022159252341)]</t>
+  </si>
+  <si>
+    <t>[np.float64(219.9624534179868), np.float64(-143.34723963729652)]</t>
+  </si>
+  <si>
+    <t>[np.float64(737.7335595855094), np.float64(584.0224320321843)]</t>
+  </si>
+  <si>
+    <t>[np.float64(100.6894789408751), np.float64(-424.0149100137003)]</t>
+  </si>
+  <si>
+    <t>[np.float64(790.0455505625107), np.float64(330.58284579699864)]</t>
+  </si>
+  <si>
+    <t>[np.float64(283.5799129181689), np.float64(-421.69605670666897)]</t>
+  </si>
+  <si>
+    <t>[np.float64(850.6215813938021), np.float64(282.69652824309617)]</t>
+  </si>
+  <si>
+    <t>[np.float64(565.8395334228353), np.float64(-574.484597879245)]</t>
+  </si>
+  <si>
+    <t>[np.float64(915.2466650373772), np.float64(-150.74482875506334)]</t>
+  </si>
+  <si>
+    <t>[np.float64(731.4828462857586), np.float64(-145.8460888323092)]</t>
+  </si>
+  <si>
+    <t>[np.float64(162.46210740643252), np.float64(-565.5189059657716)]</t>
+  </si>
+  <si>
+    <t>[np.float64(102.15423395215151), np.float64(523.1204563765011)]</t>
+  </si>
+  <si>
+    <t>[np.float64(910.7670160609576), np.float64(315.6458126775718)]</t>
+  </si>
+  <si>
+    <t>[np.float64(807.748760498035), np.float64(-523.4353254594554)]</t>
+  </si>
+  <si>
+    <t>[np.float64(766.2944790203912), np.float64(555.3088859446993)]</t>
+  </si>
+  <si>
+    <t>[np.float64(888.6905533712815), np.float64(2.9718960208653016)]</t>
+  </si>
+  <si>
+    <t>[np.float64(789.2604360538614), np.float64(-121.43103663329867)]</t>
+  </si>
+  <si>
+    <t>[np.float64(348.7764873689733), np.float64(554.472202548176)]</t>
+  </si>
+  <si>
+    <t>[np.float64(505.8054152724847), np.float64(106.54331556938791)]</t>
+  </si>
+  <si>
+    <t>[np.float64(613.6245542168343), np.float64(-177.58512426352593)]</t>
+  </si>
+  <si>
+    <t>[np.float64(6.139385761442462), np.float64(-140.8053655458337)]</t>
+  </si>
+  <si>
+    <t>[np.float64(151.86378390648713), np.float64(483.9724069219128)]</t>
+  </si>
+  <si>
+    <t>[np.float64(842.8231025435009), np.float64(-407.0826656252002)]</t>
+  </si>
+  <si>
+    <t>[np.float64(302.2132953682366), np.float64(178.97953449956822)]</t>
+  </si>
+  <si>
+    <t>[np.float64(772.0585418517728), np.float64(-168.43281031297636)]</t>
+  </si>
+  <si>
+    <t>[np.float64(700.2648733776966), np.float64(383.6553733520217)]</t>
+  </si>
+  <si>
+    <t>[np.float64(883.0427729624241), np.float64(30.313381057693732)]</t>
+  </si>
+  <si>
+    <t>[np.float64(45.90773026238093), np.float64(474.31727425539157)]</t>
+  </si>
+  <si>
+    <t>[np.float64(856.6855633965885), np.float64(-212.43070078776992)]</t>
+  </si>
+  <si>
+    <t>[np.float64(404.92548913431557), np.float64(457.9896851379849)]</t>
+  </si>
+  <si>
+    <t>[np.float64(266.57664858586804), np.float64(583.4954150211263)]</t>
+  </si>
+  <si>
+    <t>[np.float64(42.642618179858594), np.float64(166.38931120427537)]</t>
+  </si>
+  <si>
+    <t>[np.float64(691.4638215117831), np.float64(367.5536773132977)]</t>
+  </si>
+  <si>
+    <t>[np.float64(599.2730760386778), np.float64(338.24928209461723)]</t>
+  </si>
+  <si>
+    <t>[np.float64(879.9626176510224), np.float64(445.3328115761394)]</t>
+  </si>
+  <si>
+    <t>[np.float64(365.8416731560545), np.float64(330.8095794971068)]</t>
+  </si>
+  <si>
+    <t>[np.float64(272.8817784400308), np.float64(-488.31618058098195)]</t>
+  </si>
+  <si>
+    <t>[np.float64(275.26787990112166), np.float64(-182.137599367497)]</t>
+  </si>
+  <si>
+    <t>[np.float64(331.6558722317903), np.float64(-132.47328095639108)]</t>
+  </si>
+  <si>
+    <t>[np.float64(91.19434352059774), np.float64(45.564951891106034)]</t>
+  </si>
+  <si>
+    <t>[np.float64(184.9585748983198), np.float64(598.7398936451154)]</t>
+  </si>
+  <si>
+    <t>[np.float64(348.2367048018119), np.float64(-88.89758416390316)]</t>
+  </si>
+  <si>
+    <t>[np.float64(998.5345999672821), np.float64(463.82630571773643)]</t>
+  </si>
+  <si>
+    <t>[np.float64(206.45265871228526), np.float64(-120.43734039240417)]</t>
+  </si>
+  <si>
+    <t>[np.float64(622.8014121871574), np.float64(410.3045342533487)]</t>
+  </si>
+  <si>
+    <t>[np.float64(458.32303740708755), np.float64(538.7020035446417)]</t>
+  </si>
+  <si>
+    <t>[np.float64(359.46036639698355), np.float64(239.37261003249728)]</t>
+  </si>
+  <si>
+    <t>[np.float64(336.7247385091705), np.float64(-233.36508038741061)]</t>
+  </si>
+  <si>
+    <t>[np.float64(613.173146408657), np.float64(563.6698293408504)]</t>
+  </si>
+  <si>
+    <t>[np.float64(549.0393478823652), np.float64(-526.1912090945949)]</t>
+  </si>
+  <si>
+    <t>[np.float64(135.6807209493004), np.float64(-461.77354336950043)]</t>
+  </si>
+  <si>
+    <t>[np.float64(804.9646744897129), np.float64(-485.75944640331795)]</t>
+  </si>
+  <si>
+    <t>[np.float64(5.128758909079711), np.float64(277.40695846114136)]</t>
+  </si>
+  <si>
+    <t>[np.float64(8.842846518072434), np.float64(243.72781765646812)]</t>
+  </si>
+  <si>
+    <t>[np.float64(140.18449164003266), np.float64(-127.32985767923725)]</t>
+  </si>
+  <si>
+    <t>[np.float64(964.6594845204435), np.float64(-370.5370721162857)]</t>
+  </si>
+  <si>
+    <t>[np.float64(278.6330773249168), np.float64(110.21543814714892)]</t>
+  </si>
+  <si>
+    <t>[np.float64(735.2074913437694), np.float64(183.54215035997663)]</t>
+  </si>
+  <si>
+    <t>[np.float64(730.5193362511706), np.float64(-178.99014874539608)]</t>
+  </si>
+  <si>
+    <t>[np.float64(544.5596882331288), np.float64(266.6229270584131)]</t>
+  </si>
+  <si>
+    <t>[np.float64(376.1955789740511), np.float64(-391.9147556715957)]</t>
+  </si>
+  <si>
+    <t>[np.float64(770.8073848788455), np.float64(240.3887094913058)]</t>
+  </si>
+  <si>
+    <t>[np.float64(402.7293321931792), np.float64(-407.8021247656839)]</t>
+  </si>
+  <si>
+    <t>[np.float64(795.2147826820261), np.float64(-178.27392857310764)]</t>
+  </si>
+  <si>
+    <t>[np.float64(826.8820412690137), np.float64(583.2039440292722)]</t>
+  </si>
+  <si>
+    <t>[np.float64(156.42424907834484), np.float64(544.8824203776078)]</t>
+  </si>
+  <si>
+    <t>[np.float64(577.5554363600329), np.float64(-81.62993860841448)]</t>
+  </si>
+  <si>
+    <t>[np.float64(324.7724068955014), np.float64(251.36944547958205)]</t>
+  </si>
+  <si>
+    <t>[np.float64(251.41010840011813), np.float64(-515.0073337877595)]</t>
+  </si>
+  <si>
+    <t>[np.float64(407.87515494232986), np.float64(498.2385698842886)]</t>
+  </si>
+  <si>
+    <t>[np.float64(990.2343318702542), np.float64(-133.40133923884218)]</t>
+  </si>
+  <si>
+    <t>[np.float64(582.0781505534763), np.float64(107.39094957743373)]</t>
+  </si>
+  <si>
+    <t>[np.float64(991.4689781368527), np.float64(469.0450340968089)]</t>
+  </si>
+  <si>
+    <t>[np.float64(870.6598611348109), np.float64(-370.96142451024923)]</t>
+  </si>
+  <si>
+    <t>[np.float64(33.07214175556905), np.float64(-50.3991739087902)]</t>
+  </si>
+  <si>
+    <t>[np.float64(841.3286462724226), np.float64(117.44669415478393)]</t>
+  </si>
+  <si>
+    <t>[np.float64(403.70421736858975), np.float64(-408.04747255553656)]</t>
+  </si>
+  <si>
+    <t>[np.float64(100.15312538530108), np.float64(223.00793875692295)]</t>
+  </si>
+  <si>
+    <t>[np.float64(791.682292067987), np.float64(84.07790539534824)]</t>
+  </si>
+  <si>
+    <t>[np.float64(611.5022848949019), np.float64(-99.65392912008025)]</t>
+  </si>
+  <si>
+    <t>[np.float64(623.5157409321789), np.float64(-271.16043456891816)]</t>
+  </si>
+  <si>
+    <t>[np.float64(811.3569413294441), np.float64(172.5420369056602)]</t>
+  </si>
+  <si>
+    <t>[np.float64(347.84667682885674), np.float64(-135.91672409239493)]</t>
+  </si>
+  <si>
+    <t>[np.float64(718.0763316137654), np.float64(103.10713502145984)]</t>
+  </si>
+  <si>
+    <t>[np.float64(749.3615261264648), np.float64(-365.1043110394493)]</t>
+  </si>
+  <si>
+    <t>[np.float64(541.131269437889), np.float64(-446.20704693655097)]</t>
+  </si>
+  <si>
+    <t>[np.float64(525.2264806831485), np.float64(32.31137135744598)]</t>
+  </si>
+  <si>
+    <t>[np.float64(344.6738775863043), np.float64(422.1183111522023)]</t>
+  </si>
+  <si>
+    <t>[np.float64(201.68705186422875), np.float64(43.28957350652183)]</t>
+  </si>
+  <si>
+    <t>[np.float64(839.3427102907226), np.float64(-76.55906392685563)]</t>
+  </si>
+  <si>
+    <t>[np.float64(630.4078167007908), np.float64(235.24959092844313)]</t>
+  </si>
+  <si>
+    <t>[np.float64(84.02146324058579), np.float64(586.244593704753)]</t>
+  </si>
+  <si>
+    <t>[np.float64(165.15367486086663), np.float64(21.128285810152875)]</t>
+  </si>
+  <si>
+    <t>[np.float64(950.828007292074), np.float64(95.61486591748917)]</t>
+  </si>
+  <si>
+    <t>[np.float64(161.62219094638996), np.float64(77.03572530748875)]</t>
+  </si>
+  <si>
+    <t>[np.float64(188.19021239772204), np.float64(-410.00505957818723)]</t>
+  </si>
+  <si>
+    <t>[np.float64(522.2283701704829), np.float64(240.4906720203761)]</t>
+  </si>
+  <si>
+    <t>[np.float64(792.1674885152331), np.float64(136.89831559296783)]</t>
+  </si>
+  <si>
+    <t>[np.float64(109.47214631621883), np.float64(426.41818346281775)]</t>
+  </si>
+  <si>
+    <t>[np.float64(991.1612557206328), np.float64(416.61808617147267)]</t>
+  </si>
+  <si>
+    <t>[np.float64(560.3106474333013), np.float64(-328.79292891400155)]</t>
+  </si>
+  <si>
+    <t>[np.float64(501.8055162385708), np.float64(441.0269882646994)]</t>
+  </si>
+  <si>
+    <t>[np.float64(672.2569078604723), np.float64(285.1548545792406)]</t>
+  </si>
+  <si>
+    <t>[np.float64(789.7265608461339), np.float64(-131.99495471109304)]</t>
+  </si>
+  <si>
+    <t>[np.float64(41.97671276515136), np.float64(-538.1110640217273)]</t>
+  </si>
+  <si>
+    <t>[np.float64(217.52004992542484), np.float64(-415.1441459608017)]</t>
+  </si>
+  <si>
+    <t>[np.float64(965.2231828672719), np.float64(-533.3072136653794)]</t>
+  </si>
+  <si>
+    <t>[np.float64(15.970145243437873), np.float64(-503.4182414374556)]</t>
+  </si>
+  <si>
+    <t>[np.float64(41.877879902096794), np.float64(-359.7129687580525)]</t>
+  </si>
+  <si>
+    <t>[np.float64(262.7628337582751), np.float64(-450.1898452889149)]</t>
+  </si>
+  <si>
+    <t>[np.float64(595.6994202595737), np.float64(-233.974223257875)]</t>
+  </si>
+  <si>
+    <t>[np.float64(619.604288427025), np.float64(45.1612497870924)]</t>
+  </si>
+  <si>
+    <t>[np.float64(40.571111383918556), np.float64(279.1117351778779)]</t>
+  </si>
+  <si>
+    <t>[np.float64(552.4323471769615), np.float64(-71.03609085407072)]</t>
+  </si>
+  <si>
+    <t>[np.float64(53.03494629892036), np.float64(502.25185876999535)]</t>
+  </si>
+  <si>
+    <t>[np.float64(754.754588610786), np.float64(-419.1762158601679)]</t>
+  </si>
+  <si>
+    <t>[np.float64(865.5846433521908), np.float64(-106.25330837832257)]</t>
+  </si>
+  <si>
+    <t>[np.float64(182.3450973587557), np.float64(7.79112079935669)]</t>
+  </si>
+  <si>
+    <t>[np.float64(872.8566732761651), np.float64(-573.7910993925476)]</t>
+  </si>
+  <si>
+    <t>[np.float64(826.4364687377639), np.float64(-297.90613256236827)]</t>
+  </si>
+  <si>
+    <t>[np.float64(35.0650069159435), np.float64(368.29928880083423)]</t>
+  </si>
+  <si>
+    <t>[np.float64(646.1824889772478), np.float64(202.94272923678716)]</t>
+  </si>
+  <si>
+    <t>[np.float64(33.65535386869989), np.float64(-502.5994586515312)]</t>
+  </si>
+  <si>
+    <t>[np.float64(168.61014503872417), np.float64(290.77015893774615)]</t>
+  </si>
+  <si>
+    <t>[np.float64(599.1990965268244), np.float64(390.82751688941255)]</t>
+  </si>
+  <si>
+    <t>[np.float64(83.7724648064897), np.float64(-484.47869862373)]</t>
+  </si>
+  <si>
+    <t>[np.float64(698.3443129789694), np.float64(318.64499383752093)]</t>
+  </si>
+  <si>
+    <t>[np.float64(491.03028355926494), np.float64(349.9656961091621)]</t>
+  </si>
+  <si>
+    <t>[np.float64(229.2652881415327), np.float64(44.11642479226532)]</t>
+  </si>
+  <si>
+    <t>[np.float64(510.38373331301955), np.float64(-496.442879720575)]</t>
+  </si>
+  <si>
+    <t>[np.float64(863.1342587541945), np.float64(-172.19247902575842)]</t>
+  </si>
+  <si>
+    <t>[np.float64(91.78239148020484), np.float64(77.72815147066035)]</t>
+  </si>
+  <si>
+    <t>[np.float64(40.17040773287028), np.float64(389.5600398446769)]</t>
+  </si>
+  <si>
+    <t>[np.float64(888.0543787438288), np.float64(-582.1881064849108)]</t>
+  </si>
+  <si>
+    <t>[np.float64(828.883960565483), np.float64(542.6518286075732)]</t>
+  </si>
+  <si>
+    <t>[np.float64(45.05529043950085), np.float64(-333.7433503812844)]</t>
+  </si>
+  <si>
+    <t>[np.float64(413.87986440331815), np.float64(565.0373844972003)]</t>
+  </si>
+  <si>
+    <t>[np.float64(413.70954783707936), np.float64(-498.27667923265875)]</t>
+  </si>
+  <si>
+    <t>[np.float64(867.4348551396876), np.float64(-580.9204792733219)]</t>
+  </si>
+  <si>
+    <t>[np.float64(973.2833550031226), np.float64(-574.0825911071955)]</t>
+  </si>
+  <si>
+    <t>[np.float64(399.72312861941), np.float64(158.8102895704975)]</t>
+  </si>
+  <si>
+    <t>[np.float64(882.1805181681448), np.float64(-430.84013963551524)]</t>
+  </si>
+  <si>
+    <t>[np.float64(375.513813475711), np.float64(457.7718484346717)]</t>
+  </si>
+  <si>
+    <t>[np.float64(675.5377254934505), np.float64(-585.6343409873242)]</t>
+  </si>
+  <si>
+    <t>[np.float64(242.10400606859918), np.float64(-226.6204357212237)]</t>
+  </si>
+  <si>
+    <t>[np.float64(918.0646607361383), np.float64(62.25755672831065)]</t>
+  </si>
+  <si>
+    <t>[np.float64(245.08646734029548), np.float64(55.2789805991423)]</t>
+  </si>
+  <si>
+    <t>[np.float64(817.4242676181956), np.float64(74.84181931298247)]</t>
+  </si>
+  <si>
+    <t>[np.float64(605.9759925975123), np.float64(528.1239338435171)]</t>
+  </si>
+  <si>
+    <t>[np.float64(681.6306159999808), np.float64(386.71470745069723)]</t>
+  </si>
+  <si>
+    <t>[np.float64(385.0987947054014), np.float64(488.62554510429845)]</t>
+  </si>
+  <si>
+    <t>[np.float64(380.3391195281336), np.float64(-168.2017930658434)]</t>
+  </si>
+  <si>
+    <t>[np.float64(449.74336150641557), np.float64(-247.6238264892864)]</t>
+  </si>
+  <si>
+    <t>[np.float64(218.1869430616329), np.float64(-89.66677375564757)]</t>
+  </si>
+  <si>
+    <t>[np.float64(638.1157425732459), np.float64(-522.2923758663405)]</t>
+  </si>
+  <si>
+    <t>[np.float64(59.5036034910964), np.float64(306.7009808411233)]</t>
+  </si>
+  <si>
+    <t>[np.float64(441.52233515999393), np.float64(139.81125116242515)]</t>
+  </si>
+  <si>
+    <t>[np.float64(845.3123008723794), np.float64(-398.43628135029394)]</t>
+  </si>
+  <si>
+    <t>[np.float64(474.80270566870087), np.float64(541.5076783078039)]</t>
+  </si>
+  <si>
+    <t>[np.float64(428.3422606623815), np.float64(540.4097154505896)]</t>
+  </si>
+  <si>
+    <t>[np.float64(911.3157042917687), np.float64(441.416016265699)]</t>
+  </si>
+  <si>
+    <t>[np.float64(701.2169303793247), np.float64(-571.3470392884841)]</t>
+  </si>
+  <si>
+    <t>[np.float64(542.1500013618067), np.float64(282.7739942886708)]</t>
+  </si>
+  <si>
+    <t>[np.float64(597.4661116535838), np.float64(34.75725687403565)]</t>
+  </si>
+  <si>
+    <t>[np.float64(785.7896517048258), np.float64(6.931260683922915)]</t>
+  </si>
+  <si>
+    <t>[np.float64(704.1789996363191), np.float64(-314.9536730032095)]</t>
+  </si>
+  <si>
+    <t>[np.float64(9.523079489563768), np.float64(-112.05901233388676)]</t>
+  </si>
+  <si>
+    <t>[np.float64(600.4863852704435), np.float64(344.6820701603466)]</t>
+  </si>
+  <si>
+    <t>[np.float64(262.6500476728617), np.float64(113.9411858588054)]</t>
+  </si>
+  <si>
+    <t>[np.float64(773.489343292419), np.float64(588.1306648580967)]</t>
+  </si>
+  <si>
+    <t>[np.float64(96.53936969700783), np.float64(-487.83201499524654)]</t>
+  </si>
+  <si>
+    <t>[np.float64(820.5619975111845), np.float64(-214.39366697458377)]</t>
+  </si>
+  <si>
+    <t>[np.float64(644.6248440447425), np.float64(46.430438834395545)]</t>
+  </si>
+  <si>
+    <t>[np.float64(709.2865537311363), np.float64(214.44536124296644)]</t>
+  </si>
+  <si>
+    <t>[np.float64(291.38303213609805), np.float64(-182.7157988241143)]</t>
+  </si>
+  <si>
+    <t>[np.float64(158.35731150312316), np.float64(139.84330245752915)]</t>
+  </si>
+  <si>
+    <t>[np.float64(477.99219955722674), np.float64(-127.18817183770796)]</t>
+  </si>
+  <si>
+    <t>[np.float64(583.8827306294663), np.float64(254.39331513082504)]</t>
+  </si>
+  <si>
+    <t>[np.float64(287.26744775708056), np.float64(145.58376816450675)]</t>
+  </si>
+  <si>
+    <t>[np.float64(591.9585803691182), np.float64(293.392011125782)]</t>
+  </si>
+  <si>
+    <t>[np.float64(719.9141783941582), np.float64(-165.78944477491297)]</t>
+  </si>
+  <si>
+    <t>[np.float64(607.5394168786147), np.float64(143.25616024930912)]</t>
+  </si>
+  <si>
+    <t>[np.float64(172.33799203394184), np.float64(-204.64668488458494)]</t>
+  </si>
+  <si>
+    <t>[np.float64(215.02988794904786), np.float64(-385.788081884672)]</t>
+  </si>
+  <si>
+    <t>[np.float64(46.388333957288694), np.float64(-304.1319047243003)]</t>
+  </si>
+  <si>
+    <t>[np.float64(874.9511061760967), np.float64(504.9855381798559)]</t>
+  </si>
+  <si>
+    <t>[np.float64(979.7905797052548), np.float64(160.8018625323998)]</t>
+  </si>
+  <si>
+    <t>[np.float64(411.18058238595137), np.float64(-290.72402023519896)]</t>
+  </si>
+  <si>
+    <t>[np.float64(394.5079200826479), np.float64(-269.222609805374)]</t>
+  </si>
+  <si>
+    <t>[np.float64(870.5449993970024), np.float64(227.86892287760247)]</t>
+  </si>
+  <si>
+    <t>[np.float64(950.9124944137383), np.float64(171.74610318536656)]</t>
+  </si>
+  <si>
+    <t>[np.float64(41.774381841583995), np.float64(485.39038948147663)]</t>
+  </si>
+  <si>
+    <t>[np.float64(529.1246345787508), np.float64(124.65022144651277)]</t>
+  </si>
+  <si>
+    <t>[np.float64(383.3986705082982), np.float64(321.2083130055332)]</t>
+  </si>
+  <si>
+    <t>[np.float64(175.8314016395759), np.float64(-164.85341917224656)]</t>
+  </si>
+  <si>
+    <t>[np.float64(474.2674777095154), np.float64(-565.7790848767806)]</t>
+  </si>
+  <si>
+    <t>[np.float64(833.8135133997405), np.float64(-68.60573434032551)]</t>
+  </si>
+  <si>
+    <t>[np.float64(836.7634041169495), np.float64(449.6308781350331)]</t>
+  </si>
+  <si>
+    <t>[np.float64(13.600628724656838), np.float64(-329.6924115701857)]</t>
+  </si>
+  <si>
+    <t>[np.float64(888.3334124199098), np.float64(-276.77951172539434)]</t>
+  </si>
+  <si>
+    <t>[np.float64(293.3678530350633), np.float64(527.748217318418)]</t>
+  </si>
+  <si>
+    <t>[np.float64(772.1710809108065), np.float64(240.76260457605315)]</t>
+  </si>
+  <si>
+    <t>[np.float64(324.548341363475), np.float64(196.20723510368043)]</t>
+  </si>
+  <si>
+    <t>[np.float64(61.16501440543498), np.float64(-295.32174660860505)]</t>
+  </si>
+  <si>
+    <t>[np.float64(733.7887488417442), np.float64(-503.7560161808319)]</t>
+  </si>
+  <si>
+    <t>[np.float64(391.53137138534066), np.float64(504.1105884981132)]</t>
+  </si>
+  <si>
+    <t>[np.float64(398.15873395065915), np.float64(145.52506948298878)]</t>
+  </si>
+  <si>
+    <t>[np.float64(521.8532612949518), np.float64(208.25845118806285)]</t>
+  </si>
+  <si>
+    <t>[np.float64(387.8752444069031), np.float64(-257.5736480114014)]</t>
+  </si>
+  <si>
+    <t>[np.float64(328.0877360549865), np.float64(409.34195660353976)]</t>
+  </si>
+  <si>
+    <t>[np.float64(310.5720588475156), np.float64(-369.2498719272877)]</t>
+  </si>
+  <si>
+    <t>[np.float64(285.09456193912706), np.float64(190.60632410669552)]</t>
+  </si>
+  <si>
+    <t>[np.float64(115.47271483547172), np.float64(108.37018271582065)]</t>
+  </si>
+  <si>
+    <t>[np.float64(706.3058859565211), np.float64(-124.09893943302342)]</t>
+  </si>
+  <si>
+    <t>[np.float64(875.8242142248528), np.float64(-206.65793060686718)]</t>
+  </si>
+  <si>
+    <t>[np.float64(912.5878779083389), np.float64(196.40203994137948)]</t>
+  </si>
+  <si>
+    <t>[np.float64(349.595619634135), np.float64(-530.6055587821033)]</t>
+  </si>
+  <si>
+    <t>[np.float64(784.2799482658504), np.float64(-247.33428346268107)]</t>
+  </si>
+  <si>
+    <t>[np.float64(935.6385194133449), np.float64(243.33788050362693)]</t>
+  </si>
+  <si>
+    <t>[np.float64(167.32882303918606), np.float64(-452.1716296239881)]</t>
+  </si>
+  <si>
+    <t>[np.float64(71.05918307000624), np.float64(110.7715114418811)]</t>
+  </si>
+  <si>
+    <t>[np.float64(962.1730293468747), np.float64(6.697128468646156)]</t>
+  </si>
+  <si>
+    <t>[np.float64(597.9396337375595), np.float64(-302.6048871250906)]</t>
+  </si>
+  <si>
+    <t>[np.float64(960.8474844402797), np.float64(524.3902105212801)]</t>
+  </si>
+  <si>
+    <t>[np.float64(814.4864031301495), np.float64(36.26641447707834)]</t>
+  </si>
+  <si>
+    <t>[np.float64(949.6920813971825), np.float64(324.28284222651814)]</t>
+  </si>
+  <si>
+    <t>[np.float64(658.4009382118744), np.float64(-543.267495574783)]</t>
+  </si>
+  <si>
+    <t>[np.float64(233.49495451136826), np.float64(-434.29915538060266)]</t>
+  </si>
+  <si>
+    <t>[np.float64(530.586766107371), np.float64(133.78713877380483)]</t>
+  </si>
+  <si>
+    <t>[np.float64(6.899661766342602), np.float64(536.8429543841282)]</t>
+  </si>
+  <si>
+    <t>[np.float64(818.0210583174686), np.float64(-384.8301814206339)]</t>
+  </si>
+  <si>
+    <t>[np.float64(638.2505136150863), np.float64(-533.1084565103931)]</t>
+  </si>
+  <si>
+    <t>[np.float64(762.819675330464), np.float64(194.36698337126575)]</t>
+  </si>
+  <si>
+    <t>[np.float64(995.9404621975743), np.float64(-148.218050376179)]</t>
+  </si>
+  <si>
+    <t>[np.float64(681.5008241970622), np.float64(-505.35922092974187)]</t>
+  </si>
+  <si>
+    <t>[np.float64(964.9511803723009), np.float64(27.71553178101442)]</t>
+  </si>
+  <si>
+    <t>[np.float64(244.10987271167772), np.float64(-219.58597267912745)]</t>
+  </si>
+  <si>
+    <t>[np.float64(479.39906663553666), np.float64(-330.4423746674051)]</t>
+  </si>
+  <si>
+    <t>[np.float64(588.5637202084847), np.float64(286.85737396646005)]</t>
+  </si>
+  <si>
+    <t>[np.float64(803.2324564501438), np.float64(104.86426844394578)]</t>
+  </si>
+  <si>
+    <t>[np.float64(157.05334213969658), np.float64(125.66272336261773)]</t>
+  </si>
+  <si>
+    <t>[np.float64(193.27309630478794), np.float64(538.8725900409368)]</t>
+  </si>
+  <si>
+    <t>[np.float64(615.2721016050733), np.float64(358.9841982669425)]</t>
+  </si>
+  <si>
+    <t>[np.float64(7.391827346524549), np.float64(428.2951494460465)]</t>
+  </si>
+  <si>
+    <t>[np.float64(496.6407943927955), np.float64(356.3780743036274)]</t>
+  </si>
+  <si>
+    <t>[np.float64(262.1944040726264), np.float64(-527.8927537708626)]</t>
+  </si>
+  <si>
+    <t>[np.float64(975.8692340929579), np.float64(-347.1854829754651)]</t>
+  </si>
+  <si>
+    <t>[np.float64(194.84844400765112), np.float64(573.7675277256078)]</t>
+  </si>
+  <si>
+    <t>[np.float64(215.7573052132846), np.float64(-187.75268494943498)]</t>
+  </si>
+  <si>
+    <t>[np.float64(968.5927295784726), np.float64(564.2142303029693)]</t>
+  </si>
+  <si>
+    <t>[np.float64(391.26080882811823), np.float64(-203.04411145455282)]</t>
+  </si>
+  <si>
+    <t>[np.float64(30.90664032665702), np.float64(537.1317094304729)]</t>
+  </si>
+  <si>
+    <t>[np.float64(44.73572634859768), np.float64(76.0252233981754)]</t>
+  </si>
+  <si>
+    <t>[np.float64(98.50131739796308), np.float64(-192.96029911936603)]</t>
+  </si>
+  <si>
+    <t>[np.float64(176.87899849924415), np.float64(-553.6063934740864)]</t>
+  </si>
+  <si>
+    <t>[np.float64(878.5510500705412), np.float64(-276.6910228547285)]</t>
+  </si>
+  <si>
+    <t>[np.float64(432.19786773047883), np.float64(-104.61230107547323)]</t>
+  </si>
+  <si>
+    <t>[np.float64(876.343787233371), np.float64(-423.5440241208399)]</t>
+  </si>
+  <si>
+    <t>[np.float64(11.818514321525807), np.float64(-150.85818895048874)]</t>
+  </si>
+  <si>
+    <t>[np.float64(308.03031061926356), np.float64(164.26475200151174)]</t>
+  </si>
+  <si>
+    <t>[np.float64(379.384813392412), np.float64(391.78094710196615)]</t>
+  </si>
+  <si>
+    <t>[np.float64(747.6188216988764), np.float64(0.7220928281914212)]</t>
+  </si>
+  <si>
+    <t>[np.float64(467.3222668625707), np.float64(415.58037572071737)]</t>
+  </si>
+  <si>
+    <t>[np.float64(222.36985755307182), np.float64(-172.7611786553287)]</t>
+  </si>
+  <si>
+    <t>[np.float64(415.3794132312576), np.float64(99.89205336467762)]</t>
+  </si>
+  <si>
+    <t>[np.float64(645.5329648568016), np.float64(35.0443111451458)]</t>
+  </si>
+  <si>
+    <t>[np.float64(809.2603484031496), np.float64(593.8096719321366)]</t>
+  </si>
+  <si>
+    <t>[np.float64(215.4900990048796), np.float64(162.36254244021313)]</t>
+  </si>
+  <si>
+    <t>[np.float64(594.0180046176199), np.float64(207.9499802087056)]</t>
+  </si>
+  <si>
+    <t>[np.float64(553.6473691751141), np.float64(157.4805871170047)]</t>
+  </si>
+  <si>
+    <t>[np.float64(948.7748303692242), np.float64(166.67025553441079)]</t>
+  </si>
+  <si>
+    <t>[np.float64(888.9019660526354), np.float64(189.9541397831382)]</t>
+  </si>
+  <si>
+    <t>[np.float64(916.7888410041443), np.float64(378.82611760438465)]</t>
+  </si>
+  <si>
+    <t>[np.float64(229.78820155649404), np.float64(-153.64236585949112)]</t>
+  </si>
+  <si>
+    <t>[np.float64(161.7402983070174), np.float64(-480.72123908754025)]</t>
+  </si>
+  <si>
+    <t>[np.float64(819.1806019290684), np.float64(-268.0581909647278)]</t>
+  </si>
+  <si>
+    <t>[np.float64(461.9666252264801), np.float64(356.3050277456987)]</t>
+  </si>
+  <si>
+    <t>[np.float64(712.323413914918), np.float64(513.6034994973597)]</t>
+  </si>
+  <si>
+    <t>[np.float64(696.7375169300423), np.float64(486.9605625324016)]</t>
+  </si>
+  <si>
+    <t>[np.float64(431.39427171857926), np.float64(-270.2692340330623)]</t>
+  </si>
+  <si>
+    <t>[np.float64(948.6707375489879), np.float64(98.89588320907615)]</t>
+  </si>
+  <si>
+    <t>[np.float64(678.854925588889), np.float64(384.6919938344838)]</t>
+  </si>
+  <si>
+    <t>[np.float64(434.20028126293084), np.float64(216.00811390437525)]</t>
+  </si>
+  <si>
+    <t>[np.float64(570.0089765094694), np.float64(92.83956396166764)]</t>
+  </si>
+  <si>
+    <t>[np.float64(241.8602237714561), np.float64(-186.8047697131111)]</t>
+  </si>
+  <si>
+    <t>[np.float64(259.3419481149216), np.float64(-532.6983920562361)]</t>
+  </si>
+  <si>
+    <t>[np.float64(614.5792250114329), np.float64(-423.1183074333593)]</t>
+  </si>
+  <si>
+    <t>[np.float64(509.4378332112447), np.float64(-499.4342986978953)]</t>
+  </si>
+  <si>
+    <t>[np.float64(741.7008400601072), np.float64(192.82193145536235)]</t>
+  </si>
+  <si>
+    <t>[np.float64(524.0739948600018), np.float64(430.286217044953)]</t>
+  </si>
+  <si>
+    <t>[np.float64(863.4826268366392), np.float64(533.673161637324)]</t>
+  </si>
+  <si>
+    <t>[np.float64(993.1962873646097), np.float64(150.27821415663948)]</t>
+  </si>
+  <si>
+    <t>[np.float64(283.79628352106346), np.float64(118.5281590659257)]</t>
+  </si>
+  <si>
+    <t>[np.float64(261.3552505143696), np.float64(397.4264848172893)]</t>
+  </si>
+  <si>
+    <t>[np.float64(696.5797640467019), np.float64(-547.9793535530617)]</t>
+  </si>
+  <si>
+    <t>[np.float64(526.140879206703), np.float64(-407.0554524869237)]</t>
+  </si>
+  <si>
+    <t>[np.float64(883.816807268144), np.float64(-152.29026372637497)]</t>
+  </si>
+  <si>
+    <t>[np.float64(889.4107068822619), np.float64(-534.1740578705828)]</t>
+  </si>
+  <si>
+    <t>[np.float64(631.5828946489252), np.float64(286.74326201792314)]</t>
+  </si>
+  <si>
+    <t>[np.float64(456.93198718019545), np.float64(-132.9802967905996)]</t>
+  </si>
+  <si>
+    <t>[np.float64(694.2020138318653), np.float64(10.39301514985766)]</t>
+  </si>
+  <si>
+    <t>[np.float64(52.42420468375919), np.float64(517.4668697620407)]</t>
+  </si>
+  <si>
+    <t>[np.float64(508.0912539384211), np.float64(93.59628808042066)]</t>
+  </si>
+  <si>
+    <t>[np.float64(363.08337029952185), np.float64(511.5496722313044)]</t>
+  </si>
+  <si>
+    <t>[np.float64(220.67290467919264), np.float64(-407.25652521244876)]</t>
+  </si>
+  <si>
+    <t>[np.float64(814.7854897538401), np.float64(555.8337519581646)]</t>
+  </si>
+  <si>
+    <t>[np.float64(201.04807615999476), np.float64(192.81473571328945)]</t>
+  </si>
+  <si>
+    <t>[np.float64(397.9998214816739), np.float64(-86.35945871544197)]</t>
+  </si>
+  <si>
+    <t>[np.float64(200.27799373639732), np.float64(241.91956896292265)]</t>
+  </si>
+  <si>
+    <t>[np.float64(292.39196816217407), np.float64(578.7674699391373)]</t>
+  </si>
+  <si>
+    <t>[np.float64(745.289793232335), np.float64(-358.5223358682557)]</t>
+  </si>
+  <si>
+    <t>[np.float64(150.326140676436), np.float64(256.7806592210702)]</t>
+  </si>
+  <si>
+    <t>[np.float64(928.8842486621654), np.float64(343.99162310595966)]</t>
+  </si>
+  <si>
+    <t>[np.float64(187.99771032435132), np.float64(-92.3441060052603)]</t>
+  </si>
+  <si>
+    <t>[np.float64(225.2663300423041), np.float64(196.87694822987726)]</t>
+  </si>
+  <si>
+    <t>[np.float64(802.7473753748001), np.float64(359.76934634556176)]</t>
+  </si>
+  <si>
+    <t>[np.float64(493.98085710757675), np.float64(108.1386784878249)]</t>
+  </si>
+  <si>
+    <t>[np.float64(337.74824349289366), np.float64(-156.0160940443667)]</t>
+  </si>
+  <si>
+    <t>[np.float64(667.4801443764529), np.float64(-501.9792175886932)]</t>
+  </si>
+  <si>
+    <t>[np.float64(830.9471364704948), np.float64(149.4657458211251)]</t>
+  </si>
+  <si>
+    <t>[np.float64(930.7850062375654), np.float64(261.5468137169172)]</t>
+  </si>
+  <si>
+    <t>[np.float64(866.9751331088404), np.float64(367.20521429907876)]</t>
+  </si>
+  <si>
+    <t>[np.float64(15.62257251054), np.float64(3.5602678290931635)]</t>
+  </si>
+  <si>
+    <t>[np.float64(508.95343345051936), np.float64(81.1204076334443)]</t>
+  </si>
+  <si>
+    <t>[np.float64(89.11005297877372), np.float64(-53.1664752734481)]</t>
+  </si>
+  <si>
+    <t>[np.float64(169.8103702793804), np.float64(331.5437778029975)]</t>
+  </si>
+  <si>
+    <t>[np.float64(386.7323892458543), np.float64(121.09938602909199)]</t>
+  </si>
+  <si>
+    <t>[np.float64(341.6356361369767), np.float64(-425.1547970605052)]</t>
+  </si>
+  <si>
+    <t>[np.float64(619.7426305216503), np.float64(256.4684004295783)]</t>
+  </si>
+  <si>
+    <t>[np.float64(642.4986459199968), np.float64(-411.93771201642505)]</t>
+  </si>
+  <si>
+    <t>[np.float64(221.9483227389798), np.float64(257.2898595550015)]</t>
+  </si>
+  <si>
+    <t>[np.float64(561.4950636675038), np.float64(-55.08316212188254)]</t>
+  </si>
+  <si>
+    <t>[np.float64(300.6960694098374), np.float64(-132.3878155150523)]</t>
+  </si>
+  <si>
+    <t>[np.float64(790.1194278259005), np.float64(-339.8845644033425)]</t>
+  </si>
+  <si>
+    <t>[np.float64(900.7053808897239), np.float64(-331.7535584247289)]</t>
+  </si>
+  <si>
+    <t>[np.float64(399.0460473745742), np.float64(395.0940584674488)]</t>
+  </si>
+  <si>
+    <t>[np.float64(838.7061635355208), np.float64(-153.20410523430763)]</t>
+  </si>
+  <si>
+    <t>[np.float64(651.5354138059496), np.float64(415.59504763485916)]</t>
+  </si>
+  <si>
+    <t>[np.float64(465.88566383828766), np.float64(-462.8492836633757)]</t>
+  </si>
+  <si>
+    <t>[np.float64(653.1761981329661), np.float64(90.90724243174941)]</t>
+  </si>
+  <si>
+    <t>[np.float64(50.85139195048127), np.float64(35.03654759410426)]</t>
+  </si>
+  <si>
+    <t>[np.float64(976.361840919758), np.float64(-164.39222829581593)]</t>
+  </si>
+  <si>
+    <t>[np.float64(230.71131253635392), np.float64(173.02000170475492)]</t>
+  </si>
+  <si>
+    <t>[np.float64(134.9896233404575), np.float64(398.76418707083906)]</t>
+  </si>
+  <si>
+    <t>[np.float64(572.4531550476262), np.float64(-391.47827812759766)]</t>
+  </si>
+  <si>
+    <t>[np.float64(907.5276808571431), np.float64(-501.96944871533816)]</t>
+  </si>
+  <si>
+    <t>[np.float64(662.9857527765718), np.float64(94.13177390556223)]</t>
+  </si>
+  <si>
+    <t>[np.float64(692.997785029182), np.float64(332.26549996580445)]</t>
+  </si>
+  <si>
+    <t>[np.float64(381.5924603587628), np.float64(152.9358653057849)]</t>
+  </si>
+  <si>
+    <t>[np.float64(340.2944220254537), np.float64(398.1981651158104)]</t>
+  </si>
+  <si>
+    <t>[np.float64(661.9650568351917), np.float64(506.0270779180878)]</t>
+  </si>
+  <si>
+    <t>[np.float64(223.6951422273915), np.float64(381.7542548651056)]</t>
+  </si>
+  <si>
+    <t>[np.float64(479.29689346500857), np.float64(290.32137186130194)]</t>
+  </si>
+  <si>
+    <t>[np.float64(303.4951814843018), np.float64(304.39400892973936)]</t>
+  </si>
+  <si>
+    <t>[np.float64(286.8992026400663), np.float64(-545.0376572844929)]</t>
+  </si>
+  <si>
+    <t>[np.float64(500.6467074775497), np.float64(-518.0845606223032)]</t>
+  </si>
+  <si>
+    <t>[np.float64(943.1024333249151), np.float64(-165.96037940266712)]</t>
+  </si>
+  <si>
+    <t>[np.float64(84.79091563826002), np.float64(537.6370514382795)]</t>
+  </si>
+  <si>
+    <t>[np.float64(280.62364029134113), np.float64(-221.09653817828632)]</t>
+  </si>
+  <si>
+    <t>[np.float64(691.3518585461292), np.float64(327.2399316595738)]</t>
+  </si>
+  <si>
+    <t>[np.float64(347.91520488274153), np.float64(451.48727276787076)]</t>
+  </si>
+  <si>
+    <t>[np.float64(619.5274519760125), np.float64(-393.86494122334057)]</t>
+  </si>
+  <si>
+    <t>[np.float64(923.4696837080037), np.float64(464.545547974644)]</t>
+  </si>
+  <si>
+    <t>[np.float64(143.5552177825924), np.float64(-453.8935651555712)]</t>
+  </si>
+  <si>
+    <t>[np.float64(234.33861752809148), np.float64(457.70232799162886)]</t>
+  </si>
+  <si>
+    <t>[np.float64(999.4480521958579), np.float64(-134.34840780348196)]</t>
+  </si>
+  <si>
+    <t>[np.float64(695.7600549382835), np.float64(-508.5872564067859)]</t>
+  </si>
+  <si>
+    <t>[np.float64(419.05181733299037), np.float64(-363.2194677208251)]</t>
+  </si>
+  <si>
+    <t>[np.float64(279.4207033965117), np.float64(-2.4400441524838925)]</t>
+  </si>
+  <si>
+    <t>[np.float64(445.96492883849413), np.float64(580.5736898507489)]</t>
+  </si>
+  <si>
+    <t>[np.float64(42.64676792607236), np.float64(525.0605242918493)]</t>
+  </si>
+  <si>
+    <t>[np.float64(178.81634836523043), np.float64(-208.3465521724234)]</t>
+  </si>
+  <si>
+    <t>[np.float64(388.22409112677656), np.float64(441.6708120586045)]</t>
+  </si>
+  <si>
+    <t>[np.float64(487.51818927448585), np.float64(-357.4202439553601)]</t>
+  </si>
+  <si>
+    <t>[np.float64(972.5204325822779), np.float64(-505.1727330250324)]</t>
+  </si>
+  <si>
+    <t>[np.float64(768.4056693044613), np.float64(-383.5506952416093)]</t>
+  </si>
+  <si>
+    <t>[np.float64(630.2556169901363), np.float64(559.7883859650578)]</t>
+  </si>
+  <si>
+    <t>[np.float64(316.232708034652), np.float64(-378.1838823583427)]</t>
+  </si>
+  <si>
+    <t>[np.float64(254.63577290469829), np.float64(242.25852774050713)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.10462947605216488), np.float64(49.72772159877172)]</t>
+  </si>
+  <si>
+    <t>[np.float64(434.49819915580304), np.float64(64.14089400242813)]</t>
+  </si>
+  <si>
+    <t>[np.float64(856.8816249495046), np.float64(-266.41081637387856)]</t>
+  </si>
+  <si>
+    <t>[np.float64(883.813311347993), np.float64(-383.0736404586047)]</t>
+  </si>
+  <si>
+    <t>[np.float64(240.68385898943677), np.float64(334.42377074696446)]</t>
+  </si>
+  <si>
+    <t>[np.float64(330.0895841460839), np.float64(-223.68039364857975)]</t>
+  </si>
+  <si>
+    <t>[np.float64(644.9578746233767), np.float64(-580.7636261007169)]</t>
+  </si>
+  <si>
+    <t>[np.float64(314.6939069381148), np.float64(521.0161485522535)]</t>
+  </si>
+  <si>
+    <t>[np.float64(979.0200431464243), np.float64(-573.8851249961119)]</t>
+  </si>
+  <si>
+    <t>[np.float64(301.56013646910617), np.float64(-114.7448342157536)]</t>
+  </si>
+  <si>
+    <t>[np.float64(863.0673124300577), np.float64(-489.81338444122827)]</t>
+  </si>
+  <si>
+    <t>[np.float64(680.7631321110841), np.float64(432.8765970551335)]</t>
+  </si>
+  <si>
+    <t>[np.float64(744.1734100719563), np.float64(421.62057774895607)]</t>
+  </si>
+  <si>
+    <t>[np.float64(558.8020776819494), np.float64(-350.7611949669595)]</t>
+  </si>
+  <si>
+    <t>[np.float64(471.8696092436424), np.float64(276.9080396408268)]</t>
+  </si>
+  <si>
+    <t>[np.float64(323.09038169512837), np.float64(-268.2712929232998)]</t>
+  </si>
+  <si>
+    <t>[np.float64(250.48169281590305), np.float64(372.841892301797)]</t>
+  </si>
+  <si>
+    <t>[np.float64(987.4704105486879), np.float64(-553.7950921427349)]</t>
+  </si>
+  <si>
+    <t>[np.float64(930.5326757964882), np.float64(-223.33806908852722)]</t>
+  </si>
+  <si>
+    <t>[np.float64(809.2207065837875), np.float64(-526.9994249731483)]</t>
+  </si>
+  <si>
+    <t>[np.float64(946.5250513579972), np.float64(-351.1195660278637)]</t>
+  </si>
+  <si>
+    <t>[np.float64(958.8356738460433), np.float64(365.7152448634962)]</t>
+  </si>
+  <si>
+    <t>[np.float64(225.42106008131267), np.float64(185.6919727826804)]</t>
+  </si>
+  <si>
+    <t>[np.float64(782.0925973363343), np.float64(536.7028050106087)]</t>
+  </si>
+  <si>
+    <t>[np.float64(876.2072860435984), np.float64(2.5855708975985863)]</t>
+  </si>
+  <si>
+    <t>[np.float64(64.54764882936348), np.float64(557.216755934943)]</t>
+  </si>
+  <si>
+    <t>[np.float64(613.933265151042), np.float64(535.375175928157)]</t>
+  </si>
+  <si>
+    <t>[np.float64(699.6315629765755), np.float64(498.6084705540013)]</t>
+  </si>
+  <si>
+    <t>[np.float64(648.5507916251217), np.float64(-474.3701904819512)]</t>
+  </si>
+  <si>
+    <t>[np.float64(363.93026776683854), np.float64(575.908615572652)]</t>
+  </si>
+  <si>
+    <t>[np.float64(814.3767622793073), np.float64(-70.94505584653211)]</t>
+  </si>
+  <si>
+    <t>[np.float64(453.62932826624933), np.float64(182.00349187822758)]</t>
+  </si>
+  <si>
+    <t>[np.float64(987.1675247333733), np.float64(-598.516926489431)]</t>
+  </si>
+  <si>
+    <t>[np.float64(278.96421339518685), np.float64(306.20653431934534)]</t>
+  </si>
+  <si>
+    <t>[np.float64(924.1480830664975), np.float64(-210.12302365584787)]</t>
+  </si>
+  <si>
+    <t>[np.float64(537.0060309468325), np.float64(53.888846417342734)]</t>
+  </si>
+  <si>
+    <t>[np.float64(550.036921238473), np.float64(287.52757003334705)]</t>
+  </si>
+  <si>
+    <t>[np.float64(742.3926624797124), np.float64(78.23070215859866)]</t>
+  </si>
+  <si>
+    <t>[np.float64(485.4578137683837), np.float64(-425.2203679785962)]</t>
+  </si>
+  <si>
+    <t>[np.float64(924.6236156316123), np.float64(-473.5798089214058)]</t>
+  </si>
+  <si>
+    <t>[np.float64(250.48389509256853), np.float64(-397.23488150035325)]</t>
+  </si>
+  <si>
+    <t>[np.float64(895.8534123565253), np.float64(51.19933248081804)]</t>
+  </si>
+  <si>
+    <t>[np.float64(123.38068867713359), np.float64(-60.35122703185846)]</t>
+  </si>
+  <si>
+    <t>[np.float64(877.7315485595819), np.float64(-244.63080732323976)]</t>
+  </si>
+  <si>
+    <t>[np.float64(683.1453380867817), np.float64(-498.49668468377513)]</t>
+  </si>
+  <si>
+    <t>[np.float64(347.0805421927571), np.float64(-402.3222282529369)]</t>
+  </si>
+  <si>
+    <t>[np.float64(167.67060838780367), np.float64(80.90360638919958)]</t>
+  </si>
+  <si>
+    <t>[np.float64(412.62144757705653), np.float64(-389.58319138071465)]</t>
+  </si>
+  <si>
+    <t>[np.float64(633.5972535921784), np.float64(556.888455791611)]</t>
+  </si>
+  <si>
+    <t>[np.float64(957.1156209314926), np.float64(-461.579051507328)]</t>
+  </si>
+  <si>
+    <t>[np.float64(75.47592023110428), np.float64(246.2339480483945)]</t>
+  </si>
+  <si>
+    <t>[np.float64(896.0945749424918), np.float64(-360.0161329260154)]</t>
+  </si>
+  <si>
+    <t>[np.float64(513.1448722466738), np.float64(-597.7305087312882)]</t>
+  </si>
+  <si>
+    <t>[np.float64(836.6428305569606), np.float64(-92.44973609712395)]</t>
+  </si>
+  <si>
+    <t>[np.float64(459.165375914542), np.float64(-6.761279507111567)]</t>
+  </si>
+  <si>
+    <t>[np.float64(961.2225623595536), np.float64(-506.5824000325357)]</t>
+  </si>
+  <si>
+    <t>[np.float64(16.10009213551877), np.float64(-371.1193013460861)]</t>
+  </si>
+  <si>
+    <t>[np.float64(122.20082415751732), np.float64(-587.2005981936452)]</t>
+  </si>
+  <si>
+    <t>[np.float64(460.73559943611855), np.float64(-189.24045481287573)]</t>
+  </si>
+  <si>
+    <t>[np.float64(453.7614393565789), np.float64(14.822842570461262)]</t>
+  </si>
+  <si>
+    <t>[np.float64(98.12496582410279), np.float64(-593.9601034772412)]</t>
+  </si>
+  <si>
+    <t>[np.float64(166.75180604716567), np.float64(164.26361995561933)]</t>
+  </si>
+  <si>
+    <t>[np.float64(702.9309442855736), np.float64(247.84335146945682)]</t>
+  </si>
+  <si>
+    <t>[np.float64(628.8517874508265), np.float64(-552.4466595409465)]</t>
   </si>
 </sst>
 </file>
@@ -3191,7 +3254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I930"/>
+  <dimension ref="A1:I951"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -24590,6 +24653,489 @@
         <v>939</v>
       </c>
     </row>
+    <row r="931" spans="1:9">
+      <c r="A931" t="s">
+        <v>9</v>
+      </c>
+      <c r="B931">
+        <v>0</v>
+      </c>
+      <c r="D931" t="s">
+        <v>10</v>
+      </c>
+      <c r="E931" t="s">
+        <v>10</v>
+      </c>
+      <c r="F931" t="s">
+        <v>10</v>
+      </c>
+      <c r="H931" t="s">
+        <v>940</v>
+      </c>
+      <c r="I931" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="932" spans="1:9">
+      <c r="A932" t="s">
+        <v>9</v>
+      </c>
+      <c r="B932">
+        <v>0</v>
+      </c>
+      <c r="D932" t="s">
+        <v>10</v>
+      </c>
+      <c r="E932" t="s">
+        <v>10</v>
+      </c>
+      <c r="F932" t="s">
+        <v>10</v>
+      </c>
+      <c r="H932" t="s">
+        <v>941</v>
+      </c>
+      <c r="I932" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="933" spans="1:9">
+      <c r="A933" t="s">
+        <v>9</v>
+      </c>
+      <c r="B933">
+        <v>0</v>
+      </c>
+      <c r="D933" t="s">
+        <v>10</v>
+      </c>
+      <c r="E933" t="s">
+        <v>10</v>
+      </c>
+      <c r="F933" t="s">
+        <v>10</v>
+      </c>
+      <c r="H933" t="s">
+        <v>942</v>
+      </c>
+      <c r="I933" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="934" spans="1:9">
+      <c r="A934" t="s">
+        <v>9</v>
+      </c>
+      <c r="B934">
+        <v>0</v>
+      </c>
+      <c r="D934" t="s">
+        <v>10</v>
+      </c>
+      <c r="E934" t="s">
+        <v>10</v>
+      </c>
+      <c r="F934" t="s">
+        <v>10</v>
+      </c>
+      <c r="H934" t="s">
+        <v>943</v>
+      </c>
+      <c r="I934" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="935" spans="1:9">
+      <c r="A935" t="s">
+        <v>9</v>
+      </c>
+      <c r="B935">
+        <v>0</v>
+      </c>
+      <c r="D935" t="s">
+        <v>10</v>
+      </c>
+      <c r="E935" t="s">
+        <v>10</v>
+      </c>
+      <c r="F935" t="s">
+        <v>10</v>
+      </c>
+      <c r="H935" t="s">
+        <v>944</v>
+      </c>
+      <c r="I935" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="936" spans="1:9">
+      <c r="A936" t="s">
+        <v>9</v>
+      </c>
+      <c r="B936">
+        <v>0</v>
+      </c>
+      <c r="D936" t="s">
+        <v>10</v>
+      </c>
+      <c r="E936" t="s">
+        <v>10</v>
+      </c>
+      <c r="F936" t="s">
+        <v>10</v>
+      </c>
+      <c r="H936" t="s">
+        <v>945</v>
+      </c>
+      <c r="I936" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="937" spans="1:9">
+      <c r="A937" t="s">
+        <v>9</v>
+      </c>
+      <c r="B937">
+        <v>0</v>
+      </c>
+      <c r="D937" t="s">
+        <v>10</v>
+      </c>
+      <c r="E937" t="s">
+        <v>10</v>
+      </c>
+      <c r="F937" t="s">
+        <v>10</v>
+      </c>
+      <c r="H937" t="s">
+        <v>946</v>
+      </c>
+      <c r="I937" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="938" spans="1:9">
+      <c r="A938" t="s">
+        <v>9</v>
+      </c>
+      <c r="B938">
+        <v>0</v>
+      </c>
+      <c r="D938" t="s">
+        <v>10</v>
+      </c>
+      <c r="E938" t="s">
+        <v>10</v>
+      </c>
+      <c r="F938" t="s">
+        <v>10</v>
+      </c>
+      <c r="H938" t="s">
+        <v>947</v>
+      </c>
+      <c r="I938" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="939" spans="1:9">
+      <c r="A939" t="s">
+        <v>9</v>
+      </c>
+      <c r="B939">
+        <v>0</v>
+      </c>
+      <c r="D939" t="s">
+        <v>10</v>
+      </c>
+      <c r="E939" t="s">
+        <v>10</v>
+      </c>
+      <c r="F939" t="s">
+        <v>10</v>
+      </c>
+      <c r="H939" t="s">
+        <v>948</v>
+      </c>
+      <c r="I939" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="940" spans="1:9">
+      <c r="A940" t="s">
+        <v>9</v>
+      </c>
+      <c r="B940">
+        <v>0</v>
+      </c>
+      <c r="D940" t="s">
+        <v>10</v>
+      </c>
+      <c r="E940" t="s">
+        <v>10</v>
+      </c>
+      <c r="F940" t="s">
+        <v>10</v>
+      </c>
+      <c r="H940" t="s">
+        <v>949</v>
+      </c>
+      <c r="I940" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="941" spans="1:9">
+      <c r="A941" t="s">
+        <v>9</v>
+      </c>
+      <c r="B941">
+        <v>0</v>
+      </c>
+      <c r="D941" t="s">
+        <v>10</v>
+      </c>
+      <c r="E941" t="s">
+        <v>10</v>
+      </c>
+      <c r="F941" t="s">
+        <v>10</v>
+      </c>
+      <c r="H941" t="s">
+        <v>950</v>
+      </c>
+      <c r="I941" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="942" spans="1:9">
+      <c r="A942" t="s">
+        <v>9</v>
+      </c>
+      <c r="B942">
+        <v>0</v>
+      </c>
+      <c r="D942" t="s">
+        <v>10</v>
+      </c>
+      <c r="E942" t="s">
+        <v>10</v>
+      </c>
+      <c r="F942" t="s">
+        <v>10</v>
+      </c>
+      <c r="H942" t="s">
+        <v>951</v>
+      </c>
+      <c r="I942" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="943" spans="1:9">
+      <c r="A943" t="s">
+        <v>9</v>
+      </c>
+      <c r="B943">
+        <v>0</v>
+      </c>
+      <c r="D943" t="s">
+        <v>10</v>
+      </c>
+      <c r="E943" t="s">
+        <v>10</v>
+      </c>
+      <c r="F943" t="s">
+        <v>10</v>
+      </c>
+      <c r="H943" t="s">
+        <v>952</v>
+      </c>
+      <c r="I943" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="944" spans="1:9">
+      <c r="A944" t="s">
+        <v>9</v>
+      </c>
+      <c r="B944">
+        <v>0</v>
+      </c>
+      <c r="D944" t="s">
+        <v>10</v>
+      </c>
+      <c r="E944" t="s">
+        <v>10</v>
+      </c>
+      <c r="F944" t="s">
+        <v>10</v>
+      </c>
+      <c r="H944" t="s">
+        <v>953</v>
+      </c>
+      <c r="I944" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="945" spans="1:9">
+      <c r="A945" t="s">
+        <v>9</v>
+      </c>
+      <c r="B945">
+        <v>0</v>
+      </c>
+      <c r="D945" t="s">
+        <v>10</v>
+      </c>
+      <c r="E945" t="s">
+        <v>10</v>
+      </c>
+      <c r="F945" t="s">
+        <v>10</v>
+      </c>
+      <c r="H945" t="s">
+        <v>954</v>
+      </c>
+      <c r="I945" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="946" spans="1:9">
+      <c r="A946" t="s">
+        <v>9</v>
+      </c>
+      <c r="B946">
+        <v>0</v>
+      </c>
+      <c r="D946" t="s">
+        <v>10</v>
+      </c>
+      <c r="E946" t="s">
+        <v>10</v>
+      </c>
+      <c r="F946" t="s">
+        <v>10</v>
+      </c>
+      <c r="H946" t="s">
+        <v>955</v>
+      </c>
+      <c r="I946" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="947" spans="1:9">
+      <c r="A947" t="s">
+        <v>9</v>
+      </c>
+      <c r="B947">
+        <v>0</v>
+      </c>
+      <c r="D947" t="s">
+        <v>10</v>
+      </c>
+      <c r="E947" t="s">
+        <v>10</v>
+      </c>
+      <c r="F947" t="s">
+        <v>10</v>
+      </c>
+      <c r="H947" t="s">
+        <v>956</v>
+      </c>
+      <c r="I947" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="948" spans="1:9">
+      <c r="A948" t="s">
+        <v>9</v>
+      </c>
+      <c r="B948">
+        <v>0</v>
+      </c>
+      <c r="D948" t="s">
+        <v>10</v>
+      </c>
+      <c r="E948" t="s">
+        <v>10</v>
+      </c>
+      <c r="F948" t="s">
+        <v>10</v>
+      </c>
+      <c r="H948" t="s">
+        <v>957</v>
+      </c>
+      <c r="I948" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="949" spans="1:9">
+      <c r="A949" t="s">
+        <v>9</v>
+      </c>
+      <c r="B949">
+        <v>0</v>
+      </c>
+      <c r="D949" t="s">
+        <v>10</v>
+      </c>
+      <c r="E949" t="s">
+        <v>10</v>
+      </c>
+      <c r="F949" t="s">
+        <v>10</v>
+      </c>
+      <c r="H949" t="s">
+        <v>958</v>
+      </c>
+      <c r="I949" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="950" spans="1:9">
+      <c r="A950" t="s">
+        <v>9</v>
+      </c>
+      <c r="B950">
+        <v>0</v>
+      </c>
+      <c r="D950" t="s">
+        <v>10</v>
+      </c>
+      <c r="E950" t="s">
+        <v>10</v>
+      </c>
+      <c r="F950" t="s">
+        <v>10</v>
+      </c>
+      <c r="H950" t="s">
+        <v>959</v>
+      </c>
+      <c r="I950" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="951" spans="1:9">
+      <c r="A951" t="s">
+        <v>9</v>
+      </c>
+      <c r="B951">
+        <v>0</v>
+      </c>
+      <c r="D951" t="s">
+        <v>10</v>
+      </c>
+      <c r="E951" t="s">
+        <v>10</v>
+      </c>
+      <c r="F951" t="s">
+        <v>10</v>
+      </c>
+      <c r="H951" t="s">
+        <v>960</v>
+      </c>
+      <c r="I951" t="s">
+        <v>960</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Data/output/IND Stroke Position.xlsx
+++ b/Data/output/IND Stroke Position.xlsx
@@ -49,2854 +49,2854 @@
     <t>nan</t>
   </si>
   <si>
-    <t>[np.float64(931.2519084802718), np.float64(-288.4440492734075)]</t>
-  </si>
-  <si>
-    <t>[np.float64(302.25052577237955), np.float64(523.8873751036115)]</t>
-  </si>
-  <si>
-    <t>[np.float64(864.9752141885864), np.float64(548.8857783688325)]</t>
-  </si>
-  <si>
-    <t>[np.float64(457.2540942068966), np.float64(249.13977306157403)]</t>
-  </si>
-  <si>
-    <t>[np.float64(245.2977211079147), np.float64(-181.14059042797146)]</t>
-  </si>
-  <si>
-    <t>[np.float64(633.8613350392184), np.float64(572.3131259313036)]</t>
-  </si>
-  <si>
-    <t>[np.float64(324.9561724143043), np.float64(-466.3195861426045)]</t>
-  </si>
-  <si>
-    <t>[np.float64(135.04330035279867), np.float64(-78.8343481032291)]</t>
-  </si>
-  <si>
-    <t>[np.float64(978.0079008432675), np.float64(-184.9694036306579)]</t>
-  </si>
-  <si>
-    <t>[np.float64(225.90090021121756), np.float64(-424.58265987450346)]</t>
-  </si>
-  <si>
-    <t>[np.float64(939.4964750454843), np.float64(-3.3455050626386083)]</t>
-  </si>
-  <si>
-    <t>[np.float64(516.218761530275), np.float64(-457.0139693261636)]</t>
-  </si>
-  <si>
-    <t>[np.float64(670.1378091500104), np.float64(360.04875840511784)]</t>
-  </si>
-  <si>
-    <t>[np.float64(889.0230783538842), np.float64(525.9963650818811)]</t>
-  </si>
-  <si>
-    <t>[np.float64(403.925083946541), np.float64(-502.7215036368997)]</t>
-  </si>
-  <si>
-    <t>[np.float64(380.5585637362673), np.float64(243.00897690916088)]</t>
-  </si>
-  <si>
-    <t>[np.float64(826.3858843470084), np.float64(-334.49415308435323)]</t>
-  </si>
-  <si>
-    <t>[np.float64(235.1610857573403), np.float64(350.7139883666272)]</t>
-  </si>
-  <si>
-    <t>[np.float64(972.6143951952989), np.float64(194.00021485863374)]</t>
-  </si>
-  <si>
-    <t>[np.float64(402.3504572775157), np.float64(-139.7641440246186)]</t>
-  </si>
-  <si>
-    <t>[np.float64(494.3171006017334), np.float64(-361.47636880887706)]</t>
-  </si>
-  <si>
-    <t>[np.float64(351.0737922329662), np.float64(553.7855711352565)]</t>
-  </si>
-  <si>
-    <t>[np.float64(41.118485309361354), np.float64(-572.9240595684491)]</t>
-  </si>
-  <si>
-    <t>[np.float64(356.07441180601154), np.float64(38.560297959292825)]</t>
-  </si>
-  <si>
-    <t>[np.float64(236.81601459057822), np.float64(107.9200621835663)]</t>
-  </si>
-  <si>
-    <t>[np.float64(398.05447740341094), np.float64(519.2736986953148)]</t>
-  </si>
-  <si>
-    <t>[np.float64(439.83086157432126), np.float64(-343.00432070599226)]</t>
-  </si>
-  <si>
-    <t>[np.float64(137.59609303713893), np.float64(264.1660035675412)]</t>
-  </si>
-  <si>
-    <t>[np.float64(533.1755978410577), np.float64(416.75092164924763)]</t>
-  </si>
-  <si>
-    <t>[np.float64(786.480987440336), np.float64(343.37825243254804)]</t>
-  </si>
-  <si>
-    <t>[np.float64(408.64533006786394), np.float64(-60.32255382455355)]</t>
-  </si>
-  <si>
-    <t>[np.float64(601.1125300726276), np.float64(146.9803251832102)]</t>
-  </si>
-  <si>
-    <t>[np.float64(424.72476912290756), np.float64(-182.66157922953658)]</t>
-  </si>
-  <si>
-    <t>[np.float64(295.27030988322787), np.float64(-515.5309793705653)]</t>
-  </si>
-  <si>
-    <t>[np.float64(355.5280289147551), np.float64(346.32085050227545)]</t>
-  </si>
-  <si>
-    <t>[np.float64(936.5387685933697), np.float64(-392.14502745371453)]</t>
-  </si>
-  <si>
-    <t>[np.float64(966.0381093152292), np.float64(50.949729332194806)]</t>
-  </si>
-  <si>
-    <t>[np.float64(167.369615131167), np.float64(527.6607910984328)]</t>
-  </si>
-  <si>
-    <t>[np.float64(172.19621003318107), np.float64(-346.12622087975876)]</t>
-  </si>
-  <si>
-    <t>[np.float64(238.39137899414953), np.float64(371.7576385763971)]</t>
-  </si>
-  <si>
-    <t>[np.float64(142.6050616367892), np.float64(94.64938579904685)]</t>
-  </si>
-  <si>
-    <t>[np.float64(298.42214113932295), np.float64(-443.72334946396194)]</t>
-  </si>
-  <si>
-    <t>[np.float64(250.90339209428535), np.float64(110.67698259238989)]</t>
-  </si>
-  <si>
-    <t>[np.float64(952.9967156208156), np.float64(-489.30964824486017)]</t>
-  </si>
-  <si>
-    <t>[np.float64(833.9984437622417), np.float64(-418.3805400281276)]</t>
-  </si>
-  <si>
-    <t>[np.float64(980.2187566829026), np.float64(522.5261985065254)]</t>
-  </si>
-  <si>
-    <t>[np.float64(944.9820822509342), np.float64(79.40780452466163)]</t>
-  </si>
-  <si>
-    <t>[np.float64(689.4222328107293), np.float64(454.13285326997106)]</t>
-  </si>
-  <si>
-    <t>[np.float64(830.6731685417886), np.float64(568.3612293692031)]</t>
-  </si>
-  <si>
-    <t>[np.float64(72.35091557809048), np.float64(264.3783647723908)]</t>
-  </si>
-  <si>
-    <t>[np.float64(196.17680556547035), np.float64(17.329612623629487)]</t>
-  </si>
-  <si>
-    <t>[np.float64(207.33441731790558), np.float64(-294.6852430033743)]</t>
-  </si>
-  <si>
-    <t>[np.float64(305.186722242446), np.float64(-186.88846957032047)]</t>
-  </si>
-  <si>
-    <t>[np.float64(809.8108930106698), np.float64(444.7015479205088)]</t>
-  </si>
-  <si>
-    <t>[np.float64(154.39518692942167), np.float64(410.9857304396221)]</t>
-  </si>
-  <si>
-    <t>[np.float64(576.0033227091311), np.float64(-463.3629550499445)]</t>
-  </si>
-  <si>
-    <t>[np.float64(763.9123278040468), np.float64(128.43883934695998)]</t>
-  </si>
-  <si>
-    <t>[np.float64(8.277095569743874), np.float64(-222.64575345553988)]</t>
-  </si>
-  <si>
-    <t>[np.float64(193.17457519958748), np.float64(-562.8657302372881)]</t>
-  </si>
-  <si>
-    <t>[np.float64(664.1908540907127), np.float64(144.5534889259759)]</t>
-  </si>
-  <si>
-    <t>[np.float64(992.7864932713876), np.float64(-201.25619610689557)]</t>
-  </si>
-  <si>
-    <t>[np.float64(22.83083840541178), np.float64(31.288508879810138)]</t>
-  </si>
-  <si>
-    <t>[np.float64(141.07473019615114), np.float64(-185.84215697292632)]</t>
-  </si>
-  <si>
-    <t>[np.float64(443.07970904850424), np.float64(-278.4142301008743)]</t>
-  </si>
-  <si>
-    <t>[np.float64(336.4201040585182), np.float64(-249.93546645934464)]</t>
-  </si>
-  <si>
-    <t>[np.float64(670.1308032801509), np.float64(58.45018440237072)]</t>
-  </si>
-  <si>
-    <t>[np.float64(492.9937244802648), np.float64(216.47652836878262)]</t>
-  </si>
-  <si>
-    <t>[np.float64(964.0276211243828), np.float64(-422.9552496408264)]</t>
-  </si>
-  <si>
-    <t>[np.float64(83.99410687597909), np.float64(-358.20287417745163)]</t>
-  </si>
-  <si>
-    <t>[np.float64(833.2631699013612), np.float64(242.40345371699277)]</t>
-  </si>
-  <si>
-    <t>[np.float64(58.350779972014436), np.float64(-234.27625108942914)]</t>
-  </si>
-  <si>
-    <t>[np.float64(349.81784616030166), np.float64(593.7369925482742)]</t>
-  </si>
-  <si>
-    <t>[np.float64(271.5716567068017), np.float64(512.6782012756319)]</t>
-  </si>
-  <si>
-    <t>[np.float64(868.1120055778954), np.float64(-375.8361642665625)]</t>
-  </si>
-  <si>
-    <t>[np.float64(690.3861830069031), np.float64(-444.4318746222397)]</t>
-  </si>
-  <si>
-    <t>[np.float64(839.4348029731337), np.float64(249.30564897848012)]</t>
-  </si>
-  <si>
-    <t>[np.float64(417.9885412873745), np.float64(-281.9377973566957)]</t>
-  </si>
-  <si>
-    <t>[np.float64(975.8436137963284), np.float64(-454.7135898100645)]</t>
-  </si>
-  <si>
-    <t>[np.float64(445.99664691428273), np.float64(161.67562434974514)]</t>
-  </si>
-  <si>
-    <t>[np.float64(733.0946183311385), np.float64(-374.42407109615465)]</t>
-  </si>
-  <si>
-    <t>[np.float64(658.4877297392235), np.float64(504.672166408546)]</t>
-  </si>
-  <si>
-    <t>[np.float64(145.91911564654114), np.float64(-494.22163504894695)]</t>
-  </si>
-  <si>
-    <t>[np.float64(823.5988184352187), np.float64(369.02219434138874)]</t>
-  </si>
-  <si>
-    <t>[np.float64(926.3699438339537), np.float64(495.99309002793257)]</t>
-  </si>
-  <si>
-    <t>[np.float64(925.3227172583577), np.float64(284.14770463738125)]</t>
-  </si>
-  <si>
-    <t>[np.float64(143.32745847326157), np.float64(265.36928552909944)]</t>
-  </si>
-  <si>
-    <t>[np.float64(20.661147320808926), np.float64(-215.20336830791194)]</t>
-  </si>
-  <si>
-    <t>[np.float64(659.5776040309706), np.float64(543.6729057696475)]</t>
-  </si>
-  <si>
-    <t>[np.float64(837.6413262033972), np.float64(-260.0602787333419)]</t>
-  </si>
-  <si>
-    <t>[np.float64(375.42630040390367), np.float64(-342.735970914313)]</t>
-  </si>
-  <si>
-    <t>[np.float64(783.8123812876248), np.float64(370.12433895880133)]</t>
-  </si>
-  <si>
-    <t>[np.float64(871.3071578640572), np.float64(238.62639589637195)]</t>
-  </si>
-  <si>
-    <t>[np.float64(720.1486530014076), np.float64(306.3433032670563)]</t>
-  </si>
-  <si>
-    <t>[np.float64(615.1610986546553), np.float64(-132.89233729459954)]</t>
-  </si>
-  <si>
-    <t>[np.float64(327.3335865848017), np.float64(523.7686463525747)]</t>
-  </si>
-  <si>
-    <t>[np.float64(351.0428750170972), np.float64(514.4190683223294)]</t>
-  </si>
-  <si>
-    <t>[np.float64(436.6784867242532), np.float64(-112.01903101839895)]</t>
-  </si>
-  <si>
-    <t>[np.float64(68.94018598206885), np.float64(185.94527266001717)]</t>
-  </si>
-  <si>
-    <t>[np.float64(565.9339954078166), np.float64(-584.461583645543)]</t>
-  </si>
-  <si>
-    <t>[np.float64(110.08394331758198), np.float64(166.38268813841603)]</t>
-  </si>
-  <si>
-    <t>[np.float64(276.27273560335817), np.float64(-386.08454820457735)]</t>
-  </si>
-  <si>
-    <t>[np.float64(853.5689338403683), np.float64(237.636081471097)]</t>
-  </si>
-  <si>
-    <t>[np.float64(392.0246486770873), np.float64(6.615524177688144)]</t>
-  </si>
-  <si>
-    <t>[np.float64(13.820475146184119), np.float64(-320.0164788582571)]</t>
-  </si>
-  <si>
-    <t>[np.float64(496.9940410436029), np.float64(-94.2929176588562)]</t>
-  </si>
-  <si>
-    <t>[np.float64(703.408660837366), np.float64(6.6424563399239105)]</t>
-  </si>
-  <si>
-    <t>[np.float64(565.8221604910009), np.float64(367.59052222696016)]</t>
-  </si>
-  <si>
-    <t>[np.float64(330.0869988654159), np.float64(-96.17905569955758)]</t>
-  </si>
-  <si>
-    <t>[np.float64(570.0620397633071), np.float64(66.21997502376519)]</t>
-  </si>
-  <si>
-    <t>[np.float64(232.0288229173656), np.float64(-449.25807126418647)]</t>
-  </si>
-  <si>
-    <t>[np.float64(445.9269291413423), np.float64(308.1870932773229)]</t>
-  </si>
-  <si>
-    <t>[np.float64(940.5876727294808), np.float64(192.406724386708)]</t>
-  </si>
-  <si>
-    <t>[np.float64(363.5981701070526), np.float64(-345.8342797209653)]</t>
-  </si>
-  <si>
-    <t>[np.float64(341.46591306279385), np.float64(-436.13744055829704)]</t>
-  </si>
-  <si>
-    <t>[np.float64(460.4731453288825), np.float64(124.22538780224329)]</t>
-  </si>
-  <si>
-    <t>[np.float64(160.3824933332243), np.float64(111.20487208456188)]</t>
-  </si>
-  <si>
-    <t>[np.float64(460.9397279620359), np.float64(-530.5011623744097)]</t>
-  </si>
-  <si>
-    <t>[np.float64(701.3775607477215), np.float64(467.99703028355384)]</t>
-  </si>
-  <si>
-    <t>[np.float64(153.51615236074534), np.float64(168.20277626423592)]</t>
-  </si>
-  <si>
-    <t>[np.float64(100.48158573757627), np.float64(-266.36264577603276)]</t>
-  </si>
-  <si>
-    <t>[np.float64(224.38205584273064), np.float64(-516.663463293795)]</t>
-  </si>
-  <si>
-    <t>[np.float64(130.08096224064258), np.float64(-201.89379858983142)]</t>
-  </si>
-  <si>
-    <t>[np.float64(727.9397731848793), np.float64(524.853611923204)]</t>
-  </si>
-  <si>
-    <t>[np.float64(993.5976353714601), np.float64(-272.5957375575628)]</t>
-  </si>
-  <si>
-    <t>[np.float64(131.25359315022033), np.float64(182.61488383551978)]</t>
-  </si>
-  <si>
-    <t>[np.float64(545.6101992529937), np.float64(-282.10638541089065)]</t>
-  </si>
-  <si>
-    <t>[np.float64(535.5457499472051), np.float64(-523.6027409344796)]</t>
-  </si>
-  <si>
-    <t>[np.float64(4.638546256247489), np.float64(-438.1998188484213)]</t>
-  </si>
-  <si>
-    <t>[np.float64(168.7663801681547), np.float64(-528.696403409804)]</t>
-  </si>
-  <si>
-    <t>[np.float64(498.4692268974169), np.float64(223.04583187746357)]</t>
-  </si>
-  <si>
-    <t>[np.float64(592.7607711794067), np.float64(499.14012189761047)]</t>
-  </si>
-  <si>
-    <t>[np.float64(225.29615483018682), np.float64(300.99368358063543)]</t>
-  </si>
-  <si>
-    <t>[np.float64(35.19642955083613), np.float64(-261.47139900469296)]</t>
-  </si>
-  <si>
-    <t>[np.float64(369.22257641661696), np.float64(3.9827795872568004)]</t>
-  </si>
-  <si>
-    <t>[np.float64(484.6095209947078), np.float64(229.65773003887944)]</t>
-  </si>
-  <si>
-    <t>[np.float64(297.30933602456656), np.float64(53.70259144214333)]</t>
-  </si>
-  <si>
-    <t>[np.float64(686.2425663573406), np.float64(-463.68825868860426)]</t>
-  </si>
-  <si>
-    <t>[np.float64(542.7743123566627), np.float64(260.05354933118315)]</t>
-  </si>
-  <si>
-    <t>[np.float64(679.5993826661089), np.float64(-510.2863854900478)]</t>
-  </si>
-  <si>
-    <t>[np.float64(2.135465073522136), np.float64(-120.12603624219872)]</t>
-  </si>
-  <si>
-    <t>[np.float64(356.68829196451725), np.float64(-94.81061406291866)]</t>
-  </si>
-  <si>
-    <t>[np.float64(456.9441745102414), np.float64(41.471594309323336)]</t>
-  </si>
-  <si>
-    <t>[np.float64(140.7741884659698), np.float64(312.18069026766545)]</t>
-  </si>
-  <si>
-    <t>[np.float64(412.0744569287804), np.float64(-557.8113439675119)]</t>
-  </si>
-  <si>
-    <t>[np.float64(757.2094830306053), np.float64(-135.95505056033875)]</t>
-  </si>
-  <si>
-    <t>[np.float64(436.81762327963025), np.float64(-247.3991364781703)]</t>
-  </si>
-  <si>
-    <t>[np.float64(504.40672406801457), np.float64(371.0642026547723)]</t>
-  </si>
-  <si>
-    <t>[np.float64(83.76770717372261), np.float64(440.8095653077198)]</t>
-  </si>
-  <si>
-    <t>[np.float64(410.2129616556647), np.float64(431.730318072867)]</t>
-  </si>
-  <si>
-    <t>[np.float64(205.1985980623061), np.float64(261.27028990366205)]</t>
-  </si>
-  <si>
-    <t>[np.float64(685.1677563067359), np.float64(-95.14816620795227)]</t>
-  </si>
-  <si>
-    <t>[np.float64(613.2164872944971), np.float64(288.25318009302043)]</t>
-  </si>
-  <si>
-    <t>[np.float64(545.9476501686604), np.float64(386.9636277130551)]</t>
-  </si>
-  <si>
-    <t>[np.float64(696.5659757402158), np.float64(32.6872666753078)]</t>
-  </si>
-  <si>
-    <t>[np.float64(4.717470406793267), np.float64(-221.789267350668)]</t>
-  </si>
-  <si>
-    <t>[np.float64(167.13069301543925), np.float64(541.5012788239835)]</t>
-  </si>
-  <si>
-    <t>[np.float64(512.055148746956), np.float64(527.7231653887245)]</t>
-  </si>
-  <si>
-    <t>[np.float64(60.740594405386815), np.float64(177.04675986532277)]</t>
-  </si>
-  <si>
-    <t>[np.float64(627.9004579150882), np.float64(-240.24602396972205)]</t>
-  </si>
-  <si>
-    <t>[np.float64(583.2115125446113), np.float64(583.2733041502927)]</t>
-  </si>
-  <si>
-    <t>[np.float64(87.35176557257208), np.float64(210.32860785382377)]</t>
-  </si>
-  <si>
-    <t>[np.float64(171.5388929896784), np.float64(-174.450870738344)]</t>
-  </si>
-  <si>
-    <t>[np.float64(552.1223721947111), np.float64(-455.4090142723005)]</t>
-  </si>
-  <si>
-    <t>[np.float64(463.53162851876016), np.float64(276.8851490184778)]</t>
-  </si>
-  <si>
-    <t>[np.float64(860.9985915305413), np.float64(412.23964562613276)]</t>
-  </si>
-  <si>
-    <t>[np.float64(435.11651337495096), np.float64(469.1513520740855)]</t>
-  </si>
-  <si>
-    <t>[np.float64(72.05732017550326), np.float64(-278.5013806060559)]</t>
-  </si>
-  <si>
-    <t>[np.float64(633.0461474524326), np.float64(523.2175786488358)]</t>
-  </si>
-  <si>
-    <t>[np.float64(520.2496259397619), np.float64(56.82337988673396)]</t>
-  </si>
-  <si>
-    <t>[np.float64(934.8216992897266), np.float64(237.75825610863217)]</t>
-  </si>
-  <si>
-    <t>[np.float64(942.8662583575907), np.float64(-506.7405220913952)]</t>
-  </si>
-  <si>
-    <t>[np.float64(886.458081682897), np.float64(-79.18687105609831)]</t>
-  </si>
-  <si>
-    <t>[np.float64(640.2309415861794), np.float64(-549.0603023160976)]</t>
-  </si>
-  <si>
-    <t>[np.float64(326.39264510741515), np.float64(540.2298003702247)]</t>
-  </si>
-  <si>
-    <t>[np.float64(20.147321146029242), np.float64(-466.4540829823578)]</t>
-  </si>
-  <si>
-    <t>[np.float64(717.4110213075601), np.float64(243.29494724395113)]</t>
-  </si>
-  <si>
-    <t>[np.float64(110.03988235440687), np.float64(502.8499683189534)]</t>
-  </si>
-  <si>
-    <t>[np.float64(274.6579818515674), np.float64(-320.4515331531252)]</t>
-  </si>
-  <si>
-    <t>[np.float64(498.6607036839147), np.float64(-533.0205535660821)]</t>
-  </si>
-  <si>
-    <t>[np.float64(992.7135175249083), np.float64(-450.78255145407036)]</t>
-  </si>
-  <si>
-    <t>[np.float64(977.6054315719208), np.float64(49.905281092709856)]</t>
-  </si>
-  <si>
-    <t>[np.float64(52.085452421379294), np.float64(-88.65254524721382)]</t>
-  </si>
-  <si>
-    <t>[np.float64(939.0767254981756), np.float64(-6.899973234594995)]</t>
-  </si>
-  <si>
-    <t>[np.float64(350.8163886998075), np.float64(-325.9917213003569)]</t>
-  </si>
-  <si>
-    <t>[np.float64(928.9009164047922), np.float64(-325.96696279048945)]</t>
-  </si>
-  <si>
-    <t>[np.float64(687.0522433802773), np.float64(250.93803469713282)]</t>
-  </si>
-  <si>
-    <t>[np.float64(573.0629165867521), np.float64(589.7022883856866)]</t>
-  </si>
-  <si>
-    <t>[np.float64(350.8786052091296), np.float64(-497.12377688845106)]</t>
-  </si>
-  <si>
-    <t>[np.float64(949.8597487049575), np.float64(248.64159585488267)]</t>
-  </si>
-  <si>
-    <t>[np.float64(256.22700946804), np.float64(283.18626600646553)]</t>
-  </si>
-  <si>
-    <t>[np.float64(403.00048612888315), np.float64(169.50940676682671)]</t>
-  </si>
-  <si>
-    <t>[np.float64(559.5319240898799), np.float64(-173.23328231073617)]</t>
-  </si>
-  <si>
-    <t>[np.float64(935.2011985250758), np.float64(-587.5138431492638)]</t>
-  </si>
-  <si>
-    <t>[np.float64(466.40678655538215), np.float64(468.0658607662292)]</t>
-  </si>
-  <si>
-    <t>[np.float64(368.54335411252316), np.float64(-413.5167358337102)]</t>
-  </si>
-  <si>
-    <t>[np.float64(357.61013989697733), np.float64(514.7082240761933)]</t>
-  </si>
-  <si>
-    <t>[np.float64(985.8856054663692), np.float64(407.05821404707615)]</t>
-  </si>
-  <si>
-    <t>[np.float64(814.8762840160176), np.float64(392.30203383001356)]</t>
-  </si>
-  <si>
-    <t>[np.float64(313.9969576968377), np.float64(-551.6072192621085)]</t>
-  </si>
-  <si>
-    <t>[np.float64(648.8280407859625), np.float64(-247.50453164254577)]</t>
-  </si>
-  <si>
-    <t>[np.float64(687.8106849566318), np.float64(-385.51570011654405)]</t>
-  </si>
-  <si>
-    <t>[np.float64(119.55771833416429), np.float64(254.24532913253108)]</t>
-  </si>
-  <si>
-    <t>[np.float64(610.381451776966), np.float64(-214.30723749998464)]</t>
-  </si>
-  <si>
-    <t>[np.float64(13.222867286976303), np.float64(-191.079197538776)]</t>
-  </si>
-  <si>
-    <t>[np.float64(731.7620041773403), np.float64(-291.8052301805751)]</t>
-  </si>
-  <si>
-    <t>[np.float64(610.5722559239133), np.float64(-165.74489727877773)]</t>
-  </si>
-  <si>
-    <t>[np.float64(98.82930429755189), np.float64(-439.0129756669749)]</t>
-  </si>
-  <si>
-    <t>[np.float64(24.735859037187225), np.float64(-365.6699398139559)]</t>
-  </si>
-  <si>
-    <t>[np.float64(992.7152989966135), np.float64(-148.65706470204663)]</t>
-  </si>
-  <si>
-    <t>[np.float64(385.04085148676694), np.float64(-319.27077354980776)]</t>
-  </si>
-  <si>
-    <t>[np.float64(345.43616570432636), np.float64(376.82582940987777)]</t>
-  </si>
-  <si>
-    <t>[np.float64(668.0285586175735), np.float64(137.26651275703716)]</t>
-  </si>
-  <si>
-    <t>[np.float64(878.7236953118302), np.float64(230.28075632773084)]</t>
-  </si>
-  <si>
-    <t>[np.float64(663.3336243698558), np.float64(455.5980723261548)]</t>
-  </si>
-  <si>
-    <t>[np.float64(334.888394187681), np.float64(278.7704783408951)]</t>
-  </si>
-  <si>
-    <t>[np.float64(189.59325376254566), np.float64(450.7151513770825)]</t>
-  </si>
-  <si>
-    <t>[np.float64(88.84839761962537), np.float64(-278.4447957892069)]</t>
-  </si>
-  <si>
-    <t>[np.float64(982.9648003199741), np.float64(28.693711968551952)]</t>
-  </si>
-  <si>
-    <t>[np.float64(512.107570666644), np.float64(-453.60856068959015)]</t>
-  </si>
-  <si>
-    <t>[np.float64(332.81586737937073), np.float64(-422.3980676187651)]</t>
-  </si>
-  <si>
-    <t>[np.float64(746.3360983799538), np.float64(91.6798204118561)]</t>
-  </si>
-  <si>
-    <t>[np.float64(74.6342995050584), np.float64(185.61669785279094)]</t>
-  </si>
-  <si>
-    <t>[np.float64(562.3375405223248), np.float64(31.616946662413852)]</t>
-  </si>
-  <si>
-    <t>[np.float64(413.041301160192), np.float64(-489.22593980754107)]</t>
-  </si>
-  <si>
-    <t>[np.float64(187.85071367054974), np.float64(-256.612444607007)]</t>
-  </si>
-  <si>
-    <t>[np.float64(609.1846702885499), np.float64(14.220036627968511)]</t>
-  </si>
-  <si>
-    <t>[np.float64(393.57201752042823), np.float64(253.79993320975984)]</t>
-  </si>
-  <si>
-    <t>[np.float64(759.5035221043242), np.float64(-285.86658244351344)]</t>
-  </si>
-  <si>
-    <t>[np.float64(280.68055941500256), np.float64(204.83226843678221)]</t>
-  </si>
-  <si>
-    <t>[np.float64(999.1568175989997), np.float64(-28.348803450444052)]</t>
-  </si>
-  <si>
-    <t>[np.float64(567.4716820067142), np.float64(560.3401539552815)]</t>
-  </si>
-  <si>
-    <t>[np.float64(950.1435782790887), np.float64(488.27028665063654)]</t>
-  </si>
-  <si>
-    <t>[np.float64(905.7907787155686), np.float64(-452.89710788466994)]</t>
-  </si>
-  <si>
-    <t>[np.float64(602.9592138014372), np.float64(417.00925673831273)]</t>
-  </si>
-  <si>
-    <t>[np.float64(767.4392967865243), np.float64(-104.98209440244193)]</t>
-  </si>
-  <si>
-    <t>[np.float64(616.4690769765764), np.float64(91.80932584076174)]</t>
-  </si>
-  <si>
-    <t>[np.float64(696.4074980313686), np.float64(-348.8429763953332)]</t>
-  </si>
-  <si>
-    <t>[np.float64(479.47670237130677), np.float64(62.731071677528575)]</t>
-  </si>
-  <si>
-    <t>[np.float64(471.08614411754223), np.float64(298.18969302931816)]</t>
-  </si>
-  <si>
-    <t>[np.float64(45.723693357087704), np.float64(346.40940400366196)]</t>
-  </si>
-  <si>
-    <t>[np.float64(14.856174641483367), np.float64(-377.06961001047773)]</t>
-  </si>
-  <si>
-    <t>[np.float64(483.0568904054701), np.float64(117.66195248587144)]</t>
-  </si>
-  <si>
-    <t>[np.float64(615.7761485030644), np.float64(-114.77567844191424)]</t>
-  </si>
-  <si>
-    <t>[np.float64(685.124402477457), np.float64(-338.3323526983305)]</t>
-  </si>
-  <si>
-    <t>[np.float64(518.0644366765289), np.float64(-103.62930428205726)]</t>
-  </si>
-  <si>
-    <t>[np.float64(806.9271247393755), np.float64(230.65205816341177)]</t>
-  </si>
-  <si>
-    <t>[np.float64(644.0571301345019), np.float64(263.28038620821667)]</t>
-  </si>
-  <si>
-    <t>[np.float64(885.099422096345), np.float64(496.9537903211851)]</t>
-  </si>
-  <si>
-    <t>[np.float64(491.0909122623248), np.float64(389.51619863337896)]</t>
-  </si>
-  <si>
-    <t>[np.float64(969.9821555942104), np.float64(-448.04548865665447)]</t>
-  </si>
-  <si>
-    <t>[np.float64(40.435490842354646), np.float64(200.32809981378864)]</t>
-  </si>
-  <si>
-    <t>[np.float64(43.37025195639954), np.float64(182.58725272120978)]</t>
-  </si>
-  <si>
-    <t>[np.float64(825.6634062317336), np.float64(523.5345422628868)]</t>
-  </si>
-  <si>
-    <t>[np.float64(614.0457106809234), np.float64(449.0955148202904)]</t>
-  </si>
-  <si>
-    <t>[np.float64(848.6370449447766), np.float64(-257.1194721347178)]</t>
-  </si>
-  <si>
-    <t>[np.float64(841.8807435026813), np.float64(135.29173743835577)]</t>
-  </si>
-  <si>
-    <t>[np.float64(310.4308447946178), np.float64(-561.1524869687095)]</t>
-  </si>
-  <si>
-    <t>[np.float64(986.7590757170235), np.float64(-412.15329193640264)]</t>
-  </si>
-  <si>
-    <t>[np.float64(550.2461775753475), np.float64(407.599688904676)]</t>
-  </si>
-  <si>
-    <t>[np.float64(50.10141138624613), np.float64(-291.3167720433314)]</t>
-  </si>
-  <si>
-    <t>[np.float64(111.64296498687033), np.float64(37.33375203182993)]</t>
-  </si>
-  <si>
-    <t>[np.float64(100.22906410411869), np.float64(-440.5998835893165)]</t>
-  </si>
-  <si>
-    <t>[np.float64(839.7366625980628), np.float64(338.0425107009187)]</t>
-  </si>
-  <si>
-    <t>[np.float64(443.594670794607), np.float64(564.6305099333745)]</t>
-  </si>
-  <si>
-    <t>[np.float64(252.4101369293924), np.float64(-82.98790819940814)]</t>
-  </si>
-  <si>
-    <t>[np.float64(37.55931111548361), np.float64(-427.5273395919019)]</t>
-  </si>
-  <si>
-    <t>[np.float64(972.2169105619009), np.float64(537.3021157764254)]</t>
-  </si>
-  <si>
-    <t>[np.float64(90.88333417339211), np.float64(-221.97275410968535)]</t>
-  </si>
-  <si>
-    <t>[np.float64(60.41558444026074), np.float64(-514.980895651453)]</t>
-  </si>
-  <si>
-    <t>[np.float64(284.53905591939156), np.float64(-533.8919666345307)]</t>
-  </si>
-  <si>
-    <t>[np.float64(444.6576360644241), np.float64(460.39793305358717)]</t>
-  </si>
-  <si>
-    <t>[np.float64(519.548590951873), np.float64(-347.15862948258655)]</t>
-  </si>
-  <si>
-    <t>[np.float64(591.2146728954607), np.float64(-567.6376880895086)]</t>
-  </si>
-  <si>
-    <t>[np.float64(53.02483145662728), np.float64(218.81963864800707)]</t>
-  </si>
-  <si>
-    <t>[np.float64(120.4761183405818), np.float64(-508.6126045045054)]</t>
-  </si>
-  <si>
-    <t>[np.float64(237.6334885599265), np.float64(297.17709414842716)]</t>
-  </si>
-  <si>
-    <t>[np.float64(725.8483172140682), np.float64(92.55769800640849)]</t>
-  </si>
-  <si>
-    <t>[np.float64(98.52337370195308), np.float64(267.32928550835925)]</t>
-  </si>
-  <si>
-    <t>[np.float64(846.2721588734775), np.float64(563.4947677925188)]</t>
-  </si>
-  <si>
-    <t>[np.float64(728.1054423370372), np.float64(-473.0570712196757)]</t>
-  </si>
-  <si>
-    <t>[np.float64(982.7860833342111), np.float64(97.04215376531204)]</t>
-  </si>
-  <si>
-    <t>[np.float64(10.085573742943943), np.float64(478.303410788905)]</t>
-  </si>
-  <si>
-    <t>[np.float64(505.0820955198676), np.float64(136.5760440347841)]</t>
-  </si>
-  <si>
-    <t>[np.float64(544.8689827061721), np.float64(523.4909958431838)]</t>
-  </si>
-  <si>
-    <t>[np.float64(7.3488908000448605), np.float64(-149.88493928657027)]</t>
-  </si>
-  <si>
-    <t>[np.float64(543.9164398079713), np.float64(-456.75359466384845)]</t>
-  </si>
-  <si>
-    <t>[np.float64(592.4147091514521), np.float64(514.3064785935974)]</t>
-  </si>
-  <si>
-    <t>[np.float64(969.3873223250998), np.float64(-292.0034682318767)]</t>
-  </si>
-  <si>
-    <t>[np.float64(851.9408242555243), np.float64(-318.0742634800945)]</t>
-  </si>
-  <si>
-    <t>[np.float64(975.9610864342579), np.float64(-386.69792747101496)]</t>
-  </si>
-  <si>
-    <t>[np.float64(60.826004350358346), np.float64(419.3348670071164)]</t>
-  </si>
-  <si>
-    <t>[np.float64(78.57184882733715), np.float64(-343.17839555838594)]</t>
-  </si>
-  <si>
-    <t>[np.float64(106.15107135047708), np.float64(-92.76594551570167)]</t>
-  </si>
-  <si>
-    <t>[np.float64(177.24749286000176), np.float64(198.79120983070266)]</t>
-  </si>
-  <si>
-    <t>[np.float64(801.1251971559883), np.float64(321.8977599836171)]</t>
-  </si>
-  <si>
-    <t>[np.float64(542.2457923918175), np.float64(-527.6531815165426)]</t>
-  </si>
-  <si>
-    <t>[np.float64(65.0605654488099), np.float64(-424.5523880762055)]</t>
-  </si>
-  <si>
-    <t>[np.float64(228.80911326921228), np.float64(-357.50798661006655)]</t>
-  </si>
-  <si>
-    <t>[np.float64(335.99644832337736), np.float64(-57.63357952154183)]</t>
-  </si>
-  <si>
-    <t>[np.float64(537.8015784476881), np.float64(-584.4370684403235)]</t>
-  </si>
-  <si>
-    <t>[np.float64(435.298063559745), np.float64(587.021413259936)]</t>
-  </si>
-  <si>
-    <t>[np.float64(299.9211817284547), np.float64(189.75505006551293)]</t>
-  </si>
-  <si>
-    <t>[np.float64(162.9295904610073), np.float64(357.0064568870972)]</t>
-  </si>
-  <si>
-    <t>[np.float64(431.07291716303354), np.float64(-138.53468400232975)]</t>
-  </si>
-  <si>
-    <t>[np.float64(885.1899872298172), np.float64(245.27182319778194)]</t>
-  </si>
-  <si>
-    <t>[np.float64(776.7418871223531), np.float64(30.485087131778073)]</t>
-  </si>
-  <si>
-    <t>[np.float64(330.4028529580275), np.float64(179.08439364642618)]</t>
-  </si>
-  <si>
-    <t>[np.float64(651.9900925345427), np.float64(-76.35442648642118)]</t>
-  </si>
-  <si>
-    <t>[np.float64(625.2837536603148), np.float64(-510.0085575193047)]</t>
-  </si>
-  <si>
-    <t>[np.float64(132.0138752193384), np.float64(-552.1215522686269)]</t>
-  </si>
-  <si>
-    <t>[np.float64(942.0155687711895), np.float64(-77.87021993111534)]</t>
-  </si>
-  <si>
-    <t>[np.float64(579.5632868615627), np.float64(273.31110045866285)]</t>
-  </si>
-  <si>
-    <t>[np.float64(936.9267267114899), np.float64(-570.923740299295)]</t>
-  </si>
-  <si>
-    <t>[np.float64(246.1805269174644), np.float64(-508.4008557221222)]</t>
-  </si>
-  <si>
-    <t>[np.float64(458.59798670439875), np.float64(26.410318526055903)]</t>
-  </si>
-  <si>
-    <t>[np.float64(161.03075250285082), np.float64(-215.8558939946858)]</t>
-  </si>
-  <si>
-    <t>[np.float64(975.5538743595766), np.float64(-517.9320528747011)]</t>
-  </si>
-  <si>
-    <t>[np.float64(729.584959999488), np.float64(-335.1312948739525)]</t>
-  </si>
-  <si>
-    <t>[np.float64(408.33476794275015), np.float64(162.70157365002285)]</t>
-  </si>
-  <si>
-    <t>[np.float64(926.6686711559892), np.float64(421.5659722461378)]</t>
-  </si>
-  <si>
-    <t>[np.float64(889.385946928445), np.float64(496.12675220512415)]</t>
-  </si>
-  <si>
-    <t>[np.float64(624.3762675501977), np.float64(496.2276762763461)]</t>
-  </si>
-  <si>
-    <t>[np.float64(36.128248294869934), np.float64(-224.72941689460322)]</t>
-  </si>
-  <si>
-    <t>[np.float64(398.08259162218707), np.float64(526.5518504522897)]</t>
-  </si>
-  <si>
-    <t>[np.float64(22.343621599479), np.float64(521.9982837537477)]</t>
-  </si>
-  <si>
-    <t>[np.float64(177.65967126642823), np.float64(377.99185451541564)]</t>
-  </si>
-  <si>
-    <t>[np.float64(701.3385964413944), np.float64(-478.3529564130947)]</t>
-  </si>
-  <si>
-    <t>[np.float64(263.14477191794884), np.float64(194.43881250123673)]</t>
-  </si>
-  <si>
-    <t>[np.float64(478.07603032179213), np.float64(250.86412062408897)]</t>
-  </si>
-  <si>
-    <t>[np.float64(984.5827451175097), np.float64(-215.83492297339734)]</t>
-  </si>
-  <si>
-    <t>[np.float64(431.3444719841601), np.float64(349.1071135177184)]</t>
-  </si>
-  <si>
-    <t>[np.float64(237.37747565043543), np.float64(-468.741673906536)]</t>
-  </si>
-  <si>
-    <t>[np.float64(510.17273973286314), np.float64(420.96387323822444)]</t>
-  </si>
-  <si>
-    <t>[np.float64(763.6808950720795), np.float64(-581.047447455577)]</t>
-  </si>
-  <si>
-    <t>[np.float64(520.4871773887128), np.float64(-427.23055489083333)]</t>
-  </si>
-  <si>
-    <t>[np.float64(849.1364107685165), np.float64(516.5380986782698)]</t>
-  </si>
-  <si>
-    <t>[np.float64(866.6258839597716), np.float64(400.9828331002153)]</t>
-  </si>
-  <si>
-    <t>[np.float64(610.3762475322798), np.float64(174.8238496928767)]</t>
-  </si>
-  <si>
-    <t>[np.float64(471.2316414532048), np.float64(-495.26173722663117)]</t>
-  </si>
-  <si>
-    <t>[np.float64(64.15249015683943), np.float64(567.2667360857188)]</t>
-  </si>
-  <si>
-    <t>[np.float64(975.1385245671862), np.float64(-548.7929375277683)]</t>
-  </si>
-  <si>
-    <t>[np.float64(694.5314361306331), np.float64(-178.70658233506572)]</t>
-  </si>
-  <si>
-    <t>[np.float64(36.21428724881959), np.float64(-34.54328998335109)]</t>
-  </si>
-  <si>
-    <t>[np.float64(118.26113843011655), np.float64(358.3721389344936)]</t>
-  </si>
-  <si>
-    <t>[np.float64(47.29478870358861), np.float64(56.61470783782863)]</t>
-  </si>
-  <si>
-    <t>[np.float64(564.3882323667337), np.float64(-487.6706589270591)]</t>
-  </si>
-  <si>
-    <t>[np.float64(974.1365381685247), np.float64(-241.56451844207692)]</t>
-  </si>
-  <si>
-    <t>[np.float64(922.1629972308634), np.float64(525.2393229941438)]</t>
-  </si>
-  <si>
-    <t>[np.float64(853.6691886034424), np.float64(-93.81457090316917)]</t>
-  </si>
-  <si>
-    <t>[np.float64(603.0422447802732), np.float64(537.0326250199557)]</t>
-  </si>
-  <si>
-    <t>[np.float64(856.9530780129862), np.float64(-357.78550524591463)]</t>
-  </si>
-  <si>
-    <t>[np.float64(228.1521776542268), np.float64(-532.8471785684043)]</t>
-  </si>
-  <si>
-    <t>[np.float64(22.352334318267996), np.float64(152.3499288262417)]</t>
-  </si>
-  <si>
-    <t>[np.float64(519.3663927717477), np.float64(558.2148425423004)]</t>
-  </si>
-  <si>
-    <t>[np.float64(975.9421817238544), np.float64(432.86557798053605)]</t>
-  </si>
-  <si>
-    <t>[np.float64(19.812396619515617), np.float64(223.62932224296742)]</t>
-  </si>
-  <si>
-    <t>[np.float64(257.72061518415757), np.float64(234.98807789378907)]</t>
-  </si>
-  <si>
-    <t>[np.float64(271.3713628417267), np.float64(-315.67880965713215)]</t>
-  </si>
-  <si>
-    <t>[np.float64(999.3871951529745), np.float64(-344.61140447591595)]</t>
-  </si>
-  <si>
-    <t>[np.float64(647.0635266833851), np.float64(-242.087991711036)]</t>
-  </si>
-  <si>
-    <t>[np.float64(10.437777649282554), np.float64(46.133312750421624)]</t>
-  </si>
-  <si>
-    <t>[np.float64(390.5869165408761), np.float64(330.88109327058964)]</t>
-  </si>
-  <si>
-    <t>[np.float64(159.89386687778273), np.float64(416.1804535559155)]</t>
-  </si>
-  <si>
-    <t>[np.float64(824.4052030879047), np.float64(-356.92027764305186)]</t>
-  </si>
-  <si>
-    <t>[np.float64(774.4833419334789), np.float64(542.3996531407438)]</t>
-  </si>
-  <si>
-    <t>[np.float64(415.91164705195894), np.float64(166.20438647537514)]</t>
-  </si>
-  <si>
-    <t>[np.float64(560.0223332073798), np.float64(346.16101327403635)]</t>
-  </si>
-  <si>
-    <t>[np.float64(693.8491732358766), np.float64(-446.12524134013194)]</t>
-  </si>
-  <si>
-    <t>[np.float64(378.14711606309356), np.float64(283.79964654343155)]</t>
-  </si>
-  <si>
-    <t>[np.float64(815.7829707025528), np.float64(-492.564287699302)]</t>
-  </si>
-  <si>
-    <t>[np.float64(440.6605865277687), np.float64(508.42110540120757)]</t>
-  </si>
-  <si>
-    <t>[np.float64(519.200428513481), np.float64(-184.0041387432617)]</t>
-  </si>
-  <si>
-    <t>[np.float64(925.7190982431255), np.float64(-247.42577569455761)]</t>
-  </si>
-  <si>
-    <t>[np.float64(794.3838777636056), np.float64(79.4361696695147)]</t>
-  </si>
-  <si>
-    <t>[np.float64(919.4391334396253), np.float64(273.0366070464662)]</t>
-  </si>
-  <si>
-    <t>[np.float64(775.503233896183), np.float64(-561.563845634285)]</t>
-  </si>
-  <si>
-    <t>[np.float64(982.0232223815441), np.float64(-154.73528885474985)]</t>
-  </si>
-  <si>
-    <t>[np.float64(794.8835003728003), np.float64(410.53182775032803)]</t>
-  </si>
-  <si>
-    <t>[np.float64(825.1450472282477), np.float64(310.9686198847737)]</t>
-  </si>
-  <si>
-    <t>[np.float64(137.98088522534746), np.float64(-196.65314080833048)]</t>
-  </si>
-  <si>
-    <t>[np.float64(37.9823738743601), np.float64(-213.54951673472777)]</t>
-  </si>
-  <si>
-    <t>[np.float64(514.3898399479907), np.float64(249.23314608642409)]</t>
-  </si>
-  <si>
-    <t>[np.float64(349.52823613840013), np.float64(-111.99535738815854)]</t>
-  </si>
-  <si>
-    <t>[np.float64(46.98519872302575), np.float64(-524.2126119200882)]</t>
-  </si>
-  <si>
-    <t>[np.float64(707.7154093920918), np.float64(-184.4322556744973)]</t>
-  </si>
-  <si>
-    <t>[np.float64(456.86041454487537), np.float64(-347.7455835137115)]</t>
-  </si>
-  <si>
-    <t>[np.float64(990.275514145552), np.float64(-193.48638213276377)]</t>
-  </si>
-  <si>
-    <t>[np.float64(881.2918605347104), np.float64(-325.52387167308945)]</t>
-  </si>
-  <si>
-    <t>[np.float64(926.327047685708), np.float64(26.152870987305732)]</t>
-  </si>
-  <si>
-    <t>[np.float64(94.66514505938362), np.float64(-377.14679617364055)]</t>
-  </si>
-  <si>
-    <t>[np.float64(327.4475021270227), np.float64(468.36107783029865)]</t>
-  </si>
-  <si>
-    <t>[np.float64(247.55659716799215), np.float64(585.6665207233302)]</t>
-  </si>
-  <si>
-    <t>[np.float64(786.3898893412661), np.float64(564.0493385813545)]</t>
-  </si>
-  <si>
-    <t>[np.float64(587.5920019854669), np.float64(-502.62165746760337)]</t>
-  </si>
-  <si>
-    <t>[np.float64(793.737610341531), np.float64(6.841402403158327)]</t>
-  </si>
-  <si>
-    <t>[np.float64(44.867066712095834), np.float64(341.1016639039549)]</t>
-  </si>
-  <si>
-    <t>[np.float64(341.86250848992506), np.float64(522.8533945967404)]</t>
-  </si>
-  <si>
-    <t>[np.float64(243.90128051199355), np.float64(-224.81252035678762)]</t>
-  </si>
-  <si>
-    <t>[np.float64(640.9794477437322), np.float64(-473.82528820715993)]</t>
-  </si>
-  <si>
-    <t>[np.float64(624.1812925309856), np.float64(398.6143433560518)]</t>
-  </si>
-  <si>
-    <t>[np.float64(895.1614150194379), np.float64(223.66514698577384)]</t>
-  </si>
-  <si>
-    <t>[np.float64(298.9924833509512), np.float64(-433.2382890860459)]</t>
-  </si>
-  <si>
-    <t>[np.float64(953.3616363929689), np.float64(385.54263506375685)]</t>
-  </si>
-  <si>
-    <t>[np.float64(985.7568784900787), np.float64(423.1360550209382)]</t>
-  </si>
-  <si>
-    <t>[np.float64(496.94552238274116), np.float64(-242.27857458427093)]</t>
-  </si>
-  <si>
-    <t>[np.float64(955.0443442472164), np.float64(-321.23382561642336)]</t>
-  </si>
-  <si>
-    <t>[np.float64(433.9866440820055), np.float64(-254.49232642229907)]</t>
-  </si>
-  <si>
-    <t>[np.float64(394.35661919219353), np.float64(-342.3423227052332)]</t>
-  </si>
-  <si>
-    <t>[np.float64(247.82841098674058), np.float64(468.1209109005533)]</t>
-  </si>
-  <si>
-    <t>[np.float64(527.3010554734783), np.float64(551.3762866570187)]</t>
-  </si>
-  <si>
-    <t>[np.float64(64.65750130127779), np.float64(-570.8819112875661)]</t>
-  </si>
-  <si>
-    <t>[np.float64(47.28772131227244), np.float64(-405.32873020916065)]</t>
-  </si>
-  <si>
-    <t>[np.float64(618.8144852005655), np.float64(82.87742683290435)]</t>
-  </si>
-  <si>
-    <t>[np.float64(396.27207764211715), np.float64(-127.68441211038606)]</t>
-  </si>
-  <si>
-    <t>[np.float64(525.3113997091098), np.float64(118.02407858827848)]</t>
-  </si>
-  <si>
-    <t>[np.float64(719.2986190698298), np.float64(-353.763060956697)]</t>
-  </si>
-  <si>
-    <t>[np.float64(567.5920358764641), np.float64(-228.58111747427432)]</t>
-  </si>
-  <si>
-    <t>[np.float64(0.4862323476577668), np.float64(167.65145969615537)]</t>
-  </si>
-  <si>
-    <t>[np.float64(358.63027425007834), np.float64(356.40747037166716)]</t>
-  </si>
-  <si>
-    <t>[np.float64(575.8298247151856), np.float64(79.12754082006722)]</t>
-  </si>
-  <si>
-    <t>[np.float64(564.8971997710292), np.float64(-394.8161913245152)]</t>
-  </si>
-  <si>
-    <t>[np.float64(978.4445051265359), np.float64(379.18258513299224)]</t>
-  </si>
-  <si>
-    <t>[np.float64(298.63339680727273), np.float64(83.82405807705925)]</t>
-  </si>
-  <si>
-    <t>[np.float64(947.730789688553), np.float64(274.27829211130575)]</t>
-  </si>
-  <si>
-    <t>[np.float64(24.968633313939172), np.float64(581.2993171110975)]</t>
-  </si>
-  <si>
-    <t>[np.float64(335.50779085692227), np.float64(573.7717324038729)]</t>
-  </si>
-  <si>
-    <t>[np.float64(141.76471469177176), np.float64(-204.3726726038106)]</t>
-  </si>
-  <si>
-    <t>[np.float64(201.65199652927944), np.float64(-433.91191712275025)]</t>
-  </si>
-  <si>
-    <t>[np.float64(152.1721559606961), np.float64(-166.3935139114501)]</t>
-  </si>
-  <si>
-    <t>[np.float64(204.5684765489044), np.float64(-279.84090453348114)]</t>
-  </si>
-  <si>
-    <t>[np.float64(123.80051583319151), np.float64(-108.38055097264237)]</t>
-  </si>
-  <si>
-    <t>[np.float64(325.2007708265696), np.float64(260.3332418200189)]</t>
-  </si>
-  <si>
-    <t>[np.float64(980.6886392696696), np.float64(-115.94855239847078)]</t>
-  </si>
-  <si>
-    <t>[np.float64(684.5564519465856), np.float64(463.32471793325976)]</t>
-  </si>
-  <si>
-    <t>[np.float64(901.8648205682409), np.float64(423.71960146974993)]</t>
-  </si>
-  <si>
-    <t>[np.float64(393.3677705273646), np.float64(-202.10354375101127)]</t>
-  </si>
-  <si>
-    <t>[np.float64(750.2275129032759), np.float64(-271.3026541104763)]</t>
-  </si>
-  <si>
-    <t>[np.float64(659.0694876728322), np.float64(-377.5056973139547)]</t>
-  </si>
-  <si>
-    <t>[np.float64(875.619472611741), np.float64(87.0446578317825)]</t>
-  </si>
-  <si>
-    <t>[np.float64(63.74193950157747), np.float64(362.80606765598645)]</t>
-  </si>
-  <si>
-    <t>[np.float64(699.3430436677904), np.float64(-361.8027538604509)]</t>
-  </si>
-  <si>
-    <t>[np.float64(869.9885035647796), np.float64(526.5191324085663)]</t>
-  </si>
-  <si>
-    <t>[np.float64(137.33137745572688), np.float64(-444.99748122584435)]</t>
-  </si>
-  <si>
-    <t>[np.float64(709.1403653079441), np.float64(594.6171160106126)]</t>
-  </si>
-  <si>
-    <t>[np.float64(354.9582419073978), np.float64(35.92936611374944)]</t>
-  </si>
-  <si>
-    <t>[np.float64(688.0449555041441), np.float64(-416.1720991813059)]</t>
-  </si>
-  <si>
-    <t>[np.float64(273.06915281998477), np.float64(344.64465624224715)]</t>
-  </si>
-  <si>
-    <t>[np.float64(282.59875155666083), np.float64(-298.4429489516672)]</t>
-  </si>
-  <si>
-    <t>[np.float64(419.9123939992203), np.float64(-536.5607356922485)]</t>
-  </si>
-  <si>
-    <t>[np.float64(938.0664190006488), np.float64(-321.4088279707093)]</t>
-  </si>
-  <si>
-    <t>[np.float64(533.2323429979987), np.float64(-437.3484492858261)]</t>
-  </si>
-  <si>
-    <t>[np.float64(486.9268594525229), np.float64(442.9005298578554)]</t>
-  </si>
-  <si>
-    <t>[np.float64(538.7163005325297), np.float64(-399.143814036652)]</t>
-  </si>
-  <si>
-    <t>[np.float64(622.3025250496975), np.float64(215.67840928801854)]</t>
-  </si>
-  <si>
-    <t>[np.float64(273.9740104005309), np.float64(167.94201930723193)]</t>
-  </si>
-  <si>
-    <t>[np.float64(593.2299798221304), np.float64(518.3019091916035)]</t>
-  </si>
-  <si>
-    <t>[np.float64(240.86061344057265), np.float64(-435.2040552680252)]</t>
-  </si>
-  <si>
-    <t>[np.float64(352.5479153880683), np.float64(-255.9310381240823)]</t>
-  </si>
-  <si>
-    <t>[np.float64(995.139264378809), np.float64(567.6151608179346)]</t>
-  </si>
-  <si>
-    <t>[np.float64(431.21418935973566), np.float64(-397.0872026943325)]</t>
-  </si>
-  <si>
-    <t>[np.float64(618.1423352600763), np.float64(-244.38769586796502)]</t>
-  </si>
-  <si>
-    <t>[np.float64(700.1220676812137), np.float64(252.65044853548454)]</t>
-  </si>
-  <si>
-    <t>[np.float64(406.1360645479882), np.float64(542.9788454548657)]</t>
-  </si>
-  <si>
-    <t>[np.float64(301.48393400069216), np.float64(197.9748777874288)]</t>
-  </si>
-  <si>
-    <t>[np.float64(365.5497456419182), np.float64(188.96482928149055)]</t>
-  </si>
-  <si>
-    <t>[np.float64(379.648966450196), np.float64(-497.47904829830156)]</t>
-  </si>
-  <si>
-    <t>[np.float64(996.4823485666268), np.float64(-360.20675693727947)]</t>
-  </si>
-  <si>
-    <t>[np.float64(983.6418634312063), np.float64(317.30168086889114)]</t>
-  </si>
-  <si>
-    <t>[np.float64(952.0606654193499), np.float64(5.917080597385279)]</t>
-  </si>
-  <si>
-    <t>[np.float64(94.96572041927276), np.float64(-259.57634920700826)]</t>
-  </si>
-  <si>
-    <t>[np.float64(949.5606349067315), np.float64(-531.6261564396397)]</t>
-  </si>
-  <si>
-    <t>[np.float64(804.3537240877266), np.float64(-278.69497232179884)]</t>
-  </si>
-  <si>
-    <t>[np.float64(303.36265658585415), np.float64(332.72916753891957)]</t>
-  </si>
-  <si>
-    <t>[np.float64(47.05799307650382), np.float64(363.11386952363193)]</t>
-  </si>
-  <si>
-    <t>[np.float64(471.0455933305901), np.float64(353.3774972981562)]</t>
-  </si>
-  <si>
-    <t>[np.float64(398.15944899359), np.float64(295.2551585837916)]</t>
-  </si>
-  <si>
-    <t>[np.float64(108.8945662471028), np.float64(537.1006756689687)]</t>
-  </si>
-  <si>
-    <t>[np.float64(122.8089372115202), np.float64(-160.4714086991849)]</t>
-  </si>
-  <si>
-    <t>[np.float64(624.3713666510522), np.float64(-376.1104271932944)]</t>
-  </si>
-  <si>
-    <t>[np.float64(343.0228692300987), np.float64(486.5498728153116)]</t>
-  </si>
-  <si>
-    <t>[np.float64(894.5788891288403), np.float64(-383.57613870317573)]</t>
-  </si>
-  <si>
-    <t>[np.float64(458.41812599915346), np.float64(318.0237449426419)]</t>
-  </si>
-  <si>
-    <t>[np.float64(989.875036394596), np.float64(510.11256893730797)]</t>
-  </si>
-  <si>
-    <t>[np.float64(473.83317017136386), np.float64(95.71098228973972)]</t>
-  </si>
-  <si>
-    <t>[np.float64(785.104028164197), np.float64(223.02838696806418)]</t>
-  </si>
-  <si>
-    <t>[np.float64(714.2470061557054), np.float64(415.94522012918776)]</t>
-  </si>
-  <si>
-    <t>[np.float64(722.6536456887529), np.float64(-271.7945665028289)]</t>
-  </si>
-  <si>
-    <t>[np.float64(736.1553014069688), np.float64(407.75127127556584)]</t>
-  </si>
-  <si>
-    <t>[np.float64(971.6218214030062), np.float64(235.26527768723895)]</t>
-  </si>
-  <si>
-    <t>[np.float64(352.94583628611855), np.float64(143.24397755643736)]</t>
-  </si>
-  <si>
-    <t>[np.float64(11.637375538077531), np.float64(-429.5278121455931)]</t>
-  </si>
-  <si>
-    <t>[np.float64(126.13007627128825), np.float64(374.98153472916727)]</t>
-  </si>
-  <si>
-    <t>[np.float64(457.42021026186154), np.float64(340.7737574422222)]</t>
-  </si>
-  <si>
-    <t>[np.float64(732.754017396203), np.float64(-488.05993713357014)]</t>
-  </si>
-  <si>
-    <t>[np.float64(405.05432727429525), np.float64(-522.4086358167672)]</t>
-  </si>
-  <si>
-    <t>[np.float64(147.54434317526244), np.float64(303.36916874425515)]</t>
-  </si>
-  <si>
-    <t>[np.float64(674.7865348370698), np.float64(-301.04319625463404)]</t>
-  </si>
-  <si>
-    <t>[np.float64(49.25859540328581), np.float64(263.85236939268407)]</t>
-  </si>
-  <si>
-    <t>[np.float64(683.2823552006702), np.float64(-166.12021368459745)]</t>
-  </si>
-  <si>
-    <t>[np.float64(193.73567139010817), np.float64(449.9128870385939)]</t>
-  </si>
-  <si>
-    <t>[np.float64(718.8095484599286), np.float64(-423.68793556609967)]</t>
-  </si>
-  <si>
-    <t>[np.float64(316.3712087538837), np.float64(-449.9795699787144)]</t>
-  </si>
-  <si>
-    <t>[np.float64(849.7131786657652), np.float64(543.7087834836918)]</t>
-  </si>
-  <si>
-    <t>[np.float64(956.0254480247984), np.float64(-238.85152584904512)]</t>
-  </si>
-  <si>
-    <t>[np.float64(330.99000894100385), np.float64(64.51603306070876)]</t>
-  </si>
-  <si>
-    <t>[np.float64(159.98114270460383), np.float64(-524.1611090429332)]</t>
-  </si>
-  <si>
-    <t>[np.float64(910.7223259157873), np.float64(198.09410547044104)]</t>
-  </si>
-  <si>
-    <t>[np.float64(588.724299408092), np.float64(-509.4022159252341)]</t>
-  </si>
-  <si>
-    <t>[np.float64(219.9624534179868), np.float64(-143.34723963729652)]</t>
-  </si>
-  <si>
-    <t>[np.float64(737.7335595855094), np.float64(584.0224320321843)]</t>
-  </si>
-  <si>
-    <t>[np.float64(100.6894789408751), np.float64(-424.0149100137003)]</t>
-  </si>
-  <si>
-    <t>[np.float64(790.0455505625107), np.float64(330.58284579699864)]</t>
-  </si>
-  <si>
-    <t>[np.float64(283.5799129181689), np.float64(-421.69605670666897)]</t>
-  </si>
-  <si>
-    <t>[np.float64(850.6215813938021), np.float64(282.69652824309617)]</t>
-  </si>
-  <si>
-    <t>[np.float64(565.8395334228353), np.float64(-574.484597879245)]</t>
-  </si>
-  <si>
-    <t>[np.float64(915.2466650373772), np.float64(-150.74482875506334)]</t>
-  </si>
-  <si>
-    <t>[np.float64(731.4828462857586), np.float64(-145.8460888323092)]</t>
-  </si>
-  <si>
-    <t>[np.float64(162.46210740643252), np.float64(-565.5189059657716)]</t>
-  </si>
-  <si>
-    <t>[np.float64(102.15423395215151), np.float64(523.1204563765011)]</t>
-  </si>
-  <si>
-    <t>[np.float64(910.7670160609576), np.float64(315.6458126775718)]</t>
-  </si>
-  <si>
-    <t>[np.float64(807.748760498035), np.float64(-523.4353254594554)]</t>
-  </si>
-  <si>
-    <t>[np.float64(766.2944790203912), np.float64(555.3088859446993)]</t>
-  </si>
-  <si>
-    <t>[np.float64(888.6905533712815), np.float64(2.9718960208653016)]</t>
-  </si>
-  <si>
-    <t>[np.float64(789.2604360538614), np.float64(-121.43103663329867)]</t>
-  </si>
-  <si>
-    <t>[np.float64(348.7764873689733), np.float64(554.472202548176)]</t>
-  </si>
-  <si>
-    <t>[np.float64(505.8054152724847), np.float64(106.54331556938791)]</t>
-  </si>
-  <si>
-    <t>[np.float64(613.6245542168343), np.float64(-177.58512426352593)]</t>
-  </si>
-  <si>
-    <t>[np.float64(6.139385761442462), np.float64(-140.8053655458337)]</t>
-  </si>
-  <si>
-    <t>[np.float64(151.86378390648713), np.float64(483.9724069219128)]</t>
-  </si>
-  <si>
-    <t>[np.float64(842.8231025435009), np.float64(-407.0826656252002)]</t>
-  </si>
-  <si>
-    <t>[np.float64(302.2132953682366), np.float64(178.97953449956822)]</t>
-  </si>
-  <si>
-    <t>[np.float64(772.0585418517728), np.float64(-168.43281031297636)]</t>
-  </si>
-  <si>
-    <t>[np.float64(700.2648733776966), np.float64(383.6553733520217)]</t>
-  </si>
-  <si>
-    <t>[np.float64(883.0427729624241), np.float64(30.313381057693732)]</t>
-  </si>
-  <si>
-    <t>[np.float64(45.90773026238093), np.float64(474.31727425539157)]</t>
-  </si>
-  <si>
-    <t>[np.float64(856.6855633965885), np.float64(-212.43070078776992)]</t>
-  </si>
-  <si>
-    <t>[np.float64(404.92548913431557), np.float64(457.9896851379849)]</t>
-  </si>
-  <si>
-    <t>[np.float64(266.57664858586804), np.float64(583.4954150211263)]</t>
-  </si>
-  <si>
-    <t>[np.float64(42.642618179858594), np.float64(166.38931120427537)]</t>
-  </si>
-  <si>
-    <t>[np.float64(691.4638215117831), np.float64(367.5536773132977)]</t>
-  </si>
-  <si>
-    <t>[np.float64(599.2730760386778), np.float64(338.24928209461723)]</t>
-  </si>
-  <si>
-    <t>[np.float64(879.9626176510224), np.float64(445.3328115761394)]</t>
-  </si>
-  <si>
-    <t>[np.float64(365.8416731560545), np.float64(330.8095794971068)]</t>
-  </si>
-  <si>
-    <t>[np.float64(272.8817784400308), np.float64(-488.31618058098195)]</t>
-  </si>
-  <si>
-    <t>[np.float64(275.26787990112166), np.float64(-182.137599367497)]</t>
-  </si>
-  <si>
-    <t>[np.float64(331.6558722317903), np.float64(-132.47328095639108)]</t>
-  </si>
-  <si>
-    <t>[np.float64(91.19434352059774), np.float64(45.564951891106034)]</t>
-  </si>
-  <si>
-    <t>[np.float64(184.9585748983198), np.float64(598.7398936451154)]</t>
-  </si>
-  <si>
-    <t>[np.float64(348.2367048018119), np.float64(-88.89758416390316)]</t>
-  </si>
-  <si>
-    <t>[np.float64(998.5345999672821), np.float64(463.82630571773643)]</t>
-  </si>
-  <si>
-    <t>[np.float64(206.45265871228526), np.float64(-120.43734039240417)]</t>
-  </si>
-  <si>
-    <t>[np.float64(622.8014121871574), np.float64(410.3045342533487)]</t>
-  </si>
-  <si>
-    <t>[np.float64(458.32303740708755), np.float64(538.7020035446417)]</t>
-  </si>
-  <si>
-    <t>[np.float64(359.46036639698355), np.float64(239.37261003249728)]</t>
-  </si>
-  <si>
-    <t>[np.float64(336.7247385091705), np.float64(-233.36508038741061)]</t>
-  </si>
-  <si>
-    <t>[np.float64(613.173146408657), np.float64(563.6698293408504)]</t>
-  </si>
-  <si>
-    <t>[np.float64(549.0393478823652), np.float64(-526.1912090945949)]</t>
-  </si>
-  <si>
-    <t>[np.float64(135.6807209493004), np.float64(-461.77354336950043)]</t>
-  </si>
-  <si>
-    <t>[np.float64(804.9646744897129), np.float64(-485.75944640331795)]</t>
-  </si>
-  <si>
-    <t>[np.float64(5.128758909079711), np.float64(277.40695846114136)]</t>
-  </si>
-  <si>
-    <t>[np.float64(8.842846518072434), np.float64(243.72781765646812)]</t>
-  </si>
-  <si>
-    <t>[np.float64(140.18449164003266), np.float64(-127.32985767923725)]</t>
-  </si>
-  <si>
-    <t>[np.float64(964.6594845204435), np.float64(-370.5370721162857)]</t>
-  </si>
-  <si>
-    <t>[np.float64(278.6330773249168), np.float64(110.21543814714892)]</t>
-  </si>
-  <si>
-    <t>[np.float64(735.2074913437694), np.float64(183.54215035997663)]</t>
-  </si>
-  <si>
-    <t>[np.float64(730.5193362511706), np.float64(-178.99014874539608)]</t>
-  </si>
-  <si>
-    <t>[np.float64(544.5596882331288), np.float64(266.6229270584131)]</t>
-  </si>
-  <si>
-    <t>[np.float64(376.1955789740511), np.float64(-391.9147556715957)]</t>
-  </si>
-  <si>
-    <t>[np.float64(770.8073848788455), np.float64(240.3887094913058)]</t>
-  </si>
-  <si>
-    <t>[np.float64(402.7293321931792), np.float64(-407.8021247656839)]</t>
-  </si>
-  <si>
-    <t>[np.float64(795.2147826820261), np.float64(-178.27392857310764)]</t>
-  </si>
-  <si>
-    <t>[np.float64(826.8820412690137), np.float64(583.2039440292722)]</t>
-  </si>
-  <si>
-    <t>[np.float64(156.42424907834484), np.float64(544.8824203776078)]</t>
-  </si>
-  <si>
-    <t>[np.float64(577.5554363600329), np.float64(-81.62993860841448)]</t>
-  </si>
-  <si>
-    <t>[np.float64(324.7724068955014), np.float64(251.36944547958205)]</t>
-  </si>
-  <si>
-    <t>[np.float64(251.41010840011813), np.float64(-515.0073337877595)]</t>
-  </si>
-  <si>
-    <t>[np.float64(407.87515494232986), np.float64(498.2385698842886)]</t>
-  </si>
-  <si>
-    <t>[np.float64(990.2343318702542), np.float64(-133.40133923884218)]</t>
-  </si>
-  <si>
-    <t>[np.float64(582.0781505534763), np.float64(107.39094957743373)]</t>
-  </si>
-  <si>
-    <t>[np.float64(991.4689781368527), np.float64(469.0450340968089)]</t>
-  </si>
-  <si>
-    <t>[np.float64(870.6598611348109), np.float64(-370.96142451024923)]</t>
-  </si>
-  <si>
-    <t>[np.float64(33.07214175556905), np.float64(-50.3991739087902)]</t>
-  </si>
-  <si>
-    <t>[np.float64(841.3286462724226), np.float64(117.44669415478393)]</t>
-  </si>
-  <si>
-    <t>[np.float64(403.70421736858975), np.float64(-408.04747255553656)]</t>
-  </si>
-  <si>
-    <t>[np.float64(100.15312538530108), np.float64(223.00793875692295)]</t>
-  </si>
-  <si>
-    <t>[np.float64(791.682292067987), np.float64(84.07790539534824)]</t>
-  </si>
-  <si>
-    <t>[np.float64(611.5022848949019), np.float64(-99.65392912008025)]</t>
-  </si>
-  <si>
-    <t>[np.float64(623.5157409321789), np.float64(-271.16043456891816)]</t>
-  </si>
-  <si>
-    <t>[np.float64(811.3569413294441), np.float64(172.5420369056602)]</t>
-  </si>
-  <si>
-    <t>[np.float64(347.84667682885674), np.float64(-135.91672409239493)]</t>
-  </si>
-  <si>
-    <t>[np.float64(718.0763316137654), np.float64(103.10713502145984)]</t>
-  </si>
-  <si>
-    <t>[np.float64(749.3615261264648), np.float64(-365.1043110394493)]</t>
-  </si>
-  <si>
-    <t>[np.float64(541.131269437889), np.float64(-446.20704693655097)]</t>
-  </si>
-  <si>
-    <t>[np.float64(525.2264806831485), np.float64(32.31137135744598)]</t>
-  </si>
-  <si>
-    <t>[np.float64(344.6738775863043), np.float64(422.1183111522023)]</t>
-  </si>
-  <si>
-    <t>[np.float64(201.68705186422875), np.float64(43.28957350652183)]</t>
-  </si>
-  <si>
-    <t>[np.float64(839.3427102907226), np.float64(-76.55906392685563)]</t>
-  </si>
-  <si>
-    <t>[np.float64(630.4078167007908), np.float64(235.24959092844313)]</t>
-  </si>
-  <si>
-    <t>[np.float64(84.02146324058579), np.float64(586.244593704753)]</t>
-  </si>
-  <si>
-    <t>[np.float64(165.15367486086663), np.float64(21.128285810152875)]</t>
-  </si>
-  <si>
-    <t>[np.float64(950.828007292074), np.float64(95.61486591748917)]</t>
-  </si>
-  <si>
-    <t>[np.float64(161.62219094638996), np.float64(77.03572530748875)]</t>
-  </si>
-  <si>
-    <t>[np.float64(188.19021239772204), np.float64(-410.00505957818723)]</t>
-  </si>
-  <si>
-    <t>[np.float64(522.2283701704829), np.float64(240.4906720203761)]</t>
-  </si>
-  <si>
-    <t>[np.float64(792.1674885152331), np.float64(136.89831559296783)]</t>
-  </si>
-  <si>
-    <t>[np.float64(109.47214631621883), np.float64(426.41818346281775)]</t>
-  </si>
-  <si>
-    <t>[np.float64(991.1612557206328), np.float64(416.61808617147267)]</t>
-  </si>
-  <si>
-    <t>[np.float64(560.3106474333013), np.float64(-328.79292891400155)]</t>
-  </si>
-  <si>
-    <t>[np.float64(501.8055162385708), np.float64(441.0269882646994)]</t>
-  </si>
-  <si>
-    <t>[np.float64(672.2569078604723), np.float64(285.1548545792406)]</t>
-  </si>
-  <si>
-    <t>[np.float64(789.7265608461339), np.float64(-131.99495471109304)]</t>
-  </si>
-  <si>
-    <t>[np.float64(41.97671276515136), np.float64(-538.1110640217273)]</t>
-  </si>
-  <si>
-    <t>[np.float64(217.52004992542484), np.float64(-415.1441459608017)]</t>
-  </si>
-  <si>
-    <t>[np.float64(965.2231828672719), np.float64(-533.3072136653794)]</t>
-  </si>
-  <si>
-    <t>[np.float64(15.970145243437873), np.float64(-503.4182414374556)]</t>
-  </si>
-  <si>
-    <t>[np.float64(41.877879902096794), np.float64(-359.7129687580525)]</t>
-  </si>
-  <si>
-    <t>[np.float64(262.7628337582751), np.float64(-450.1898452889149)]</t>
-  </si>
-  <si>
-    <t>[np.float64(595.6994202595737), np.float64(-233.974223257875)]</t>
-  </si>
-  <si>
-    <t>[np.float64(619.604288427025), np.float64(45.1612497870924)]</t>
-  </si>
-  <si>
-    <t>[np.float64(40.571111383918556), np.float64(279.1117351778779)]</t>
-  </si>
-  <si>
-    <t>[np.float64(552.4323471769615), np.float64(-71.03609085407072)]</t>
-  </si>
-  <si>
-    <t>[np.float64(53.03494629892036), np.float64(502.25185876999535)]</t>
-  </si>
-  <si>
-    <t>[np.float64(754.754588610786), np.float64(-419.1762158601679)]</t>
-  </si>
-  <si>
-    <t>[np.float64(865.5846433521908), np.float64(-106.25330837832257)]</t>
-  </si>
-  <si>
-    <t>[np.float64(182.3450973587557), np.float64(7.79112079935669)]</t>
-  </si>
-  <si>
-    <t>[np.float64(872.8566732761651), np.float64(-573.7910993925476)]</t>
-  </si>
-  <si>
-    <t>[np.float64(826.4364687377639), np.float64(-297.90613256236827)]</t>
-  </si>
-  <si>
-    <t>[np.float64(35.0650069159435), np.float64(368.29928880083423)]</t>
-  </si>
-  <si>
-    <t>[np.float64(646.1824889772478), np.float64(202.94272923678716)]</t>
-  </si>
-  <si>
-    <t>[np.float64(33.65535386869989), np.float64(-502.5994586515312)]</t>
-  </si>
-  <si>
-    <t>[np.float64(168.61014503872417), np.float64(290.77015893774615)]</t>
-  </si>
-  <si>
-    <t>[np.float64(599.1990965268244), np.float64(390.82751688941255)]</t>
-  </si>
-  <si>
-    <t>[np.float64(83.7724648064897), np.float64(-484.47869862373)]</t>
-  </si>
-  <si>
-    <t>[np.float64(698.3443129789694), np.float64(318.64499383752093)]</t>
-  </si>
-  <si>
-    <t>[np.float64(491.03028355926494), np.float64(349.9656961091621)]</t>
-  </si>
-  <si>
-    <t>[np.float64(229.2652881415327), np.float64(44.11642479226532)]</t>
-  </si>
-  <si>
-    <t>[np.float64(510.38373331301955), np.float64(-496.442879720575)]</t>
-  </si>
-  <si>
-    <t>[np.float64(863.1342587541945), np.float64(-172.19247902575842)]</t>
-  </si>
-  <si>
-    <t>[np.float64(91.78239148020484), np.float64(77.72815147066035)]</t>
-  </si>
-  <si>
-    <t>[np.float64(40.17040773287028), np.float64(389.5600398446769)]</t>
-  </si>
-  <si>
-    <t>[np.float64(888.0543787438288), np.float64(-582.1881064849108)]</t>
-  </si>
-  <si>
-    <t>[np.float64(828.883960565483), np.float64(542.6518286075732)]</t>
-  </si>
-  <si>
-    <t>[np.float64(45.05529043950085), np.float64(-333.7433503812844)]</t>
-  </si>
-  <si>
-    <t>[np.float64(413.87986440331815), np.float64(565.0373844972003)]</t>
-  </si>
-  <si>
-    <t>[np.float64(413.70954783707936), np.float64(-498.27667923265875)]</t>
-  </si>
-  <si>
-    <t>[np.float64(867.4348551396876), np.float64(-580.9204792733219)]</t>
-  </si>
-  <si>
-    <t>[np.float64(973.2833550031226), np.float64(-574.0825911071955)]</t>
-  </si>
-  <si>
-    <t>[np.float64(399.72312861941), np.float64(158.8102895704975)]</t>
-  </si>
-  <si>
-    <t>[np.float64(882.1805181681448), np.float64(-430.84013963551524)]</t>
-  </si>
-  <si>
-    <t>[np.float64(375.513813475711), np.float64(457.7718484346717)]</t>
-  </si>
-  <si>
-    <t>[np.float64(675.5377254934505), np.float64(-585.6343409873242)]</t>
-  </si>
-  <si>
-    <t>[np.float64(242.10400606859918), np.float64(-226.6204357212237)]</t>
-  </si>
-  <si>
-    <t>[np.float64(918.0646607361383), np.float64(62.25755672831065)]</t>
-  </si>
-  <si>
-    <t>[np.float64(245.08646734029548), np.float64(55.2789805991423)]</t>
-  </si>
-  <si>
-    <t>[np.float64(817.4242676181956), np.float64(74.84181931298247)]</t>
-  </si>
-  <si>
-    <t>[np.float64(605.9759925975123), np.float64(528.1239338435171)]</t>
-  </si>
-  <si>
-    <t>[np.float64(681.6306159999808), np.float64(386.71470745069723)]</t>
-  </si>
-  <si>
-    <t>[np.float64(385.0987947054014), np.float64(488.62554510429845)]</t>
-  </si>
-  <si>
-    <t>[np.float64(380.3391195281336), np.float64(-168.2017930658434)]</t>
-  </si>
-  <si>
-    <t>[np.float64(449.74336150641557), np.float64(-247.6238264892864)]</t>
-  </si>
-  <si>
-    <t>[np.float64(218.1869430616329), np.float64(-89.66677375564757)]</t>
-  </si>
-  <si>
-    <t>[np.float64(638.1157425732459), np.float64(-522.2923758663405)]</t>
-  </si>
-  <si>
-    <t>[np.float64(59.5036034910964), np.float64(306.7009808411233)]</t>
-  </si>
-  <si>
-    <t>[np.float64(441.52233515999393), np.float64(139.81125116242515)]</t>
-  </si>
-  <si>
-    <t>[np.float64(845.3123008723794), np.float64(-398.43628135029394)]</t>
-  </si>
-  <si>
-    <t>[np.float64(474.80270566870087), np.float64(541.5076783078039)]</t>
-  </si>
-  <si>
-    <t>[np.float64(428.3422606623815), np.float64(540.4097154505896)]</t>
-  </si>
-  <si>
-    <t>[np.float64(911.3157042917687), np.float64(441.416016265699)]</t>
-  </si>
-  <si>
-    <t>[np.float64(701.2169303793247), np.float64(-571.3470392884841)]</t>
-  </si>
-  <si>
-    <t>[np.float64(542.1500013618067), np.float64(282.7739942886708)]</t>
-  </si>
-  <si>
-    <t>[np.float64(597.4661116535838), np.float64(34.75725687403565)]</t>
-  </si>
-  <si>
-    <t>[np.float64(785.7896517048258), np.float64(6.931260683922915)]</t>
-  </si>
-  <si>
-    <t>[np.float64(704.1789996363191), np.float64(-314.9536730032095)]</t>
-  </si>
-  <si>
-    <t>[np.float64(9.523079489563768), np.float64(-112.05901233388676)]</t>
-  </si>
-  <si>
-    <t>[np.float64(600.4863852704435), np.float64(344.6820701603466)]</t>
-  </si>
-  <si>
-    <t>[np.float64(262.6500476728617), np.float64(113.9411858588054)]</t>
-  </si>
-  <si>
-    <t>[np.float64(773.489343292419), np.float64(588.1306648580967)]</t>
-  </si>
-  <si>
-    <t>[np.float64(96.53936969700783), np.float64(-487.83201499524654)]</t>
-  </si>
-  <si>
-    <t>[np.float64(820.5619975111845), np.float64(-214.39366697458377)]</t>
-  </si>
-  <si>
-    <t>[np.float64(644.6248440447425), np.float64(46.430438834395545)]</t>
-  </si>
-  <si>
-    <t>[np.float64(709.2865537311363), np.float64(214.44536124296644)]</t>
-  </si>
-  <si>
-    <t>[np.float64(291.38303213609805), np.float64(-182.7157988241143)]</t>
-  </si>
-  <si>
-    <t>[np.float64(158.35731150312316), np.float64(139.84330245752915)]</t>
-  </si>
-  <si>
-    <t>[np.float64(477.99219955722674), np.float64(-127.18817183770796)]</t>
-  </si>
-  <si>
-    <t>[np.float64(583.8827306294663), np.float64(254.39331513082504)]</t>
-  </si>
-  <si>
-    <t>[np.float64(287.26744775708056), np.float64(145.58376816450675)]</t>
-  </si>
-  <si>
-    <t>[np.float64(591.9585803691182), np.float64(293.392011125782)]</t>
-  </si>
-  <si>
-    <t>[np.float64(719.9141783941582), np.float64(-165.78944477491297)]</t>
-  </si>
-  <si>
-    <t>[np.float64(607.5394168786147), np.float64(143.25616024930912)]</t>
-  </si>
-  <si>
-    <t>[np.float64(172.33799203394184), np.float64(-204.64668488458494)]</t>
-  </si>
-  <si>
-    <t>[np.float64(215.02988794904786), np.float64(-385.788081884672)]</t>
-  </si>
-  <si>
-    <t>[np.float64(46.388333957288694), np.float64(-304.1319047243003)]</t>
-  </si>
-  <si>
-    <t>[np.float64(874.9511061760967), np.float64(504.9855381798559)]</t>
-  </si>
-  <si>
-    <t>[np.float64(979.7905797052548), np.float64(160.8018625323998)]</t>
-  </si>
-  <si>
-    <t>[np.float64(411.18058238595137), np.float64(-290.72402023519896)]</t>
-  </si>
-  <si>
-    <t>[np.float64(394.5079200826479), np.float64(-269.222609805374)]</t>
-  </si>
-  <si>
-    <t>[np.float64(870.5449993970024), np.float64(227.86892287760247)]</t>
-  </si>
-  <si>
-    <t>[np.float64(950.9124944137383), np.float64(171.74610318536656)]</t>
-  </si>
-  <si>
-    <t>[np.float64(41.774381841583995), np.float64(485.39038948147663)]</t>
-  </si>
-  <si>
-    <t>[np.float64(529.1246345787508), np.float64(124.65022144651277)]</t>
-  </si>
-  <si>
-    <t>[np.float64(383.3986705082982), np.float64(321.2083130055332)]</t>
-  </si>
-  <si>
-    <t>[np.float64(175.8314016395759), np.float64(-164.85341917224656)]</t>
-  </si>
-  <si>
-    <t>[np.float64(474.2674777095154), np.float64(-565.7790848767806)]</t>
-  </si>
-  <si>
-    <t>[np.float64(833.8135133997405), np.float64(-68.60573434032551)]</t>
-  </si>
-  <si>
-    <t>[np.float64(836.7634041169495), np.float64(449.6308781350331)]</t>
-  </si>
-  <si>
-    <t>[np.float64(13.600628724656838), np.float64(-329.6924115701857)]</t>
-  </si>
-  <si>
-    <t>[np.float64(888.3334124199098), np.float64(-276.77951172539434)]</t>
-  </si>
-  <si>
-    <t>[np.float64(293.3678530350633), np.float64(527.748217318418)]</t>
-  </si>
-  <si>
-    <t>[np.float64(772.1710809108065), np.float64(240.76260457605315)]</t>
-  </si>
-  <si>
-    <t>[np.float64(324.548341363475), np.float64(196.20723510368043)]</t>
-  </si>
-  <si>
-    <t>[np.float64(61.16501440543498), np.float64(-295.32174660860505)]</t>
-  </si>
-  <si>
-    <t>[np.float64(733.7887488417442), np.float64(-503.7560161808319)]</t>
-  </si>
-  <si>
-    <t>[np.float64(391.53137138534066), np.float64(504.1105884981132)]</t>
-  </si>
-  <si>
-    <t>[np.float64(398.15873395065915), np.float64(145.52506948298878)]</t>
-  </si>
-  <si>
-    <t>[np.float64(521.8532612949518), np.float64(208.25845118806285)]</t>
-  </si>
-  <si>
-    <t>[np.float64(387.8752444069031), np.float64(-257.5736480114014)]</t>
-  </si>
-  <si>
-    <t>[np.float64(328.0877360549865), np.float64(409.34195660353976)]</t>
-  </si>
-  <si>
-    <t>[np.float64(310.5720588475156), np.float64(-369.2498719272877)]</t>
-  </si>
-  <si>
-    <t>[np.float64(285.09456193912706), np.float64(190.60632410669552)]</t>
-  </si>
-  <si>
-    <t>[np.float64(115.47271483547172), np.float64(108.37018271582065)]</t>
-  </si>
-  <si>
-    <t>[np.float64(706.3058859565211), np.float64(-124.09893943302342)]</t>
-  </si>
-  <si>
-    <t>[np.float64(875.8242142248528), np.float64(-206.65793060686718)]</t>
-  </si>
-  <si>
-    <t>[np.float64(912.5878779083389), np.float64(196.40203994137948)]</t>
-  </si>
-  <si>
-    <t>[np.float64(349.595619634135), np.float64(-530.6055587821033)]</t>
-  </si>
-  <si>
-    <t>[np.float64(784.2799482658504), np.float64(-247.33428346268107)]</t>
-  </si>
-  <si>
-    <t>[np.float64(935.6385194133449), np.float64(243.33788050362693)]</t>
-  </si>
-  <si>
-    <t>[np.float64(167.32882303918606), np.float64(-452.1716296239881)]</t>
-  </si>
-  <si>
-    <t>[np.float64(71.05918307000624), np.float64(110.7715114418811)]</t>
-  </si>
-  <si>
-    <t>[np.float64(962.1730293468747), np.float64(6.697128468646156)]</t>
-  </si>
-  <si>
-    <t>[np.float64(597.9396337375595), np.float64(-302.6048871250906)]</t>
-  </si>
-  <si>
-    <t>[np.float64(960.8474844402797), np.float64(524.3902105212801)]</t>
-  </si>
-  <si>
-    <t>[np.float64(814.4864031301495), np.float64(36.26641447707834)]</t>
-  </si>
-  <si>
-    <t>[np.float64(949.6920813971825), np.float64(324.28284222651814)]</t>
-  </si>
-  <si>
-    <t>[np.float64(658.4009382118744), np.float64(-543.267495574783)]</t>
-  </si>
-  <si>
-    <t>[np.float64(233.49495451136826), np.float64(-434.29915538060266)]</t>
-  </si>
-  <si>
-    <t>[np.float64(530.586766107371), np.float64(133.78713877380483)]</t>
-  </si>
-  <si>
-    <t>[np.float64(6.899661766342602), np.float64(536.8429543841282)]</t>
-  </si>
-  <si>
-    <t>[np.float64(818.0210583174686), np.float64(-384.8301814206339)]</t>
-  </si>
-  <si>
-    <t>[np.float64(638.2505136150863), np.float64(-533.1084565103931)]</t>
-  </si>
-  <si>
-    <t>[np.float64(762.819675330464), np.float64(194.36698337126575)]</t>
-  </si>
-  <si>
-    <t>[np.float64(995.9404621975743), np.float64(-148.218050376179)]</t>
-  </si>
-  <si>
-    <t>[np.float64(681.5008241970622), np.float64(-505.35922092974187)]</t>
-  </si>
-  <si>
-    <t>[np.float64(964.9511803723009), np.float64(27.71553178101442)]</t>
-  </si>
-  <si>
-    <t>[np.float64(244.10987271167772), np.float64(-219.58597267912745)]</t>
-  </si>
-  <si>
-    <t>[np.float64(479.39906663553666), np.float64(-330.4423746674051)]</t>
-  </si>
-  <si>
-    <t>[np.float64(588.5637202084847), np.float64(286.85737396646005)]</t>
-  </si>
-  <si>
-    <t>[np.float64(803.2324564501438), np.float64(104.86426844394578)]</t>
-  </si>
-  <si>
-    <t>[np.float64(157.05334213969658), np.float64(125.66272336261773)]</t>
-  </si>
-  <si>
-    <t>[np.float64(193.27309630478794), np.float64(538.8725900409368)]</t>
-  </si>
-  <si>
-    <t>[np.float64(615.2721016050733), np.float64(358.9841982669425)]</t>
-  </si>
-  <si>
-    <t>[np.float64(7.391827346524549), np.float64(428.2951494460465)]</t>
-  </si>
-  <si>
-    <t>[np.float64(496.6407943927955), np.float64(356.3780743036274)]</t>
-  </si>
-  <si>
-    <t>[np.float64(262.1944040726264), np.float64(-527.8927537708626)]</t>
-  </si>
-  <si>
-    <t>[np.float64(975.8692340929579), np.float64(-347.1854829754651)]</t>
-  </si>
-  <si>
-    <t>[np.float64(194.84844400765112), np.float64(573.7675277256078)]</t>
-  </si>
-  <si>
-    <t>[np.float64(215.7573052132846), np.float64(-187.75268494943498)]</t>
-  </si>
-  <si>
-    <t>[np.float64(968.5927295784726), np.float64(564.2142303029693)]</t>
-  </si>
-  <si>
-    <t>[np.float64(391.26080882811823), np.float64(-203.04411145455282)]</t>
-  </si>
-  <si>
-    <t>[np.float64(30.90664032665702), np.float64(537.1317094304729)]</t>
-  </si>
-  <si>
-    <t>[np.float64(44.73572634859768), np.float64(76.0252233981754)]</t>
-  </si>
-  <si>
-    <t>[np.float64(98.50131739796308), np.float64(-192.96029911936603)]</t>
-  </si>
-  <si>
-    <t>[np.float64(176.87899849924415), np.float64(-553.6063934740864)]</t>
-  </si>
-  <si>
-    <t>[np.float64(878.5510500705412), np.float64(-276.6910228547285)]</t>
-  </si>
-  <si>
-    <t>[np.float64(432.19786773047883), np.float64(-104.61230107547323)]</t>
-  </si>
-  <si>
-    <t>[np.float64(876.343787233371), np.float64(-423.5440241208399)]</t>
-  </si>
-  <si>
-    <t>[np.float64(11.818514321525807), np.float64(-150.85818895048874)]</t>
-  </si>
-  <si>
-    <t>[np.float64(308.03031061926356), np.float64(164.26475200151174)]</t>
-  </si>
-  <si>
-    <t>[np.float64(379.384813392412), np.float64(391.78094710196615)]</t>
-  </si>
-  <si>
-    <t>[np.float64(747.6188216988764), np.float64(0.7220928281914212)]</t>
-  </si>
-  <si>
-    <t>[np.float64(467.3222668625707), np.float64(415.58037572071737)]</t>
-  </si>
-  <si>
-    <t>[np.float64(222.36985755307182), np.float64(-172.7611786553287)]</t>
-  </si>
-  <si>
-    <t>[np.float64(415.3794132312576), np.float64(99.89205336467762)]</t>
-  </si>
-  <si>
-    <t>[np.float64(645.5329648568016), np.float64(35.0443111451458)]</t>
-  </si>
-  <si>
-    <t>[np.float64(809.2603484031496), np.float64(593.8096719321366)]</t>
-  </si>
-  <si>
-    <t>[np.float64(215.4900990048796), np.float64(162.36254244021313)]</t>
-  </si>
-  <si>
-    <t>[np.float64(594.0180046176199), np.float64(207.9499802087056)]</t>
-  </si>
-  <si>
-    <t>[np.float64(553.6473691751141), np.float64(157.4805871170047)]</t>
-  </si>
-  <si>
-    <t>[np.float64(948.7748303692242), np.float64(166.67025553441079)]</t>
-  </si>
-  <si>
-    <t>[np.float64(888.9019660526354), np.float64(189.9541397831382)]</t>
-  </si>
-  <si>
-    <t>[np.float64(916.7888410041443), np.float64(378.82611760438465)]</t>
-  </si>
-  <si>
-    <t>[np.float64(229.78820155649404), np.float64(-153.64236585949112)]</t>
-  </si>
-  <si>
-    <t>[np.float64(161.7402983070174), np.float64(-480.72123908754025)]</t>
-  </si>
-  <si>
-    <t>[np.float64(819.1806019290684), np.float64(-268.0581909647278)]</t>
-  </si>
-  <si>
-    <t>[np.float64(461.9666252264801), np.float64(356.3050277456987)]</t>
-  </si>
-  <si>
-    <t>[np.float64(712.323413914918), np.float64(513.6034994973597)]</t>
-  </si>
-  <si>
-    <t>[np.float64(696.7375169300423), np.float64(486.9605625324016)]</t>
-  </si>
-  <si>
-    <t>[np.float64(431.39427171857926), np.float64(-270.2692340330623)]</t>
-  </si>
-  <si>
-    <t>[np.float64(948.6707375489879), np.float64(98.89588320907615)]</t>
-  </si>
-  <si>
-    <t>[np.float64(678.854925588889), np.float64(384.6919938344838)]</t>
-  </si>
-  <si>
-    <t>[np.float64(434.20028126293084), np.float64(216.00811390437525)]</t>
-  </si>
-  <si>
-    <t>[np.float64(570.0089765094694), np.float64(92.83956396166764)]</t>
-  </si>
-  <si>
-    <t>[np.float64(241.8602237714561), np.float64(-186.8047697131111)]</t>
-  </si>
-  <si>
-    <t>[np.float64(259.3419481149216), np.float64(-532.6983920562361)]</t>
-  </si>
-  <si>
-    <t>[np.float64(614.5792250114329), np.float64(-423.1183074333593)]</t>
-  </si>
-  <si>
-    <t>[np.float64(509.4378332112447), np.float64(-499.4342986978953)]</t>
-  </si>
-  <si>
-    <t>[np.float64(741.7008400601072), np.float64(192.82193145536235)]</t>
-  </si>
-  <si>
-    <t>[np.float64(524.0739948600018), np.float64(430.286217044953)]</t>
-  </si>
-  <si>
-    <t>[np.float64(863.4826268366392), np.float64(533.673161637324)]</t>
-  </si>
-  <si>
-    <t>[np.float64(993.1962873646097), np.float64(150.27821415663948)]</t>
-  </si>
-  <si>
-    <t>[np.float64(283.79628352106346), np.float64(118.5281590659257)]</t>
-  </si>
-  <si>
-    <t>[np.float64(261.3552505143696), np.float64(397.4264848172893)]</t>
-  </si>
-  <si>
-    <t>[np.float64(696.5797640467019), np.float64(-547.9793535530617)]</t>
-  </si>
-  <si>
-    <t>[np.float64(526.140879206703), np.float64(-407.0554524869237)]</t>
-  </si>
-  <si>
-    <t>[np.float64(883.816807268144), np.float64(-152.29026372637497)]</t>
-  </si>
-  <si>
-    <t>[np.float64(889.4107068822619), np.float64(-534.1740578705828)]</t>
-  </si>
-  <si>
-    <t>[np.float64(631.5828946489252), np.float64(286.74326201792314)]</t>
-  </si>
-  <si>
-    <t>[np.float64(456.93198718019545), np.float64(-132.9802967905996)]</t>
-  </si>
-  <si>
-    <t>[np.float64(694.2020138318653), np.float64(10.39301514985766)]</t>
-  </si>
-  <si>
-    <t>[np.float64(52.42420468375919), np.float64(517.4668697620407)]</t>
-  </si>
-  <si>
-    <t>[np.float64(508.0912539384211), np.float64(93.59628808042066)]</t>
-  </si>
-  <si>
-    <t>[np.float64(363.08337029952185), np.float64(511.5496722313044)]</t>
-  </si>
-  <si>
-    <t>[np.float64(220.67290467919264), np.float64(-407.25652521244876)]</t>
-  </si>
-  <si>
-    <t>[np.float64(814.7854897538401), np.float64(555.8337519581646)]</t>
-  </si>
-  <si>
-    <t>[np.float64(201.04807615999476), np.float64(192.81473571328945)]</t>
-  </si>
-  <si>
-    <t>[np.float64(397.9998214816739), np.float64(-86.35945871544197)]</t>
-  </si>
-  <si>
-    <t>[np.float64(200.27799373639732), np.float64(241.91956896292265)]</t>
-  </si>
-  <si>
-    <t>[np.float64(292.39196816217407), np.float64(578.7674699391373)]</t>
-  </si>
-  <si>
-    <t>[np.float64(745.289793232335), np.float64(-358.5223358682557)]</t>
-  </si>
-  <si>
-    <t>[np.float64(150.326140676436), np.float64(256.7806592210702)]</t>
-  </si>
-  <si>
-    <t>[np.float64(928.8842486621654), np.float64(343.99162310595966)]</t>
-  </si>
-  <si>
-    <t>[np.float64(187.99771032435132), np.float64(-92.3441060052603)]</t>
-  </si>
-  <si>
-    <t>[np.float64(225.2663300423041), np.float64(196.87694822987726)]</t>
-  </si>
-  <si>
-    <t>[np.float64(802.7473753748001), np.float64(359.76934634556176)]</t>
-  </si>
-  <si>
-    <t>[np.float64(493.98085710757675), np.float64(108.1386784878249)]</t>
-  </si>
-  <si>
-    <t>[np.float64(337.74824349289366), np.float64(-156.0160940443667)]</t>
-  </si>
-  <si>
-    <t>[np.float64(667.4801443764529), np.float64(-501.9792175886932)]</t>
-  </si>
-  <si>
-    <t>[np.float64(830.9471364704948), np.float64(149.4657458211251)]</t>
-  </si>
-  <si>
-    <t>[np.float64(930.7850062375654), np.float64(261.5468137169172)]</t>
-  </si>
-  <si>
-    <t>[np.float64(866.9751331088404), np.float64(367.20521429907876)]</t>
-  </si>
-  <si>
-    <t>[np.float64(15.62257251054), np.float64(3.5602678290931635)]</t>
-  </si>
-  <si>
-    <t>[np.float64(508.95343345051936), np.float64(81.1204076334443)]</t>
-  </si>
-  <si>
-    <t>[np.float64(89.11005297877372), np.float64(-53.1664752734481)]</t>
-  </si>
-  <si>
-    <t>[np.float64(169.8103702793804), np.float64(331.5437778029975)]</t>
-  </si>
-  <si>
-    <t>[np.float64(386.7323892458543), np.float64(121.09938602909199)]</t>
-  </si>
-  <si>
-    <t>[np.float64(341.6356361369767), np.float64(-425.1547970605052)]</t>
-  </si>
-  <si>
-    <t>[np.float64(619.7426305216503), np.float64(256.4684004295783)]</t>
-  </si>
-  <si>
-    <t>[np.float64(642.4986459199968), np.float64(-411.93771201642505)]</t>
-  </si>
-  <si>
-    <t>[np.float64(221.9483227389798), np.float64(257.2898595550015)]</t>
-  </si>
-  <si>
-    <t>[np.float64(561.4950636675038), np.float64(-55.08316212188254)]</t>
-  </si>
-  <si>
-    <t>[np.float64(300.6960694098374), np.float64(-132.3878155150523)]</t>
-  </si>
-  <si>
-    <t>[np.float64(790.1194278259005), np.float64(-339.8845644033425)]</t>
-  </si>
-  <si>
-    <t>[np.float64(900.7053808897239), np.float64(-331.7535584247289)]</t>
-  </si>
-  <si>
-    <t>[np.float64(399.0460473745742), np.float64(395.0940584674488)]</t>
-  </si>
-  <si>
-    <t>[np.float64(838.7061635355208), np.float64(-153.20410523430763)]</t>
-  </si>
-  <si>
-    <t>[np.float64(651.5354138059496), np.float64(415.59504763485916)]</t>
-  </si>
-  <si>
-    <t>[np.float64(465.88566383828766), np.float64(-462.8492836633757)]</t>
-  </si>
-  <si>
-    <t>[np.float64(653.1761981329661), np.float64(90.90724243174941)]</t>
-  </si>
-  <si>
-    <t>[np.float64(50.85139195048127), np.float64(35.03654759410426)]</t>
-  </si>
-  <si>
-    <t>[np.float64(976.361840919758), np.float64(-164.39222829581593)]</t>
-  </si>
-  <si>
-    <t>[np.float64(230.71131253635392), np.float64(173.02000170475492)]</t>
-  </si>
-  <si>
-    <t>[np.float64(134.9896233404575), np.float64(398.76418707083906)]</t>
-  </si>
-  <si>
-    <t>[np.float64(572.4531550476262), np.float64(-391.47827812759766)]</t>
-  </si>
-  <si>
-    <t>[np.float64(907.5276808571431), np.float64(-501.96944871533816)]</t>
-  </si>
-  <si>
-    <t>[np.float64(662.9857527765718), np.float64(94.13177390556223)]</t>
-  </si>
-  <si>
-    <t>[np.float64(692.997785029182), np.float64(332.26549996580445)]</t>
-  </si>
-  <si>
-    <t>[np.float64(381.5924603587628), np.float64(152.9358653057849)]</t>
-  </si>
-  <si>
-    <t>[np.float64(340.2944220254537), np.float64(398.1981651158104)]</t>
-  </si>
-  <si>
-    <t>[np.float64(661.9650568351917), np.float64(506.0270779180878)]</t>
-  </si>
-  <si>
-    <t>[np.float64(223.6951422273915), np.float64(381.7542548651056)]</t>
-  </si>
-  <si>
-    <t>[np.float64(479.29689346500857), np.float64(290.32137186130194)]</t>
-  </si>
-  <si>
-    <t>[np.float64(303.4951814843018), np.float64(304.39400892973936)]</t>
-  </si>
-  <si>
-    <t>[np.float64(286.8992026400663), np.float64(-545.0376572844929)]</t>
-  </si>
-  <si>
-    <t>[np.float64(500.6467074775497), np.float64(-518.0845606223032)]</t>
-  </si>
-  <si>
-    <t>[np.float64(943.1024333249151), np.float64(-165.96037940266712)]</t>
-  </si>
-  <si>
-    <t>[np.float64(84.79091563826002), np.float64(537.6370514382795)]</t>
-  </si>
-  <si>
-    <t>[np.float64(280.62364029134113), np.float64(-221.09653817828632)]</t>
-  </si>
-  <si>
-    <t>[np.float64(691.3518585461292), np.float64(327.2399316595738)]</t>
-  </si>
-  <si>
-    <t>[np.float64(347.91520488274153), np.float64(451.48727276787076)]</t>
-  </si>
-  <si>
-    <t>[np.float64(619.5274519760125), np.float64(-393.86494122334057)]</t>
-  </si>
-  <si>
-    <t>[np.float64(923.4696837080037), np.float64(464.545547974644)]</t>
-  </si>
-  <si>
-    <t>[np.float64(143.5552177825924), np.float64(-453.8935651555712)]</t>
-  </si>
-  <si>
-    <t>[np.float64(234.33861752809148), np.float64(457.70232799162886)]</t>
-  </si>
-  <si>
-    <t>[np.float64(999.4480521958579), np.float64(-134.34840780348196)]</t>
-  </si>
-  <si>
-    <t>[np.float64(695.7600549382835), np.float64(-508.5872564067859)]</t>
-  </si>
-  <si>
-    <t>[np.float64(419.05181733299037), np.float64(-363.2194677208251)]</t>
-  </si>
-  <si>
-    <t>[np.float64(279.4207033965117), np.float64(-2.4400441524838925)]</t>
-  </si>
-  <si>
-    <t>[np.float64(445.96492883849413), np.float64(580.5736898507489)]</t>
-  </si>
-  <si>
-    <t>[np.float64(42.64676792607236), np.float64(525.0605242918493)]</t>
-  </si>
-  <si>
-    <t>[np.float64(178.81634836523043), np.float64(-208.3465521724234)]</t>
-  </si>
-  <si>
-    <t>[np.float64(388.22409112677656), np.float64(441.6708120586045)]</t>
-  </si>
-  <si>
-    <t>[np.float64(487.51818927448585), np.float64(-357.4202439553601)]</t>
-  </si>
-  <si>
-    <t>[np.float64(972.5204325822779), np.float64(-505.1727330250324)]</t>
-  </si>
-  <si>
-    <t>[np.float64(768.4056693044613), np.float64(-383.5506952416093)]</t>
-  </si>
-  <si>
-    <t>[np.float64(630.2556169901363), np.float64(559.7883859650578)]</t>
-  </si>
-  <si>
-    <t>[np.float64(316.232708034652), np.float64(-378.1838823583427)]</t>
-  </si>
-  <si>
-    <t>[np.float64(254.63577290469829), np.float64(242.25852774050713)]</t>
-  </si>
-  <si>
-    <t>[np.float64(0.10462947605216488), np.float64(49.72772159877172)]</t>
-  </si>
-  <si>
-    <t>[np.float64(434.49819915580304), np.float64(64.14089400242813)]</t>
-  </si>
-  <si>
-    <t>[np.float64(856.8816249495046), np.float64(-266.41081637387856)]</t>
-  </si>
-  <si>
-    <t>[np.float64(883.813311347993), np.float64(-383.0736404586047)]</t>
-  </si>
-  <si>
-    <t>[np.float64(240.68385898943677), np.float64(334.42377074696446)]</t>
-  </si>
-  <si>
-    <t>[np.float64(330.0895841460839), np.float64(-223.68039364857975)]</t>
-  </si>
-  <si>
-    <t>[np.float64(644.9578746233767), np.float64(-580.7636261007169)]</t>
-  </si>
-  <si>
-    <t>[np.float64(314.6939069381148), np.float64(521.0161485522535)]</t>
-  </si>
-  <si>
-    <t>[np.float64(979.0200431464243), np.float64(-573.8851249961119)]</t>
-  </si>
-  <si>
-    <t>[np.float64(301.56013646910617), np.float64(-114.7448342157536)]</t>
-  </si>
-  <si>
-    <t>[np.float64(863.0673124300577), np.float64(-489.81338444122827)]</t>
-  </si>
-  <si>
-    <t>[np.float64(680.7631321110841), np.float64(432.8765970551335)]</t>
-  </si>
-  <si>
-    <t>[np.float64(744.1734100719563), np.float64(421.62057774895607)]</t>
-  </si>
-  <si>
-    <t>[np.float64(558.8020776819494), np.float64(-350.7611949669595)]</t>
-  </si>
-  <si>
-    <t>[np.float64(471.8696092436424), np.float64(276.9080396408268)]</t>
-  </si>
-  <si>
-    <t>[np.float64(323.09038169512837), np.float64(-268.2712929232998)]</t>
-  </si>
-  <si>
-    <t>[np.float64(250.48169281590305), np.float64(372.841892301797)]</t>
-  </si>
-  <si>
-    <t>[np.float64(987.4704105486879), np.float64(-553.7950921427349)]</t>
-  </si>
-  <si>
-    <t>[np.float64(930.5326757964882), np.float64(-223.33806908852722)]</t>
-  </si>
-  <si>
-    <t>[np.float64(809.2207065837875), np.float64(-526.9994249731483)]</t>
-  </si>
-  <si>
-    <t>[np.float64(946.5250513579972), np.float64(-351.1195660278637)]</t>
-  </si>
-  <si>
-    <t>[np.float64(958.8356738460433), np.float64(365.7152448634962)]</t>
-  </si>
-  <si>
-    <t>[np.float64(225.42106008131267), np.float64(185.6919727826804)]</t>
-  </si>
-  <si>
-    <t>[np.float64(782.0925973363343), np.float64(536.7028050106087)]</t>
-  </si>
-  <si>
-    <t>[np.float64(876.2072860435984), np.float64(2.5855708975985863)]</t>
-  </si>
-  <si>
-    <t>[np.float64(64.54764882936348), np.float64(557.216755934943)]</t>
-  </si>
-  <si>
-    <t>[np.float64(613.933265151042), np.float64(535.375175928157)]</t>
-  </si>
-  <si>
-    <t>[np.float64(699.6315629765755), np.float64(498.6084705540013)]</t>
-  </si>
-  <si>
-    <t>[np.float64(648.5507916251217), np.float64(-474.3701904819512)]</t>
-  </si>
-  <si>
-    <t>[np.float64(363.93026776683854), np.float64(575.908615572652)]</t>
-  </si>
-  <si>
-    <t>[np.float64(814.3767622793073), np.float64(-70.94505584653211)]</t>
-  </si>
-  <si>
-    <t>[np.float64(453.62932826624933), np.float64(182.00349187822758)]</t>
-  </si>
-  <si>
-    <t>[np.float64(987.1675247333733), np.float64(-598.516926489431)]</t>
-  </si>
-  <si>
-    <t>[np.float64(278.96421339518685), np.float64(306.20653431934534)]</t>
-  </si>
-  <si>
-    <t>[np.float64(924.1480830664975), np.float64(-210.12302365584787)]</t>
-  </si>
-  <si>
-    <t>[np.float64(537.0060309468325), np.float64(53.888846417342734)]</t>
-  </si>
-  <si>
-    <t>[np.float64(550.036921238473), np.float64(287.52757003334705)]</t>
-  </si>
-  <si>
-    <t>[np.float64(742.3926624797124), np.float64(78.23070215859866)]</t>
-  </si>
-  <si>
-    <t>[np.float64(485.4578137683837), np.float64(-425.2203679785962)]</t>
-  </si>
-  <si>
-    <t>[np.float64(924.6236156316123), np.float64(-473.5798089214058)]</t>
-  </si>
-  <si>
-    <t>[np.float64(250.48389509256853), np.float64(-397.23488150035325)]</t>
-  </si>
-  <si>
-    <t>[np.float64(895.8534123565253), np.float64(51.19933248081804)]</t>
-  </si>
-  <si>
-    <t>[np.float64(123.38068867713359), np.float64(-60.35122703185846)]</t>
-  </si>
-  <si>
-    <t>[np.float64(877.7315485595819), np.float64(-244.63080732323976)]</t>
-  </si>
-  <si>
-    <t>[np.float64(683.1453380867817), np.float64(-498.49668468377513)]</t>
-  </si>
-  <si>
-    <t>[np.float64(347.0805421927571), np.float64(-402.3222282529369)]</t>
-  </si>
-  <si>
-    <t>[np.float64(167.67060838780367), np.float64(80.90360638919958)]</t>
-  </si>
-  <si>
-    <t>[np.float64(412.62144757705653), np.float64(-389.58319138071465)]</t>
-  </si>
-  <si>
-    <t>[np.float64(633.5972535921784), np.float64(556.888455791611)]</t>
-  </si>
-  <si>
-    <t>[np.float64(957.1156209314926), np.float64(-461.579051507328)]</t>
-  </si>
-  <si>
-    <t>[np.float64(75.47592023110428), np.float64(246.2339480483945)]</t>
-  </si>
-  <si>
-    <t>[np.float64(896.0945749424918), np.float64(-360.0161329260154)]</t>
-  </si>
-  <si>
-    <t>[np.float64(513.1448722466738), np.float64(-597.7305087312882)]</t>
-  </si>
-  <si>
-    <t>[np.float64(836.6428305569606), np.float64(-92.44973609712395)]</t>
-  </si>
-  <si>
-    <t>[np.float64(459.165375914542), np.float64(-6.761279507111567)]</t>
-  </si>
-  <si>
-    <t>[np.float64(961.2225623595536), np.float64(-506.5824000325357)]</t>
-  </si>
-  <si>
-    <t>[np.float64(16.10009213551877), np.float64(-371.1193013460861)]</t>
-  </si>
-  <si>
-    <t>[np.float64(122.20082415751732), np.float64(-587.2005981936452)]</t>
-  </si>
-  <si>
-    <t>[np.float64(460.73559943611855), np.float64(-189.24045481287573)]</t>
-  </si>
-  <si>
-    <t>[np.float64(453.7614393565789), np.float64(14.822842570461262)]</t>
-  </si>
-  <si>
-    <t>[np.float64(98.12496582410279), np.float64(-593.9601034772412)]</t>
-  </si>
-  <si>
-    <t>[np.float64(166.75180604716567), np.float64(164.26361995561933)]</t>
-  </si>
-  <si>
-    <t>[np.float64(702.9309442855736), np.float64(247.84335146945682)]</t>
-  </si>
-  <si>
-    <t>[np.float64(628.8517874508265), np.float64(-552.4466595409465)]</t>
+    <t>[np.float64(928.522750449942), np.float64(357.11631933508613)]</t>
+  </si>
+  <si>
+    <t>[np.float64(328.1906122605378), np.float64(-150.4104187154934)]</t>
+  </si>
+  <si>
+    <t>[np.float64(825.7836939079865), np.float64(493.9472206882708)]</t>
+  </si>
+  <si>
+    <t>[np.float64(765.3598250904188), np.float64(-451.28985194011904)]</t>
+  </si>
+  <si>
+    <t>[np.float64(763.5597990551202), np.float64(-249.22865101499127)]</t>
+  </si>
+  <si>
+    <t>[np.float64(752.992575851932), np.float64(599.1703265540095)]</t>
+  </si>
+  <si>
+    <t>[np.float64(941.6777531606919), np.float64(389.386714994303)]</t>
+  </si>
+  <si>
+    <t>[np.float64(599.2425638580712), np.float64(475.0782596457384)]</t>
+  </si>
+  <si>
+    <t>[np.float64(53.67946856430128), np.float64(-259.93074525570574)]</t>
+  </si>
+  <si>
+    <t>[np.float64(928.5706554209611), np.float64(-330.42545122443823)]</t>
+  </si>
+  <si>
+    <t>[np.float64(960.1548290952483), np.float64(-182.0154597079527)]</t>
+  </si>
+  <si>
+    <t>[np.float64(634.2409848922152), np.float64(86.22863481524848)]</t>
+  </si>
+  <si>
+    <t>[np.float64(154.33535762537454), np.float64(297.0784871972553)]</t>
+  </si>
+  <si>
+    <t>[np.float64(141.22257278741358), np.float64(137.33329485120078)]</t>
+  </si>
+  <si>
+    <t>[np.float64(627.0234470006698), np.float64(-193.66434172374318)]</t>
+  </si>
+  <si>
+    <t>[np.float64(694.0807146709218), np.float64(-263.77851385573354)]</t>
+  </si>
+  <si>
+    <t>[np.float64(431.7889641779353), np.float64(-121.26088639184348)]</t>
+  </si>
+  <si>
+    <t>[np.float64(646.2356640980007), np.float64(-391.78180816294775)]</t>
+  </si>
+  <si>
+    <t>[np.float64(845.6972217251731), np.float64(402.9910025791137)]</t>
+  </si>
+  <si>
+    <t>[np.float64(184.74863028309386), np.float64(282.43076751745343)]</t>
+  </si>
+  <si>
+    <t>[np.float64(337.66687609230326), np.float64(-76.48443667449362)]</t>
+  </si>
+  <si>
+    <t>[np.float64(59.02698661577266), np.float64(-177.82013306860415)]</t>
+  </si>
+  <si>
+    <t>[np.float64(690.9229722647661), np.float64(-310.1687251175941)]</t>
+  </si>
+  <si>
+    <t>[np.float64(633.5756417563811), np.float64(-12.366503857014663)]</t>
+  </si>
+  <si>
+    <t>[np.float64(886.1418433827093), np.float64(70.63990959676255)]</t>
+  </si>
+  <si>
+    <t>[np.float64(83.3534758292891), np.float64(439.3306159916831)]</t>
+  </si>
+  <si>
+    <t>[np.float64(949.7863119279687), np.float64(266.64783935039793)]</t>
+  </si>
+  <si>
+    <t>[np.float64(473.8530038695944), np.float64(-376.7290645529582)]</t>
+  </si>
+  <si>
+    <t>[np.float64(471.80521468647964), np.float64(-82.6924911662934)]</t>
+  </si>
+  <si>
+    <t>[np.float64(349.4534135847852), np.float64(211.2091024738902)]</t>
+  </si>
+  <si>
+    <t>[np.float64(13.749581161124347), np.float64(-436.1693715028731)]</t>
+  </si>
+  <si>
+    <t>[np.float64(474.49024844232565), np.float64(-279.5694857514411)]</t>
+  </si>
+  <si>
+    <t>[np.float64(196.97712176840344), np.float64(-126.94369068401801)]</t>
+  </si>
+  <si>
+    <t>[np.float64(579.2195804405037), np.float64(475.1718419713584)]</t>
+  </si>
+  <si>
+    <t>[np.float64(312.21771378419203), np.float64(454.288442496387)]</t>
+  </si>
+  <si>
+    <t>[np.float64(716.5835757890447), np.float64(-474.99476611802237)]</t>
+  </si>
+  <si>
+    <t>[np.float64(795.3060838366777), np.float64(4.90929396870979)]</t>
+  </si>
+  <si>
+    <t>[np.float64(201.95559830131836), np.float64(-320.63737721214443)]</t>
+  </si>
+  <si>
+    <t>[np.float64(836.1916717055783), np.float64(33.991056197461035)]</t>
+  </si>
+  <si>
+    <t>[np.float64(862.8808112278259), np.float64(269.0281806322623)]</t>
+  </si>
+  <si>
+    <t>[np.float64(637.7593249162057), np.float64(587.7587114131784)]</t>
+  </si>
+  <si>
+    <t>[np.float64(534.6050964000126), np.float64(12.197668085459895)]</t>
+  </si>
+  <si>
+    <t>[np.float64(21.75527505903341), np.float64(-166.85049891921165)]</t>
+  </si>
+  <si>
+    <t>[np.float64(439.2414566091959), np.float64(99.05353360630454)]</t>
+  </si>
+  <si>
+    <t>[np.float64(512.3840958798116), np.float64(-343.1338910351759)]</t>
+  </si>
+  <si>
+    <t>[np.float64(695.5793747076299), np.float64(-7.719028734181393)]</t>
+  </si>
+  <si>
+    <t>[np.float64(157.07939650670576), np.float64(481.9785874622023)]</t>
+  </si>
+  <si>
+    <t>[np.float64(356.60909549671084), np.float64(227.24784666798791)]</t>
+  </si>
+  <si>
+    <t>[np.float64(352.00436879024653), np.float64(36.963309076624796)]</t>
+  </si>
+  <si>
+    <t>[np.float64(833.7980386711588), np.float64(-454.03270766049275)]</t>
+  </si>
+  <si>
+    <t>[np.float64(982.2204446249965), np.float64(-335.51634494115194)]</t>
+  </si>
+  <si>
+    <t>[np.float64(708.1910649954052), np.float64(96.41252457790313)]</t>
+  </si>
+  <si>
+    <t>[np.float64(535.3800981162716), np.float64(21.59450996184171)]</t>
+  </si>
+  <si>
+    <t>[np.float64(242.62996334312447), np.float64(-349.45052552969383)]</t>
+  </si>
+  <si>
+    <t>[np.float64(248.82171401527097), np.float64(260.4931648562541)]</t>
+  </si>
+  <si>
+    <t>[np.float64(806.5441168016409), np.float64(482.09583441364043)]</t>
+  </si>
+  <si>
+    <t>[np.float64(90.60229468691993), np.float64(56.50592106096053)]</t>
+  </si>
+  <si>
+    <t>[np.float64(534.2950138899998), np.float64(545.9413005972601)]</t>
+  </si>
+  <si>
+    <t>[np.float64(182.2764009036616), np.float64(-441.0357321518922)]</t>
+  </si>
+  <si>
+    <t>[np.float64(882.3786271689646), np.float64(365.5069124008552)]</t>
+  </si>
+  <si>
+    <t>[np.float64(412.27972450966354), np.float64(556.1457155335052)]</t>
+  </si>
+  <si>
+    <t>[np.float64(546.5079461376673), np.float64(-271.7930574082238)]</t>
+  </si>
+  <si>
+    <t>[np.float64(255.75234979458196), np.float64(363.49907191962836)]</t>
+  </si>
+  <si>
+    <t>[np.float64(267.0422096276385), np.float64(348.3074492247589)]</t>
+  </si>
+  <si>
+    <t>[np.float64(506.23031337778156), np.float64(532.3832396647163)]</t>
+  </si>
+  <si>
+    <t>[np.float64(518.2158017456842), np.float64(-523.9147528834327)]</t>
+  </si>
+  <si>
+    <t>[np.float64(504.84934943927175), np.float64(-594.3316532311756)]</t>
+  </si>
+  <si>
+    <t>[np.float64(659.6669159171863), np.float64(178.51379669386324)]</t>
+  </si>
+  <si>
+    <t>[np.float64(162.11903324633238), np.float64(-209.14345378325595)]</t>
+  </si>
+  <si>
+    <t>[np.float64(272.45887419574876), np.float64(-150.20939453580166)]</t>
+  </si>
+  <si>
+    <t>[np.float64(841.9160455711844), np.float64(527.1959540264431)]</t>
+  </si>
+  <si>
+    <t>[np.float64(681.0943848067795), np.float64(444.8916815958951)]</t>
+  </si>
+  <si>
+    <t>[np.float64(957.7428212457634), np.float64(-496.92933864701104)]</t>
+  </si>
+  <si>
+    <t>[np.float64(289.597203286891), np.float64(-573.3542307787962)]</t>
+  </si>
+  <si>
+    <t>[np.float64(470.39782535685714), np.float64(350.3084100413058)]</t>
+  </si>
+  <si>
+    <t>[np.float64(67.43166475920293), np.float64(-278.83915233181733)]</t>
+  </si>
+  <si>
+    <t>[np.float64(38.37131514111625), np.float64(-210.02758714785818)]</t>
+  </si>
+  <si>
+    <t>[np.float64(562.666639064167), np.float64(-281.64878507145164)]</t>
+  </si>
+  <si>
+    <t>[np.float64(300.39538242740105), np.float64(311.6008032595919)]</t>
+  </si>
+  <si>
+    <t>[np.float64(916.1339179717088), np.float64(95.93068689465667)]</t>
+  </si>
+  <si>
+    <t>[np.float64(394.73953116953066), np.float64(497.2653068392626)]</t>
+  </si>
+  <si>
+    <t>[np.float64(525.9442968197137), np.float64(256.3724230490749)]</t>
+  </si>
+  <si>
+    <t>[np.float64(588.1870404549738), np.float64(535.2509615396727)]</t>
+  </si>
+  <si>
+    <t>[np.float64(790.0954820838413), np.float64(161.2236314304921)]</t>
+  </si>
+  <si>
+    <t>[np.float64(994.8760760682513), np.float64(595.4767164758841)]</t>
+  </si>
+  <si>
+    <t>[np.float64(227.02983049952385), np.float64(-86.86686818755481)]</t>
+  </si>
+  <si>
+    <t>[np.float64(748.7650974923445), np.float64(-116.58818809270116)]</t>
+  </si>
+  <si>
+    <t>[np.float64(952.1876235634097), np.float64(-330.3231663989621)]</t>
+  </si>
+  <si>
+    <t>[np.float64(411.1265907180378), np.float64(548.2901765723338)]</t>
+  </si>
+  <si>
+    <t>[np.float64(510.83388801644514), np.float64(79.19226625650981)]</t>
+  </si>
+  <si>
+    <t>[np.float64(906.7199969147991), np.float64(-359.08081255920445)]</t>
+  </si>
+  <si>
+    <t>[np.float64(426.9566720064424), np.float64(442.4008203479541)]</t>
+  </si>
+  <si>
+    <t>[np.float64(684.8702256277573), np.float64(189.41346560359773)]</t>
+  </si>
+  <si>
+    <t>[np.float64(428.87807222175644), np.float64(148.09071213703737)]</t>
+  </si>
+  <si>
+    <t>[np.float64(843.3584167580376), np.float64(-519.1564069703579)]</t>
+  </si>
+  <si>
+    <t>[np.float64(221.40686386222174), np.float64(-165.48037126613428)]</t>
+  </si>
+  <si>
+    <t>[np.float64(14.70026629069887), np.float64(-557.5735284673864)]</t>
+  </si>
+  <si>
+    <t>[np.float64(504.58985639772135), np.float64(-109.86733786270986)]</t>
+  </si>
+  <si>
+    <t>[np.float64(168.10136602202797), np.float64(-319.3330885649067)]</t>
+  </si>
+  <si>
+    <t>[np.float64(552.3758166308496), np.float64(-545.419169254042)]</t>
+  </si>
+  <si>
+    <t>[np.float64(199.94900423945694), np.float64(-313.6002870906283)]</t>
+  </si>
+  <si>
+    <t>[np.float64(714.7847604657846), np.float64(472.4240214695126)]</t>
+  </si>
+  <si>
+    <t>[np.float64(138.7594329236328), np.float64(164.36922642898708)]</t>
+  </si>
+  <si>
+    <t>[np.float64(235.0371612163291), np.float64(-424.5810220592991)]</t>
+  </si>
+  <si>
+    <t>[np.float64(391.1644060829268), np.float64(-580.5824802161989)]</t>
+  </si>
+  <si>
+    <t>[np.float64(336.05449237835126), np.float64(509.75545047781)]</t>
+  </si>
+  <si>
+    <t>[np.float64(511.64156188055455), np.float64(595.8298311887565)]</t>
+  </si>
+  <si>
+    <t>[np.float64(968.1178388039448), np.float64(145.71434669837356)]</t>
+  </si>
+  <si>
+    <t>[np.float64(109.58852638055883), np.float64(-190.69144322429884)]</t>
+  </si>
+  <si>
+    <t>[np.float64(979.4702479850579), np.float64(-157.26896345459306)]</t>
+  </si>
+  <si>
+    <t>[np.float64(361.92494917160025), np.float64(-437.10919863757454)]</t>
+  </si>
+  <si>
+    <t>[np.float64(224.69022550089846), np.float64(-144.42332867593097)]</t>
+  </si>
+  <si>
+    <t>[np.float64(339.7899694816995), np.float64(181.13390437774615)]</t>
+  </si>
+  <si>
+    <t>[np.float64(535.7816677648751), np.float64(-209.0479178601188)]</t>
+  </si>
+  <si>
+    <t>[np.float64(342.50178273974865), np.float64(509.96065964134846)]</t>
+  </si>
+  <si>
+    <t>[np.float64(555.9810515434843), np.float64(129.35920438107712)]</t>
+  </si>
+  <si>
+    <t>[np.float64(338.43176813777296), np.float64(-505.9549375114143)]</t>
+  </si>
+  <si>
+    <t>[np.float64(641.2806916964972), np.float64(127.5701372443458)]</t>
+  </si>
+  <si>
+    <t>[np.float64(708.8614819520508), np.float64(-127.88709439666991)]</t>
+  </si>
+  <si>
+    <t>[np.float64(877.2254436440074), np.float64(-578.0133519176987)]</t>
+  </si>
+  <si>
+    <t>[np.float64(79.72137414469016), np.float64(314.6403229189159)]</t>
+  </si>
+  <si>
+    <t>[np.float64(872.716837679494), np.float64(391.9344857778922)]</t>
+  </si>
+  <si>
+    <t>[np.float64(28.16167329554076), np.float64(-441.56305985623226)]</t>
+  </si>
+  <si>
+    <t>[np.float64(673.1583766316865), np.float64(78.68178443949705)]</t>
+  </si>
+  <si>
+    <t>[np.float64(896.3198391535597), np.float64(18.250605650032867)]</t>
+  </si>
+  <si>
+    <t>[np.float64(849.7654764714612), np.float64(94.62479865017224)]</t>
+  </si>
+  <si>
+    <t>[np.float64(572.2412798982298), np.float64(-444.10170368807803)]</t>
+  </si>
+  <si>
+    <t>[np.float64(369.162531955851), np.float64(338.17943443599734)]</t>
+  </si>
+  <si>
+    <t>[np.float64(331.9672301140768), np.float64(-510.71722872682903)]</t>
+  </si>
+  <si>
+    <t>[np.float64(45.8759572961005), np.float64(340.34804119054206)]</t>
+  </si>
+  <si>
+    <t>[np.float64(355.68241303644163), np.float64(340.0695255773429)]</t>
+  </si>
+  <si>
+    <t>[np.float64(263.4752419593167), np.float64(-307.04556577481185)]</t>
+  </si>
+  <si>
+    <t>[np.float64(364.7854867205379), np.float64(357.63685508194203)]</t>
+  </si>
+  <si>
+    <t>[np.float64(410.6177863618747), np.float64(-335.53627229988683)]</t>
+  </si>
+  <si>
+    <t>[np.float64(843.10148861495), np.float64(-134.51998427259008)]</t>
+  </si>
+  <si>
+    <t>[np.float64(368.5272905626885), np.float64(338.96431673696895)]</t>
+  </si>
+  <si>
+    <t>[np.float64(274.23615344034323), np.float64(-302.26009868821666)]</t>
+  </si>
+  <si>
+    <t>[np.float64(779.5672668233051), np.float64(343.7217681054185)]</t>
+  </si>
+  <si>
+    <t>[np.float64(871.8771473395607), np.float64(134.77690959108315)]</t>
+  </si>
+  <si>
+    <t>[np.float64(780.2383927364405), np.float64(409.3594523641764)]</t>
+  </si>
+  <si>
+    <t>[np.float64(189.94162634088374), np.float64(449.361144169015)]</t>
+  </si>
+  <si>
+    <t>[np.float64(355.76767740196226), np.float64(19.919868916848145)]</t>
+  </si>
+  <si>
+    <t>[np.float64(29.37460568874295), np.float64(-385.9096375247389)]</t>
+  </si>
+  <si>
+    <t>[np.float64(971.4840400742931), np.float64(-304.1826500591734)]</t>
+  </si>
+  <si>
+    <t>[np.float64(530.3927054187325), np.float64(45.015952315801655)]</t>
+  </si>
+  <si>
+    <t>[np.float64(430.3861200185509), np.float64(46.128968936434376)]</t>
+  </si>
+  <si>
+    <t>[np.float64(610.8455724313475), np.float64(-366.7999417163816)]</t>
+  </si>
+  <si>
+    <t>[np.float64(741.2752619822568), np.float64(-546.139653941597)]</t>
+  </si>
+  <si>
+    <t>[np.float64(215.38577718084107), np.float64(-556.699012217757)]</t>
+  </si>
+  <si>
+    <t>[np.float64(349.9458612572377), np.float64(304.1597274319614)]</t>
+  </si>
+  <si>
+    <t>[np.float64(131.2560249711202), np.float64(246.72311693506526)]</t>
+  </si>
+  <si>
+    <t>[np.float64(397.5170563048116), np.float64(-242.40332094314005)]</t>
+  </si>
+  <si>
+    <t>[np.float64(244.64804299455355), np.float64(400.24011451703996)]</t>
+  </si>
+  <si>
+    <t>[np.float64(606.7489490810368), np.float64(393.3565451882422)]</t>
+  </si>
+  <si>
+    <t>[np.float64(802.374179061507), np.float64(336.62263360526606)]</t>
+  </si>
+  <si>
+    <t>[np.float64(114.95312354883858), np.float64(-542.3065539565406)]</t>
+  </si>
+  <si>
+    <t>[np.float64(134.9652498783608), np.float64(185.57733954172613)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.3851959094167725), np.float64(-95.57542243254517)]</t>
+  </si>
+  <si>
+    <t>[np.float64(965.6355732572052), np.float64(-289.41115881315625)]</t>
+  </si>
+  <si>
+    <t>[np.float64(960.7533786843219), np.float64(131.49678144905988)]</t>
+  </si>
+  <si>
+    <t>[np.float64(630.6354228522517), np.float64(-265.36265110167346)]</t>
+  </si>
+  <si>
+    <t>[np.float64(70.61730124114551), np.float64(144.98342052454598)]</t>
+  </si>
+  <si>
+    <t>[np.float64(130.879106409833), np.float64(55.3897700775434)]</t>
+  </si>
+  <si>
+    <t>[np.float64(359.9423937660126), np.float64(222.59619641268466)]</t>
+  </si>
+  <si>
+    <t>[np.float64(835.9721219544576), np.float64(-56.916966449965344)]</t>
+  </si>
+  <si>
+    <t>[np.float64(326.40260953916857), np.float64(474.6646252890964)]</t>
+  </si>
+  <si>
+    <t>[np.float64(686.3063564968053), np.float64(-266.88756131695675)]</t>
+  </si>
+  <si>
+    <t>[np.float64(137.90356957442984), np.float64(-516.9187827848652)]</t>
+  </si>
+  <si>
+    <t>[np.float64(671.8395757220432), np.float64(59.23014061810841)]</t>
+  </si>
+  <si>
+    <t>[np.float64(190.41000779226303), np.float64(-267.01634459111926)]</t>
+  </si>
+  <si>
+    <t>[np.float64(631.3791644739073), np.float64(389.1792688673072)]</t>
+  </si>
+  <si>
+    <t>[np.float64(619.2676450541175), np.float64(-299.4522030531618)]</t>
+  </si>
+  <si>
+    <t>[np.float64(648.9749172117183), np.float64(260.38178619388646)]</t>
+  </si>
+  <si>
+    <t>[np.float64(319.12054051042327), np.float64(522.5416973309354)]</t>
+  </si>
+  <si>
+    <t>[np.float64(990.3659428170041), np.float64(168.67193184550626)]</t>
+  </si>
+  <si>
+    <t>[np.float64(115.90058510515911), np.float64(368.56792663970987)]</t>
+  </si>
+  <si>
+    <t>[np.float64(723.7489561281282), np.float64(440.9113106483396)]</t>
+  </si>
+  <si>
+    <t>[np.float64(654.9694033310286), np.float64(-216.9096736265194)]</t>
+  </si>
+  <si>
+    <t>[np.float64(6.269857593537709), np.float64(459.1229716777741)]</t>
+  </si>
+  <si>
+    <t>[np.float64(593.9253052734525), np.float64(33.36563309543908)]</t>
+  </si>
+  <si>
+    <t>[np.float64(152.35508604782223), np.float64(-529.9259349945786)]</t>
+  </si>
+  <si>
+    <t>[np.float64(813.438193779783), np.float64(-480.3793462708842)]</t>
+  </si>
+  <si>
+    <t>[np.float64(322.658100960029), np.float64(-550.1255447305306)]</t>
+  </si>
+  <si>
+    <t>[np.float64(288.67527049739607), np.float64(-423.6056182039275)]</t>
+  </si>
+  <si>
+    <t>[np.float64(212.9396402010225), np.float64(-487.556821729524)]</t>
+  </si>
+  <si>
+    <t>[np.float64(592.6644330524531), np.float64(-212.94295637986835)]</t>
+  </si>
+  <si>
+    <t>[np.float64(652.071686753595), np.float64(-89.67037897842442)]</t>
+  </si>
+  <si>
+    <t>[np.float64(75.43697375934877), np.float64(-105.55048605877448)]</t>
+  </si>
+  <si>
+    <t>[np.float64(107.17208414919077), np.float64(376.83540800008336)]</t>
+  </si>
+  <si>
+    <t>[np.float64(555.2749725462967), np.float64(-532.6113155509997)]</t>
+  </si>
+  <si>
+    <t>[np.float64(507.95143786489507), np.float64(-525.4275431666151)]</t>
+  </si>
+  <si>
+    <t>[np.float64(348.4760274158254), np.float64(522.3707323439421)]</t>
+  </si>
+  <si>
+    <t>[np.float64(889.6166774034738), np.float64(13.684707346883897)]</t>
+  </si>
+  <si>
+    <t>[np.float64(493.65972644136605), np.float64(-175.90609317872736)]</t>
+  </si>
+  <si>
+    <t>[np.float64(698.758386381971), np.float64(-348.89602216402415)]</t>
+  </si>
+  <si>
+    <t>[np.float64(614.1025711048547), np.float64(335.33635159406583)]</t>
+  </si>
+  <si>
+    <t>[np.float64(932.96747920727), np.float64(-301.4051406748656)]</t>
+  </si>
+  <si>
+    <t>[np.float64(683.1197730394689), np.float64(-299.8922538170656)]</t>
+  </si>
+  <si>
+    <t>[np.float64(430.2602744892579), np.float64(91.79696547109256)]</t>
+  </si>
+  <si>
+    <t>[np.float64(69.88227174438234), np.float64(-527.3537829910747)]</t>
+  </si>
+  <si>
+    <t>[np.float64(459.2490189123963), np.float64(-17.741223318828247)]</t>
+  </si>
+  <si>
+    <t>[np.float64(842.1776301638633), np.float64(-514.0793995346331)]</t>
+  </si>
+  <si>
+    <t>[np.float64(937.1288040261087), np.float64(-108.92831094818683)]</t>
+  </si>
+  <si>
+    <t>[np.float64(41.232575174415146), np.float64(580.9637380346928)]</t>
+  </si>
+  <si>
+    <t>[np.float64(215.2423502645121), np.float64(134.55660938429992)]</t>
+  </si>
+  <si>
+    <t>[np.float64(518.3528229103377), np.float64(485.5228392443071)]</t>
+  </si>
+  <si>
+    <t>[np.float64(747.7296703335435), np.float64(-312.5358581266792)]</t>
+  </si>
+  <si>
+    <t>[np.float64(150.92112714101458), np.float64(407.75813509243085)]</t>
+  </si>
+  <si>
+    <t>[np.float64(574.0027709796217), np.float64(135.80183026803672)]</t>
+  </si>
+  <si>
+    <t>[np.float64(652.0546425369212), np.float64(-292.9251576143107)]</t>
+  </si>
+  <si>
+    <t>[np.float64(868.0374992105512), np.float64(108.94944152357823)]</t>
+  </si>
+  <si>
+    <t>[np.float64(226.85409926726297), np.float64(428.8042587141574)]</t>
+  </si>
+  <si>
+    <t>[np.float64(377.7446703207794), np.float64(-269.74441465063626)]</t>
+  </si>
+  <si>
+    <t>[np.float64(207.22626771962814), np.float64(-121.85543967852573)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.752977594188132), np.float64(-226.59440791720925)]</t>
+  </si>
+  <si>
+    <t>[np.float64(286.1277173631226), np.float64(-554.7843919597146)]</t>
+  </si>
+  <si>
+    <t>[np.float64(472.95092362278615), np.float64(488.26951745232645)]</t>
+  </si>
+  <si>
+    <t>[np.float64(58.82448267417762), np.float64(-455.56200481342665)]</t>
+  </si>
+  <si>
+    <t>[np.float64(985.3018074200859), np.float64(-255.7541740945303)]</t>
+  </si>
+  <si>
+    <t>[np.float64(912.8152875415017), np.float64(354.70878791883047)]</t>
+  </si>
+  <si>
+    <t>[np.float64(25.86973929005898), np.float64(467.58784398060357)]</t>
+  </si>
+  <si>
+    <t>[np.float64(665.8484261767198), np.float64(436.05002200978515)]</t>
+  </si>
+  <si>
+    <t>[np.float64(936.2002091903208), np.float64(539.9699023308697)]</t>
+  </si>
+  <si>
+    <t>[np.float64(976.0936819835491), np.float64(-379.31634623889147)]</t>
+  </si>
+  <si>
+    <t>[np.float64(623.1330053545394), np.float64(-588.4235015374069)]</t>
+  </si>
+  <si>
+    <t>[np.float64(704.6055124429195), np.float64(69.31432758408062)]</t>
+  </si>
+  <si>
+    <t>[np.float64(928.8439885684155), np.float64(98.00026772186538)]</t>
+  </si>
+  <si>
+    <t>[np.float64(331.05669936494144), np.float64(-136.17905582632852)]</t>
+  </si>
+  <si>
+    <t>[np.float64(742.6486315373993), np.float64(-404.8965458651262)]</t>
+  </si>
+  <si>
+    <t>[np.float64(953.5274889686599), np.float64(190.30582915251694)]</t>
+  </si>
+  <si>
+    <t>[np.float64(187.23644451594478), np.float64(164.67500006081173)]</t>
+  </si>
+  <si>
+    <t>[np.float64(118.49030793896654), np.float64(-240.7267208429359)]</t>
+  </si>
+  <si>
+    <t>[np.float64(322.5889158166617), np.float64(-496.35082848180133)]</t>
+  </si>
+  <si>
+    <t>[np.float64(617.0916090497007), np.float64(342.0225601689831)]</t>
+  </si>
+  <si>
+    <t>[np.float64(892.6681087602675), np.float64(145.4168419402955)]</t>
+  </si>
+  <si>
+    <t>[np.float64(312.40708695125653), np.float64(278.67631592773466)]</t>
+  </si>
+  <si>
+    <t>[np.float64(499.4857812686258), np.float64(126.01639776413492)]</t>
+  </si>
+  <si>
+    <t>[np.float64(649.7013476456219), np.float64(502.3887475797808)]</t>
+  </si>
+  <si>
+    <t>[np.float64(640.3637004374261), np.float64(-248.21039010441683)]</t>
+  </si>
+  <si>
+    <t>[np.float64(8.55156509822541), np.float64(126.99173689816212)]</t>
+  </si>
+  <si>
+    <t>[np.float64(415.4742959696321), np.float64(365.2759700454826)]</t>
+  </si>
+  <si>
+    <t>[np.float64(962.8971381775303), np.float64(20.867806831878738)]</t>
+  </si>
+  <si>
+    <t>[np.float64(415.5171547525981), np.float64(-267.98669617789)]</t>
+  </si>
+  <si>
+    <t>[np.float64(70.71313729654227), np.float64(81.22499223486523)]</t>
+  </si>
+  <si>
+    <t>[np.float64(273.7619467938256), np.float64(85.55010421900079)]</t>
+  </si>
+  <si>
+    <t>[np.float64(506.5221884430654), np.float64(508.1977766805642)]</t>
+  </si>
+  <si>
+    <t>[np.float64(713.6780988636708), np.float64(362.7941673159204)]</t>
+  </si>
+  <si>
+    <t>[np.float64(215.3227706727977), np.float64(-593.7780367264622)]</t>
+  </si>
+  <si>
+    <t>[np.float64(277.6960233919377), np.float64(-272.6149639349972)]</t>
+  </si>
+  <si>
+    <t>[np.float64(399.0334787501124), np.float64(-523.0069653921297)]</t>
+  </si>
+  <si>
+    <t>[np.float64(942.0955768514422), np.float64(-230.6479605622232)]</t>
+  </si>
+  <si>
+    <t>[np.float64(872.7448975391319), np.float64(-172.7895734462166)]</t>
+  </si>
+  <si>
+    <t>[np.float64(197.44299857588655), np.float64(-56.40599912614209)]</t>
+  </si>
+  <si>
+    <t>[np.float64(716.1213182297626), np.float64(265.6574724407536)]</t>
+  </si>
+  <si>
+    <t>[np.float64(908.3021455015127), np.float64(385.27686798412753)]</t>
+  </si>
+  <si>
+    <t>[np.float64(578.3021939661603), np.float64(-40.431568498893625)]</t>
+  </si>
+  <si>
+    <t>[np.float64(356.5000228243328), np.float64(-254.96313235019153)]</t>
+  </si>
+  <si>
+    <t>[np.float64(124.22432308941644), np.float64(-448.06895778426895)]</t>
+  </si>
+  <si>
+    <t>[np.float64(907.1314904035778), np.float64(357.9251800660071)]</t>
+  </si>
+  <si>
+    <t>[np.float64(391.13345656503276), np.float64(-130.8275175727627)]</t>
+  </si>
+  <si>
+    <t>[np.float64(815.1643480875895), np.float64(476.15725241216137)]</t>
+  </si>
+  <si>
+    <t>[np.float64(80.95591803753499), np.float64(125.36201617463814)]</t>
+  </si>
+  <si>
+    <t>[np.float64(238.98309187280177), np.float64(403.65053819835)]</t>
+  </si>
+  <si>
+    <t>[np.float64(753.2412944536138), np.float64(-267.74121388615833)]</t>
+  </si>
+  <si>
+    <t>[np.float64(776.8467825304475), np.float64(202.25265972669524)]</t>
+  </si>
+  <si>
+    <t>[np.float64(126.1219348776893), np.float64(563.4087347346979)]</t>
+  </si>
+  <si>
+    <t>[np.float64(912.6053614967032), np.float64(-486.8576197789245)]</t>
+  </si>
+  <si>
+    <t>[np.float64(87.4802360248551), np.float64(-359.9021629882351)]</t>
+  </si>
+  <si>
+    <t>[np.float64(812.7372992262178), np.float64(114.12432830752391)]</t>
+  </si>
+  <si>
+    <t>[np.float64(294.3834534519766), np.float64(224.3213926300632)]</t>
+  </si>
+  <si>
+    <t>[np.float64(132.97901073915864), np.float64(-590.8232606871107)]</t>
+  </si>
+  <si>
+    <t>[np.float64(694.6935500764201), np.float64(364.0555346442387)]</t>
+  </si>
+  <si>
+    <t>[np.float64(400.12111976701516), np.float64(238.32634552455693)]</t>
+  </si>
+  <si>
+    <t>[np.float64(658.2298546614398), np.float64(411.361400309268)]</t>
+  </si>
+  <si>
+    <t>[np.float64(135.7437428830829), np.float64(438.3372694628463)]</t>
+  </si>
+  <si>
+    <t>[np.float64(576.9049393843369), np.float64(368.916208642406)]</t>
+  </si>
+  <si>
+    <t>[np.float64(712.8977661634214), np.float64(-562.8531507414268)]</t>
+  </si>
+  <si>
+    <t>[np.float64(933.4825541479189), np.float64(-81.59134805449912)]</t>
+  </si>
+  <si>
+    <t>[np.float64(792.1550507113271), np.float64(-213.31561652244488)]</t>
+  </si>
+  <si>
+    <t>[np.float64(736.4038664441834), np.float64(363.4303031337172)]</t>
+  </si>
+  <si>
+    <t>[np.float64(887.3182848363568), np.float64(-473.19880079727363)]</t>
+  </si>
+  <si>
+    <t>[np.float64(324.5536068460729), np.float64(248.17971863029447)]</t>
+  </si>
+  <si>
+    <t>[np.float64(194.70966469141604), np.float64(91.66499551672996)]</t>
+  </si>
+  <si>
+    <t>[np.float64(934.6181362695687), np.float64(275.36032418773095)]</t>
+  </si>
+  <si>
+    <t>[np.float64(698.4545267498131), np.float64(-73.6156160734788)]</t>
+  </si>
+  <si>
+    <t>[np.float64(248.3791841034574), np.float64(-475.96911378830214)]</t>
+  </si>
+  <si>
+    <t>[np.float64(470.02225533448996), np.float64(544.1027568879415)]</t>
+  </si>
+  <si>
+    <t>[np.float64(503.3276120465131), np.float64(292.53213819723817)]</t>
+  </si>
+  <si>
+    <t>[np.float64(498.11559217492163), np.float64(437.2936680859759)]</t>
+  </si>
+  <si>
+    <t>[np.float64(659.9414709138807), np.float64(425.62812040212384)]</t>
+  </si>
+  <si>
+    <t>[np.float64(535.3483339252772), np.float64(82.66426435800338)]</t>
+  </si>
+  <si>
+    <t>[np.float64(615.6842905311285), np.float64(36.2507375601823)]</t>
+  </si>
+  <si>
+    <t>[np.float64(446.7758440020463), np.float64(-120.05155319520901)]</t>
+  </si>
+  <si>
+    <t>[np.float64(458.0718995963516), np.float64(-204.1303501456884)]</t>
+  </si>
+  <si>
+    <t>[np.float64(471.61505252660106), np.float64(-263.3061906656799)]</t>
+  </si>
+  <si>
+    <t>[np.float64(803.0684420862348), np.float64(-126.84607994505342)]</t>
+  </si>
+  <si>
+    <t>[np.float64(275.41763037172706), np.float64(338.5759935087558)]</t>
+  </si>
+  <si>
+    <t>[np.float64(431.39676330224665), np.float64(-563.423658987178)]</t>
+  </si>
+  <si>
+    <t>[np.float64(978.3175811250246), np.float64(217.413322201881)]</t>
+  </si>
+  <si>
+    <t>[np.float64(888.1232347108735), np.float64(-263.18956975349784)]</t>
+  </si>
+  <si>
+    <t>[np.float64(659.2339495735346), np.float64(349.0315473184472)]</t>
+  </si>
+  <si>
+    <t>[np.float64(435.53923349240773), np.float64(-64.08894968039601)]</t>
+  </si>
+  <si>
+    <t>[np.float64(528.2058786143913), np.float64(473.40795639413454)]</t>
+  </si>
+  <si>
+    <t>[np.float64(332.26933603530586), np.float64(91.52402311791309)]</t>
+  </si>
+  <si>
+    <t>[np.float64(161.36222442742266), np.float64(-450.28057151487246)]</t>
+  </si>
+  <si>
+    <t>[np.float64(319.68731248940287), np.float64(-526.0088550361555)]</t>
+  </si>
+  <si>
+    <t>[np.float64(849.8970352828333), np.float64(-189.30968345547302)]</t>
+  </si>
+  <si>
+    <t>[np.float64(613.4595899749336), np.float64(-455.82887650908924)]</t>
+  </si>
+  <si>
+    <t>[np.float64(650.2244553766325), np.float64(134.4099938576045)]</t>
+  </si>
+  <si>
+    <t>[np.float64(643.8726964569568), np.float64(-550.4194437359527)]</t>
+  </si>
+  <si>
+    <t>[np.float64(342.13290940795946), np.float64(-572.8600109440147)]</t>
+  </si>
+  <si>
+    <t>[np.float64(750.2819201005647), np.float64(-337.95530347201463)]</t>
+  </si>
+  <si>
+    <t>[np.float64(806.2388982114348), np.float64(136.47284003416598)]</t>
+  </si>
+  <si>
+    <t>[np.float64(355.1663352201828), np.float64(111.55969387065193)]</t>
+  </si>
+  <si>
+    <t>[np.float64(680.6185548685089), np.float64(-248.48225518286853)]</t>
+  </si>
+  <si>
+    <t>[np.float64(767.0032546447128), np.float64(570.495448488685)]</t>
+  </si>
+  <si>
+    <t>[np.float64(50.208017923125794), np.float64(39.9127076490297)]</t>
+  </si>
+  <si>
+    <t>[np.float64(617.8484547643728), np.float64(283.5008488396237)]</t>
+  </si>
+  <si>
+    <t>[np.float64(861.1247707247121), np.float64(62.375478643024394)]</t>
+  </si>
+  <si>
+    <t>[np.float64(731.2741248234164), np.float64(-566.5913291304205)]</t>
+  </si>
+  <si>
+    <t>[np.float64(898.9038797582451), np.float64(76.66111055530064)]</t>
+  </si>
+  <si>
+    <t>[np.float64(939.6986713977161), np.float64(131.2809224662003)]</t>
+  </si>
+  <si>
+    <t>[np.float64(874.0246488319332), np.float64(-106.19846145926294)]</t>
+  </si>
+  <si>
+    <t>[np.float64(859.8425895029421), np.float64(-511.5893853054006)]</t>
+  </si>
+  <si>
+    <t>[np.float64(97.16869009170249), np.float64(-332.32947199842135)]</t>
+  </si>
+  <si>
+    <t>[np.float64(784.7339937334625), np.float64(-226.21260596579975)]</t>
+  </si>
+  <si>
+    <t>[np.float64(561.1069197745719), np.float64(-116.73818882660362)]</t>
+  </si>
+  <si>
+    <t>[np.float64(891.9447162047879), np.float64(-398.9534980298961)]</t>
+  </si>
+  <si>
+    <t>[np.float64(333.63052032287834), np.float64(-585.0104888962297)]</t>
+  </si>
+  <si>
+    <t>[np.float64(150.32092192586666), np.float64(-215.8961215539664)]</t>
+  </si>
+  <si>
+    <t>[np.float64(297.5559555795222), np.float64(-578.2978233772528)]</t>
+  </si>
+  <si>
+    <t>[np.float64(704.1896633032779), np.float64(-100.17126049005054)]</t>
+  </si>
+  <si>
+    <t>[np.float64(188.65400119976738), np.float64(452.83515341225575)]</t>
+  </si>
+  <si>
+    <t>[np.float64(114.33644085836048), np.float64(180.28074416566596)]</t>
+  </si>
+  <si>
+    <t>[np.float64(383.87113903383965), np.float64(347.1326691310354)]</t>
+  </si>
+  <si>
+    <t>[np.float64(691.0675921988893), np.float64(-378.0135688132983)]</t>
+  </si>
+  <si>
+    <t>[np.float64(545.9942373705861), np.float64(-232.49514579684973)]</t>
+  </si>
+  <si>
+    <t>[np.float64(199.37240379244847), np.float64(-334.3641662460048)]</t>
+  </si>
+  <si>
+    <t>[np.float64(421.30081495152103), np.float64(504.00084586675325)]</t>
+  </si>
+  <si>
+    <t>[np.float64(544.6439013842191), np.float64(-483.4726483709368)]</t>
+  </si>
+  <si>
+    <t>[np.float64(127.0276744444897), np.float64(175.5606917157802)]</t>
+  </si>
+  <si>
+    <t>[np.float64(298.08342889730676), np.float64(469.97188830874893)]</t>
+  </si>
+  <si>
+    <t>[np.float64(465.10027463937274), np.float64(-514.6307600306352)]</t>
+  </si>
+  <si>
+    <t>[np.float64(838.9915911172807), np.float64(186.55733789661463)]</t>
+  </si>
+  <si>
+    <t>[np.float64(232.28778394512628), np.float64(336.9867330609885)]</t>
+  </si>
+  <si>
+    <t>[np.float64(639.8669083381145), np.float64(273.62570696695207)]</t>
+  </si>
+  <si>
+    <t>[np.float64(698.0078763408977), np.float64(143.81516790102)]</t>
+  </si>
+  <si>
+    <t>[np.float64(235.7850465467195), np.float64(377.8610436143059)]</t>
+  </si>
+  <si>
+    <t>[np.float64(907.6152297880291), np.float64(35.53411972292179)]</t>
+  </si>
+  <si>
+    <t>[np.float64(812.9421008243612), np.float64(-593.8529134817809)]</t>
+  </si>
+  <si>
+    <t>[np.float64(955.9928822236136), np.float64(332.85440371800723)]</t>
+  </si>
+  <si>
+    <t>[np.float64(771.066812698446), np.float64(-524.9740727313522)]</t>
+  </si>
+  <si>
+    <t>[np.float64(554.8238519042081), np.float64(32.24969228884822)]</t>
+  </si>
+  <si>
+    <t>[np.float64(10.446502995135054), np.float64(-582.5214868161869)]</t>
+  </si>
+  <si>
+    <t>[np.float64(291.14779043127703), np.float64(-246.6226705586853)]</t>
+  </si>
+  <si>
+    <t>[np.float64(981.7327044971692), np.float64(585.1279263000933)]</t>
+  </si>
+  <si>
+    <t>[np.float64(240.1304207248638), np.float64(-455.7607984525357)]</t>
+  </si>
+  <si>
+    <t>[np.float64(341.4603845127249), np.float64(587.7673129140794)]</t>
+  </si>
+  <si>
+    <t>[np.float64(25.099957168672084), np.float64(-151.46620439545353)]</t>
+  </si>
+  <si>
+    <t>[np.float64(332.412098341344), np.float64(-268.708113710565)]</t>
+  </si>
+  <si>
+    <t>[np.float64(976.7857549431109), np.float64(450.33033420785387)]</t>
+  </si>
+  <si>
+    <t>[np.float64(393.51710147649663), np.float64(-219.9074133408007)]</t>
+  </si>
+  <si>
+    <t>[np.float64(198.83661794094175), np.float64(-296.42874483812056)]</t>
+  </si>
+  <si>
+    <t>[np.float64(486.5482779799172), np.float64(-472.6425634587905)]</t>
+  </si>
+  <si>
+    <t>[np.float64(792.3104473529883), np.float64(202.60028525907774)]</t>
+  </si>
+  <si>
+    <t>[np.float64(316.84548509760646), np.float64(-508.7976446194646)]</t>
+  </si>
+  <si>
+    <t>[np.float64(280.6398272776488), np.float64(-380.5770004153983)]</t>
+  </si>
+  <si>
+    <t>[np.float64(575.6165049052707), np.float64(332.98088912659034)]</t>
+  </si>
+  <si>
+    <t>[np.float64(396.8206686250006), np.float64(236.5818468887096)]</t>
+  </si>
+  <si>
+    <t>[np.float64(77.4598440331048), np.float64(-145.576341215509)]</t>
+  </si>
+  <si>
+    <t>[np.float64(538.910555757918), np.float64(-324.73540370810247)]</t>
+  </si>
+  <si>
+    <t>[np.float64(611.7589408138499), np.float64(-170.115356646993)]</t>
+  </si>
+  <si>
+    <t>[np.float64(480.1375022034776), np.float64(243.24919425970984)]</t>
+  </si>
+  <si>
+    <t>[np.float64(437.5007662438408), np.float64(-241.52014883438073)]</t>
+  </si>
+  <si>
+    <t>[np.float64(713.190024287126), np.float64(136.4497974786159)]</t>
+  </si>
+  <si>
+    <t>[np.float64(837.2972423821495), np.float64(-170.6024427434716)]</t>
+  </si>
+  <si>
+    <t>[np.float64(565.1599845587507), np.float64(435.0619053654243)]</t>
+  </si>
+  <si>
+    <t>[np.float64(280.00649242309106), np.float64(-341.43617768306325)]</t>
+  </si>
+  <si>
+    <t>[np.float64(432.27401648086004), np.float64(516.5700835776427)]</t>
+  </si>
+  <si>
+    <t>[np.float64(35.277940493518734), np.float64(-573.6341050701085)]</t>
+  </si>
+  <si>
+    <t>[np.float64(668.931310453458), np.float64(-529.6601658469957)]</t>
+  </si>
+  <si>
+    <t>[np.float64(418.17738375886483), np.float64(270.6062968303513)]</t>
+  </si>
+  <si>
+    <t>[np.float64(688.0405510470647), np.float64(-165.61404056395338)]</t>
+  </si>
+  <si>
+    <t>[np.float64(921.44934332814), np.float64(-261.46640698011083)]</t>
+  </si>
+  <si>
+    <t>[np.float64(605.3649763037914), np.float64(-348.0478592624116)]</t>
+  </si>
+  <si>
+    <t>[np.float64(653.7800437688685), np.float64(-101.83242881248583)]</t>
+  </si>
+  <si>
+    <t>[np.float64(784.844416819342), np.float64(-568.8963220765144)]</t>
+  </si>
+  <si>
+    <t>[np.float64(466.4977937765519), np.float64(410.8612437872855)]</t>
+  </si>
+  <si>
+    <t>[np.float64(833.5419193866041), np.float64(-189.14403068917306)]</t>
+  </si>
+  <si>
+    <t>[np.float64(196.72661637020406), np.float64(-102.63026054304788)]</t>
+  </si>
+  <si>
+    <t>[np.float64(990.1902062065354), np.float64(-554.5247665554297)]</t>
+  </si>
+  <si>
+    <t>[np.float64(752.9178001280404), np.float64(494.4715257132375)]</t>
+  </si>
+  <si>
+    <t>[np.float64(437.6374618212787), np.float64(117.26632616273628)]</t>
+  </si>
+  <si>
+    <t>[np.float64(597.1874720708008), np.float64(362.9721460629545)]</t>
+  </si>
+  <si>
+    <t>[np.float64(73.73852361702637), np.float64(95.58969111564079)]</t>
+  </si>
+  <si>
+    <t>[np.float64(784.6580021160926), np.float64(200.4141244546414)]</t>
+  </si>
+  <si>
+    <t>[np.float64(901.7707021672683), np.float64(-262.49266449725013)]</t>
+  </si>
+  <si>
+    <t>[np.float64(283.2527866389205), np.float64(-576.5908948699721)]</t>
+  </si>
+  <si>
+    <t>[np.float64(92.4351395656402), np.float64(542.5340600267286)]</t>
+  </si>
+  <si>
+    <t>[np.float64(975.4123778145455), np.float64(-266.1975973240158)]</t>
+  </si>
+  <si>
+    <t>[np.float64(812.2969855338954), np.float64(70.31431775050214)]</t>
+  </si>
+  <si>
+    <t>[np.float64(749.9927432550769), np.float64(459.42237082112615)]</t>
+  </si>
+  <si>
+    <t>[np.float64(671.0449348662462), np.float64(-483.3642100418999)]</t>
+  </si>
+  <si>
+    <t>[np.float64(883.4202569231753), np.float64(-393.6152990089905)]</t>
+  </si>
+  <si>
+    <t>[np.float64(903.3868381000351), np.float64(480.7883255056113)]</t>
+  </si>
+  <si>
+    <t>[np.float64(445.68161880125734), np.float64(596.8783051431299)]</t>
+  </si>
+  <si>
+    <t>[np.float64(920.4546000187963), np.float64(-498.68226765099564)]</t>
+  </si>
+  <si>
+    <t>[np.float64(921.5905013805302), np.float64(-581.1394779620271)]</t>
+  </si>
+  <si>
+    <t>[np.float64(28.052334162760985), np.float64(361.44205692448895)]</t>
+  </si>
+  <si>
+    <t>[np.float64(692.0704002567335), np.float64(267.0888287537865)]</t>
+  </si>
+  <si>
+    <t>[np.float64(413.3941042003193), np.float64(426.51461933534665)]</t>
+  </si>
+  <si>
+    <t>[np.float64(582.3172393890924), np.float64(-88.97594558672665)]</t>
+  </si>
+  <si>
+    <t>[np.float64(80.14210439860159), np.float64(235.9521689368985)]</t>
+  </si>
+  <si>
+    <t>[np.float64(271.68756516943415), np.float64(331.2413554953629)]</t>
+  </si>
+  <si>
+    <t>[np.float64(174.9856607634561), np.float64(235.92563913670483)]</t>
+  </si>
+  <si>
+    <t>[np.float64(613.5147604302182), np.float64(184.7753036772832)]</t>
+  </si>
+  <si>
+    <t>[np.float64(412.70392473083774), np.float64(-423.37239299408657)]</t>
+  </si>
+  <si>
+    <t>[np.float64(455.29305144295705), np.float64(573.218401693249)]</t>
+  </si>
+  <si>
+    <t>[np.float64(688.0068765134001), np.float64(-157.03095813194096)]</t>
+  </si>
+  <si>
+    <t>[np.float64(926.6104350818632), np.float64(251.31996254691728)]</t>
+  </si>
+  <si>
+    <t>[np.float64(145.34661115253888), np.float64(-77.24532608552886)]</t>
+  </si>
+  <si>
+    <t>[np.float64(345.4596760445194), np.float64(24.830039255321367)]</t>
+  </si>
+  <si>
+    <t>[np.float64(249.9605982808145), np.float64(81.81420711480314)]</t>
+  </si>
+  <si>
+    <t>[np.float64(483.39125215507573), np.float64(-47.83510514404361)]</t>
+  </si>
+  <si>
+    <t>[np.float64(170.24102097493764), np.float64(430.30294353132194)]</t>
+  </si>
+  <si>
+    <t>[np.float64(222.83731082395332), np.float64(596.8988216254807)]</t>
+  </si>
+  <si>
+    <t>[np.float64(194.8123245341664), np.float64(515.5911880933072)]</t>
+  </si>
+  <si>
+    <t>[np.float64(429.46391750902245), np.float64(567.3105859106929)]</t>
+  </si>
+  <si>
+    <t>[np.float64(461.2386215928819), np.float64(183.2111791010492)]</t>
+  </si>
+  <si>
+    <t>[np.float64(712.2736386913114), np.float64(521.4163511811234)]</t>
+  </si>
+  <si>
+    <t>[np.float64(40.54016572741803), np.float64(-516.622565648422)]</t>
+  </si>
+  <si>
+    <t>[np.float64(73.04983873235604), np.float64(-168.47679920764296)]</t>
+  </si>
+  <si>
+    <t>[np.float64(922.0106900859194), np.float64(-458.2268645328186)]</t>
+  </si>
+  <si>
+    <t>[np.float64(382.5683174575396), np.float64(-401.7787078867169)]</t>
+  </si>
+  <si>
+    <t>[np.float64(284.61815780144195), np.float64(394.3106009924336)]</t>
+  </si>
+  <si>
+    <t>[np.float64(180.2629320616953), np.float64(-253.85610057890722)]</t>
+  </si>
+  <si>
+    <t>[np.float64(751.3312566425141), np.float64(240.55021740649158)]</t>
+  </si>
+  <si>
+    <t>[np.float64(190.25707038285034), np.float64(242.7350540585751)]</t>
+  </si>
+  <si>
+    <t>[np.float64(292.28141793146324), np.float64(403.1281199254437)]</t>
+  </si>
+  <si>
+    <t>[np.float64(578.4776445555101), np.float64(63.32370314305592)]</t>
+  </si>
+  <si>
+    <t>[np.float64(36.07552899423716), np.float64(274.22862521083493)]</t>
+  </si>
+  <si>
+    <t>[np.float64(518.195329077162), np.float64(274.3789106290094)]</t>
+  </si>
+  <si>
+    <t>[np.float64(875.3418983109779), np.float64(-439.69034899837794)]</t>
+  </si>
+  <si>
+    <t>[np.float64(667.5770125476549), np.float64(95.07306783540707)]</t>
+  </si>
+  <si>
+    <t>[np.float64(666.1521661901203), np.float64(-268.0984813406304)]</t>
+  </si>
+  <si>
+    <t>[np.float64(444.0987853136978), np.float64(-545.8804496351121)]</t>
+  </si>
+  <si>
+    <t>[np.float64(306.1657243063903), np.float64(539.6442983143024)]</t>
+  </si>
+  <si>
+    <t>[np.float64(424.8719518263572), np.float64(344.0153519626682)]</t>
+  </si>
+  <si>
+    <t>[np.float64(717.3025047914476), np.float64(-410.82458182948574)]</t>
+  </si>
+  <si>
+    <t>[np.float64(750.0904119830265), np.float64(-543.0274734394044)]</t>
+  </si>
+  <si>
+    <t>[np.float64(33.88345647490254), np.float64(-307.7555389717008)]</t>
+  </si>
+  <si>
+    <t>[np.float64(293.0654463765824), np.float64(182.75367762411622)]</t>
+  </si>
+  <si>
+    <t>[np.float64(341.1127401125822), np.float64(69.6930383540722)]</t>
+  </si>
+  <si>
+    <t>[np.float64(452.2088793057054), np.float64(-301.3621083043009)]</t>
+  </si>
+  <si>
+    <t>[np.float64(979.2565844493755), np.float64(-335.615830557967)]</t>
+  </si>
+  <si>
+    <t>[np.float64(219.38387887491893), np.float64(-6.74724320252983)]</t>
+  </si>
+  <si>
+    <t>[np.float64(301.1330659898173), np.float64(14.981020578091716)]</t>
+  </si>
+  <si>
+    <t>[np.float64(785.3900610223741), np.float64(-459.73863137836474)]</t>
+  </si>
+  <si>
+    <t>[np.float64(332.45490554211943), np.float64(-319.3628599217313)]</t>
+  </si>
+  <si>
+    <t>[np.float64(748.9376966560055), np.float64(85.37906635916659)]</t>
+  </si>
+  <si>
+    <t>[np.float64(681.4278932693697), np.float64(87.1479050165135)]</t>
+  </si>
+  <si>
+    <t>[np.float64(917.2640281754781), np.float64(482.7333083602364)]</t>
+  </si>
+  <si>
+    <t>[np.float64(333.2523809061476), np.float64(-336.50649094663135)]</t>
+  </si>
+  <si>
+    <t>[np.float64(668.825651666149), np.float64(-487.5492853558004)]</t>
+  </si>
+  <si>
+    <t>[np.float64(971.5935470146314), np.float64(-585.0106419605784)]</t>
+  </si>
+  <si>
+    <t>[np.float64(79.39032249461853), np.float64(132.7141845163477)]</t>
+  </si>
+  <si>
+    <t>[np.float64(492.78922352423916), np.float64(252.2812298233556)]</t>
+  </si>
+  <si>
+    <t>[np.float64(644.8182866342459), np.float64(-575.1349617453824)]</t>
+  </si>
+  <si>
+    <t>[np.float64(321.9549893059115), np.float64(429.608965064474)]</t>
+  </si>
+  <si>
+    <t>[np.float64(83.46975206966655), np.float64(565.1200025800072)]</t>
+  </si>
+  <si>
+    <t>[np.float64(500.0292817622519), np.float64(-313.20369009926094)]</t>
+  </si>
+  <si>
+    <t>[np.float64(709.3879845283864), np.float64(200.54437759353027)]</t>
+  </si>
+  <si>
+    <t>[np.float64(975.5729181649762), np.float64(-531.3705845418185)]</t>
+  </si>
+  <si>
+    <t>[np.float64(571.7015676827373), np.float64(561.2561628265082)]</t>
+  </si>
+  <si>
+    <t>[np.float64(551.3307303016829), np.float64(-269.4602641587574)]</t>
+  </si>
+  <si>
+    <t>[np.float64(366.77614709728834), np.float64(-463.5044724523186)]</t>
+  </si>
+  <si>
+    <t>[np.float64(137.41244540217266), np.float64(47.567037454480555)]</t>
+  </si>
+  <si>
+    <t>[np.float64(933.8382357673611), np.float64(-473.43456276251993)]</t>
+  </si>
+  <si>
+    <t>[np.float64(542.105819307652), np.float64(-112.2368288629844)]</t>
+  </si>
+  <si>
+    <t>[np.float64(546.3232507904113), np.float64(379.329192920983)]</t>
+  </si>
+  <si>
+    <t>[np.float64(753.0275695149987), np.float64(-404.6820767776036)]</t>
+  </si>
+  <si>
+    <t>[np.float64(300.6429862420956), np.float64(2.950224729533261)]</t>
+  </si>
+  <si>
+    <t>[np.float64(744.2389250756984), np.float64(-560.3959977984964)]</t>
+  </si>
+  <si>
+    <t>[np.float64(838.4104184355037), np.float64(-417.8454830250164)]</t>
+  </si>
+  <si>
+    <t>[np.float64(302.11318818424013), np.float64(-127.80387467515146)]</t>
+  </si>
+  <si>
+    <t>[np.float64(718.7958092529702), np.float64(-541.3070290591107)]</t>
+  </si>
+  <si>
+    <t>[np.float64(877.506840372412), np.float64(-167.44017766005982)]</t>
+  </si>
+  <si>
+    <t>[np.float64(410.6629452030536), np.float64(517.3057006417014)]</t>
+  </si>
+  <si>
+    <t>[np.float64(92.06391296443628), np.float64(161.78035500280316)]</t>
+  </si>
+  <si>
+    <t>[np.float64(665.9894406185875), np.float64(495.39695868234185)]</t>
+  </si>
+  <si>
+    <t>[np.float64(348.6623151996887), np.float64(-404.4002407520802)]</t>
+  </si>
+  <si>
+    <t>[np.float64(66.25679438481569), np.float64(79.6182018271702)]</t>
+  </si>
+  <si>
+    <t>[np.float64(798.6901047209323), np.float64(-423.8515234630047)]</t>
+  </si>
+  <si>
+    <t>[np.float64(256.51447825040776), np.float64(-187.44437774035475)]</t>
+  </si>
+  <si>
+    <t>[np.float64(473.0120047512433), np.float64(322.7653498035536)]</t>
+  </si>
+  <si>
+    <t>[np.float64(152.59284178354392), np.float64(528.4071606459465)]</t>
+  </si>
+  <si>
+    <t>[np.float64(484.3270097286373), np.float64(446.14656088652123)]</t>
+  </si>
+  <si>
+    <t>[np.float64(902.4666084823704), np.float64(21.03603456085591)]</t>
+  </si>
+  <si>
+    <t>[np.float64(136.9198345773145), np.float64(524.220786968928)]</t>
+  </si>
+  <si>
+    <t>[np.float64(676.5941575604901), np.float64(-564.7228276411348)]</t>
+  </si>
+  <si>
+    <t>[np.float64(888.4216619756432), np.float64(116.52412547480708)]</t>
+  </si>
+  <si>
+    <t>[np.float64(205.0727496349052), np.float64(-75.69624648840477)]</t>
+  </si>
+  <si>
+    <t>[np.float64(771.3161042410336), np.float64(540.7038835359922)]</t>
+  </si>
+  <si>
+    <t>[np.float64(449.0870165727304), np.float64(-469.9923109886062)]</t>
+  </si>
+  <si>
+    <t>[np.float64(156.7481110190464), np.float64(-423.762054107698)]</t>
+  </si>
+  <si>
+    <t>[np.float64(539.0523204157387), np.float64(-509.50393212191403)]</t>
+  </si>
+  <si>
+    <t>[np.float64(276.6228526891915), np.float64(208.75825042501833)]</t>
+  </si>
+  <si>
+    <t>[np.float64(844.230576695361), np.float64(483.003684925028)]</t>
+  </si>
+  <si>
+    <t>[np.float64(520.7837154501871), np.float64(521.1232836735967)]</t>
+  </si>
+  <si>
+    <t>[np.float64(876.6288778905284), np.float64(-104.30739567993032)]</t>
+  </si>
+  <si>
+    <t>[np.float64(662.3396932314113), np.float64(-326.20458542872785)]</t>
+  </si>
+  <si>
+    <t>[np.float64(66.5719683162952), np.float64(-254.7457784929859)]</t>
+  </si>
+  <si>
+    <t>[np.float64(12.028642285700442), np.float64(415.835021291963)]</t>
+  </si>
+  <si>
+    <t>[np.float64(427.0185462398204), np.float64(-310.91524205585824)]</t>
+  </si>
+  <si>
+    <t>[np.float64(952.2090006043038), np.float64(-127.60631395142019)]</t>
+  </si>
+  <si>
+    <t>[np.float64(862.9176436133897), np.float64(-255.37871466436377)]</t>
+  </si>
+  <si>
+    <t>[np.float64(35.47729526854704), np.float64(570.5115640910362)]</t>
+  </si>
+  <si>
+    <t>[np.float64(456.54718330097245), np.float64(0.5561137307337276)]</t>
+  </si>
+  <si>
+    <t>[np.float64(924.666044182942), np.float64(75.58654769286477)]</t>
+  </si>
+  <si>
+    <t>[np.float64(418.8516088673704), np.float64(-248.72582704675222)]</t>
+  </si>
+  <si>
+    <t>[np.float64(364.9064667845222), np.float64(170.57523213634613)]</t>
+  </si>
+  <si>
+    <t>[np.float64(641.825432131482), np.float64(-357.58768436730156)]</t>
+  </si>
+  <si>
+    <t>[np.float64(444.65975396559674), np.float64(-378.00373192185214)]</t>
+  </si>
+  <si>
+    <t>[np.float64(140.94488855179145), np.float64(337.5162400020116)]</t>
+  </si>
+  <si>
+    <t>[np.float64(489.24576419698917), np.float64(75.56970301502031)]</t>
+  </si>
+  <si>
+    <t>[np.float64(813.1330478564626), np.float64(-211.39206902146282)]</t>
+  </si>
+  <si>
+    <t>[np.float64(579.051340999873), np.float64(-255.43792870614953)]</t>
+  </si>
+  <si>
+    <t>[np.float64(604.1203312406723), np.float64(521.2387668931765)]</t>
+  </si>
+  <si>
+    <t>[np.float64(244.08910174821486), np.float64(-83.591599950454)]</t>
+  </si>
+  <si>
+    <t>[np.float64(785.2606937344839), np.float64(525.0153434633933)]</t>
+  </si>
+  <si>
+    <t>[np.float64(428.8482683693009), np.float64(573.91799459618)]</t>
+  </si>
+  <si>
+    <t>[np.float64(875.9084534031426), np.float64(-48.030402141237346)]</t>
+  </si>
+  <si>
+    <t>[np.float64(441.7844810314797), np.float64(184.90675564844014)]</t>
+  </si>
+  <si>
+    <t>[np.float64(361.48384930333367), np.float64(428.01039463432994)]</t>
+  </si>
+  <si>
+    <t>[np.float64(924.9448437457611), np.float64(-112.24828048356727)]</t>
+  </si>
+  <si>
+    <t>[np.float64(18.386324038766055), np.float64(-158.90531941575983)]</t>
+  </si>
+  <si>
+    <t>[np.float64(823.2419756526086), np.float64(258.6597850633758)]</t>
+  </si>
+  <si>
+    <t>[np.float64(204.61689871521716), np.float64(118.85708786514147)]</t>
+  </si>
+  <si>
+    <t>[np.float64(901.3811950878114), np.float64(-319.8457269963491)]</t>
+  </si>
+  <si>
+    <t>[np.float64(492.76817605985644), np.float64(403.57620998617256)]</t>
+  </si>
+  <si>
+    <t>[np.float64(557.9425389765167), np.float64(53.84707285651905)]</t>
+  </si>
+  <si>
+    <t>[np.float64(421.17468131077106), np.float64(-334.9025783413278)]</t>
+  </si>
+  <si>
+    <t>[np.float64(995.1592113590958), np.float64(-517.7265331061384)]</t>
+  </si>
+  <si>
+    <t>[np.float64(527.8974950916198), np.float64(-100.73835673739944)]</t>
+  </si>
+  <si>
+    <t>[np.float64(457.8922780073933), np.float64(-329.3900416531924)]</t>
+  </si>
+  <si>
+    <t>[np.float64(589.0357489775356), np.float64(-224.64333424235917)]</t>
+  </si>
+  <si>
+    <t>[np.float64(228.60691664917377), np.float64(246.54173800303977)]</t>
+  </si>
+  <si>
+    <t>[np.float64(8.898367930646245), np.float64(249.5372174297912)]</t>
+  </si>
+  <si>
+    <t>[np.float64(304.4752688684383), np.float64(-468.9172291798778)]</t>
+  </si>
+  <si>
+    <t>[np.float64(70.59994576673657), np.float64(587.1257296291585)]</t>
+  </si>
+  <si>
+    <t>[np.float64(525.1262967249686), np.float64(-196.41783686805172)]</t>
+  </si>
+  <si>
+    <t>[np.float64(951.3668690006004), np.float64(399.2379125228048)]</t>
+  </si>
+  <si>
+    <t>[np.float64(90.59090899638333), np.float64(-451.37020513989887)]</t>
+  </si>
+  <si>
+    <t>[np.float64(568.5544865933127), np.float64(-432.3912511991728)]</t>
+  </si>
+  <si>
+    <t>[np.float64(194.75933520014044), np.float64(-295.6973470553416)]</t>
+  </si>
+  <si>
+    <t>[np.float64(814.419739503426), np.float64(-49.729128272155435)]</t>
+  </si>
+  <si>
+    <t>[np.float64(737.0860131022007), np.float64(-162.6568047375594)]</t>
+  </si>
+  <si>
+    <t>[np.float64(686.5538499477726), np.float64(-430.86591675854027)]</t>
+  </si>
+  <si>
+    <t>[np.float64(285.7727728033025), np.float64(366.3798772055477)]</t>
+  </si>
+  <si>
+    <t>[np.float64(97.67523440108138), np.float64(-518.7284992367634)]</t>
+  </si>
+  <si>
+    <t>[np.float64(693.8447153542668), np.float64(323.2441167974721)]</t>
+  </si>
+  <si>
+    <t>[np.float64(636.926389611678), np.float64(181.78808938271254)]</t>
+  </si>
+  <si>
+    <t>[np.float64(237.05937507792507), np.float64(-448.4022013578891)]</t>
+  </si>
+  <si>
+    <t>[np.float64(770.7480883208509), np.float64(-485.84846782049203)]</t>
+  </si>
+  <si>
+    <t>[np.float64(981.31467066466), np.float64(-366.3011339230537)]</t>
+  </si>
+  <si>
+    <t>[np.float64(292.11676219866143), np.float64(-486.63037422498024)]</t>
+  </si>
+  <si>
+    <t>[np.float64(373.31701329376324), np.float64(424.92682597697785)]</t>
+  </si>
+  <si>
+    <t>[np.float64(47.906922471015804), np.float64(61.92087518330709)]</t>
+  </si>
+  <si>
+    <t>[np.float64(102.83083534978866), np.float64(-142.30184797018637)]</t>
+  </si>
+  <si>
+    <t>[np.float64(398.4269201833504), np.float64(-50.89470443480013)]</t>
+  </si>
+  <si>
+    <t>[np.float64(714.5382160138889), np.float64(-323.2560493888246)]</t>
+  </si>
+  <si>
+    <t>[np.float64(255.80145719139668), np.float64(-183.6205332078515)]</t>
+  </si>
+  <si>
+    <t>[np.float64(701.3386552933196), np.float64(-241.36476211808275)]</t>
+  </si>
+  <si>
+    <t>[np.float64(855.7040453197159), np.float64(-191.40711515026385)]</t>
+  </si>
+  <si>
+    <t>[np.float64(941.5474525228744), np.float64(-530.2649896922574)]</t>
+  </si>
+  <si>
+    <t>[np.float64(505.2516560322968), np.float64(136.06167712119134)]</t>
+  </si>
+  <si>
+    <t>[np.float64(586.9292807812523), np.float64(557.2072892344734)]</t>
+  </si>
+  <si>
+    <t>[np.float64(234.93034114854171), np.float64(-295.70124667323523)]</t>
+  </si>
+  <si>
+    <t>[np.float64(256.50534051551585), np.float64(366.29902934597044)]</t>
+  </si>
+  <si>
+    <t>[np.float64(129.6335212498787), np.float64(-554.7889440499677)]</t>
+  </si>
+  <si>
+    <t>[np.float64(597.0305028732852), np.float64(-342.16800430669923)]</t>
+  </si>
+  <si>
+    <t>[np.float64(884.3306503550411), np.float64(-296.799539766859)]</t>
+  </si>
+  <si>
+    <t>[np.float64(185.73665673282002), np.float64(-419.477651974591)]</t>
+  </si>
+  <si>
+    <t>[np.float64(38.39780672889304), np.float64(-300.4605160871788)]</t>
+  </si>
+  <si>
+    <t>[np.float64(520.8335638243649), np.float64(-506.0326486643721)]</t>
+  </si>
+  <si>
+    <t>[np.float64(80.78264370454879), np.float64(155.44550656992328)]</t>
+  </si>
+  <si>
+    <t>[np.float64(218.04113413309966), np.float64(-377.24611539516616)]</t>
+  </si>
+  <si>
+    <t>[np.float64(268.3310482177205), np.float64(544.5080724604379)]</t>
+  </si>
+  <si>
+    <t>[np.float64(522.5097014558044), np.float64(56.5226702667087)]</t>
+  </si>
+  <si>
+    <t>[np.float64(37.23871004087576), np.float64(-577.1177881688453)]</t>
+  </si>
+  <si>
+    <t>[np.float64(90.82884771871092), np.float64(-232.914172726301)]</t>
+  </si>
+  <si>
+    <t>[np.float64(527.4524923281776), np.float64(483.5728017817198)]</t>
+  </si>
+  <si>
+    <t>[np.float64(652.2324798073884), np.float64(487.6714416792822)]</t>
+  </si>
+  <si>
+    <t>[np.float64(250.1674046822585), np.float64(-182.38439696465065)]</t>
+  </si>
+  <si>
+    <t>[np.float64(946.4503430252415), np.float64(-513.139842318828)]</t>
+  </si>
+  <si>
+    <t>[np.float64(269.35048231244207), np.float64(153.57788656352557)]</t>
+  </si>
+  <si>
+    <t>[np.float64(727.8433563966848), np.float64(420.27003105443885)]</t>
+  </si>
+  <si>
+    <t>[np.float64(114.2981945292002), np.float64(572.1751600128675)]</t>
+  </si>
+  <si>
+    <t>[np.float64(222.26305379937196), np.float64(-580.7271997803123)]</t>
+  </si>
+  <si>
+    <t>[np.float64(924.3228420654631), np.float64(465.749164678773)]</t>
+  </si>
+  <si>
+    <t>[np.float64(168.25301959921813), np.float64(170.48288832075355)]</t>
+  </si>
+  <si>
+    <t>[np.float64(635.1503901227948), np.float64(374.9141889686307)]</t>
+  </si>
+  <si>
+    <t>[np.float64(468.06211518704), np.float64(279.7232311557516)]</t>
+  </si>
+  <si>
+    <t>[np.float64(211.7346058071875), np.float64(575.657786128304)]</t>
+  </si>
+  <si>
+    <t>[np.float64(590.6239600935461), np.float64(-303.9912521204468)]</t>
+  </si>
+  <si>
+    <t>[np.float64(682.1345801331584), np.float64(549.0271391385575)]</t>
+  </si>
+  <si>
+    <t>[np.float64(324.3736482242221), np.float64(-201.43394090479273)]</t>
+  </si>
+  <si>
+    <t>[np.float64(386.56527256773757), np.float64(-457.1428597159622)]</t>
+  </si>
+  <si>
+    <t>[np.float64(30.150013524412156), np.float64(297.674803019504)]</t>
+  </si>
+  <si>
+    <t>[np.float64(272.8787713827191), np.float64(-571.1019509876731)]</t>
+  </si>
+  <si>
+    <t>[np.float64(981.7909737699802), np.float64(513.6180418304155)]</t>
+  </si>
+  <si>
+    <t>[np.float64(981.6536534434266), np.float64(387.1256624093851)]</t>
+  </si>
+  <si>
+    <t>[np.float64(152.3954576980966), np.float64(371.72851164757174)]</t>
+  </si>
+  <si>
+    <t>[np.float64(62.263930934228775), np.float64(151.46008782598915)]</t>
+  </si>
+  <si>
+    <t>[np.float64(14.417035493833996), np.float64(363.3585722964765)]</t>
+  </si>
+  <si>
+    <t>[np.float64(90.85040566339408), np.float64(73.16320336555964)]</t>
+  </si>
+  <si>
+    <t>[np.float64(332.9074860047716), np.float64(248.0280091768982)]</t>
+  </si>
+  <si>
+    <t>[np.float64(541.7313171175072), np.float64(-164.9712617669553)]</t>
+  </si>
+  <si>
+    <t>[np.float64(627.7664950504751), np.float64(21.28707478391027)]</t>
+  </si>
+  <si>
+    <t>[np.float64(808.796637619401), np.float64(-127.18238170578286)]</t>
+  </si>
+  <si>
+    <t>[np.float64(255.25853661890295), np.float64(-581.003285249211)]</t>
+  </si>
+  <si>
+    <t>[np.float64(692.4963343765181), np.float64(4.6746093423971615)]</t>
+  </si>
+  <si>
+    <t>[np.float64(662.2518446700105), np.float64(24.576392644344196)]</t>
+  </si>
+  <si>
+    <t>[np.float64(685.8474316456975), np.float64(-156.5433195380914)]</t>
+  </si>
+  <si>
+    <t>[np.float64(51.18335926329043), np.float64(52.563264302982475)]</t>
+  </si>
+  <si>
+    <t>[np.float64(198.21926921800258), np.float64(256.29787702122974)]</t>
+  </si>
+  <si>
+    <t>[np.float64(764.8715907449857), np.float64(-80.11460321195273)]</t>
+  </si>
+  <si>
+    <t>[np.float64(112.6021649246044), np.float64(367.39341739175984)]</t>
+  </si>
+  <si>
+    <t>[np.float64(634.7487047500545), np.float64(93.62798567143977)]</t>
+  </si>
+  <si>
+    <t>[np.float64(80.40885798720821), np.float64(-104.13545964329097)]</t>
+  </si>
+  <si>
+    <t>[np.float64(518.8343674717916), np.float64(88.29662980807996)]</t>
+  </si>
+  <si>
+    <t>[np.float64(820.6032600599738), np.float64(-497.3647475728286)]</t>
+  </si>
+  <si>
+    <t>[np.float64(988.4085029001928), np.float64(-328.50671385813723)]</t>
+  </si>
+  <si>
+    <t>[np.float64(520.779760028696), np.float64(-154.40487083314036)]</t>
+  </si>
+  <si>
+    <t>[np.float64(542.8705419052992), np.float64(-512.6075791899482)]</t>
+  </si>
+  <si>
+    <t>[np.float64(779.1198044154825), np.float64(383.9114371122183)]</t>
+  </si>
+  <si>
+    <t>[np.float64(472.55564625316094), np.float64(560.4966976906114)]</t>
+  </si>
+  <si>
+    <t>[np.float64(653.9073643745251), np.float64(-573.6696838429367)]</t>
+  </si>
+  <si>
+    <t>[np.float64(941.7566306416155), np.float64(-139.83430567444617)]</t>
+  </si>
+  <si>
+    <t>[np.float64(183.72695455442056), np.float64(127.30176471480547)]</t>
+  </si>
+  <si>
+    <t>[np.float64(381.6768411862149), np.float64(-334.8576959209883)]</t>
+  </si>
+  <si>
+    <t>[np.float64(109.96722360652834), np.float64(82.31696309149413)]</t>
+  </si>
+  <si>
+    <t>[np.float64(706.7366854218968), np.float64(586.8186541565617)]</t>
+  </si>
+  <si>
+    <t>[np.float64(519.5249082736455), np.float64(183.65556071432013)]</t>
+  </si>
+  <si>
+    <t>[np.float64(862.2375849805093), np.float64(517.0923431263905)]</t>
+  </si>
+  <si>
+    <t>[np.float64(221.03539143889327), np.float64(-268.1960710489525)]</t>
+  </si>
+  <si>
+    <t>[np.float64(18.240411698168923), np.float64(-334.365110062109)]</t>
+  </si>
+  <si>
+    <t>[np.float64(549.8183873256746), np.float64(-460.1940683043257)]</t>
+  </si>
+  <si>
+    <t>[np.float64(622.9225405760285), np.float64(89.92041865179158)]</t>
+  </si>
+  <si>
+    <t>[np.float64(472.8545766102703), np.float64(50.079232066286295)]</t>
+  </si>
+  <si>
+    <t>[np.float64(820.8133301712929), np.float64(-343.04130303584236)]</t>
+  </si>
+  <si>
+    <t>[np.float64(242.633592223504), np.float64(438.10417352137665)]</t>
+  </si>
+  <si>
+    <t>[np.float64(352.9573030670855), np.float64(307.3121486031223)]</t>
+  </si>
+  <si>
+    <t>[np.float64(608.3929603900448), np.float64(-115.20861005857955)]</t>
+  </si>
+  <si>
+    <t>[np.float64(574.6867906845157), np.float64(-197.46377597326352)]</t>
+  </si>
+  <si>
+    <t>[np.float64(386.1148856237271), np.float64(119.78209719744609)]</t>
+  </si>
+  <si>
+    <t>[np.float64(58.47062628733091), np.float64(-361.7576577936062)]</t>
+  </si>
+  <si>
+    <t>[np.float64(203.6980481790256), np.float64(540.509750533532)]</t>
+  </si>
+  <si>
+    <t>[np.float64(38.77060221486695), np.float64(-78.1440660265688)]</t>
+  </si>
+  <si>
+    <t>[np.float64(881.6116789902926), np.float64(397.5229854008811)]</t>
+  </si>
+  <si>
+    <t>[np.float64(842.8486513052773), np.float64(293.90180546175725)]</t>
+  </si>
+  <si>
+    <t>[np.float64(216.5050848566481), np.float64(-202.9132844327263)]</t>
+  </si>
+  <si>
+    <t>[np.float64(201.59474166459967), np.float64(415.84424880612346)]</t>
+  </si>
+  <si>
+    <t>[np.float64(921.6311080629014), np.float64(376.2741978939396)]</t>
+  </si>
+  <si>
+    <t>[np.float64(851.234077741872), np.float64(373.92090183321113)]</t>
+  </si>
+  <si>
+    <t>[np.float64(843.2031944344943), np.float64(-106.78145914810858)]</t>
+  </si>
+  <si>
+    <t>[np.float64(421.8459208569376), np.float64(-543.0401294515611)]</t>
+  </si>
+  <si>
+    <t>[np.float64(494.1504602106528), np.float64(-397.8667821082381)]</t>
+  </si>
+  <si>
+    <t>[np.float64(989.0762086914085), np.float64(-403.1491487043032)]</t>
+  </si>
+  <si>
+    <t>[np.float64(679.8795789859514), np.float64(346.709249065422)]</t>
+  </si>
+  <si>
+    <t>[np.float64(999.5783364490527), np.float64(-363.16896203416155)]</t>
+  </si>
+  <si>
+    <t>[np.float64(803.6489864417281), np.float64(-167.4418348364759)]</t>
+  </si>
+  <si>
+    <t>[np.float64(773.901662930006), np.float64(-435.2927760047021)]</t>
+  </si>
+  <si>
+    <t>[np.float64(446.1655174890806), np.float64(246.38712393291496)]</t>
+  </si>
+  <si>
+    <t>[np.float64(188.19779731847396), np.float64(458.6194206175355)]</t>
+  </si>
+  <si>
+    <t>[np.float64(327.947079785855), np.float64(-226.67719922536895)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.8577779811433937), np.float64(77.49308743826418)]</t>
+  </si>
+  <si>
+    <t>[np.float64(499.1948158477981), np.float64(-300.40245549621073)]</t>
+  </si>
+  <si>
+    <t>[np.float64(176.52073111023537), np.float64(525.180881307914)]</t>
+  </si>
+  <si>
+    <t>[np.float64(263.48455435055916), np.float64(561.4840445350203)]</t>
+  </si>
+  <si>
+    <t>[np.float64(847.8246952024252), np.float64(213.07980665842354)]</t>
+  </si>
+  <si>
+    <t>[np.float64(159.44490854309723), np.float64(67.78334449025851)]</t>
+  </si>
+  <si>
+    <t>[np.float64(393.8929324698763), np.float64(85.8034959659401)]</t>
+  </si>
+  <si>
+    <t>[np.float64(128.16209229545473), np.float64(455.7705711642409)]</t>
+  </si>
+  <si>
+    <t>[np.float64(459.9213568068841), np.float64(-536.1010484693802)]</t>
+  </si>
+  <si>
+    <t>[np.float64(534.817040606112), np.float64(378.71438340372504)]</t>
+  </si>
+  <si>
+    <t>[np.float64(637.5543197688964), np.float64(494.2539427749157)]</t>
+  </si>
+  <si>
+    <t>[np.float64(741.5835815471889), np.float64(185.83307252907173)]</t>
+  </si>
+  <si>
+    <t>[np.float64(463.34101937252956), np.float64(103.78132971270747)]</t>
+  </si>
+  <si>
+    <t>[np.float64(344.9887578899872), np.float64(26.368605659834202)]</t>
+  </si>
+  <si>
+    <t>[np.float64(623.1991873475075), np.float64(427.3664649978132)]</t>
+  </si>
+  <si>
+    <t>[np.float64(35.17258535440892), np.float64(-281.8340459090761)]</t>
+  </si>
+  <si>
+    <t>[np.float64(320.018851422579), np.float64(-232.0770957934028)]</t>
+  </si>
+  <si>
+    <t>[np.float64(191.56917135289785), np.float64(-235.79923488718515)]</t>
+  </si>
+  <si>
+    <t>[np.float64(658.1737909997327), np.float64(-469.8736493148342)]</t>
+  </si>
+  <si>
+    <t>[np.float64(278.94609939333156), np.float64(593.8894273694705)]</t>
+  </si>
+  <si>
+    <t>[np.float64(81.43929456649201), np.float64(8.084031153044293)]</t>
+  </si>
+  <si>
+    <t>[np.float64(71.3293686762555), np.float64(-263.1214727321299)]</t>
+  </si>
+  <si>
+    <t>[np.float64(638.505717228613), np.float64(168.67706600655333)]</t>
+  </si>
+  <si>
+    <t>[np.float64(486.89113536195026), np.float64(-377.6973629336061)]</t>
+  </si>
+  <si>
+    <t>[np.float64(411.54388153724517), np.float64(-313.38066150160853)]</t>
+  </si>
+  <si>
+    <t>[np.float64(68.08457745250018), np.float64(546.5884728008568)]</t>
+  </si>
+  <si>
+    <t>[np.float64(485.8340103431789), np.float64(-161.13455651568694)]</t>
+  </si>
+  <si>
+    <t>[np.float64(336.09173828823646), np.float64(123.82849036783796)]</t>
+  </si>
+  <si>
+    <t>[np.float64(605.4459617974857), np.float64(-330.1881049064644)]</t>
+  </si>
+  <si>
+    <t>[np.float64(196.53306936876402), np.float64(108.01891207139658)]</t>
+  </si>
+  <si>
+    <t>[np.float64(107.98407547213262), np.float64(75.7745506142411)]</t>
+  </si>
+  <si>
+    <t>[np.float64(74.95558497593558), np.float64(262.79030198874693)]</t>
+  </si>
+  <si>
+    <t>[np.float64(621.4801725401237), np.float64(109.13941908062475)]</t>
+  </si>
+  <si>
+    <t>[np.float64(938.5939631573077), np.float64(429.85877589067854)]</t>
+  </si>
+  <si>
+    <t>[np.float64(522.1931879399953), np.float64(523.6876896625031)]</t>
+  </si>
+  <si>
+    <t>[np.float64(306.70589535320113), np.float64(434.3728979733114)]</t>
+  </si>
+  <si>
+    <t>[np.float64(44.19834851096782), np.float64(-280.6190877860607)]</t>
+  </si>
+  <si>
+    <t>[np.float64(288.8051838121064), np.float64(46.84814941713546)]</t>
+  </si>
+  <si>
+    <t>[np.float64(869.9728283209193), np.float64(-156.450950405115)]</t>
+  </si>
+  <si>
+    <t>[np.float64(805.9977390302374), np.float64(-145.9916936271133)]</t>
+  </si>
+  <si>
+    <t>[np.float64(483.6415010437051), np.float64(-151.8139191661162)]</t>
+  </si>
+  <si>
+    <t>[np.float64(20.890385097434017), np.float64(596.6300732353213)]</t>
+  </si>
+  <si>
+    <t>[np.float64(407.08628659267174), np.float64(312.03393493936596)]</t>
+  </si>
+  <si>
+    <t>[np.float64(983.5606167647999), np.float64(302.9794706047354)]</t>
+  </si>
+  <si>
+    <t>[np.float64(704.1750982876142), np.float64(333.3054510077088)]</t>
+  </si>
+  <si>
+    <t>[np.float64(818.8224896486895), np.float64(569.7425308359466)]</t>
+  </si>
+  <si>
+    <t>[np.float64(780.5529962962039), np.float64(-507.98527989113086)]</t>
+  </si>
+  <si>
+    <t>[np.float64(440.03357293201526), np.float64(-336.80757676412736)]</t>
+  </si>
+  <si>
+    <t>[np.float64(654.5206174900544), np.float64(330.9362314661014)]</t>
+  </si>
+  <si>
+    <t>[np.float64(914.1499356775331), np.float64(-492.6821322917193)]</t>
+  </si>
+  <si>
+    <t>[np.float64(413.02961108791646), np.float64(-401.1066964369137)]</t>
+  </si>
+  <si>
+    <t>[np.float64(176.64028284660594), np.float64(-66.99745776214343)]</t>
+  </si>
+  <si>
+    <t>[np.float64(933.2506092972014), np.float64(390.67071795893)]</t>
+  </si>
+  <si>
+    <t>[np.float64(157.70273232954136), np.float64(-573.5264725656389)]</t>
+  </si>
+  <si>
+    <t>[np.float64(525.2909240058608), np.float64(593.3653739455647)]</t>
+  </si>
+  <si>
+    <t>[np.float64(255.77676073432198), np.float64(-254.41463428400868)]</t>
+  </si>
+  <si>
+    <t>[np.float64(226.766938641782), np.float64(75.11478926258053)]</t>
+  </si>
+  <si>
+    <t>[np.float64(814.8124512404703), np.float64(-80.76317549743726)]</t>
+  </si>
+  <si>
+    <t>[np.float64(960.4834497659856), np.float64(-317.89563469207076)]</t>
+  </si>
+  <si>
+    <t>[np.float64(497.99591221349004), np.float64(-131.06366275103085)]</t>
+  </si>
+  <si>
+    <t>[np.float64(516.2191970749403), np.float64(-524.3368032918506)]</t>
+  </si>
+  <si>
+    <t>[np.float64(953.1703749784592), np.float64(511.2470871743287)]</t>
+  </si>
+  <si>
+    <t>[np.float64(168.20133481916), np.float64(-595.6484523507154)]</t>
+  </si>
+  <si>
+    <t>[np.float64(168.550011656588), np.float64(-163.7494074283676)]</t>
+  </si>
+  <si>
+    <t>[np.float64(78.58976913541859), np.float64(569.2969586259749)]</t>
+  </si>
+  <si>
+    <t>[np.float64(435.9875195725036), np.float64(-510.046775966171)]</t>
+  </si>
+  <si>
+    <t>[np.float64(347.0087687269852), np.float64(47.43857866463827)]</t>
+  </si>
+  <si>
+    <t>[np.float64(189.9129048863376), np.float64(-220.1521804525823)]</t>
+  </si>
+  <si>
+    <t>[np.float64(275.8936606086547), np.float64(-347.65762527071604)]</t>
+  </si>
+  <si>
+    <t>[np.float64(480.01666341209483), np.float64(239.5526906631436)]</t>
+  </si>
+  <si>
+    <t>[np.float64(329.0349790367555), np.float64(184.06366099355228)]</t>
+  </si>
+  <si>
+    <t>[np.float64(297.05692365948477), np.float64(167.80729176680904)]</t>
+  </si>
+  <si>
+    <t>[np.float64(919.4702474891146), np.float64(-570.7506539248163)]</t>
+  </si>
+  <si>
+    <t>[np.float64(677.8103367795472), np.float64(457.9750812001996)]</t>
+  </si>
+  <si>
+    <t>[np.float64(921.2274445401024), np.float64(-286.8411754886549)]</t>
+  </si>
+  <si>
+    <t>[np.float64(483.8615772349516), np.float64(87.585895224002)]</t>
+  </si>
+  <si>
+    <t>[np.float64(177.93684573430235), np.float64(33.183309731811505)]</t>
+  </si>
+  <si>
+    <t>[np.float64(859.0075216722738), np.float64(-455.42582793510667)]</t>
+  </si>
+  <si>
+    <t>[np.float64(639.4046050597946), np.float64(-333.674002722325)]</t>
+  </si>
+  <si>
+    <t>[np.float64(122.73236298906498), np.float64(575.9178587860738)]</t>
+  </si>
+  <si>
+    <t>[np.float64(392.0133083946167), np.float64(182.6578498967442)]</t>
+  </si>
+  <si>
+    <t>[np.float64(780.8269806979911), np.float64(107.52891166302129)]</t>
+  </si>
+  <si>
+    <t>[np.float64(401.2841842038881), np.float64(280.856842323676)]</t>
+  </si>
+  <si>
+    <t>[np.float64(402.99012681738475), np.float64(586.2787273910715)]</t>
+  </si>
+  <si>
+    <t>[np.float64(596.1399843510974), np.float64(109.3263674033924)]</t>
+  </si>
+  <si>
+    <t>[np.float64(516.4200969797118), np.float64(-151.94652945019538)]</t>
+  </si>
+  <si>
+    <t>[np.float64(238.40311545615322), np.float64(180.44027206941257)]</t>
+  </si>
+  <si>
+    <t>[np.float64(127.31589419842749), np.float64(-229.33534069796917)]</t>
+  </si>
+  <si>
+    <t>[np.float64(612.2978432525597), np.float64(-501.4355184267397)]</t>
+  </si>
+  <si>
+    <t>[np.float64(820.5586123410245), np.float64(-252.05504853940522)]</t>
+  </si>
+  <si>
+    <t>[np.float64(696.4922172850896), np.float64(-582.3784254676378)]</t>
+  </si>
+  <si>
+    <t>[np.float64(188.26713366128612), np.float64(489.6840195359416)]</t>
+  </si>
+  <si>
+    <t>[np.float64(722.2237120802707), np.float64(593.2536383117706)]</t>
+  </si>
+  <si>
+    <t>[np.float64(830.2634093998382), np.float64(-251.24529107108066)]</t>
+  </si>
+  <si>
+    <t>[np.float64(351.83807505928576), np.float64(0.606545904747918)]</t>
+  </si>
+  <si>
+    <t>[np.float64(68.8050821679399), np.float64(-306.403327209866)]</t>
+  </si>
+  <si>
+    <t>[np.float64(843.8399839212835), np.float64(-472.44181131753226)]</t>
+  </si>
+  <si>
+    <t>[np.float64(297.4374242121571), np.float64(536.6330369783298)]</t>
+  </si>
+  <si>
+    <t>[np.float64(620.3608511277636), np.float64(50.691655923245094)]</t>
+  </si>
+  <si>
+    <t>[np.float64(967.5271223446704), np.float64(-582.9987985708142)]</t>
+  </si>
+  <si>
+    <t>[np.float64(169.37995415018935), np.float64(-378.9022315267275)]</t>
+  </si>
+  <si>
+    <t>[np.float64(309.15386985740867), np.float64(-321.1295109297405)]</t>
+  </si>
+  <si>
+    <t>[np.float64(345.0268129585999), np.float64(-413.74955083846504)]</t>
+  </si>
+  <si>
+    <t>[np.float64(252.7058189469007), np.float64(233.22823338918784)]</t>
+  </si>
+  <si>
+    <t>[np.float64(890.4545020692657), np.float64(1.6858971810707999)]</t>
+  </si>
+  <si>
+    <t>[np.float64(462.763240243409), np.float64(-429.25683849666837)]</t>
+  </si>
+  <si>
+    <t>[np.float64(819.0261534937896), np.float64(568.0023138794052)]</t>
+  </si>
+  <si>
+    <t>[np.float64(344.3085888433537), np.float64(-526.5906940116208)]</t>
+  </si>
+  <si>
+    <t>[np.float64(860.6699439951049), np.float64(228.14377861038224)]</t>
+  </si>
+  <si>
+    <t>[np.float64(222.68297074523136), np.float64(358.6496464704136)]</t>
+  </si>
+  <si>
+    <t>[np.float64(183.64451068280317), np.float64(206.69552367889605)]</t>
+  </si>
+  <si>
+    <t>[np.float64(558.6393291788529), np.float64(172.14920937596753)]</t>
+  </si>
+  <si>
+    <t>[np.float64(237.96006939193114), np.float64(51.00530076510552)]</t>
+  </si>
+  <si>
+    <t>[np.float64(469.08198140857627), np.float64(-506.1443042796966)]</t>
+  </si>
+  <si>
+    <t>[np.float64(519.8481713073672), np.float64(-416.07378827949447)]</t>
+  </si>
+  <si>
+    <t>[np.float64(863.7326927364801), np.float64(-69.42444762466823)]</t>
+  </si>
+  <si>
+    <t>[np.float64(675.3105717512753), np.float64(-86.8857516659308)]</t>
+  </si>
+  <si>
+    <t>[np.float64(412.17375514051815), np.float64(-418.83167517335755)]</t>
+  </si>
+  <si>
+    <t>[np.float64(306.48193650264153), np.float64(-278.7605342030716)]</t>
+  </si>
+  <si>
+    <t>[np.float64(664.1518961537192), np.float64(-444.78109465568787)]</t>
+  </si>
+  <si>
+    <t>[np.float64(639.1220077714306), np.float64(250.31227787744206)]</t>
+  </si>
+  <si>
+    <t>[np.float64(779.410565047926), np.float64(370.9662998582136)]</t>
+  </si>
+  <si>
+    <t>[np.float64(780.9785725585405), np.float64(324.68927264660806)]</t>
+  </si>
+  <si>
+    <t>[np.float64(433.0999977799133), np.float64(320.39097603695427)]</t>
+  </si>
+  <si>
+    <t>[np.float64(284.80365201710254), np.float64(-232.9776739075238)]</t>
+  </si>
+  <si>
+    <t>[np.float64(880.9393933316909), np.float64(-318.54864136116043)]</t>
+  </si>
+  <si>
+    <t>[np.float64(228.0590379338302), np.float64(113.54548154999804)]</t>
+  </si>
+  <si>
+    <t>[np.float64(622.3848711260958), np.float64(5.895487327162527)]</t>
+  </si>
+  <si>
+    <t>[np.float64(901.3693865489977), np.float64(-273.4430604132976)]</t>
+  </si>
+  <si>
+    <t>[np.float64(36.223635196497185), np.float64(162.8784918882202)]</t>
+  </si>
+  <si>
+    <t>[np.float64(876.0368937878516), np.float64(190.5893390216322)]</t>
+  </si>
+  <si>
+    <t>[np.float64(514.7650023556275), np.float64(-436.99010881374113)]</t>
+  </si>
+  <si>
+    <t>[np.float64(721.861476254273), np.float64(-212.1948405004934)]</t>
+  </si>
+  <si>
+    <t>[np.float64(511.0168581664587), np.float64(116.69338544031643)]</t>
+  </si>
+  <si>
+    <t>[np.float64(722.3261793273829), np.float64(-195.19670234557947)]</t>
+  </si>
+  <si>
+    <t>[np.float64(104.27186093241447), np.float64(-509.2437330227152)]</t>
+  </si>
+  <si>
+    <t>[np.float64(82.63194346126713), np.float64(126.96942143887009)]</t>
+  </si>
+  <si>
+    <t>[np.float64(258.9190344233042), np.float64(-190.16677597925968)]</t>
+  </si>
+  <si>
+    <t>[np.float64(873.4827294349964), np.float64(265.46242367861726)]</t>
+  </si>
+  <si>
+    <t>[np.float64(709.318330889292), np.float64(-282.6218471059067)]</t>
+  </si>
+  <si>
+    <t>[np.float64(732.4044829093799), np.float64(-462.98692981984226)]</t>
+  </si>
+  <si>
+    <t>[np.float64(9.993155290450307), np.float64(-592.6041941856492)]</t>
+  </si>
+  <si>
+    <t>[np.float64(63.01561703758662), np.float64(131.96403251052652)]</t>
+  </si>
+  <si>
+    <t>[np.float64(700.4864569879178), np.float64(594.9351290323459)]</t>
+  </si>
+  <si>
+    <t>[np.float64(246.63554084688056), np.float64(160.42536693408658)]</t>
+  </si>
+  <si>
+    <t>[np.float64(844.9963463946776), np.float64(21.211671126723218)]</t>
+  </si>
+  <si>
+    <t>[np.float64(556.3253531531784), np.float64(234.98234729193973)]</t>
+  </si>
+  <si>
+    <t>[np.float64(33.94186149233425), np.float64(172.23200098537723)]</t>
+  </si>
+  <si>
+    <t>[np.float64(798.6584638242717), np.float64(-557.2398162416262)]</t>
+  </si>
+  <si>
+    <t>[np.float64(186.66893107553173), np.float64(530.074901481496)]</t>
+  </si>
+  <si>
+    <t>[np.float64(624.2519164211017), np.float64(515.5236237275642)]</t>
+  </si>
+  <si>
+    <t>[np.float64(232.7205013760212), np.float64(-259.1142740690676)]</t>
+  </si>
+  <si>
+    <t>[np.float64(382.71066982857604), np.float64(158.47340010001244)]</t>
+  </si>
+  <si>
+    <t>[np.float64(771.7181587208853), np.float64(572.0237279513105)]</t>
+  </si>
+  <si>
+    <t>[np.float64(875.0287013800702), np.float64(-305.63412885876204)]</t>
+  </si>
+  <si>
+    <t>[np.float64(633.3833822834212), np.float64(64.7334785673005)]</t>
+  </si>
+  <si>
+    <t>[np.float64(720.1442357934915), np.float64(-105.94273308678322)]</t>
+  </si>
+  <si>
+    <t>[np.float64(426.7732224390918), np.float64(287.11843717823444)]</t>
+  </si>
+  <si>
+    <t>[np.float64(999.5475540226506), np.float64(-362.80985757967414)]</t>
+  </si>
+  <si>
+    <t>[np.float64(735.9415339132597), np.float64(308.1129822828633)]</t>
+  </si>
+  <si>
+    <t>[np.float64(937.333310173101), np.float64(-58.890314602117314)]</t>
+  </si>
+  <si>
+    <t>[np.float64(49.302892384556095), np.float64(104.39251688616082)]</t>
+  </si>
+  <si>
+    <t>[np.float64(466.0767199925079), np.float64(508.75842972217197)]</t>
+  </si>
+  <si>
+    <t>[np.float64(677.6330943672897), np.float64(223.60613457503746)]</t>
+  </si>
+  <si>
+    <t>[np.float64(600.7822020713463), np.float64(395.59151037162053)]</t>
+  </si>
+  <si>
+    <t>[np.float64(121.10535738950378), np.float64(375.167444782507)]</t>
+  </si>
+  <si>
+    <t>[np.float64(528.1994496415891), np.float64(360.6970199986141)]</t>
+  </si>
+  <si>
+    <t>[np.float64(231.46429652642487), np.float64(137.93872692193702)]</t>
+  </si>
+  <si>
+    <t>[np.float64(817.554512545945), np.float64(246.70239283435535)]</t>
+  </si>
+  <si>
+    <t>[np.float64(556.0246049263734), np.float64(-345.06549718311896)]</t>
+  </si>
+  <si>
+    <t>[np.float64(913.3354152661884), np.float64(392.7430603971436)]</t>
+  </si>
+  <si>
+    <t>[np.float64(96.44490764413305), np.float64(-39.05678794571497)]</t>
+  </si>
+  <si>
+    <t>[np.float64(65.1855686378774), np.float64(371.49369207978077)]</t>
+  </si>
+  <si>
+    <t>[np.float64(456.9981698981115), np.float64(8.092690256223136)]</t>
+  </si>
+  <si>
+    <t>[np.float64(469.04838876967125), np.float64(73.80067119199305)]</t>
+  </si>
+  <si>
+    <t>[np.float64(269.6188438808521), np.float64(69.80813210260771)]</t>
+  </si>
+  <si>
+    <t>[np.float64(395.58045247817506), np.float64(325.2958417951337)]</t>
+  </si>
+  <si>
+    <t>[np.float64(245.95293282080212), np.float64(-71.57337079499735)]</t>
+  </si>
+  <si>
+    <t>[np.float64(485.77621426662733), np.float64(-330.23449890944903)]</t>
+  </si>
+  <si>
+    <t>[np.float64(541.2552574160487), np.float64(220.96581458368144)]</t>
+  </si>
+  <si>
+    <t>[np.float64(500.9703248588817), np.float64(26.02075354518911)]</t>
+  </si>
+  <si>
+    <t>[np.float64(999.7656884413103), np.float64(321.39693670943313)]</t>
+  </si>
+  <si>
+    <t>[np.float64(562.997461540282), np.float64(-164.58524687529717)]</t>
+  </si>
+  <si>
+    <t>[np.float64(893.759281691743), np.float64(-255.16790776430872)]</t>
+  </si>
+  <si>
+    <t>[np.float64(139.97144672908223), np.float64(-594.030933068855)]</t>
+  </si>
+  <si>
+    <t>[np.float64(560.5138914333291), np.float64(219.331442515616)]</t>
+  </si>
+  <si>
+    <t>[np.float64(799.409192456889), np.float64(-192.71943706546858)]</t>
+  </si>
+  <si>
+    <t>[np.float64(643.7582182470327), np.float64(-161.7362460274776)]</t>
+  </si>
+  <si>
+    <t>[np.float64(599.3858349587682), np.float64(-331.4783974812912)]</t>
+  </si>
+  <si>
+    <t>[np.float64(131.06567520510092), np.float64(460.34779747267976)]</t>
+  </si>
+  <si>
+    <t>[np.float64(547.2128615122363), np.float64(-248.9962863333132)]</t>
+  </si>
+  <si>
+    <t>[np.float64(52.15009948205596), np.float64(160.41004469518407)]</t>
+  </si>
+  <si>
+    <t>[np.float64(123.53087885622737), np.float64(432.84040614445644)]</t>
+  </si>
+  <si>
+    <t>[np.float64(496.4959440704739), np.float64(416.93985432371903)]</t>
+  </si>
+  <si>
+    <t>[np.float64(782.0705316874927), np.float64(-119.16712697475668)]</t>
+  </si>
+  <si>
+    <t>[np.float64(226.63162163364748), np.float64(-479.1386522587647)]</t>
+  </si>
+  <si>
+    <t>[np.float64(453.2597104074543), np.float64(-103.7488262008934)]</t>
+  </si>
+  <si>
+    <t>[np.float64(895.9830251112143), np.float64(215.90251088081186)]</t>
+  </si>
+  <si>
+    <t>[np.float64(912.5472951174752), np.float64(408.58590736890517)]</t>
+  </si>
+  <si>
+    <t>[np.float64(822.1353033452035), np.float64(-318.2041855539105)]</t>
+  </si>
+  <si>
+    <t>[np.float64(612.2329994506854), np.float64(-203.33370959393278)]</t>
+  </si>
+  <si>
+    <t>[np.float64(592.9285745564359), np.float64(405.30344291062477)]</t>
+  </si>
+  <si>
+    <t>[np.float64(667.4716440065923), np.float64(-430.8806175573744)]</t>
+  </si>
+  <si>
+    <t>[np.float64(585.7676770571438), np.float64(278.0845766766156)]</t>
+  </si>
+  <si>
+    <t>[np.float64(328.083630931556), np.float64(-238.3288249534407)]</t>
+  </si>
+  <si>
+    <t>[np.float64(809.8440998905787), np.float64(118.72419374025503)]</t>
+  </si>
+  <si>
+    <t>[np.float64(28.765996951726102), np.float64(103.99168530611007)]</t>
+  </si>
+  <si>
+    <t>[np.float64(762.3185858085335), np.float64(56.4309003060564)]</t>
+  </si>
+  <si>
+    <t>[np.float64(342.782955756847), np.float64(-79.57672183275076)]</t>
+  </si>
+  <si>
+    <t>[np.float64(112.08988697015032), np.float64(-547.4579777177618)]</t>
+  </si>
+  <si>
+    <t>[np.float64(902.68947089481), np.float64(159.38100226541837)]</t>
+  </si>
+  <si>
+    <t>[np.float64(94.94224832799813), np.float64(-583.384891077499)]</t>
+  </si>
+  <si>
+    <t>[np.float64(552.8849757292268), np.float64(137.88551675264512)]</t>
+  </si>
+  <si>
+    <t>[np.float64(387.64684088364186), np.float64(513.6878048260744)]</t>
+  </si>
+  <si>
+    <t>[np.float64(857.821874160396), np.float64(302.927300455013)]</t>
+  </si>
+  <si>
+    <t>[np.float64(727.5595073984733), np.float64(239.42734707631269)]</t>
+  </si>
+  <si>
+    <t>[np.float64(269.0500900246026), np.float64(-251.69030159198013)]</t>
+  </si>
+  <si>
+    <t>[np.float64(256.4788651031494), np.float64(-135.03301304144088)]</t>
+  </si>
+  <si>
+    <t>[np.float64(59.33979984491777), np.float64(389.8072538417732)]</t>
+  </si>
+  <si>
+    <t>[np.float64(749.0107922202734), np.float64(90.46556020388641)]</t>
+  </si>
+  <si>
+    <t>[np.float64(665.9388211037126), np.float64(-271.6355684515977)]</t>
+  </si>
+  <si>
+    <t>[np.float64(665.4390032895176), np.float64(-157.3414722607592)]</t>
+  </si>
+  <si>
+    <t>[np.float64(103.33690081580593), np.float64(299.13352540156507)]</t>
+  </si>
+  <si>
+    <t>[np.float64(393.65192622708736), np.float64(102.50682711399577)]</t>
+  </si>
+  <si>
+    <t>[np.float64(732.1326770564497), np.float64(-88.90336695442306)]</t>
+  </si>
+  <si>
+    <t>[np.float64(303.9258444265762), np.float64(119.63722065806246)]</t>
+  </si>
+  <si>
+    <t>[np.float64(786.0760484216445), np.float64(-169.86344872020254)]</t>
+  </si>
+  <si>
+    <t>[np.float64(484.79989889066286), np.float64(456.7871983363143)]</t>
+  </si>
+  <si>
+    <t>[np.float64(283.204020725945), np.float64(-279.5947004605871)]</t>
+  </si>
+  <si>
+    <t>[np.float64(206.83183416538898), np.float64(233.6831123393057)]</t>
+  </si>
+  <si>
+    <t>[np.float64(129.74037206922563), np.float64(170.71138881492948)]</t>
+  </si>
+  <si>
+    <t>[np.float64(850.2719621521064), np.float64(-424.67333923375156)]</t>
+  </si>
+  <si>
+    <t>[np.float64(918.8747445735413), np.float64(358.67174990689875)]</t>
+  </si>
+  <si>
+    <t>[np.float64(497.8519894924104), np.float64(-511.3523042792927)]</t>
+  </si>
+  <si>
+    <t>[np.float64(984.3527628211485), np.float64(-488.6110399287527)]</t>
+  </si>
+  <si>
+    <t>[np.float64(389.0629355194005), np.float64(-194.75443887333267)]</t>
+  </si>
+  <si>
+    <t>[np.float64(932.7292795505972), np.float64(-277.31195632335056)]</t>
+  </si>
+  <si>
+    <t>[np.float64(960.4357175997543), np.float64(-82.69876304778745)]</t>
+  </si>
+  <si>
+    <t>[np.float64(625.8725974215329), np.float64(-227.21699424428704)]</t>
+  </si>
+  <si>
+    <t>[np.float64(786.8100006665181), np.float64(547.4538217363092)]</t>
+  </si>
+  <si>
+    <t>[np.float64(382.2889944626518), np.float64(-317.7803219041451)]</t>
+  </si>
+  <si>
+    <t>[np.float64(25.72921777541137), np.float64(-151.25715246700247)]</t>
+  </si>
+  <si>
+    <t>[np.float64(643.2686896679818), np.float64(-293.137957564297)]</t>
+  </si>
+  <si>
+    <t>[np.float64(926.9864130241793), np.float64(-512.4559779540913)]</t>
+  </si>
+  <si>
+    <t>[np.float64(270.5663885704127), np.float64(530.2682471651649)]</t>
+  </si>
+  <si>
+    <t>[np.float64(311.1105124825533), np.float64(152.15455940662594)]</t>
+  </si>
+  <si>
+    <t>[np.float64(944.3678625446844), np.float64(36.528392985713026)]</t>
+  </si>
+  <si>
+    <t>[np.float64(891.7110971224184), np.float64(446.8733296127905)]</t>
+  </si>
+  <si>
+    <t>[np.float64(453.9038204349157), np.float64(-363.287175744398)]</t>
+  </si>
+  <si>
+    <t>[np.float64(855.5485569312931), np.float64(133.4274366253983)]</t>
+  </si>
+  <si>
+    <t>[np.float64(754.0062466497873), np.float64(-291.7852899171876)]</t>
+  </si>
+  <si>
+    <t>[np.float64(357.3661734809279), np.float64(-520.3941924200934)]</t>
+  </si>
+  <si>
+    <t>[np.float64(535.0510990767804), np.float64(-152.61088134358232)]</t>
+  </si>
+  <si>
+    <t>[np.float64(671.5166076015179), np.float64(108.19054791295923)]</t>
+  </si>
+  <si>
+    <t>[np.float64(304.3925423878375), np.float64(-483.6590500380834)]</t>
+  </si>
+  <si>
+    <t>[np.float64(68.17206105886552), np.float64(-258.6290788649344)]</t>
+  </si>
+  <si>
+    <t>[np.float64(214.2286881919624), np.float64(-220.97679855300265)]</t>
+  </si>
+  <si>
+    <t>[np.float64(334.8078708261999), np.float64(516.0893559394672)]</t>
+  </si>
+  <si>
+    <t>[np.float64(8.395271272188642), np.float64(578.1250071736458)]</t>
+  </si>
+  <si>
+    <t>[np.float64(53.323850700667585), np.float64(-358.74178375307247)]</t>
+  </si>
+  <si>
+    <t>[np.float64(940.1398386756241), np.float64(295.1506501734681)]</t>
+  </si>
+  <si>
+    <t>[np.float64(834.1556047498626), np.float64(-257.72587143554097)]</t>
+  </si>
+  <si>
+    <t>[np.float64(970.1567534908557), np.float64(-275.8471807661121)]</t>
+  </si>
+  <si>
+    <t>[np.float64(346.32955665281764), np.float64(-491.6641601348761)]</t>
+  </si>
+  <si>
+    <t>[np.float64(842.9375485377813), np.float64(383.31248516046355)]</t>
+  </si>
+  <si>
+    <t>[np.float64(467.4425509700868), np.float64(-494.6146478543708)]</t>
+  </si>
+  <si>
+    <t>[np.float64(238.3150861264751), np.float64(539.4003230761891)]</t>
+  </si>
+  <si>
+    <t>[np.float64(605.4509099108064), np.float64(-164.94890789874017)]</t>
+  </si>
+  <si>
+    <t>[np.float64(827.4311551362554), np.float64(-54.91777284089676)]</t>
+  </si>
+  <si>
+    <t>[np.float64(14.390728458438362), np.float64(305.1371867262435)]</t>
+  </si>
+  <si>
+    <t>[np.float64(612.2099066425451), np.float64(191.24309540893387)]</t>
+  </si>
+  <si>
+    <t>[np.float64(987.5765779566269), np.float64(548.4557214063914)]</t>
+  </si>
+  <si>
+    <t>[np.float64(853.8794295464805), np.float64(253.54609236910164)]</t>
+  </si>
+  <si>
+    <t>[np.float64(142.29074917029638), np.float64(312.5516839662969)]</t>
   </si>
 </sst>
 </file>
